--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -520,7 +520,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PRABHA</t>
+          <t>Prabha Energy Limited</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -554,7 +554,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
+          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - tradebrains.in</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -564,19 +564,15 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N K Industries Ltd leads gainers in 'B' group - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
-        </is>
-      </c>
+          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - tradebrains.in</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -589,7 +585,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SUBEXLTD</t>
+          <t>Subex Limited</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -618,22 +614,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Subex Ltd. Share Price Gain: Price Action and Valuation - Univest</t>
+          <t>Subex Ltd hosts non-deal analyst roadshow in Mumbai on August 19 - scanx.trade</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Subex Ltd. Share Price Gain: Price Action and Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>Subex Ltd hosts non-deal analyst roadshow in Mumbai on August 19 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Subex seeks shareholder nod for new ESOP scheme, trust loan - scanx.trade</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AARNAV</t>
+          <t>Aarnav Fashions Limited</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -673,16 +673,8 @@
       <c r="L4" t="n">
         <v>13.26</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
@@ -690,7 +682,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -703,7 +695,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>YASHO</t>
+          <t>Yasho Industries Limited</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -730,28 +722,16 @@
       <c r="L5" t="n">
         <v>12.69</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Yasho Industries Ltd Hits All-Time High of Rs 4640.95 as Momentum Builds Across Timeframes - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Yasho Industries Ltd Hits All-Time High of Rs 4640.95 as Momentum Builds Across Timeframes - MarketsMojo</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -759,60 +739,68 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MACPOWER.NS</t>
+          <t>ICIL.NS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MACPOWER</t>
+          <t>Indo Count Industries Limited</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1782.5</v>
+        <v>388.7000122070312</v>
       </c>
       <c r="F6" t="n">
-        <v>2000</v>
+        <v>462</v>
       </c>
       <c r="G6" t="n">
-        <v>1782.5</v>
+        <v>387.0499877929688</v>
       </c>
       <c r="H6" t="n">
-        <v>1983.599975585938</v>
+        <v>437.7000122070312</v>
       </c>
       <c r="I6" t="n">
-        <v>1781.400024414062</v>
+        <v>388.7000122070312</v>
       </c>
       <c r="J6" t="n">
-        <v>1983.599975585938</v>
+        <v>437.7000122070312</v>
       </c>
       <c r="K6" t="n">
-        <v>190615</v>
+        <v>25217469</v>
       </c>
       <c r="L6" t="n">
-        <v>11.35</v>
+        <v>12.61</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Ltd. Share Price Rises 8.64% Today - Univest</t>
+          <t>Indo Count Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Ltd. Share Price Rises 8.64% Today - Univest</t>
+          <t>Indo Count Industries Q1 Results: Audio of investor call uploaded - scanx.trade</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Ltd. Share Price News and Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+          <t>Indo Count Industries Q1 Results: Audio of investor call uploaded - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Indo Count Industries appoints Pankaj Saxena as President-Retail - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Indo Count reports record Q1FY27 revenue of ₹1,224 crore - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -820,51 +808,51 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INDSWFTLAB.NS</t>
+          <t>SIGACHI.NS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>Sigachi Industries Limited</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>317.9500122070312</v>
+        <v>25.90999984741211</v>
       </c>
       <c r="F7" t="n">
-        <v>351.2999877929688</v>
+        <v>30.09000015258789</v>
       </c>
       <c r="G7" t="n">
-        <v>316.8999938964844</v>
+        <v>25.90999984741211</v>
       </c>
       <c r="H7" t="n">
-        <v>346.8699951171875</v>
+        <v>29.61000061035156</v>
       </c>
       <c r="I7" t="n">
-        <v>313.0199890136719</v>
+        <v>26.35000038146973</v>
       </c>
       <c r="J7" t="n">
-        <v>346.8699951171875</v>
+        <v>29.61000061035156</v>
       </c>
       <c r="K7" t="n">
-        <v>5070304</v>
+        <v>10330178</v>
       </c>
       <c r="L7" t="n">
-        <v>10.81</v>
+        <v>12.37</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - Univest</t>
+          <t>Sigachi Industries Q1 Results: Net profit turns positive to ₹814 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - Univest</t>
+          <t>Sigachi Industries Q1 Results: Net profit turns positive to ₹814 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Ind-Swift Laboratories Sets Q1 FY27 Earnings Call for August 17 - TipRanks</t>
+          <t>Sigachi Industries Q1 Results: Net profit rebounds to ₹8.14 crore - scanx.trade</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -873,7 +861,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -881,64 +869,56 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>REGAAL.NS</t>
+          <t>MACPOWER.NS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>REGAAL</t>
+          <t>Macpower CNC Machines Limited</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>90.27999877929688</v>
+        <v>1782.5</v>
       </c>
       <c r="F8" t="n">
-        <v>101.5</v>
+        <v>2000</v>
       </c>
       <c r="G8" t="n">
-        <v>88.65000152587891</v>
+        <v>1782.5</v>
       </c>
       <c r="H8" t="n">
-        <v>99.52999877929688</v>
+        <v>1983.599975585938</v>
       </c>
       <c r="I8" t="n">
-        <v>90.45999908447266</v>
+        <v>1781.400024414062</v>
       </c>
       <c r="J8" t="n">
-        <v>99.52999877929688</v>
+        <v>1983.599975585938</v>
       </c>
       <c r="K8" t="n">
-        <v>2972532</v>
+        <v>190615</v>
       </c>
       <c r="L8" t="n">
-        <v>10.03</v>
+        <v>11.35</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest</t>
+          <t>The National Stock Exchange has sought clarification on unusual price fluctuations in several stocks. - Traders Union</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Regaal Resources Q1 Results: Earnings call audio uploaded for investors - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Regaal Resources Ltd Surges 17% to Hit Upper Circuit Amid Robust Buying Pressure - MarketsMojo</t>
-        </is>
-      </c>
+          <t>The National Stock Exchange has sought clarification on unusual price fluctuations in several stocks. - Traders Union</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -946,68 +926,56 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PARAS.NS</t>
+          <t>JINDRILL.NS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>Jindal Drilling &amp; Industries Limited</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1385</v>
+        <v>587.0999755859375</v>
       </c>
       <c r="F9" t="n">
-        <v>1527.300048828125</v>
+        <v>673.5499877929688</v>
       </c>
       <c r="G9" t="n">
-        <v>1384.699951171875</v>
+        <v>587.0999755859375</v>
       </c>
       <c r="H9" t="n">
-        <v>1527.300048828125</v>
+        <v>651.1500244140625</v>
       </c>
       <c r="I9" t="n">
-        <v>1388.5</v>
+        <v>586.2000122070312</v>
       </c>
       <c r="J9" t="n">
-        <v>1527.300048828125</v>
+        <v>651.1500244140625</v>
       </c>
       <c r="K9" t="n">
-        <v>5405026</v>
+        <v>17885600</v>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>11.08</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Paras Defence, Zen Tech, other defence shares rise up to 8% as MoD notifies sixth Positive Indigenisation... - Moneycontrol.com</t>
+          <t>Jindal Drilling Q1 Results: New ONGC Rig Contract, Order Book At ₹1,310 Crore - scanx.trade</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Paras Defence zooms 163% from March low; hits 52-week high on huge volume - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Paras Defence Share Price at Fresh 52-Week High - Univest</t>
-        </is>
-      </c>
+          <t>Jindal Drilling Q1 Results: New ONGC Rig Contract, Order Book At ₹1,310 Crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1015,56 +983,56 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DHOOTTRANS.NS</t>
+          <t>INDSWFTLAB.NS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DHOOTTRANS</t>
+          <t>Ind-Swift Laboratories Limited</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1170</v>
+        <v>317.9500122070312</v>
       </c>
       <c r="F10" t="n">
-        <v>1305.75</v>
+        <v>351.2999877929688</v>
       </c>
       <c r="G10" t="n">
-        <v>1165</v>
+        <v>316.8999938964844</v>
       </c>
       <c r="H10" t="n">
-        <v>1305.75</v>
+        <v>346.8699951171875</v>
       </c>
       <c r="I10" t="n">
-        <v>1187.050048828125</v>
+        <v>313.0199890136719</v>
       </c>
       <c r="J10" t="n">
-        <v>1305.75</v>
+        <v>346.8699951171875</v>
       </c>
       <c r="K10" t="n">
-        <v>9337471</v>
+        <v>5070304</v>
       </c>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>10.81</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
+          <t>Ind-Swift Labs releases Q1FY27 earnings call audio recording - scanx.trade</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
+          <t>Ind-Swift Laboratories: जम्मू प्लांटमध्ये ₹45 कोटींची गुंतवणूक, जागतिक बाजारात प्रवेशाची तयारी! - Whalesbook</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Average basic shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
+          <t>Ind-Swift Laboratories: పెట్టుబడుల సమీకరణలో బ్రేక్.. ₹58.99 కోట్ల షార్ట్‌ఫాల్.. ఆందోళనలో ఇన్వెస్టర్లు? - Whalesbook</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dhoot Transmission Limited Statistics – NSE:DHOOTTRANS - TradingView</t>
+          <t>Ind-Swift Laboratories: जम्मू प्लांटमध्ये ₹45 कोटींची गुंतवणूक, जागतिक बाजारात प्रवेशाची तयारी! - Whalesbook</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1072,7 +1040,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1080,56 +1048,64 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BI.NS</t>
+          <t>ABINFRA.NS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>A B INFRABUILD LIMITED</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>94</v>
+        <v>11.32999992370605</v>
       </c>
       <c r="F11" t="n">
-        <v>101.379997253418</v>
+        <v>12.98999977111816</v>
       </c>
       <c r="G11" t="n">
-        <v>92.16999816894531</v>
+        <v>10.97999954223633</v>
       </c>
       <c r="H11" t="n">
-        <v>101.379997253418</v>
+        <v>12.56999969482422</v>
       </c>
       <c r="I11" t="n">
-        <v>92.16999816894531</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="J11" t="n">
-        <v>101.379997253418</v>
+        <v>12.56999969482422</v>
       </c>
       <c r="K11" t="n">
-        <v>523283</v>
+        <v>25170195</v>
       </c>
       <c r="L11" t="n">
-        <v>9.99</v>
+        <v>10.65</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
+          <t>A B Infrabuild Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+          <t>A B Infrabuild reports Q1 FY27 revenue of ₹7,625.1 lakh, a 25.9% increase YoY - Business Upturn</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>AB Infrabuild Q1FY27 net profit up 4.4% to ₹534.3M on revenue growth - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A B Infrabuild reports Q1 FY27 revenue of ₹7,625.1 lakh, a 25.9% increase YoY - Business Upturn</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1137,68 +1113,68 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ASIANENE.NS</t>
+          <t>REGAAL.NS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ASIANENE</t>
+          <t>REGAAL RESOURCES LIMITED</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>426.8999938964844</v>
+        <v>90.27999877929688</v>
       </c>
       <c r="F12" t="n">
-        <v>465.1000061035156</v>
+        <v>101.5</v>
       </c>
       <c r="G12" t="n">
-        <v>419.7999877929688</v>
+        <v>88.65000152587891</v>
       </c>
       <c r="H12" t="n">
-        <v>463.0499877929688</v>
+        <v>99.52999877929688</v>
       </c>
       <c r="I12" t="n">
-        <v>425.25</v>
+        <v>90.45999908447266</v>
       </c>
       <c r="J12" t="n">
-        <v>463.0499877929688</v>
+        <v>99.52999877929688</v>
       </c>
       <c r="K12" t="n">
-        <v>3647695</v>
+        <v>2972532</v>
       </c>
       <c r="L12" t="n">
-        <v>8.890000000000001</v>
+        <v>10.03</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Asian Energy Services Share Price Today and Valuation View - Univest</t>
+          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Asian Energy Services Share Price Today and Valuation View - Univest</t>
+          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Asian Energy Services Share Price Today: Price Rise Review - Univest</t>
+          <t>Regaal Resources Q1 Results: Earnings call audio uploaded for investors - scanx.trade</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Asian Energy Services Share Price Today: Fall and Valuation - Univest</t>
+          <t>Regaal Resources Q1 Results: Earnings Call Scheduled for August 17 - scanx.trade</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Asian Energy Services Files June-Quarter Unaudited Results with SEBI - TipRanks</t>
+          <t>Regaal Resources షేర్లలో జోరు: Q1 లాభం **47%** దూసుకుపోయింది! - Whalesbook</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1206,56 +1182,68 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SUNDARAM.NS</t>
+          <t>PARAS.NS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SUNDARAM</t>
+          <t>Paras Defence and Space Technologies Limited</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.159999966621399</v>
+        <v>1385</v>
       </c>
       <c r="F13" t="n">
-        <v>1.240000009536743</v>
+        <v>1527.300048828125</v>
       </c>
       <c r="G13" t="n">
-        <v>1.149999976158142</v>
+        <v>1384.699951171875</v>
       </c>
       <c r="H13" t="n">
-        <v>1.230000019073486</v>
+        <v>1527.300048828125</v>
       </c>
       <c r="I13" t="n">
-        <v>1.129999995231628</v>
+        <v>1388.5</v>
       </c>
       <c r="J13" t="n">
-        <v>1.230000019073486</v>
+        <v>1527.300048828125</v>
       </c>
       <c r="K13" t="n">
-        <v>1399675</v>
+        <v>5405026</v>
       </c>
       <c r="L13" t="n">
-        <v>8.85</v>
+        <v>10</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - Univest</t>
+          <t>Paras Defence files FY26 BRSR report detailing ESG metrics - scanx.trade</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - Univest</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+          <t>Paras Defence Stock Hits 52-Week High at ₹1,527.65 - Whalesbook</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Paras Defence PAT up 45% to ₹89.46 crore in FY26; proposes ₹600 cr RPT limits - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Paras Defence to host analyst meet at Manufacturing Forum 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Paras Defence hosts analyst meet at Motilal Oswal conference - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1263,56 +1251,64 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TPHQ.NS</t>
+          <t>DHOOTTRANS.NS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TPHQ</t>
+          <t>DHOOTTRANS</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.6100000143051147</v>
+        <v>1170</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6299999952316284</v>
+        <v>1305.75</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5400000214576721</v>
+        <v>1165</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6299999952316284</v>
+        <v>1305.75</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5799999833106995</v>
+        <v>1187.050048828125</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6299999952316284</v>
+        <v>1305.75</v>
       </c>
       <c r="K14" t="n">
-        <v>33421631</v>
+        <v>9337471</v>
       </c>
       <c r="L14" t="n">
-        <v>8.619999999999999</v>
+        <v>10</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Average basic shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Dhoot Transmission Limited Statistics – NSE:DHOOTTRANS - TradingView</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1320,68 +1316,68 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PVP.NS</t>
+          <t>INDOMIM.NS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PVP</t>
+          <t>INDO-MIM LIMITED</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>36.79999923706055</v>
+        <v>910</v>
       </c>
       <c r="F15" t="n">
-        <v>40.90000152587891</v>
+        <v>952.75</v>
       </c>
       <c r="G15" t="n">
-        <v>36.40000152587891</v>
+        <v>905</v>
       </c>
       <c r="H15" t="n">
-        <v>40.20000076293945</v>
+        <v>952.75</v>
       </c>
       <c r="I15" t="n">
-        <v>37.0099983215332</v>
+        <v>866.1500244140625</v>
       </c>
       <c r="J15" t="n">
-        <v>40.20000076293945</v>
+        <v>952.75</v>
       </c>
       <c r="K15" t="n">
-        <v>3327170</v>
+        <v>10245867</v>
       </c>
       <c r="L15" t="n">
-        <v>8.619999999999999</v>
+        <v>10</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - Univest</t>
+          <t>INDO-MIM Q1 Consolidated Net Profit Rises to 2.4B Rupees, Revenue at 12.2B Rupees - Sahi</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Broad-Based Technical Strength Lifts PVP Ventures Ltd to 52-Week High of Rs 39.89 - MarketsMojo</t>
+          <t>INDO-MIM Q1 Consolidated Net Profit Rises to 2.4B Rupees, Revenue at 12.2B Rupees - Sahi</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PVP Ventures Q1 FY27 Results: Revenue grew to Rs 46 Cr, PAT new - Univest</t>
+          <t>Indo-MIM Q1 EBITDA up 23% to ₹4,000 million; net profit surges 32% - scanx.trade</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Only 7% of Escape from Tarkov Players Are In Standard PvP Mode - Insider Gaming</t>
+          <t>Newly-listed Indo-MIM surges to upper circuit, Trading 96% above issue price - Zee Business</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd Downgraded to Strong Sell Amid Mixed Financial and Technical Signals - MarketsMojo</t>
+          <t>Indo-MIM shares decline ahead of Q1 results; here's how the stock is performing vs issue price - Dailyhunt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1389,56 +1385,56 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EMUDHRA.NS</t>
+          <t>BI.NS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>Bilcare Limited</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>517.7000122070312</v>
+        <v>94</v>
       </c>
       <c r="F16" t="n">
-        <v>565</v>
+        <v>101.379997253418</v>
       </c>
       <c r="G16" t="n">
-        <v>509</v>
+        <v>92.16999816894531</v>
       </c>
       <c r="H16" t="n">
-        <v>562.0499877929688</v>
+        <v>101.379997253418</v>
       </c>
       <c r="I16" t="n">
-        <v>518.75</v>
+        <v>92.16999816894531</v>
       </c>
       <c r="J16" t="n">
-        <v>562.0499877929688</v>
+        <v>101.379997253418</v>
       </c>
       <c r="K16" t="n">
-        <v>704938</v>
+        <v>523283</v>
       </c>
       <c r="L16" t="n">
-        <v>8.35</v>
+        <v>9.99</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Navi Mumbai police closes 3i Infotech complaint against eMudhra as civil dispute - scanx.trade</t>
+          <t>Bilcare Limited Announces Winding Up of Bilcare INC, A Wholly Owned Subsidiary of the Company - marketscreener.com</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Navi Mumbai police closes 3i Infotech complaint against eMudhra as civil dispute - scanx.trade</t>
+          <t>Bilcare Q1FY26 Results: Net profit falls 16% YoY to ₹13.00 crore - scanx.trade</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>eMudhra Ltd. Share Price Today - eMudhra Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+          <t>Bilcare Q1FY26 Results: Net profit falls 16% YoY to ₹13.00 crore - scanx.trade</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>eMudhra Ltd Surges 7.59% to Day's High of Rs 564 — Outperforms Sector by 8.85 Percentage Points - MarketsMojo</t>
+          <t>7 Stocks That Have Hit the 20% Upper Circuit Today; Are You Holding Any? - tradebrains.in</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -1446,7 +1442,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1454,68 +1450,48 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JYOTICNC.NS</t>
+          <t>NITINSPIN.NS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>JYOTICNC</t>
+          <t>Nitin Spinners Limited</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>870</v>
+        <v>556.75</v>
       </c>
       <c r="F17" t="n">
-        <v>947.9000244140625</v>
+        <v>610</v>
       </c>
       <c r="G17" t="n">
-        <v>860.0499877929688</v>
+        <v>554.5</v>
       </c>
       <c r="H17" t="n">
-        <v>929.2000122070312</v>
+        <v>606.9000244140625</v>
       </c>
       <c r="I17" t="n">
-        <v>857.9500122070312</v>
+        <v>553.75</v>
       </c>
       <c r="J17" t="n">
-        <v>929.2000122070312</v>
+        <v>606.9000244140625</v>
       </c>
       <c r="K17" t="n">
-        <v>5438303</v>
+        <v>3703976</v>
       </c>
       <c r="L17" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Jyoti CNC Automation Ltd. Share Price News on 5.4% Rise - Univest</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Jyoti CNC Automation Ltd. Share Price News on 5.4% Rise - Univest</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Indian Export Stocks Retail Investors May Watch As US Scrutiny Of Transshipment Grows - simplywall.st</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>JYOTICNC Share Price | Jyoti CNC Automation Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Jyoti CNC Wins MeitY Nod for ₹1,020 Crore Expansion at Rajkot Plant - TipRanks</t>
-        </is>
-      </c>
+        <v>9.6</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1523,60 +1499,68 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TIINDIA.NS</t>
+          <t>ABCOTS.NS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>A B COTSPIN INDIA LIMITED</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2755.800048828125</v>
+        <v>202.4799957275391</v>
       </c>
       <c r="F18" t="n">
-        <v>2989</v>
+        <v>225</v>
       </c>
       <c r="G18" t="n">
-        <v>2755.800048828125</v>
+        <v>201.8800048828125</v>
       </c>
       <c r="H18" t="n">
-        <v>2959</v>
+        <v>217.3999938964844</v>
       </c>
       <c r="I18" t="n">
-        <v>2741.39990234375</v>
+        <v>199.6600036621094</v>
       </c>
       <c r="J18" t="n">
-        <v>2959</v>
+        <v>217.3999938964844</v>
       </c>
       <c r="K18" t="n">
-        <v>4187661</v>
+        <v>152577</v>
       </c>
       <c r="L18" t="n">
-        <v>7.94</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>TIINDIA Share Price | Tube Investments of India Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+          <t>A B Cotspin India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>TIINDIA Share Price | Tube Investments of India Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+          <t>AB Cotspin India Q1 Results: Unaudited financials approved by board - scanx.trade</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Tube Investments of India Receives Crisil ESG and Core ESG Ratings for FY 2026 - TipRanks</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+          <t>AB Cotspin India Q1 Results: Unaudited financials approved by board - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A B Cotspin India Limited Announces Appointment of Nidhi Sharma as Company Secretary and Compliance Officer, Effective August 12, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>AB Cotspin Q1FY27 revenue up 53% to ₹101.98 crore; PAT rises 21% - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1584,46 +1568,46 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SOLARA.NS</t>
+          <t>ASIANENE.NS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SOLARA</t>
+          <t>Asian Energy Services Limited</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>509.1000061035156</v>
+        <v>426.8999938964844</v>
       </c>
       <c r="F19" t="n">
-        <v>559.7999877929688</v>
+        <v>465.1000061035156</v>
       </c>
       <c r="G19" t="n">
-        <v>509.1000061035156</v>
+        <v>419.7999877929688</v>
       </c>
       <c r="H19" t="n">
-        <v>549.0499877929688</v>
+        <v>463.0499877929688</v>
       </c>
       <c r="I19" t="n">
-        <v>509.1000061035156</v>
+        <v>425.25</v>
       </c>
       <c r="J19" t="n">
-        <v>549.0499877929688</v>
+        <v>463.0499877929688</v>
       </c>
       <c r="K19" t="n">
-        <v>672938</v>
+        <v>3647695</v>
       </c>
       <c r="L19" t="n">
-        <v>7.85</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Ltd is Rated Sell - MarketsMojo</t>
+          <t>Asian Energy Services secures ₹131.39 crore from convertible warrants - Business Upturn</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Ltd is Rated Sell - MarketsMojo</t>
+          <t>Asian Energy Services secures ₹131.39 crore from convertible warrants - Business Upturn</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -1633,7 +1617,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1641,68 +1625,48 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MCLOUD.NS</t>
+          <t>SUNDARAM.NS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MCLOUD</t>
+          <t>Sundaram Multi Pap Limited</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>26.97999954223633</v>
+        <v>1.159999966621399</v>
       </c>
       <c r="F20" t="n">
-        <v>29.10000038146973</v>
+        <v>1.240000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>26.84000015258789</v>
+        <v>1.149999976158142</v>
       </c>
       <c r="H20" t="n">
-        <v>28.85000038146973</v>
+        <v>1.230000019073486</v>
       </c>
       <c r="I20" t="n">
-        <v>26.77000045776367</v>
+        <v>1.129999995231628</v>
       </c>
       <c r="J20" t="n">
-        <v>28.85000038146973</v>
+        <v>1.230000019073486</v>
       </c>
       <c r="K20" t="n">
-        <v>9814518</v>
+        <v>1399675</v>
       </c>
       <c r="L20" t="n">
-        <v>7.77</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Magellanic Cloud bags ₹8.90 crore DFCCIL surveillance contract, stock jumps nearly 7% - BusinessLine</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Magellanic Cloud bags ₹8.90 crore DFCCIL surveillance contract, stock jumps nearly 7% - BusinessLine</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Magellanic Cloud Unit Wins ₹8.90 Crore DFCCIL Order; Shares Rise 4.74% - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Magellanic Cloud Unit Wins ₹8.90 Crore DFCCIL AI Surveillance Contract - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Magellanic Cloud Publishes Q1 FY27 Unaudited Results via Newspaper and Web - TipRanks</t>
-        </is>
-      </c>
+        <v>8.85</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1710,43 +1674,63 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>JGCHEM.NS</t>
+          <t>PVP.NS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>JGCHEM</t>
+          <t>PVP Ventures Limited</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>605</v>
+        <v>36.79999923706055</v>
       </c>
       <c r="F21" t="n">
-        <v>652.4000244140625</v>
+        <v>40.90000152587891</v>
       </c>
       <c r="G21" t="n">
-        <v>602.1500244140625</v>
+        <v>36.40000152587891</v>
       </c>
       <c r="H21" t="n">
-        <v>645.8499755859375</v>
+        <v>40.20000076293945</v>
       </c>
       <c r="I21" t="n">
-        <v>600.7999877929688</v>
+        <v>37.0099983215332</v>
       </c>
       <c r="J21" t="n">
-        <v>645.8499755859375</v>
+        <v>40.20000076293945</v>
       </c>
       <c r="K21" t="n">
-        <v>871395</v>
+        <v>3327170</v>
       </c>
       <c r="L21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+        <v>8.619999999999999</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>PVP Ventures Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>PVP Ventures Limited Announces Change in Designation of Dr. Ellen Jane Feehan as Chief Executive Officer - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>PVP Ventures Limited Announces Change in Designation of Dr. Ellen Jane Feehan as Chief Executive Officer - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>PVP Ventures Q1 Consolidated Net Profit Rises to ₹12.1 Crore; Revenue Reaches ₹45.6 Crore - Sahi</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>PVP Ventures: संचालक मंडळात मोठे बदल! दोन दिग्गजांनी दिले राजीनामे - Whalesbook</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1852,7 +1836,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1865,7 +1849,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HARDWYN</t>
+          <t>Hardwyn India Limited</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1894,34 +1878,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Hardwyn India Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Hardwyn India Reports Q1 Net Profit of ₹2.8 Crore on ₹34.6 Crore Revenue - Sahi</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Hardwyn India Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Hardwyn India net profit falls 22% to ₹28 million in Q1FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Hardwyn Q1 FY27 Results: Revenue fell to Rs 35 Cr, PAT -25% - Univest</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
           <t>Hardwyn India net profit falls 22% to ₹28 million in Q1FY26 - scanx.trade</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hardwyn India Ltd is Rated Sell - MarketsMojo</t>
-        </is>
-      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1934,7 +1910,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KRISHIVAL</t>
+          <t>KRISHIVAL FOODS LIMITED</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1973,20 +1949,24 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Krishival Foods Standalone June 2026 Net Sales at Rs 37.38 crore, up 9.79% Y-o-Y - Moneycontrol.com</t>
+          <t>Krishival Foods utilizes ₹799.15 lakh of rights issue funds in Q4FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>Krishival Foods Q1 Results: Net profit rises 27% YoY to ₹560.29 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1999,7 +1979,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NELCO</t>
+          <t>Nelco Limited</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2028,34 +2008,34 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Nelco Share Price Falls over 12%: Why the $20 Million Elveo Investment Has Investors Worried - India Infoline</t>
+          <t>Nelco completes $20 million CCD investment in Lunar Holdco for satellite D2D - scanx.trade</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Tata's Nelco shares tumble 12% on Tuesday after ₹1,120 peak - NewsBytes</t>
+          <t>Nelco Shares Rise 5.5% on $20 Million Investment in US Firm Elveo - Whalesbook</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>News by CNBC TV18 on TradingView, 2026-08-18 — cnbctv:f2ab86df1094b:0 - TradingView</t>
+          <t>Nelco partners with Elveo for D2D satellite connectivity in South Asia - scanx.trade</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nelco invests $20 mn in US-based Elveo for satellite connectivity; shares fall 12% - Upstox</t>
+          <t>Nelco Shares Rise 5.5% on $20 Million Investment in US Firm Elveo - Whalesbook</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Tata Group stock: Nelco zooms 108% from March low; hits 52-week high - Business Standard</t>
+          <t>Nelco Share Price: அமெரிக்க நிறுவனத்தில் முதலீடு; **5.55%** ஏற்றத்துடன் வர்த்தகம்! - Whalesbook</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2063,48 +2043,68 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SHYAMTEL.NS</t>
+          <t>AHLUCONT.NS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SHYAMTEL</t>
+          <t>Ahluwalia Contracts (India) Limited</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>14.5</v>
+        <v>776</v>
       </c>
       <c r="F5" t="n">
-        <v>14.94999980926514</v>
+        <v>782.4000244140625</v>
       </c>
       <c r="G5" t="n">
-        <v>13.90999984741211</v>
+        <v>702.5</v>
       </c>
       <c r="H5" t="n">
-        <v>13.9399995803833</v>
+        <v>707.7000122070312</v>
       </c>
       <c r="I5" t="n">
-        <v>15.14000034332275</v>
+        <v>793.8499755859375</v>
       </c>
       <c r="J5" t="n">
-        <v>13.9399995803833</v>
+        <v>707.7000122070312</v>
       </c>
       <c r="K5" t="n">
-        <v>7220</v>
+        <v>545834</v>
       </c>
       <c r="L5" t="n">
-        <v>-7.93</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+        <v>-10.85</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Ahluwalia Contracts Q1FY27 net profit falls 78% to ₹114 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Ahluwalia Contracts Q1FY27 net profit falls 78% to ₹114 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: Ahluwalia Contracts posts Q1 FY27 miss as margins shrink - Investing.com</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ahluwalia Contracts sets Sept 22 record date for final dividend - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Ahluwalia Contracts Q1 Results: Net profit down 78% YoY to ₹114 lakh - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2112,64 +2112,56 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>THOMASCOTT.NS</t>
+          <t>PRAXIS.NS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>THOMASCOTT</t>
+          <t>Praxis Home Retail Limited</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>293</v>
+        <v>6.039999961853027</v>
       </c>
       <c r="F6" t="n">
-        <v>297.1499938964844</v>
+        <v>6.039999961853027</v>
       </c>
       <c r="G6" t="n">
-        <v>276</v>
+        <v>5.349999904632568</v>
       </c>
       <c r="H6" t="n">
-        <v>278.7999877929688</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="I6" t="n">
-        <v>301.1000061035156</v>
+        <v>5.869999885559082</v>
       </c>
       <c r="J6" t="n">
-        <v>278.7999877929688</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="K6" t="n">
-        <v>360673</v>
+        <v>554400</v>
       </c>
       <c r="L6" t="n">
-        <v>-7.41</v>
+        <v>-8.01</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - Univest</t>
+          <t>Praxis Home Retail revises promoter reclassification disclosure - scanx.trade</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - Univest</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
-        </is>
-      </c>
+          <t>Praxis Home Retail revises promoter reclassification disclosure - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2177,40 +2169,48 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KANPRPLA.NS</t>
+          <t>SHYAMTEL.NS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KANPRPLA</t>
+          <t>Shyam Telecom Limited</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>263</v>
+        <v>14.5</v>
       </c>
       <c r="F7" t="n">
-        <v>266.3900146484375</v>
+        <v>14.94999980926514</v>
       </c>
       <c r="G7" t="n">
-        <v>240.5</v>
+        <v>13.90999984741211</v>
       </c>
       <c r="H7" t="n">
-        <v>244.25</v>
+        <v>13.9399995803833</v>
       </c>
       <c r="I7" t="n">
-        <v>262.8500061035156</v>
+        <v>15.14000034332275</v>
       </c>
       <c r="J7" t="n">
-        <v>244.25</v>
+        <v>13.9399995803833</v>
       </c>
       <c r="K7" t="n">
-        <v>54440</v>
+        <v>7220</v>
       </c>
       <c r="L7" t="n">
-        <v>-7.08</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+        <v>-7.93</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Shyam Telecom Q1FY27 loss narrows to ₹199 lakh amid going concern doubts - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Shyam Telecom Q1FY27 loss narrows to ₹199 lakh amid going concern doubts - scanx.trade</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
@@ -2218,7 +2218,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2226,60 +2226,64 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TARSONS.NS</t>
+          <t>THOMASCOTT.NS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TARSONS</t>
+          <t>Thomas Scott (India) Limited</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>365</v>
+        <v>293</v>
       </c>
       <c r="F8" t="n">
-        <v>365</v>
+        <v>297.1499938964844</v>
       </c>
       <c r="G8" t="n">
-        <v>332</v>
+        <v>276</v>
       </c>
       <c r="H8" t="n">
-        <v>336.6499938964844</v>
+        <v>278.7999877929688</v>
       </c>
       <c r="I8" t="n">
-        <v>361.5</v>
+        <v>301.1000061035156</v>
       </c>
       <c r="J8" t="n">
-        <v>336.6499938964844</v>
+        <v>278.7999877929688</v>
       </c>
       <c r="K8" t="n">
-        <v>1199280</v>
+        <v>360673</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.87</v>
+        <v>-7.41</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Tarsons Products Ltd. Share Price Today Near 52-Week High - Univest</t>
+          <t>Thomas Scott India releases Q1 FY27 earnings call audio recording - scanx.trade</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tarsons Products Ltd. Share Price Today Near 52-Week High - Univest</t>
+          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Tarsons Products Share Price Rise: Technicals, Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
+          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2287,56 +2291,60 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>S&amp;SPOWER.NS</t>
+          <t>DCMSIL.NS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>S&amp;SPOWER</t>
+          <t>DCM Shriram International Limited</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>296</v>
+        <v>74</v>
       </c>
       <c r="F9" t="n">
-        <v>296</v>
+        <v>75.48999786376953</v>
       </c>
       <c r="G9" t="n">
-        <v>270</v>
+        <v>67.16000366210938</v>
       </c>
       <c r="H9" t="n">
-        <v>277.7000122070312</v>
+        <v>68.94000244140625</v>
       </c>
       <c r="I9" t="n">
-        <v>297.7000122070312</v>
+        <v>74.26000213623047</v>
       </c>
       <c r="J9" t="n">
-        <v>277.7000122070312</v>
+        <v>68.94000244140625</v>
       </c>
       <c r="K9" t="n">
-        <v>10586</v>
+        <v>208024</v>
       </c>
       <c r="L9" t="n">
-        <v>-6.72</v>
+        <v>-7.16</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
+          <t>DCM Shriram Fine Chemicals promoter acquires 3.52% stake via gift - scanx.trade</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+          <t>DCM Shriram Fine Chemicals promoter acquires 3.52% stake via gift - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>DCM Shriram Fine Chemicals posts Q1FY27 profit of ₹2.4 crore; appoints Rudra Shriram as MD - scanx.trade</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2344,37 +2352,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JUBLCPL.NS</t>
+          <t>KANPRPLA.NS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JUBLCPL</t>
+          <t>Kanpur Plastipack Limited</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2362.39990234375</v>
+        <v>263</v>
       </c>
       <c r="F10" t="n">
-        <v>2397.89990234375</v>
+        <v>266.3900146484375</v>
       </c>
       <c r="G10" t="n">
-        <v>2142</v>
+        <v>240.5</v>
       </c>
       <c r="H10" t="n">
-        <v>2199.10009765625</v>
+        <v>244.25</v>
       </c>
       <c r="I10" t="n">
-        <v>2342.39990234375</v>
+        <v>262.8500061035156</v>
       </c>
       <c r="J10" t="n">
-        <v>2199.10009765625</v>
+        <v>244.25</v>
       </c>
       <c r="K10" t="n">
-        <v>16482</v>
+        <v>54440</v>
       </c>
       <c r="L10" t="n">
-        <v>-6.12</v>
+        <v>-7.08</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -2385,7 +2393,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2393,40 +2401,48 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NDLVENTURE.NS</t>
+          <t>TARSONS.NS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NDLVENTURE</t>
+          <t>Tarsons Products Limited</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>122.1500015258789</v>
+        <v>365</v>
       </c>
       <c r="F11" t="n">
-        <v>122.7399978637695</v>
+        <v>365</v>
       </c>
       <c r="G11" t="n">
-        <v>113.9499969482422</v>
+        <v>332</v>
       </c>
       <c r="H11" t="n">
-        <v>116.1699981689453</v>
+        <v>336.6499938964844</v>
       </c>
       <c r="I11" t="n">
-        <v>123.5599975585938</v>
+        <v>361.5</v>
       </c>
       <c r="J11" t="n">
-        <v>116.1699981689453</v>
+        <v>336.6499938964844</v>
       </c>
       <c r="K11" t="n">
-        <v>57175</v>
+        <v>1199280</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.98</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+        <v>-6.87</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Tarsons Products Q1 Results: Earnings call audio uploaded - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Tarsons Products Q1 Results: Earnings call audio uploaded - scanx.trade</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
@@ -2434,7 +2450,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2442,68 +2458,56 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>APEX.NS</t>
+          <t>S&amp;SPOWER.NS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>APEX</t>
+          <t>S&amp;S Power Switchgear Limited</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>424</v>
+        <v>296</v>
       </c>
       <c r="F12" t="n">
-        <v>427.7999877929688</v>
+        <v>296</v>
       </c>
       <c r="G12" t="n">
-        <v>395.3999938964844</v>
+        <v>270</v>
       </c>
       <c r="H12" t="n">
-        <v>398.5</v>
+        <v>277.7000122070312</v>
       </c>
       <c r="I12" t="n">
-        <v>422.5499877929688</v>
+        <v>297.7000122070312</v>
       </c>
       <c r="J12" t="n">
-        <v>398.5</v>
+        <v>277.7000122070312</v>
       </c>
       <c r="K12" t="n">
-        <v>944026</v>
+        <v>10586</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.69</v>
+        <v>-6.72</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Apex Capital An Standalone June 2026 Net Sales at Rs 2.47 crore, up 65.98% Y-o-Y - Moneycontrol.com</t>
+          <t>S&amp;S Power revenue up 18% in Q1FY27; EBITDA falls 46% on delays - scanx.trade</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Apex Capital An Standalone June 2026 Net Sales at Rs 2.47 crore, up 65.98% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Apex Frozen Food shares zoom 19% after Q1FY27 net profit jumps 140% YoY - Upstox</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Apex Frozen Foods shares hit 20% upper circuit after Q1 profit more than doubles - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Apex Frozen Foods Share Price Rises 11.95%: Full Analysis - Univest</t>
-        </is>
-      </c>
+          <t>S&amp;S Power revenue up 18% in Q1FY27; EBITDA falls 46% on delays - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2511,37 +2515,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NEXTMEDIA.NS</t>
+          <t>LPDC.NS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NEXTMEDIA</t>
+          <t>Landmark Property Development Company Limited</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3.980000019073486</v>
+        <v>7.860000133514404</v>
       </c>
       <c r="F13" t="n">
-        <v>3.980000019073486</v>
+        <v>7.860000133514404</v>
       </c>
       <c r="G13" t="n">
-        <v>3.700000047683716</v>
+        <v>7.25</v>
       </c>
       <c r="H13" t="n">
-        <v>3.710000038146973</v>
+        <v>7.380000114440918</v>
       </c>
       <c r="I13" t="n">
-        <v>3.910000085830688</v>
+        <v>7.869999885559082</v>
       </c>
       <c r="J13" t="n">
-        <v>3.710000038146973</v>
+        <v>7.380000114440918</v>
       </c>
       <c r="K13" t="n">
-        <v>38951</v>
+        <v>96741</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.12</v>
+        <v>-6.23</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -2552,7 +2556,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2560,46 +2564,46 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KHAICHEM.NS</t>
+          <t>JUBLCPL.NS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KHAICHEM</t>
+          <t>Jubilant Agri and Consumer Products Limited</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>60.34000015258789</v>
+        <v>2362.39990234375</v>
       </c>
       <c r="F14" t="n">
-        <v>63.29999923706055</v>
+        <v>2397.89990234375</v>
       </c>
       <c r="G14" t="n">
-        <v>56.11000061035156</v>
+        <v>2142</v>
       </c>
       <c r="H14" t="n">
-        <v>56.72000122070312</v>
+        <v>2199.10009765625</v>
       </c>
       <c r="I14" t="n">
-        <v>59.75</v>
+        <v>2342.39990234375</v>
       </c>
       <c r="J14" t="n">
-        <v>56.72000122070312</v>
+        <v>2199.10009765625</v>
       </c>
       <c r="K14" t="n">
-        <v>1445339</v>
+        <v>16482</v>
       </c>
       <c r="L14" t="n">
-        <v>-5.07</v>
+        <v>-6.12</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Khaitan Chemicals &amp; Fertilizers Ltd. (KHAICHEM) Share Price Rises 10.63% as Stock Enters Top Gainers Today - Univest</t>
+          <t>Jubilant Agri &amp; Consumer Q1 Results: Net profit rises 7.5% YoY - scanx.trade</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Khaitan Chemicals &amp; Fertilizers Ltd. (KHAICHEM) Share Price Rises 10.63% as Stock Enters Top Gainers Today - Univest</t>
+          <t>Jubilant Agri &amp; Consumer Q1 Results: Net profit rises 7.5% YoY - scanx.trade</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -2609,7 +2613,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2617,48 +2621,68 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NATIONSTD.NS</t>
+          <t>SIGIND.NS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NATIONSTD</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>134</v>
+        <v>70.84999847412109</v>
       </c>
       <c r="F15" t="n">
-        <v>148.1000061035156</v>
+        <v>71.5</v>
       </c>
       <c r="G15" t="n">
-        <v>134</v>
+        <v>65.31999969482422</v>
       </c>
       <c r="H15" t="n">
-        <v>134</v>
+        <v>66.84999847412109</v>
       </c>
       <c r="I15" t="n">
-        <v>141.0500030517578</v>
+        <v>71.15000152587891</v>
       </c>
       <c r="J15" t="n">
-        <v>134</v>
+        <v>66.84999847412109</v>
       </c>
       <c r="K15" t="n">
-        <v>335324</v>
+        <v>95414</v>
       </c>
       <c r="L15" t="n">
-        <v>-5</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+        <v>-6.04</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Signet Industries promoter Mukesh Sangla buys 13,904 shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Signet Industries promoter Mukesh Sangla buys 13,904 shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Signet Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Signet Industries Q1 Results: Net profit rises 10.7% QoQ to ₹8.05 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Signet Industries షేర్ ధర: ఇన్వెస్టర్లకు పండగే! తొలిసారిగా భారీ లాభాలు.. 1066% జంప్ - Whalesbook</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2666,37 +2690,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RAMCOSYS.NS</t>
+          <t>NDLVENTURE.NS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>RAMCOSYS</t>
+          <t>NDL Ventures Limited</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>593.0999755859375</v>
+        <v>122.1500015258789</v>
       </c>
       <c r="F16" t="n">
-        <v>598</v>
+        <v>122.7399978637695</v>
       </c>
       <c r="G16" t="n">
-        <v>564.5</v>
+        <v>113.9499969482422</v>
       </c>
       <c r="H16" t="n">
-        <v>564.5</v>
+        <v>116.1699981689453</v>
       </c>
       <c r="I16" t="n">
-        <v>594.2000122070312</v>
+        <v>123.5599975585938</v>
       </c>
       <c r="J16" t="n">
-        <v>564.5</v>
+        <v>116.1699981689453</v>
       </c>
       <c r="K16" t="n">
-        <v>245328</v>
+        <v>57175</v>
       </c>
       <c r="L16" t="n">
-        <v>-5</v>
+        <v>-5.98</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2707,7 +2731,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2715,37 +2739,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INDOTHAI.NS</t>
+          <t>MOIL.NS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>INDOTHAI</t>
+          <t>MOIL Limited</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>69.56999969482422</v>
+        <v>271.2000122070312</v>
       </c>
       <c r="F17" t="n">
-        <v>69.56999969482422</v>
+        <v>271.7999877929688</v>
       </c>
       <c r="G17" t="n">
-        <v>69.56999969482422</v>
+        <v>255.6000061035156</v>
       </c>
       <c r="H17" t="n">
-        <v>69.56999969482422</v>
+        <v>257.25</v>
       </c>
       <c r="I17" t="n">
-        <v>73.23000335693359</v>
+        <v>272.7999877929688</v>
       </c>
       <c r="J17" t="n">
-        <v>69.56999969482422</v>
+        <v>257.25</v>
       </c>
       <c r="K17" t="n">
-        <v>20955</v>
+        <v>2810988</v>
       </c>
       <c r="L17" t="n">
-        <v>-5</v>
+        <v>-5.7</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2756,7 +2780,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2764,48 +2788,68 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OSWALSEEDS.NS</t>
+          <t>APEX.NS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OSWALSEEDS</t>
+          <t>Apex Frozen Foods Limited</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>13.44999980926514</v>
+        <v>424</v>
       </c>
       <c r="F18" t="n">
-        <v>13.5600004196167</v>
+        <v>427.7999877929688</v>
       </c>
       <c r="G18" t="n">
-        <v>12.88000011444092</v>
+        <v>395.3999938964844</v>
       </c>
       <c r="H18" t="n">
-        <v>12.92000007629395</v>
+        <v>398.5</v>
       </c>
       <c r="I18" t="n">
-        <v>13.59000015258789</v>
+        <v>422.5499877929688</v>
       </c>
       <c r="J18" t="n">
-        <v>12.92000007629395</v>
+        <v>398.5</v>
       </c>
       <c r="K18" t="n">
-        <v>400753</v>
+        <v>944026</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.93</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+        <v>-5.69</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Volume Gainers, August 14, 2026, 4:00 PM IST - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Apex Frozen Foods reports burgeoning profits with YoY surge in Q1 FY27 - Business Upturn</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>7 Stocks That Have Hit the 20% Upper Circuit Today; Are You Holding Any? - tradebrains.in</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Apex Frozen Foods Hits 20% Upper Circuit on 138% Profit Jump - Whalesbook</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Apex Frozen Foods reports burgeoning profits with YoY surge in Q1 FY27 - Business Upturn</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2813,60 +2857,56 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SHANTIGOLD.NS</t>
+          <t>AGL.NS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SHANTIGOLD</t>
+          <t>ALLCARGO GLOBAL LIMITED</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>269</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>269.9700012207031</v>
+        <v>14.01000022888184</v>
       </c>
       <c r="G19" t="n">
-        <v>251.2100067138672</v>
+        <v>13.02999973297119</v>
       </c>
       <c r="H19" t="n">
-        <v>253.8500061035156</v>
+        <v>13.25</v>
       </c>
       <c r="I19" t="n">
-        <v>266.8399963378906</v>
+        <v>14.01000022888184</v>
       </c>
       <c r="J19" t="n">
-        <v>253.8500061035156</v>
+        <v>13.25</v>
       </c>
       <c r="K19" t="n">
-        <v>2594125</v>
+        <v>3444947</v>
       </c>
       <c r="L19" t="n">
-        <v>-4.87</v>
+        <v>-5.42</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Shanti Gold International Ltd. Share Price Today Up 8.24% - Univest</t>
+          <t>Allcargo Global makes Q1FY27 earnings call audio recording available - scanx.trade</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Shanti Gold International Ltd. Share Price Today Up 8.24% - Univest</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Shanti Gold International Ltd. Share Price Today Up 8.83% - Univest</t>
-        </is>
-      </c>
+          <t>Allcargo Global makes Q1FY27 earnings call audio recording available - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2874,48 +2914,60 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GANGAFORGE.NS</t>
+          <t>ATALREAL.NS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>GANGAFORGE</t>
+          <t>Atal Realtech Limited</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2.369999885559082</v>
+        <v>36.09999847412109</v>
       </c>
       <c r="F20" t="n">
-        <v>2.369999885559082</v>
+        <v>36.33000183105469</v>
       </c>
       <c r="G20" t="n">
-        <v>2.369999885559082</v>
+        <v>31.42000007629395</v>
       </c>
       <c r="H20" t="n">
-        <v>2.369999885559082</v>
+        <v>33.93000030517578</v>
       </c>
       <c r="I20" t="n">
-        <v>2.490000009536743</v>
+        <v>35.84999847412109</v>
       </c>
       <c r="J20" t="n">
-        <v>2.369999885559082</v>
+        <v>33.93000030517578</v>
       </c>
       <c r="K20" t="n">
-        <v>668561</v>
+        <v>20786651</v>
       </c>
       <c r="L20" t="n">
-        <v>-4.82</v>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+        <v>-5.36</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Atal Realtech board approves ₹16 crore rights issue for equity shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Atal Realtech board approves ₹16 crore rights issue for equity shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Atal Realtech Q1FY27 net profit rises 52% to ₹1 crore as margins expand - scanx.trade</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-18 19:09:25</t>
+          <t>2026-08-18 14:44:15</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2923,48 +2975,40 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SUMEETINDS.NS</t>
+          <t>NDGL.NS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>Naga Dhunseri Group Limited</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>14.14000034332275</v>
+        <v>2875</v>
       </c>
       <c r="F21" t="n">
-        <v>14.27999973297119</v>
+        <v>2875</v>
       </c>
       <c r="G21" t="n">
-        <v>13.38000011444092</v>
+        <v>2669</v>
       </c>
       <c r="H21" t="n">
-        <v>13.42000007629395</v>
+        <v>2727.89990234375</v>
       </c>
       <c r="I21" t="n">
-        <v>14.07999992370605</v>
+        <v>2878.699951171875</v>
       </c>
       <c r="J21" t="n">
-        <v>13.42000007629395</v>
+        <v>2727.89990234375</v>
       </c>
       <c r="K21" t="n">
-        <v>4474052</v>
+        <v>558</v>
       </c>
       <c r="L21" t="n">
-        <v>-4.69</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - Univest</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - Univest</t>
-        </is>
-      </c>
+        <v>-5.24</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,7 +567,6 @@
           <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - tradebrains.in</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -627,8 +626,6 @@
           <t>Subex seeks shareholder nod for new ESOP scheme, trust loan - scanx.trade</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,11 +670,6 @@
       <c r="L4" t="n">
         <v>13.26</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -722,11 +714,6 @@
       <c r="L5" t="n">
         <v>12.69</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -855,8 +842,6 @@
           <t>Sigachi Industries Q1 Results: Net profit rebounds to ₹8.14 crore - scanx.trade</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -911,9 +896,6 @@
           <t>The National Stock Exchange has sought clarification on unusual price fluctuations in several stocks. - Traders Union</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -968,9 +950,6 @@
           <t>Jindal Drilling Q1 Results: New ONGC Rig Contract, Order Book At ₹1,310 Crore - scanx.trade</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1035,7 +1014,6 @@
           <t>Ind-Swift Laboratories: जम्मू प्लांटमध्ये ₹45 कोटींची गुंतवणूक, जागतिक बाजारात प्रवेशाची तयारी! - Whalesbook</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1100,7 +1078,6 @@
           <t>A B Infrabuild reports Q1 FY27 revenue of ₹7,625.1 lakh, a 25.9% increase YoY - Business Upturn</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1303,7 +1280,6 @@
           <t>Dhoot Transmission Limited Statistics – NSE:DHOOTTRANS - TradingView</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1437,7 +1413,6 @@
           <t>7 Stocks That Have Hit the 20% Upper Circuit Today; Are You Holding Any? - tradebrains.in</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1482,11 +1457,6 @@
       <c r="L17" t="n">
         <v>9.6</v>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1610,9 +1580,6 @@
           <t>Asian Energy Services secures ₹131.39 crore from convertible warrants - Business Upturn</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1657,11 +1624,6 @@
       <c r="L20" t="n">
         <v>8.85</v>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1731,6 +1693,1238 @@
           <t>PVP Ventures: संचालक मंडळात मोठे बदल! दोन दिग्गजांनी दिले राजीनामे - Whalesbook</t>
         </is>
       </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PRABHA.NS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PRABHA</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>164.3099975585938</v>
+      </c>
+      <c r="F22" t="n">
+        <v>196.0500030517578</v>
+      </c>
+      <c r="G22" t="n">
+        <v>163</v>
+      </c>
+      <c r="H22" t="n">
+        <v>192.1999969482422</v>
+      </c>
+      <c r="I22" t="n">
+        <v>163.3800048828125</v>
+      </c>
+      <c r="J22" t="n">
+        <v>192.1999969482422</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5357086</v>
+      </c>
+      <c r="L22" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>PRABHA ENERGY Share Price Gain: Technicals and Valuation - univest.in</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Prabha Energy seeks ₹150 crore QIP approval at upcoming AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>N K Industries Ltd leads gainers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SUBEXLTD.NS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SUBEXLTD</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>14.10999965667725</v>
+      </c>
+      <c r="F23" t="n">
+        <v>16.93000030517578</v>
+      </c>
+      <c r="G23" t="n">
+        <v>14.07999992370605</v>
+      </c>
+      <c r="H23" t="n">
+        <v>16.48999977111816</v>
+      </c>
+      <c r="I23" t="n">
+        <v>14.10999965667725</v>
+      </c>
+      <c r="J23" t="n">
+        <v>16.48999977111816</v>
+      </c>
+      <c r="K23" t="n">
+        <v>44567365</v>
+      </c>
+      <c r="L23" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Subex Ltd. Share Price Gain: Price Action and Valuation - univest.in</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Subex Ltd. Share Price Gain: Price Action and Valuation - univest.in</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AARNAV.NS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AARNAV</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>31.35000038146973</v>
+      </c>
+      <c r="F24" t="n">
+        <v>36.04000091552734</v>
+      </c>
+      <c r="G24" t="n">
+        <v>30.70000076293945</v>
+      </c>
+      <c r="H24" t="n">
+        <v>35.36999893188477</v>
+      </c>
+      <c r="I24" t="n">
+        <v>31.22999954223633</v>
+      </c>
+      <c r="J24" t="n">
+        <v>35.36999893188477</v>
+      </c>
+      <c r="K24" t="n">
+        <v>220800</v>
+      </c>
+      <c r="L24" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Share Price News: Technicals, Valuation - univest.in</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Share Price News: Technicals, Valuation - univest.in</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>YASHO.NS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>YASHO</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4400</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4994</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4399.89990234375</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4915.7998046875</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4362.2998046875</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4915.7998046875</v>
+      </c>
+      <c r="K25" t="n">
+        <v>240190</v>
+      </c>
+      <c r="L25" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd Hits All-Time High of Rs 4640.95 as Momentum Builds Across Timeframes - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd Hits All-Time High of Rs 4640.95 as Momentum Builds Across Timeframes - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>INDSWFTLAB.NS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>INDSWFTLAB</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>317.9500122070312</v>
+      </c>
+      <c r="F26" t="n">
+        <v>351.2999877929688</v>
+      </c>
+      <c r="G26" t="n">
+        <v>316.8999938964844</v>
+      </c>
+      <c r="H26" t="n">
+        <v>346.8699951171875</v>
+      </c>
+      <c r="I26" t="n">
+        <v>313.0199890136719</v>
+      </c>
+      <c r="J26" t="n">
+        <v>346.8699951171875</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5070304</v>
+      </c>
+      <c r="L26" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - univest.in</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - univest.in</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Sets Q1 FY27 Earnings Call for August 17 - TipRanks</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ABINFRA.NS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ABINFRA</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>11.32999992370605</v>
+      </c>
+      <c r="F27" t="n">
+        <v>12.98999977111816</v>
+      </c>
+      <c r="G27" t="n">
+        <v>10.97999954223633</v>
+      </c>
+      <c r="H27" t="n">
+        <v>12.56999969482422</v>
+      </c>
+      <c r="I27" t="n">
+        <v>11.35999965667725</v>
+      </c>
+      <c r="J27" t="n">
+        <v>12.56999969482422</v>
+      </c>
+      <c r="K27" t="n">
+        <v>25170195</v>
+      </c>
+      <c r="L27" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>7</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PARAS.NS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PARAS</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1385</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1527.300048828125</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1384.699951171875</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1527.300048828125</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1388.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1527.300048828125</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5405026</v>
+      </c>
+      <c r="L28" t="n">
+        <v>10</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Paras Defence, Zen Tech, other defence shares rise up to 8% as MoD notifies sixth Positive Indigenisation... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Paras Defence zooms 163% from March low; hits 52-week high on huge volume - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Paras Defence Share Price at Fresh 52-Week High - univest.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS.NS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1305.75</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1165</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1305.75</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1187.050048828125</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1305.75</v>
+      </c>
+      <c r="K29" t="n">
+        <v>9337471</v>
+      </c>
+      <c r="L29" t="n">
+        <v>10</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - univest.in</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - univest.in</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Average basic shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Dhoot Transmission Limited Statistics – NSE:DHOOTTRANS - TradingView</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BI.NS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BI</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>94</v>
+      </c>
+      <c r="F30" t="n">
+        <v>101.379997253418</v>
+      </c>
+      <c r="G30" t="n">
+        <v>92.16999816894531</v>
+      </c>
+      <c r="H30" t="n">
+        <v>101.379997253418</v>
+      </c>
+      <c r="I30" t="n">
+        <v>92.16999816894531</v>
+      </c>
+      <c r="J30" t="n">
+        <v>101.379997253418</v>
+      </c>
+      <c r="K30" t="n">
+        <v>523283</v>
+      </c>
+      <c r="L30" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NITINSPIN.NS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NITINSPIN</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>556.75</v>
+      </c>
+      <c r="F31" t="n">
+        <v>610</v>
+      </c>
+      <c r="G31" t="n">
+        <v>554.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>606.9000244140625</v>
+      </c>
+      <c r="I31" t="n">
+        <v>553.75</v>
+      </c>
+      <c r="J31" t="n">
+        <v>606.9000244140625</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3703976</v>
+      </c>
+      <c r="L31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - univest.in</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - univest.in</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ASIANENE.NS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ASIANENE</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>426.8999938964844</v>
+      </c>
+      <c r="F32" t="n">
+        <v>465.1000061035156</v>
+      </c>
+      <c r="G32" t="n">
+        <v>419.7999877929688</v>
+      </c>
+      <c r="H32" t="n">
+        <v>463.0499877929688</v>
+      </c>
+      <c r="I32" t="n">
+        <v>425.25</v>
+      </c>
+      <c r="J32" t="n">
+        <v>463.0499877929688</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3647695</v>
+      </c>
+      <c r="L32" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Share Price Today and Valuation View - univest.in</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Share Price Today and Valuation View - univest.in</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Share Price Today: Price Rise Review - univest.in</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Share Price Today: Fall and Valuation - univest.in</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Files June-Quarter Unaudited Results with SEBI - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>12</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SUNDARAM.NS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SUNDARAM</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1.159999966621399</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.240000009536743</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.149999976158142</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.230000019073486</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.129999995231628</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.230000019073486</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1399675</v>
+      </c>
+      <c r="L33" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - univest.in</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - univest.in</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>13</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PVP.NS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PVP</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>36.79999923706055</v>
+      </c>
+      <c r="F34" t="n">
+        <v>40.90000152587891</v>
+      </c>
+      <c r="G34" t="n">
+        <v>36.40000152587891</v>
+      </c>
+      <c r="H34" t="n">
+        <v>40.20000076293945</v>
+      </c>
+      <c r="I34" t="n">
+        <v>37.0099983215332</v>
+      </c>
+      <c r="J34" t="n">
+        <v>40.20000076293945</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3327170</v>
+      </c>
+      <c r="L34" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - univest.in</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Broad-Based Technical Strength Lifts PVP Ventures Ltd to 52-Week High of Rs 39.89 - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>PVP Ventures Q1 FY27 Results: Revenue grew to Rs 46 Cr, PAT new - univest.in</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Only 7% of Escape from Tarkov Players Are In Standard PvP Mode - Insider Gaming</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd Downgraded to Strong Sell Amid Mixed Financial and Technical Signals - MarketsMojo</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>14</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>TPHQ.NS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TPHQ</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6100000143051147</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.6299999952316284</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.5400000214576721</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.6299999952316284</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.5799999833106995</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.6299999952316284</v>
+      </c>
+      <c r="K35" t="n">
+        <v>33421631</v>
+      </c>
+      <c r="L35" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>15</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>KERNEX.NS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>KERNEX</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1820</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1920</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1756.099975585938</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1901.800048828125</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1751.699951171875</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1901.800048828125</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1425146</v>
+      </c>
+      <c r="L36" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Kernex Microsystems Q1FY27 net profit rises 13.7x to ₹10,984.57 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Kernex Microsystems Q1FY27 net profit rises 13.7x to ₹10,984.57 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>16</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMUDHRA.NS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>EMUDHRA</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>517.7000122070312</v>
+      </c>
+      <c r="F37" t="n">
+        <v>565</v>
+      </c>
+      <c r="G37" t="n">
+        <v>509</v>
+      </c>
+      <c r="H37" t="n">
+        <v>562.0499877929688</v>
+      </c>
+      <c r="I37" t="n">
+        <v>518.75</v>
+      </c>
+      <c r="J37" t="n">
+        <v>562.0499877929688</v>
+      </c>
+      <c r="K37" t="n">
+        <v>704938</v>
+      </c>
+      <c r="L37" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Navi Mumbai police closes 3i Infotech complaint against eMudhra as civil dispute - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Navi Mumbai police closes 3i Infotech complaint against eMudhra as civil dispute - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>eMudhra Ltd. Share Price Today - eMudhra Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>eMudhra Ltd Surges 7.59% to Day's High of Rs 564 — Outperforms Sector by 8.85 Percentage Points - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>17</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>JYOTICNC.NS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>JYOTICNC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>870</v>
+      </c>
+      <c r="F38" t="n">
+        <v>947.9000244140625</v>
+      </c>
+      <c r="G38" t="n">
+        <v>860.0499877929688</v>
+      </c>
+      <c r="H38" t="n">
+        <v>929.2000122070312</v>
+      </c>
+      <c r="I38" t="n">
+        <v>857.9500122070312</v>
+      </c>
+      <c r="J38" t="n">
+        <v>929.2000122070312</v>
+      </c>
+      <c r="K38" t="n">
+        <v>5438303</v>
+      </c>
+      <c r="L38" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Jyoti CNC Automation Ltd. Share Price News on 5.4% Rise - univest.in</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Jyoti CNC Automation Ltd. Share Price News on 5.4% Rise - univest.in</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Indian Export Stocks Retail Investors May Watch As US Scrutiny Of Transshipment Grows - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>JYOTICNC Share Price | Jyoti CNC Automation Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Jyoti CNC Wins MeitY Nod for ₹1,020 Crore Expansion at Rajkot Plant - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>18</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MCLOUD.NS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>MCLOUD</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>26.97999954223633</v>
+      </c>
+      <c r="F39" t="n">
+        <v>29.10000038146973</v>
+      </c>
+      <c r="G39" t="n">
+        <v>26.84000015258789</v>
+      </c>
+      <c r="H39" t="n">
+        <v>28.85000038146973</v>
+      </c>
+      <c r="I39" t="n">
+        <v>26.77000045776367</v>
+      </c>
+      <c r="J39" t="n">
+        <v>28.85000038146973</v>
+      </c>
+      <c r="K39" t="n">
+        <v>9814518</v>
+      </c>
+      <c r="L39" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Magellanic Cloud bags ₹8.90 crore DFCCIL surveillance contract, stock jumps nearly 7% - BusinessLine</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Magellanic Cloud bags ₹8.90 crore DFCCIL surveillance contract, stock jumps nearly 7% - BusinessLine</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Magellanic Cloud Unit Wins ₹8.90 Crore DFCCIL Order; Shares Rise 4.74% - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Magellanic Cloud Unit Wins ₹8.90 Crore DFCCIL AI Surveillance Contract - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Magellanic Cloud Publishes Q1 FY27 Unaudited Results via Newspaper and Web - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>19</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MMP.NS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>MMP</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>353.8500061035156</v>
+      </c>
+      <c r="F40" t="n">
+        <v>383</v>
+      </c>
+      <c r="G40" t="n">
+        <v>345</v>
+      </c>
+      <c r="H40" t="n">
+        <v>377.0499877929688</v>
+      </c>
+      <c r="I40" t="n">
+        <v>350</v>
+      </c>
+      <c r="J40" t="n">
+        <v>377.0499877929688</v>
+      </c>
+      <c r="K40" t="n">
+        <v>191009</v>
+      </c>
+      <c r="L40" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>MMP Industries Standalone June 2026 Net Sales at Rs 232.11 crore, up 26.66% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>MMP Industries Standalone June 2026 Net Sales at Rs 232.11 crore, up 26.66% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>MMP Industries Share Price: 52-Week High, Valuation View - univest.in</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>MMP Industries Share Price Target 2027 to 2030: Analyst Outlook - univest.in</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>What's Going On With Precious Metals And Mining Trust Stock Sunday? - Wealth Awesome</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>KPEL.NS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>KPEL</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>243.6999969482422</v>
+      </c>
+      <c r="F41" t="n">
+        <v>264.9500122070312</v>
+      </c>
+      <c r="G41" t="n">
+        <v>240</v>
+      </c>
+      <c r="H41" t="n">
+        <v>262.2999877929688</v>
+      </c>
+      <c r="I41" t="n">
+        <v>243.75</v>
+      </c>
+      <c r="J41" t="n">
+        <v>262.2999877929688</v>
+      </c>
+      <c r="K41" t="n">
+        <v>859114</v>
+      </c>
+      <c r="L41" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1743,7 +2937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1891,8 +3085,6 @@
           <t>Hardwyn India net profit falls 22% to ₹28 million in Q1FY26 - scanx.trade</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2154,9 +3346,6 @@
           <t>Praxis Home Retail revises promoter reclassification disclosure - scanx.trade</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2211,9 +3400,6 @@
           <t>Shyam Telecom Q1FY27 loss narrows to ₹199 lakh amid going concern doubts - scanx.trade</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2278,7 +3464,6 @@
           <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2338,8 +3523,6 @@
           <t>DCM Shriram Fine Chemicals posts Q1FY27 profit of ₹2.4 crore; appoints Rudra Shriram as MD - scanx.trade</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2384,11 +3567,6 @@
       <c r="L10" t="n">
         <v>-7.08</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2443,9 +3621,6 @@
           <t>Tarsons Products Q1 Results: Earnings call audio uploaded - scanx.trade</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2500,9 +3675,6 @@
           <t>S&amp;S Power revenue up 18% in Q1FY27; EBITDA falls 46% on delays - scanx.trade</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2547,11 +3719,6 @@
       <c r="L13" t="n">
         <v>-6.23</v>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2606,9 +3773,6 @@
           <t>Jubilant Agri &amp; Consumer Q1 Results: Net profit rises 7.5% YoY - scanx.trade</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2722,11 +3886,6 @@
       <c r="L16" t="n">
         <v>-5.98</v>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2771,11 +3930,6 @@
       <c r="L17" t="n">
         <v>-5.7</v>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2899,9 +4053,6 @@
           <t>Allcargo Global makes Q1FY27 earnings call audio recording available - scanx.trade</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2961,8 +4112,6 @@
           <t>Atal Realtech Q1FY27 net profit rises 52% to ₹1 crore as margins expand - scanx.trade</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3007,11 +4156,1126 @@
       <c r="L21" t="n">
         <v>-5.24</v>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HARDWYN.NS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HARDWYN</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>10.94999980926514</v>
+      </c>
+      <c r="F22" t="n">
+        <v>11.10999965667725</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8.800000190734863</v>
+      </c>
+      <c r="H22" t="n">
+        <v>9.420000076293945</v>
+      </c>
+      <c r="I22" t="n">
+        <v>10.94999980926514</v>
+      </c>
+      <c r="J22" t="n">
+        <v>9.420000076293945</v>
+      </c>
+      <c r="K22" t="n">
+        <v>9633380</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-13.97</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Hardwyn India Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Hardwyn India Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Hardwyn Q1 FY27 Results: Revenue fell to Rs 35 Cr, PAT -25% - univest.in</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hardwyn India net profit falls 22% to ₹28 million in Q1FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>KRISHIVAL.NS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>KRISHIVAL</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>403</v>
+      </c>
+      <c r="F23" t="n">
+        <v>403</v>
+      </c>
+      <c r="G23" t="n">
+        <v>350.6000061035156</v>
+      </c>
+      <c r="H23" t="n">
+        <v>355.75</v>
+      </c>
+      <c r="I23" t="n">
+        <v>408.2999877929688</v>
+      </c>
+      <c r="J23" t="n">
+        <v>355.75</v>
+      </c>
+      <c r="K23" t="n">
+        <v>170799</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-12.87</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Krishival Foods lists converted equity shares on NSE and BSE - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Krishival Foods Standalone June 2026 Net Sales at Rs 37.38 crore, up 9.79% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PRAXIS.NS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PRAXIS</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6.039999961853027</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6.039999961853027</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.349999904632568</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5.400000095367432</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5.869999885559082</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5.400000095367432</v>
+      </c>
+      <c r="K24" t="n">
+        <v>554400</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-8.01</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Praxis Home Retail Share Price Today: Price Fall Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Praxis Home Retail Share Price Today: Price Fall Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Praxis Precision Medicines stock hits 52-week high at 388.27 USD - Investing.com India</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>9,840 Shares in Praxis Precision Medicines, Inc. $PRAX Purchased by Handelsbanken Fonder AB - MarketBeat</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Praxis Precision Medicines (PRAX): Orbis, Allan Gray disclose 5.5% ownership stake - stocktitan.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SHYAMTEL.NS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SHYAMTEL</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>14.94999980926514</v>
+      </c>
+      <c r="G25" t="n">
+        <v>13.90999984741211</v>
+      </c>
+      <c r="H25" t="n">
+        <v>13.9399995803833</v>
+      </c>
+      <c r="I25" t="n">
+        <v>15.14000034332275</v>
+      </c>
+      <c r="J25" t="n">
+        <v>13.9399995803833</v>
+      </c>
+      <c r="K25" t="n">
+        <v>7220</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-7.93</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>THOMASCOTT.NS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>THOMASCOTT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>293</v>
+      </c>
+      <c r="F26" t="n">
+        <v>297.1499938964844</v>
+      </c>
+      <c r="G26" t="n">
+        <v>276</v>
+      </c>
+      <c r="H26" t="n">
+        <v>278.7999877929688</v>
+      </c>
+      <c r="I26" t="n">
+        <v>301.1000061035156</v>
+      </c>
+      <c r="J26" t="n">
+        <v>278.7999877929688</v>
+      </c>
+      <c r="K26" t="n">
+        <v>360673</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-7.41</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - univest.in</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - univest.in</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DCMSIL.NS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DCMSIL</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>74</v>
+      </c>
+      <c r="F27" t="n">
+        <v>75.48999786376953</v>
+      </c>
+      <c r="G27" t="n">
+        <v>67.16000366210938</v>
+      </c>
+      <c r="H27" t="n">
+        <v>68.94000244140625</v>
+      </c>
+      <c r="I27" t="n">
+        <v>74.26000213623047</v>
+      </c>
+      <c r="J27" t="n">
+        <v>68.94000244140625</v>
+      </c>
+      <c r="K27" t="n">
+        <v>208024</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-7.16</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>DCMSIL Share Price Today - DCM Shriram International Ltd. Stock Price Live NSE/BSE - univest.in</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>DCM Shriram International Ltd. Share Price Today After Fall - univest.in</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>DCM Shriram International Ltd. Share Price Today After Fall - univest.in</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>7</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>KANPRPLA.NS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>KANPRPLA</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>263</v>
+      </c>
+      <c r="F28" t="n">
+        <v>266.3900146484375</v>
+      </c>
+      <c r="G28" t="n">
+        <v>240.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>244.25</v>
+      </c>
+      <c r="I28" t="n">
+        <v>262.8500061035156</v>
+      </c>
+      <c r="J28" t="n">
+        <v>244.25</v>
+      </c>
+      <c r="K28" t="n">
+        <v>54440</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-7.08</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TARSONS.NS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TARSONS</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>365</v>
+      </c>
+      <c r="F29" t="n">
+        <v>365</v>
+      </c>
+      <c r="G29" t="n">
+        <v>332</v>
+      </c>
+      <c r="H29" t="n">
+        <v>336.6499938964844</v>
+      </c>
+      <c r="I29" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>336.6499938964844</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1199280</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-6.87</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Tarsons Products Ltd. Share Price Today Near 52-Week High - univest.in</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarsons Products Ltd. Share Price Today Near 52-Week High - univest.in</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Tarsons Products Share Price Rise: Technicals, Valuation - univest.in</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>JUBLCPL.NS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>JUBLCPL</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2362.39990234375</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2397.89990234375</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2142</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2199.10009765625</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2342.39990234375</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2199.10009765625</v>
+      </c>
+      <c r="K30" t="n">
+        <v>16482</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NDLVENTURE.NS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NDLVENTURE</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>122.1500015258789</v>
+      </c>
+      <c r="F31" t="n">
+        <v>122.7399978637695</v>
+      </c>
+      <c r="G31" t="n">
+        <v>113.9499969482422</v>
+      </c>
+      <c r="H31" t="n">
+        <v>116.1699981689453</v>
+      </c>
+      <c r="I31" t="n">
+        <v>123.5599975585938</v>
+      </c>
+      <c r="J31" t="n">
+        <v>116.1699981689453</v>
+      </c>
+      <c r="K31" t="n">
+        <v>57175</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-5.98</v>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MOIL.NS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>MOIL</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>271.2000122070312</v>
+      </c>
+      <c r="F32" t="n">
+        <v>271.7999877929688</v>
+      </c>
+      <c r="G32" t="n">
+        <v>255.6000061035156</v>
+      </c>
+      <c r="H32" t="n">
+        <v>257.25</v>
+      </c>
+      <c r="I32" t="n">
+        <v>272.7999877929688</v>
+      </c>
+      <c r="J32" t="n">
+        <v>257.25</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2810988</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>12</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AGL.NS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AGL</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>14</v>
+      </c>
+      <c r="F33" t="n">
+        <v>14.01000022888184</v>
+      </c>
+      <c r="G33" t="n">
+        <v>13.02999973297119</v>
+      </c>
+      <c r="H33" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="I33" t="n">
+        <v>14.01000022888184</v>
+      </c>
+      <c r="J33" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3444947</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>AGL Energy Shares Up 1.9% as Battery Performance Offsets 47% Electricity Price Fall - TechStock²</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>AGL Energy Shares Up 1.9% as Battery Performance Offsets 47% Electricity Price Fall - TechStock²</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Allcargo Global Ltd Share Price Today,, AGL Share Price NSE, BSE - Business Today</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Why is AGL Energy stock surging today? - Investing.com</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Agilon Health Inc (AGL) Stock Up 9.0% but GF Value Says Overvalued -- GF Score: 71/100 - GuruFocus</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>13</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ATALREAL.NS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ATALREAL</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>36.09999847412109</v>
+      </c>
+      <c r="F34" t="n">
+        <v>36.33000183105469</v>
+      </c>
+      <c r="G34" t="n">
+        <v>31.42000007629395</v>
+      </c>
+      <c r="H34" t="n">
+        <v>33.93000030517578</v>
+      </c>
+      <c r="I34" t="n">
+        <v>35.84999847412109</v>
+      </c>
+      <c r="J34" t="n">
+        <v>33.93000030517578</v>
+      </c>
+      <c r="K34" t="n">
+        <v>20786651</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-5.36</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - univest.in</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - univest.in</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Atal Realtech Share Price Near ATH With Fundamental View - univest.in</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>14</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>NDGL.NS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NDGL</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2875</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2875</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2669</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2727.89990234375</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2878.699951171875</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2727.89990234375</v>
+      </c>
+      <c r="K35" t="n">
+        <v>558</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>15</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>KHAICHEM.NS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>KHAICHEM</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>60.34000015258789</v>
+      </c>
+      <c r="F36" t="n">
+        <v>63.29999923706055</v>
+      </c>
+      <c r="G36" t="n">
+        <v>56.11000061035156</v>
+      </c>
+      <c r="H36" t="n">
+        <v>56.72000122070312</v>
+      </c>
+      <c r="I36" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="J36" t="n">
+        <v>56.72000122070312</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1445339</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Khaitan Chemicals &amp; Fertilizers Ltd. (KHAICHEM) Share Price Rises 10.63% as Stock Enters Top Gainers Today - univest.in</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Khaitan Chemicals &amp; Fertilizers Ltd. (KHAICHEM) Share Price Rises 10.63% as Stock Enters Top Gainers Today - univest.in</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>16</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NATIONSTD.NS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NATIONSTD</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>134</v>
+      </c>
+      <c r="F37" t="n">
+        <v>148.1000061035156</v>
+      </c>
+      <c r="G37" t="n">
+        <v>134</v>
+      </c>
+      <c r="H37" t="n">
+        <v>134</v>
+      </c>
+      <c r="I37" t="n">
+        <v>141.0500030517578</v>
+      </c>
+      <c r="J37" t="n">
+        <v>134</v>
+      </c>
+      <c r="K37" t="n">
+        <v>335324</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>17</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>RAMCOSYS.NS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>RAMCOSYS</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>593.0999755859375</v>
+      </c>
+      <c r="F38" t="n">
+        <v>598</v>
+      </c>
+      <c r="G38" t="n">
+        <v>564.5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>564.5</v>
+      </c>
+      <c r="I38" t="n">
+        <v>594.2000122070312</v>
+      </c>
+      <c r="J38" t="n">
+        <v>564.5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>245328</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>18</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>OSWALSEEDS.NS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>OSWALSEEDS</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>13.44999980926514</v>
+      </c>
+      <c r="F39" t="n">
+        <v>13.5600004196167</v>
+      </c>
+      <c r="G39" t="n">
+        <v>12.88000011444092</v>
+      </c>
+      <c r="H39" t="n">
+        <v>12.92000007629395</v>
+      </c>
+      <c r="I39" t="n">
+        <v>13.59000015258789</v>
+      </c>
+      <c r="J39" t="n">
+        <v>12.92000007629395</v>
+      </c>
+      <c r="K39" t="n">
+        <v>400753</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-4.93</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>19</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>LORDSCHLO.NS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LORDSCHLO</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>140.0299987792969</v>
+      </c>
+      <c r="F40" t="n">
+        <v>142.4499969482422</v>
+      </c>
+      <c r="G40" t="n">
+        <v>133</v>
+      </c>
+      <c r="H40" t="n">
+        <v>133.4199981689453</v>
+      </c>
+      <c r="I40" t="n">
+        <v>139.9799957275391</v>
+      </c>
+      <c r="J40" t="n">
+        <v>133.4199981689453</v>
+      </c>
+      <c r="K40" t="n">
+        <v>29362</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-4.69</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:18:32</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SUMEETINDS.NS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SUMEETINDS</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>14.14000034332275</v>
+      </c>
+      <c r="F41" t="n">
+        <v>14.27999973297119</v>
+      </c>
+      <c r="G41" t="n">
+        <v>13.38000011444092</v>
+      </c>
+      <c r="H41" t="n">
+        <v>13.42000007629395</v>
+      </c>
+      <c r="I41" t="n">
+        <v>14.07999992370605</v>
+      </c>
+      <c r="J41" t="n">
+        <v>13.42000007629395</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4474052</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-4.69</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1816,9 +1816,6 @@
           <t>Subex Ltd. Share Price Gain: Price Action and Valuation - univest.in</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1873,9 +1870,6 @@
           <t>Aarnav Fashions Share Price News: Technicals, Valuation - univest.in</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1935,8 +1929,6 @@
           <t>Yasho Industries Ltd Hits All-Time High of Rs 4640.95 as Momentum Builds Across Timeframes - MarketsMojo</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1996,8 +1988,6 @@
           <t>Ind-Swift Laboratories Sets Q1 FY27 Earnings Call for August 17 - TipRanks</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2042,11 +2032,6 @@
       <c r="L27" t="n">
         <v>10.65</v>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2180,7 +2165,6 @@
           <t>Dhoot Transmission Limited Statistics – NSE:DHOOTTRANS - TradingView</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2235,9 +2219,6 @@
           <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2292,9 +2273,6 @@
           <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - univest.in</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2418,9 +2396,6 @@
           <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - univest.in</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2544,9 +2519,6 @@
           <t>Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2601,9 +2573,6 @@
           <t>Kernex Microsystems Q1FY27 net profit rises 13.7x to ₹10,984.57 lakh - scanx.trade</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2668,7 +2637,6 @@
           <t>eMudhra Ltd Surges 7.59% to Day's High of Rs 564 — Outperforms Sector by 8.85 Percentage Points - MarketsMojo</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2920,11 +2888,1210 @@
       <c r="L41" t="n">
         <v>7.61</v>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PRABHA.NS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PRABHA</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>164.3099975585938</v>
+      </c>
+      <c r="F42" t="n">
+        <v>196.0500030517578</v>
+      </c>
+      <c r="G42" t="n">
+        <v>163</v>
+      </c>
+      <c r="H42" t="n">
+        <v>192.1999969482422</v>
+      </c>
+      <c r="I42" t="n">
+        <v>163.3800048828125</v>
+      </c>
+      <c r="J42" t="n">
+        <v>192.1999969482422</v>
+      </c>
+      <c r="K42" t="n">
+        <v>5357086</v>
+      </c>
+      <c r="L42" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>PRABHA ENERGY Share Price Gain: Technicals and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - tradebrains.in</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Volume Gainers, August 18, 2026, 3:00 PM IST - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Prabha Energy seeks ₹150 crore QIP approval at upcoming AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>N K Industries Ltd leads gainers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SUBEXLTD.NS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SUBEXLTD</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>14.10999965667725</v>
+      </c>
+      <c r="F43" t="n">
+        <v>16.93000030517578</v>
+      </c>
+      <c r="G43" t="n">
+        <v>14.07999992370605</v>
+      </c>
+      <c r="H43" t="n">
+        <v>16.48999977111816</v>
+      </c>
+      <c r="I43" t="n">
+        <v>14.10999965667725</v>
+      </c>
+      <c r="J43" t="n">
+        <v>16.48999977111816</v>
+      </c>
+      <c r="K43" t="n">
+        <v>44567365</v>
+      </c>
+      <c r="L43" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Subex Ltd. Share Price Gain: Price Action and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Subex Ltd. Share Price Gain: Price Action and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AARNAV.NS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AARNAV</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>31.35000038146973</v>
+      </c>
+      <c r="F44" t="n">
+        <v>36.04000091552734</v>
+      </c>
+      <c r="G44" t="n">
+        <v>30.70000076293945</v>
+      </c>
+      <c r="H44" t="n">
+        <v>35.36999893188477</v>
+      </c>
+      <c r="I44" t="n">
+        <v>31.22999954223633</v>
+      </c>
+      <c r="J44" t="n">
+        <v>35.36999893188477</v>
+      </c>
+      <c r="K44" t="n">
+        <v>220800</v>
+      </c>
+      <c r="L44" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>YASHO.NS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>YASHO</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4400</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4994</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4399.89990234375</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4915.7998046875</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4362.2998046875</v>
+      </c>
+      <c r="J45" t="n">
+        <v>4915.7998046875</v>
+      </c>
+      <c r="K45" t="n">
+        <v>240190</v>
+      </c>
+      <c r="L45" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - indianexpress.com</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd Hits All-Time High of Rs 4640.95 as Momentum Builds Across Timeframes - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd Hits All-Time High of Rs 4640.95 as Momentum Builds Across Timeframes - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ICIL.NS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ICIL</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>388.7000122070312</v>
+      </c>
+      <c r="F46" t="n">
+        <v>462</v>
+      </c>
+      <c r="G46" t="n">
+        <v>387.0499877929688</v>
+      </c>
+      <c r="H46" t="n">
+        <v>437.7000122070312</v>
+      </c>
+      <c r="I46" t="n">
+        <v>388.7000122070312</v>
+      </c>
+      <c r="J46" t="n">
+        <v>437.7000122070312</v>
+      </c>
+      <c r="K46" t="n">
+        <v>25217469</v>
+      </c>
+      <c r="L46" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>6</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SIGACHI.NS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SIGACHI</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>25.90999984741211</v>
+      </c>
+      <c r="F47" t="n">
+        <v>30.09000015258789</v>
+      </c>
+      <c r="G47" t="n">
+        <v>25.90999984741211</v>
+      </c>
+      <c r="H47" t="n">
+        <v>29.61000061035156</v>
+      </c>
+      <c r="I47" t="n">
+        <v>26.35000038146973</v>
+      </c>
+      <c r="J47" t="n">
+        <v>29.61000061035156</v>
+      </c>
+      <c r="K47" t="n">
+        <v>10330178</v>
+      </c>
+      <c r="L47" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Sigachi posts Q1 FY 2026-27 earnings call audio on website - TipRanks</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Sigachi posts Q1 FY 2026-27 earnings call audio on website - TipRanks</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>7</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MACPOWER.NS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>MACPOWER</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1782.5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1782.5</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1983.599975585938</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1781.400024414062</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1983.599975585938</v>
+      </c>
+      <c r="K48" t="n">
+        <v>190615</v>
+      </c>
+      <c r="L48" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Macpower CNC Machines Ltd. Share Price Rises 8.64% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Macpower CNC Machines Ltd. Share Price Rises 8.64% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Macpower CNC Machines Ltd. Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>JINDRILL.NS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>JINDRILL</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>587.0999755859375</v>
+      </c>
+      <c r="F49" t="n">
+        <v>673.5499877929688</v>
+      </c>
+      <c r="G49" t="n">
+        <v>587.0999755859375</v>
+      </c>
+      <c r="H49" t="n">
+        <v>651.1500244140625</v>
+      </c>
+      <c r="I49" t="n">
+        <v>586.2000122070312</v>
+      </c>
+      <c r="J49" t="n">
+        <v>651.1500244140625</v>
+      </c>
+      <c r="K49" t="n">
+        <v>17885600</v>
+      </c>
+      <c r="L49" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>9</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>INDSWFTLAB.NS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>INDSWFTLAB</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>317.9500122070312</v>
+      </c>
+      <c r="F50" t="n">
+        <v>351.2999877929688</v>
+      </c>
+      <c r="G50" t="n">
+        <v>316.8999938964844</v>
+      </c>
+      <c r="H50" t="n">
+        <v>346.8699951171875</v>
+      </c>
+      <c r="I50" t="n">
+        <v>313.0199890136719</v>
+      </c>
+      <c r="J50" t="n">
+        <v>346.8699951171875</v>
+      </c>
+      <c r="K50" t="n">
+        <v>5070304</v>
+      </c>
+      <c r="L50" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - Univest</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - Univest</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Sets Q1 FY27 Earnings Call for August 17 - TipRanks</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>10</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ABINFRA.NS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ABINFRA</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>11.32999992370605</v>
+      </c>
+      <c r="F51" t="n">
+        <v>12.98999977111816</v>
+      </c>
+      <c r="G51" t="n">
+        <v>10.97999954223633</v>
+      </c>
+      <c r="H51" t="n">
+        <v>12.56999969482422</v>
+      </c>
+      <c r="I51" t="n">
+        <v>11.35999965667725</v>
+      </c>
+      <c r="J51" t="n">
+        <v>12.56999969482422</v>
+      </c>
+      <c r="K51" t="n">
+        <v>25170195</v>
+      </c>
+      <c r="L51" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>11</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>REGAAL.NS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>REGAAL</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>90.27999877929688</v>
+      </c>
+      <c r="F52" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>88.65000152587891</v>
+      </c>
+      <c r="H52" t="n">
+        <v>99.52999877929688</v>
+      </c>
+      <c r="I52" t="n">
+        <v>90.45999908447266</v>
+      </c>
+      <c r="J52" t="n">
+        <v>99.52999877929688</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2972532</v>
+      </c>
+      <c r="L52" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Regaal Resources Q1 Results: Earnings call audio uploaded for investors - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Regaal Resources Ltd Surges 17% to Hit Upper Circuit Amid Robust Buying Pressure - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>12</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS.NS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1305.75</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1165</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1305.75</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1187.050048828125</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1305.75</v>
+      </c>
+      <c r="K53" t="n">
+        <v>9337471</v>
+      </c>
+      <c r="L53" t="n">
+        <v>10</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Average basic shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Dhoot Transmission Limited Statistics – NSE:DHOOTTRANS - TradingView</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>13</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>PARAS.NS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>PARAS</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1385</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1527.300048828125</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1384.699951171875</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1527.300048828125</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1388.5</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1527.300048828125</v>
+      </c>
+      <c r="K54" t="n">
+        <v>5405026</v>
+      </c>
+      <c r="L54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Paras Defence, Zen Tech, other defence shares rise up to 8% as MoD notifies sixth Positive Indigenisation... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Paras Defence zooms 163% from March low; hits 52-week high on huge volume - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Paras Defence Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>14</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>INDOMIM.NS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>INDOMIM</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>910</v>
+      </c>
+      <c r="F55" t="n">
+        <v>952.75</v>
+      </c>
+      <c r="G55" t="n">
+        <v>905</v>
+      </c>
+      <c r="H55" t="n">
+        <v>952.75</v>
+      </c>
+      <c r="I55" t="n">
+        <v>866.1500244140625</v>
+      </c>
+      <c r="J55" t="n">
+        <v>952.75</v>
+      </c>
+      <c r="K55" t="n">
+        <v>10245867</v>
+      </c>
+      <c r="L55" t="n">
+        <v>10</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Indo-MIM shares hit 10% upper circuit on strong Q1 growth as raw material costs decline 11% in June quarter - Upstox</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Stocks to watch, August 18: GMR Airports, Oberoi Realty, Paytm, Nelco, INDO-MIM, Netweb Technologies - Dailyhunt</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>INDOMIM Historical Data - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>INDO-MIM Board Clears Q1 FY27 Results, New Secretarial Auditor and ESOP Ratification - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>INDO-MIM Clears Q1 FY27 Results, Appoints New Secretarial Auditor and Ratifies ESOP - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>15</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BI.NS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BI</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>94</v>
+      </c>
+      <c r="F56" t="n">
+        <v>101.379997253418</v>
+      </c>
+      <c r="G56" t="n">
+        <v>92.16999816894531</v>
+      </c>
+      <c r="H56" t="n">
+        <v>101.379997253418</v>
+      </c>
+      <c r="I56" t="n">
+        <v>92.16999816894531</v>
+      </c>
+      <c r="J56" t="n">
+        <v>101.379997253418</v>
+      </c>
+      <c r="K56" t="n">
+        <v>523283</v>
+      </c>
+      <c r="L56" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>16</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>NITINSPIN.NS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NITINSPIN</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>556.75</v>
+      </c>
+      <c r="F57" t="n">
+        <v>610</v>
+      </c>
+      <c r="G57" t="n">
+        <v>554.5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>606.9000244140625</v>
+      </c>
+      <c r="I57" t="n">
+        <v>553.75</v>
+      </c>
+      <c r="J57" t="n">
+        <v>606.9000244140625</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3703976</v>
+      </c>
+      <c r="L57" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>17</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ASIANENE.NS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ASIANENE</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>426.8999938964844</v>
+      </c>
+      <c r="F58" t="n">
+        <v>465.1000061035156</v>
+      </c>
+      <c r="G58" t="n">
+        <v>419.7999877929688</v>
+      </c>
+      <c r="H58" t="n">
+        <v>463.0499877929688</v>
+      </c>
+      <c r="I58" t="n">
+        <v>425.25</v>
+      </c>
+      <c r="J58" t="n">
+        <v>463.0499877929688</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3647695</v>
+      </c>
+      <c r="L58" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Share Price Today and Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Share Price Today and Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Share Price Today: Price Rise Review - Univest</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Share Price Today: Fall and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Files June-Quarter Unaudited Results with SEBI - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>18</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ABCOTS.NS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ABCOTS</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>202.4799957275391</v>
+      </c>
+      <c r="F59" t="n">
+        <v>225</v>
+      </c>
+      <c r="G59" t="n">
+        <v>201.8800048828125</v>
+      </c>
+      <c r="H59" t="n">
+        <v>217.3999938964844</v>
+      </c>
+      <c r="I59" t="n">
+        <v>199.6600036621094</v>
+      </c>
+      <c r="J59" t="n">
+        <v>217.3999938964844</v>
+      </c>
+      <c r="K59" t="n">
+        <v>152577</v>
+      </c>
+      <c r="L59" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>AB Cotspin India Ltd. Share Price Today: Textile Stock Up - Univest</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>AB Cotspin India Ltd. Share Price Today: Textile Stock Up - Univest</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>ABCOTS Share Price Today - AB Cotspin on NSE/BSE - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>AB Cotspin India Ltd. Share Price and 52-Week Low Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>AB Cotspin India Board Clears Q1 FY27 Results, Appoints New Compliance Officer - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>19</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SUNDARAM.NS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SUNDARAM</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1.159999966621399</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.240000009536743</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.149999976158142</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.230000019073486</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.129999995231628</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.230000019073486</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1399675</v>
+      </c>
+      <c r="L60" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>20</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>TPHQ.NS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>TPHQ</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.6100000143051147</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.6299999952316284</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.5400000214576721</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.6299999952316284</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.5799999833106995</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.6299999952316284</v>
+      </c>
+      <c r="K61" t="n">
+        <v>33421631</v>
+      </c>
+      <c r="L61" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2937,7 +4104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4220,7 +5387,6 @@
           <t>Hardwyn India net profit falls 22% to ₹28 million in Q1FY26 - scanx.trade</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4285,7 +5451,6 @@
           <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4399,11 +5564,6 @@
       <c r="L25" t="n">
         <v>-7.93</v>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4468,7 +5628,6 @@
           <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4528,8 +5687,6 @@
           <t>DCM Shriram International Ltd. Share Price Today After Fall - univest.in</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4574,11 +5731,6 @@
       <c r="L28" t="n">
         <v>-7.08</v>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4638,8 +5790,6 @@
           <t>Tarsons Products Share Price Rise: Technicals, Valuation - univest.in</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4684,11 +5834,6 @@
       <c r="L30" t="n">
         <v>-6.12</v>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4733,11 +5878,6 @@
       <c r="L31" t="n">
         <v>-5.98</v>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4782,11 +5922,6 @@
       <c r="L32" t="n">
         <v>-5.7</v>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4915,8 +6050,6 @@
           <t>Atal Realtech Share Price Near ATH With Fundamental View - univest.in</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4961,11 +6094,6 @@
       <c r="L35" t="n">
         <v>-5.24</v>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5020,9 +6148,6 @@
           <t>Khaitan Chemicals &amp; Fertilizers Ltd. (KHAICHEM) Share Price Rises 10.63% as Stock Enters Top Gainers Today - univest.in</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5067,11 +6192,6 @@
       <c r="L37" t="n">
         <v>-5</v>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5116,11 +6236,6 @@
       <c r="L38" t="n">
         <v>-5</v>
       </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5165,11 +6280,6 @@
       <c r="L39" t="n">
         <v>-4.93</v>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5214,11 +6324,6 @@
       <c r="L40" t="n">
         <v>-4.69</v>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5273,9 +6378,1182 @@
           <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HARDWYN.NS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>HARDWYN</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>10.94999980926514</v>
+      </c>
+      <c r="F42" t="n">
+        <v>11.10999965667725</v>
+      </c>
+      <c r="G42" t="n">
+        <v>8.800000190734863</v>
+      </c>
+      <c r="H42" t="n">
+        <v>9.420000076293945</v>
+      </c>
+      <c r="I42" t="n">
+        <v>10.94999980926514</v>
+      </c>
+      <c r="J42" t="n">
+        <v>9.420000076293945</v>
+      </c>
+      <c r="K42" t="n">
+        <v>9633380</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-13.97</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Hardwyn India Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Hardwyn India Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Hardwyn Q1 FY27 Results: Revenue Rs 35 Cr, PAT Rs 3 Cr - Univest</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hardwyn India net profit falls 22% to ₹28 million in Q1FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>KRISHIVAL.NS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>KRISHIVAL</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>403</v>
+      </c>
+      <c r="F43" t="n">
+        <v>403</v>
+      </c>
+      <c r="G43" t="n">
+        <v>350.6000061035156</v>
+      </c>
+      <c r="H43" t="n">
+        <v>355.75</v>
+      </c>
+      <c r="I43" t="n">
+        <v>408.2999877929688</v>
+      </c>
+      <c r="J43" t="n">
+        <v>355.75</v>
+      </c>
+      <c r="K43" t="n">
+        <v>170799</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-12.87</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Krishival Foods lists converted equity shares on NSE and BSE - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Krishival Foods Standalone June 2026 Net Sales at Rs 37.38 crore, up 9.79% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NELCO.NS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NELCO</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1092.300048828125</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1098</v>
+      </c>
+      <c r="G44" t="n">
+        <v>938.5999755859375</v>
+      </c>
+      <c r="H44" t="n">
+        <v>948.7999877929688</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1081.5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>948.7999877929688</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2128333</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-12.27</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Nelco Share Price Falls over 12%: Why the $20 Million Elveo Investment Has Investors Worried - India Infoline</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Tata's Nelco shares tumble 12% on Tuesday after ₹1,120 peak - NewsBytes</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-18 — cnbctv:f2ab86df1094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Nelco invests $20 mn in US-based Elveo for satellite connectivity; shares fall 12% - Upstox</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Tata Group stock: Nelco zooms 108% from March low; hits 52-week high - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AHLUCONT.NS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AHLUCONT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>776</v>
+      </c>
+      <c r="F45" t="n">
+        <v>782.4000244140625</v>
+      </c>
+      <c r="G45" t="n">
+        <v>702.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>707.7000122070312</v>
+      </c>
+      <c r="I45" t="n">
+        <v>793.8499755859375</v>
+      </c>
+      <c r="J45" t="n">
+        <v>707.7000122070312</v>
+      </c>
+      <c r="K45" t="n">
+        <v>545834</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-10.85</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Hold Ahluwalia Contracts India; target of Rs 780: ICICI Securities - TradingView</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Hold Ahluwalia Contracts India; target of Rs 780: ICICI Securities - TradingView</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PRAXIS.NS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PRAXIS</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6.039999961853027</v>
+      </c>
+      <c r="F46" t="n">
+        <v>6.039999961853027</v>
+      </c>
+      <c r="G46" t="n">
+        <v>5.349999904632568</v>
+      </c>
+      <c r="H46" t="n">
+        <v>5.400000095367432</v>
+      </c>
+      <c r="I46" t="n">
+        <v>5.869999885559082</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5.400000095367432</v>
+      </c>
+      <c r="K46" t="n">
+        <v>554400</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-8.01</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Praxis Home Retail Share Price Today: Price Fall Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Praxis Home Retail Share Price Today: Price Fall Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Praxis Precision Medicines stock hits 52-week high at 388.27 USD - Investing.com India</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>9,840 Shares in Praxis Precision Medicines, Inc. $PRAX Purchased by Handelsbanken Fonder AB - MarketBeat</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Praxis Precision Medicines (PRAX): Orbis, Allan Gray disclose 5.5% ownership stake - Stock Titan</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>6</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SHYAMTEL.NS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SHYAMTEL</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F47" t="n">
+        <v>14.94999980926514</v>
+      </c>
+      <c r="G47" t="n">
+        <v>13.90999984741211</v>
+      </c>
+      <c r="H47" t="n">
+        <v>13.9399995803833</v>
+      </c>
+      <c r="I47" t="n">
+        <v>15.14000034332275</v>
+      </c>
+      <c r="J47" t="n">
+        <v>13.9399995803833</v>
+      </c>
+      <c r="K47" t="n">
+        <v>7220</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-7.93</v>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>7</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>THOMASCOTT.NS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>THOMASCOTT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>293</v>
+      </c>
+      <c r="F48" t="n">
+        <v>297.1499938964844</v>
+      </c>
+      <c r="G48" t="n">
+        <v>276</v>
+      </c>
+      <c r="H48" t="n">
+        <v>278.7999877929688</v>
+      </c>
+      <c r="I48" t="n">
+        <v>301.1000061035156</v>
+      </c>
+      <c r="J48" t="n">
+        <v>278.7999877929688</v>
+      </c>
+      <c r="K48" t="n">
+        <v>360673</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-7.41</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - Univest</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - Univest</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DCMSIL.NS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DCMSIL</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>74</v>
+      </c>
+      <c r="F49" t="n">
+        <v>75.48999786376953</v>
+      </c>
+      <c r="G49" t="n">
+        <v>67.16000366210938</v>
+      </c>
+      <c r="H49" t="n">
+        <v>68.94000244140625</v>
+      </c>
+      <c r="I49" t="n">
+        <v>74.26000213623047</v>
+      </c>
+      <c r="J49" t="n">
+        <v>68.94000244140625</v>
+      </c>
+      <c r="K49" t="n">
+        <v>208024</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-7.16</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>DCMSIL Share Price Today - DCM Shriram International Ltd. Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>DCM Shriram International Ltd. Share Price Today After Fall - Univest</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>DCM Shriram International Ltd. Share Price Today After Fall - Univest</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>9</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>KANPRPLA.NS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>KANPRPLA</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>263</v>
+      </c>
+      <c r="F50" t="n">
+        <v>266.3900146484375</v>
+      </c>
+      <c r="G50" t="n">
+        <v>240.5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>244.25</v>
+      </c>
+      <c r="I50" t="n">
+        <v>262.8500061035156</v>
+      </c>
+      <c r="J50" t="n">
+        <v>244.25</v>
+      </c>
+      <c r="K50" t="n">
+        <v>54440</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-7.08</v>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>10</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TARSONS.NS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TARSONS</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>365</v>
+      </c>
+      <c r="F51" t="n">
+        <v>365</v>
+      </c>
+      <c r="G51" t="n">
+        <v>332</v>
+      </c>
+      <c r="H51" t="n">
+        <v>336.6499938964844</v>
+      </c>
+      <c r="I51" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="J51" t="n">
+        <v>336.6499938964844</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1199280</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-6.87</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Tarsons Products Ltd. Share Price Today Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Tarsons Products Ltd. Share Price Today Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Tarsons Products Share Price Rise: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>11</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>S&amp;SPOWER.NS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>S&amp;SPOWER</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>296</v>
+      </c>
+      <c r="F52" t="n">
+        <v>296</v>
+      </c>
+      <c r="G52" t="n">
+        <v>270</v>
+      </c>
+      <c r="H52" t="n">
+        <v>277.7000122070312</v>
+      </c>
+      <c r="I52" t="n">
+        <v>297.7000122070312</v>
+      </c>
+      <c r="J52" t="n">
+        <v>277.7000122070312</v>
+      </c>
+      <c r="K52" t="n">
+        <v>10586</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-6.72</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>12</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LPDC.NS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LPDC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>7.860000133514404</v>
+      </c>
+      <c r="F53" t="n">
+        <v>7.860000133514404</v>
+      </c>
+      <c r="G53" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="H53" t="n">
+        <v>7.380000114440918</v>
+      </c>
+      <c r="I53" t="n">
+        <v>7.869999885559082</v>
+      </c>
+      <c r="J53" t="n">
+        <v>7.380000114440918</v>
+      </c>
+      <c r="K53" t="n">
+        <v>96741</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-6.23</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Landmark Property Development Company Ltd. (LPDC) Share Price Rises 12.24% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Landmark Property Development Company Ltd. (LPDC) Share Price Rises 12.24% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>13</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>JUBLCPL.NS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>JUBLCPL</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2362.39990234375</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2397.89990234375</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2142</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2199.10009765625</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2342.39990234375</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2199.10009765625</v>
+      </c>
+      <c r="K54" t="n">
+        <v>16482</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>14</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SIGIND.NS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SIGIND</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>70.84999847412109</v>
+      </c>
+      <c r="F55" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>65.31999969482422</v>
+      </c>
+      <c r="H55" t="n">
+        <v>66.84999847412109</v>
+      </c>
+      <c r="I55" t="n">
+        <v>71.15000152587891</v>
+      </c>
+      <c r="J55" t="n">
+        <v>66.84999847412109</v>
+      </c>
+      <c r="K55" t="n">
+        <v>95414</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-6.04</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Signet Industries Ltd. Share Price Rise With Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Signet Industries Ltd. Share Price Rise With Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>15</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>NDLVENTURE.NS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NDLVENTURE</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>122.1500015258789</v>
+      </c>
+      <c r="F56" t="n">
+        <v>122.7399978637695</v>
+      </c>
+      <c r="G56" t="n">
+        <v>113.9499969482422</v>
+      </c>
+      <c r="H56" t="n">
+        <v>116.1699981689453</v>
+      </c>
+      <c r="I56" t="n">
+        <v>123.5599975585938</v>
+      </c>
+      <c r="J56" t="n">
+        <v>116.1699981689453</v>
+      </c>
+      <c r="K56" t="n">
+        <v>57175</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-5.98</v>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>16</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MOIL.NS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>MOIL</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>271.2000122070312</v>
+      </c>
+      <c r="F57" t="n">
+        <v>271.7999877929688</v>
+      </c>
+      <c r="G57" t="n">
+        <v>255.6000061035156</v>
+      </c>
+      <c r="H57" t="n">
+        <v>257.25</v>
+      </c>
+      <c r="I57" t="n">
+        <v>272.7999877929688</v>
+      </c>
+      <c r="J57" t="n">
+        <v>257.25</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2810988</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>17</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>APEX.NS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>APEX</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>424</v>
+      </c>
+      <c r="F58" t="n">
+        <v>427.7999877929688</v>
+      </c>
+      <c r="G58" t="n">
+        <v>395.3999938964844</v>
+      </c>
+      <c r="H58" t="n">
+        <v>398.5</v>
+      </c>
+      <c r="I58" t="n">
+        <v>422.5499877929688</v>
+      </c>
+      <c r="J58" t="n">
+        <v>398.5</v>
+      </c>
+      <c r="K58" t="n">
+        <v>944026</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-5.69</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Apex Capital An Standalone June 2026 Net Sales at Rs 2.47 crore, up 65.98% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Apex Capital An Standalone June 2026 Net Sales at Rs 2.47 crore, up 65.98% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Apex Frozen Food shares zoom 19% after Q1FY27 net profit jumps 140% YoY - Upstox</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Apex Frozen Foods shares hit 20% upper circuit after Q1 profit more than doubles - cnbctv18.com</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Apex Frozen Foods Share Price Rises 11.95%: Full Analysis - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>18</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AGL.NS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AGL</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>14</v>
+      </c>
+      <c r="F59" t="n">
+        <v>14.01000022888184</v>
+      </c>
+      <c r="G59" t="n">
+        <v>13.02999973297119</v>
+      </c>
+      <c r="H59" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="I59" t="n">
+        <v>14.01000022888184</v>
+      </c>
+      <c r="J59" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3444947</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>AGL Energy Shares Up 1.9% as Battery Performance Offsets 47% Electricity Price Fall - TechStock²</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>AGL Energy Shares Up 1.9% as Battery Performance Offsets 47% Electricity Price Fall - TechStock²</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Allcargo Global Ltd Share Price Today,, AGL Share Price NSE, BSE - Business Today</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Why is AGL Energy stock surging today? - Investing.com</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Agilon Health Inc (AGL) Stock Up 9.0% but GF Value Says Overvalued -- GF Score: 71/100 - GuruFocus</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>19</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ATALREAL.NS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ATALREAL</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>36.09999847412109</v>
+      </c>
+      <c r="F60" t="n">
+        <v>36.33000183105469</v>
+      </c>
+      <c r="G60" t="n">
+        <v>31.42000007629395</v>
+      </c>
+      <c r="H60" t="n">
+        <v>33.93000030517578</v>
+      </c>
+      <c r="I60" t="n">
+        <v>35.84999847412109</v>
+      </c>
+      <c r="J60" t="n">
+        <v>33.93000030517578</v>
+      </c>
+      <c r="K60" t="n">
+        <v>20786651</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-5.36</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Atal Realtech Share Price Near ATH With Fundamental View - Univest</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:01:48</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>20</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>NDGL.NS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NDGL</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2875</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2875</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2669</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2727.89990234375</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2878.699951171875</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2727.89990234375</v>
+      </c>
+      <c r="K61" t="n">
+        <v>558</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3011,9 +3011,6 @@
           <t>Subex Ltd. Share Price Gain: Price Action and Valuation - Univest</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3068,9 +3065,6 @@
           <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3130,8 +3124,6 @@
           <t>Yasho Industries Ltd Hits All-Time High of Rs 4640.95 as Momentum Builds Across Timeframes - MarketsMojo</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3176,11 +3168,6 @@
       <c r="L46" t="n">
         <v>12.61</v>
       </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3235,9 +3222,6 @@
           <t>Sigachi posts Q1 FY 2026-27 earnings call audio on website - TipRanks</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3297,8 +3281,6 @@
           <t>Macpower CNC Machines Ltd. Share Price News and Analysis - Univest</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3343,11 +3325,6 @@
       <c r="L49" t="n">
         <v>11.08</v>
       </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3407,8 +3384,6 @@
           <t>Ind-Swift Laboratories Sets Q1 FY27 Earnings Call for August 17 - TipRanks</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3453,11 +3428,6 @@
       <c r="L51" t="n">
         <v>10.65</v>
       </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3522,7 +3492,6 @@
           <t>Regaal Resources Ltd Surges 17% to Hit Upper Circuit Amid Robust Buying Pressure - MarketsMojo</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3587,7 +3556,6 @@
           <t>Dhoot Transmission Limited Statistics – NSE:DHOOTTRANS - TradingView</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3780,9 +3748,6 @@
           <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3837,9 +3802,6 @@
           <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - Univest</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4032,9 +3994,6 @@
           <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - Univest</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4089,9 +4048,1226 @@
           <t>Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PRABHA.NS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>PRABHA</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>164.3099975585938</v>
+      </c>
+      <c r="F62" t="n">
+        <v>196.0500030517578</v>
+      </c>
+      <c r="G62" t="n">
+        <v>163</v>
+      </c>
+      <c r="H62" t="n">
+        <v>192.1999969482422</v>
+      </c>
+      <c r="I62" t="n">
+        <v>163.3800048828125</v>
+      </c>
+      <c r="J62" t="n">
+        <v>192.1999969482422</v>
+      </c>
+      <c r="K62" t="n">
+        <v>5357086</v>
+      </c>
+      <c r="L62" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>PRABHA ENERGY Share Price Gain: Technicals and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Volume Gainers, August 18, 2026, 3:00 PM IST - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Prabha Energy seeks ₹150 crore QIP approval at upcoming AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>N K Industries Ltd leads gainers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SUBEXLTD.NS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SUBEXLTD</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>14.10999965667725</v>
+      </c>
+      <c r="F63" t="n">
+        <v>16.93000030517578</v>
+      </c>
+      <c r="G63" t="n">
+        <v>14.07999992370605</v>
+      </c>
+      <c r="H63" t="n">
+        <v>16.48999977111816</v>
+      </c>
+      <c r="I63" t="n">
+        <v>14.10999965667725</v>
+      </c>
+      <c r="J63" t="n">
+        <v>16.48999977111816</v>
+      </c>
+      <c r="K63" t="n">
+        <v>44567365</v>
+      </c>
+      <c r="L63" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Subex Ltd. Share Price Gain: Price Action and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Subex Ltd. Share Price Gain: Price Action and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AARNAV.NS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AARNAV</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>31.35000038146973</v>
+      </c>
+      <c r="F64" t="n">
+        <v>36.04000091552734</v>
+      </c>
+      <c r="G64" t="n">
+        <v>30.70000076293945</v>
+      </c>
+      <c r="H64" t="n">
+        <v>35.36999893188477</v>
+      </c>
+      <c r="I64" t="n">
+        <v>31.22999954223633</v>
+      </c>
+      <c r="J64" t="n">
+        <v>35.36999893188477</v>
+      </c>
+      <c r="K64" t="n">
+        <v>220800</v>
+      </c>
+      <c r="L64" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>YASHO.NS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>YASHO</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>4400</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4994</v>
+      </c>
+      <c r="G65" t="n">
+        <v>4399.89990234375</v>
+      </c>
+      <c r="H65" t="n">
+        <v>4915.7998046875</v>
+      </c>
+      <c r="I65" t="n">
+        <v>4362.2998046875</v>
+      </c>
+      <c r="J65" t="n">
+        <v>4915.7998046875</v>
+      </c>
+      <c r="K65" t="n">
+        <v>240190</v>
+      </c>
+      <c r="L65" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd Hits All-Time High of Rs 4640.95 as Momentum Builds Across Timeframes - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd Hits All-Time High of Rs 4640.95 as Momentum Builds Across Timeframes - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>5</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ICIL.NS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ICIL</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>388.7000122070312</v>
+      </c>
+      <c r="F66" t="n">
+        <v>462</v>
+      </c>
+      <c r="G66" t="n">
+        <v>387.0499877929688</v>
+      </c>
+      <c r="H66" t="n">
+        <v>437.7000122070312</v>
+      </c>
+      <c r="I66" t="n">
+        <v>388.7000122070312</v>
+      </c>
+      <c r="J66" t="n">
+        <v>437.7000122070312</v>
+      </c>
+      <c r="K66" t="n">
+        <v>25217469</v>
+      </c>
+      <c r="L66" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>6</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SIGACHI.NS</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SIGACHI</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>25.90999984741211</v>
+      </c>
+      <c r="F67" t="n">
+        <v>30.09000015258789</v>
+      </c>
+      <c r="G67" t="n">
+        <v>25.90999984741211</v>
+      </c>
+      <c r="H67" t="n">
+        <v>29.61000061035156</v>
+      </c>
+      <c r="I67" t="n">
+        <v>26.35000038146973</v>
+      </c>
+      <c r="J67" t="n">
+        <v>29.61000061035156</v>
+      </c>
+      <c r="K67" t="n">
+        <v>10330178</v>
+      </c>
+      <c r="L67" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Sigachi posts Q1 FY 2026-27 earnings call audio on website - TipRanks</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Sigachi posts Q1 FY 2026-27 earnings call audio on website - TipRanks</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>7</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MACPOWER.NS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>MACPOWER</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1782.5</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1782.5</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1983.599975585938</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1781.400024414062</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1983.599975585938</v>
+      </c>
+      <c r="K68" t="n">
+        <v>190615</v>
+      </c>
+      <c r="L68" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Macpower CNC Machines Ltd. Share Price Rises 8.64% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Macpower CNC Machines Ltd. Share Price Rises 8.64% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Macpower CNC Machines Ltd. Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>8</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>JINDRILL.NS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>JINDRILL</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>587.0999755859375</v>
+      </c>
+      <c r="F69" t="n">
+        <v>673.5499877929688</v>
+      </c>
+      <c r="G69" t="n">
+        <v>587.0999755859375</v>
+      </c>
+      <c r="H69" t="n">
+        <v>651.1500244140625</v>
+      </c>
+      <c r="I69" t="n">
+        <v>586.2000122070312</v>
+      </c>
+      <c r="J69" t="n">
+        <v>651.1500244140625</v>
+      </c>
+      <c r="K69" t="n">
+        <v>17885600</v>
+      </c>
+      <c r="L69" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>9</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>INDSWFTLAB.NS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>INDSWFTLAB</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>317.9500122070312</v>
+      </c>
+      <c r="F70" t="n">
+        <v>351.2999877929688</v>
+      </c>
+      <c r="G70" t="n">
+        <v>316.8999938964844</v>
+      </c>
+      <c r="H70" t="n">
+        <v>346.8699951171875</v>
+      </c>
+      <c r="I70" t="n">
+        <v>313.0199890136719</v>
+      </c>
+      <c r="J70" t="n">
+        <v>346.8699951171875</v>
+      </c>
+      <c r="K70" t="n">
+        <v>5070304</v>
+      </c>
+      <c r="L70" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - Univest</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - Univest</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Sets Q1 FY27 Earnings Call for August 17 - TipRanks</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>10</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ABINFRA.NS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ABINFRA</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>11.32999992370605</v>
+      </c>
+      <c r="F71" t="n">
+        <v>12.98999977111816</v>
+      </c>
+      <c r="G71" t="n">
+        <v>10.97999954223633</v>
+      </c>
+      <c r="H71" t="n">
+        <v>12.56999969482422</v>
+      </c>
+      <c r="I71" t="n">
+        <v>11.35999965667725</v>
+      </c>
+      <c r="J71" t="n">
+        <v>12.56999969482422</v>
+      </c>
+      <c r="K71" t="n">
+        <v>25170195</v>
+      </c>
+      <c r="L71" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>11</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>REGAAL.NS</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>REGAAL</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>90.27999877929688</v>
+      </c>
+      <c r="F72" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>88.65000152587891</v>
+      </c>
+      <c r="H72" t="n">
+        <v>99.52999877929688</v>
+      </c>
+      <c r="I72" t="n">
+        <v>90.45999908447266</v>
+      </c>
+      <c r="J72" t="n">
+        <v>99.52999877929688</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2972532</v>
+      </c>
+      <c r="L72" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Regaal Resources Q1 Results: Earnings call audio uploaded for investors - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Regaal Resources Q1 Results: Earnings Call Scheduled for August 17 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Regaal Resources Ltd Surges 17% to Hit Upper Circuit Amid Robust Buying Pressure - MarketsMojo</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>12</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>PARAS.NS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>PARAS</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1385</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1527.300048828125</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1384.699951171875</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1527.300048828125</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1388.5</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1527.300048828125</v>
+      </c>
+      <c r="K73" t="n">
+        <v>5405026</v>
+      </c>
+      <c r="L73" t="n">
+        <v>10</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Paras Defence, Zen Tech, other defence shares rise up to 8% as MoD notifies sixth Positive Indigenisation... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Paras Defence Hits 52-Week High, Up 163% From Low - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Paras Defence zooms 163% from March low; hits 52-week high on huge volume - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Paras Defence Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>13</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS.NS</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1305.75</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1165</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1305.75</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1187.050048828125</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1305.75</v>
+      </c>
+      <c r="K74" t="n">
+        <v>9337471</v>
+      </c>
+      <c r="L74" t="n">
+        <v>10</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Average basic shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Dhoot Transmission Limited Statistics – NSE:DHOOTTRANS - TradingView</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>14</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>INDOMIM.NS</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>INDOMIM</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>910</v>
+      </c>
+      <c r="F75" t="n">
+        <v>952.75</v>
+      </c>
+      <c r="G75" t="n">
+        <v>905</v>
+      </c>
+      <c r="H75" t="n">
+        <v>952.75</v>
+      </c>
+      <c r="I75" t="n">
+        <v>866.1500244140625</v>
+      </c>
+      <c r="J75" t="n">
+        <v>952.75</v>
+      </c>
+      <c r="K75" t="n">
+        <v>10245867</v>
+      </c>
+      <c r="L75" t="n">
+        <v>10</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Indo-MIM shares hit 10% upper circuit on strong Q1 growth as raw material costs decline 11% in June quarter - Upstox</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Stocks to watch, August 18: GMR Airports, Oberoi Realty, Paytm, Nelco, INDO-MIM, Netweb Technologies - Dailyhunt</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>INDOMIM Historical Data - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>INDO-MIM Board Clears Q1 FY27 Results, New Secretarial Auditor and ESOP Ratification - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Indo-MIM shares decline ahead of Q1 results; here's how the stock is performing vs issue price - Dailyhunt</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>15</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BI.NS</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>BI</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>94</v>
+      </c>
+      <c r="F76" t="n">
+        <v>101.379997253418</v>
+      </c>
+      <c r="G76" t="n">
+        <v>92.16999816894531</v>
+      </c>
+      <c r="H76" t="n">
+        <v>101.379997253418</v>
+      </c>
+      <c r="I76" t="n">
+        <v>92.16999816894531</v>
+      </c>
+      <c r="J76" t="n">
+        <v>101.379997253418</v>
+      </c>
+      <c r="K76" t="n">
+        <v>523283</v>
+      </c>
+      <c r="L76" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>16</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>NITINSPIN.NS</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NITINSPIN</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>556.75</v>
+      </c>
+      <c r="F77" t="n">
+        <v>610</v>
+      </c>
+      <c r="G77" t="n">
+        <v>554.5</v>
+      </c>
+      <c r="H77" t="n">
+        <v>606.9000244140625</v>
+      </c>
+      <c r="I77" t="n">
+        <v>553.75</v>
+      </c>
+      <c r="J77" t="n">
+        <v>606.9000244140625</v>
+      </c>
+      <c r="K77" t="n">
+        <v>3703976</v>
+      </c>
+      <c r="L77" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>17</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ABCOTS.NS</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ABCOTS</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>202.4799957275391</v>
+      </c>
+      <c r="F78" t="n">
+        <v>225</v>
+      </c>
+      <c r="G78" t="n">
+        <v>201.8800048828125</v>
+      </c>
+      <c r="H78" t="n">
+        <v>217.3999938964844</v>
+      </c>
+      <c r="I78" t="n">
+        <v>199.6600036621094</v>
+      </c>
+      <c r="J78" t="n">
+        <v>217.3999938964844</v>
+      </c>
+      <c r="K78" t="n">
+        <v>152577</v>
+      </c>
+      <c r="L78" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>AB Cotspin India Ltd. Share Price Today: Textile Stock Up - Univest</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>AB Cotspin India Ltd. Share Price Today: Textile Stock Up - Univest</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>AB Cotspin India Ltd. Share Price and 52-Week Low Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>AB Cotspin India Board Clears Q1 FY27 Results, Appoints New Compliance Officer - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>A B Cotspin India clears Q1 FY27 results, appoints new compliance chief - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>18</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ASIANENE.NS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ASIANENE</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>426.8999938964844</v>
+      </c>
+      <c r="F79" t="n">
+        <v>465.1000061035156</v>
+      </c>
+      <c r="G79" t="n">
+        <v>419.7999877929688</v>
+      </c>
+      <c r="H79" t="n">
+        <v>463.0499877929688</v>
+      </c>
+      <c r="I79" t="n">
+        <v>425.25</v>
+      </c>
+      <c r="J79" t="n">
+        <v>463.0499877929688</v>
+      </c>
+      <c r="K79" t="n">
+        <v>3647695</v>
+      </c>
+      <c r="L79" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Share Price Today and Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Share Price Today and Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Share Price Today: Price Rise Review - Univest</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Share Price Today: Fall and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Files June-Quarter Unaudited Results with SEBI - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>19</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SUNDARAM.NS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>SUNDARAM</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1.159999966621399</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1.240000009536743</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1.149999976158142</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1.230000019073486</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1.129999995231628</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1.230000019073486</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1399675</v>
+      </c>
+      <c r="L80" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>20</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PVP.NS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>PVP</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>36.79999923706055</v>
+      </c>
+      <c r="F81" t="n">
+        <v>40.90000152587891</v>
+      </c>
+      <c r="G81" t="n">
+        <v>36.40000152587891</v>
+      </c>
+      <c r="H81" t="n">
+        <v>40.20000076293945</v>
+      </c>
+      <c r="I81" t="n">
+        <v>37.0099983215332</v>
+      </c>
+      <c r="J81" t="n">
+        <v>40.20000076293945</v>
+      </c>
+      <c r="K81" t="n">
+        <v>3327170</v>
+      </c>
+      <c r="L81" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - Univest</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Broad-Based Technical Strength Lifts PVP Ventures Ltd to 52-Week High of Rs 39.89 - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>PVP Ventures Q1 FY27 Results: Revenue grew to Rs 46 Cr, PAT new - Univest</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Only 7% of Escape from Tarkov Players Are In Standard PvP Mode - insider-gaming.com</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd Downgraded to Strong Sell Amid Mixed Financial and Technical Signals - MarketsMojo</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4104,7 +5280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6442,7 +7618,6 @@
           <t>Hardwyn India net profit falls 22% to ₹28 million in Q1FY26 - scanx.trade</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6507,7 +7682,6 @@
           <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6631,9 +7805,6 @@
           <t>Hold Ahluwalia Contracts India; target of Rs 780: ICICI Securities - TradingView</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6747,11 +7918,6 @@
       <c r="L47" t="n">
         <v>-7.93</v>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6816,7 +7982,6 @@
           <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6876,8 +8041,6 @@
           <t>DCM Shriram International Ltd. Share Price Today After Fall - Univest</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6922,11 +8085,6 @@
       <c r="L50" t="n">
         <v>-7.08</v>
       </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6986,8 +8144,6 @@
           <t>Tarsons Products Share Price Rise: Technicals, Valuation - Univest</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7042,9 +8198,6 @@
           <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7099,9 +8252,6 @@
           <t>Landmark Property Development Company Ltd. (LPDC) Share Price Rises 12.24% Today - Univest</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7146,11 +8296,6 @@
       <c r="L54" t="n">
         <v>-6.12</v>
       </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7205,9 +8350,6 @@
           <t>Signet Industries Ltd. Share Price Rise With Valuation View - Univest</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7252,11 +8394,6 @@
       <c r="L56" t="n">
         <v>-5.98</v>
       </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7301,11 +8438,6 @@
       <c r="L57" t="n">
         <v>-5.7</v>
       </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7503,8 +8635,6 @@
           <t>Atal Realtech Share Price Near ATH With Fundamental View - Univest</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7549,11 +8679,1194 @@
       <c r="L61" t="n">
         <v>-5.24</v>
       </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>HARDWYN.NS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>HARDWYN</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>10.94999980926514</v>
+      </c>
+      <c r="F62" t="n">
+        <v>11.10999965667725</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8.800000190734863</v>
+      </c>
+      <c r="H62" t="n">
+        <v>9.420000076293945</v>
+      </c>
+      <c r="I62" t="n">
+        <v>10.94999980926514</v>
+      </c>
+      <c r="J62" t="n">
+        <v>9.420000076293945</v>
+      </c>
+      <c r="K62" t="n">
+        <v>9633380</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-13.97</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Hardwyn India Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Hardwyn India Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Hardwyn Q1 FY27 Results: Revenue fell to Rs 35 Cr, PAT -25% - Univest</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hardwyn India net profit falls 22% to ₹28 million in Q1FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Hardwyn India Ltd is Rated Sell - MarketsMojo</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>KRISHIVAL.NS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>KRISHIVAL</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>403</v>
+      </c>
+      <c r="F63" t="n">
+        <v>403</v>
+      </c>
+      <c r="G63" t="n">
+        <v>350.6000061035156</v>
+      </c>
+      <c r="H63" t="n">
+        <v>355.75</v>
+      </c>
+      <c r="I63" t="n">
+        <v>408.2999877929688</v>
+      </c>
+      <c r="J63" t="n">
+        <v>355.75</v>
+      </c>
+      <c r="K63" t="n">
+        <v>170799</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-12.87</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Krishival Foods lists converted equity shares on NSE and BSE - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Krishival Foods Standalone June 2026 Net Sales at Rs 37.38 crore, up 9.79% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Krishival Foods utilizes ₹799.15 lakh of rights issue funds in Q4FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>NELCO.NS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NELCO</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1092.300048828125</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1098</v>
+      </c>
+      <c r="G64" t="n">
+        <v>938.5999755859375</v>
+      </c>
+      <c r="H64" t="n">
+        <v>948.7999877929688</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1081.5</v>
+      </c>
+      <c r="J64" t="n">
+        <v>948.7999877929688</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2128333</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-12.27</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Nelco Share Price Falls over 12%: Why the $20 Million Elveo Investment Has Investors Worried - India Infoline</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Tata's Nelco shares tumble 12% on Tuesday after ₹1,120 peak - NewsBytes</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-18 — cnbctv:f2ab86df1094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Nelco invests $20 mn in US-based Elveo for satellite connectivity; shares fall 12% - Upstox</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Tata Group stock: Nelco zooms 108% from March low; hits 52-week high - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AHLUCONT.NS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AHLUCONT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>776</v>
+      </c>
+      <c r="F65" t="n">
+        <v>782.4000244140625</v>
+      </c>
+      <c r="G65" t="n">
+        <v>702.5</v>
+      </c>
+      <c r="H65" t="n">
+        <v>707.7000122070312</v>
+      </c>
+      <c r="I65" t="n">
+        <v>793.8499755859375</v>
+      </c>
+      <c r="J65" t="n">
+        <v>707.7000122070312</v>
+      </c>
+      <c r="K65" t="n">
+        <v>545834</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-10.85</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Hold Ahluwalia Contracts India; target of Rs 780: ICICI Securities - TradingView</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Hold Ahluwalia Contracts India; target of Rs 780: ICICI Securities - TradingView</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>5</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PRAXIS.NS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>PRAXIS</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6.039999961853027</v>
+      </c>
+      <c r="F66" t="n">
+        <v>6.039999961853027</v>
+      </c>
+      <c r="G66" t="n">
+        <v>5.349999904632568</v>
+      </c>
+      <c r="H66" t="n">
+        <v>5.400000095367432</v>
+      </c>
+      <c r="I66" t="n">
+        <v>5.869999885559082</v>
+      </c>
+      <c r="J66" t="n">
+        <v>5.400000095367432</v>
+      </c>
+      <c r="K66" t="n">
+        <v>554400</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-8.01</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Praxis Home Retail Share Price Today: Price Fall Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Praxis Home Retail Share Price Today: Price Fall Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Praxis Precision Medicines stock hits 52-week high at 388.27 USD - Investing.com India</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>9,840 Shares in Praxis Precision Medicines, Inc. $PRAX Purchased by Handelsbanken Fonder AB - MarketBeat</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Praxis Precision Medicines (PRAX): Orbis, Allan Gray disclose 5.5% ownership stake - stocktitan.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>6</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SHYAMTEL.NS</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SHYAMTEL</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F67" t="n">
+        <v>14.94999980926514</v>
+      </c>
+      <c r="G67" t="n">
+        <v>13.90999984741211</v>
+      </c>
+      <c r="H67" t="n">
+        <v>13.9399995803833</v>
+      </c>
+      <c r="I67" t="n">
+        <v>15.14000034332275</v>
+      </c>
+      <c r="J67" t="n">
+        <v>13.9399995803833</v>
+      </c>
+      <c r="K67" t="n">
+        <v>7220</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-7.93</v>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>7</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>THOMASCOTT.NS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>THOMASCOTT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>293</v>
+      </c>
+      <c r="F68" t="n">
+        <v>297.1499938964844</v>
+      </c>
+      <c r="G68" t="n">
+        <v>276</v>
+      </c>
+      <c r="H68" t="n">
+        <v>278.7999877929688</v>
+      </c>
+      <c r="I68" t="n">
+        <v>301.1000061035156</v>
+      </c>
+      <c r="J68" t="n">
+        <v>278.7999877929688</v>
+      </c>
+      <c r="K68" t="n">
+        <v>360673</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-7.41</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - Univest</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - Univest</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>8</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DCMSIL.NS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>DCMSIL</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>74</v>
+      </c>
+      <c r="F69" t="n">
+        <v>75.48999786376953</v>
+      </c>
+      <c r="G69" t="n">
+        <v>67.16000366210938</v>
+      </c>
+      <c r="H69" t="n">
+        <v>68.94000244140625</v>
+      </c>
+      <c r="I69" t="n">
+        <v>74.26000213623047</v>
+      </c>
+      <c r="J69" t="n">
+        <v>68.94000244140625</v>
+      </c>
+      <c r="K69" t="n">
+        <v>208024</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-7.16</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>DCMSIL Share Price Today - DCM Shriram International Ltd. Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>DCM Shriram International Ltd. Share Price Today After Fall - Univest</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>DCM Shriram International Ltd. Share Price Today After Fall - Univest</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>9</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>KANPRPLA.NS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>KANPRPLA</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>263</v>
+      </c>
+      <c r="F70" t="n">
+        <v>266.3900146484375</v>
+      </c>
+      <c r="G70" t="n">
+        <v>240.5</v>
+      </c>
+      <c r="H70" t="n">
+        <v>244.25</v>
+      </c>
+      <c r="I70" t="n">
+        <v>262.8500061035156</v>
+      </c>
+      <c r="J70" t="n">
+        <v>244.25</v>
+      </c>
+      <c r="K70" t="n">
+        <v>54440</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-7.08</v>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>10</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>TARSONS.NS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>TARSONS</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>365</v>
+      </c>
+      <c r="F71" t="n">
+        <v>365</v>
+      </c>
+      <c r="G71" t="n">
+        <v>332</v>
+      </c>
+      <c r="H71" t="n">
+        <v>336.6499938964844</v>
+      </c>
+      <c r="I71" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="J71" t="n">
+        <v>336.6499938964844</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1199280</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-6.87</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Tarsons Products Ltd. Share Price Today Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Tarsons Products Ltd. Share Price Today Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Tarsons Products Q1 Results: Earnings call audio uploaded - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Tarsons Products Share Price Rise: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>11</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>S&amp;SPOWER.NS</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>S&amp;SPOWER</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>296</v>
+      </c>
+      <c r="F72" t="n">
+        <v>296</v>
+      </c>
+      <c r="G72" t="n">
+        <v>270</v>
+      </c>
+      <c r="H72" t="n">
+        <v>277.7000122070312</v>
+      </c>
+      <c r="I72" t="n">
+        <v>297.7000122070312</v>
+      </c>
+      <c r="J72" t="n">
+        <v>277.7000122070312</v>
+      </c>
+      <c r="K72" t="n">
+        <v>10586</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-6.72</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>12</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>LPDC.NS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LPDC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>7.860000133514404</v>
+      </c>
+      <c r="F73" t="n">
+        <v>7.860000133514404</v>
+      </c>
+      <c r="G73" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="H73" t="n">
+        <v>7.380000114440918</v>
+      </c>
+      <c r="I73" t="n">
+        <v>7.869999885559082</v>
+      </c>
+      <c r="J73" t="n">
+        <v>7.380000114440918</v>
+      </c>
+      <c r="K73" t="n">
+        <v>96741</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-6.23</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Landmark Property Development Company Ltd. (LPDC) Share Price Rises 12.24% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Landmark Property Development Company Ltd. (LPDC) Share Price Rises 12.24% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>13</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>JUBLCPL.NS</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>JUBLCPL</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>2362.39990234375</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2397.89990234375</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2142</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2199.10009765625</v>
+      </c>
+      <c r="I74" t="n">
+        <v>2342.39990234375</v>
+      </c>
+      <c r="J74" t="n">
+        <v>2199.10009765625</v>
+      </c>
+      <c r="K74" t="n">
+        <v>16482</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>14</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SIGIND.NS</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SIGIND</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>70.84999847412109</v>
+      </c>
+      <c r="F75" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>65.31999969482422</v>
+      </c>
+      <c r="H75" t="n">
+        <v>66.84999847412109</v>
+      </c>
+      <c r="I75" t="n">
+        <v>71.15000152587891</v>
+      </c>
+      <c r="J75" t="n">
+        <v>66.84999847412109</v>
+      </c>
+      <c r="K75" t="n">
+        <v>95414</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-6.04</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Signet Industries Ltd. Share Price Rise With Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Signet Industries Ltd. Share Price Rise With Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>15</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>NDLVENTURE.NS</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NDLVENTURE</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>122.1500015258789</v>
+      </c>
+      <c r="F76" t="n">
+        <v>122.7399978637695</v>
+      </c>
+      <c r="G76" t="n">
+        <v>113.9499969482422</v>
+      </c>
+      <c r="H76" t="n">
+        <v>116.1699981689453</v>
+      </c>
+      <c r="I76" t="n">
+        <v>123.5599975585938</v>
+      </c>
+      <c r="J76" t="n">
+        <v>116.1699981689453</v>
+      </c>
+      <c r="K76" t="n">
+        <v>57175</v>
+      </c>
+      <c r="L76" t="n">
+        <v>-5.98</v>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>16</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MOIL.NS</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>MOIL</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>271.2000122070312</v>
+      </c>
+      <c r="F77" t="n">
+        <v>271.7999877929688</v>
+      </c>
+      <c r="G77" t="n">
+        <v>255.6000061035156</v>
+      </c>
+      <c r="H77" t="n">
+        <v>257.25</v>
+      </c>
+      <c r="I77" t="n">
+        <v>272.7999877929688</v>
+      </c>
+      <c r="J77" t="n">
+        <v>257.25</v>
+      </c>
+      <c r="K77" t="n">
+        <v>2810988</v>
+      </c>
+      <c r="L77" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>17</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>APEX.NS</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>APEX</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>424</v>
+      </c>
+      <c r="F78" t="n">
+        <v>427.7999877929688</v>
+      </c>
+      <c r="G78" t="n">
+        <v>395.3999938964844</v>
+      </c>
+      <c r="H78" t="n">
+        <v>398.5</v>
+      </c>
+      <c r="I78" t="n">
+        <v>422.5499877929688</v>
+      </c>
+      <c r="J78" t="n">
+        <v>398.5</v>
+      </c>
+      <c r="K78" t="n">
+        <v>944026</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-5.69</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Apex Capital An Standalone June 2026 Net Sales at Rs 2.47 crore, up 65.98% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Apex Capital An Standalone June 2026 Net Sales at Rs 2.47 crore, up 65.98% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Apex Frozen Food shares zoom 19% after Q1FY27 net profit jumps 140% YoY - Upstox</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Apex Frozen Foods shares hit 20% upper circuit after Q1 profit more than doubles - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Apex Frozen Foods Share Price Rises 11.95%: Full Analysis - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>18</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AGL.NS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AGL</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>14</v>
+      </c>
+      <c r="F79" t="n">
+        <v>14.01000022888184</v>
+      </c>
+      <c r="G79" t="n">
+        <v>13.02999973297119</v>
+      </c>
+      <c r="H79" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="I79" t="n">
+        <v>14.01000022888184</v>
+      </c>
+      <c r="J79" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="K79" t="n">
+        <v>3444947</v>
+      </c>
+      <c r="L79" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>AGL Energy Shares Up 1.9% as Battery Performance Offsets 47% Electricity Price Fall - TechStock²</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>AGL Energy Shares Up 1.9% as Battery Performance Offsets 47% Electricity Price Fall - TechStock²</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Allcargo Global Ltd Share Price Today,, AGL Share Price NSE, BSE - businesstoday.in</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Why is AGL Energy stock surging today? - Investing.com</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Agilon Health Inc (AGL) Stock Up 9.0% but GF Value Says Overvalued -- GF Score: 71/100 - GuruFocus</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>19</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ATALREAL.NS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ATALREAL</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>36.09999847412109</v>
+      </c>
+      <c r="F80" t="n">
+        <v>36.33000183105469</v>
+      </c>
+      <c r="G80" t="n">
+        <v>31.42000007629395</v>
+      </c>
+      <c r="H80" t="n">
+        <v>33.93000030517578</v>
+      </c>
+      <c r="I80" t="n">
+        <v>35.84999847412109</v>
+      </c>
+      <c r="J80" t="n">
+        <v>33.93000030517578</v>
+      </c>
+      <c r="K80" t="n">
+        <v>20786651</v>
+      </c>
+      <c r="L80" t="n">
+        <v>-5.36</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Atal Realtech Share Price Near ATH With Fundamental View - Univest</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:38</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>20</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>NDGL.NS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NDGL</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>2875</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2875</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2669</v>
+      </c>
+      <c r="H81" t="n">
+        <v>2727.89990234375</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2878.699951171875</v>
+      </c>
+      <c r="J81" t="n">
+        <v>2727.89990234375</v>
+      </c>
+      <c r="K81" t="n">
+        <v>558</v>
+      </c>
+      <c r="L81" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4171,9 +4171,6 @@
           <t>Subex Ltd. Share Price Gain: Price Action and Valuation - Univest</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4228,9 +4225,6 @@
           <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4290,8 +4284,6 @@
           <t>Yasho Industries Ltd Hits All-Time High of Rs 4640.95 as Momentum Builds Across Timeframes - MarketsMojo</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4336,11 +4328,6 @@
       <c r="L66" t="n">
         <v>12.61</v>
       </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4395,9 +4382,6 @@
           <t>Sigachi posts Q1 FY 2026-27 earnings call audio on website - TipRanks</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4457,8 +4441,6 @@
           <t>Macpower CNC Machines Ltd. Share Price News and Analysis - Univest</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4503,11 +4485,6 @@
       <c r="L69" t="n">
         <v>11.08</v>
       </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4567,8 +4544,6 @@
           <t>Ind-Swift Laboratories Sets Q1 FY27 Earnings Call for August 17 - TipRanks</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4613,11 +4588,6 @@
       <c r="L71" t="n">
         <v>10.65</v>
       </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4820,7 +4790,6 @@
           <t>Dhoot Transmission Limited Statistics – NSE:DHOOTTRANS - TradingView</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4944,9 +4913,6 @@
           <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5001,9 +4967,6 @@
           <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - Univest</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5196,9 +5159,6 @@
           <t>Sundaram Brake Linings Ltd. Share Price Near 52-Week High - Univest</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5266,6 +5226,1210 @@
       <c r="Q81" t="inlineStr">
         <is>
           <t>PVP Ventures Ltd Downgraded to Strong Sell Amid Mixed Financial and Technical Signals - MarketsMojo</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SIGACHI.NS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>SIGACHI</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>25.90999984741211</v>
+      </c>
+      <c r="F82" t="n">
+        <v>30.09000015258789</v>
+      </c>
+      <c r="G82" t="n">
+        <v>25.90999984741211</v>
+      </c>
+      <c r="H82" t="n">
+        <v>29.61000061035156</v>
+      </c>
+      <c r="I82" t="n">
+        <v>26.35000038146973</v>
+      </c>
+      <c r="J82" t="n">
+        <v>29.61000061035156</v>
+      </c>
+      <c r="K82" t="n">
+        <v>10361044</v>
+      </c>
+      <c r="L82" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Sigachi posts Q1 FY 2026-27 earnings call audio on website - TipRanks</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Sigachi posts Q1 FY 2026-27 earnings call audio on website - TipRanks</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>JINDRILL.NS</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>JINDRILL</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>587.0999755859375</v>
+      </c>
+      <c r="F83" t="n">
+        <v>673.5499877929688</v>
+      </c>
+      <c r="G83" t="n">
+        <v>587.0999755859375</v>
+      </c>
+      <c r="H83" t="n">
+        <v>651.1500244140625</v>
+      </c>
+      <c r="I83" t="n">
+        <v>586.2000122070312</v>
+      </c>
+      <c r="J83" t="n">
+        <v>651.1500244140625</v>
+      </c>
+      <c r="K83" t="n">
+        <v>17885822</v>
+      </c>
+      <c r="L83" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>3</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ABINFRA.NS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ABINFRA</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>11.32999992370605</v>
+      </c>
+      <c r="F84" t="n">
+        <v>12.98999977111816</v>
+      </c>
+      <c r="G84" t="n">
+        <v>10.97999954223633</v>
+      </c>
+      <c r="H84" t="n">
+        <v>12.56999969482422</v>
+      </c>
+      <c r="I84" t="n">
+        <v>11.35999965667725</v>
+      </c>
+      <c r="J84" t="n">
+        <v>12.56999969482422</v>
+      </c>
+      <c r="K84" t="n">
+        <v>25170295</v>
+      </c>
+      <c r="L84" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>4</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>REGAAL.NS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>REGAAL</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>90.27999877929688</v>
+      </c>
+      <c r="F85" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="G85" t="n">
+        <v>88.65000152587891</v>
+      </c>
+      <c r="H85" t="n">
+        <v>99.52999877929688</v>
+      </c>
+      <c r="I85" t="n">
+        <v>90.45999908447266</v>
+      </c>
+      <c r="J85" t="n">
+        <v>99.52999877929688</v>
+      </c>
+      <c r="K85" t="n">
+        <v>2975990</v>
+      </c>
+      <c r="L85" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Regaal Resources Q1 Results: Earnings call audio uploaded for investors - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Regaal Resources Ltd Surges 17% to Hit Upper Circuit Amid Robust Buying Pressure - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>5</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>INDOMIM.NS</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>INDOMIM</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>910</v>
+      </c>
+      <c r="F86" t="n">
+        <v>952.75</v>
+      </c>
+      <c r="G86" t="n">
+        <v>905</v>
+      </c>
+      <c r="H86" t="n">
+        <v>952.75</v>
+      </c>
+      <c r="I86" t="n">
+        <v>866.1500244140625</v>
+      </c>
+      <c r="J86" t="n">
+        <v>952.75</v>
+      </c>
+      <c r="K86" t="n">
+        <v>10246021</v>
+      </c>
+      <c r="L86" t="n">
+        <v>10</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Indo-MIM shares hit 10% upper circuit on strong Q1 growth as raw material costs decline 11% in June quarter - Upstox</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Indo-MIM shares hit 10% upper circuit on strong Q1 growth as raw material costs decline 11% in June quarter - Upstox</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>INDOMIM Historical Data - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Stocks to watch, August 18: GMR Airports, Oberoi Realty, Paytm, Nelco, INDO-MIM, Netweb Technologies - Upstox</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Indo-MIM shares decline ahead of Q1 results; here's how the stock is performing vs issue price - Dailyhunt</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>6</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BI.NS</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>BI</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>94</v>
+      </c>
+      <c r="F87" t="n">
+        <v>101.379997253418</v>
+      </c>
+      <c r="G87" t="n">
+        <v>92.16999816894531</v>
+      </c>
+      <c r="H87" t="n">
+        <v>101.379997253418</v>
+      </c>
+      <c r="I87" t="n">
+        <v>92.16999816894531</v>
+      </c>
+      <c r="J87" t="n">
+        <v>101.379997253418</v>
+      </c>
+      <c r="K87" t="n">
+        <v>523283</v>
+      </c>
+      <c r="L87" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>7</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>NITINSPIN.NS</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NITINSPIN</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>556.75</v>
+      </c>
+      <c r="F88" t="n">
+        <v>610</v>
+      </c>
+      <c r="G88" t="n">
+        <v>554.5</v>
+      </c>
+      <c r="H88" t="n">
+        <v>606.9000244140625</v>
+      </c>
+      <c r="I88" t="n">
+        <v>553.75</v>
+      </c>
+      <c r="J88" t="n">
+        <v>606.9000244140625</v>
+      </c>
+      <c r="K88" t="n">
+        <v>3703991</v>
+      </c>
+      <c r="L88" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - univest.in</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - univest.in</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>8</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ABCOTS.NS</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ABCOTS</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>202.4799957275391</v>
+      </c>
+      <c r="F89" t="n">
+        <v>225</v>
+      </c>
+      <c r="G89" t="n">
+        <v>201.8800048828125</v>
+      </c>
+      <c r="H89" t="n">
+        <v>217.3999938964844</v>
+      </c>
+      <c r="I89" t="n">
+        <v>199.6600036621094</v>
+      </c>
+      <c r="J89" t="n">
+        <v>217.3999938964844</v>
+      </c>
+      <c r="K89" t="n">
+        <v>152579</v>
+      </c>
+      <c r="L89" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>AB Cotspin India Ltd. Share Price Today: Textile Stock Up - univest.in</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>AB Cotspin India Ltd. Share Price Today: Textile Stock Up - univest.in</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>ABCOTS Share Price Today - AB Cotspin on NSE/BSE - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>AB Cotspin India Ltd. Share Price and 52-Week Low Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>AB Cotspin India Board Clears Q1 FY27 Results, Appoints New Compliance Officer - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>9</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>PVP.NS</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>PVP</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>36.79999923706055</v>
+      </c>
+      <c r="F90" t="n">
+        <v>40.90000152587891</v>
+      </c>
+      <c r="G90" t="n">
+        <v>36.40000152587891</v>
+      </c>
+      <c r="H90" t="n">
+        <v>40.20000076293945</v>
+      </c>
+      <c r="I90" t="n">
+        <v>37.0099983215332</v>
+      </c>
+      <c r="J90" t="n">
+        <v>40.20000076293945</v>
+      </c>
+      <c r="K90" t="n">
+        <v>3330020</v>
+      </c>
+      <c r="L90" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd. Share Price Gain: Technicals, Valuation - univest.in</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Broad-Based Technical Strength Lifts PVP Ventures Ltd to 52-Week High of Rs 39.89 - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - univest.in</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>PVP Ventures Q1 FY27 Results: Revenue grew to Rs 46 Cr, PAT new - univest.in</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Only 7% of Escape from Tarkov Players Are In Standard PvP Mode - Insider Gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>10</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>EMUDHRA.NS</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>EMUDHRA</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>517.7000122070312</v>
+      </c>
+      <c r="F91" t="n">
+        <v>565</v>
+      </c>
+      <c r="G91" t="n">
+        <v>509</v>
+      </c>
+      <c r="H91" t="n">
+        <v>562.0499877929688</v>
+      </c>
+      <c r="I91" t="n">
+        <v>518.75</v>
+      </c>
+      <c r="J91" t="n">
+        <v>562.0499877929688</v>
+      </c>
+      <c r="K91" t="n">
+        <v>705436</v>
+      </c>
+      <c r="L91" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Navi Mumbai police closes 3i Infotech complaint against eMudhra as civil dispute - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Navi Mumbai police closes 3i Infotech complaint against eMudhra as civil dispute - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>eMudhra Ltd. Share Price Today - eMudhra Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>eMudhra shares surge as police close 3i Infotech's fraud complaint - Whalesbook</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>eMudhra Ltd Surges 7.59% to Day's High of Rs 564 — Outperforms Sector by 8.85 Percentage Points - MarketsMojo</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>11</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>JYOTICNC.NS</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>JYOTICNC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>870</v>
+      </c>
+      <c r="F92" t="n">
+        <v>947.9000244140625</v>
+      </c>
+      <c r="G92" t="n">
+        <v>860.0499877929688</v>
+      </c>
+      <c r="H92" t="n">
+        <v>929.2000122070312</v>
+      </c>
+      <c r="I92" t="n">
+        <v>857.9500122070312</v>
+      </c>
+      <c r="J92" t="n">
+        <v>929.2000122070312</v>
+      </c>
+      <c r="K92" t="n">
+        <v>5438972</v>
+      </c>
+      <c r="L92" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Indian Export Stocks Retail Investors May Watch As US Scrutiny Of Transshipment Grows - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>JYOTICNC Share Price | Jyoti CNC Automation Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>JYOTICNC Share Price | Jyoti CNC Automation Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>12</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>TIINDIA.NS</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>2755.800048828125</v>
+      </c>
+      <c r="F93" t="n">
+        <v>2989</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2755.800048828125</v>
+      </c>
+      <c r="H93" t="n">
+        <v>2959</v>
+      </c>
+      <c r="I93" t="n">
+        <v>2741.39990234375</v>
+      </c>
+      <c r="J93" t="n">
+        <v>2959</v>
+      </c>
+      <c r="K93" t="n">
+        <v>4188005</v>
+      </c>
+      <c r="L93" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>TIINDIA Share Price | Tube Investments of India Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>TIINDIA Share Price | Tube Investments of India Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>13</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>KPEL.NS</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>KPEL</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>243.6999969482422</v>
+      </c>
+      <c r="F94" t="n">
+        <v>264.9500122070312</v>
+      </c>
+      <c r="G94" t="n">
+        <v>240</v>
+      </c>
+      <c r="H94" t="n">
+        <v>262.2999877929688</v>
+      </c>
+      <c r="I94" t="n">
+        <v>243.75</v>
+      </c>
+      <c r="J94" t="n">
+        <v>262.2999877929688</v>
+      </c>
+      <c r="K94" t="n">
+        <v>859476</v>
+      </c>
+      <c r="L94" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>14</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>MMFL.NS</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>MMFL</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>639.7000122070312</v>
+      </c>
+      <c r="F95" t="n">
+        <v>687.9500122070312</v>
+      </c>
+      <c r="G95" t="n">
+        <v>632.7999877929688</v>
+      </c>
+      <c r="H95" t="n">
+        <v>680.2000122070312</v>
+      </c>
+      <c r="I95" t="n">
+        <v>632.2999877929688</v>
+      </c>
+      <c r="J95" t="n">
+        <v>680.2000122070312</v>
+      </c>
+      <c r="K95" t="n">
+        <v>935497</v>
+      </c>
+      <c r="L95" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>MM Forgings Ltd. Share Price Today Up 8.43%: Stock Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>MM Forgings Ltd. Share Price Today Up 8.43%: Stock Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>IOC Share Dividend Stocks Split MMFL KPIT TARIL Afcons Share Midwest Gold FII DII Stock Finshots Atp Rome (HN86imV77B) - Mshale</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>MM Forgings Clarifies ₹56.25 Crore Exceptional Gain from Oragadam Land Sale - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>15</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>PFOCUS.NS</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>PFOCUS</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>266.0499877929688</v>
+      </c>
+      <c r="F96" t="n">
+        <v>289</v>
+      </c>
+      <c r="G96" t="n">
+        <v>264</v>
+      </c>
+      <c r="H96" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="I96" t="n">
+        <v>266.3999938964844</v>
+      </c>
+      <c r="J96" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="K96" t="n">
+        <v>2789751</v>
+      </c>
+      <c r="L96" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>16</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>MSTCLTD.NS</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>MSTCLTD</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>658.1500244140625</v>
+      </c>
+      <c r="F97" t="n">
+        <v>709</v>
+      </c>
+      <c r="G97" t="n">
+        <v>655</v>
+      </c>
+      <c r="H97" t="n">
+        <v>701.5499877929688</v>
+      </c>
+      <c r="I97" t="n">
+        <v>653.2000122070312</v>
+      </c>
+      <c r="J97" t="n">
+        <v>701.5499877929688</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1266456</v>
+      </c>
+      <c r="L97" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>17</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>RITCO.NS</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>RITCO</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>288.0499877929688</v>
+      </c>
+      <c r="F98" t="n">
+        <v>318.3999938964844</v>
+      </c>
+      <c r="G98" t="n">
+        <v>288.0499877929688</v>
+      </c>
+      <c r="H98" t="n">
+        <v>313</v>
+      </c>
+      <c r="I98" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="J98" t="n">
+        <v>313</v>
+      </c>
+      <c r="K98" t="n">
+        <v>381642</v>
+      </c>
+      <c r="L98" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Ritco Logistics Ltd. (RITCO) Share Price Today: Price Action Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Ritco Logistics Ltd. (RITCO) Share Price Today: Price Action Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Ritco Logistics Q1 Results: Unaudited financials published - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Ritco Logistics consolidated net profit declines 43.36% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Ritco Logistics Q1 Results FY27: PAT Rs 3 Cr, Revenue Rs 365 cror - univest.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>18</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SGMART.NS</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>SGMART</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>750.6500244140625</v>
+      </c>
+      <c r="F99" t="n">
+        <v>809</v>
+      </c>
+      <c r="G99" t="n">
+        <v>744</v>
+      </c>
+      <c r="H99" t="n">
+        <v>804.9500122070312</v>
+      </c>
+      <c r="I99" t="n">
+        <v>752.2999877929688</v>
+      </c>
+      <c r="J99" t="n">
+        <v>804.9500122070312</v>
+      </c>
+      <c r="K99" t="n">
+        <v>907346</v>
+      </c>
+      <c r="L99" t="n">
+        <v>7</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>SG Mart Share Price at Fresh 52-Week High: Full Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>SG Mart Share Price at Fresh 52-Week High: Full Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>19</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>RBA.NS</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>RBA</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>99.80000305175781</v>
+      </c>
+      <c r="F100" t="n">
+        <v>108.4100036621094</v>
+      </c>
+      <c r="G100" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="H100" t="n">
+        <v>106.3399963378906</v>
+      </c>
+      <c r="I100" t="n">
+        <v>99.58999633789062</v>
+      </c>
+      <c r="J100" t="n">
+        <v>106.3399963378906</v>
+      </c>
+      <c r="K100" t="n">
+        <v>17134006</v>
+      </c>
+      <c r="L100" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>RBA stock hits 52-week low at 83.55 USD By Investing.com - Investing.com India</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>The Goldman Sachs Group, Inc. $GS Shares Sold by RBA Wealth Management LLC - marketbeat.com</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Why RB Global (RBA) Stock Is Down Today - Quiver Quantitative</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>The Goldman Sachs Group, Inc. $GS Shares Sold by RBA Wealth Management LLC - marketbeat.com</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Lenexis pledges 14.84% RBA stake to fund INR 3,873 crore acquisition debt - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>20</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>AVALON.NS</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AVALON</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>2059.39990234375</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2258</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2055.89990234375</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2197.300048828125</v>
+      </c>
+      <c r="I101" t="n">
+        <v>2059.39990234375</v>
+      </c>
+      <c r="J101" t="n">
+        <v>2197.300048828125</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1136151</v>
+      </c>
+      <c r="L101" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Avalon Technologies Share Price Today Near One-Year High - univest.in</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>98,730 Shares in The TJX Companies, Inc. $TJX Acquired by Avalon Trust Co - marketbeat.com</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Avalon Technologies Ltd. Share Price at Fresh 52-Week High - univest.in</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Avalon Trust Co Buys Shares of 35,466 Thermo Fisher Scientific Inc. $TMO - marketbeat.com</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Avalon Trust Co Purchases Shares of 8,734 The Travelers Companies, Inc. $TRV - marketbeat.com</t>
         </is>
       </c>
     </row>
@@ -5280,7 +6444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8940,9 +10104,6 @@
           <t>Hold Ahluwalia Contracts India; target of Rs 780: ICICI Securities - TradingView</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -9056,11 +10217,6 @@
       <c r="L67" t="n">
         <v>-7.93</v>
       </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9125,7 +10281,6 @@
           <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9185,8 +10340,6 @@
           <t>DCM Shriram International Ltd. Share Price Today After Fall - Univest</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9231,11 +10384,6 @@
       <c r="L70" t="n">
         <v>-7.08</v>
       </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9300,7 +10448,6 @@
           <t>Tarsons Products Share Price Rise: Technicals, Valuation - Univest</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9355,9 +10502,6 @@
           <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9412,9 +10556,6 @@
           <t>Landmark Property Development Company Ltd. (LPDC) Share Price Rises 12.24% Today - Univest</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9459,11 +10600,6 @@
       <c r="L74" t="n">
         <v>-6.12</v>
       </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9518,9 +10654,6 @@
           <t>Signet Industries Ltd. Share Price Rise With Valuation View - Univest</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9565,11 +10698,6 @@
       <c r="L76" t="n">
         <v>-5.98</v>
       </c>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9614,11 +10742,6 @@
       <c r="L77" t="n">
         <v>-5.7</v>
       </c>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9816,8 +10939,6 @@
           <t>Atal Realtech Share Price Near ATH With Fundamental View - Univest</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9862,11 +10983,1150 @@
       <c r="L81" t="n">
         <v>-5.24</v>
       </c>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>KRISHIVAL.NS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>KRISHIVAL</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>403</v>
+      </c>
+      <c r="F82" t="n">
+        <v>403</v>
+      </c>
+      <c r="G82" t="n">
+        <v>350.6000061035156</v>
+      </c>
+      <c r="H82" t="n">
+        <v>355.75</v>
+      </c>
+      <c r="I82" t="n">
+        <v>408.2999877929688</v>
+      </c>
+      <c r="J82" t="n">
+        <v>355.75</v>
+      </c>
+      <c r="K82" t="n">
+        <v>170859</v>
+      </c>
+      <c r="L82" t="n">
+        <v>-12.87</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Krishival Foods lists converted equity shares on NSE and BSE - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Krishival Foods Standalone June 2026 Net Sales at Rs 37.38 crore, up 9.79% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AHLUCONT.NS</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AHLUCONT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>776</v>
+      </c>
+      <c r="F83" t="n">
+        <v>782.4000244140625</v>
+      </c>
+      <c r="G83" t="n">
+        <v>702.5</v>
+      </c>
+      <c r="H83" t="n">
+        <v>707.7000122070312</v>
+      </c>
+      <c r="I83" t="n">
+        <v>793.8499755859375</v>
+      </c>
+      <c r="J83" t="n">
+        <v>707.7000122070312</v>
+      </c>
+      <c r="K83" t="n">
+        <v>545925</v>
+      </c>
+      <c r="L83" t="n">
+        <v>-10.85</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Hold Ahluwalia Contracts India; target of Rs 780: ICICI Securities - TradingView</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Hold Ahluwalia Contracts India; target of Rs 780: ICICI Securities - TradingView</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>3</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>THOMASCOTT.NS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>THOMASCOTT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>293</v>
+      </c>
+      <c r="F84" t="n">
+        <v>297.1499938964844</v>
+      </c>
+      <c r="G84" t="n">
+        <v>276</v>
+      </c>
+      <c r="H84" t="n">
+        <v>278.7999877929688</v>
+      </c>
+      <c r="I84" t="n">
+        <v>301.1000061035156</v>
+      </c>
+      <c r="J84" t="n">
+        <v>278.7999877929688</v>
+      </c>
+      <c r="K84" t="n">
+        <v>360674</v>
+      </c>
+      <c r="L84" t="n">
+        <v>-7.41</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - univest.in</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - univest.in</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>4</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>MOIL.NS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>MOIL</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>271.2000122070312</v>
+      </c>
+      <c r="F85" t="n">
+        <v>271.7999877929688</v>
+      </c>
+      <c r="G85" t="n">
+        <v>255.6000061035156</v>
+      </c>
+      <c r="H85" t="n">
+        <v>257.25</v>
+      </c>
+      <c r="I85" t="n">
+        <v>272.7999877929688</v>
+      </c>
+      <c r="J85" t="n">
+        <v>257.25</v>
+      </c>
+      <c r="K85" t="n">
+        <v>2820394</v>
+      </c>
+      <c r="L85" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>5</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>APEX.NS</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>APEX</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>424</v>
+      </c>
+      <c r="F86" t="n">
+        <v>427.7999877929688</v>
+      </c>
+      <c r="G86" t="n">
+        <v>395.3999938964844</v>
+      </c>
+      <c r="H86" t="n">
+        <v>398.5</v>
+      </c>
+      <c r="I86" t="n">
+        <v>422.5499877929688</v>
+      </c>
+      <c r="J86" t="n">
+        <v>398.5</v>
+      </c>
+      <c r="K86" t="n">
+        <v>944431</v>
+      </c>
+      <c r="L86" t="n">
+        <v>-5.69</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Apex Frozen Food shares zoom 19% after Q1FY27 net profit jumps 140% YoY - Upstox</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Apex Capital An Standalone June 2026 Net Sales at Rs 2.47 crore, up 65.98% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Apex Frozen Foods shares hit 20% upper circuit after Q1 profit more than doubles - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Apex Capital An Standalone June 2026 Net Sales at Rs 2.47 crore, up 65.98% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Apex Frozen Foods Share Price Rises 11.95%: Full Analysis - univest.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>6</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ATALREAL.NS</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ATALREAL</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>36.09999847412109</v>
+      </c>
+      <c r="F87" t="n">
+        <v>36.33000183105469</v>
+      </c>
+      <c r="G87" t="n">
+        <v>31.42000007629395</v>
+      </c>
+      <c r="H87" t="n">
+        <v>33.93000030517578</v>
+      </c>
+      <c r="I87" t="n">
+        <v>35.84999847412109</v>
+      </c>
+      <c r="J87" t="n">
+        <v>33.93000030517578</v>
+      </c>
+      <c r="K87" t="n">
+        <v>20814653</v>
+      </c>
+      <c r="L87" t="n">
+        <v>-5.36</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - univest.in</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - univest.in</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Atal Realtech Share Price Near ATH With Fundamental View - univest.in</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>7</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>MASTEK.NS</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>MASTEK</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1811</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1811</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1702</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1717.5</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1811.800048828125</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1717.5</v>
+      </c>
+      <c r="K88" t="n">
+        <v>103567</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Mastek Ltd. Share Price Today: Price Fall and Fundamentals - univest.in</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Mastek Ltd. Share Price Today: Price Fall and Fundamentals - univest.in</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Mastek fixes Aug 31 record date for ₹16 per share final dividend - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>8</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>INDOTHAI.NS</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>INDOTHAI</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>69.56999969482422</v>
+      </c>
+      <c r="F89" t="n">
+        <v>69.56999969482422</v>
+      </c>
+      <c r="G89" t="n">
+        <v>69.56999969482422</v>
+      </c>
+      <c r="H89" t="n">
+        <v>69.56999969482422</v>
+      </c>
+      <c r="I89" t="n">
+        <v>73.23000335693359</v>
+      </c>
+      <c r="J89" t="n">
+        <v>69.56999969482422</v>
+      </c>
+      <c r="K89" t="n">
+        <v>20979</v>
+      </c>
+      <c r="L89" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>9</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>RAMCOSYS.NS</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>RAMCOSYS</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>593.0999755859375</v>
+      </c>
+      <c r="F90" t="n">
+        <v>598</v>
+      </c>
+      <c r="G90" t="n">
+        <v>564.5</v>
+      </c>
+      <c r="H90" t="n">
+        <v>564.5</v>
+      </c>
+      <c r="I90" t="n">
+        <v>594.2000122070312</v>
+      </c>
+      <c r="J90" t="n">
+        <v>564.5</v>
+      </c>
+      <c r="K90" t="n">
+        <v>245543</v>
+      </c>
+      <c r="L90" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>10</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ABANSENT.NS</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ABANSENT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>32.79000091552734</v>
+      </c>
+      <c r="F91" t="n">
+        <v>32.79000091552734</v>
+      </c>
+      <c r="G91" t="n">
+        <v>30.29999923706055</v>
+      </c>
+      <c r="H91" t="n">
+        <v>30.29999923706055</v>
+      </c>
+      <c r="I91" t="n">
+        <v>31.88999938964844</v>
+      </c>
+      <c r="J91" t="n">
+        <v>30.29999923706055</v>
+      </c>
+      <c r="K91" t="n">
+        <v>28145</v>
+      </c>
+      <c r="L91" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>11</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SUMEETINDS.NS</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>SUMEETINDS</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>14.14000034332275</v>
+      </c>
+      <c r="F92" t="n">
+        <v>14.27999973297119</v>
+      </c>
+      <c r="G92" t="n">
+        <v>13.38000011444092</v>
+      </c>
+      <c r="H92" t="n">
+        <v>13.42000007629395</v>
+      </c>
+      <c r="I92" t="n">
+        <v>14.07999992370605</v>
+      </c>
+      <c r="J92" t="n">
+        <v>13.42000007629395</v>
+      </c>
+      <c r="K92" t="n">
+        <v>4474212</v>
+      </c>
+      <c r="L92" t="n">
+        <v>-4.69</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>12</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ARVIND.NS</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ARVIND</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>554.4500122070312</v>
+      </c>
+      <c r="F93" t="n">
+        <v>555.2000122070312</v>
+      </c>
+      <c r="G93" t="n">
+        <v>522.5999755859375</v>
+      </c>
+      <c r="H93" t="n">
+        <v>526.5</v>
+      </c>
+      <c r="I93" t="n">
+        <v>552.2999877929688</v>
+      </c>
+      <c r="J93" t="n">
+        <v>526.5</v>
+      </c>
+      <c r="K93" t="n">
+        <v>928757</v>
+      </c>
+      <c r="L93" t="n">
+        <v>-4.67</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Arvind SmartSpaces submits FY26 business responsibility report - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Arvind SmartSpaces submits FY26 business responsibility report - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: Arvind posts strong Q1 2026 growth, shares slip - Investing.com</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Arvind sees no immediate acquisitions, focuses on Dalco GFT integration - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Rubrik CTO Arvind Nithrakashyap Sells $3.0 Million Stock - fool.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>13</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SHRIKRISH.NS</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>SHRIKRISH</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>38.54999923706055</v>
+      </c>
+      <c r="F94" t="n">
+        <v>38.97000122070312</v>
+      </c>
+      <c r="G94" t="n">
+        <v>38</v>
+      </c>
+      <c r="H94" t="n">
+        <v>38.45999908447266</v>
+      </c>
+      <c r="I94" t="n">
+        <v>40.29999923706055</v>
+      </c>
+      <c r="J94" t="n">
+        <v>38.45999908447266</v>
+      </c>
+      <c r="K94" t="n">
+        <v>709</v>
+      </c>
+      <c r="L94" t="n">
+        <v>-4.57</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Shri Krishna Devcon Ltd. Share Price Fall and Stock Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Shri Krishna Devcon Ltd. Share Price Fall and Stock Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>14</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ASIANTILES.NS</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ASIANTILES</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>47.97000122070312</v>
+      </c>
+      <c r="F95" t="n">
+        <v>47.97000122070312</v>
+      </c>
+      <c r="G95" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H95" t="n">
+        <v>45.81000137329102</v>
+      </c>
+      <c r="I95" t="n">
+        <v>47.97000122070312</v>
+      </c>
+      <c r="J95" t="n">
+        <v>45.81000137329102</v>
+      </c>
+      <c r="K95" t="n">
+        <v>9346225</v>
+      </c>
+      <c r="L95" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>15</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SBICARD.NS</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>642</v>
+      </c>
+      <c r="F96" t="n">
+        <v>643.1500244140625</v>
+      </c>
+      <c r="G96" t="n">
+        <v>613.9000244140625</v>
+      </c>
+      <c r="H96" t="n">
+        <v>615</v>
+      </c>
+      <c r="I96" t="n">
+        <v>641.75</v>
+      </c>
+      <c r="J96" t="n">
+        <v>615</v>
+      </c>
+      <c r="K96" t="n">
+        <v>2769735</v>
+      </c>
+      <c r="L96" t="n">
+        <v>-4.17</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>SBICARD Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>SBI Cards And Payment Services Ltd. (SBICARD) Share Price Falls 3.35%: Price Action, Sector and Peer Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>SBI Cards And Payment Services Ltd. (SBICARD) Share Price Falls 3.35%: Price Action, Sector and Peer Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>16</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>INOXWIND.NS</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>INOXWIND</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>78</v>
+      </c>
+      <c r="F97" t="n">
+        <v>78.19000244140625</v>
+      </c>
+      <c r="G97" t="n">
+        <v>74.69000244140625</v>
+      </c>
+      <c r="H97" t="n">
+        <v>74.94999694824219</v>
+      </c>
+      <c r="I97" t="n">
+        <v>78.12999725341797</v>
+      </c>
+      <c r="J97" t="n">
+        <v>74.94999694824219</v>
+      </c>
+      <c r="K97" t="n">
+        <v>18198825</v>
+      </c>
+      <c r="L97" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Inox Wind Limited (NSE:INOXWIND) Analysts Just Slashed This Year's Estimates - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Inox Wind Limited (NSE:INOXWIND) Analysts Just Slashed This Year's Estimates - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>17</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>HMAAGRO.NS</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>HMAAGRO</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>22.89999961853027</v>
+      </c>
+      <c r="F98" t="n">
+        <v>24</v>
+      </c>
+      <c r="G98" t="n">
+        <v>21.93000030517578</v>
+      </c>
+      <c r="H98" t="n">
+        <v>22.02000045776367</v>
+      </c>
+      <c r="I98" t="n">
+        <v>22.95000076293945</v>
+      </c>
+      <c r="J98" t="n">
+        <v>22.02000045776367</v>
+      </c>
+      <c r="K98" t="n">
+        <v>9306605</v>
+      </c>
+      <c r="L98" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>HMA Agro Industries Ltd. Share Price Rise: Price Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>HMA Agro Industries Ltd. Share Price Rise: Price Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>HMA Agro Publishes Investor Presentation for June 2026 Quarter - TipRanks</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>HMA Agro Industries Releases Q1 FY2026 Investor Presentation - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>18</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>MANCREDIT.NS</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>MANCREDIT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>242.5</v>
+      </c>
+      <c r="F99" t="n">
+        <v>243.6999969482422</v>
+      </c>
+      <c r="G99" t="n">
+        <v>225</v>
+      </c>
+      <c r="H99" t="n">
+        <v>227.2100067138672</v>
+      </c>
+      <c r="I99" t="n">
+        <v>236.7299957275391</v>
+      </c>
+      <c r="J99" t="n">
+        <v>227.2100067138672</v>
+      </c>
+      <c r="K99" t="n">
+        <v>169721</v>
+      </c>
+      <c r="L99" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>19</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>AAREYDRUGS.NS</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>AAREYDRUGS</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>83.01000213623047</v>
+      </c>
+      <c r="F100" t="n">
+        <v>85.45999908447266</v>
+      </c>
+      <c r="G100" t="n">
+        <v>81.30999755859375</v>
+      </c>
+      <c r="H100" t="n">
+        <v>82.16000366210938</v>
+      </c>
+      <c r="I100" t="n">
+        <v>85.58000183105469</v>
+      </c>
+      <c r="J100" t="n">
+        <v>82.16000366210938</v>
+      </c>
+      <c r="K100" t="n">
+        <v>668238</v>
+      </c>
+      <c r="L100" t="n">
+        <v>-4</v>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-19 08:56:49</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>20</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>KSHITIJPOL.NS</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>KSHITIJPOL</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>3.039999961853027</v>
+      </c>
+      <c r="F101" t="n">
+        <v>3.089999914169312</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2.880000114440918</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2.910000085830688</v>
+      </c>
+      <c r="I101" t="n">
+        <v>3.029999971389771</v>
+      </c>
+      <c r="J101" t="n">
+        <v>2.910000085830688</v>
+      </c>
+      <c r="K101" t="n">
+        <v>2109693</v>
+      </c>
+      <c r="L101" t="n">
+        <v>-3.96</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Kshitij Polyline launches Rs 29.3 crore rights issue to bolster equity base - TipRanks</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Kshitij Polyline launches Rs 29.3 crore rights issue to bolster equity base - TipRanks</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:Q121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5282,9 +5282,6 @@
           <t>Sigachi posts Q1 FY 2026-27 earnings call audio on website - TipRanks</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5329,11 +5326,6 @@
       <c r="L83" t="n">
         <v>11.08</v>
       </c>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5378,11 +5370,6 @@
       <c r="L84" t="n">
         <v>10.65</v>
       </c>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5447,7 +5434,6 @@
           <t>Regaal Resources Ltd Surges 17% to Hit Upper Circuit Amid Robust Buying Pressure - MarketsMojo</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5571,9 +5557,6 @@
           <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5628,9 +5611,6 @@
           <t>Nitin Spinners Share Price Gain: Technicals and Fundamentals - univest.in</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5897,8 +5877,6 @@
           <t>JYOTICNC Share Price | Jyoti CNC Automation Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5953,9 +5931,6 @@
           <t>TIINDIA Share Price | Tube Investments of India Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6000,11 +5975,6 @@
       <c r="L94" t="n">
         <v>7.61</v>
       </c>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6069,7 +6039,6 @@
           <t>MM Forgings Clarifies ₹56.25 Crore Exceptional Gain from Oragadam Land Sale - TipRanks</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6114,11 +6083,6 @@
       <c r="L96" t="n">
         <v>7.45</v>
       </c>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6163,11 +6127,6 @@
       <c r="L97" t="n">
         <v>7.4</v>
       </c>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6291,9 +6250,6 @@
           <t>SG Mart Share Price at Fresh 52-Week High: Full Analysis - univest.in</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6432,6 +6388,1170 @@
           <t>Avalon Trust Co Purchases Shares of 8,734 The Travelers Companies, Inc. $TRV - marketbeat.com</t>
         </is>
       </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>MYSORPETRO.NS</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>MYSORPETRO</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>116</v>
+      </c>
+      <c r="F102" t="n">
+        <v>137.9100036621094</v>
+      </c>
+      <c r="G102" t="n">
+        <v>116</v>
+      </c>
+      <c r="H102" t="n">
+        <v>137.9100036621094</v>
+      </c>
+      <c r="I102" t="n">
+        <v>114.9300003051758</v>
+      </c>
+      <c r="J102" t="n">
+        <v>137.9100036621094</v>
+      </c>
+      <c r="K102" t="n">
+        <v>68040</v>
+      </c>
+      <c r="L102" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>2</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>TECILCHEM.NS</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>TECILCHEM</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="F103" t="n">
+        <v>10.23999977111816</v>
+      </c>
+      <c r="G103" t="n">
+        <v>8.350000381469727</v>
+      </c>
+      <c r="H103" t="n">
+        <v>10.23999977111816</v>
+      </c>
+      <c r="I103" t="n">
+        <v>8.539999961853027</v>
+      </c>
+      <c r="J103" t="n">
+        <v>10.23999977111816</v>
+      </c>
+      <c r="K103" t="n">
+        <v>80792</v>
+      </c>
+      <c r="L103" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>3</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>EXCELINDUS.NS</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>EXCELINDUS</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>991.0499877929688</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1148.550048828125</v>
+      </c>
+      <c r="G104" t="n">
+        <v>990.9000244140625</v>
+      </c>
+      <c r="H104" t="n">
+        <v>1133.25</v>
+      </c>
+      <c r="I104" t="n">
+        <v>985.2000122070312</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1133.25</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1055759</v>
+      </c>
+      <c r="L104" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Excel Industries Ltd. Share Price Update: Price Action View - univest.in</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Excel Industries Ltd. Share Price Update: Price Action View - univest.in</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>4</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>KAMANWALA.NS</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>KAMANWALA</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>19.3799991607666</v>
+      </c>
+      <c r="F105" t="n">
+        <v>19.51000022888184</v>
+      </c>
+      <c r="G105" t="n">
+        <v>18</v>
+      </c>
+      <c r="H105" t="n">
+        <v>18.6299991607666</v>
+      </c>
+      <c r="I105" t="n">
+        <v>16.26000022888184</v>
+      </c>
+      <c r="J105" t="n">
+        <v>18.6299991607666</v>
+      </c>
+      <c r="K105" t="n">
+        <v>474236</v>
+      </c>
+      <c r="L105" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Volume Gainers on August 19, 2026 at 11:30 AM IST - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Volume Gainers on August 19, 2026 at 11:30 AM IST - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Most Active Equities on August 19, 2026 at 11:30 AM IST - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Lalithaa Jewellery Mart IPO Day 3 Subscription Status: Issue Booked 6.84x so Far - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>20% Upper Circuit: 10 Stocks That Hit Upper Circuit Today; Do You Own Any? - tradebrains.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>5</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>KOHINOOR.NS</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>KOHINOOR</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>27.8799991607666</v>
+      </c>
+      <c r="F106" t="n">
+        <v>32.72999954223633</v>
+      </c>
+      <c r="G106" t="n">
+        <v>27.42000007629395</v>
+      </c>
+      <c r="H106" t="n">
+        <v>31.27000045776367</v>
+      </c>
+      <c r="I106" t="n">
+        <v>27.42000007629395</v>
+      </c>
+      <c r="J106" t="n">
+        <v>31.27000045776367</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1432482</v>
+      </c>
+      <c r="L106" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd Locks at Upper Circuit With 20% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd Locks at Upper Circuit With 20% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>6</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ZAGGLE.NS</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ZAGGLE</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>187.3999938964844</v>
+      </c>
+      <c r="F107" t="n">
+        <v>194.6999969482422</v>
+      </c>
+      <c r="G107" t="n">
+        <v>180</v>
+      </c>
+      <c r="H107" t="n">
+        <v>186.0399932861328</v>
+      </c>
+      <c r="I107" t="n">
+        <v>165.8800048828125</v>
+      </c>
+      <c r="J107" t="n">
+        <v>186.0399932861328</v>
+      </c>
+      <c r="K107" t="n">
+        <v>39145837</v>
+      </c>
+      <c r="L107" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Zaggle rebounds 26% from Tuesday's low on heavy volumes; here's why - Business Standard</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Vijay Kedia's Kedia Securities acquires stake in AI-led SaaS fintech Zaggle Prepaid, stock surges more than 17% on NSE - TradingView</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>YC Holdings sells Rs 1,435 crore Groww stake; Vijay Kedia firm buys 1.48% in Zaggle Prepaid - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Vijay Kedia buys Rs 33 crore stake in Zaggle Prepaid Ocean Services via bulk deal, stock skyrockets 17% - The Economic Times</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>Zaggle Prepaid Ocean Services Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>7</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SONAMLTD.NS</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>SONAMLTD</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>62.29999923706055</v>
+      </c>
+      <c r="F108" t="n">
+        <v>68.98999786376953</v>
+      </c>
+      <c r="G108" t="n">
+        <v>60.7400016784668</v>
+      </c>
+      <c r="H108" t="n">
+        <v>67.19000244140625</v>
+      </c>
+      <c r="I108" t="n">
+        <v>60.31000137329102</v>
+      </c>
+      <c r="J108" t="n">
+        <v>67.19000244140625</v>
+      </c>
+      <c r="K108" t="n">
+        <v>964817</v>
+      </c>
+      <c r="L108" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Here's Why We Think Sonam (NSE:SONAMLTD) Is Well Worth Watching - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Here's Why We Think Sonam (NSE:SONAMLTD) Is Well Worth Watching - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>8</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>LAXMICOT.NS</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LAXMICOT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="F109" t="n">
+        <v>16.14999961853027</v>
+      </c>
+      <c r="G109" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H109" t="n">
+        <v>14.89000034332275</v>
+      </c>
+      <c r="I109" t="n">
+        <v>13.46000003814697</v>
+      </c>
+      <c r="J109" t="n">
+        <v>14.89000034332275</v>
+      </c>
+      <c r="K109" t="n">
+        <v>357640</v>
+      </c>
+      <c r="L109" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>9</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>NILKAMAL.NS</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NILKAMAL</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>1848.699951171875</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2105</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1832.5</v>
+      </c>
+      <c r="H110" t="n">
+        <v>2033.800048828125</v>
+      </c>
+      <c r="I110" t="n">
+        <v>1846.699951171875</v>
+      </c>
+      <c r="J110" t="n">
+        <v>2033.800048828125</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1423712</v>
+      </c>
+      <c r="L110" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Nilkamal Ltd Upgraded to Buy on Improved Technicals and Valuation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Nilkamal Ltd Surges 8.0% to Day's High of Rs 1970 — Outperforms Sector by 7.27 Percentage Points - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Nilkamal Ltd Technical Momentum Shifts Signal Bullish Outlook Amid Market Volatility - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Nilkamal Ltd Upgraded to Buy by MarketsMOJO on Strong Financial and Technical Grounds - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>Nilkamal Ltd Surges 8.0% to Day's High of Rs 1970 — Outperforms Sector by 7.27 Percentage Points - MarketsMojo</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>10</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>MANBRO.NS</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>MANBRO</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>53</v>
+      </c>
+      <c r="F111" t="n">
+        <v>58.40999984741211</v>
+      </c>
+      <c r="G111" t="n">
+        <v>52.79999923706055</v>
+      </c>
+      <c r="H111" t="n">
+        <v>58.40999984741211</v>
+      </c>
+      <c r="I111" t="n">
+        <v>53.09999847412109</v>
+      </c>
+      <c r="J111" t="n">
+        <v>58.40999984741211</v>
+      </c>
+      <c r="K111" t="n">
+        <v>132482</v>
+      </c>
+      <c r="L111" t="n">
+        <v>10</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of KD Green Industries Limited – NSE:MANBRO - TradingView</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of KD Green Industries Limited – NSE:MANBRO - TradingView</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Manbro Ind Q1 Results FY27: Revenue Rs 34 crore, Net Profit Rs 3 Crore - univest.in</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>11</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>MILKYMIST.NS</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>MILKYMIST</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>190</v>
+      </c>
+      <c r="F112" t="n">
+        <v>199.6499938964844</v>
+      </c>
+      <c r="G112" t="n">
+        <v>190</v>
+      </c>
+      <c r="H112" t="n">
+        <v>199.6499938964844</v>
+      </c>
+      <c r="I112" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="J112" t="n">
+        <v>199.6499938964844</v>
+      </c>
+      <c r="K112" t="n">
+        <v>27974362</v>
+      </c>
+      <c r="L112" t="n">
+        <v>10</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Milky Mist shares make decent market debut at 18% premium; should you buy, sell or hold? - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Milky Mist Dairy Food Limited: Target Price Consensus and Analysts Recommendations | MILKYMIST | INE00IT01020 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Milky Mist IPO Listing: Shares Debut at ₹165, Gain 18%; Stock Rises 29.64% From Issue Price - India Infoline</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Milky Mist share price up 30% after IPO listing: Should investors hold or book profits? - India Today</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Milky Mist Share Price Hits 10% Upper Circuit After Strong Listing. Should Investors Buy, Sell Or Hold? - NDTV Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>12</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SIEL.NS</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>SIEL</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>42.41999816894531</v>
+      </c>
+      <c r="F113" t="n">
+        <v>42.41999816894531</v>
+      </c>
+      <c r="G113" t="n">
+        <v>39.38999938964844</v>
+      </c>
+      <c r="H113" t="n">
+        <v>42.41999816894531</v>
+      </c>
+      <c r="I113" t="n">
+        <v>38.56999969482422</v>
+      </c>
+      <c r="J113" t="n">
+        <v>42.41999816894531</v>
+      </c>
+      <c r="K113" t="n">
+        <v>13463</v>
+      </c>
+      <c r="L113" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Diluted shares outstanding of Superior Industrial Enterprises Limited – NSE:SIEL - TradingView</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Diluted shares outstanding of Superior Industrial Enterprises Limited – NSE:SIEL - TradingView</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>13</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>BAJAJHIND.NS</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>BAJAJHIND</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>18.60000038146973</v>
+      </c>
+      <c r="F114" t="n">
+        <v>21.28000068664551</v>
+      </c>
+      <c r="G114" t="n">
+        <v>18.54000091552734</v>
+      </c>
+      <c r="H114" t="n">
+        <v>20.3799991607666</v>
+      </c>
+      <c r="I114" t="n">
+        <v>18.60000038146973</v>
+      </c>
+      <c r="J114" t="n">
+        <v>20.3799991607666</v>
+      </c>
+      <c r="K114" t="n">
+        <v>176267431</v>
+      </c>
+      <c r="L114" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Stock Price Forecast. Should You Buy BAJAJHIND.NS? - StockInvest.us</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Stock Price Forecast. Should You Buy BAJAJHIND.NS? - StockInvest.us</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>14</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>TPHQ.NS</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>TPHQ</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0.6499999761581421</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.6899999976158142</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.6100000143051147</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.6899999976158142</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.6299999952316284</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0.6899999976158142</v>
+      </c>
+      <c r="K115" t="n">
+        <v>23477345</v>
+      </c>
+      <c r="L115" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>15</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>RPEL.NS</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>RPEL</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1665</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1637.400024414062</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1495.199951171875</v>
+      </c>
+      <c r="J116" t="n">
+        <v>1637.400024414062</v>
+      </c>
+      <c r="K116" t="n">
+        <v>375042</v>
+      </c>
+      <c r="L116" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Raghav Productivity Enhancers Ltd. Share Price Near High - univest.in</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Raghav Productivity Enhancers Ltd. Share Price Near High - univest.in</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>16</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>HEALTHX.NS</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>HEALTHX</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>288</v>
+      </c>
+      <c r="F117" t="n">
+        <v>327.8999938964844</v>
+      </c>
+      <c r="G117" t="n">
+        <v>286.5</v>
+      </c>
+      <c r="H117" t="n">
+        <v>313.7000122070312</v>
+      </c>
+      <c r="I117" t="n">
+        <v>288.5</v>
+      </c>
+      <c r="J117" t="n">
+        <v>313.7000122070312</v>
+      </c>
+      <c r="K117" t="n">
+        <v>8983</v>
+      </c>
+      <c r="L117" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Sastasundar Ventures Ltd. Share Price Rise: Key Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Sastasundar Ventures Ltd. Share Price Rise: Key Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>17</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>AVROIND.NS</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>AVROIND</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>8.630000114440918</v>
+      </c>
+      <c r="F118" t="n">
+        <v>9.829999923706055</v>
+      </c>
+      <c r="G118" t="n">
+        <v>8.420000076293945</v>
+      </c>
+      <c r="H118" t="n">
+        <v>9.539999961853027</v>
+      </c>
+      <c r="I118" t="n">
+        <v>8.800000190734863</v>
+      </c>
+      <c r="J118" t="n">
+        <v>9.539999961853027</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1242003</v>
+      </c>
+      <c r="L118" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Avro India Ltd. Share Price Today: Price Rise Breakdown - univest.in</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Avro India Ltd. Share Price Today: Price Rise Breakdown - univest.in</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>18</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>DCMSIL.NS</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>DCMSIL</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>70</v>
+      </c>
+      <c r="F119" t="n">
+        <v>75.11000061035156</v>
+      </c>
+      <c r="G119" t="n">
+        <v>68.01999664306641</v>
+      </c>
+      <c r="H119" t="n">
+        <v>74.58000183105469</v>
+      </c>
+      <c r="I119" t="n">
+        <v>68.94000244140625</v>
+      </c>
+      <c r="J119" t="n">
+        <v>74.58000183105469</v>
+      </c>
+      <c r="K119" t="n">
+        <v>144562</v>
+      </c>
+      <c r="L119" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>DCMSIL Share Price Today - DCM Shriram International Ltd. Stock Price Live NSE/BSE - univest.in</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>DCMSIL Share Price Today - DCM Shriram International Ltd. Stock Price Live NSE/BSE - univest.in</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>19</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>DWARKESH.NS</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>DWARKESH</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>44.86000061035156</v>
+      </c>
+      <c r="F120" t="n">
+        <v>50.04999923706055</v>
+      </c>
+      <c r="G120" t="n">
+        <v>44.56000137329102</v>
+      </c>
+      <c r="H120" t="n">
+        <v>48.27999877929688</v>
+      </c>
+      <c r="I120" t="n">
+        <v>44.63999938964844</v>
+      </c>
+      <c r="J120" t="n">
+        <v>48.27999877929688</v>
+      </c>
+      <c r="K120" t="n">
+        <v>9610957</v>
+      </c>
+      <c r="L120" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar surges more than 6% on buyback plans, fixes record date on March 20 - Upstox</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar surges more than 6% on buyback plans, fixes record date on March 20 - Upstox</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>20</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>BLUSPRING.NS</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>BLUSPRING</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="F121" t="n">
+        <v>120.7600021362305</v>
+      </c>
+      <c r="G121" t="n">
+        <v>110</v>
+      </c>
+      <c r="H121" t="n">
+        <v>119.8600006103516</v>
+      </c>
+      <c r="I121" t="n">
+        <v>111.2099990844727</v>
+      </c>
+      <c r="J121" t="n">
+        <v>119.8600006103516</v>
+      </c>
+      <c r="K121" t="n">
+        <v>872655</v>
+      </c>
+      <c r="L121" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6444,7 +7564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:Q121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11047,7 +12167,6 @@
           <t>Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -11102,9 +12221,6 @@
           <t>Hold Ahluwalia Contracts India; target of Rs 780: ICICI Securities - TradingView</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -11169,7 +12285,6 @@
           <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -11214,11 +12329,6 @@
       <c r="L85" t="n">
         <v>-5.7</v>
       </c>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -11347,8 +12457,6 @@
           <t>Atal Realtech Share Price Near ATH With Fundamental View - univest.in</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -11408,8 +12516,6 @@
           <t>Mastek fixes Aug 31 record date for ₹16 per share final dividend - scanx.trade</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -11454,11 +12560,6 @@
       <c r="L89" t="n">
         <v>-5</v>
       </c>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -11503,11 +12604,6 @@
       <c r="L90" t="n">
         <v>-5</v>
       </c>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11552,11 +12648,6 @@
       <c r="L91" t="n">
         <v>-4.99</v>
       </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11611,9 +12702,6 @@
           <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11737,9 +12825,6 @@
           <t>Shri Krishna Devcon Ltd. Share Price Fall and Stock Analysis - univest.in</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11784,11 +12869,6 @@
       <c r="L95" t="n">
         <v>-4.5</v>
       </c>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11848,8 +12928,6 @@
           <t>SBI Cards And Payment Services Ltd. (SBICARD) Share Price Falls 3.35%: Price Action, Sector and Peer Analysis - univest.in</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -11904,9 +12982,6 @@
           <t>Inox Wind Limited (NSE:INOXWIND) Analysts Just Slashed This Year's Estimates - simplywall.st</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -11971,7 +13046,6 @@
           <t>HMA Agro Industries Releases Q1 FY2026 Investor Presentation - TipRanks</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -12016,11 +13090,6 @@
       <c r="L99" t="n">
         <v>-4.02</v>
       </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -12065,11 +13134,6 @@
       <c r="L100" t="n">
         <v>-4</v>
       </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -12124,9 +13188,1162 @@
           <t>Kshitij Polyline launches Rs 29.3 crore rights issue to bolster equity base - TipRanks</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>KJMCFIN.NS</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>KJMCFIN</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>61.9900016784668</v>
+      </c>
+      <c r="F102" t="n">
+        <v>61.9900016784668</v>
+      </c>
+      <c r="G102" t="n">
+        <v>55.34999847412109</v>
+      </c>
+      <c r="H102" t="n">
+        <v>55.34999847412109</v>
+      </c>
+      <c r="I102" t="n">
+        <v>61.9900016784668</v>
+      </c>
+      <c r="J102" t="n">
+        <v>55.34999847412109</v>
+      </c>
+      <c r="K102" t="n">
+        <v>322</v>
+      </c>
+      <c r="L102" t="n">
+        <v>-10.71</v>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>2</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>YASHO.NS</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>YASHO</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>4910</v>
+      </c>
+      <c r="F103" t="n">
+        <v>4911.2001953125</v>
+      </c>
+      <c r="G103" t="n">
+        <v>4411.60009765625</v>
+      </c>
+      <c r="H103" t="n">
+        <v>4470.7998046875</v>
+      </c>
+      <c r="I103" t="n">
+        <v>4915.7998046875</v>
+      </c>
+      <c r="J103" t="n">
+        <v>4470.7998046875</v>
+      </c>
+      <c r="K103" t="n">
+        <v>167699</v>
+      </c>
+      <c r="L103" t="n">
+        <v>-9.050000000000001</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Why Yasho Industries’ ₹150 Cr Deal Could Change Its Growth Story - outlookbusiness.com</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>183.68% Stock Return, 372.3% Profit Growth: What's Driving Yasho Industries Ltd's Multibagger Rerating? - MarketsMojo</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>3</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>AAKASH.NS</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>AAKASH</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>9.130000114440918</v>
+      </c>
+      <c r="F104" t="n">
+        <v>9.199999809265137</v>
+      </c>
+      <c r="G104" t="n">
+        <v>8.060000419616699</v>
+      </c>
+      <c r="H104" t="n">
+        <v>8.449999809265137</v>
+      </c>
+      <c r="I104" t="n">
+        <v>9.130000114440918</v>
+      </c>
+      <c r="J104" t="n">
+        <v>8.449999809265137</v>
+      </c>
+      <c r="K104" t="n">
+        <v>719753</v>
+      </c>
+      <c r="L104" t="n">
+        <v>-7.45</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Aakash Explorat Standalone June 2026 Net Sales at Rs 27.89 crore, up 16.93% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Aakash Explorat Standalone June 2026 Net Sales at Rs 27.89 crore, up 16.93% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>If you have a genius like Jasprit Bumrah, and if his body needs some rest, why would you play him? Aakash Chopra on star pacer's workload - CricTracker</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Aakash Exploration Promoters Reshuffle Holdings via Exempt Share Transfer - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>4</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>INDSWFTLAB.NS</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>INDSWFTLAB</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>347.4700012207031</v>
+      </c>
+      <c r="F105" t="n">
+        <v>348</v>
+      </c>
+      <c r="G105" t="n">
+        <v>320.0499877929688</v>
+      </c>
+      <c r="H105" t="n">
+        <v>322.0599975585938</v>
+      </c>
+      <c r="I105" t="n">
+        <v>346.8699951171875</v>
+      </c>
+      <c r="J105" t="n">
+        <v>322.0599975585938</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1534549</v>
+      </c>
+      <c r="L105" t="n">
+        <v>-7.15</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - univest.in</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - univest.in</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>5</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>CGVAK.NS</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>CGVAK</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>151.2400054931641</v>
+      </c>
+      <c r="F106" t="n">
+        <v>151.2400054931641</v>
+      </c>
+      <c r="G106" t="n">
+        <v>136.6199951171875</v>
+      </c>
+      <c r="H106" t="n">
+        <v>140.7299957275391</v>
+      </c>
+      <c r="I106" t="n">
+        <v>151.2400054931641</v>
+      </c>
+      <c r="J106" t="n">
+        <v>140.7299957275391</v>
+      </c>
+      <c r="K106" t="n">
+        <v>508</v>
+      </c>
+      <c r="L106" t="n">
+        <v>-6.95</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Average basic shares outstanding of CG-VAK Software &amp; Exports Ltd. – NSE:CGVAK - TradingView</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Average basic shares outstanding of CG-VAK Software &amp; Exports Ltd. – NSE:CGVAK - TradingView</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>6</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ANTELOPUS.NS</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>863</v>
+      </c>
+      <c r="F107" t="n">
+        <v>863</v>
+      </c>
+      <c r="G107" t="n">
+        <v>793.75</v>
+      </c>
+      <c r="H107" t="n">
+        <v>798.3499755859375</v>
+      </c>
+      <c r="I107" t="n">
+        <v>856.5499877929688</v>
+      </c>
+      <c r="J107" t="n">
+        <v>798.3499755859375</v>
+      </c>
+      <c r="K107" t="n">
+        <v>209718</v>
+      </c>
+      <c r="L107" t="n">
+        <v>-6.79</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Antelopus Selan Energy Ltd Surges 7.14% to Day's High of Rs 857.5 — Outperforms Sector by 6.12 Percentage Points - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Antelopus Selan Energy Ltd Surges 7.14% to Day's High of Rs 857.5 — Outperforms Sector by 6.12 Percentage Points - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>7</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>MEDICAPQ.NS</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>MEDICAPQ</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F108" t="n">
+        <v>27.45000076293945</v>
+      </c>
+      <c r="G108" t="n">
+        <v>21</v>
+      </c>
+      <c r="H108" t="n">
+        <v>23.55999946594238</v>
+      </c>
+      <c r="I108" t="n">
+        <v>25.04999923706055</v>
+      </c>
+      <c r="J108" t="n">
+        <v>23.55999946594238</v>
+      </c>
+      <c r="K108" t="n">
+        <v>2778</v>
+      </c>
+      <c r="L108" t="n">
+        <v>-5.95</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Medi-Caps Ltd. Financial Statements – NSE:MEDICAPQ - TradingView</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Medi-Caps Ltd. Financial Statements – NSE:MEDICAPQ - TradingView</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>8</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>BHARATSE.NS</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>BHARATSE</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>240.9100036621094</v>
+      </c>
+      <c r="F109" t="n">
+        <v>240.9100036621094</v>
+      </c>
+      <c r="G109" t="n">
+        <v>224.9900054931641</v>
+      </c>
+      <c r="H109" t="n">
+        <v>227.1900024414062</v>
+      </c>
+      <c r="I109" t="n">
+        <v>240.9100036621094</v>
+      </c>
+      <c r="J109" t="n">
+        <v>227.1900024414062</v>
+      </c>
+      <c r="K109" t="n">
+        <v>440887</v>
+      </c>
+      <c r="L109" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>9</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>MALUPAPER.NS</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>MALUPAPER</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>32.20000076293945</v>
+      </c>
+      <c r="F110" t="n">
+        <v>32.20000076293945</v>
+      </c>
+      <c r="G110" t="n">
+        <v>30.20000076293945</v>
+      </c>
+      <c r="H110" t="n">
+        <v>30.81999969482422</v>
+      </c>
+      <c r="I110" t="n">
+        <v>32.58000183105469</v>
+      </c>
+      <c r="J110" t="n">
+        <v>30.81999969482422</v>
+      </c>
+      <c r="K110" t="n">
+        <v>61691</v>
+      </c>
+      <c r="L110" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>10</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>UEL.NS</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>UEL</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>200.8000030517578</v>
+      </c>
+      <c r="F111" t="n">
+        <v>200.8000030517578</v>
+      </c>
+      <c r="G111" t="n">
+        <v>200.8000030517578</v>
+      </c>
+      <c r="H111" t="n">
+        <v>200.8000030517578</v>
+      </c>
+      <c r="I111" t="n">
+        <v>211.3600006103516</v>
+      </c>
+      <c r="J111" t="n">
+        <v>200.8000030517578</v>
+      </c>
+      <c r="K111" t="n">
+        <v>4624</v>
+      </c>
+      <c r="L111" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Boehly Holds Talks Over Selling Shares To Majority Owners At Chelsea - Complete Sports</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Boehly Holds Talks Over Selling Shares To Majority Owners At Chelsea - Complete Sports</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>11</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>INDOTHAI.NS</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>INDOTHAI</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>66.09999847412109</v>
+      </c>
+      <c r="F112" t="n">
+        <v>66.09999847412109</v>
+      </c>
+      <c r="G112" t="n">
+        <v>66.09999847412109</v>
+      </c>
+      <c r="H112" t="n">
+        <v>66.09999847412109</v>
+      </c>
+      <c r="I112" t="n">
+        <v>69.56999969482422</v>
+      </c>
+      <c r="J112" t="n">
+        <v>66.09999847412109</v>
+      </c>
+      <c r="K112" t="n">
+        <v>42916</v>
+      </c>
+      <c r="L112" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>12</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ONIXSOLAR.NS</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ONIXSOLAR</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>338.8500061035156</v>
+      </c>
+      <c r="F113" t="n">
+        <v>338.8500061035156</v>
+      </c>
+      <c r="G113" t="n">
+        <v>338.8500061035156</v>
+      </c>
+      <c r="H113" t="n">
+        <v>338.8500061035156</v>
+      </c>
+      <c r="I113" t="n">
+        <v>356.6499938964844</v>
+      </c>
+      <c r="J113" t="n">
+        <v>338.8500061035156</v>
+      </c>
+      <c r="K113" t="n">
+        <v>5926</v>
+      </c>
+      <c r="L113" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of Onix Solar Energy Ltd. – NSE:ONIXSOLAR - TradingView</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>ONIXSOLAR Share Price Today - Onix Solar Energy Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>ONIXSOLAR Share Price Today - Onix Solar Energy Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Onix Solar Energy shares permitted to trade on NSE from August 17 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Onix Solar Energy Ltd - Equitypandit</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>13</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SUMEETINDS.NS</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>SUMEETINDS</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>13.39999961853027</v>
+      </c>
+      <c r="F114" t="n">
+        <v>13.39999961853027</v>
+      </c>
+      <c r="G114" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="H114" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="I114" t="n">
+        <v>13.42000007629395</v>
+      </c>
+      <c r="J114" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="K114" t="n">
+        <v>3255667</v>
+      </c>
+      <c r="L114" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>14</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>KEEPLEARN.NS</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>KEEPLEARN</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>2.049999952316284</v>
+      </c>
+      <c r="F115" t="n">
+        <v>2.049999952316284</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1.899999976158142</v>
+      </c>
+      <c r="H115" t="n">
+        <v>1.909999966621399</v>
+      </c>
+      <c r="I115" t="n">
+        <v>2.009999990463257</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1.909999966621399</v>
+      </c>
+      <c r="K115" t="n">
+        <v>50562</v>
+      </c>
+      <c r="L115" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>DSJ Keep Learning Posts Q1 FY27 Unaudited Results in Line with SEBI Norms - TipRanks</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>DSJ Keep Learning Posts Q1 FY27 Unaudited Results in Line with SEBI Norms - TipRanks</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>15</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>RBA.NS</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>RBA</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="F116" t="n">
+        <v>104.5999984741211</v>
+      </c>
+      <c r="G116" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="H116" t="n">
+        <v>101.0599975585938</v>
+      </c>
+      <c r="I116" t="n">
+        <v>106.3399963378906</v>
+      </c>
+      <c r="J116" t="n">
+        <v>101.0599975585938</v>
+      </c>
+      <c r="K116" t="n">
+        <v>12913965</v>
+      </c>
+      <c r="L116" t="n">
+        <v>-4.97</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>RBA stock hits 52-week low at 83.55 USD By Investing.com - Investing.com India</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>ANZ Stock And 2 Australian Bank Shares Facing the Next RBA Rate Test - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>RB Global Inc (RBA) Stock Up 4.5% and Still Undervalued -- GF Sc - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>ANZ Stock And 2 Australian Bank Shares Facing the Next RBA Rate Test - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Why RB Global (RBA) Stock Is Down Today - Quiver Quantitative</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>16</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>POWERICA.NS</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>POWERICA</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>562.7999877929688</v>
+      </c>
+      <c r="F117" t="n">
+        <v>562.7999877929688</v>
+      </c>
+      <c r="G117" t="n">
+        <v>530.2999877929688</v>
+      </c>
+      <c r="H117" t="n">
+        <v>532.8499755859375</v>
+      </c>
+      <c r="I117" t="n">
+        <v>560.6500244140625</v>
+      </c>
+      <c r="J117" t="n">
+        <v>532.8499755859375</v>
+      </c>
+      <c r="K117" t="n">
+        <v>218225</v>
+      </c>
+      <c r="L117" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Powerica Ltd. Share Price Today - Powerica Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Powerica schedules virtual analyst meet on August 21 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>POWERICA Share Price Today - Powerica Ltd. Stock Price Live NSE/BSE - univest.in</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Powerica schedules virtual analyst meet on August 21 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>17</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>CESC.NS</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>162</v>
+      </c>
+      <c r="F118" t="n">
+        <v>162.2599945068359</v>
+      </c>
+      <c r="G118" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="H118" t="n">
+        <v>159.6600036621094</v>
+      </c>
+      <c r="I118" t="n">
+        <v>167.9799957275391</v>
+      </c>
+      <c r="J118" t="n">
+        <v>159.6600036621094</v>
+      </c>
+      <c r="K118" t="n">
+        <v>2881453</v>
+      </c>
+      <c r="L118" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Adani Power, BHEL, Suzlon, Waaree, IEX, Tata Power, CESC: Target prices, top 5 stock picks - businesstoday.in</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Adani Power, BHEL, Suzlon, Waaree, IEX, Tata Power, CESC: Target prices, top 5 stock picks - businesstoday.in</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>CESC Limited Earnings Missed Analyst Estimates: Here's What Analysts Are Forecasting Now - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Stocks to Watch Today: PB Fintech, Juniper Green, CESC, Dr Reddys Labs, Texmaco Rail, Voltas,... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>CESC Ltd soars 1.23% - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>18</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ADROITINFO.NS</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ADROITINFO</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>10.10000038146973</v>
+      </c>
+      <c r="F119" t="n">
+        <v>10.23999977111816</v>
+      </c>
+      <c r="G119" t="n">
+        <v>9.800000190734863</v>
+      </c>
+      <c r="H119" t="n">
+        <v>9.850000381469727</v>
+      </c>
+      <c r="I119" t="n">
+        <v>10.35999965667725</v>
+      </c>
+      <c r="J119" t="n">
+        <v>9.850000381469727</v>
+      </c>
+      <c r="K119" t="n">
+        <v>19995</v>
+      </c>
+      <c r="L119" t="n">
+        <v>-4.92</v>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>19</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>WEBELSOLAR.NS</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>WEBELSOLAR</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>86.93000030517578</v>
+      </c>
+      <c r="F120" t="n">
+        <v>87.12000274658203</v>
+      </c>
+      <c r="G120" t="n">
+        <v>82.58999633789062</v>
+      </c>
+      <c r="H120" t="n">
+        <v>82.72000122070312</v>
+      </c>
+      <c r="I120" t="n">
+        <v>86.93000030517578</v>
+      </c>
+      <c r="J120" t="n">
+        <v>82.72000122070312</v>
+      </c>
+      <c r="K120" t="n">
+        <v>2433185</v>
+      </c>
+      <c r="L120" t="n">
+        <v>-4.84</v>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:02</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>20</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>PLAZACABLE.NS</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>PLAZACABLE</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="F121" t="n">
+        <v>53.02000045776367</v>
+      </c>
+      <c r="G121" t="n">
+        <v>49.77000045776367</v>
+      </c>
+      <c r="H121" t="n">
+        <v>49.86000061035156</v>
+      </c>
+      <c r="I121" t="n">
+        <v>52.38000106811523</v>
+      </c>
+      <c r="J121" t="n">
+        <v>49.86000061035156</v>
+      </c>
+      <c r="K121" t="n">
+        <v>75805</v>
+      </c>
+      <c r="L121" t="n">
+        <v>-4.81</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Here's Why We Think Plaza Wires (NSE:PLAZACABLE) Is Well Worth Watching - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Here's Why We Think Plaza Wires (NSE:PLAZACABLE) Is Well Worth Watching - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q121"/>
+  <dimension ref="A1:Q141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6442,9 +6442,6 @@
           <t>Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6489,11 +6486,6 @@
       <c r="L103" t="n">
         <v>19.91</v>
       </c>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6548,9 +6540,6 @@
           <t>Excel Industries Ltd. Share Price Update: Price Action View - univest.in</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6674,9 +6663,6 @@
           <t>Kohinoor Foods Ltd Locks at Upper Circuit With 20% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
         </is>
       </c>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6800,9 +6786,6 @@
           <t>Here's Why We Think Sonam (NSE:SONAMLTD) Is Well Worth Watching - simplywall.st</t>
         </is>
       </c>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6847,11 +6830,6 @@
       <c r="L109" t="n">
         <v>10.62</v>
       </c>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6980,8 +6958,6 @@
           <t>Manbro Ind Q1 Results FY27: Revenue Rs 34 crore, Net Profit Rs 3 Crore - univest.in</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7110,8 +7086,6 @@
           <t>Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7166,9 +7140,6 @@
           <t>Bajaj Hindusthan Sugar Stock Price Forecast. Should You Buy BAJAJHIND.NS? - StockInvest.us</t>
         </is>
       </c>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7213,11 +7184,6 @@
       <c r="L115" t="n">
         <v>9.52</v>
       </c>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7272,9 +7238,6 @@
           <t>Raghav Productivity Enhancers Ltd. Share Price Near High - univest.in</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7329,9 +7292,6 @@
           <t>Sastasundar Ventures Ltd. Share Price Rise: Key Analysis - univest.in</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7386,9 +7346,6 @@
           <t>Avro India Ltd. Share Price Today: Price Rise Breakdown - univest.in</t>
         </is>
       </c>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7443,9 +7400,6 @@
           <t>DCMSIL Share Price Today - DCM Shriram International Ltd. Stock Price Live NSE/BSE - univest.in</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7500,9 +7454,6 @@
           <t>Dwarikesh Sugar surges more than 6% on buyback plans, fixes record date on March 20 - Upstox</t>
         </is>
       </c>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7547,11 +7498,1106 @@
       <c r="L121" t="n">
         <v>7.78</v>
       </c>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>EXCELINDUS.NS</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>EXCELINDUS</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>991.0499877929688</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1148.550048828125</v>
+      </c>
+      <c r="G122" t="n">
+        <v>990.9000244140625</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1133.25</v>
+      </c>
+      <c r="I122" t="n">
+        <v>985.2000122070312</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1133.25</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1055831</v>
+      </c>
+      <c r="L122" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>2</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>KOHINOOR.NS</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>KOHINOOR</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>27.8799991607666</v>
+      </c>
+      <c r="F123" t="n">
+        <v>32.72999954223633</v>
+      </c>
+      <c r="G123" t="n">
+        <v>27.42000007629395</v>
+      </c>
+      <c r="H123" t="n">
+        <v>31.27000045776367</v>
+      </c>
+      <c r="I123" t="n">
+        <v>27.42000007629395</v>
+      </c>
+      <c r="J123" t="n">
+        <v>31.27000045776367</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1434186</v>
+      </c>
+      <c r="L123" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>3</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ZAGGLE.NS</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ZAGGLE</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>187.3999938964844</v>
+      </c>
+      <c r="F124" t="n">
+        <v>194.6999969482422</v>
+      </c>
+      <c r="G124" t="n">
+        <v>180</v>
+      </c>
+      <c r="H124" t="n">
+        <v>186.0399932861328</v>
+      </c>
+      <c r="I124" t="n">
+        <v>165.8800048828125</v>
+      </c>
+      <c r="J124" t="n">
+        <v>186.0399932861328</v>
+      </c>
+      <c r="K124" t="n">
+        <v>39149680</v>
+      </c>
+      <c r="L124" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Vijay Kedia buys Rs 33 crore stake in Zaggle Prepaid Ocean Services via bulk deal, stock skyrockets 17% - economictimes.com</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Vijay Kedia-backed firm buys 20 lakh Zaggle shares | Tap to know more | Inshorts - Inshorts</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>YC Holdings sells Rs 1,435 crore Groww stake; Vijay Kedia firm buys 1.48% in Zaggle Prepaid - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Zaggle rebounds 26% from Tuesday's low on heavy volumes; here's why - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Zaggle Prepaid Ocean Services crashes 20%, hits lower circuit after Q1 PAT declines 33% YoY - economictimes.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>4</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>AHLADA.NS</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>AHLADA</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>37.40000152587891</v>
+      </c>
+      <c r="F125" t="n">
+        <v>43.70999908447266</v>
+      </c>
+      <c r="G125" t="n">
+        <v>36.15999984741211</v>
+      </c>
+      <c r="H125" t="n">
+        <v>40.81999969482422</v>
+      </c>
+      <c r="I125" t="n">
+        <v>36.43000030517578</v>
+      </c>
+      <c r="J125" t="n">
+        <v>40.81999969482422</v>
+      </c>
+      <c r="K125" t="n">
+        <v>230285</v>
+      </c>
+      <c r="L125" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>5</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>SONAMLTD.NS</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>SONAMLTD</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>62.29999923706055</v>
+      </c>
+      <c r="F126" t="n">
+        <v>68.98999786376953</v>
+      </c>
+      <c r="G126" t="n">
+        <v>60.7400016784668</v>
+      </c>
+      <c r="H126" t="n">
+        <v>67.19000244140625</v>
+      </c>
+      <c r="I126" t="n">
+        <v>60.31000137329102</v>
+      </c>
+      <c r="J126" t="n">
+        <v>67.19000244140625</v>
+      </c>
+      <c r="K126" t="n">
+        <v>977582</v>
+      </c>
+      <c r="L126" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>6</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>GFLLIMITED.NS</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>GFLLIMITED</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>52</v>
+      </c>
+      <c r="F127" t="n">
+        <v>58.04999923706055</v>
+      </c>
+      <c r="G127" t="n">
+        <v>51.22999954223633</v>
+      </c>
+      <c r="H127" t="n">
+        <v>56.7599983215332</v>
+      </c>
+      <c r="I127" t="n">
+        <v>51.22000122070312</v>
+      </c>
+      <c r="J127" t="n">
+        <v>56.7599983215332</v>
+      </c>
+      <c r="K127" t="n">
+        <v>770053</v>
+      </c>
+      <c r="L127" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>7</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>MILKYMIST.NS</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>MILKYMIST</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>190</v>
+      </c>
+      <c r="F128" t="n">
+        <v>199.6499938964844</v>
+      </c>
+      <c r="G128" t="n">
+        <v>190</v>
+      </c>
+      <c r="H128" t="n">
+        <v>199.6499938964844</v>
+      </c>
+      <c r="I128" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="J128" t="n">
+        <v>199.6499938964844</v>
+      </c>
+      <c r="K128" t="n">
+        <v>29368751</v>
+      </c>
+      <c r="L128" t="n">
+        <v>10</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Milky Mist shares make decent market debut at 18% premium; should you buy, sell or hold? - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Average basic shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Milky Mist share price extends post-listing gains, hits 10% upper circuit - Business Standard</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Milky Mist IPO Listing: Shares Debut at ₹165, Gain 18%; Stock Rises 29.64% From Issue Price - India Infoline</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>Milky Mist share price up 30% after IPO listing: Should investors hold or book profits? - India Today</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>8</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SIEL.NS</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>SIEL</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>42.41999816894531</v>
+      </c>
+      <c r="F129" t="n">
+        <v>42.41999816894531</v>
+      </c>
+      <c r="G129" t="n">
+        <v>39.38999938964844</v>
+      </c>
+      <c r="H129" t="n">
+        <v>42.41999816894531</v>
+      </c>
+      <c r="I129" t="n">
+        <v>38.56999969482422</v>
+      </c>
+      <c r="J129" t="n">
+        <v>42.41999816894531</v>
+      </c>
+      <c r="K129" t="n">
+        <v>20184</v>
+      </c>
+      <c r="L129" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Diluted shares outstanding of Superior Industrial Enterprises Limited – NSE:SIEL - TradingView</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>9</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>TPHQ.NS</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>TPHQ</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0.6499999761581421</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.6899999976158142</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.6100000143051147</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.6899999976158142</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.6299999952316284</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.6899999976158142</v>
+      </c>
+      <c r="K130" t="n">
+        <v>23488941</v>
+      </c>
+      <c r="L130" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>10</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>RPEL.NS</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>RPEL</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1665</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H131" t="n">
+        <v>1637.400024414062</v>
+      </c>
+      <c r="I131" t="n">
+        <v>1495.199951171875</v>
+      </c>
+      <c r="J131" t="n">
+        <v>1637.400024414062</v>
+      </c>
+      <c r="K131" t="n">
+        <v>375056</v>
+      </c>
+      <c r="L131" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>11</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>DWARKESH.NS</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>DWARKESH</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>44.86000061035156</v>
+      </c>
+      <c r="F132" t="n">
+        <v>50.04999923706055</v>
+      </c>
+      <c r="G132" t="n">
+        <v>44.56000137329102</v>
+      </c>
+      <c r="H132" t="n">
+        <v>48.27999877929688</v>
+      </c>
+      <c r="I132" t="n">
+        <v>44.63999938964844</v>
+      </c>
+      <c r="J132" t="n">
+        <v>48.27999877929688</v>
+      </c>
+      <c r="K132" t="n">
+        <v>9613344</v>
+      </c>
+      <c r="L132" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>12</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS.NS</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>1297.699951171875</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1436.300048828125</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1272</v>
+      </c>
+      <c r="H133" t="n">
+        <v>1404.050048828125</v>
+      </c>
+      <c r="I133" t="n">
+        <v>1305.75</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1404.050048828125</v>
+      </c>
+      <c r="K133" t="n">
+        <v>16993686</v>
+      </c>
+      <c r="L133" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS Share Price Today - Dhoot Transmission Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS Share Price Today - Dhoot Transmission Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>13</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>TFCILTD.NS</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>TFCILTD</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>125</v>
+      </c>
+      <c r="F134" t="n">
+        <v>131.9900054931641</v>
+      </c>
+      <c r="G134" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="H134" t="n">
+        <v>131.4100036621094</v>
+      </c>
+      <c r="I134" t="n">
+        <v>123.6999969482422</v>
+      </c>
+      <c r="J134" t="n">
+        <v>131.4100036621094</v>
+      </c>
+      <c r="K134" t="n">
+        <v>18203710</v>
+      </c>
+      <c r="L134" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>14</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>DBOL.NS</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DBOL</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>123</v>
+      </c>
+      <c r="F135" t="n">
+        <v>131.3999938964844</v>
+      </c>
+      <c r="G135" t="n">
+        <v>123</v>
+      </c>
+      <c r="H135" t="n">
+        <v>129.2599945068359</v>
+      </c>
+      <c r="I135" t="n">
+        <v>121.9899978637695</v>
+      </c>
+      <c r="J135" t="n">
+        <v>129.2599945068359</v>
+      </c>
+      <c r="K135" t="n">
+        <v>814499</v>
+      </c>
+      <c r="L135" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>15</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>SINGERIND.NS</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>SINGERIND</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>79.80000305175781</v>
+      </c>
+      <c r="F136" t="n">
+        <v>84.98999786376953</v>
+      </c>
+      <c r="G136" t="n">
+        <v>77.41999816894531</v>
+      </c>
+      <c r="H136" t="n">
+        <v>83.36000061035156</v>
+      </c>
+      <c r="I136" t="n">
+        <v>78.69999694824219</v>
+      </c>
+      <c r="J136" t="n">
+        <v>83.36000061035156</v>
+      </c>
+      <c r="K136" t="n">
+        <v>116136</v>
+      </c>
+      <c r="L136" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>16</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>MARSONS.NS</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>MARSONS</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>102.7799987792969</v>
+      </c>
+      <c r="F137" t="n">
+        <v>111.5999984741211</v>
+      </c>
+      <c r="G137" t="n">
+        <v>102.3099975585938</v>
+      </c>
+      <c r="H137" t="n">
+        <v>108.370002746582</v>
+      </c>
+      <c r="I137" t="n">
+        <v>102.3099975585938</v>
+      </c>
+      <c r="J137" t="n">
+        <v>108.370002746582</v>
+      </c>
+      <c r="K137" t="n">
+        <v>4951490</v>
+      </c>
+      <c r="L137" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Marsons Ltd is Rated Sell by MarketsMOJO - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Marsons Ltd is Rated Sell by MarketsMOJO - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>17</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>RAJSREESUG.NS</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>RAJSREESUG</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="F138" t="n">
+        <v>38.43999862670898</v>
+      </c>
+      <c r="G138" t="n">
+        <v>34.95999908447266</v>
+      </c>
+      <c r="H138" t="n">
+        <v>36.90000152587891</v>
+      </c>
+      <c r="I138" t="n">
+        <v>34.95999908447266</v>
+      </c>
+      <c r="J138" t="n">
+        <v>36.90000152587891</v>
+      </c>
+      <c r="K138" t="n">
+        <v>308611</v>
+      </c>
+      <c r="L138" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>18</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>JNPR.NS</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>JNPR</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>241.1000061035156</v>
+      </c>
+      <c r="F139" t="n">
+        <v>258.7999877929688</v>
+      </c>
+      <c r="G139" t="n">
+        <v>238.8099975585938</v>
+      </c>
+      <c r="H139" t="n">
+        <v>253.7100067138672</v>
+      </c>
+      <c r="I139" t="n">
+        <v>240.5899963378906</v>
+      </c>
+      <c r="J139" t="n">
+        <v>253.7100067138672</v>
+      </c>
+      <c r="K139" t="n">
+        <v>3169674</v>
+      </c>
+      <c r="L139" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>JNPR Share Price Today - Juniper Green Energy Ltd. Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise (HPE Stock) Is Buying Juniper Networks (JNPR Stock) For New AI Technology Solar Flare (dzB5EnUYhH) - Mshale</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise (HPE Stock) Is Buying Juniper Networks (JNPR Stock) For New AI Technology Solar Flare (dzB5EnUYhH) - Mshale</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>HPE Shares Rise, NextEra Falls, Robinhood Launches Stock Tokens | Stock Movers Xrp (mFxBq7V8sx) - Mshale</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>19</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ARIHANTCAP.NS</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ARIHANTCAP</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>73.98000335693359</v>
+      </c>
+      <c r="F140" t="n">
+        <v>79</v>
+      </c>
+      <c r="G140" t="n">
+        <v>73.08999633789062</v>
+      </c>
+      <c r="H140" t="n">
+        <v>77.68000030517578</v>
+      </c>
+      <c r="I140" t="n">
+        <v>73.76999664306641</v>
+      </c>
+      <c r="J140" t="n">
+        <v>77.68000030517578</v>
+      </c>
+      <c r="K140" t="n">
+        <v>541197</v>
+      </c>
+      <c r="L140" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>20</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>EMSLIMITED.NS</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>EMSLIMITED</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>388.7999877929688</v>
+      </c>
+      <c r="F141" t="n">
+        <v>411</v>
+      </c>
+      <c r="G141" t="n">
+        <v>382.2000122070312</v>
+      </c>
+      <c r="H141" t="n">
+        <v>394.9500122070312</v>
+      </c>
+      <c r="I141" t="n">
+        <v>375.75</v>
+      </c>
+      <c r="J141" t="n">
+        <v>394.9500122070312</v>
+      </c>
+      <c r="K141" t="n">
+        <v>3336792</v>
+      </c>
+      <c r="L141" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>EMS shares in focus on project win worth Rs 1,908 crore in Rajasthan - TradingView</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>EMS shares in focus on project win worth Rs 1,908 crore in Rajasthan - TradingView</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7564,7 +8610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q121"/>
+  <dimension ref="A1:Q141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13232,11 +14278,6 @@
       <c r="L102" t="n">
         <v>-10.71</v>
       </c>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -13370,7 +14411,6 @@
           <t>Aakash Exploration Promoters Reshuffle Holdings via Exempt Share Transfer - TipRanks</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -13425,9 +14465,6 @@
           <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - univest.in</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -13482,9 +14519,6 @@
           <t>Average basic shares outstanding of CG-VAK Software &amp; Exports Ltd. – NSE:CGVAK - TradingView</t>
         </is>
       </c>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -13539,9 +14573,6 @@
           <t>Antelopus Selan Energy Ltd Surges 7.14% to Day's High of Rs 857.5 — Outperforms Sector by 6.12 Percentage Points - MarketsMojo</t>
         </is>
       </c>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -13596,9 +14627,6 @@
           <t>Medi-Caps Ltd. Financial Statements – NSE:MEDICAPQ - TradingView</t>
         </is>
       </c>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -13643,11 +14671,6 @@
       <c r="L109" t="n">
         <v>-5.7</v>
       </c>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -13692,11 +14715,6 @@
       <c r="L110" t="n">
         <v>-5.4</v>
       </c>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -13751,9 +14769,6 @@
           <t>Boehly Holds Talks Over Selling Shares To Majority Owners At Chelsea - Complete Sports</t>
         </is>
       </c>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -13798,11 +14813,6 @@
       <c r="L112" t="n">
         <v>-4.99</v>
       </c>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -13926,9 +14936,6 @@
           <t>Sumeet Industries Ltd. Share Price Today: Within 2% of 52-Week Low - univest.in</t>
         </is>
       </c>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -13983,9 +14990,6 @@
           <t>DSJ Keep Learning Posts Q1 FY27 Unaudited Results in Line with SEBI Norms - TipRanks</t>
         </is>
       </c>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -14119,7 +15123,6 @@
           <t>Powerica schedules virtual analyst meet on August 21 - scanx.trade</t>
         </is>
       </c>
-      <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -14233,11 +15236,6 @@
       <c r="L119" t="n">
         <v>-4.92</v>
       </c>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -14282,11 +15280,6 @@
       <c r="L120" t="n">
         <v>-4.84</v>
       </c>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -14341,9 +15334,1118 @@
           <t>Here's Why We Think Plaza Wires (NSE:PLAZACABLE) Is Well Worth Watching - simplywall.st</t>
         </is>
       </c>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>YASHO.NS</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>YASHO</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>4910</v>
+      </c>
+      <c r="F122" t="n">
+        <v>4911.2001953125</v>
+      </c>
+      <c r="G122" t="n">
+        <v>4411.60009765625</v>
+      </c>
+      <c r="H122" t="n">
+        <v>4470.7998046875</v>
+      </c>
+      <c r="I122" t="n">
+        <v>4915.7998046875</v>
+      </c>
+      <c r="J122" t="n">
+        <v>4470.7998046875</v>
+      </c>
+      <c r="K122" t="n">
+        <v>167724</v>
+      </c>
+      <c r="L122" t="n">
+        <v>-9.050000000000001</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd is Rated Buy - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>183.68% Stock Return, 372.3% Profit Growth: What's Driving Yasho Industries Ltd's Multibagger Rerating? - MarketsMojo</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>2</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>DEEPINDS.NS</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>DEEPINDS</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>717.9500122070312</v>
+      </c>
+      <c r="F123" t="n">
+        <v>720</v>
+      </c>
+      <c r="G123" t="n">
+        <v>656.7000122070312</v>
+      </c>
+      <c r="H123" t="n">
+        <v>667.3499755859375</v>
+      </c>
+      <c r="I123" t="n">
+        <v>717.9500122070312</v>
+      </c>
+      <c r="J123" t="n">
+        <v>667.3499755859375</v>
+      </c>
+      <c r="K123" t="n">
+        <v>622935</v>
+      </c>
+      <c r="L123" t="n">
+        <v>-7.05</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>There's A Lot To Like About Deep Industries' (NSE:DEEPINDS) Upcoming ₹2.50 Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>There's A Lot To Like About Deep Industries' (NSE:DEEPINDS) Upcoming ₹2.50 Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>3</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>BHARATSE.NS</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>BHARATSE</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>240.9100036621094</v>
+      </c>
+      <c r="F124" t="n">
+        <v>240.9100036621094</v>
+      </c>
+      <c r="G124" t="n">
+        <v>224.9900054931641</v>
+      </c>
+      <c r="H124" t="n">
+        <v>227.1900024414062</v>
+      </c>
+      <c r="I124" t="n">
+        <v>240.9100036621094</v>
+      </c>
+      <c r="J124" t="n">
+        <v>227.1900024414062</v>
+      </c>
+      <c r="K124" t="n">
+        <v>441229</v>
+      </c>
+      <c r="L124" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>4</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>HATSUN.NS</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>HATSUN</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>985.3499755859375</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G125" t="n">
+        <v>921</v>
+      </c>
+      <c r="H125" t="n">
+        <v>930.2999877929688</v>
+      </c>
+      <c r="I125" t="n">
+        <v>985.3499755859375</v>
+      </c>
+      <c r="J125" t="n">
+        <v>930.2999877929688</v>
+      </c>
+      <c r="K125" t="n">
+        <v>147018</v>
+      </c>
+      <c r="L125" t="n">
+        <v>-5.59</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Hatsun Agro Product Ltd leads losers in 'A' group - Dailyhunt</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Hatsun Agro Product Ltd leads losers in 'A' group - Dailyhunt</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>5</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>SUYOG.NS</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>SUYOG</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>801.8499755859375</v>
+      </c>
+      <c r="F126" t="n">
+        <v>805.0499877929688</v>
+      </c>
+      <c r="G126" t="n">
+        <v>750.5</v>
+      </c>
+      <c r="H126" t="n">
+        <v>759.25</v>
+      </c>
+      <c r="I126" t="n">
+        <v>801.2000122070312</v>
+      </c>
+      <c r="J126" t="n">
+        <v>759.25</v>
+      </c>
+      <c r="K126" t="n">
+        <v>90236</v>
+      </c>
+      <c r="L126" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Suyog Tele Standalone June 2026 Net Sales at Rs 65.27 crore, up 26.45% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Suyog Telematics Downgraded to Sell Amid Technical and Valuation Concerns - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Suyog Gurbaxani Funicular Ropeways recommends ₹0.50 final dividend for FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Suyog Gurbaxani Funicular Ropeways Ltd. (SGFRL) Share Price Rises 8.25% Today - Univest</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>Suyog Telematics Downgraded to Sell Amid Technical and Valuation Concerns - MarketsMojo</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>6</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>WEBELSOLAR.NS</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>WEBELSOLAR</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>86.93000030517578</v>
+      </c>
+      <c r="F127" t="n">
+        <v>87.12000274658203</v>
+      </c>
+      <c r="G127" t="n">
+        <v>82.58999633789062</v>
+      </c>
+      <c r="H127" t="n">
+        <v>82.72000122070312</v>
+      </c>
+      <c r="I127" t="n">
+        <v>86.93000030517578</v>
+      </c>
+      <c r="J127" t="n">
+        <v>82.72000122070312</v>
+      </c>
+      <c r="K127" t="n">
+        <v>2436130</v>
+      </c>
+      <c r="L127" t="n">
+        <v>-4.84</v>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>7</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>KUSUMGAR.NS</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>KUSUMGAR</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>595.9500122070312</v>
+      </c>
+      <c r="F128" t="n">
+        <v>599</v>
+      </c>
+      <c r="G128" t="n">
+        <v>560.7000122070312</v>
+      </c>
+      <c r="H128" t="n">
+        <v>566.3499755859375</v>
+      </c>
+      <c r="I128" t="n">
+        <v>595</v>
+      </c>
+      <c r="J128" t="n">
+        <v>566.3499755859375</v>
+      </c>
+      <c r="K128" t="n">
+        <v>451848</v>
+      </c>
+      <c r="L128" t="n">
+        <v>-4.82</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Kusumgar seeks shareholder approval to ratify ESOP scheme post-IPO - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Kusumgar seeks shareholder approval to ratify ESOP scheme post-IPO - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>8</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ACUTAAS.NS</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ACUTAAS</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>3399.10009765625</v>
+      </c>
+      <c r="F129" t="n">
+        <v>3399.10009765625</v>
+      </c>
+      <c r="G129" t="n">
+        <v>3219</v>
+      </c>
+      <c r="H129" t="n">
+        <v>3228.89990234375</v>
+      </c>
+      <c r="I129" t="n">
+        <v>3391.39990234375</v>
+      </c>
+      <c r="J129" t="n">
+        <v>3228.89990234375</v>
+      </c>
+      <c r="K129" t="n">
+        <v>279967</v>
+      </c>
+      <c r="L129" t="n">
+        <v>-4.79</v>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>9</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>AARTIPHARM.NS</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>AARTIPHARM</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>878</v>
+      </c>
+      <c r="F130" t="n">
+        <v>878.9500122070312</v>
+      </c>
+      <c r="G130" t="n">
+        <v>826.5499877929688</v>
+      </c>
+      <c r="H130" t="n">
+        <v>834.1500244140625</v>
+      </c>
+      <c r="I130" t="n">
+        <v>874.5499877929688</v>
+      </c>
+      <c r="J130" t="n">
+        <v>834.1500244140625</v>
+      </c>
+      <c r="K130" t="n">
+        <v>377267</v>
+      </c>
+      <c r="L130" t="n">
+        <v>-4.62</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>AARTIPHARM Consolidated June 2026 Net Sales at Rs 535.80 crore, up 38.74% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>AARTIPHARM Consolidated June 2026 Net Sales at Rs 535.80 crore, up 38.74% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Mercantile Ventures Posts Consolidated Net Loss of Rs 0.65 Crore in June 2026 Quarter; Sales Climb 9.25% - Guidance Revision Trend - Vinanet</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>10</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>DBREALTY.NS</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>DBREALTY</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="F131" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="G131" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="H131" t="n">
+        <v>101.7900009155273</v>
+      </c>
+      <c r="I131" t="n">
+        <v>106.4800033569336</v>
+      </c>
+      <c r="J131" t="n">
+        <v>101.7900009155273</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1242300</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>11</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>CEMPRO.NS</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>CEMPRO</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>1324</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1334</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1257.800048828125</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1265.699951171875</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1324</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1265.699951171875</v>
+      </c>
+      <c r="K132" t="n">
+        <v>344424</v>
+      </c>
+      <c r="L132" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>12</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>INDOFARM.NS</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>INDOFARM</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>143.8999938964844</v>
+      </c>
+      <c r="F133" t="n">
+        <v>144.1699981689453</v>
+      </c>
+      <c r="G133" t="n">
+        <v>135.9100036621094</v>
+      </c>
+      <c r="H133" t="n">
+        <v>137.1600036621094</v>
+      </c>
+      <c r="I133" t="n">
+        <v>143.3300018310547</v>
+      </c>
+      <c r="J133" t="n">
+        <v>137.1600036621094</v>
+      </c>
+      <c r="K133" t="n">
+        <v>324275</v>
+      </c>
+      <c r="L133" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>13</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SHREERAMA.NS</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>SHREERAMA</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>46.79999923706055</v>
+      </c>
+      <c r="F134" t="n">
+        <v>46.79999923706055</v>
+      </c>
+      <c r="G134" t="n">
+        <v>44.11000061035156</v>
+      </c>
+      <c r="H134" t="n">
+        <v>44.36999893188477</v>
+      </c>
+      <c r="I134" t="n">
+        <v>46.34000015258789</v>
+      </c>
+      <c r="J134" t="n">
+        <v>44.36999893188477</v>
+      </c>
+      <c r="K134" t="n">
+        <v>113898</v>
+      </c>
+      <c r="L134" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>14</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>THYROCARE.NS</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>THYROCARE</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>620</v>
+      </c>
+      <c r="F135" t="n">
+        <v>620</v>
+      </c>
+      <c r="G135" t="n">
+        <v>577</v>
+      </c>
+      <c r="H135" t="n">
+        <v>582.5</v>
+      </c>
+      <c r="I135" t="n">
+        <v>608.25</v>
+      </c>
+      <c r="J135" t="n">
+        <v>582.5</v>
+      </c>
+      <c r="K135" t="n">
+        <v>544224</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>API Holdings turns debt-free — frees Thyrocare shares from pledge - expresshealthcare.in</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>API Holdings Clears ₹1,050 Cr Debt, Unpledges Thyrocare Stake - BW Healthcare</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>API Holdings repays Rs 1050 Cr, frees Thyrocare shares from pledge - BioSpectrum India</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Why PharmEasy Keeps Selling Thyrocare Shares? - UnlistedZone</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>API Holdings Clears ₹1,050 Cr Debt, Unpledges Thyrocare Stake - BW Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>15</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>BATAINDIA.NS</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>730</v>
+      </c>
+      <c r="F136" t="n">
+        <v>730</v>
+      </c>
+      <c r="G136" t="n">
+        <v>710.1500244140625</v>
+      </c>
+      <c r="H136" t="n">
+        <v>721.2999877929688</v>
+      </c>
+      <c r="I136" t="n">
+        <v>753.0999755859375</v>
+      </c>
+      <c r="J136" t="n">
+        <v>721.2999877929688</v>
+      </c>
+      <c r="K136" t="n">
+        <v>770121</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-4.22</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Here's What Analysts Are Forecasting For Bata India Limited (NSE:BATAINDIA) After Its First-Quarter Results - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Here's What Analysts Are Forecasting For Bata India Limited (NSE:BATAINDIA) After Its First-Quarter Results - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>16</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>KRISHNADEF.NS</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>KRISHNADEF</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>1130</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1143.699951171875</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1072</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1077.800048828125</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1125</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1077.800048828125</v>
+      </c>
+      <c r="K137" t="n">
+        <v>94943</v>
+      </c>
+      <c r="L137" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>17</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>POWERINDIA.NS</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>POWERINDIA</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>35100</v>
+      </c>
+      <c r="F138" t="n">
+        <v>35100</v>
+      </c>
+      <c r="G138" t="n">
+        <v>33360</v>
+      </c>
+      <c r="H138" t="n">
+        <v>33800</v>
+      </c>
+      <c r="I138" t="n">
+        <v>35275</v>
+      </c>
+      <c r="J138" t="n">
+        <v>33800</v>
+      </c>
+      <c r="K138" t="n">
+        <v>186593</v>
+      </c>
+      <c r="L138" t="n">
+        <v>-4.18</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Hitachi Energy India Stock Leads A Fresh Look At Power Capex Winners - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Hitachi Energy India Stock Leads A Fresh Look At Power Capex Winners - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>POWERINDIA Share Price | Hitachi Energy India Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>18</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>FILATEX.NS</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>FILATEX</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="F139" t="n">
+        <v>86.59999847412109</v>
+      </c>
+      <c r="G139" t="n">
+        <v>82.51000213623047</v>
+      </c>
+      <c r="H139" t="n">
+        <v>83.15000152587891</v>
+      </c>
+      <c r="I139" t="n">
+        <v>86.75</v>
+      </c>
+      <c r="J139" t="n">
+        <v>83.15000152587891</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1502803</v>
+      </c>
+      <c r="L139" t="n">
+        <v>-4.15</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Filatex Fashions fined ₹56,640 each by NSE and BSE for compliance lapse - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Filatex Fashions Share News Today,filatex Fashions Share Analysis,filatex Fashions Share Price/news Julio Rodríguez (hxc2EVlwyH) - Mshale</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Filatex Fashion | Filatex Fashion Share Latest News | Filatex Fashion News | Filatex Fashion Share Cigarette (pEVfqWC9K9) - Mshale</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Filatex Fashions Share News Today,filatex Fashions Share Analysis,filatex Fashions Share Price/news Julio Rodríguez (hxc2EVlwyH) - Mshale</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>19</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>GUJRAFFIA.NS</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>GUJRAFFIA</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>42.45000076293945</v>
+      </c>
+      <c r="F140" t="n">
+        <v>42.45000076293945</v>
+      </c>
+      <c r="G140" t="n">
+        <v>40.2599983215332</v>
+      </c>
+      <c r="H140" t="n">
+        <v>40.65999984741211</v>
+      </c>
+      <c r="I140" t="n">
+        <v>42.40999984741211</v>
+      </c>
+      <c r="J140" t="n">
+        <v>40.65999984741211</v>
+      </c>
+      <c r="K140" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L140" t="n">
+        <v>-4.13</v>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-20 08:55:20</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>20</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>3MINDIA.NS</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>3MINDIA</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>35100</v>
+      </c>
+      <c r="F141" t="n">
+        <v>35100</v>
+      </c>
+      <c r="G141" t="n">
+        <v>33355</v>
+      </c>
+      <c r="H141" t="n">
+        <v>33505</v>
+      </c>
+      <c r="I141" t="n">
+        <v>34945</v>
+      </c>
+      <c r="J141" t="n">
+        <v>33505</v>
+      </c>
+      <c r="K141" t="n">
+        <v>7449</v>
+      </c>
+      <c r="L141" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Gainers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Losers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gainers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Losers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q141"/>
+  <dimension ref="A1:Q221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7542,11 +7542,6 @@
       <c r="L122" t="n">
         <v>15.03</v>
       </c>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7601,9 +7596,6 @@
           <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7717,11 +7709,6 @@
       <c r="L125" t="n">
         <v>12.05</v>
       </c>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7766,11 +7753,6 @@
       <c r="L126" t="n">
         <v>11.41</v>
       </c>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7815,11 +7797,6 @@
       <c r="L127" t="n">
         <v>10.82</v>
       </c>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7953,7 +7930,6 @@
           <t>Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView</t>
         </is>
       </c>
-      <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7998,11 +7974,6 @@
       <c r="L130" t="n">
         <v>9.52</v>
       </c>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8047,11 +8018,6 @@
       <c r="L131" t="n">
         <v>9.51</v>
       </c>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8106,9 +8072,6 @@
           <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
         </is>
       </c>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8173,7 +8136,6 @@
           <t>DHOOTTRANS Share Price Today - Dhoot Transmission Stock Analysis - Equitypandit</t>
         </is>
       </c>
-      <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8218,11 +8180,6 @@
       <c r="L134" t="n">
         <v>6.23</v>
       </c>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8267,11 +8224,6 @@
       <c r="L135" t="n">
         <v>5.96</v>
       </c>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8316,11 +8268,6 @@
       <c r="L136" t="n">
         <v>5.92</v>
       </c>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8375,9 +8322,6 @@
           <t>Marsons Ltd is Rated Sell by MarketsMOJO - MarketsMojo</t>
         </is>
       </c>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8422,11 +8366,6 @@
       <c r="L138" t="n">
         <v>5.55</v>
       </c>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8491,7 +8430,6 @@
           <t>HPE Shares Rise, NextEra Falls, Robinhood Launches Stock Tokens | Stock Movers Xrp (mFxBq7V8sx) - Mshale</t>
         </is>
       </c>
-      <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8536,11 +8474,6 @@
       <c r="L140" t="n">
         <v>5.3</v>
       </c>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8595,9 +8528,4632 @@
           <t>EMS shares in focus on project win worth Rs 1,908 crore in Rajasthan - TradingView</t>
         </is>
       </c>
-      <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>KOTARISUG.NS</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>KOTARISUG</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>27.8799991607666</v>
+      </c>
+      <c r="F142" t="n">
+        <v>31.10000038146973</v>
+      </c>
+      <c r="G142" t="n">
+        <v>27.68000030517578</v>
+      </c>
+      <c r="H142" t="n">
+        <v>30.95999908447266</v>
+      </c>
+      <c r="I142" t="n">
+        <v>27.21999931335449</v>
+      </c>
+      <c r="J142" t="n">
+        <v>30.95999908447266</v>
+      </c>
+      <c r="K142" t="n">
+        <v>600574</v>
+      </c>
+      <c r="L142" t="n">
+        <v>13.74</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>2</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>DWARKESH.NS</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>DWARKESH</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>48.77000045776367</v>
+      </c>
+      <c r="F143" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="G143" t="n">
+        <v>48.70000076293945</v>
+      </c>
+      <c r="H143" t="n">
+        <v>54.40999984741211</v>
+      </c>
+      <c r="I143" t="n">
+        <v>48.27999877929688</v>
+      </c>
+      <c r="J143" t="n">
+        <v>54.40999984741211</v>
+      </c>
+      <c r="K143" t="n">
+        <v>20638915</v>
+      </c>
+      <c r="L143" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar surges more than 6% on buyback plans, fixes record date on March 20 - Upstox</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>3</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN.NS</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>658.25</v>
+      </c>
+      <c r="F144" t="n">
+        <v>735</v>
+      </c>
+      <c r="G144" t="n">
+        <v>655.0499877929688</v>
+      </c>
+      <c r="H144" t="n">
+        <v>730.5</v>
+      </c>
+      <c r="I144" t="n">
+        <v>650.7999877929688</v>
+      </c>
+      <c r="J144" t="n">
+        <v>730.5</v>
+      </c>
+      <c r="K144" t="n">
+        <v>9153703</v>
+      </c>
+      <c r="L144" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price Hits One-Year High - Univest</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>4</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>KRONOX.NS</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>KRONOX</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>155.0099945068359</v>
+      </c>
+      <c r="F145" t="n">
+        <v>175</v>
+      </c>
+      <c r="G145" t="n">
+        <v>155.0099945068359</v>
+      </c>
+      <c r="H145" t="n">
+        <v>172.8600006103516</v>
+      </c>
+      <c r="I145" t="n">
+        <v>155.1600036621094</v>
+      </c>
+      <c r="J145" t="n">
+        <v>172.8600006103516</v>
+      </c>
+      <c r="K145" t="n">
+        <v>1562028</v>
+      </c>
+      <c r="L145" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Share Price Rise With Peer Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Share Price Rise With Peer Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Q1 Results: Net profit up 60% YoY to ₹25.8 crore - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>5</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>KOHINOOR.NS</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>KOHINOOR</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>32.09999847412109</v>
+      </c>
+      <c r="F146" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G146" t="n">
+        <v>30.95000076293945</v>
+      </c>
+      <c r="H146" t="n">
+        <v>34.54999923706055</v>
+      </c>
+      <c r="I146" t="n">
+        <v>31.27000045776367</v>
+      </c>
+      <c r="J146" t="n">
+        <v>34.54999923706055</v>
+      </c>
+      <c r="K146" t="n">
+        <v>1289439</v>
+      </c>
+      <c r="L146" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd is Rated Strong Sell - marketsmojo.com</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods to Review Quarterly Results and Mull Fundraising at August Board Meeting - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>6</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>CORDELIA.NS</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>CORDELIA</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>820.5499877929688</v>
+      </c>
+      <c r="F147" t="n">
+        <v>907.75</v>
+      </c>
+      <c r="G147" t="n">
+        <v>820.5499877929688</v>
+      </c>
+      <c r="H147" t="n">
+        <v>907.75</v>
+      </c>
+      <c r="I147" t="n">
+        <v>825.25</v>
+      </c>
+      <c r="J147" t="n">
+        <v>907.75</v>
+      </c>
+      <c r="K147" t="n">
+        <v>681030</v>
+      </c>
+      <c r="L147" t="n">
+        <v>10</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Waterways Leisure Tourism Limited Share Price Today,, CORDELIA Share Price NSE, BSE - Business Today</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Waterways Leisure Tourism Limited Share Price Today,, CORDELIA Share Price NSE, BSE - Business Today</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>7</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>BAJAJHIND.NS</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>BAJAJHIND</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>20.73999977111816</v>
+      </c>
+      <c r="F148" t="n">
+        <v>22.6200008392334</v>
+      </c>
+      <c r="G148" t="n">
+        <v>20.59000015258789</v>
+      </c>
+      <c r="H148" t="n">
+        <v>22.3700008392334</v>
+      </c>
+      <c r="I148" t="n">
+        <v>20.3799991607666</v>
+      </c>
+      <c r="J148" t="n">
+        <v>22.3700008392334</v>
+      </c>
+      <c r="K148" t="n">
+        <v>116977075</v>
+      </c>
+      <c r="L148" t="n">
+        <v>9.76</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>8</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SIGACHI.NS</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>SIGACHI</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>29</v>
+      </c>
+      <c r="F149" t="n">
+        <v>31.81999969482422</v>
+      </c>
+      <c r="G149" t="n">
+        <v>29</v>
+      </c>
+      <c r="H149" t="n">
+        <v>31.68000030517578</v>
+      </c>
+      <c r="I149" t="n">
+        <v>28.8799991607666</v>
+      </c>
+      <c r="J149" t="n">
+        <v>31.68000030517578</v>
+      </c>
+      <c r="K149" t="n">
+        <v>5747826</v>
+      </c>
+      <c r="L149" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Sigachi Industries Share Price Today Up 8.33%: Stock View - Univest</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Sigachi Industries Share Price Today Up 8.33%: Stock View - Univest</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Sigachi Industries board to consider preferential issue on August 22 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Sigachi Ind Q1 Results FY27: PAT Rs 8 Cr, Revenue Rs 121 crore - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>9</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>MAWANASUG.NS</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>MAWANASUG</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>130.9900054931641</v>
+      </c>
+      <c r="F150" t="n">
+        <v>142.7400054931641</v>
+      </c>
+      <c r="G150" t="n">
+        <v>129.3000030517578</v>
+      </c>
+      <c r="H150" t="n">
+        <v>140.8000030517578</v>
+      </c>
+      <c r="I150" t="n">
+        <v>128.7200012207031</v>
+      </c>
+      <c r="J150" t="n">
+        <v>140.8000030517578</v>
+      </c>
+      <c r="K150" t="n">
+        <v>1031984</v>
+      </c>
+      <c r="L150" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Mawana Sugars Ltd. Share Price Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Mawana Sugars Ltd. Share Price Near 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>10</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>NIBE.NS</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NIBE</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>1435</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1542.800048828125</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1421</v>
+      </c>
+      <c r="H151" t="n">
+        <v>1536.5</v>
+      </c>
+      <c r="I151" t="n">
+        <v>1411.099975585938</v>
+      </c>
+      <c r="J151" t="n">
+        <v>1536.5</v>
+      </c>
+      <c r="K151" t="n">
+        <v>220045</v>
+      </c>
+      <c r="L151" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>NIBE Q1 FY27 Results: Revenue fell to Rs 63 Cr, Net Loss -1300% - Univest</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Di: This is what it will take for the Nibe stock to gain momentum - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Di: This is what it will take for the Nibe stock to gain momentum - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Nibe Industrier stock holds steady as leadership change adds to long term growth story - Ad-hoc-news.de</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Nibe Industrier stock holds firm after Q2 sales rose - Ad-hoc-news.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>11</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>RANASUG.NS</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>RANASUG</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>13.85999965667725</v>
+      </c>
+      <c r="F152" t="n">
+        <v>14.89999961853027</v>
+      </c>
+      <c r="G152" t="n">
+        <v>13.85999965667725</v>
+      </c>
+      <c r="H152" t="n">
+        <v>14.85999965667725</v>
+      </c>
+      <c r="I152" t="n">
+        <v>13.76000022888184</v>
+      </c>
+      <c r="J152" t="n">
+        <v>14.85999965667725</v>
+      </c>
+      <c r="K152" t="n">
+        <v>1570432</v>
+      </c>
+      <c r="L152" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>12</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>KAYA.NS</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>KAYA</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>339.9500122070312</v>
+      </c>
+      <c r="F153" t="n">
+        <v>370</v>
+      </c>
+      <c r="G153" t="n">
+        <v>336.5499877929688</v>
+      </c>
+      <c r="H153" t="n">
+        <v>365.1000061035156</v>
+      </c>
+      <c r="I153" t="n">
+        <v>338.4500122070312</v>
+      </c>
+      <c r="J153" t="n">
+        <v>365.1000061035156</v>
+      </c>
+      <c r="K153" t="n">
+        <v>114640</v>
+      </c>
+      <c r="L153" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Scholastic director Kaya Henderson sells $130,812 in stock - Investing.com</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Wladimir Klitschko vows to protect Hayden Panettiere’s memory for daughter Kaya as WWE star Jacob Fatu sh - The Times of India</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Wladimir Klitschko vows to protect Hayden Panettiere’s memory for daughter Kaya as WWE star Jacob Fatu sh - The Times of India</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Kaya To Issue 1.82 Million Equity Shares At 274.10 Rupees Per Share For Aggregate Cash Consideration Of Approx 500 Million Rupees - TradingView</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Kaya Standalone June 2026 Net Sales at Rs 60.14 crore, up 13.91% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>13</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>TRIVENI.NS</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>TRIVENI</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>294.1199951171875</v>
+      </c>
+      <c r="F154" t="n">
+        <v>314.8999938964844</v>
+      </c>
+      <c r="G154" t="n">
+        <v>288.6099853515625</v>
+      </c>
+      <c r="H154" t="n">
+        <v>311.9599914550781</v>
+      </c>
+      <c r="I154" t="n">
+        <v>289.2300109863281</v>
+      </c>
+      <c r="J154" t="n">
+        <v>311.9599914550781</v>
+      </c>
+      <c r="K154" t="n">
+        <v>2564300</v>
+      </c>
+      <c r="L154" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Triveni Engineering &amp; Industries Ltd. Share Price Up 5.66% - Univest</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Triveni Turbine Standalone June 2026 Net Sales at Rs 396.80 crore, up 15.15% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Triveni Turbine Standalone June 2026 Net Sales at Rs 396.80 crore, up 15.15% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Triveni Turbine shares tumble 8% after Q1 profit drops 20%, margins shrink - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Triveni Turbine shares fall most in over a year after profit declines 25% in June quarter - Upstox</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>14</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>DALMIASUG.NS</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>DALMIASUG</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>475.8500061035156</v>
+      </c>
+      <c r="F155" t="n">
+        <v>517</v>
+      </c>
+      <c r="G155" t="n">
+        <v>469.2000122070312</v>
+      </c>
+      <c r="H155" t="n">
+        <v>512.5</v>
+      </c>
+      <c r="I155" t="n">
+        <v>475.5499877929688</v>
+      </c>
+      <c r="J155" t="n">
+        <v>512.5</v>
+      </c>
+      <c r="K155" t="n">
+        <v>1114213</v>
+      </c>
+      <c r="L155" t="n">
+        <v>7.77</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>15</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>DHAMPURSUG.NS</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>DHAMPURSUG</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>179.6999969482422</v>
+      </c>
+      <c r="F156" t="n">
+        <v>190.75</v>
+      </c>
+      <c r="G156" t="n">
+        <v>178.9700012207031</v>
+      </c>
+      <c r="H156" t="n">
+        <v>189.7599945068359</v>
+      </c>
+      <c r="I156" t="n">
+        <v>176.1799926757812</v>
+      </c>
+      <c r="J156" t="n">
+        <v>189.7599945068359</v>
+      </c>
+      <c r="K156" t="n">
+        <v>3234786</v>
+      </c>
+      <c r="L156" t="n">
+        <v>7.71</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>16</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>RAJSREESUG.NS</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>RAJSREESUG</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>37.0099983215332</v>
+      </c>
+      <c r="F157" t="n">
+        <v>40.79000091552734</v>
+      </c>
+      <c r="G157" t="n">
+        <v>37</v>
+      </c>
+      <c r="H157" t="n">
+        <v>39.66999816894531</v>
+      </c>
+      <c r="I157" t="n">
+        <v>36.90000152587891</v>
+      </c>
+      <c r="J157" t="n">
+        <v>39.66999816894531</v>
+      </c>
+      <c r="K157" t="n">
+        <v>456618</v>
+      </c>
+      <c r="L157" t="n">
+        <v>7.51</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>17</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>EBGNG.NS</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>EBGNG</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>594</v>
+      </c>
+      <c r="F158" t="n">
+        <v>634.5</v>
+      </c>
+      <c r="G158" t="n">
+        <v>589.1500244140625</v>
+      </c>
+      <c r="H158" t="n">
+        <v>632.5</v>
+      </c>
+      <c r="I158" t="n">
+        <v>588.4000244140625</v>
+      </c>
+      <c r="J158" t="n">
+        <v>632.5</v>
+      </c>
+      <c r="K158" t="n">
+        <v>1013581</v>
+      </c>
+      <c r="L158" t="n">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>18</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>KWIL.NS</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>KWIL</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>38</v>
+      </c>
+      <c r="F159" t="n">
+        <v>40.56999969482422</v>
+      </c>
+      <c r="G159" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="H159" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="I159" t="n">
+        <v>37.70999908447266</v>
+      </c>
+      <c r="J159" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K159" t="n">
+        <v>26481751</v>
+      </c>
+      <c r="L159" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>19</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>RENUKA.NS</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>RENUKA</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>24.70000076293945</v>
+      </c>
+      <c r="F160" t="n">
+        <v>26.19000053405762</v>
+      </c>
+      <c r="G160" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H160" t="n">
+        <v>26.03000068664551</v>
+      </c>
+      <c r="I160" t="n">
+        <v>24.23999977111816</v>
+      </c>
+      <c r="J160" t="n">
+        <v>26.03000068664551</v>
+      </c>
+      <c r="K160" t="n">
+        <v>51382325</v>
+      </c>
+      <c r="L160" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Sweet Gains Continue: Shree Renuka, Dalmia Bharat Rally Up To 7% Despite Govt's Inventory Clampdown - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Sweet Gains Continue: Shree Renuka, Dalmia Bharat Rally Up To 7% Despite Govt's Inventory Clampdown - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Bajaj Hind, Dwarikesh, Renuka rally up to 14%; what's driving sugar stocks? - Business Standard</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Sugar stocks: Bajaj Hindusthan, Shree Renuka, Dwarikesh shares rally up to 12%; here's why - Business Today</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>Shree Renuka Standalone June 2026 Net Sales at Rs 1,969.70 crore, up 3.49% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>20</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>KIRIINDUS.NS</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>KIRIINDUS</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>435</v>
+      </c>
+      <c r="F161" t="n">
+        <v>479.9500122070312</v>
+      </c>
+      <c r="G161" t="n">
+        <v>434</v>
+      </c>
+      <c r="H161" t="n">
+        <v>463</v>
+      </c>
+      <c r="I161" t="n">
+        <v>431.2999877929688</v>
+      </c>
+      <c r="J161" t="n">
+        <v>463</v>
+      </c>
+      <c r="K161" t="n">
+        <v>5013020</v>
+      </c>
+      <c r="L161" t="n">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN.NS</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>658.25</v>
+      </c>
+      <c r="F162" t="n">
+        <v>738</v>
+      </c>
+      <c r="G162" t="n">
+        <v>655.0499877929688</v>
+      </c>
+      <c r="H162" t="n">
+        <v>731</v>
+      </c>
+      <c r="I162" t="n">
+        <v>650.7999877929688</v>
+      </c>
+      <c r="J162" t="n">
+        <v>731</v>
+      </c>
+      <c r="K162" t="n">
+        <v>10644454</v>
+      </c>
+      <c r="L162" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd Share Price Target, Forecast for Long Term Equity. - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price Hits One-Year High - Univest</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>2</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>RAJSREESUG.NS</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>RAJSREESUG</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>37.0099983215332</v>
+      </c>
+      <c r="F163" t="n">
+        <v>40.79000091552734</v>
+      </c>
+      <c r="G163" t="n">
+        <v>37</v>
+      </c>
+      <c r="H163" t="n">
+        <v>40.2400016784668</v>
+      </c>
+      <c r="I163" t="n">
+        <v>36.90000152587891</v>
+      </c>
+      <c r="J163" t="n">
+        <v>40.2400016784668</v>
+      </c>
+      <c r="K163" t="n">
+        <v>469135</v>
+      </c>
+      <c r="L163" t="n">
+        <v>9.050000000000001</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>3</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>BAJAJHIND.NS</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>BAJAJHIND</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>20.73999977111816</v>
+      </c>
+      <c r="F164" t="n">
+        <v>22.6200008392334</v>
+      </c>
+      <c r="G164" t="n">
+        <v>20.59000015258789</v>
+      </c>
+      <c r="H164" t="n">
+        <v>22.14999961853027</v>
+      </c>
+      <c r="I164" t="n">
+        <v>20.3799991607666</v>
+      </c>
+      <c r="J164" t="n">
+        <v>22.14999961853027</v>
+      </c>
+      <c r="K164" t="n">
+        <v>123549787</v>
+      </c>
+      <c r="L164" t="n">
+        <v>8.68</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>4</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>DHAMPURSUG.NS</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>DHAMPURSUG</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>179.6999969482422</v>
+      </c>
+      <c r="F165" t="n">
+        <v>190.75</v>
+      </c>
+      <c r="G165" t="n">
+        <v>178.9700012207031</v>
+      </c>
+      <c r="H165" t="n">
+        <v>188.3999938964844</v>
+      </c>
+      <c r="I165" t="n">
+        <v>176.1799926757812</v>
+      </c>
+      <c r="J165" t="n">
+        <v>188.3999938964844</v>
+      </c>
+      <c r="K165" t="n">
+        <v>3343971</v>
+      </c>
+      <c r="L165" t="n">
+        <v>6.94</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>5</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ZUARIIND.NS</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ZUARIIND</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>268.8999938964844</v>
+      </c>
+      <c r="F166" t="n">
+        <v>284.8999938964844</v>
+      </c>
+      <c r="G166" t="n">
+        <v>261.8500061035156</v>
+      </c>
+      <c r="H166" t="n">
+        <v>278</v>
+      </c>
+      <c r="I166" t="n">
+        <v>262.1000061035156</v>
+      </c>
+      <c r="J166" t="n">
+        <v>278</v>
+      </c>
+      <c r="K166" t="n">
+        <v>273901</v>
+      </c>
+      <c r="L166" t="n">
+        <v>6.07</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>6</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ARVIND.NS</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>ARVIND</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>519.9000244140625</v>
+      </c>
+      <c r="F167" t="n">
+        <v>541</v>
+      </c>
+      <c r="G167" t="n">
+        <v>519.5499877929688</v>
+      </c>
+      <c r="H167" t="n">
+        <v>534.9500122070312</v>
+      </c>
+      <c r="I167" t="n">
+        <v>516.5</v>
+      </c>
+      <c r="J167" t="n">
+        <v>534.9500122070312</v>
+      </c>
+      <c r="K167" t="n">
+        <v>524222</v>
+      </c>
+      <c r="L167" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Arvind Ltd sets September 4 deadline for dividend tax docs - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Arvind Ltd sets September 4 deadline for dividend tax docs - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: Arvind posts strong Q1 2026 growth, shares slip - Investing.com</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Arvind sees no immediate acquisitions, focuses on Dalco GFT integration - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Rubrik CTO Arvind Nithrakashyap Sells $3.0 Million Stock - The Motley Fool</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>7</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>EIDPARRY.NS</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>EIDPARRY</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>793.7999877929688</v>
+      </c>
+      <c r="F168" t="n">
+        <v>814.8499755859375</v>
+      </c>
+      <c r="G168" t="n">
+        <v>787.5499877929688</v>
+      </c>
+      <c r="H168" t="n">
+        <v>812</v>
+      </c>
+      <c r="I168" t="n">
+        <v>787.0499877929688</v>
+      </c>
+      <c r="J168" t="n">
+        <v>812</v>
+      </c>
+      <c r="K168" t="n">
+        <v>1036297</v>
+      </c>
+      <c r="L168" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Raja Venkatraman recommends three stocks for 5 August - livemint.com</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Abakkus, Carnelian, Motilal Oswal acquire additional 2.9% Anawil Wire shares; promoter offloads Rs 171 crore worth Capillary Tech shares - TradingView</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Abakkus, Carnelian, Motilal Oswal acquire additional 2.9% Anawil Wire shares; promoter offloads Rs 171 crore worth Capillary Tech shares - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>8</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>DCW.NS</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>DCW</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>43.47000122070312</v>
+      </c>
+      <c r="F169" t="n">
+        <v>44.38000106811523</v>
+      </c>
+      <c r="G169" t="n">
+        <v>43.33000183105469</v>
+      </c>
+      <c r="H169" t="n">
+        <v>44.08000183105469</v>
+      </c>
+      <c r="I169" t="n">
+        <v>43.2599983215332</v>
+      </c>
+      <c r="J169" t="n">
+        <v>44.08000183105469</v>
+      </c>
+      <c r="K169" t="n">
+        <v>359701</v>
+      </c>
+      <c r="L169" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>DCW Share Price Target 2027 to 2030: Analyst Outlook - Univest</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>DCW Limited recognized as Three Star Export House till 2031 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>DCW Limited recognized as Three Star Export House till 2031 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>‘Call 181, receive justice quickly’: Delhi DCW Chair Lata Gupta's first message after appointment - The Economic Times</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>DCW Limited to host Q1FY27 earnings call on August 14 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>9</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>SAIL.NS</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>174.1000061035156</v>
+      </c>
+      <c r="F170" t="n">
+        <v>176.4299926757812</v>
+      </c>
+      <c r="G170" t="n">
+        <v>173.4100036621094</v>
+      </c>
+      <c r="H170" t="n">
+        <v>175.0500030517578</v>
+      </c>
+      <c r="I170" t="n">
+        <v>172.75</v>
+      </c>
+      <c r="J170" t="n">
+        <v>175.0500030517578</v>
+      </c>
+      <c r="K170" t="n">
+        <v>7667643</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>SailPoint (SAIL) Holds A Special Call, Is The Stock Already Overvalued? - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>SailPoint (SAIL) Holds A Special Call, Is The Stock Already Overvalued? - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>CrowdStrike Setup 'Constructive,' But Truist Favors Rubrik, SailPoint Ahead Of Q2 Earnings - TradingView</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>SailPoint (SAIL) Outlook: Records a Muted Move to $19.19 on the Day; Chart View: Price Remains Between $18.23 Support and $20.15 Resistance in the Latest Session - Daily Profile - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>A 9-Day Winning Streak Has SailPoint Stock Up 25% - Trefis</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>10</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>BOMDYEING.NS</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>BOMDYEING</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>113.2399978637695</v>
+      </c>
+      <c r="F171" t="n">
+        <v>113.4300003051758</v>
+      </c>
+      <c r="G171" t="n">
+        <v>112.6600036621094</v>
+      </c>
+      <c r="H171" t="n">
+        <v>112.9199981689453</v>
+      </c>
+      <c r="I171" t="n">
+        <v>111.5699996948242</v>
+      </c>
+      <c r="J171" t="n">
+        <v>112.9199981689453</v>
+      </c>
+      <c r="K171" t="n">
+        <v>135790</v>
+      </c>
+      <c r="L171" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>BOMDYEING Standalone June 2026 Net Sales at Rs 410.80 crore, up 8.72% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>BOMDYEING Standalone June 2026 Net Sales at Rs 410.80 crore, up 8.72% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>11</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ASHOKLEY.NS</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>174.6999969482422</v>
+      </c>
+      <c r="F172" t="n">
+        <v>175.5700073242188</v>
+      </c>
+      <c r="G172" t="n">
+        <v>173.7400054931641</v>
+      </c>
+      <c r="H172" t="n">
+        <v>174.8600006103516</v>
+      </c>
+      <c r="I172" t="n">
+        <v>173.1000061035156</v>
+      </c>
+      <c r="J172" t="n">
+        <v>174.8600006103516</v>
+      </c>
+      <c r="K172" t="n">
+        <v>2959231</v>
+      </c>
+      <c r="L172" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>ASHOKLEY Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>ASHOKLEY Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>12</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>INFY.NS</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>1143</v>
+      </c>
+      <c r="F173" t="n">
+        <v>1144.699951171875</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1125.699951171875</v>
+      </c>
+      <c r="H173" t="n">
+        <v>1129.800048828125</v>
+      </c>
+      <c r="I173" t="n">
+        <v>1119.800048828125</v>
+      </c>
+      <c r="J173" t="n">
+        <v>1129.800048828125</v>
+      </c>
+      <c r="K173" t="n">
+        <v>4109171</v>
+      </c>
+      <c r="L173" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>IT crash ahead? CLSA downgrades TCS, Infosys, Wipro, other stocks; revises target prices. Here's why - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Infosys: Discipline Priced As Decline (NYSE:INFY) - Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>CLSA turns cautious on Indian IT, downgrades TCS, Infosys, Tech Mahindra; prefers mid-tier stocks amid AI... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>CLSA downgrades five largecap IT stocks including Infosys, TCS; Find out why and what is it betting on - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>TCS, Infosys, Wipro Face CLSA Downgrade; These Midcap IT Stocks Stay Top Picks — Check Target Price - NDTV Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>13</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>FEDERALBNK.NS</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>361.8999938964844</v>
+      </c>
+      <c r="F174" t="n">
+        <v>364.2000122070312</v>
+      </c>
+      <c r="G174" t="n">
+        <v>360.25</v>
+      </c>
+      <c r="H174" t="n">
+        <v>361.2999877929688</v>
+      </c>
+      <c r="I174" t="n">
+        <v>358.7999877929688</v>
+      </c>
+      <c r="J174" t="n">
+        <v>361.2999877929688</v>
+      </c>
+      <c r="K174" t="n">
+        <v>2083165</v>
+      </c>
+      <c r="L174" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Federal Bank (NSEI:FEDERALBNK) Stock Gets Fair Value Boost Before Board Results Review - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>FEDERALBNK Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>FEDERALBNK Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>The Federal Bank Ltd. (FEDERALBNK) Share Price Hits 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>14</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SURYAROSNI.NS</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>SURYAROSNI</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>219.8999938964844</v>
+      </c>
+      <c r="F175" t="n">
+        <v>222.0899963378906</v>
+      </c>
+      <c r="G175" t="n">
+        <v>216.8000030517578</v>
+      </c>
+      <c r="H175" t="n">
+        <v>220.0800018310547</v>
+      </c>
+      <c r="I175" t="n">
+        <v>218.7100067138672</v>
+      </c>
+      <c r="J175" t="n">
+        <v>220.0800018310547</v>
+      </c>
+      <c r="K175" t="n">
+        <v>638460</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Surya Roshni Sets September AGM to Approve Dividend and ₹1,000 Crore Working Capital Security - TipRanks</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Surya Roshni Sets September AGM to Approve Dividend and ₹1,000 Crore Working Capital Security - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>15</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>CGPOWER.NS</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>868.5499877929688</v>
+      </c>
+      <c r="F176" t="n">
+        <v>874</v>
+      </c>
+      <c r="G176" t="n">
+        <v>862.6500244140625</v>
+      </c>
+      <c r="H176" t="n">
+        <v>867.8499755859375</v>
+      </c>
+      <c r="I176" t="n">
+        <v>863.0499877929688</v>
+      </c>
+      <c r="J176" t="n">
+        <v>867.8499755859375</v>
+      </c>
+      <c r="K176" t="n">
+        <v>987064</v>
+      </c>
+      <c r="L176" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>CG Power and Industrial Solutions Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>CG Power and Industrial Solutions Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>16</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>BIRLACORPN.NS</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>BIRLACORPN</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>885</v>
+      </c>
+      <c r="F177" t="n">
+        <v>892</v>
+      </c>
+      <c r="G177" t="n">
+        <v>884.7999877929688</v>
+      </c>
+      <c r="H177" t="n">
+        <v>888.9500122070312</v>
+      </c>
+      <c r="I177" t="n">
+        <v>884.9000244140625</v>
+      </c>
+      <c r="J177" t="n">
+        <v>888.9500122070312</v>
+      </c>
+      <c r="K177" t="n">
+        <v>9756</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Birla Corporation Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Birla Corporation Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>17</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>HINDUNILVR.NS</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>2022.900024414062</v>
+      </c>
+      <c r="F178" t="n">
+        <v>2041.699951171875</v>
+      </c>
+      <c r="G178" t="n">
+        <v>2018.199951171875</v>
+      </c>
+      <c r="H178" t="n">
+        <v>2029.5</v>
+      </c>
+      <c r="I178" t="n">
+        <v>2020.699951171875</v>
+      </c>
+      <c r="J178" t="n">
+        <v>2029.5</v>
+      </c>
+      <c r="K178" t="n">
+        <v>656518</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>HINDUNILVR Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>HINDUNILVR Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>18</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>ABB.NS</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>7450.5</v>
+      </c>
+      <c r="F179" t="n">
+        <v>7481.5</v>
+      </c>
+      <c r="G179" t="n">
+        <v>7393</v>
+      </c>
+      <c r="H179" t="n">
+        <v>7458</v>
+      </c>
+      <c r="I179" t="n">
+        <v>7430</v>
+      </c>
+      <c r="J179" t="n">
+        <v>7458</v>
+      </c>
+      <c r="K179" t="n">
+        <v>109465</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>ABB stock benefits from strong Q2 orders as valuation debate grows - Ad-hoc-news.de</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>ABB (OTCMKTS:ABBNY) Shares Pass Above 200 Day Moving Average - Here's What Happened - MarketBeat</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>ABB (OTCMKTS:ABBNY) Shares Pass Above 200 Day Moving Average - Here's What Happened - MarketBeat</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>ABB Ltd: ABB share buybacks - August 6, 2026 - August 12, 2026 - TradingView</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Is ABB (SWX:ABBN) Fully Priced Following Its LevelTen Energy Deal? - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>19</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>CANFINHOME.NS</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>CANFINHOME</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>821.4000244140625</v>
+      </c>
+      <c r="F180" t="n">
+        <v>829.7999877929688</v>
+      </c>
+      <c r="G180" t="n">
+        <v>817.9000244140625</v>
+      </c>
+      <c r="H180" t="n">
+        <v>820.6500244140625</v>
+      </c>
+      <c r="I180" t="n">
+        <v>817.6500244140625</v>
+      </c>
+      <c r="J180" t="n">
+        <v>820.6500244140625</v>
+      </c>
+      <c r="K180" t="n">
+        <v>114300</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>20</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>UNIVCABLES.NS</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>UNIVCABLES</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>1662</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1687</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1650</v>
+      </c>
+      <c r="H181" t="n">
+        <v>1664.800048828125</v>
+      </c>
+      <c r="I181" t="n">
+        <v>1662</v>
+      </c>
+      <c r="J181" t="n">
+        <v>1664.800048828125</v>
+      </c>
+      <c r="K181" t="n">
+        <v>36023</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN.NS</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>658.25</v>
+      </c>
+      <c r="F182" t="n">
+        <v>738</v>
+      </c>
+      <c r="G182" t="n">
+        <v>655.0499877929688</v>
+      </c>
+      <c r="H182" t="n">
+        <v>730</v>
+      </c>
+      <c r="I182" t="n">
+        <v>650.7999877929688</v>
+      </c>
+      <c r="J182" t="n">
+        <v>730</v>
+      </c>
+      <c r="K182" t="n">
+        <v>11532723</v>
+      </c>
+      <c r="L182" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd Share Price Target, Forecast for Long Term Equity. - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price Hits One-Year High - Univest</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>2</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>BAJAJHIND.NS</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>BAJAJHIND</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>20.73999977111816</v>
+      </c>
+      <c r="F183" t="n">
+        <v>22.6200008392334</v>
+      </c>
+      <c r="G183" t="n">
+        <v>20.59000015258789</v>
+      </c>
+      <c r="H183" t="n">
+        <v>22.20000076293945</v>
+      </c>
+      <c r="I183" t="n">
+        <v>20.3799991607666</v>
+      </c>
+      <c r="J183" t="n">
+        <v>22.20000076293945</v>
+      </c>
+      <c r="K183" t="n">
+        <v>130370012</v>
+      </c>
+      <c r="L183" t="n">
+        <v>8.93</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>3</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>RAJSREESUG.NS</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>RAJSREESUG</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>37.0099983215332</v>
+      </c>
+      <c r="F184" t="n">
+        <v>40.79000091552734</v>
+      </c>
+      <c r="G184" t="n">
+        <v>37</v>
+      </c>
+      <c r="H184" t="n">
+        <v>39.81000137329102</v>
+      </c>
+      <c r="I184" t="n">
+        <v>36.90000152587891</v>
+      </c>
+      <c r="J184" t="n">
+        <v>39.81000137329102</v>
+      </c>
+      <c r="K184" t="n">
+        <v>487113</v>
+      </c>
+      <c r="L184" t="n">
+        <v>7.89</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>4</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>DHAMPURSUG.NS</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>DHAMPURSUG</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>179.6999969482422</v>
+      </c>
+      <c r="F185" t="n">
+        <v>190.75</v>
+      </c>
+      <c r="G185" t="n">
+        <v>178.9700012207031</v>
+      </c>
+      <c r="H185" t="n">
+        <v>187.5899963378906</v>
+      </c>
+      <c r="I185" t="n">
+        <v>176.1799926757812</v>
+      </c>
+      <c r="J185" t="n">
+        <v>187.5899963378906</v>
+      </c>
+      <c r="K185" t="n">
+        <v>3503742</v>
+      </c>
+      <c r="L185" t="n">
+        <v>6.48</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>5</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>ZUARIIND.NS</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>ZUARIIND</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>268.8999938964844</v>
+      </c>
+      <c r="F186" t="n">
+        <v>284.8999938964844</v>
+      </c>
+      <c r="G186" t="n">
+        <v>261.8500061035156</v>
+      </c>
+      <c r="H186" t="n">
+        <v>278.6499938964844</v>
+      </c>
+      <c r="I186" t="n">
+        <v>262.1000061035156</v>
+      </c>
+      <c r="J186" t="n">
+        <v>278.6499938964844</v>
+      </c>
+      <c r="K186" t="n">
+        <v>281085</v>
+      </c>
+      <c r="L186" t="n">
+        <v>6.31</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>6</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ARVIND.NS</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ARVIND</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>519.9000244140625</v>
+      </c>
+      <c r="F187" t="n">
+        <v>541</v>
+      </c>
+      <c r="G187" t="n">
+        <v>519.5499877929688</v>
+      </c>
+      <c r="H187" t="n">
+        <v>534.7999877929688</v>
+      </c>
+      <c r="I187" t="n">
+        <v>516.5</v>
+      </c>
+      <c r="J187" t="n">
+        <v>534.7999877929688</v>
+      </c>
+      <c r="K187" t="n">
+        <v>535172</v>
+      </c>
+      <c r="L187" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Arvind Ltd sets September 4 deadline for dividend tax docs - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Arvind Ltd sets September 4 deadline for dividend tax docs - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: Arvind posts strong Q1 2026 growth, shares slip - Investing.com</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Arvind sees no immediate acquisitions, focuses on Dalco GFT integration - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>Rubrik CTO Arvind Nithrakashyap Sells $3.0 Million Stock - The Motley Fool</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>7</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>EIDPARRY.NS</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>EIDPARRY</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>793.7999877929688</v>
+      </c>
+      <c r="F188" t="n">
+        <v>814.8499755859375</v>
+      </c>
+      <c r="G188" t="n">
+        <v>787.5499877929688</v>
+      </c>
+      <c r="H188" t="n">
+        <v>811.25</v>
+      </c>
+      <c r="I188" t="n">
+        <v>787.0499877929688</v>
+      </c>
+      <c r="J188" t="n">
+        <v>811.25</v>
+      </c>
+      <c r="K188" t="n">
+        <v>1089120</v>
+      </c>
+      <c r="L188" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Raja Venkatraman recommends three stocks for 5 August - livemint.com</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>Abakkus, Carnelian, Motilal Oswal acquire additional 2.9% Anawil Wire shares; promoter offloads Rs 171 crore worth Capillary Tech shares - TradingView</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Abakkus, Carnelian, Motilal Oswal acquire additional 2.9% Anawil Wire shares; promoter offloads Rs 171 crore worth Capillary Tech shares - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>8</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>DCW.NS</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>DCW</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>43.47000122070312</v>
+      </c>
+      <c r="F189" t="n">
+        <v>44.38000106811523</v>
+      </c>
+      <c r="G189" t="n">
+        <v>43.33000183105469</v>
+      </c>
+      <c r="H189" t="n">
+        <v>44.09999847412109</v>
+      </c>
+      <c r="I189" t="n">
+        <v>43.2599983215332</v>
+      </c>
+      <c r="J189" t="n">
+        <v>44.09999847412109</v>
+      </c>
+      <c r="K189" t="n">
+        <v>383059</v>
+      </c>
+      <c r="L189" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>DCW Share Price Target 2027 to 2030: Analyst Outlook - Univest</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>DCW Limited recognized as Three Star Export House till 2031 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>DCW Limited recognized as Three Star Export House till 2031 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>‘Call 181, receive justice quickly’: Delhi DCW Chair Lata Gupta's first message after appointment - The Economic Times</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>DCW Limited to host Q1FY27 earnings call on August 14 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>9</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>BOMDYEING.NS</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>BOMDYEING</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>113.2399978637695</v>
+      </c>
+      <c r="F190" t="n">
+        <v>113.4300003051758</v>
+      </c>
+      <c r="G190" t="n">
+        <v>112.6600036621094</v>
+      </c>
+      <c r="H190" t="n">
+        <v>112.9700012207031</v>
+      </c>
+      <c r="I190" t="n">
+        <v>111.5699996948242</v>
+      </c>
+      <c r="J190" t="n">
+        <v>112.9700012207031</v>
+      </c>
+      <c r="K190" t="n">
+        <v>144210</v>
+      </c>
+      <c r="L190" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>BOMDYEING Standalone June 2026 Net Sales at Rs 410.80 crore, up 8.72% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>BOMDYEING Standalone June 2026 Net Sales at Rs 410.80 crore, up 8.72% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>10</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>SAIL.NS</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>174.1000061035156</v>
+      </c>
+      <c r="F191" t="n">
+        <v>176.4299926757812</v>
+      </c>
+      <c r="G191" t="n">
+        <v>173.4100036621094</v>
+      </c>
+      <c r="H191" t="n">
+        <v>174.8999938964844</v>
+      </c>
+      <c r="I191" t="n">
+        <v>172.75</v>
+      </c>
+      <c r="J191" t="n">
+        <v>174.8999938964844</v>
+      </c>
+      <c r="K191" t="n">
+        <v>7806042</v>
+      </c>
+      <c r="L191" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>SailPoint (SAIL) Holds A Special Call, Is The Stock Already Overvalued? - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>SailPoint (SAIL) Holds A Special Call, Is The Stock Already Overvalued? - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>CrowdStrike Setup 'Constructive,' But Truist Favors Rubrik, SailPoint Ahead Of Q2 Earnings - TradingView</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Nifty Metal tanks 3% in two days on profit-taking; NALCO, SAIL top losers - business-standard.com</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>SailPoint (SAIL) Outlook: Records a Muted Move to $19.19 on the Day; Chart View: Price Remains Between $18.23 Support and $20.15 Resistance in the Latest Session - Daily Profile - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>11</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>INFY.NS</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>1143</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1144.699951171875</v>
+      </c>
+      <c r="G192" t="n">
+        <v>1125.699951171875</v>
+      </c>
+      <c r="H192" t="n">
+        <v>1130.900024414062</v>
+      </c>
+      <c r="I192" t="n">
+        <v>1119.800048828125</v>
+      </c>
+      <c r="J192" t="n">
+        <v>1130.900024414062</v>
+      </c>
+      <c r="K192" t="n">
+        <v>4305781</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Infosys: Discipline Priced As Decline (NYSE:INFY) - Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Infosys: Discipline Priced As Decline (NYSE:INFY) - Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Infosys Ltd (INFY) Stock Down 3.9% -- Now Undervalued? GF Score: 86/100 - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Infosys (NSEI:INFY) Stock Fair Value Falls After Analysts Cut Targets On Weaker Outlook - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>INFY Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>12</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ASHOKLEY.NS</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>174.6999969482422</v>
+      </c>
+      <c r="F193" t="n">
+        <v>175.5700073242188</v>
+      </c>
+      <c r="G193" t="n">
+        <v>173.7400054931641</v>
+      </c>
+      <c r="H193" t="n">
+        <v>174.6999969482422</v>
+      </c>
+      <c r="I193" t="n">
+        <v>173.1000061035156</v>
+      </c>
+      <c r="J193" t="n">
+        <v>174.6999969482422</v>
+      </c>
+      <c r="K193" t="n">
+        <v>3020079</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>13</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>SURYAROSNI.NS</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>SURYAROSNI</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>219.8999938964844</v>
+      </c>
+      <c r="F194" t="n">
+        <v>222.0899963378906</v>
+      </c>
+      <c r="G194" t="n">
+        <v>216.8000030517578</v>
+      </c>
+      <c r="H194" t="n">
+        <v>220.2299957275391</v>
+      </c>
+      <c r="I194" t="n">
+        <v>218.7100067138672</v>
+      </c>
+      <c r="J194" t="n">
+        <v>220.2299957275391</v>
+      </c>
+      <c r="K194" t="n">
+        <v>644456</v>
+      </c>
+      <c r="L194" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Surya Roshni Sets September AGM to Approve Dividend and ₹1,000 Crore Working Capital Security - TipRanks</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>Surya Roshni Sets September AGM to Approve Dividend and ₹1,000 Crore Working Capital Security - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>14</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>CGPOWER.NS</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>868.5499877929688</v>
+      </c>
+      <c r="F195" t="n">
+        <v>874</v>
+      </c>
+      <c r="G195" t="n">
+        <v>862.6500244140625</v>
+      </c>
+      <c r="H195" t="n">
+        <v>868.7999877929688</v>
+      </c>
+      <c r="I195" t="n">
+        <v>863.0499877929688</v>
+      </c>
+      <c r="J195" t="n">
+        <v>868.7999877929688</v>
+      </c>
+      <c r="K195" t="n">
+        <v>1003617</v>
+      </c>
+      <c r="L195" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>CG Power and Industrial Solutions Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>CG Power and Industrial Solutions Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>15</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>FEDERALBNK.NS</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>361.8999938964844</v>
+      </c>
+      <c r="F196" t="n">
+        <v>364.2000122070312</v>
+      </c>
+      <c r="G196" t="n">
+        <v>360.25</v>
+      </c>
+      <c r="H196" t="n">
+        <v>361</v>
+      </c>
+      <c r="I196" t="n">
+        <v>358.7999877929688</v>
+      </c>
+      <c r="J196" t="n">
+        <v>361</v>
+      </c>
+      <c r="K196" t="n">
+        <v>2160378</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Federal Bank (NSEI:FEDERALBNK) Stock Gets Fair Value Boost Before Board Results Review - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>FEDERALBNK Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>FEDERALBNK Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>The Federal Bank Ltd. (FEDERALBNK) Share Price Hits 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>16</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>BIRLACORPN.NS</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>BIRLACORPN</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>885</v>
+      </c>
+      <c r="F197" t="n">
+        <v>892</v>
+      </c>
+      <c r="G197" t="n">
+        <v>884.7999877929688</v>
+      </c>
+      <c r="H197" t="n">
+        <v>889</v>
+      </c>
+      <c r="I197" t="n">
+        <v>884.9000244140625</v>
+      </c>
+      <c r="J197" t="n">
+        <v>889</v>
+      </c>
+      <c r="K197" t="n">
+        <v>9789</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>Birla Corporation Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>Birla Corporation Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>17</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>HINDUNILVR.NS</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>2022.900024414062</v>
+      </c>
+      <c r="F198" t="n">
+        <v>2041.699951171875</v>
+      </c>
+      <c r="G198" t="n">
+        <v>2018.199951171875</v>
+      </c>
+      <c r="H198" t="n">
+        <v>2029</v>
+      </c>
+      <c r="I198" t="n">
+        <v>2020.699951171875</v>
+      </c>
+      <c r="J198" t="n">
+        <v>2029</v>
+      </c>
+      <c r="K198" t="n">
+        <v>677072</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>HINDUNILVR Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>HINDUNILVR Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>18</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>ABB.NS</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>7450.5</v>
+      </c>
+      <c r="F199" t="n">
+        <v>7481.5</v>
+      </c>
+      <c r="G199" t="n">
+        <v>7393</v>
+      </c>
+      <c r="H199" t="n">
+        <v>7460</v>
+      </c>
+      <c r="I199" t="n">
+        <v>7430</v>
+      </c>
+      <c r="J199" t="n">
+        <v>7460</v>
+      </c>
+      <c r="K199" t="n">
+        <v>113778</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>ABB stock benefits from strong Q2 orders as valuation debate grows - Ad-hoc-news.de</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>ABB (OTCMKTS:ABBNY) Shares Pass Above 200 Day Moving Average - Here's What Happened - MarketBeat</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>ABB (OTCMKTS:ABBNY) Shares Pass Above 200 Day Moving Average - Here's What Happened - MarketBeat</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>ABB Ltd: ABB share buybacks - August 6, 2026 - August 12, 2026 - TradingView</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>Is ABB (SWX:ABBN) Fully Priced Following Its LevelTen Energy Deal? - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>19</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>CANFINHOME.NS</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CANFINHOME</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>821.4000244140625</v>
+      </c>
+      <c r="F200" t="n">
+        <v>829.7999877929688</v>
+      </c>
+      <c r="G200" t="n">
+        <v>817.9000244140625</v>
+      </c>
+      <c r="H200" t="n">
+        <v>820.3499755859375</v>
+      </c>
+      <c r="I200" t="n">
+        <v>817.6500244140625</v>
+      </c>
+      <c r="J200" t="n">
+        <v>820.3499755859375</v>
+      </c>
+      <c r="K200" t="n">
+        <v>116573</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>20</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>UNIVCABLES.NS</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>UNIVCABLES</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>1662</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1687</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1650</v>
+      </c>
+      <c r="H201" t="n">
+        <v>1666.699951171875</v>
+      </c>
+      <c r="I201" t="n">
+        <v>1662</v>
+      </c>
+      <c r="J201" t="n">
+        <v>1666.699951171875</v>
+      </c>
+      <c r="K201" t="n">
+        <v>36126</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN.NS</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>658.25</v>
+      </c>
+      <c r="F202" t="n">
+        <v>738.9500122070312</v>
+      </c>
+      <c r="G202" t="n">
+        <v>655.0499877929688</v>
+      </c>
+      <c r="H202" t="n">
+        <v>736.7999877929688</v>
+      </c>
+      <c r="I202" t="n">
+        <v>650.7999877929688</v>
+      </c>
+      <c r="J202" t="n">
+        <v>736.7999877929688</v>
+      </c>
+      <c r="K202" t="n">
+        <v>12573227</v>
+      </c>
+      <c r="L202" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd Share Price Target, Forecast for Long Term Equity. - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price Hits One-Year High - Univest</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>2</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>BAJAJHIND.NS</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>BAJAJHIND</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>20.73999977111816</v>
+      </c>
+      <c r="F203" t="n">
+        <v>22.6200008392334</v>
+      </c>
+      <c r="G203" t="n">
+        <v>20.59000015258789</v>
+      </c>
+      <c r="H203" t="n">
+        <v>22.17000007629395</v>
+      </c>
+      <c r="I203" t="n">
+        <v>20.3799991607666</v>
+      </c>
+      <c r="J203" t="n">
+        <v>22.17000007629395</v>
+      </c>
+      <c r="K203" t="n">
+        <v>131939293</v>
+      </c>
+      <c r="L203" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>We Think That There Are Some Issues For Bajaj Hindusthan Sugar (NSE:BAJAJHIND) Beyond Its Promising Earnings - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>BAJAJHIND Mar 2026 Earnings: Solid EPS of ₹1.65 on Revenue of ₹1,657 Crore - Downward Estimate Revision - Vinanet</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>BAJAJHIND Mar 2026 Earnings: Solid EPS of ₹1.65 on Revenue of ₹1,657 Crore - Downward Estimate Revision - Vinanet</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>There's No Escaping Bajaj Hindusthan Sugar Limited's (NSE:BAJAJHIND) Muted Revenues - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>BAJAJHIND Mar 2026 Earnings: EPS of ₹1.65 on Revenue of ₹1,657 Crore as Sugar &amp; Ethanol Operations Hold Steady - Long-Term Guidance - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>3</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>RAJSREESUG.NS</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>RAJSREESUG</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>37.0099983215332</v>
+      </c>
+      <c r="F204" t="n">
+        <v>40.79000091552734</v>
+      </c>
+      <c r="G204" t="n">
+        <v>37</v>
+      </c>
+      <c r="H204" t="n">
+        <v>39.65000152587891</v>
+      </c>
+      <c r="I204" t="n">
+        <v>36.90000152587891</v>
+      </c>
+      <c r="J204" t="n">
+        <v>39.65000152587891</v>
+      </c>
+      <c r="K204" t="n">
+        <v>487665</v>
+      </c>
+      <c r="L204" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Rajshree Sugars Gains 3%: Sugar Sector Momentum and Key Levels for RAJSREESUG.NS - Stock Analysis - Vinanet</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Rajshree Sugars (RAJSREESUG.NS) Holds Near Support as Sugar Sector Awaits Policy Clarity - Fund Manager Survey - Vinanet</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>RAJSREESUG Share Price Today - Rajshree Sugars &amp; Chemicals Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Rajshree Sugars (RAJSREESUG.NS) Holds Near Support as Sugar Sector Awaits Policy Clarity - Fund Manager Survey - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>Rajshree Sugar &amp; Chem Share Price - Upstox</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>4</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>DHAMPURSUG.NS</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>DHAMPURSUG</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>179.6999969482422</v>
+      </c>
+      <c r="F205" t="n">
+        <v>190.75</v>
+      </c>
+      <c r="G205" t="n">
+        <v>178.9700012207031</v>
+      </c>
+      <c r="H205" t="n">
+        <v>188</v>
+      </c>
+      <c r="I205" t="n">
+        <v>176.1799926757812</v>
+      </c>
+      <c r="J205" t="n">
+        <v>188</v>
+      </c>
+      <c r="K205" t="n">
+        <v>3569317</v>
+      </c>
+      <c r="L205" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills (DHAMPURSUG) Gains 2.33%: Support Holds amid Sugar Sector Activity - Bearish Pattern Stocks - Vinanet</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Q2 2026 Earnings: EPS of ₹10.09 on Steady Revenue of ₹19,674.4 Million - Basic EPS Analysis - Vinanet</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills (DHAMPURSUG.NS): Mild Decline as Price Hovers Near Support Zone - Fibonacci Fan - Vinanet</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Share Price - Live NSE: DHAMPURSUG Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Fined by Uttar Pradesh Excise Authority for Storage Lapses - The Globe and Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>5</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ZUARIIND.NS</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>ZUARIIND</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>268.8999938964844</v>
+      </c>
+      <c r="F206" t="n">
+        <v>284.8999938964844</v>
+      </c>
+      <c r="G206" t="n">
+        <v>261.8500061035156</v>
+      </c>
+      <c r="H206" t="n">
+        <v>278.7999877929688</v>
+      </c>
+      <c r="I206" t="n">
+        <v>262.1000061035156</v>
+      </c>
+      <c r="J206" t="n">
+        <v>278.7999877929688</v>
+      </c>
+      <c r="K206" t="n">
+        <v>283179</v>
+      </c>
+      <c r="L206" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>Zuari Industries Limited's (NSE:ZUARIIND) 25% Price Boost Is Out Of Tune With Revenues - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>ZUARIIND Q2 FY26 Earnings: Revenue Grows 7.68% YoY to ₹1,044.82 Crore, EPS at ₹36.25 - Next Quarter Guidance - Vinanet</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>ZUARI Industries (ZUARIIND.NS) Slips Over 3% as Selling Pressure Intensifies - Narrow Range Breakout - Vinanet</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>ZUARIIND Stock Price and Chart — NSE:ZUARIIND - TradingView</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>ZUARIIND Q2 FY26 Earnings: Revenue Grows 7.68% YoY to ₹1,044.82 Crore, EPS at ₹36.25 - Next Quarter Guidance - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>6</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>ARVIND.NS</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>ARVIND</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>519.9000244140625</v>
+      </c>
+      <c r="F207" t="n">
+        <v>541</v>
+      </c>
+      <c r="G207" t="n">
+        <v>519.5499877929688</v>
+      </c>
+      <c r="H207" t="n">
+        <v>534.75</v>
+      </c>
+      <c r="I207" t="n">
+        <v>516.5</v>
+      </c>
+      <c r="J207" t="n">
+        <v>534.75</v>
+      </c>
+      <c r="K207" t="n">
+        <v>541059</v>
+      </c>
+      <c r="L207" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Arvind Ltd sets September 4 deadline for dividend tax docs - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Arvind Ltd sets September 4 deadline for dividend tax docs - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: Arvind posts strong Q1 2026 growth, shares slip - Investing.com</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Arvind sees no immediate acquisitions, focuses on Dalco GFT integration - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>Rubrik CTO Arvind Nithrakashyap Sells $3.0 Million Stock - The Motley Fool</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>7</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>EIDPARRY.NS</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>EIDPARRY</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>793.7999877929688</v>
+      </c>
+      <c r="F208" t="n">
+        <v>814.8499755859375</v>
+      </c>
+      <c r="G208" t="n">
+        <v>787.5499877929688</v>
+      </c>
+      <c r="H208" t="n">
+        <v>803.4500122070312</v>
+      </c>
+      <c r="I208" t="n">
+        <v>787.0499877929688</v>
+      </c>
+      <c r="J208" t="n">
+        <v>803.4500122070312</v>
+      </c>
+      <c r="K208" t="n">
+        <v>1151102</v>
+      </c>
+      <c r="L208" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>Raja Venkatraman recommends three stocks for 5 August - livemint.com</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>Abakkus, Carnelian, Motilal Oswal acquire additional 2.9% Anawil Wire shares; promoter offloads Rs 171 crore worth Capillary Tech shares - TradingView</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Abakkus, Carnelian, Motilal Oswal acquire additional 2.9% Anawil Wire shares; promoter offloads Rs 171 crore worth Capillary Tech shares - TradingView</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>8</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>DCW.NS</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>DCW</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>43.47000122070312</v>
+      </c>
+      <c r="F209" t="n">
+        <v>44.38000106811523</v>
+      </c>
+      <c r="G209" t="n">
+        <v>43.33000183105469</v>
+      </c>
+      <c r="H209" t="n">
+        <v>44.13000106811523</v>
+      </c>
+      <c r="I209" t="n">
+        <v>43.2599983215332</v>
+      </c>
+      <c r="J209" t="n">
+        <v>44.13000106811523</v>
+      </c>
+      <c r="K209" t="n">
+        <v>383685</v>
+      </c>
+      <c r="L209" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>DCW Share Price Target 2027 to 2030: Analyst Outlook - Univest</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>DCW Limited recognized as Three Star Export House till 2031 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>DCW Limited recognized as Three Star Export House till 2031 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>‘Call 181, receive justice quickly’: Delhi DCW Chair Lata Gupta's first message after appointment - The Economic Times</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>DCW Limited to host Q1FY27 earnings call on August 14 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>9</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>BOMDYEING.NS</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>BOMDYEING</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>113.2399978637695</v>
+      </c>
+      <c r="F210" t="n">
+        <v>113.4300003051758</v>
+      </c>
+      <c r="G210" t="n">
+        <v>112.6600036621094</v>
+      </c>
+      <c r="H210" t="n">
+        <v>113</v>
+      </c>
+      <c r="I210" t="n">
+        <v>111.5699996948242</v>
+      </c>
+      <c r="J210" t="n">
+        <v>113</v>
+      </c>
+      <c r="K210" t="n">
+        <v>144788</v>
+      </c>
+      <c r="L210" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>BOMDYEING Standalone June 2026 Net Sales at Rs 410.80 crore, up 8.72% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>BOMDYEING Standalone June 2026 Net Sales at Rs 410.80 crore, up 8.72% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>10</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>SAIL.NS</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>174.1000061035156</v>
+      </c>
+      <c r="F211" t="n">
+        <v>176.4299926757812</v>
+      </c>
+      <c r="G211" t="n">
+        <v>173.4100036621094</v>
+      </c>
+      <c r="H211" t="n">
+        <v>174.8999938964844</v>
+      </c>
+      <c r="I211" t="n">
+        <v>172.75</v>
+      </c>
+      <c r="J211" t="n">
+        <v>174.8999938964844</v>
+      </c>
+      <c r="K211" t="n">
+        <v>7842795</v>
+      </c>
+      <c r="L211" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>SailPoint (SAIL) Holds A Special Call, Is The Stock Already Overvalued? - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>SailPoint (SAIL) Holds A Special Call, Is The Stock Already Overvalued? - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>CrowdStrike Setup 'Constructive,' But Truist Favors Rubrik, SailPoint Ahead Of Q2 Earnings - TradingView</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Nifty Metal tanks 3% in two days on profit-taking; NALCO, SAIL top losers - business-standard.com</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>SailPoint (SAIL) Outlook: Records a Muted Move to $19.19 on the Day; Chart View: Price Remains Between $18.23 Support and $20.15 Resistance in the Latest Session - Daily Profile - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>11</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>INFY.NS</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>1143</v>
+      </c>
+      <c r="F212" t="n">
+        <v>1144.699951171875</v>
+      </c>
+      <c r="G212" t="n">
+        <v>1125.699951171875</v>
+      </c>
+      <c r="H212" t="n">
+        <v>1130.300048828125</v>
+      </c>
+      <c r="I212" t="n">
+        <v>1119.800048828125</v>
+      </c>
+      <c r="J212" t="n">
+        <v>1130.300048828125</v>
+      </c>
+      <c r="K212" t="n">
+        <v>4384372</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>Infosys: Discipline Priced As Decline (NYSE:INFY) - Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Infosys: Discipline Priced As Decline (NYSE:INFY) - Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Infosys Ltd (INFY) Stock Down 3.9% -- Now Undervalued? GF Score: 86/100 - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Infosys (NSEI:INFY) Stock Fair Value Falls After Analysts Cut Targets On Weaker Outlook - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>INFY Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>12</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>ASHOKLEY.NS</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>174.6999969482422</v>
+      </c>
+      <c r="F213" t="n">
+        <v>175.5700073242188</v>
+      </c>
+      <c r="G213" t="n">
+        <v>173.7400054931641</v>
+      </c>
+      <c r="H213" t="n">
+        <v>174.6000061035156</v>
+      </c>
+      <c r="I213" t="n">
+        <v>173.1000061035156</v>
+      </c>
+      <c r="J213" t="n">
+        <v>174.6000061035156</v>
+      </c>
+      <c r="K213" t="n">
+        <v>3036626</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>ASHOKLEY Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>ASHOKLEY Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>13</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>SURYAROSNI.NS</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>SURYAROSNI</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>219.8999938964844</v>
+      </c>
+      <c r="F214" t="n">
+        <v>222.0899963378906</v>
+      </c>
+      <c r="G214" t="n">
+        <v>216.8000030517578</v>
+      </c>
+      <c r="H214" t="n">
+        <v>220.3300018310547</v>
+      </c>
+      <c r="I214" t="n">
+        <v>218.7100067138672</v>
+      </c>
+      <c r="J214" t="n">
+        <v>220.3300018310547</v>
+      </c>
+      <c r="K214" t="n">
+        <v>645331</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>Surya Roshni Sets September AGM to Approve Dividend and ₹1,000 Crore Working Capital Security - TipRanks</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>Surya Roshni Sets September AGM to Approve Dividend and ₹1,000 Crore Working Capital Security - TipRanks</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>14</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>CGPOWER.NS</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>868.5499877929688</v>
+      </c>
+      <c r="F215" t="n">
+        <v>874</v>
+      </c>
+      <c r="G215" t="n">
+        <v>862.6500244140625</v>
+      </c>
+      <c r="H215" t="n">
+        <v>868.6500244140625</v>
+      </c>
+      <c r="I215" t="n">
+        <v>863.0499877929688</v>
+      </c>
+      <c r="J215" t="n">
+        <v>868.6500244140625</v>
+      </c>
+      <c r="K215" t="n">
+        <v>1012503</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>CG Power and Industrial Solutions Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>CG Power and Industrial Solutions Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>15</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>FEDERALBNK.NS</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>361.8999938964844</v>
+      </c>
+      <c r="F216" t="n">
+        <v>364.2000122070312</v>
+      </c>
+      <c r="G216" t="n">
+        <v>360.25</v>
+      </c>
+      <c r="H216" t="n">
+        <v>361</v>
+      </c>
+      <c r="I216" t="n">
+        <v>358.7999877929688</v>
+      </c>
+      <c r="J216" t="n">
+        <v>361</v>
+      </c>
+      <c r="K216" t="n">
+        <v>2183173</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Federal Bank (NSEI:FEDERALBNK) Stock Gets Fair Value Boost Before Board Results Review - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>FEDERALBNK Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>FEDERALBNK Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>The Federal Bank Ltd. (FEDERALBNK) Share Price Hits 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>16</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>BIRLACORPN.NS</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>BIRLACORPN</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>885</v>
+      </c>
+      <c r="F217" t="n">
+        <v>892</v>
+      </c>
+      <c r="G217" t="n">
+        <v>884.7999877929688</v>
+      </c>
+      <c r="H217" t="n">
+        <v>889.7000122070312</v>
+      </c>
+      <c r="I217" t="n">
+        <v>884.9000244140625</v>
+      </c>
+      <c r="J217" t="n">
+        <v>889.7000122070312</v>
+      </c>
+      <c r="K217" t="n">
+        <v>9790</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Birla Corporation Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>Birla Corporation Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>17</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>ABB.NS</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>7450.5</v>
+      </c>
+      <c r="F218" t="n">
+        <v>7481.5</v>
+      </c>
+      <c r="G218" t="n">
+        <v>7393</v>
+      </c>
+      <c r="H218" t="n">
+        <v>7461.5</v>
+      </c>
+      <c r="I218" t="n">
+        <v>7430</v>
+      </c>
+      <c r="J218" t="n">
+        <v>7461.5</v>
+      </c>
+      <c r="K218" t="n">
+        <v>115415</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>ABB stock benefits from strong Q2 orders as valuation debate grows - Ad-hoc-news.de</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>ABB (OTCMKTS:ABBNY) Shares Pass Above 200 Day Moving Average - Here's What Happened - MarketBeat</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>ABB (OTCMKTS:ABBNY) Shares Pass Above 200 Day Moving Average - Here's What Happened - MarketBeat</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>ABB Ltd: ABB share buybacks - August 6, 2026 - August 12, 2026 - TradingView</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>Is ABB (SWX:ABBN) Fully Priced Following Its LevelTen Energy Deal? - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>18</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>HINDUNILVR.NS</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>2022.900024414062</v>
+      </c>
+      <c r="F219" t="n">
+        <v>2041.699951171875</v>
+      </c>
+      <c r="G219" t="n">
+        <v>2018.199951171875</v>
+      </c>
+      <c r="H219" t="n">
+        <v>2029</v>
+      </c>
+      <c r="I219" t="n">
+        <v>2020.699951171875</v>
+      </c>
+      <c r="J219" t="n">
+        <v>2029</v>
+      </c>
+      <c r="K219" t="n">
+        <v>684111</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>HINDUNILVR Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>HINDUNILVR Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>19</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>VOLTAS.NS</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>1234</v>
+      </c>
+      <c r="F220" t="n">
+        <v>1234</v>
+      </c>
+      <c r="G220" t="n">
+        <v>1215.599975585938</v>
+      </c>
+      <c r="H220" t="n">
+        <v>1227.699951171875</v>
+      </c>
+      <c r="I220" t="n">
+        <v>1223</v>
+      </c>
+      <c r="J220" t="n">
+        <v>1227.699951171875</v>
+      </c>
+      <c r="K220" t="n">
+        <v>710177</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>Voltas stock falls 4% after Q1, top midcap loser; brokerages split as margin concerns outweigh strong AC... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>Voltas Share Price Declines 2.05% in Mid-Morning Trade - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Voltas shares fall 6% from intraday high post Q1; brokerages split - BusinessLine</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Voltas shares slip 4% despite strong Q1 show; analysts flag margin risk - business-standard.com</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: Voltas posts strong Q1 2026 profit growth, shares rise 2.4% - Investing.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>20</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>CANFINHOME.NS</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>CANFINHOME</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>821.4000244140625</v>
+      </c>
+      <c r="F221" t="n">
+        <v>829.7999877929688</v>
+      </c>
+      <c r="G221" t="n">
+        <v>817.9000244140625</v>
+      </c>
+      <c r="H221" t="n">
+        <v>820.4500122070312</v>
+      </c>
+      <c r="I221" t="n">
+        <v>817.6500244140625</v>
+      </c>
+      <c r="J221" t="n">
+        <v>820.4500122070312</v>
+      </c>
+      <c r="K221" t="n">
+        <v>118262</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>CANFINHOME Forecast — Price Target — Prediction for 2027 - TradingView</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>CANFINHOME Mar 2026 Earnings: EPS of ₹25.96 Reflects Steady Performance Amidst Housing Finance Sector Tailwinds - Estimate Uncertainty - Vinanet</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Can Fin Homes (CANFINHOME) Holds Steady at ₹886 – Key Levels in Focus - Chandelier Stop - Vinanet</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Can Fin Homes Ltd (CANFINHOME.NS) Falls 5.5% – Testing Key Support Near ₹795 - Fear Greed Extreme - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>With EPS Growth And More, Can Fin Homes (NSE:CANFINHOME) Makes An Interesting Case - simplywall.st</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8610,7 +13166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q141"/>
+  <dimension ref="A1:Q221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15457,9 +20013,6 @@
           <t>There's A Lot To Like About Deep Industries' (NSE:DEEPINDS) Upcoming ₹2.50 Dividend - simplywall.st</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -15504,11 +20057,6 @@
       <c r="L124" t="n">
         <v>-5.7</v>
       </c>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -15563,9 +20111,6 @@
           <t>Hatsun Agro Product Ltd leads losers in 'A' group - Dailyhunt</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -15679,11 +20224,6 @@
       <c r="L127" t="n">
         <v>-4.84</v>
       </c>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -15738,9 +20278,6 @@
           <t>Kusumgar seeks shareholder approval to ratify ESOP scheme post-IPO - scanx.trade</t>
         </is>
       </c>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -15785,11 +20322,6 @@
       <c r="L129" t="n">
         <v>-4.79</v>
       </c>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -15849,8 +20381,6 @@
           <t>Mercantile Ventures Posts Consolidated Net Loss of Rs 0.65 Crore in June 2026 Quarter; Sales Climb 9.25% - Guidance Revision Trend - Vinanet</t>
         </is>
       </c>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -15895,11 +20425,6 @@
       <c r="L131" t="n">
         <v>-4.4</v>
       </c>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -15944,11 +20469,6 @@
       <c r="L132" t="n">
         <v>-4.4</v>
       </c>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -15993,11 +20513,6 @@
       <c r="L133" t="n">
         <v>-4.3</v>
       </c>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -16042,11 +20557,6 @@
       <c r="L134" t="n">
         <v>-4.25</v>
       </c>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -16170,9 +20680,6 @@
           <t>Here's What Analysts Are Forecasting For Bata India Limited (NSE:BATAINDIA) After Its First-Quarter Results - simplywall.st</t>
         </is>
       </c>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -16217,11 +20724,6 @@
       <c r="L137" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -16281,8 +20783,6 @@
           <t>POWERINDIA Share Price | Hitachi Energy India Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
         </is>
       </c>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -16347,7 +20847,6 @@
           <t>Filatex Fashions Share News Today,filatex Fashions Share Analysis,filatex Fashions Share Price/news Julio Rodríguez (hxc2EVlwyH) - Mshale</t>
         </is>
       </c>
-      <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -16392,11 +20891,6 @@
       <c r="L140" t="n">
         <v>-4.13</v>
       </c>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -16441,11 +20935,4687 @@
       <c r="L141" t="n">
         <v>-4.12</v>
       </c>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>SIEL.NS</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>SIEL</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>44.54000091552734</v>
+      </c>
+      <c r="F142" t="n">
+        <v>44.54000091552734</v>
+      </c>
+      <c r="G142" t="n">
+        <v>40.29999923706055</v>
+      </c>
+      <c r="H142" t="n">
+        <v>40.29999923706055</v>
+      </c>
+      <c r="I142" t="n">
+        <v>42.41999816894531</v>
+      </c>
+      <c r="J142" t="n">
+        <v>40.29999923706055</v>
+      </c>
+      <c r="K142" t="n">
+        <v>8873</v>
+      </c>
+      <c r="L142" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Diluted shares outstanding of Superior Industrial Enterprises Limited – NSE:SIEL - TradingView</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>2</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>INDOMIM.NS</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>INDOMIM</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>965</v>
+      </c>
+      <c r="F143" t="n">
+        <v>965</v>
+      </c>
+      <c r="G143" t="n">
+        <v>907.2999877929688</v>
+      </c>
+      <c r="H143" t="n">
+        <v>922.75</v>
+      </c>
+      <c r="I143" t="n">
+        <v>967.9500122070312</v>
+      </c>
+      <c r="J143" t="n">
+        <v>922.75</v>
+      </c>
+      <c r="K143" t="n">
+        <v>2285691</v>
+      </c>
+      <c r="L143" t="n">
+        <v>-4.67</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>INDOMIM Historical Data - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>INDO-MIM Board Clears Q1 FY27 Unaudited Results, Publishes in Newspapers - TipRanks</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Indo-MIM shares hit 10% upper circuit on strong Q1 growth as raw material costs decline 11% in June quarter - Upstox</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Indo-MIM Share News - Latest Updates, Live News &amp; More - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>INDO-MIM Board Clears Q1 FY27 Unaudited Results, Publishes in Newspapers - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>3</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>KUANTUM.NS</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>KUANTUM</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="F144" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G144" t="n">
+        <v>74.20999908447266</v>
+      </c>
+      <c r="H144" t="n">
+        <v>75.37999725341797</v>
+      </c>
+      <c r="I144" t="n">
+        <v>78.69999694824219</v>
+      </c>
+      <c r="J144" t="n">
+        <v>75.37999725341797</v>
+      </c>
+      <c r="K144" t="n">
+        <v>215320</v>
+      </c>
+      <c r="L144" t="n">
+        <v>-4.22</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Kuantum Papers Share Price Target 2027 to 2030: Analyst Outlook - Univest</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Mazagon Dock and 9 Other Stocks in Focus as They Turn Ex-Dividend Tomorrow - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Kuantum Papers standalone net profit declines 48.34% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Kuantum Papers Q1 net profit falls 48% to ₹6.23 crore; guidance revised lower - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Kuantum Papers Q1 Results: Earnings call scheduled for Aug 14 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>4</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>UCAL.NS</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>UCAL</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>147.8999938964844</v>
+      </c>
+      <c r="F145" t="n">
+        <v>147.8999938964844</v>
+      </c>
+      <c r="G145" t="n">
+        <v>138.8800048828125</v>
+      </c>
+      <c r="H145" t="n">
+        <v>141</v>
+      </c>
+      <c r="I145" t="n">
+        <v>146.1799926757812</v>
+      </c>
+      <c r="J145" t="n">
+        <v>141</v>
+      </c>
+      <c r="K145" t="n">
+        <v>25931</v>
+      </c>
+      <c r="L145" t="n">
+        <v>-3.54</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>UCAL Ltd. Share Price Near 52-Week High Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>UCAL Ltd. Share Price Near 52-Week High Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>UCAL Ltd. Share Price Today: 9.08% Rise, Valuation Check - Univest</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>UCAL Share Price Rises 10.34%: Technicals, Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Ucal Q1 net profit up 1,702% to ₹5.87 crore; appoints new CEO - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>5</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ASTERDM.NS</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ASTERDM</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>798.3499755859375</v>
+      </c>
+      <c r="F146" t="n">
+        <v>798.3499755859375</v>
+      </c>
+      <c r="G146" t="n">
+        <v>771.0499877929688</v>
+      </c>
+      <c r="H146" t="n">
+        <v>774</v>
+      </c>
+      <c r="I146" t="n">
+        <v>800.2000122070312</v>
+      </c>
+      <c r="J146" t="n">
+        <v>774</v>
+      </c>
+      <c r="K146" t="n">
+        <v>3325406</v>
+      </c>
+      <c r="L146" t="n">
+        <v>-3.27</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Aster DM Quality Care Limited (NSE:ASTERDM) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹898 - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Aster DM Healthcare Ltd. Share Price Fall and Market Action - Univest</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Aster DM Healthcare Ltd. Share Price Fall and Market Action - Univest</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Aster DM Healthcare Ltd. (ASTERDM) Share Price Hits Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Aster DM Quality Care Board Clears Q1 FY27 Unaudited Results After Clean Auditor Review - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>6</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>AHLADA.NS</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>AHLADA</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>40.81999969482422</v>
+      </c>
+      <c r="F147" t="n">
+        <v>40.81999969482422</v>
+      </c>
+      <c r="G147" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="H147" t="n">
+        <v>39.4900016784668</v>
+      </c>
+      <c r="I147" t="n">
+        <v>40.81999969482422</v>
+      </c>
+      <c r="J147" t="n">
+        <v>39.4900016784668</v>
+      </c>
+      <c r="K147" t="n">
+        <v>31885</v>
+      </c>
+      <c r="L147" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Ahlada Engineers Ltd is Rated Strong Sell - marketsmojo.com</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Ahlada Engineers Ltd is Rated Strong Sell - marketsmojo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>7</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>FCL.NS</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>FCL</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>45.09999847412109</v>
+      </c>
+      <c r="F148" t="n">
+        <v>45.47999954223633</v>
+      </c>
+      <c r="G148" t="n">
+        <v>43.36999893188477</v>
+      </c>
+      <c r="H148" t="n">
+        <v>43.56000137329102</v>
+      </c>
+      <c r="I148" t="n">
+        <v>44.97999954223633</v>
+      </c>
+      <c r="J148" t="n">
+        <v>43.56000137329102</v>
+      </c>
+      <c r="K148" t="n">
+        <v>5672129</v>
+      </c>
+      <c r="L148" t="n">
+        <v>-3.16</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Manulife Ideal Cnd Div Growth7575 FCL (0P000180PM.TO) interactive stock chart - Yahoo Finance UK</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Cash Flow Decline and Customer Concentration Remain Key Risks for FCL - Kalkine</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Why Are Investors Watching Fineos (ASX:FCL) After Its Latest Share Price Decline? - Kalkine</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>FINEOS (ASX:FCL) Shares Rebound As Profit Emerges Under Rich P E - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Fineos (ASX: FCL) Crosses Profitability Inflection Point In H1 FY 2026 - arichlife.com.au</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>8</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>GLFL.NS</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>GLFL</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>6</v>
+      </c>
+      <c r="F149" t="n">
+        <v>6</v>
+      </c>
+      <c r="G149" t="n">
+        <v>5.639999866485596</v>
+      </c>
+      <c r="H149" t="n">
+        <v>5.639999866485596</v>
+      </c>
+      <c r="I149" t="n">
+        <v>5.820000171661377</v>
+      </c>
+      <c r="J149" t="n">
+        <v>5.639999866485596</v>
+      </c>
+      <c r="K149" t="n">
+        <v>143</v>
+      </c>
+      <c r="L149" t="n">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>9</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>DREDGECORP.NS</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>DREDGECORP</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>1199</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1204</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1155.099975585938</v>
+      </c>
+      <c r="H150" t="n">
+        <v>1156.599975585938</v>
+      </c>
+      <c r="I150" t="n">
+        <v>1189.199951171875</v>
+      </c>
+      <c r="J150" t="n">
+        <v>1156.599975585938</v>
+      </c>
+      <c r="K150" t="n">
+        <v>101771</v>
+      </c>
+      <c r="L150" t="n">
+        <v>-2.74</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>10</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>CHENNPETRO.NS</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>CHENNPETRO</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>1457</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1466</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1379.599975585938</v>
+      </c>
+      <c r="H151" t="n">
+        <v>1403.599975585938</v>
+      </c>
+      <c r="I151" t="n">
+        <v>1440.300048828125</v>
+      </c>
+      <c r="J151" t="n">
+        <v>1403.599975585938</v>
+      </c>
+      <c r="K151" t="n">
+        <v>1468357</v>
+      </c>
+      <c r="L151" t="n">
+        <v>-2.55</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>11</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>YASHO.NS</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>YASHO</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F152" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G152" t="n">
+        <v>4300</v>
+      </c>
+      <c r="H152" t="n">
+        <v>4358</v>
+      </c>
+      <c r="I152" t="n">
+        <v>4470.7998046875</v>
+      </c>
+      <c r="J152" t="n">
+        <v>4358</v>
+      </c>
+      <c r="K152" t="n">
+        <v>76746</v>
+      </c>
+      <c r="L152" t="n">
+        <v>-2.52</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - marketsmojo.com</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Yasho Ind. Standalone June 2026 Net Sales at Rs 314.09 crore, up 58.73% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Yasho Ind. Consolidated June 2026 Net Sales at Rs 307.74 crore, up 54.93% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Yasho Industries shareholders approve ₹0.50 dividend, reappoint directors at 40th AGM - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>12</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>RECLTD.NS</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>338</v>
+      </c>
+      <c r="F153" t="n">
+        <v>338.6000061035156</v>
+      </c>
+      <c r="G153" t="n">
+        <v>327.5499877929688</v>
+      </c>
+      <c r="H153" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="I153" t="n">
+        <v>337</v>
+      </c>
+      <c r="J153" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="K153" t="n">
+        <v>3402656</v>
+      </c>
+      <c r="L153" t="n">
+        <v>-2.52</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>13</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>LCL.NS</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>LCL</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>552</v>
+      </c>
+      <c r="F154" t="n">
+        <v>576.9500122070312</v>
+      </c>
+      <c r="G154" t="n">
+        <v>542.8499755859375</v>
+      </c>
+      <c r="H154" t="n">
+        <v>548.0999755859375</v>
+      </c>
+      <c r="I154" t="n">
+        <v>561.2999877929688</v>
+      </c>
+      <c r="J154" t="n">
+        <v>548.0999755859375</v>
+      </c>
+      <c r="K154" t="n">
+        <v>1255241</v>
+      </c>
+      <c r="L154" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>LOHIA CORP LIMITED Share Price: New One-Year High Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>LOHIA CORP LIMITED Share Price: New One-Year High Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Tour De France Femmes Avec Zwift 2026 - Stage 1 Minute Maillot Jaune LCL Broadcom Stock (4dymOXXZjv) - Mshale</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>14</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>PFC.NS</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>374.4500122070312</v>
+      </c>
+      <c r="F155" t="n">
+        <v>375.1000061035156</v>
+      </c>
+      <c r="G155" t="n">
+        <v>365.0499877929688</v>
+      </c>
+      <c r="H155" t="n">
+        <v>365.7000122070312</v>
+      </c>
+      <c r="I155" t="n">
+        <v>374.4500122070312</v>
+      </c>
+      <c r="J155" t="n">
+        <v>365.7000122070312</v>
+      </c>
+      <c r="K155" t="n">
+        <v>5806073</v>
+      </c>
+      <c r="L155" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>PFC, REC Shares Fall As Morgan Stanley Downgrades Both Stocks — Check Target Price, Potential Upside - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>PFC, REC Shares Fall As Morgan Stanley Downgrades Both Stocks — Check Target Price, Potential Upside - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>'Consensus buy' PFC, 'no sell' REC get downgraded; Check rationale and new targets - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>PFC shares tumble 5% to 4-month low after weak Q1 earnings. Why Motilal Oswal still recommends Buy - The Economic Times</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>PFC, REC shares fall up to 8% as CLSA cuts target prices on 'mixed' Q1 results - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>15</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>SUBEXLTD.NS</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>SUBEXLTD</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>15.98999977111816</v>
+      </c>
+      <c r="F156" t="n">
+        <v>16.07999992370605</v>
+      </c>
+      <c r="G156" t="n">
+        <v>15.26000022888184</v>
+      </c>
+      <c r="H156" t="n">
+        <v>15.57999992370605</v>
+      </c>
+      <c r="I156" t="n">
+        <v>15.92000007629395</v>
+      </c>
+      <c r="J156" t="n">
+        <v>15.57999992370605</v>
+      </c>
+      <c r="K156" t="n">
+        <v>4575797</v>
+      </c>
+      <c r="L156" t="n">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>16</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>SSWL.NS</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>SSWL</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>316.25</v>
+      </c>
+      <c r="F157" t="n">
+        <v>319.6000061035156</v>
+      </c>
+      <c r="G157" t="n">
+        <v>307.9500122070312</v>
+      </c>
+      <c r="H157" t="n">
+        <v>309.1000061035156</v>
+      </c>
+      <c r="I157" t="n">
+        <v>315.8500061035156</v>
+      </c>
+      <c r="J157" t="n">
+        <v>309.1000061035156</v>
+      </c>
+      <c r="K157" t="n">
+        <v>285688</v>
+      </c>
+      <c r="L157" t="n">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>17</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>MILKYMIST.NS</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>MILKYMIST</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>207.8000030517578</v>
+      </c>
+      <c r="F158" t="n">
+        <v>211.8000030517578</v>
+      </c>
+      <c r="G158" t="n">
+        <v>191.25</v>
+      </c>
+      <c r="H158" t="n">
+        <v>195.3999938964844</v>
+      </c>
+      <c r="I158" t="n">
+        <v>199.6499938964844</v>
+      </c>
+      <c r="J158" t="n">
+        <v>195.3999938964844</v>
+      </c>
+      <c r="K158" t="n">
+        <v>40109363</v>
+      </c>
+      <c r="L158" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Milky Mist shares make decent market debut at 18% premium; should you buy, sell or hold? - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Average basic shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Milky Mist share price extends post-listing gains, hits 10% upper circuit - Business Standard</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Milky Mist IPO Listing: Shares Debut at ₹165, Gain 18%; Stock Rises 29.64% From Issue Price - India Infoline</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Milky Mist share price up 30% after IPO listing: Should investors hold or book profits? - India Today</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>18</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>EXCELINDUS.NS</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>EXCELINDUS</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>1133.25</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1139.5</v>
+      </c>
+      <c r="G159" t="n">
+        <v>1096</v>
+      </c>
+      <c r="H159" t="n">
+        <v>1109.800048828125</v>
+      </c>
+      <c r="I159" t="n">
+        <v>1133.25</v>
+      </c>
+      <c r="J159" t="n">
+        <v>1109.800048828125</v>
+      </c>
+      <c r="K159" t="n">
+        <v>73966</v>
+      </c>
+      <c r="L159" t="n">
+        <v>-2.07</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>19</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>TALBROAUTO.NS</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>TALBROAUTO</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>423.1000061035156</v>
+      </c>
+      <c r="F160" t="n">
+        <v>428.1499938964844</v>
+      </c>
+      <c r="G160" t="n">
+        <v>410.3500061035156</v>
+      </c>
+      <c r="H160" t="n">
+        <v>414.5</v>
+      </c>
+      <c r="I160" t="n">
+        <v>423.0499877929688</v>
+      </c>
+      <c r="J160" t="n">
+        <v>414.5</v>
+      </c>
+      <c r="K160" t="n">
+        <v>204348</v>
+      </c>
+      <c r="L160" t="n">
+        <v>-2.02</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:44:21</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>20</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SONAMLTD.NS</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>SONAMLTD</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>66</v>
+      </c>
+      <c r="F161" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="G161" t="n">
+        <v>65.11000061035156</v>
+      </c>
+      <c r="H161" t="n">
+        <v>65.84999847412109</v>
+      </c>
+      <c r="I161" t="n">
+        <v>67.19000244140625</v>
+      </c>
+      <c r="J161" t="n">
+        <v>65.84999847412109</v>
+      </c>
+      <c r="K161" t="n">
+        <v>166441</v>
+      </c>
+      <c r="L161" t="n">
+        <v>-1.99</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>GLFL.NS</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>GLFL</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>6</v>
+      </c>
+      <c r="F162" t="n">
+        <v>6</v>
+      </c>
+      <c r="G162" t="n">
+        <v>5.639999866485596</v>
+      </c>
+      <c r="H162" t="n">
+        <v>5.639999866485596</v>
+      </c>
+      <c r="I162" t="n">
+        <v>5.820000171661377</v>
+      </c>
+      <c r="J162" t="n">
+        <v>5.639999866485596</v>
+      </c>
+      <c r="K162" t="n">
+        <v>143</v>
+      </c>
+      <c r="L162" t="n">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>2</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>CESC.NS</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>159.2100067138672</v>
+      </c>
+      <c r="F163" t="n">
+        <v>160.1999969482422</v>
+      </c>
+      <c r="G163" t="n">
+        <v>156.5599975585938</v>
+      </c>
+      <c r="H163" t="n">
+        <v>157.3200073242188</v>
+      </c>
+      <c r="I163" t="n">
+        <v>159.6600036621094</v>
+      </c>
+      <c r="J163" t="n">
+        <v>157.3200073242188</v>
+      </c>
+      <c r="K163" t="n">
+        <v>1110292</v>
+      </c>
+      <c r="L163" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>For CESC investors, renewable energy should yield dual benefits of stock rerating and growth - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Adani Power, BHEL, Suzlon, Waaree, IEX, Tata Power, CESC: Target prices, top 5 stock picks - Business Today</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Adani Power, BHEL, Suzlon, Waaree, IEX, Tata Power, CESC: Target prices, top 5 stock picks - Business Today</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>CESC Limited Earnings Missed Analyst Estimates: Here's What Analysts Are Forecasting Now - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>CESC Ltd soars 1.23% - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>3</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>IPCALAB.NS</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>1922</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1928.400024414062</v>
+      </c>
+      <c r="G164" t="n">
+        <v>1884.300048828125</v>
+      </c>
+      <c r="H164" t="n">
+        <v>1885.599975585938</v>
+      </c>
+      <c r="I164" t="n">
+        <v>1903.699951171875</v>
+      </c>
+      <c r="J164" t="n">
+        <v>1885.599975585938</v>
+      </c>
+      <c r="K164" t="n">
+        <v>88293</v>
+      </c>
+      <c r="L164" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories Ltd. Share Price Fall: Price Action View - Univest</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories shares gain 5.35% to Rs 1,827 - TradingView</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories Ltd. Stock News: Share Price Up 4.76% - Univest</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories shares fall over 2%; strong financial performance reported - TradingView</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories shares gain 5.35% to Rs 1,827 - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>4</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>GNFC.NS</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>GNFC</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>603</v>
+      </c>
+      <c r="F165" t="n">
+        <v>606.25</v>
+      </c>
+      <c r="G165" t="n">
+        <v>593.2999877929688</v>
+      </c>
+      <c r="H165" t="n">
+        <v>597.4500122070312</v>
+      </c>
+      <c r="I165" t="n">
+        <v>602.2999877929688</v>
+      </c>
+      <c r="J165" t="n">
+        <v>597.4500122070312</v>
+      </c>
+      <c r="K165" t="n">
+        <v>233575</v>
+      </c>
+      <c r="L165" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>GNFC Share Price Today: 5.56% Gain, Price Action Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Top stock picks: MCX, L&amp;T Finance among Mitessh Thakkar's buys; JSW Energy, Marico get sell calls - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Top stock picks: MCX, L&amp;T Finance among Mitessh Thakkar's buys; JSW Energy, Marico get sell calls - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>GNFC Standalone June 2026 Net Sales at Rs 2,238.00 crore, up 39.79% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>GNFC transfers unclaimed equity shares to IEPF account - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>5</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>IFCI.NS</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>IFCI</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>82</v>
+      </c>
+      <c r="F166" t="n">
+        <v>82.52999877929688</v>
+      </c>
+      <c r="G166" t="n">
+        <v>80.37000274658203</v>
+      </c>
+      <c r="H166" t="n">
+        <v>81.08999633789062</v>
+      </c>
+      <c r="I166" t="n">
+        <v>81.68000030517578</v>
+      </c>
+      <c r="J166" t="n">
+        <v>81.08999633789062</v>
+      </c>
+      <c r="K166" t="n">
+        <v>12834793</v>
+      </c>
+      <c r="L166" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Stock to buy today: IFCI (₹81.40) – BUY - BusinessLine</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Stock to buy today: IFCI (₹81.40) – BUY - BusinessLine</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>IFCI Share Price Rises 3.19% Today: Price Action Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>IFCI Standalone June 2026 Net Sales at Rs 102.64 crore, down 34% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>IFCI Q1 Results: Revenue declines, profit improves sequentially to ₹60 crore - livemint.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>6</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>GFLLIMITED.NS</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>GFLLIMITED</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>57.95000076293945</v>
+      </c>
+      <c r="F167" t="n">
+        <v>57.95000076293945</v>
+      </c>
+      <c r="G167" t="n">
+        <v>55</v>
+      </c>
+      <c r="H167" t="n">
+        <v>56.40000152587891</v>
+      </c>
+      <c r="I167" t="n">
+        <v>56.7599983215332</v>
+      </c>
+      <c r="J167" t="n">
+        <v>56.40000152587891</v>
+      </c>
+      <c r="K167" t="n">
+        <v>150881</v>
+      </c>
+      <c r="L167" t="n">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>7</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ASIANPAINT.NS</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>2635.10009765625</v>
+      </c>
+      <c r="F168" t="n">
+        <v>2641.800048828125</v>
+      </c>
+      <c r="G168" t="n">
+        <v>2607</v>
+      </c>
+      <c r="H168" t="n">
+        <v>2615</v>
+      </c>
+      <c r="I168" t="n">
+        <v>2630.800048828125</v>
+      </c>
+      <c r="J168" t="n">
+        <v>2615</v>
+      </c>
+      <c r="K168" t="n">
+        <v>182487</v>
+      </c>
+      <c r="L168" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>8</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>FINCABLES.NS</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>FINCABLES</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>1313.699951171875</v>
+      </c>
+      <c r="F169" t="n">
+        <v>1331</v>
+      </c>
+      <c r="G169" t="n">
+        <v>1302</v>
+      </c>
+      <c r="H169" t="n">
+        <v>1306.199951171875</v>
+      </c>
+      <c r="I169" t="n">
+        <v>1313.699951171875</v>
+      </c>
+      <c r="J169" t="n">
+        <v>1306.199951171875</v>
+      </c>
+      <c r="K169" t="n">
+        <v>261217</v>
+      </c>
+      <c r="L169" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>9</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>CUMMINSIND.NS</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>5250</v>
+      </c>
+      <c r="F170" t="n">
+        <v>5252.5</v>
+      </c>
+      <c r="G170" t="n">
+        <v>5192.5</v>
+      </c>
+      <c r="H170" t="n">
+        <v>5207</v>
+      </c>
+      <c r="I170" t="n">
+        <v>5220</v>
+      </c>
+      <c r="J170" t="n">
+        <v>5207</v>
+      </c>
+      <c r="K170" t="n">
+        <v>116554</v>
+      </c>
+      <c r="L170" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>The Cummins India Limited (NSE:CUMMINSIND) First-Quarter Results Are Out And Analysts Have Published New Forecasts - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>The Cummins India Limited (NSE:CUMMINSIND) First-Quarter Results Are Out And Analysts Have Published New Forecasts - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>10</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>PCBL.NS</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>PCBL</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>328</v>
+      </c>
+      <c r="F171" t="n">
+        <v>328</v>
+      </c>
+      <c r="G171" t="n">
+        <v>324</v>
+      </c>
+      <c r="H171" t="n">
+        <v>326</v>
+      </c>
+      <c r="I171" t="n">
+        <v>326.7000122070312</v>
+      </c>
+      <c r="J171" t="n">
+        <v>326</v>
+      </c>
+      <c r="K171" t="n">
+        <v>308168</v>
+      </c>
+      <c r="L171" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>PCBL Chemical Gets ₹329 Crore ECMS Approval; Shares Rise 3.52% - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>PCBL Chemical secures ECMS nod for ₹329 crore Acetylene Black project - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Govt clears ₹7,877 crore ECMS investments; Wipro, PCBL Chemical, Syrma SGS shares in focus - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>We Wouldn't Be Too Quick To Buy PCBL Chemical Limited (NSE:PCBL) Before It Goes Ex-Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>PCBL Chemical secures ECMS nod for ₹329 crore Acetylene Black project - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>11</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>BPL.NS</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>BPL</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>50.90000152587891</v>
+      </c>
+      <c r="F172" t="n">
+        <v>50.91999816894531</v>
+      </c>
+      <c r="G172" t="n">
+        <v>50</v>
+      </c>
+      <c r="H172" t="n">
+        <v>50.2599983215332</v>
+      </c>
+      <c r="I172" t="n">
+        <v>50.33000183105469</v>
+      </c>
+      <c r="J172" t="n">
+        <v>50.2599983215332</v>
+      </c>
+      <c r="K172" t="n">
+        <v>21214</v>
+      </c>
+      <c r="L172" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>12</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>SUNPHARMA.NS</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>1905</v>
+      </c>
+      <c r="F173" t="n">
+        <v>1911.599975585938</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1890.300048828125</v>
+      </c>
+      <c r="H173" t="n">
+        <v>1897.400024414062</v>
+      </c>
+      <c r="I173" t="n">
+        <v>1900</v>
+      </c>
+      <c r="J173" t="n">
+        <v>1897.400024414062</v>
+      </c>
+      <c r="K173" t="n">
+        <v>489986</v>
+      </c>
+      <c r="L173" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>SUNPHARMA Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>SUNPHARMA Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Why is Sun Pharmaceutical Industries stock falling today? - Investing.com</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Results: Sun Pharmaceutical Industries Limited Exceeded Expectations And The Consensus Has Updated Its Estimates - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>13</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>SBIN.NS</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>1052.900024414062</v>
+      </c>
+      <c r="F174" t="n">
+        <v>1052.900024414062</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1045.699951171875</v>
+      </c>
+      <c r="H174" t="n">
+        <v>1047.900024414062</v>
+      </c>
+      <c r="I174" t="n">
+        <v>1048.599975585938</v>
+      </c>
+      <c r="J174" t="n">
+        <v>1047.900024414062</v>
+      </c>
+      <c r="K174" t="n">
+        <v>2904758</v>
+      </c>
+      <c r="L174" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>SBI Share Price - Live NSE: SBIN Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>State Bank of India Stock Update: Shares Dip Amid Recruitment Woes, RBI Policy Shift - latestly.com</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>SBIN Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>SBIN Share Price Today - State Bank Of India Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>State Bank of India Stock Update: Share Price Dips on Recruitment Concerns - latestly.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>14</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ITC.NS</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>268.2000122070312</v>
+      </c>
+      <c r="F175" t="n">
+        <v>268.5499877929688</v>
+      </c>
+      <c r="G175" t="n">
+        <v>265</v>
+      </c>
+      <c r="H175" t="n">
+        <v>266.9500122070312</v>
+      </c>
+      <c r="I175" t="n">
+        <v>267.0499877929688</v>
+      </c>
+      <c r="J175" t="n">
+        <v>266.9500122070312</v>
+      </c>
+      <c r="K175" t="n">
+        <v>9999434</v>
+      </c>
+      <c r="L175" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>ITC Share Price Today at 52-Week Low: Price and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>ITC Share Price Today at 52-Week Low: Price and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>ITC share price slips 2%, hits 52-week low; what's making Street nervous? - Business Standard</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>ITC stock hits 52-week low for second day, price targets and more - Business Today</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>ITC shares bounce back as analysts back volume resilience despite cigarette earnings hit - BusinessLine</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>15</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>HEG.NS</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>HEG</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>710</v>
+      </c>
+      <c r="F176" t="n">
+        <v>718.6500244140625</v>
+      </c>
+      <c r="G176" t="n">
+        <v>696.0999755859375</v>
+      </c>
+      <c r="H176" t="n">
+        <v>707.9500122070312</v>
+      </c>
+      <c r="I176" t="n">
+        <v>708.0499877929688</v>
+      </c>
+      <c r="J176" t="n">
+        <v>707.9500122070312</v>
+      </c>
+      <c r="K176" t="n">
+        <v>701780</v>
+      </c>
+      <c r="L176" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Stocks in news: Hyundai Motor India, BSE, HEG, Hexaware Tech and Oil India - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Stocks to Watch, August 20: Hyundai Motor, HDFC Life, Airtel, BSE, HEG in focus today - Zee Business</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>HEG gets NCLT nod for demerger; shareholders to receive 1:1 shares in HEG Graphite - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>HEG Share Price Today Down 4% - Equitymaster</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Stocks to Watch, August 20: Hyundai Motor, HDFC Life, Airtel, BSE, HEG in focus today - Zee Business</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>16</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>FMGOETZE.NS</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>FMGOETZE</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>471.6499938964844</v>
+      </c>
+      <c r="F177" t="n">
+        <v>480.4500122070312</v>
+      </c>
+      <c r="G177" t="n">
+        <v>464.1000061035156</v>
+      </c>
+      <c r="H177" t="n">
+        <v>474.8999938964844</v>
+      </c>
+      <c r="J177" t="n">
+        <v>474.8999938964844</v>
+      </c>
+      <c r="K177" t="n">
+        <v>25800</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>17</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>WILLAMAGOR.NS</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>WILLAMAGOR</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>25.10000038146973</v>
+      </c>
+      <c r="F178" t="n">
+        <v>25.71999931335449</v>
+      </c>
+      <c r="G178" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H178" t="n">
+        <v>25.42000007629395</v>
+      </c>
+      <c r="J178" t="n">
+        <v>25.42000007629395</v>
+      </c>
+      <c r="K178" t="n">
+        <v>1669</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>18</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>VINDHYATEL.NS</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>VINDHYATEL</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>2459</v>
+      </c>
+      <c r="F179" t="n">
+        <v>2498</v>
+      </c>
+      <c r="G179" t="n">
+        <v>2421.89990234375</v>
+      </c>
+      <c r="H179" t="n">
+        <v>2435.5</v>
+      </c>
+      <c r="J179" t="n">
+        <v>2435.5</v>
+      </c>
+      <c r="K179" t="n">
+        <v>12998</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>19</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ESCORTS.NS</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ESCORTS</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>3059.60009765625</v>
+      </c>
+      <c r="F180" t="n">
+        <v>3099</v>
+      </c>
+      <c r="G180" t="n">
+        <v>3059</v>
+      </c>
+      <c r="H180" t="n">
+        <v>3086.89990234375</v>
+      </c>
+      <c r="J180" t="n">
+        <v>3086.89990234375</v>
+      </c>
+      <c r="K180" t="n">
+        <v>34239</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Escorts Kubota Shares Fall 2.13% to Rs 3,067.00 Amid Bullish Sentiment - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Escorts Kubota breaks ground on ₹2,000 crore greenfield plant in Uttar Pradesh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Escorts Kubota breaks ground on ₹2,000 crore greenfield plant in Uttar Pradesh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Escorts Kubota July Tractor Sales Grow 22% to 8,731 Units Led by Strong Domestic Market - Univest</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Escorts Kubota Q1FY27: Revenue jumps 28% Y-o-Y, profit at ₹386 crore - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:49:02</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>20</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>JAYSREETEA.NS</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>JAYSREETEA</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>94.52999877929688</v>
+      </c>
+      <c r="F181" t="n">
+        <v>99.40000152587891</v>
+      </c>
+      <c r="G181" t="n">
+        <v>94</v>
+      </c>
+      <c r="H181" t="n">
+        <v>98.26999664306641</v>
+      </c>
+      <c r="J181" t="n">
+        <v>98.26999664306641</v>
+      </c>
+      <c r="K181" t="n">
+        <v>156216</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Jay Shree Tea &amp; Industries Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Jay Shree Tea &amp; Industries Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>GLFL.NS</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>GLFL</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>6</v>
+      </c>
+      <c r="F182" t="n">
+        <v>6</v>
+      </c>
+      <c r="G182" t="n">
+        <v>5.639999866485596</v>
+      </c>
+      <c r="H182" t="n">
+        <v>5.639999866485596</v>
+      </c>
+      <c r="I182" t="n">
+        <v>5.820000171661377</v>
+      </c>
+      <c r="J182" t="n">
+        <v>5.639999866485596</v>
+      </c>
+      <c r="K182" t="n">
+        <v>143</v>
+      </c>
+      <c r="L182" t="n">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>2</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>CESC.NS</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>159.2100067138672</v>
+      </c>
+      <c r="F183" t="n">
+        <v>160.1999969482422</v>
+      </c>
+      <c r="G183" t="n">
+        <v>156.5599975585938</v>
+      </c>
+      <c r="H183" t="n">
+        <v>157.2599945068359</v>
+      </c>
+      <c r="I183" t="n">
+        <v>159.6600036621094</v>
+      </c>
+      <c r="J183" t="n">
+        <v>157.2599945068359</v>
+      </c>
+      <c r="K183" t="n">
+        <v>1137522</v>
+      </c>
+      <c r="L183" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Adani Power, BHEL, Suzlon, Waaree, IEX, Tata Power, CESC: Target prices, top 5 stock picks - Business Today</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Adani Power, BHEL, Suzlon, Waaree, IEX, Tata Power, CESC: Target prices, top 5 stock picks - Business Today</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>For CESC investors, renewable energy should yield dual benefits of stock rerating and growth - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>CESC Limited Earnings Missed Analyst Estimates: Here's What Analysts Are Forecasting Now - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>CESC Ltd soars 1.23% - business-standard.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>3</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>BPL.NS</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>BPL</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>50.90000152587891</v>
+      </c>
+      <c r="F184" t="n">
+        <v>50.91999816894531</v>
+      </c>
+      <c r="G184" t="n">
+        <v>49.41999816894531</v>
+      </c>
+      <c r="H184" t="n">
+        <v>49.61000061035156</v>
+      </c>
+      <c r="I184" t="n">
+        <v>50.33000183105469</v>
+      </c>
+      <c r="J184" t="n">
+        <v>49.61000061035156</v>
+      </c>
+      <c r="K184" t="n">
+        <v>23142</v>
+      </c>
+      <c r="L184" t="n">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>4</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>IPCALAB.NS</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>1922</v>
+      </c>
+      <c r="F185" t="n">
+        <v>1928.400024414062</v>
+      </c>
+      <c r="G185" t="n">
+        <v>1883.099975585938</v>
+      </c>
+      <c r="H185" t="n">
+        <v>1884.300048828125</v>
+      </c>
+      <c r="I185" t="n">
+        <v>1903.699951171875</v>
+      </c>
+      <c r="J185" t="n">
+        <v>1884.300048828125</v>
+      </c>
+      <c r="K185" t="n">
+        <v>89435</v>
+      </c>
+      <c r="L185" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories Ltd. Share Price Fall: Price Action View - Univest</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories shares gain 5.35% to Rs 1,827 - TradingView</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories Ltd. Stock News: Share Price Up 4.76% - Univest</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories shares fall over 2%; strong financial performance reported - TradingView</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories shares gain 5.35% to Rs 1,827 - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>5</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>GFLLIMITED.NS</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>GFLLIMITED</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>57.95000076293945</v>
+      </c>
+      <c r="F186" t="n">
+        <v>57.95000076293945</v>
+      </c>
+      <c r="G186" t="n">
+        <v>55</v>
+      </c>
+      <c r="H186" t="n">
+        <v>56.29999923706055</v>
+      </c>
+      <c r="I186" t="n">
+        <v>56.7599983215332</v>
+      </c>
+      <c r="J186" t="n">
+        <v>56.29999923706055</v>
+      </c>
+      <c r="K186" t="n">
+        <v>155386</v>
+      </c>
+      <c r="L186" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>6</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>GNFC.NS</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>GNFC</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>603</v>
+      </c>
+      <c r="F187" t="n">
+        <v>606.25</v>
+      </c>
+      <c r="G187" t="n">
+        <v>593.2999877929688</v>
+      </c>
+      <c r="H187" t="n">
+        <v>597.5999755859375</v>
+      </c>
+      <c r="I187" t="n">
+        <v>602.2999877929688</v>
+      </c>
+      <c r="J187" t="n">
+        <v>597.5999755859375</v>
+      </c>
+      <c r="K187" t="n">
+        <v>241303</v>
+      </c>
+      <c r="L187" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>GNFC Share Price Today: 5.56% Gain, Price Action Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Top stock picks: MCX, L&amp;T Finance among Mitessh Thakkar's buys; JSW Energy, Marico get sell calls - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Top stock picks: MCX, L&amp;T Finance among Mitessh Thakkar's buys; JSW Energy, Marico get sell calls - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>GNFC Standalone June 2026 Net Sales at Rs 2,238.00 crore, up 39.79% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>GNFC transfers unclaimed equity shares to IEPF account - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>7</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>IFCI.NS</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>IFCI</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>82</v>
+      </c>
+      <c r="F188" t="n">
+        <v>82.52999877929688</v>
+      </c>
+      <c r="G188" t="n">
+        <v>80.37000274658203</v>
+      </c>
+      <c r="H188" t="n">
+        <v>81.19999694824219</v>
+      </c>
+      <c r="I188" t="n">
+        <v>81.68000030517578</v>
+      </c>
+      <c r="J188" t="n">
+        <v>81.19999694824219</v>
+      </c>
+      <c r="K188" t="n">
+        <v>13157188</v>
+      </c>
+      <c r="L188" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Stock to buy today: IFCI (₹81.40) – BUY - BusinessLine</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>Stock to buy today: IFCI (₹81.40) – BUY - BusinessLine</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>IFCI Share Price Rises 3.19% Today: Price Action Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>IFCI Standalone June 2026 Net Sales at Rs 102.64 crore, down 34% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>IFCI Q1 Results: Revenue declines, profit improves sequentially to ₹60 crore - livemint.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>8</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>ASIANPAINT.NS</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>2635.10009765625</v>
+      </c>
+      <c r="F189" t="n">
+        <v>2641.800048828125</v>
+      </c>
+      <c r="G189" t="n">
+        <v>2607</v>
+      </c>
+      <c r="H189" t="n">
+        <v>2616.300048828125</v>
+      </c>
+      <c r="I189" t="n">
+        <v>2630.800048828125</v>
+      </c>
+      <c r="J189" t="n">
+        <v>2616.300048828125</v>
+      </c>
+      <c r="K189" t="n">
+        <v>188286</v>
+      </c>
+      <c r="L189" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>9</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>FINCABLES.NS</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>FINCABLES</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>1313.699951171875</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1331</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1302</v>
+      </c>
+      <c r="H190" t="n">
+        <v>1308.800048828125</v>
+      </c>
+      <c r="I190" t="n">
+        <v>1313.699951171875</v>
+      </c>
+      <c r="J190" t="n">
+        <v>1308.800048828125</v>
+      </c>
+      <c r="K190" t="n">
+        <v>266377</v>
+      </c>
+      <c r="L190" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>10</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>HEG.NS</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>HEG</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>710</v>
+      </c>
+      <c r="F191" t="n">
+        <v>718.6500244140625</v>
+      </c>
+      <c r="G191" t="n">
+        <v>696.0999755859375</v>
+      </c>
+      <c r="H191" t="n">
+        <v>706.9500122070312</v>
+      </c>
+      <c r="I191" t="n">
+        <v>708.0499877929688</v>
+      </c>
+      <c r="J191" t="n">
+        <v>706.9500122070312</v>
+      </c>
+      <c r="K191" t="n">
+        <v>723529</v>
+      </c>
+      <c r="L191" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>HEG gets NCLT nod for demerger; shareholders to receive 1:1 shares in HEG Graphite - CNBC TV18 - LinkedIn</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>HEG receives NCLT approval for demerger scheme; shareholders to get 1:1 shares in HEG Graphite - livemint.com</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>HEG Gets NCLT Approval For Demerger Plan In 1:1 Share Ratio - Sahi</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>HEG receives NCLT approval for demerger scheme; shareholders to get 1:1 shares in HEG Graphite - livemint.com</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-19 — cnbctv:02f6ca213094b:0 - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>11</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>SBIN.NS</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>1052.900024414062</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1052.900024414062</v>
+      </c>
+      <c r="G192" t="n">
+        <v>1045.699951171875</v>
+      </c>
+      <c r="H192" t="n">
+        <v>1047</v>
+      </c>
+      <c r="I192" t="n">
+        <v>1048.599975585938</v>
+      </c>
+      <c r="J192" t="n">
+        <v>1047</v>
+      </c>
+      <c r="K192" t="n">
+        <v>3024906</v>
+      </c>
+      <c r="L192" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>SBI Share Price - Live NSE: SBIN Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>State Bank of India Stock Update: Shares Dip Amid Recruitment Woes, RBI Policy Shift - latestly.com</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>SBIN Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>SBIN Share Price Today - State Bank Of India Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>State Bank of India Stock Update: Share Price Dips on Recruitment Concerns - latestly.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>12</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>CUMMINSIND.NS</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>5250</v>
+      </c>
+      <c r="F193" t="n">
+        <v>5252.5</v>
+      </c>
+      <c r="G193" t="n">
+        <v>5192.5</v>
+      </c>
+      <c r="H193" t="n">
+        <v>5213</v>
+      </c>
+      <c r="I193" t="n">
+        <v>5220</v>
+      </c>
+      <c r="J193" t="n">
+        <v>5213</v>
+      </c>
+      <c r="K193" t="n">
+        <v>120905</v>
+      </c>
+      <c r="L193" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>The Cummins India Limited (NSE:CUMMINSIND) First-Quarter Results Are Out And Analysts Have Published New Forecasts - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>The Cummins India Limited (NSE:CUMMINSIND) First-Quarter Results Are Out And Analysts Have Published New Forecasts - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>13</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>SUNPHARMA.NS</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>1905</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1911.599975585938</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1890.300048828125</v>
+      </c>
+      <c r="H194" t="n">
+        <v>1897.900024414062</v>
+      </c>
+      <c r="I194" t="n">
+        <v>1900</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1897.900024414062</v>
+      </c>
+      <c r="K194" t="n">
+        <v>499721</v>
+      </c>
+      <c r="L194" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>SUNPHARMA Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>SUNPHARMA Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>Results: Sun Pharmaceutical Industries Limited Exceeded Expectations And The Consensus Has Updated Its Estimates - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Why is Sun Pharmaceutical Industries stock falling today? - Investing.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>14</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>HIMATSEIDE.NS</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>HIMATSEIDE</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>70.09999847412109</v>
+      </c>
+      <c r="F195" t="n">
+        <v>71.69999694824219</v>
+      </c>
+      <c r="G195" t="n">
+        <v>69.05999755859375</v>
+      </c>
+      <c r="H195" t="n">
+        <v>71.29000091552734</v>
+      </c>
+      <c r="J195" t="n">
+        <v>71.29000091552734</v>
+      </c>
+      <c r="K195" t="n">
+        <v>430507</v>
+      </c>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>15</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>FMGOETZE.NS</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>FMGOETZE</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>471.6499938964844</v>
+      </c>
+      <c r="F196" t="n">
+        <v>480.4500122070312</v>
+      </c>
+      <c r="G196" t="n">
+        <v>464.1000061035156</v>
+      </c>
+      <c r="H196" t="n">
+        <v>472</v>
+      </c>
+      <c r="J196" t="n">
+        <v>472</v>
+      </c>
+      <c r="K196" t="n">
+        <v>30378</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>16</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>MARALOVER.NS</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>MARALOVER</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>53.27000045776367</v>
+      </c>
+      <c r="F197" t="n">
+        <v>56.79999923706055</v>
+      </c>
+      <c r="G197" t="n">
+        <v>52.20999908447266</v>
+      </c>
+      <c r="H197" t="n">
+        <v>55.31000137329102</v>
+      </c>
+      <c r="J197" t="n">
+        <v>55.31000137329102</v>
+      </c>
+      <c r="K197" t="n">
+        <v>53013</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>17</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>WILLAMAGOR.NS</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>WILLAMAGOR</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>25.10000038146973</v>
+      </c>
+      <c r="F198" t="n">
+        <v>25.71999931335449</v>
+      </c>
+      <c r="G198" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H198" t="n">
+        <v>25.42000007629395</v>
+      </c>
+      <c r="J198" t="n">
+        <v>25.42000007629395</v>
+      </c>
+      <c r="K198" t="n">
+        <v>1647</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>18</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>VINDHYATEL.NS</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>VINDHYATEL</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>2459</v>
+      </c>
+      <c r="F199" t="n">
+        <v>2498</v>
+      </c>
+      <c r="G199" t="n">
+        <v>2421.89990234375</v>
+      </c>
+      <c r="H199" t="n">
+        <v>2436</v>
+      </c>
+      <c r="J199" t="n">
+        <v>2436</v>
+      </c>
+      <c r="K199" t="n">
+        <v>13031</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>19</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>ESCORTS.NS</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>ESCORTS</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>3059.60009765625</v>
+      </c>
+      <c r="F200" t="n">
+        <v>3099</v>
+      </c>
+      <c r="G200" t="n">
+        <v>3059</v>
+      </c>
+      <c r="H200" t="n">
+        <v>3087.89990234375</v>
+      </c>
+      <c r="J200" t="n">
+        <v>3087.89990234375</v>
+      </c>
+      <c r="K200" t="n">
+        <v>34920</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Escorts Kubota Shares Fall 2.13% to Rs 3,067.00 Amid Bullish Sentiment - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>Escorts Kubota breaks ground on ₹2,000 crore greenfield plant in Uttar Pradesh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Escorts Kubota breaks ground on ₹2,000 crore greenfield plant in Uttar Pradesh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Escorts Kubota Q1FY27: Revenue jumps 28% Y-o-Y, profit at ₹386 crore - business-standard.com</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>Escorts Kubota schedules analyst meet with Valuequest on Aug 21 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:59:33</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>20</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>JAYSREETEA.NS</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>JAYSREETEA</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>94.52999877929688</v>
+      </c>
+      <c r="F201" t="n">
+        <v>99.40000152587891</v>
+      </c>
+      <c r="G201" t="n">
+        <v>94</v>
+      </c>
+      <c r="H201" t="n">
+        <v>98.01000213623047</v>
+      </c>
+      <c r="J201" t="n">
+        <v>98.01000213623047</v>
+      </c>
+      <c r="K201" t="n">
+        <v>157071</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>Jay Shree Tea &amp; Industries Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>Jay Shree Tea &amp; Industries Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>GLFL.NS</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>GLFL</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>6</v>
+      </c>
+      <c r="F202" t="n">
+        <v>6</v>
+      </c>
+      <c r="G202" t="n">
+        <v>5.639999866485596</v>
+      </c>
+      <c r="H202" t="n">
+        <v>5.639999866485596</v>
+      </c>
+      <c r="I202" t="n">
+        <v>5.820000171661377</v>
+      </c>
+      <c r="J202" t="n">
+        <v>5.639999866485596</v>
+      </c>
+      <c r="K202" t="n">
+        <v>143</v>
+      </c>
+      <c r="L202" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>Gujarat Lease Financing (GLFL) Slips 2%: Stock Tests Key Support at ₹6.05 - Long Short Pair - Vinanet</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>Gujarat Lease Financing Limited (GLFL.NS): Consolidating Near Support at ₹6.0 Amidst Stalled Momentum - Value ETF - Vinanet</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Gujarat Lease Financing Limited (GLFL.NS): Consolidating Near Support at ₹6.0 Amidst Stalled Momentum - Value ETF - Vinanet</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Gujarat Lease Financing Limited (GLFL.NS) Q2 2025 Earnings: Minimal EPS of ₹0.02 Reflecting Subdued Activity - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>Gujarat Lease Financing (GLFL) Slips 1.96% as Stock Tests Critical Support Zone - Passive Flow - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>2</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>CESC.NS</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>159.2100067138672</v>
+      </c>
+      <c r="F203" t="n">
+        <v>160.1999969482422</v>
+      </c>
+      <c r="G203" t="n">
+        <v>156.5599975585938</v>
+      </c>
+      <c r="H203" t="n">
+        <v>157.3500061035156</v>
+      </c>
+      <c r="I203" t="n">
+        <v>159.6600036621094</v>
+      </c>
+      <c r="J203" t="n">
+        <v>157.3500061035156</v>
+      </c>
+      <c r="K203" t="n">
+        <v>1144241</v>
+      </c>
+      <c r="L203" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>Adani Power, BHEL, Suzlon, Waaree, IEX, Tata Power, CESC: Target prices, top 5 stock picks - Business Today</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>Adani Power, BHEL, Suzlon, Waaree, IEX, Tata Power, CESC: Target prices, top 5 stock picks - Business Today</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>For CESC investors, renewable energy should yield dual benefits of stock rerating and growth - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>CESC Limited Earnings Missed Analyst Estimates: Here's What Analysts Are Forecasting Now - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>CESC Ltd soars 1.23% - business-standard.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>3</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>BPL.NS</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>BPL</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>50.90000152587891</v>
+      </c>
+      <c r="F204" t="n">
+        <v>50.91999816894531</v>
+      </c>
+      <c r="G204" t="n">
+        <v>49.41999816894531</v>
+      </c>
+      <c r="H204" t="n">
+        <v>49.63000106811523</v>
+      </c>
+      <c r="I204" t="n">
+        <v>50.33000183105469</v>
+      </c>
+      <c r="J204" t="n">
+        <v>49.63000106811523</v>
+      </c>
+      <c r="K204" t="n">
+        <v>23151</v>
+      </c>
+      <c r="L204" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>This consumer electronics firm shares hit 20% upper circuit after NCLT move; what investors need to know - Upstox</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Eli Lilly to Boost Neuroscience Pipeline With AtaiBeckley Buyout - TradingView</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>BPL Share Price Forecast: 3 Year Outlook to 2030 - Univest</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>AtaiBeckley Stock Outlook Depends on Key Pipeline Catalysts in 2026 - TradingView</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>BPL Limited (BPL.NS) Gains 3.31% as Price Approaches Key Resistance at ₹59.98 - ETF Outflow Streak - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>4</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>IPCALAB.NS</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>1922</v>
+      </c>
+      <c r="F205" t="n">
+        <v>1928.400024414062</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1882.099975585938</v>
+      </c>
+      <c r="H205" t="n">
+        <v>1883.800048828125</v>
+      </c>
+      <c r="I205" t="n">
+        <v>1903.699951171875</v>
+      </c>
+      <c r="J205" t="n">
+        <v>1883.800048828125</v>
+      </c>
+      <c r="K205" t="n">
+        <v>89876</v>
+      </c>
+      <c r="L205" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories Ltd. Share Price Fall: Price Action View - Univest</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories shares gain 5.35% to Rs 1,827 - TradingView</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories Ltd. Stock News: Share Price Up 4.76% - Univest</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories shares fall over 2%; strong financial performance reported - TradingView</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>Ipca Laboratories shares gain 5.35% to Rs 1,827 - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>5</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>FINCABLES.NS</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>FINCABLES</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>1313.699951171875</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1331</v>
+      </c>
+      <c r="G206" t="n">
+        <v>1301.449951171875</v>
+      </c>
+      <c r="H206" t="n">
+        <v>1301.75</v>
+      </c>
+      <c r="I206" t="n">
+        <v>1313.699951171875</v>
+      </c>
+      <c r="J206" t="n">
+        <v>1301.75</v>
+      </c>
+      <c r="K206" t="n">
+        <v>283491</v>
+      </c>
+      <c r="L206" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>FINCABLES Forecast — Price Target — Prediction for 2027 - TradingView</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>Finolex Cables Declines Over 3.5%, Finds Support Near ₹995.6 - Donchian Channel - Vinanet</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Finolex Cables Limited (NSE:FINCABLES) Stock's Been Sliding But Fundamentals Look Decent: Will The Market Correct The Share Price In The Future? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Finolex Cables (FINCABLES.NS) Declines 2.13% as Stock Approaches Key Support Zone - Advance Decline Line - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>Solid Earnings May Not Tell The Whole Story For Finolex Cables (NSE:FINCABLES) - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>6</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>GNFC.NS</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>GNFC</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>603</v>
+      </c>
+      <c r="F207" t="n">
+        <v>606.25</v>
+      </c>
+      <c r="G207" t="n">
+        <v>593.2999877929688</v>
+      </c>
+      <c r="H207" t="n">
+        <v>597.4500122070312</v>
+      </c>
+      <c r="I207" t="n">
+        <v>602.2999877929688</v>
+      </c>
+      <c r="J207" t="n">
+        <v>597.4500122070312</v>
+      </c>
+      <c r="K207" t="n">
+        <v>242386</v>
+      </c>
+      <c r="L207" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>GNFC Share Price Today: 5.56% Gain, Price Action Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Top stock picks: MCX, L&amp;T Finance among Mitessh Thakkar's buys; JSW Energy, Marico get sell calls - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Top stock picks: MCX, L&amp;T Finance among Mitessh Thakkar's buys; JSW Energy, Marico get sell calls - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>GNFC Standalone June 2026 Net Sales at Rs 2,238.00 crore, up 39.79% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>GNFC transfers unclaimed equity shares to IEPF account - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>7</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>ASIANPAINT.NS</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>2635.10009765625</v>
+      </c>
+      <c r="F208" t="n">
+        <v>2641.800048828125</v>
+      </c>
+      <c r="G208" t="n">
+        <v>2607</v>
+      </c>
+      <c r="H208" t="n">
+        <v>2614.300048828125</v>
+      </c>
+      <c r="I208" t="n">
+        <v>2630.800048828125</v>
+      </c>
+      <c r="J208" t="n">
+        <v>2614.300048828125</v>
+      </c>
+      <c r="K208" t="n">
+        <v>191499</v>
+      </c>
+      <c r="L208" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>ASIANPAINT Forecast — Price Target — Prediction for 2027 - TradingView</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>ASIANPAINT Q2 FY2026 Earnings: Steady Revenue Growth of 5.1% Supports Stable Bottom Line - Earnings Revision Downgrade - Vinanet</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Investing in Asian Paints (NSE:ASIANPAINT) a year ago would have delivered you a 21% gain - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Asian Paints (ASIANPAINT) Sees Mild Dip; Support Level at ₹2,598 in Sight - Day Trade Opportunities - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>While institutions own 30% of Asian Paints Limited (NSE:ASIANPAINT), private companies are its largest shareholders with 40% ownership - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>8</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>IFCI.NS</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>IFCI</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>82</v>
+      </c>
+      <c r="F209" t="n">
+        <v>82.52999877929688</v>
+      </c>
+      <c r="G209" t="n">
+        <v>80.37000274658203</v>
+      </c>
+      <c r="H209" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="I209" t="n">
+        <v>81.68000030517578</v>
+      </c>
+      <c r="J209" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="K209" t="n">
+        <v>13197842</v>
+      </c>
+      <c r="L209" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>Stock to buy today: IFCI (₹81.40) – BUY - BusinessLine</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>Stock to buy today: IFCI (₹81.40) – BUY - BusinessLine</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>IFCI Share Price Rises 3.19% Today: Price Action Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>IFCI Standalone June 2026 Net Sales at Rs 102.64 crore, down 34% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>IFCI Q1 Results: Revenue declines, profit improves sequentially to ₹60 crore - livemint.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>9</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>GFLLIMITED.NS</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>GFLLIMITED</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>57.95000076293945</v>
+      </c>
+      <c r="F210" t="n">
+        <v>57.95000076293945</v>
+      </c>
+      <c r="G210" t="n">
+        <v>55</v>
+      </c>
+      <c r="H210" t="n">
+        <v>56.54999923706055</v>
+      </c>
+      <c r="I210" t="n">
+        <v>56.7599983215332</v>
+      </c>
+      <c r="J210" t="n">
+        <v>56.54999923706055</v>
+      </c>
+      <c r="K210" t="n">
+        <v>157949</v>
+      </c>
+      <c r="L210" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>GFL Limited Gains Slightly as Stock Hovers Near Mid-Range Levels - Wide Range Bar - Vinanet</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>GFL Limited Gains Slightly as Stock Hovers Near Mid-Range Levels - Wide Range Bar - Vinanet</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>GFL Limited Sees Modest Gain as Stock Holds Key Support Levels - ETF Flow - Vinanet</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>GFL Limited Stock Dips 1.19%: Support and Resistance Levels in Focus - TRIN Signal - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>GFL Limited (GFLLIMITED) Declines 1.54%; Support at ₹43.08 in Focus - Counter Trend Trade - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>10</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>HEG.NS</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>HEG</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>710</v>
+      </c>
+      <c r="F211" t="n">
+        <v>718.6500244140625</v>
+      </c>
+      <c r="G211" t="n">
+        <v>696.0999755859375</v>
+      </c>
+      <c r="H211" t="n">
+        <v>705.9000244140625</v>
+      </c>
+      <c r="I211" t="n">
+        <v>708.0499877929688</v>
+      </c>
+      <c r="J211" t="n">
+        <v>705.9000244140625</v>
+      </c>
+      <c r="K211" t="n">
+        <v>730425</v>
+      </c>
+      <c r="L211" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>HEG gets NCLT nod for demerger; shareholders to receive 1:1 shares in HEG Graphite - CNBC TV18 - LinkedIn</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>HEG receives NCLT approval for demerger scheme; shareholders to get 1:1 shares in HEG Graphite - livemint.com</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>HEG Gets NCLT Approval For Demerger Plan In 1:1 Share Ratio - Sahi</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>HEG receives NCLT approval for demerger scheme; shareholders to get 1:1 shares in HEG Graphite - livemint.com</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-19 — cnbctv:02f6ca213094b:0 - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>11</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>WEIZMANIND.NS</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>WEIZMANIND</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>76.45999908447266</v>
+      </c>
+      <c r="F212" t="n">
+        <v>76.47000122070312</v>
+      </c>
+      <c r="G212" t="n">
+        <v>74.09999847412109</v>
+      </c>
+      <c r="H212" t="n">
+        <v>75.66999816894531</v>
+      </c>
+      <c r="I212" t="n">
+        <v>75.90000152587891</v>
+      </c>
+      <c r="J212" t="n">
+        <v>75.66999816894531</v>
+      </c>
+      <c r="K212" t="n">
+        <v>195</v>
+      </c>
+      <c r="L212" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>Weizmann Limited (WEIZMANIND.NS) Faces Mild Selling Pressure as Price Holds Above Key Support - Volume Breadth - Vinanet</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Here's What We Like About Weizmann's (NSE:WEIZMANIND) Upcoming Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Here's What We Like About Weizmann's (NSE:WEIZMANIND) Upcoming Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Weizmann Limited Holds Near Support Amid Modest Gains – WEIZMANIND.NS Analysis - Fundamental Weighted - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>Weizmann Limited (WEIZMANIND.NS): Mild Uptick Near ₹84.5 as Stock Holds Support Zone - Leading Diagonal - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>12</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>CUMMINSIND.NS</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>5250</v>
+      </c>
+      <c r="F213" t="n">
+        <v>5252.5</v>
+      </c>
+      <c r="G213" t="n">
+        <v>5192.5</v>
+      </c>
+      <c r="H213" t="n">
+        <v>5211</v>
+      </c>
+      <c r="I213" t="n">
+        <v>5220</v>
+      </c>
+      <c r="J213" t="n">
+        <v>5211</v>
+      </c>
+      <c r="K213" t="n">
+        <v>122662</v>
+      </c>
+      <c r="L213" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>The Cummins India Limited (NSE:CUMMINSIND) First-Quarter Results Are Out And Analysts Have Published New Forecasts - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>The Cummins India Limited (NSE:CUMMINSIND) First-Quarter Results Are Out And Analysts Have Published New Forecasts - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>13</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>HLVLTD.NS</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>HLVLTD</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>6.699999809265137</v>
+      </c>
+      <c r="F214" t="n">
+        <v>6.699999809265137</v>
+      </c>
+      <c r="G214" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H214" t="n">
+        <v>6.619999885559082</v>
+      </c>
+      <c r="I214" t="n">
+        <v>6.630000114440918</v>
+      </c>
+      <c r="J214" t="n">
+        <v>6.619999885559082</v>
+      </c>
+      <c r="K214" t="n">
+        <v>129901</v>
+      </c>
+      <c r="L214" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>HLV Limited's (NSE:HLVLTD) Shares May Have Run Too Fast Too Soon - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>HLV Limited: Navigating Resistance Near ₹8.05 Amid Modest Decline - Ratio Spread Trade - Vinanet</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>HLV Limited (HLVLTD.NS) Gains Modestly as Stock Holds Above Key Support Level - Extension Target - Vinanet</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>HLV (NSE:HLVLTD) Seems To Use Debt Quite Sensibly - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>HLV Limited (HLVLTD.NS) Gains 2.43% – Approaching Key Resistance at ₹8.42 - Monthly Profile - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>14</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>SBIN.NS</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>1052.900024414062</v>
+      </c>
+      <c r="F215" t="n">
+        <v>1052.900024414062</v>
+      </c>
+      <c r="G215" t="n">
+        <v>1045.699951171875</v>
+      </c>
+      <c r="H215" t="n">
+        <v>1047</v>
+      </c>
+      <c r="I215" t="n">
+        <v>1048.599975585938</v>
+      </c>
+      <c r="J215" t="n">
+        <v>1047</v>
+      </c>
+      <c r="K215" t="n">
+        <v>3080220</v>
+      </c>
+      <c r="L215" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>SBI Share Price - Live NSE: SBIN Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>State Bank of India Stock Update: Shares Dip Amid Recruitment Woes, RBI Policy Shift - latestly.com</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>SBIN Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>SBIN Share Price Today - State Bank Of India Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>State Bank of India Stock Update: Share Price Dips on Recruitment Concerns - latestly.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>15</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>SUNPHARMA.NS</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>1905</v>
+      </c>
+      <c r="F216" t="n">
+        <v>1911.599975585938</v>
+      </c>
+      <c r="G216" t="n">
+        <v>1890.300048828125</v>
+      </c>
+      <c r="H216" t="n">
+        <v>1898</v>
+      </c>
+      <c r="I216" t="n">
+        <v>1900</v>
+      </c>
+      <c r="J216" t="n">
+        <v>1898</v>
+      </c>
+      <c r="K216" t="n">
+        <v>501385</v>
+      </c>
+      <c r="L216" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>SUNPHARMA Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>SUNPHARMA Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Why is Sun Pharmaceutical Industries stock falling today? - Investing.com</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Results: Sun Pharmaceutical Industries Limited Exceeded Expectations And The Consensus Has Updated Its Estimates - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>16</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>HIMATSEIDE.NS</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>HIMATSEIDE</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>70.09999847412109</v>
+      </c>
+      <c r="F217" t="n">
+        <v>71.69999694824219</v>
+      </c>
+      <c r="G217" t="n">
+        <v>69.05999755859375</v>
+      </c>
+      <c r="H217" t="n">
+        <v>71.47000122070312</v>
+      </c>
+      <c r="I217" t="n">
+        <v/>
+      </c>
+      <c r="J217" t="n">
+        <v>71.47000122070312</v>
+      </c>
+      <c r="K217" t="n">
+        <v>444716</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Himatsingka Seide Limited. Actuals &amp; Estimates (NSE:HIMATSEIDE) - TradingView</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>HIMATSEIDE Q2 2026 Earnings: Revenue Declines 9.5% YoY; EPS at ₹4.93 Amid Challenging Textile Demand - Vinanet</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Himatsingka Seide Share Price Target 2026: Rs 89 Analyst Forecast - Univest</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Himatsingka Seide Falls 3% – Stock Nears Key Support at ₹73.50 Amid Weaker Textile Sentiment - RVOL Spike - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>Here's What We Like About Himatsingka Seide's (NSE:HIMATSEIDE) Upcoming Dividend - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>17</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>WILLAMAGOR.NS</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>WILLAMAGOR</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>25.10000038146973</v>
+      </c>
+      <c r="F218" t="n">
+        <v>25.71999931335449</v>
+      </c>
+      <c r="G218" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H218" t="n">
+        <v>25.42000007629395</v>
+      </c>
+      <c r="I218" t="n">
+        <v/>
+      </c>
+      <c r="J218" t="n">
+        <v>25.42000007629395</v>
+      </c>
+      <c r="K218" t="n">
+        <v>1647</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Williamson Magor (WILLAMAGOR.NS) Gains 3.58% – Support and Resistance Levels in Focus - Trade Entry Signals - Vinanet</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>Williamson Magor Q2 2026 Earnings: Revenue Plunges 46% YoY as Investment Holding Company Posts Net Loss - Return On Equity - Vinanet</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Williamson Magor Holds Near Support; Resistance Test Ahead for WILLAMAGOR.NS - Scalping Stock Signals - Vinanet</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>WILLAMAGOR Q2 2025 Earnings: Revenue Growth of 18.1% Driven by Higher Other Income, but Net Loss Deepens to ₹165.56 Per Share - Analyst Coverage Count - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>WILLAMAGOR Stock Price and Chart — NSE:WILLAMAGOR - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>18</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>VINDHYATEL.NS</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>VINDHYATEL</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>2459</v>
+      </c>
+      <c r="F219" t="n">
+        <v>2498</v>
+      </c>
+      <c r="G219" t="n">
+        <v>2421.89990234375</v>
+      </c>
+      <c r="H219" t="n">
+        <v>2439.199951171875</v>
+      </c>
+      <c r="I219" t="n">
+        <v/>
+      </c>
+      <c r="J219" t="n">
+        <v>2439.199951171875</v>
+      </c>
+      <c r="K219" t="n">
+        <v>13066</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>Vindhya Telelinks Limited's (NSE:VINDHYATEL) largest shareholders are individual investors who were rewarded as market cap surged ₹2.6b last week - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>VINDHYATEL Mar 2026 Earnings: EPS of ₹16.75 on Revenue of ₹1,005.0 Crore; Stock Declines 1.5% - Estimate Dispersion - Vinanet</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>VINDHYATEL Stock Price and Chart — NSE:VINDHYATEL - TradingView</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Vindhya Telelinks (VINDHYATEL.NS) Retreats from Resistance, Tests Key Support Levels - MAMA Signal - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>Vindhya Telelinks (VINDHYATEL.NS): Modest Decline as Stock Consolidates Near Key Support Levels - Flat Correction - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>19</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>ESCORTS.NS</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>ESCORTS</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>3059.60009765625</v>
+      </c>
+      <c r="F220" t="n">
+        <v>3099</v>
+      </c>
+      <c r="G220" t="n">
+        <v>3059</v>
+      </c>
+      <c r="H220" t="n">
+        <v>3087.699951171875</v>
+      </c>
+      <c r="I220" t="n">
+        <v/>
+      </c>
+      <c r="J220" t="n">
+        <v>3087.699951171875</v>
+      </c>
+      <c r="K220" t="n">
+        <v>35023</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>Escorts Kubota Shares Fall 2.13% to Rs 3,067.00 Amid Bullish Sentiment - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>Escorts Kubota breaks ground on ₹2,000 crore greenfield plant in Uttar Pradesh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Escorts Kubota breaks ground on ₹2,000 crore greenfield plant in Uttar Pradesh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Escorts Kubota Q1FY27: Revenue jumps 28% Y-o-Y, profit at ₹386 crore - business-standard.com</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>Escorts Kubota schedules analyst meet with Valuequest on Aug 21 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:04:21</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>20</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>JAYSREETEA.NS</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>JAYSREETEA</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>94.52999877929688</v>
+      </c>
+      <c r="F221" t="n">
+        <v>99.40000152587891</v>
+      </c>
+      <c r="G221" t="n">
+        <v>94</v>
+      </c>
+      <c r="H221" t="n">
+        <v>99.19999694824219</v>
+      </c>
+      <c r="I221" t="n">
+        <v/>
+      </c>
+      <c r="J221" t="n">
+        <v>99.19999694824219</v>
+      </c>
+      <c r="K221" t="n">
+        <v>173240</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>Jay Shree Tea &amp; Industries Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>Jay Shree Tea &amp; Industries Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q221"/>
+  <dimension ref="A1:Q241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12331,8 +12331,6 @@
           <t>Abakkus, Carnelian, Motilal Oswal acquire additional 2.9% Anawil Wire shares; promoter offloads Rs 171 crore worth Capillary Tech shares - TradingView</t>
         </is>
       </c>
-      <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12456,9 +12454,6 @@
           <t>BOMDYEING Standalone June 2026 Net Sales at Rs 410.80 crore, up 8.72% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
-      <c r="O210" t="inlineStr"/>
-      <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12651,9 +12646,6 @@
           <t>ASHOKLEY Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
         </is>
       </c>
-      <c r="O213" t="inlineStr"/>
-      <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12708,9 +12700,6 @@
           <t>Surya Roshni Sets September AGM to Approve Dividend and ₹1,000 Crore Working Capital Security - TipRanks</t>
         </is>
       </c>
-      <c r="O214" t="inlineStr"/>
-      <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12765,9 +12754,6 @@
           <t>CG Power and Industrial Solutions Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
         </is>
       </c>
-      <c r="O215" t="inlineStr"/>
-      <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -12832,7 +12818,6 @@
           <t>The Federal Bank Ltd. (FEDERALBNK) Share Price Hits 52-Week High - Univest</t>
         </is>
       </c>
-      <c r="Q216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -12887,9 +12872,6 @@
           <t>Birla Corporation Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
         </is>
       </c>
-      <c r="O217" t="inlineStr"/>
-      <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -13013,9 +12995,6 @@
           <t>HINDUNILVR Outlook for the Week (August 17, 2026 – August 21, 2026) - Equitypandit</t>
         </is>
       </c>
-      <c r="O219" t="inlineStr"/>
-      <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13152,6 +13131,1330 @@
       <c r="Q221" t="inlineStr">
         <is>
           <t>With EPS Growth And More, Can Fin Homes (NSE:CANFINHOME) Makes An Interesting Case - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>KRONOX.NS</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Limited</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>155.0099945068359</v>
+      </c>
+      <c r="F222" t="n">
+        <v>178.6999969482422</v>
+      </c>
+      <c r="G222" t="n">
+        <v>155.0099945068359</v>
+      </c>
+      <c r="H222" t="n">
+        <v>176.0500030517578</v>
+      </c>
+      <c r="I222" t="n">
+        <v>155.1600036621094</v>
+      </c>
+      <c r="J222" t="n">
+        <v>176.0500030517578</v>
+      </c>
+      <c r="K222" t="n">
+        <v>2949367</v>
+      </c>
+      <c r="L222" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Share Price Rise With Peer Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Rs 246 Crore Acquisition: Indo Borax &amp; Chemicals to Acquire 64.26% Stake in Kronox Lab Sciences; Share Price Rises 7% - insights.dsij.in</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Momentum Stocks: Kronox Lab Sciences, Waterways Leisure, Genus Power rise up to % on sheer momentum - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Indo Borax acquires 64.26% stake in Kronox Lab Sciences for ₹246.12 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Q1 Results: Net profit up 60% YoY to ₹25.8 crore - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>2</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN.NS</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Limited</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>658.25</v>
+      </c>
+      <c r="F223" t="n">
+        <v>739.8499755859375</v>
+      </c>
+      <c r="G223" t="n">
+        <v>655.0499877929688</v>
+      </c>
+      <c r="H223" t="n">
+        <v>734</v>
+      </c>
+      <c r="I223" t="n">
+        <v>650.7999877929688</v>
+      </c>
+      <c r="J223" t="n">
+        <v>734</v>
+      </c>
+      <c r="K223" t="n">
+        <v>14806969</v>
+      </c>
+      <c r="L223" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd Share Price Target, Forecast for Long Term Equity. - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: Balrampur Chini Mills Q1 2026 stock falls as outlook stays firm - Investing.com</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price Hits One-Year High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>3</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>DWARKESH.NS</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar Industries Limited</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>48.77000045776367</v>
+      </c>
+      <c r="F224" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="G224" t="n">
+        <v>48.70000076293945</v>
+      </c>
+      <c r="H224" t="n">
+        <v>54.34000015258789</v>
+      </c>
+      <c r="I224" t="n">
+        <v>48.27999877929688</v>
+      </c>
+      <c r="J224" t="n">
+        <v>54.34000015258789</v>
+      </c>
+      <c r="K224" t="n">
+        <v>25736600</v>
+      </c>
+      <c r="L224" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar surges more than 6% on buyback plans, fixes record date on March 20 - Upstox</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Is It Worth Considering Dwarikesh Sugar Industries Limited (NSE:DWARKESH) For Its Upcoming Dividend? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar Industries Ltd. Share Price: Major Drop - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>4</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>KOHINOOR.NS</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Limited</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>32.09999847412109</v>
+      </c>
+      <c r="F225" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G225" t="n">
+        <v>30.95000076293945</v>
+      </c>
+      <c r="H225" t="n">
+        <v>35.04999923706055</v>
+      </c>
+      <c r="I225" t="n">
+        <v>31.27000045776367</v>
+      </c>
+      <c r="J225" t="n">
+        <v>35.04999923706055</v>
+      </c>
+      <c r="K225" t="n">
+        <v>1400201</v>
+      </c>
+      <c r="L225" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd is Rated Strong Sell - marketsmojo.com</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods to Review Quarterly Results and Mull Fundraising at August Board Meeting - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>5</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>KWIL.NS</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Kwality Wall's (India) Limited</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>38</v>
+      </c>
+      <c r="F226" t="n">
+        <v>42.2400016784668</v>
+      </c>
+      <c r="G226" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="H226" t="n">
+        <v>42.11000061035156</v>
+      </c>
+      <c r="I226" t="n">
+        <v>37.70999908447266</v>
+      </c>
+      <c r="J226" t="n">
+        <v>42.11000061035156</v>
+      </c>
+      <c r="K226" t="n">
+        <v>39174599</v>
+      </c>
+      <c r="L226" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>TMICC completes KWIL stake buy in HUL’s ice-cream demerger - Law.asia</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>Kwality Wall's (KWIL.NS) Gains 3.45%: Ice Cream Major Tests ₹34.66 Resistance - Supply Zone - Vinanet</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>HUL Demerger: Ice-Cream Business Spun off Into Kwality Wall’s; Record Date Set for 5 December - Groww</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>HUL completes acquisition of Zywie ventures; KWIL shares to be traded from Feb. 16 - thehindu.com</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>Kwality Wall''s Stock Debuts After HUL Demerger - Rediff MoneyWiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>6</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>KOTARISUG.NS</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Kothari Sugars And Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>27.8799991607666</v>
+      </c>
+      <c r="F227" t="n">
+        <v>31.39999961853027</v>
+      </c>
+      <c r="G227" t="n">
+        <v>27.68000030517578</v>
+      </c>
+      <c r="H227" t="n">
+        <v>30.20000076293945</v>
+      </c>
+      <c r="I227" t="n">
+        <v>27.21999931335449</v>
+      </c>
+      <c r="J227" t="n">
+        <v>30.20000076293945</v>
+      </c>
+      <c r="K227" t="n">
+        <v>817791</v>
+      </c>
+      <c r="L227" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>Turkcell (TKC) Holds Above Support After Modest Gain as Resistance at $5.73 Looms - CTA Positioning - Vinanet</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>Turkcell (TKC) Holds Above Support After Modest Gain as Resistance at $5.73 Looms - CTA Positioning - Vinanet</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Are Wall Street Analysts Predicting PepsiCo Stock Will Climb or Sink? - Earnings Call Q&amp;A - Vinanet</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>7</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>SUVEN.NS</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Suven Life Sciences Limited</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>335</v>
+      </c>
+      <c r="F228" t="n">
+        <v>367.8500061035156</v>
+      </c>
+      <c r="G228" t="n">
+        <v>335</v>
+      </c>
+      <c r="H228" t="n">
+        <v>367.3999938964844</v>
+      </c>
+      <c r="I228" t="n">
+        <v>332.5499877929688</v>
+      </c>
+      <c r="J228" t="n">
+        <v>367.3999938964844</v>
+      </c>
+      <c r="K228" t="n">
+        <v>1501088</v>
+      </c>
+      <c r="L228" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>Suven Pharmaceuticals Ltd. Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>Suven Pharmaceuticals Ltd. Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>Suven Life Sciences Limited Rights 2022-10.11.22 For Shares Revenue Breakdown – BSE:SUVEN_RE - TradingView</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Suven Life Sciences Shares Decline Over 5% As Q1 Net Loss Widens To Rs 128 Crore - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>Suven Life Sciences seeks AGM approval for related party transaction and fund reallocation - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>8</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>MAWANASUG.NS</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Mawana Sugars Limited</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>130.9900054931641</v>
+      </c>
+      <c r="F229" t="n">
+        <v>143.1499938964844</v>
+      </c>
+      <c r="G229" t="n">
+        <v>129.3000030517578</v>
+      </c>
+      <c r="H229" t="n">
+        <v>141.7100067138672</v>
+      </c>
+      <c r="I229" t="n">
+        <v>128.7200012207031</v>
+      </c>
+      <c r="J229" t="n">
+        <v>141.7100067138672</v>
+      </c>
+      <c r="K229" t="n">
+        <v>1294171</v>
+      </c>
+      <c r="L229" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>Mawana Sugars Ltd. Share Price Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Mawana Sugars Ltd. Share Price Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>9</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>CORDELIA.NS</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Waterways Leisure Tourism Limited</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>820.5499877929688</v>
+      </c>
+      <c r="F230" t="n">
+        <v>907.75</v>
+      </c>
+      <c r="G230" t="n">
+        <v>820.5499877929688</v>
+      </c>
+      <c r="H230" t="n">
+        <v>907.75</v>
+      </c>
+      <c r="I230" t="n">
+        <v>825.25</v>
+      </c>
+      <c r="J230" t="n">
+        <v>907.75</v>
+      </c>
+      <c r="K230" t="n">
+        <v>686273</v>
+      </c>
+      <c r="L230" t="n">
+        <v>10</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>Waterways Leisure Tourism Limited Share Price Today,, CORDELIA Share Price NSE, BSE - Business Today</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Waterways Leisure Tourism Limited Share Price Today,, CORDELIA Share Price NSE, BSE - Business Today</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>Share Market News: Waterways Leisure Tourism's profit increases 28 percent in first quarter post listing, rev - India.com</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Josh Da Costa Shares Another Facet of New Wave Graveyard with the Hypnagogic (and Possibly Psychic) “Cordelia” - floodmagazine.com</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>10</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>NETWORK18.NS</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Network18 Media &amp; Investments Limited</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>28.23999977111816</v>
+      </c>
+      <c r="F231" t="n">
+        <v>31.21999931335449</v>
+      </c>
+      <c r="G231" t="n">
+        <v>28.04999923706055</v>
+      </c>
+      <c r="H231" t="n">
+        <v>30.86000061035156</v>
+      </c>
+      <c r="I231" t="n">
+        <v>28.06999969482422</v>
+      </c>
+      <c r="J231" t="n">
+        <v>30.86000061035156</v>
+      </c>
+      <c r="K231" t="n">
+        <v>24924047</v>
+      </c>
+      <c r="L231" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>Network18 Media &amp; Investments schedules 31st AGM for September 16 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Network18 Media &amp; Investments schedules 31st AGM for September 16 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Network18 sets Oct 1 hearing for News18 Marathi amalgamation - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>11</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>RANASUG.NS</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Rana Sugars Limited</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>13.85999965667725</v>
+      </c>
+      <c r="F232" t="n">
+        <v>15.17000007629395</v>
+      </c>
+      <c r="G232" t="n">
+        <v>13.85999965667725</v>
+      </c>
+      <c r="H232" t="n">
+        <v>15.02999973297119</v>
+      </c>
+      <c r="I232" t="n">
+        <v>13.76000022888184</v>
+      </c>
+      <c r="J232" t="n">
+        <v>15.02999973297119</v>
+      </c>
+      <c r="K232" t="n">
+        <v>2286027</v>
+      </c>
+      <c r="L232" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>Two Harbors Investment Corp (TWO) Edges Lower to $12.09: Key Support and Resistance in Focus - BPI Bear Correction - Vinanet</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Two Harbors Investment Corp (TWO) Edges Lower to $12.09: Key Support and Resistance in Focus - BPI Bear Correction - Vinanet</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>12</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>SIGACHI.NS</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Sigachi Industries Limited</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>29</v>
+      </c>
+      <c r="F233" t="n">
+        <v>31.81999969482422</v>
+      </c>
+      <c r="G233" t="n">
+        <v>29</v>
+      </c>
+      <c r="H233" t="n">
+        <v>31.51000022888184</v>
+      </c>
+      <c r="I233" t="n">
+        <v>28.8799991607666</v>
+      </c>
+      <c r="J233" t="n">
+        <v>31.51000022888184</v>
+      </c>
+      <c r="K233" t="n">
+        <v>6444144</v>
+      </c>
+      <c r="L233" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>Sigachi Industries Share Price Today Up 8.33%: Stock View - Univest</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Sigachi Industries Share Price Today Up 8.33%: Stock View - Univest</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Sigachi Industries board to consider preferential issue on August 22 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Sigachi Ind Q1 Results FY27: PAT Rs 8 Cr, Revenue Rs 121 crore - Univest</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>Sigachi Industries postpones Q1FY27 earnings call due to unavoidable circumstances - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>13</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>BAJAJHIND.NS</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>20.73999977111816</v>
+      </c>
+      <c r="F234" t="n">
+        <v>22.6200008392334</v>
+      </c>
+      <c r="G234" t="n">
+        <v>20.59000015258789</v>
+      </c>
+      <c r="H234" t="n">
+        <v>22.19000053405762</v>
+      </c>
+      <c r="I234" t="n">
+        <v>20.3799991607666</v>
+      </c>
+      <c r="J234" t="n">
+        <v>22.19000053405762</v>
+      </c>
+      <c r="K234" t="n">
+        <v>145436948</v>
+      </c>
+      <c r="L234" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Publishes Q1 FY27 Results Extracts and Sets Board Meeting - TipRanks</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>14</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>PVP.NS</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>PVP Ventures Limited</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>39.97000122070312</v>
+      </c>
+      <c r="F235" t="n">
+        <v>42.70000076293945</v>
+      </c>
+      <c r="G235" t="n">
+        <v>39.45999908447266</v>
+      </c>
+      <c r="H235" t="n">
+        <v>42.54999923706055</v>
+      </c>
+      <c r="I235" t="n">
+        <v>39.13000106811523</v>
+      </c>
+      <c r="J235" t="n">
+        <v>42.54999923706055</v>
+      </c>
+      <c r="K235" t="n">
+        <v>2238046</v>
+      </c>
+      <c r="L235" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd. Share Price Gain: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>Broad-Based Technical Strength Lifts PVP Ventures Ltd to 52-Week High of Rs 39.89 - marketsmojo.com</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - Univest</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>PVP Ventures Share Price Forecast: 3 Year Outlook to 2030 - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>15</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>RAJSREESUG.NS</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Rajshree Sugars &amp; Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>37.0099983215332</v>
+      </c>
+      <c r="F236" t="n">
+        <v>40.79000091552734</v>
+      </c>
+      <c r="G236" t="n">
+        <v>37</v>
+      </c>
+      <c r="H236" t="n">
+        <v>40.09999847412109</v>
+      </c>
+      <c r="I236" t="n">
+        <v>36.90000152587891</v>
+      </c>
+      <c r="J236" t="n">
+        <v>40.09999847412109</v>
+      </c>
+      <c r="K236" t="n">
+        <v>509524</v>
+      </c>
+      <c r="L236" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>Rajshree Sugars Gains 3%: Sugar Sector Momentum and Key Levels for RAJSREESUG.NS - Stock Analysis - Vinanet</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>Rajshree Sugars &amp; Chemicals: Mild Decline Amid Consolidation near Support - Momentum Surge Alerts - Vinanet</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>RAJSREESUG Share Price Today - Rajshree Sugars &amp; Chemicals Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Rajshree Sugars &amp; Chemicals Ltd: Stock Climbs 1.67%, Testing Key Resistance at ₹35.72 - Mean Reversion Trade - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>Rajshree Sugars &amp; Chemicals: Mild Decline Amid Consolidation near Support - Momentum Surge Alerts - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>16</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>KAYA.NS</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Kaya Limited</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>339.9500122070312</v>
+      </c>
+      <c r="F237" t="n">
+        <v>370</v>
+      </c>
+      <c r="G237" t="n">
+        <v>336.5499877929688</v>
+      </c>
+      <c r="H237" t="n">
+        <v>365.25</v>
+      </c>
+      <c r="I237" t="n">
+        <v>338.4500122070312</v>
+      </c>
+      <c r="J237" t="n">
+        <v>365.25</v>
+      </c>
+      <c r="K237" t="n">
+        <v>119931</v>
+      </c>
+      <c r="L237" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>Scholastic director Kaya Henderson sells $130,812 in stock - Investing.com</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>Wladimir Klitschko vows to protect Hayden Panettiere’s memory for daughter Kaya as WWE star Jacob Fatu sh - The Times of India</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>Wladimir Klitschko vows to protect Hayden Panettiere’s memory for daughter Kaya as WWE star Jacob Fatu sh - The Times of India</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Kaya To Issue 1.82 Million Equity Shares At 274.10 Rupees Per Share For Aggregate Cash Consideration Of Approx 500 Million Rupees - TradingView</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>Kaya Standalone June 2026 Net Sales at Rs 60.14 crore, up 13.91% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>17</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>DHAMPURSUG.NS</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Limited</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>179.6999969482422</v>
+      </c>
+      <c r="F238" t="n">
+        <v>190.75</v>
+      </c>
+      <c r="G238" t="n">
+        <v>178.9700012207031</v>
+      </c>
+      <c r="H238" t="n">
+        <v>189.2100067138672</v>
+      </c>
+      <c r="I238" t="n">
+        <v>176.1799926757812</v>
+      </c>
+      <c r="J238" t="n">
+        <v>189.2100067138672</v>
+      </c>
+      <c r="K238" t="n">
+        <v>3891705</v>
+      </c>
+      <c r="L238" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Limited Submits Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Limited Submits Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar to Consider Quarterly Results Tomorrow; Stock Declines 2.75% in Previous Session - TradingView</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills sets book closure dates for 91st AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills settles ₹100 crore commercial paper - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>18</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>NIBE.NS</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>NIBE Limited</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>1435</v>
+      </c>
+      <c r="F239" t="n">
+        <v>1542.800048828125</v>
+      </c>
+      <c r="G239" t="n">
+        <v>1421</v>
+      </c>
+      <c r="H239" t="n">
+        <v>1513</v>
+      </c>
+      <c r="I239" t="n">
+        <v>1411.099975585938</v>
+      </c>
+      <c r="J239" t="n">
+        <v>1513</v>
+      </c>
+      <c r="K239" t="n">
+        <v>254734</v>
+      </c>
+      <c r="L239" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>NIBE Q1 FY27 Results: Revenue fell to Rs 63 Cr, Net Loss -1300% - Univest</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>Di: This is what it will take for the Nibe stock to gain momentum - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>Di: This is what it will take for the Nibe stock to gain momentum - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Nibe Industrier stock holds steady as leadership change adds to long term growth story - Ad-hoc-news.de</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>Nibe Industrier stock holds firm after Q2 sales rose - Ad-hoc-news.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>19</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>KIRIINDUS.NS</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Kiri Industries Limited</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>435</v>
+      </c>
+      <c r="F240" t="n">
+        <v>479.9500122070312</v>
+      </c>
+      <c r="G240" t="n">
+        <v>434</v>
+      </c>
+      <c r="H240" t="n">
+        <v>462</v>
+      </c>
+      <c r="I240" t="n">
+        <v>431.2999877929688</v>
+      </c>
+      <c r="J240" t="n">
+        <v>462</v>
+      </c>
+      <c r="K240" t="n">
+        <v>5177321</v>
+      </c>
+      <c r="L240" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>Kiri Industries Limited (NSE:KIRIINDUS) Stock Rockets 34% As Investors Are Less Pessimistic Than Expected - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>KIRIINDUS.NS Q2 2026 Earnings: Robust Profitability Amidst Modest Revenue Growth - Earnings Cycle Report - Vinanet</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>Kiri Industries (KIRIINDUS) Stock Consolidates Near Key Support Amid Modest Decline - Percent Above MA - Vinanet</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>KIRIDYES.BO interactive stock chart | Kiri Industries Limited stock - Yahoo Finance Australia</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>Shareholders Shouldn’t Be Too Comfortable With Kiri Industries' (NSE:KIRIINDUS) Strong Earnings - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>20</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>DALMIASUG.NS</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Dalmia Bharat Sugar and Industries Limited</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>475.8500061035156</v>
+      </c>
+      <c r="F241" t="n">
+        <v>517</v>
+      </c>
+      <c r="G241" t="n">
+        <v>469.2000122070312</v>
+      </c>
+      <c r="H241" t="n">
+        <v>508.5</v>
+      </c>
+      <c r="I241" t="n">
+        <v>475.5499877929688</v>
+      </c>
+      <c r="J241" t="n">
+        <v>508.5</v>
+      </c>
+      <c r="K241" t="n">
+        <v>1379021</v>
+      </c>
+      <c r="L241" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>Dalmia Bharat Sugar and Industries Limited (NSE:DALMIASUG) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹560 - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>Breakout stocks to buy or sell: Sumeet Bagadia recommends five shares to buy today - 20 August 2026 - TradingView</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>Dalmia Bharat Sugar And Industries Ltd. (DALMIASUG) Share Price Rises 14.03% Today - Univest</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>Dalmia Bharat Sugar Share Price Technicals and Market Cap - Univest</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>Breakout stocks to buy or sell: Sumeet Bagadia recommends five shares to buy today - 20 August 2026 - TradingView</t>
         </is>
       </c>
     </row>
@@ -13166,7 +14469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q221"/>
+  <dimension ref="A1:Q241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25077,9 +26380,6 @@
           <t>The Cummins India Limited (NSE:CUMMINSIND) First-Quarter Results Are Out And Analysts Have Published New Forecasts - simplywall.st</t>
         </is>
       </c>
-      <c r="O213" t="inlineStr"/>
-      <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -25282,7 +26582,6 @@
           <t>Results: Sun Pharmaceutical Industries Limited Exceeded Expectations And The Consensus Has Updated Its Estimates - simplywall.st</t>
         </is>
       </c>
-      <c r="Q216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -25315,9 +26614,6 @@
       <c r="H217" t="n">
         <v>71.47000122070312</v>
       </c>
-      <c r="I217" t="n">
-        <v/>
-      </c>
       <c r="J217" t="n">
         <v>71.47000122070312</v>
       </c>
@@ -25384,9 +26680,6 @@
       <c r="H218" t="n">
         <v>25.42000007629395</v>
       </c>
-      <c r="I218" t="n">
-        <v/>
-      </c>
       <c r="J218" t="n">
         <v>25.42000007629395</v>
       </c>
@@ -25453,9 +26746,6 @@
       <c r="H219" t="n">
         <v>2439.199951171875</v>
       </c>
-      <c r="I219" t="n">
-        <v/>
-      </c>
       <c r="J219" t="n">
         <v>2439.199951171875</v>
       </c>
@@ -25522,9 +26812,6 @@
       <c r="H220" t="n">
         <v>3087.699951171875</v>
       </c>
-      <c r="I220" t="n">
-        <v/>
-      </c>
       <c r="J220" t="n">
         <v>3087.699951171875</v>
       </c>
@@ -25591,9 +26878,6 @@
       <c r="H221" t="n">
         <v>99.19999694824219</v>
       </c>
-      <c r="I221" t="n">
-        <v/>
-      </c>
       <c r="J221" t="n">
         <v>99.19999694824219</v>
       </c>
@@ -25613,9 +26897,1346 @@
           <t>Jay Shree Tea &amp; Industries Share Price News and Analysis - Univest</t>
         </is>
       </c>
-      <c r="O221" t="inlineStr"/>
-      <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>INDOMIM.NS</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>INDO-MIM Limited</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>965</v>
+      </c>
+      <c r="F222" t="n">
+        <v>965</v>
+      </c>
+      <c r="G222" t="n">
+        <v>907.2999877929688</v>
+      </c>
+      <c r="H222" t="n">
+        <v>918.5</v>
+      </c>
+      <c r="I222" t="n">
+        <v>967.9500122070312</v>
+      </c>
+      <c r="J222" t="n">
+        <v>918.5</v>
+      </c>
+      <c r="K222" t="n">
+        <v>2577690</v>
+      </c>
+      <c r="L222" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>INDO-MIM LIMITED Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>INDO-MIM Board Clears Q1 FY27 Unaudited Results, Publishes in Newspapers - TipRanks</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>INDOMIM Share Price Today - INDO-MIM LIMITED Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>IndoMIM Share Price Today - Indo-MIM Ltd. Stock Price Live NSE/BSE - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>Indo-MIM IPO: GMP jumps as issue subscribed 72.34 times - livemint.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>2</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>SIEL.NS</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>44.54000091552734</v>
+      </c>
+      <c r="F223" t="n">
+        <v>44.54000091552734</v>
+      </c>
+      <c r="G223" t="n">
+        <v>40.29999923706055</v>
+      </c>
+      <c r="H223" t="n">
+        <v>40.29999923706055</v>
+      </c>
+      <c r="I223" t="n">
+        <v>42.41999816894531</v>
+      </c>
+      <c r="J223" t="n">
+        <v>40.29999923706055</v>
+      </c>
+      <c r="K223" t="n">
+        <v>8873</v>
+      </c>
+      <c r="L223" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>Diluted shares outstanding of Superior Industrial Enterprises Limited – NSE:SIEL - TradingView</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises standalone profit rises 21.8% in Q1FY27 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>3</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>UCAL.NS</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>UCAL LIMITED</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>147.8999938964844</v>
+      </c>
+      <c r="F224" t="n">
+        <v>147.8999938964844</v>
+      </c>
+      <c r="G224" t="n">
+        <v>138.8800048828125</v>
+      </c>
+      <c r="H224" t="n">
+        <v>140.0099945068359</v>
+      </c>
+      <c r="I224" t="n">
+        <v>146.1799926757812</v>
+      </c>
+      <c r="J224" t="n">
+        <v>140.0099945068359</v>
+      </c>
+      <c r="K224" t="n">
+        <v>26454</v>
+      </c>
+      <c r="L224" t="n">
+        <v>-4.22</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>UCAL Ltd. Share Price Near 52-Week High Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>UCAL Ltd. Share Price Near 52-Week High Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>UCAL Ltd. Share Price Today: 9.08% Rise, Valuation Check - Univest</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>UCAL Share Price Rises 10.34%: Technicals, Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>Ucal reports consolidated net profit of Rs 5.84 crore in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>4</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>KUANTUM.NS</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Kuantum Papers Limited</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="F225" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G225" t="n">
+        <v>74.20999908447266</v>
+      </c>
+      <c r="H225" t="n">
+        <v>75.37999725341797</v>
+      </c>
+      <c r="I225" t="n">
+        <v>78.69999694824219</v>
+      </c>
+      <c r="J225" t="n">
+        <v>75.37999725341797</v>
+      </c>
+      <c r="K225" t="n">
+        <v>237483</v>
+      </c>
+      <c r="L225" t="n">
+        <v>-4.22</v>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>Kuantum Papers Q1 Results: Earnings call scheduled for Aug 14 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>Mazagon Dock and 9 Other Stocks in Focus as They Turn Ex-Dividend Tomorrow - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Kuantum Papers proposes ₹2.50 dividend, sets August 27 AGM date - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Kuantum Papers declares ₹2.50 dividend for FY26, sets Aug 20 record date - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>Kuantum Papers reports 100% sustainable sourcing in FY26 BRSR filing - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>5</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>AHLADA.NS</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Ahlada Engineers Limited</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>40.81999969482422</v>
+      </c>
+      <c r="F226" t="n">
+        <v>40.81999969482422</v>
+      </c>
+      <c r="G226" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="H226" t="n">
+        <v>39.29999923706055</v>
+      </c>
+      <c r="I226" t="n">
+        <v>40.81999969482422</v>
+      </c>
+      <c r="J226" t="n">
+        <v>39.29999923706055</v>
+      </c>
+      <c r="K226" t="n">
+        <v>32335</v>
+      </c>
+      <c r="L226" t="n">
+        <v>-3.72</v>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>Ahlada Engineers to hold 21st AGM on August 5, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>Ahlada Engineers Ltd is Rated Strong Sell - marketsmojo.com</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>RYN Q1 2026 Earnings: EPS of $0.07 Delivers 112.94% Surprise, Shares Gain 1.82% - Management Tone Analysis - Vinanet</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>15 Best Bank Account Bonuses of August 2026: Earn Up to $3,000 in Cash Rewards - Next Quarter Guidance - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>Ahlada Engineers Ltd is Rated Strong Sell - marketsmojo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>6</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>ASTERDM.NS</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Aster DM Quality Care Limited</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>798.3499755859375</v>
+      </c>
+      <c r="F227" t="n">
+        <v>798.3499755859375</v>
+      </c>
+      <c r="G227" t="n">
+        <v>771.0499877929688</v>
+      </c>
+      <c r="H227" t="n">
+        <v>776.4000244140625</v>
+      </c>
+      <c r="I227" t="n">
+        <v>800.2000122070312</v>
+      </c>
+      <c r="J227" t="n">
+        <v>776.4000244140625</v>
+      </c>
+      <c r="K227" t="n">
+        <v>3948903</v>
+      </c>
+      <c r="L227" t="n">
+        <v>-2.97</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>Aster DM Healthcare to rename as Aster DM Quality Care Limited - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>Aster DM Healthcare: Over 84M Shares Pledged as Security - InvestyWise</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Aster DM Quality Care Limited (NSE:ASTERDM) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹898 - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Aster DM Healthcare Ltd. Share Price Fall and Market Action - Univest</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>Aster DM Healthcare Ltd. (ASTERDM) Share Price Hits Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>7</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>FCL.NS</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Fineotex Chemical Limited</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>45.09999847412109</v>
+      </c>
+      <c r="F228" t="n">
+        <v>45.47999954223633</v>
+      </c>
+      <c r="G228" t="n">
+        <v>43.36999893188477</v>
+      </c>
+      <c r="H228" t="n">
+        <v>43.65000152587891</v>
+      </c>
+      <c r="I228" t="n">
+        <v>44.97999954223633</v>
+      </c>
+      <c r="J228" t="n">
+        <v>43.65000152587891</v>
+      </c>
+      <c r="K228" t="n">
+        <v>6874033</v>
+      </c>
+      <c r="L228" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>FINEOS (ASX:FCL) Shares Rebound As Profit Emerges Under Rich P E - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>FINEOS (ASX:FCL) Shares Rebound As Profit Emerges Under Rich P E - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>Why Are Investors Watching Fineos (ASX:FCL) After Its Latest Share Price Decline? - Kalkine</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Fineos (ASX: FCL) Crosses Profitability Inflection Point In H1 FY 2026 - arichlife.com.au</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>Manulife Ideal Cnd Div Growth7575 FCL (0P000180PM.TO) interactive stock chart - uk.finance.yahoo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>8</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>CHENNPETRO.NS</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Chennai Petroleum Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>1457</v>
+      </c>
+      <c r="F229" t="n">
+        <v>1466</v>
+      </c>
+      <c r="G229" t="n">
+        <v>1379.599975585938</v>
+      </c>
+      <c r="H229" t="n">
+        <v>1397.800048828125</v>
+      </c>
+      <c r="I229" t="n">
+        <v>1440.300048828125</v>
+      </c>
+      <c r="J229" t="n">
+        <v>1397.800048828125</v>
+      </c>
+      <c r="K229" t="n">
+        <v>1565064</v>
+      </c>
+      <c r="L229" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>Chennai Petroleum Corporation Limited (NSE:CHENNPETRO) Looks Interesting, And It's About To Pay A Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Chennai Petroleum Corporation Ltd. Share Price at 52-Week - Univest</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>Chennai Petroleum Corporation Ltd. (CHENNPETRO) Share Price Rises 5.01% Today - Univest</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Chennai Petroleum Corporation Ltd. Share Price at 52-Week - Univest</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>Chennai Petroleum Corporation Ltd. Stock News: Price Up 5.8% - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>9</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>MILKYMIST.NS</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Milky Mist Dairy Food Limited</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>207.8000030517578</v>
+      </c>
+      <c r="F230" t="n">
+        <v>211.8000030517578</v>
+      </c>
+      <c r="G230" t="n">
+        <v>191.25</v>
+      </c>
+      <c r="H230" t="n">
+        <v>194.0700073242188</v>
+      </c>
+      <c r="I230" t="n">
+        <v>199.6499938964844</v>
+      </c>
+      <c r="J230" t="n">
+        <v>194.0700073242188</v>
+      </c>
+      <c r="K230" t="n">
+        <v>42030536</v>
+      </c>
+      <c r="L230" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>Average basic shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Milky Mist Dairy Food Ltd. Financial Statements – NSE:MILKYMIST - TradingView</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>MILKYMIST Share Price Today - Milky Mist Dairy Food Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>MILKYMIST Share Price Today - MILKY MIST DAIRY FOOD L Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>Milky Mist Dairy Food IPO listing date today. Here’s what GMP, experts hint ahead of debut - livemint.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>10</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>DREDGECORP.NS</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Dredging Corporation of India Limited</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>1199</v>
+      </c>
+      <c r="F231" t="n">
+        <v>1204</v>
+      </c>
+      <c r="G231" t="n">
+        <v>1154.800048828125</v>
+      </c>
+      <c r="H231" t="n">
+        <v>1156</v>
+      </c>
+      <c r="I231" t="n">
+        <v>1189.199951171875</v>
+      </c>
+      <c r="J231" t="n">
+        <v>1156</v>
+      </c>
+      <c r="K231" t="n">
+        <v>114984</v>
+      </c>
+      <c r="L231" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>11</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>SSWL.NS</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Steel Strips Wheels Limited</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>316.25</v>
+      </c>
+      <c r="F232" t="n">
+        <v>319.6000061035156</v>
+      </c>
+      <c r="G232" t="n">
+        <v>306.6000061035156</v>
+      </c>
+      <c r="H232" t="n">
+        <v>307.3500061035156</v>
+      </c>
+      <c r="I232" t="n">
+        <v>315.8500061035156</v>
+      </c>
+      <c r="J232" t="n">
+        <v>307.3500061035156</v>
+      </c>
+      <c r="K232" t="n">
+        <v>337310</v>
+      </c>
+      <c r="L232" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>SSWL Forecast — Price Target — Prediction for 2027 - TradingView</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Steel Strips Wheels (SSWL) Dips 2.45%: Testing Near-Term Support After Pullback - RSI Oversold Picks - Vinanet</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Steel Strips Wheels (NSE:SSWL) Is Looking To Continue Growing Its Returns On Capital - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>SSWL Mar 2026 Earnings: Robust Revenue and Positive Stock Momentum Amidst Operational Efficiency - EPS Surprise History - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>Steel Strips Wheels Limited Receives ESG Score of 68.6 from SES ESG Research - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>12</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>YASHO.NS</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Yasho Industries Limited</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F233" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G233" t="n">
+        <v>4300</v>
+      </c>
+      <c r="H233" t="n">
+        <v>4365</v>
+      </c>
+      <c r="I233" t="n">
+        <v>4470.7998046875</v>
+      </c>
+      <c r="J233" t="n">
+        <v>4365</v>
+      </c>
+      <c r="K233" t="n">
+        <v>81327</v>
+      </c>
+      <c r="L233" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - marketsmojo.com</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Yasho Ind. Standalone June 2026 Net Sales at Rs 314.09 crore, up 58.73% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Yasho Industries Q1 FY27 Results: PAT Rs 36 Cr, Revenue Rs 307 Cr - Univest</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>Yasho Industries Q1 Results: Net profit surges 547% YoY - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>13</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>VSSL.NS</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Vardhman Special Steels Limited</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>362</v>
+      </c>
+      <c r="F234" t="n">
+        <v>362.1000061035156</v>
+      </c>
+      <c r="G234" t="n">
+        <v>350</v>
+      </c>
+      <c r="H234" t="n">
+        <v>350.25</v>
+      </c>
+      <c r="I234" t="n">
+        <v>358.6499938964844</v>
+      </c>
+      <c r="J234" t="n">
+        <v>350.25</v>
+      </c>
+      <c r="K234" t="n">
+        <v>59020</v>
+      </c>
+      <c r="L234" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Vardhman Special Steels lays foundation for ₹1,116 crore forging unit - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Vardhman Special Steels Ltd. Share Price at 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Vardhman Special Steels Ltd. Share Price at 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Vardhman Special Steels hosts investor meet in Mumbai on Aug 14 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>14</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>LCL.NS</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Lohia Corp Limited</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>552</v>
+      </c>
+      <c r="F235" t="n">
+        <v>576.9500122070312</v>
+      </c>
+      <c r="G235" t="n">
+        <v>542.8499755859375</v>
+      </c>
+      <c r="H235" t="n">
+        <v>548.2999877929688</v>
+      </c>
+      <c r="I235" t="n">
+        <v>561.2999877929688</v>
+      </c>
+      <c r="J235" t="n">
+        <v>548.2999877929688</v>
+      </c>
+      <c r="K235" t="n">
+        <v>1288345</v>
+      </c>
+      <c r="L235" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>LOHIA CORP LIMITED Share Price: New One-Year High Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>Lohia Corp Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of Lohia Corp Limited – NSE:LCL - TradingView</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Lohia Corp Shares List At Over 8% Premium On NSE - fintechbiznews.com</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>Lohia Corp raises ₹492 crore from anchor investors ahead of IPO opening on Thursday - livemint.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>15</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>PFC.NS</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>374.4500122070312</v>
+      </c>
+      <c r="F236" t="n">
+        <v>375.1000061035156</v>
+      </c>
+      <c r="G236" t="n">
+        <v>365.0499877929688</v>
+      </c>
+      <c r="H236" t="n">
+        <v>365.8500061035156</v>
+      </c>
+      <c r="I236" t="n">
+        <v>374.4500122070312</v>
+      </c>
+      <c r="J236" t="n">
+        <v>365.8500061035156</v>
+      </c>
+      <c r="K236" t="n">
+        <v>7174654</v>
+      </c>
+      <c r="L236" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>PFC, REC Shares Fall As Morgan Stanley Downgrades Both Stocks — Check Target Price, Potential Upside - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation and REC shares fall up to 3% after Morgan Stanley downgrade - The Economic Times</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>'Consensus buy' PFC, 'no sell' REC get downgraded; Check rationale and new targets - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation and REC shares fall up to 3% after Morgan Stanley downgrade - The Economic Times</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>PFC, REC shares fall up to 8% as CLSA cuts target prices on 'mixed' Q1 results - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>16</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>SRM.NS</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>SRM Contractors Limited</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>497.3999938964844</v>
+      </c>
+      <c r="F237" t="n">
+        <v>498.3999938964844</v>
+      </c>
+      <c r="G237" t="n">
+        <v>482.6499938964844</v>
+      </c>
+      <c r="H237" t="n">
+        <v>482.6499938964844</v>
+      </c>
+      <c r="I237" t="n">
+        <v>493.75</v>
+      </c>
+      <c r="J237" t="n">
+        <v>482.6499938964844</v>
+      </c>
+      <c r="K237" t="n">
+        <v>41403</v>
+      </c>
+      <c r="L237" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>SRM Contractors Share Price Forecast to 2030 - Univest</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>SRM Contractors Share Price Forecast to 2030 - Univest</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr"/>
+      <c r="Q237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>17</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>SAMMAANCAP.NS</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Sammaan Capital Limited</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="F238" t="n">
+        <v>155.3999938964844</v>
+      </c>
+      <c r="G238" t="n">
+        <v>149.6999969482422</v>
+      </c>
+      <c r="H238" t="n">
+        <v>150.1999969482422</v>
+      </c>
+      <c r="I238" t="n">
+        <v>153.6300048828125</v>
+      </c>
+      <c r="J238" t="n">
+        <v>150.1999969482422</v>
+      </c>
+      <c r="K238" t="n">
+        <v>5950881</v>
+      </c>
+      <c r="L238" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>Sammaan Capital Ltd Actuals &amp; Estimates (NSE:SAMMAANCAP) - TradingView</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>SAMMAANCAP Mar 2026 Earnings: Massive Loss of ₹72.97 Per Share Reported - Earnings Season Outlook - Vinanet</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Sammaan Capital Limited Open Offer Receives 41,110 Shares Tendered by April 30, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Indiabulls Housing Finance Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>Sammaan Capital Limited Gains 1.70%: Price Action and Key Levels - Factor Crowding - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>18</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>NEPHROPLUS.NS</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Nephrocare Health Services Limited</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>698</v>
+      </c>
+      <c r="F239" t="n">
+        <v>698</v>
+      </c>
+      <c r="G239" t="n">
+        <v>673.1500244140625</v>
+      </c>
+      <c r="H239" t="n">
+        <v>676.5499877929688</v>
+      </c>
+      <c r="I239" t="n">
+        <v>691</v>
+      </c>
+      <c r="J239" t="n">
+        <v>676.5499877929688</v>
+      </c>
+      <c r="K239" t="n">
+        <v>132304</v>
+      </c>
+      <c r="L239" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>NEPHROPLUS Stock Price and Chart — NSE:NEPHROPLUS - TradingView</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>Nephrocare Health Services Limited (NEPHROPLUS.NS) Q2 2026 Earnings: Revenue Surges 32% YoY, EPS of ₹8.1 Reflects Strong Operational Execution - Performance Review - Vinanet</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>NEPHROPLUS to acquire dialysis center assets in Paranaque City, Philippines - Business Standard</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Nephrocare Health Services Ltd Share Price Today – Live NSE/BSE - INDmoney</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>SAM, Khaitan, CAM, Trilegal guide Nephroplus’ INR 871 cr IPO - ETLegalWorld.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>19</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>MMFL.NS</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>MM Forgings Limited</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>660.0999755859375</v>
+      </c>
+      <c r="F240" t="n">
+        <v>669.4500122070312</v>
+      </c>
+      <c r="G240" t="n">
+        <v>635</v>
+      </c>
+      <c r="H240" t="n">
+        <v>644.0999755859375</v>
+      </c>
+      <c r="I240" t="n">
+        <v>657.7999877929688</v>
+      </c>
+      <c r="J240" t="n">
+        <v>644.0999755859375</v>
+      </c>
+      <c r="K240" t="n">
+        <v>138252</v>
+      </c>
+      <c r="L240" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>IOC Share Dividend Stocks Split MMFL KPIT TARIL Afcons Share Midwest Gold FII DII Stock Finshots Atp Rome (HN86imV77B) - Mshale</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>MM Forgings Ltd. Share Price Today Up 8.43%: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>MM Forgings Ltd. Share Price Today Up 8.43%: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>M M Forgings Limited Announces Resignation of Chandrasekar S from Company Secretary and Compliance Officer, Effective August 14, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>M M Forgings postpones Q1FY26 board meeting to Aug 14 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:47 IST</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>20</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>TALBROAUTO.NS</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Talbros Automotive Components Limited</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>423.1000061035156</v>
+      </c>
+      <c r="F241" t="n">
+        <v>428.1499938964844</v>
+      </c>
+      <c r="G241" t="n">
+        <v>410.3500061035156</v>
+      </c>
+      <c r="H241" t="n">
+        <v>414.25</v>
+      </c>
+      <c r="I241" t="n">
+        <v>423.0499877929688</v>
+      </c>
+      <c r="J241" t="n">
+        <v>414.25</v>
+      </c>
+      <c r="K241" t="n">
+        <v>220538</v>
+      </c>
+      <c r="L241" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>Transcript : Talbros Automotive Components Limited, Q1 2027 Earnings Call, Aug 11, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>Transcript : Talbros Automotive Components Limited, Q1 2027 Earnings Call, Aug 11, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gainers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Losers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gainers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Losers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q241"/>
+  <dimension ref="A1:Q261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13404,7 +13404,6 @@
           <t>Kohinoor Foods to Review Quarterly Results and Mull Fundraising at August Board Meeting - TipRanks</t>
         </is>
       </c>
-      <c r="Q225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13533,8 +13532,6 @@
           <t>Are Wall Street Analysts Predicting PepsiCo Stock Will Climb or Sink? - Earnings Call Q&amp;A - Vinanet</t>
         </is>
       </c>
-      <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13658,9 +13655,6 @@
           <t>Mawana Sugars Ltd. Share Price Near 52-Week High - Univest</t>
         </is>
       </c>
-      <c r="O229" t="inlineStr"/>
-      <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13725,7 +13719,6 @@
           <t>Josh Da Costa Shares Another Facet of New Wave Graveyard with the Hypnagogic (and Possibly Psychic) “Cordelia” - floodmagazine.com</t>
         </is>
       </c>
-      <c r="Q230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13785,8 +13778,6 @@
           <t>Network18 sets Oct 1 hearing for News18 Marathi amalgamation - scanx.trade</t>
         </is>
       </c>
-      <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13841,9 +13832,6 @@
           <t>Two Harbors Investment Corp (TWO) Edges Lower to $12.09: Key Support and Resistance in Focus - BPI Bear Correction - Vinanet</t>
         </is>
       </c>
-      <c r="O232" t="inlineStr"/>
-      <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -13972,8 +13960,6 @@
           <t>Bajaj Hindusthan Sugar Publishes Q1 FY27 Results Extracts and Sets Board Meeting - TipRanks</t>
         </is>
       </c>
-      <c r="P234" t="inlineStr"/>
-      <c r="Q234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14457,6 +14443,1330 @@
           <t>Breakout stocks to buy or sell: Sumeet Bagadia recommends five shares to buy today - 20 August 2026 - TradingView</t>
         </is>
       </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>1</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>MPDL.NS</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>MPDL Limited</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>34.29999923706055</v>
+      </c>
+      <c r="F242" t="n">
+        <v>34.31999969482422</v>
+      </c>
+      <c r="G242" t="n">
+        <v>23.26000022888184</v>
+      </c>
+      <c r="H242" t="n">
+        <v>34.31999969482422</v>
+      </c>
+      <c r="I242" t="n">
+        <v>28.60000038146973</v>
+      </c>
+      <c r="J242" t="n">
+        <v>34.31999969482422</v>
+      </c>
+      <c r="K242" t="n">
+        <v>8795</v>
+      </c>
+      <c r="L242" t="n">
+        <v>20</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>MPDL Share Price Today - MPDL Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>MPDL Share Price Today - MPDL Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of MPDL Ltd – NSE:MPDL - TradingView</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>MPDL Ltd Q1 Results: Board approves financials for quarter ended June 30 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>MPDL reports consolidated net loss of Rs 4.20 crore in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>2</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>MYSORPETRO.NS</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>160</v>
+      </c>
+      <c r="F243" t="n">
+        <v>165.4900054931641</v>
+      </c>
+      <c r="G243" t="n">
+        <v>155.3000030517578</v>
+      </c>
+      <c r="H243" t="n">
+        <v>165.4900054931641</v>
+      </c>
+      <c r="I243" t="n">
+        <v>137.9100036621094</v>
+      </c>
+      <c r="J243" t="n">
+        <v>165.4900054931641</v>
+      </c>
+      <c r="K243" t="n">
+        <v>383979</v>
+      </c>
+      <c r="L243" t="n">
+        <v>20</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>20% Upper Circuit: 8 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals shareholders approve FY26 financials, dividend, director reappointment - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>20% Upper Circuit: 8 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>3</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>KRONOX.NS</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Limited</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>155.0099945068359</v>
+      </c>
+      <c r="F244" t="n">
+        <v>186.1900024414062</v>
+      </c>
+      <c r="G244" t="n">
+        <v>155.0099945068359</v>
+      </c>
+      <c r="H244" t="n">
+        <v>186.1900024414062</v>
+      </c>
+      <c r="I244" t="n">
+        <v>155.1600036621094</v>
+      </c>
+      <c r="J244" t="n">
+        <v>186.1900024414062</v>
+      </c>
+      <c r="K244" t="n">
+        <v>5888825</v>
+      </c>
+      <c r="L244" t="n">
+        <v>20</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>Kronox Lab shares hit 20% upper circuit as Indo Borax and Chemicals to acquire 64.26% stake - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>Indo Borax &amp; Chemicals Limited executed a Share Purchase Agreement to acquire 64.26% stake in Kronox Lab Sciences Limited from Ketan Vinodchandra Ramani, Pritesh Vinodchandra Ramani and Jogindersingh Gianchand Jaswal for INR 2.5 billion. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Share Price Rise With Peer Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>Indo Borax Approves Kronox Lab Stake Purchase; Shares Rise 7.44% - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>Momentum Stocks: Kronox Lab Sciences, Waterways Leisure, Genus Power rise up to % on sheer momentum - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>4</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>KJMCFIN.NS</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>66.34999847412109</v>
+      </c>
+      <c r="F245" t="n">
+        <v>66.41999816894531</v>
+      </c>
+      <c r="G245" t="n">
+        <v>61.90000152587891</v>
+      </c>
+      <c r="H245" t="n">
+        <v>66.41999816894531</v>
+      </c>
+      <c r="I245" t="n">
+        <v>55.34999847412109</v>
+      </c>
+      <c r="J245" t="n">
+        <v>66.41999816894531</v>
+      </c>
+      <c r="K245" t="n">
+        <v>3326</v>
+      </c>
+      <c r="L245" t="n">
+        <v>20</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services net profit rises to ₹162.85 lakh in Q1FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr"/>
+      <c r="Q245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>5</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>MINALIND.NS</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Minal Industries Limited</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>2.240000009536743</v>
+      </c>
+      <c r="F246" t="n">
+        <v>2.650000095367432</v>
+      </c>
+      <c r="G246" t="n">
+        <v>2.230000019073486</v>
+      </c>
+      <c r="H246" t="n">
+        <v>2.650000095367432</v>
+      </c>
+      <c r="I246" t="n">
+        <v>2.210000038146973</v>
+      </c>
+      <c r="J246" t="n">
+        <v>2.650000095367432</v>
+      </c>
+      <c r="K246" t="n">
+        <v>312753</v>
+      </c>
+      <c r="L246" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of Minal Industries Limited – NSE:MINALIND - TradingView</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of Minal Industries Limited – NSE:MINALIND - TradingView</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>MINALIND Share Price Today - Minal Industries Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Minal Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>Minal Industries Ltd - Equitypandit</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>6</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>CRSL.NS</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>2.789999961853027</v>
+      </c>
+      <c r="F247" t="n">
+        <v>3.089999914169312</v>
+      </c>
+      <c r="G247" t="n">
+        <v>2.700000047683716</v>
+      </c>
+      <c r="H247" t="n">
+        <v>3.089999914169312</v>
+      </c>
+      <c r="I247" t="n">
+        <v>2.579999923706055</v>
+      </c>
+      <c r="J247" t="n">
+        <v>3.089999914169312</v>
+      </c>
+      <c r="K247" t="n">
+        <v>8160294</v>
+      </c>
+      <c r="L247" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>CRSL Share Price Today - Cressanda Railway Solutions Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Ltd - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Ltd Statistics – NSE:CRSL - TradingView</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Ltd Income Statement – NSE:CRSL - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>7</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN.NS</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Limited</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>658.25</v>
+      </c>
+      <c r="F248" t="n">
+        <v>780.9500122070312</v>
+      </c>
+      <c r="G248" t="n">
+        <v>655.0499877929688</v>
+      </c>
+      <c r="H248" t="n">
+        <v>767.0999755859375</v>
+      </c>
+      <c r="I248" t="n">
+        <v>650.7999877929688</v>
+      </c>
+      <c r="J248" t="n">
+        <v>767.0999755859375</v>
+      </c>
+      <c r="K248" t="n">
+        <v>33513023</v>
+      </c>
+      <c r="L248" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd Share Price Target, Forecast for Long Term Equity. - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: Balrampur Chini Mills Q1 2026 stock falls as outlook stays firm - Investing.com</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price Hits One-Year High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>8</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>BANARISUG.NS</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Limited</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>3635</v>
+      </c>
+      <c r="F249" t="n">
+        <v>4338</v>
+      </c>
+      <c r="G249" t="n">
+        <v>3635</v>
+      </c>
+      <c r="H249" t="n">
+        <v>4240.7001953125</v>
+      </c>
+      <c r="I249" t="n">
+        <v>3617.39990234375</v>
+      </c>
+      <c r="J249" t="n">
+        <v>4240.7001953125</v>
+      </c>
+      <c r="K249" t="n">
+        <v>71288</v>
+      </c>
+      <c r="L249" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars secures Madras HC stay on ₹12.72 crore tax recovery - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>AfCFTA Trade Finance: Small Businesses Gain New Access via ITC-Equity Partnership - Earnings Weakness Phase - Vinanet</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>Stardust Power Inc. (SDST) Drops 5.95% as Stock Tests Key Support at $1.5 - Mutual Fund Flow - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>9</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>SOLARA.NS</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences Limited</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>551.9500122070312</v>
+      </c>
+      <c r="F250" t="n">
+        <v>654.4000244140625</v>
+      </c>
+      <c r="G250" t="n">
+        <v>551.9500122070312</v>
+      </c>
+      <c r="H250" t="n">
+        <v>640</v>
+      </c>
+      <c r="I250" t="n">
+        <v>550.0499877929688</v>
+      </c>
+      <c r="J250" t="n">
+        <v>640</v>
+      </c>
+      <c r="K250" t="n">
+        <v>6915514</v>
+      </c>
+      <c r="L250" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Today Up - Univest</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma shares jump 5% as Q1 profit rises 55%; Ibuprofen business remains a drag - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>SOLARA ACTIVE P Standalone June 2026 Net Sales at Rs 381.60 crore, up 19.57% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>10</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>SOMICONVEY.NS</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Somi Conveyor Beltings Limited</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>96</v>
+      </c>
+      <c r="F251" t="n">
+        <v>103.9300003051758</v>
+      </c>
+      <c r="G251" t="n">
+        <v>95</v>
+      </c>
+      <c r="H251" t="n">
+        <v>100.0699996948242</v>
+      </c>
+      <c r="I251" t="n">
+        <v>86.61000061035156</v>
+      </c>
+      <c r="J251" t="n">
+        <v>100.0699996948242</v>
+      </c>
+      <c r="K251" t="n">
+        <v>687119</v>
+      </c>
+      <c r="L251" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>Somi Conveyor Beltings Ltd. Share Price Today Up 19.97% - Univest</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>Somi Conveyor Beltings Ltd. Share Price Today Up 19.97% - Univest</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Somi Conveyor Beltings Ltd. Share Price Near 52-Week Low - Univest</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr"/>
+      <c r="Q251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>11</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>KWIL.NS</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Kwality Wall's (India) Limited</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>38</v>
+      </c>
+      <c r="F252" t="n">
+        <v>44.29999923706055</v>
+      </c>
+      <c r="G252" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="H252" t="n">
+        <v>43.47000122070312</v>
+      </c>
+      <c r="I252" t="n">
+        <v>37.70999908447266</v>
+      </c>
+      <c r="J252" t="n">
+        <v>43.47000122070312</v>
+      </c>
+      <c r="K252" t="n">
+        <v>101230788</v>
+      </c>
+      <c r="L252" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>TMICC completes KWIL stake buy in HUL’s ice-cream demerger - Law.asia</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>Kwality Wall's (KWIL.NS) Gains 3.45%: Ice Cream Major Tests ₹34.66 Resistance - Supply Zone - Vinanet</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>HUL Demerger: Ice-Cream Business Spun off Into Kwality Wall’s; Record Date Set for 5 December - Groww</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>HUL completes acquisition of Zywie ventures; KWIL shares to be traded from Feb. 16 - The Hindu</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>Kwality Wall''s Stock Debuts After HUL Demerger - Rediff MoneyWiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>12</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>INDOBORAX.NS</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Indo Borax &amp; Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>439</v>
+      </c>
+      <c r="F253" t="n">
+        <v>509.8999938964844</v>
+      </c>
+      <c r="G253" t="n">
+        <v>431</v>
+      </c>
+      <c r="H253" t="n">
+        <v>498.1499938964844</v>
+      </c>
+      <c r="I253" t="n">
+        <v>433.8500061035156</v>
+      </c>
+      <c r="J253" t="n">
+        <v>498.1499938964844</v>
+      </c>
+      <c r="K253" t="n">
+        <v>6099190</v>
+      </c>
+      <c r="L253" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>Shareholders May Be More Conservative With Indo Borax &amp; Chemicals Limited's (NSE:INDOBORAX) CEO Compensation For Now - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>INDOBORAX Q2 FY2026 Earnings: Robust Revenue Growth of 22.9% Drives Strong EPS of ₹15.67 - EPS Consistency Score - Vinanet</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Indo Borax &amp; Chemicals Limited Receives Open Offer from Zenrock Chemicals for 83.43 Lakh Shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>INDOBORAX Mar 2026 Earnings: Steady Profitability Driven by Stable Input Costs and Consistent Demand - Investor Earnings Call - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>INDOBORAX.NS News: Latest Updates and Market Outlook - Vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>13</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>DWARKESH.NS</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar Industries Limited</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>48.77000045776367</v>
+      </c>
+      <c r="F254" t="n">
+        <v>56.45000076293945</v>
+      </c>
+      <c r="G254" t="n">
+        <v>48.70000076293945</v>
+      </c>
+      <c r="H254" t="n">
+        <v>55.38000106811523</v>
+      </c>
+      <c r="I254" t="n">
+        <v>48.27999877929688</v>
+      </c>
+      <c r="J254" t="n">
+        <v>55.38000106811523</v>
+      </c>
+      <c r="K254" t="n">
+        <v>42665668</v>
+      </c>
+      <c r="L254" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar Industries Ltd. (DWARKESH) Share Price Rises 8.84% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar surges more than 6% on buyback plans, fixes record date on March 20 - Upstox</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>Is It Worth Considering Dwarikesh Sugar Industries Limited (NSE:DWARKESH) For Its Upcoming Dividend? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar Industries Ltd. (DWARKESH) Share Price Rises 8.84% Today - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>14</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>BAJAJHIND.NS</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>20.73999977111816</v>
+      </c>
+      <c r="F255" t="n">
+        <v>23.97999954223633</v>
+      </c>
+      <c r="G255" t="n">
+        <v>20.59000015258789</v>
+      </c>
+      <c r="H255" t="n">
+        <v>23.32999992370605</v>
+      </c>
+      <c r="I255" t="n">
+        <v>20.3799991607666</v>
+      </c>
+      <c r="J255" t="n">
+        <v>23.32999992370605</v>
+      </c>
+      <c r="K255" t="n">
+        <v>256544491</v>
+      </c>
+      <c r="L255" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Publishes Q1 FY27 Results Extracts and Sets Board Meeting - TipRanks</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr"/>
+      <c r="Q255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>15</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>PACIFICI.NS</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Pacific Industries Limited</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>133.5500030517578</v>
+      </c>
+      <c r="F256" t="n">
+        <v>159</v>
+      </c>
+      <c r="G256" t="n">
+        <v>133.5500030517578</v>
+      </c>
+      <c r="H256" t="n">
+        <v>150.9799957275391</v>
+      </c>
+      <c r="I256" t="n">
+        <v>133.5500030517578</v>
+      </c>
+      <c r="J256" t="n">
+        <v>150.9799957275391</v>
+      </c>
+      <c r="K256" t="n">
+        <v>8374</v>
+      </c>
+      <c r="L256" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>PACIFICI Share Price Today - Pacific Industries Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>PACIFICI Share Price Today - Pacific Industries Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Pacific Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr"/>
+      <c r="Q256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>16</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>CGVAK.NS</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>CG Vak Software &amp; Exports Limited</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>159</v>
+      </c>
+      <c r="F257" t="n">
+        <v>162.5500030517578</v>
+      </c>
+      <c r="G257" t="n">
+        <v>152.0099945068359</v>
+      </c>
+      <c r="H257" t="n">
+        <v>158.5800018310547</v>
+      </c>
+      <c r="I257" t="n">
+        <v>140.7299957275391</v>
+      </c>
+      <c r="J257" t="n">
+        <v>158.5800018310547</v>
+      </c>
+      <c r="K257" t="n">
+        <v>13494</v>
+      </c>
+      <c r="L257" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>CGVAK Share Price Today - CG-VAK Software &amp; Exports Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>CG-VAK Software &amp; Exports Ltd - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>CG-VAK Software &amp; Exports Ltd - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr"/>
+      <c r="Q257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>17</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>SUVEN.NS</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Suven Life Sciences Limited</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>335</v>
+      </c>
+      <c r="F258" t="n">
+        <v>377.4500122070312</v>
+      </c>
+      <c r="G258" t="n">
+        <v>335</v>
+      </c>
+      <c r="H258" t="n">
+        <v>373.6000061035156</v>
+      </c>
+      <c r="I258" t="n">
+        <v>332.5499877929688</v>
+      </c>
+      <c r="J258" t="n">
+        <v>373.6000061035156</v>
+      </c>
+      <c r="K258" t="n">
+        <v>3256156</v>
+      </c>
+      <c r="L258" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>Suven Pharmaceuticals Ltd. Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>Suven Pharmaceuticals Ltd. Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>Suven Life Sciences Limited Rights 2022-10.11.22 For Shares Revenue Breakdown – BSE:SUVEN_RE - TradingView</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Suven Life Sciences Shares Decline Over 5% As Q1 Net Loss Widens To Rs 128 Crore - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>Suven Life Sciences seeks AGM approval for related party transaction and fund reallocation - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>18</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>UTTAMSUGAR.NS</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Limited</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>303.0899963378906</v>
+      </c>
+      <c r="F259" t="n">
+        <v>344</v>
+      </c>
+      <c r="G259" t="n">
+        <v>301.8500061035156</v>
+      </c>
+      <c r="H259" t="n">
+        <v>336.2200012207031</v>
+      </c>
+      <c r="I259" t="n">
+        <v>300.989990234375</v>
+      </c>
+      <c r="J259" t="n">
+        <v>336.2200012207031</v>
+      </c>
+      <c r="K259" t="n">
+        <v>2292635</v>
+      </c>
+      <c r="L259" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Ltd. Stock News: Price Increase Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Share Price: Technical, Fundamental View - Univest</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Share Price: Technical, Fundamental View - Univest</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr"/>
+      <c r="Q259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>19</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>SWISSMLTRY.NS</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Swiss Military Consumer Goods Limited</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>15.1899995803833</v>
+      </c>
+      <c r="F260" t="n">
+        <v>16.79999923706055</v>
+      </c>
+      <c r="G260" t="n">
+        <v>14</v>
+      </c>
+      <c r="H260" t="n">
+        <v>16.44000053405762</v>
+      </c>
+      <c r="I260" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="J260" t="n">
+        <v>16.44000053405762</v>
+      </c>
+      <c r="K260" t="n">
+        <v>870159</v>
+      </c>
+      <c r="L260" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>SWISSMLTRY Share Price Today - Swiss Military Consumer Goods Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>Swiss Military Consumer Goods equity shares admitted on NSE - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Swiss Military Consumer Goods Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Swiss Military Consumer Goods equity shares admitted on NSE - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>20</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>KOHINOOR.NS</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Limited</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>32.09999847412109</v>
+      </c>
+      <c r="F261" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G261" t="n">
+        <v>30.95000076293945</v>
+      </c>
+      <c r="H261" t="n">
+        <v>34.81000137329102</v>
+      </c>
+      <c r="I261" t="n">
+        <v>31.27000045776367</v>
+      </c>
+      <c r="J261" t="n">
+        <v>34.81000137329102</v>
+      </c>
+      <c r="K261" t="n">
+        <v>1739882</v>
+      </c>
+      <c r="L261" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd is Rated Strong Sell - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods to Review Quarterly Results and Mull Fundraising at August Board Meeting - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14469,7 +15779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q241"/>
+  <dimension ref="A1:Q261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27572,9 +28882,6 @@
           <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
         </is>
       </c>
-      <c r="O231" t="inlineStr"/>
-      <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -27777,7 +29084,6 @@
           <t>Vardhman Special Steels hosts investor meet in Mumbai on Aug 14 - scanx.trade</t>
         </is>
       </c>
-      <c r="Q234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -27970,9 +29276,6 @@
           <t>SRM Contractors Share Price Forecast to 2030 - Univest</t>
         </is>
       </c>
-      <c r="O237" t="inlineStr"/>
-      <c r="P237" t="inlineStr"/>
-      <c r="Q237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -28234,9 +29537,1310 @@
           <t>Transcript : Talbros Automotive Components Limited, Q1 2027 Earnings Call, Aug 11, 2026 - marketscreener.com</t>
         </is>
       </c>
-      <c r="O241" t="inlineStr"/>
-      <c r="P241" t="inlineStr"/>
-      <c r="Q241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>1</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>TECILCHEM.NS</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>TECIL Chemicals and Hydro Power Limited</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>11.28999996185303</v>
+      </c>
+      <c r="F242" t="n">
+        <v>11.55000019073486</v>
+      </c>
+      <c r="G242" t="n">
+        <v>9</v>
+      </c>
+      <c r="H242" t="n">
+        <v>9.140000343322754</v>
+      </c>
+      <c r="I242" t="n">
+        <v>10.23999977111816</v>
+      </c>
+      <c r="J242" t="n">
+        <v>9.140000343322754</v>
+      </c>
+      <c r="K242" t="n">
+        <v>306021</v>
+      </c>
+      <c r="L242" t="n">
+        <v>-10.74</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>TECIL Chemicals (TECILCHEM) Declines to ₹11.6, Approaches Key Support Zone - McClellan Summation - Vinanet</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>Dollar Steadies as US-Iran Tensions Escalate; Yen Weakens on Pension Concerns - Profit Announcement - Vinanet</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>TECILCHEM Holds Support Amid Weakness – Key Levels to Watch - BPI Bear Correction - Vinanet</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>TECIL Chemicals (TECILCHEM.NS) Declines Nearly 3.5%, Approaches Key Support at ₹9.19 - Liquidity Order Flow - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>TECILCHEM.NS Q2 2025 Earnings: No Revenue, Net Loss Amid Minimal Business Activity - EBITDA Margin Trends - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>2</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>KAMANWALA.NS</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Kamanwala Housing Construction Limited</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>18.59000015258789</v>
+      </c>
+      <c r="F243" t="n">
+        <v>18.59000015258789</v>
+      </c>
+      <c r="G243" t="n">
+        <v>16.11000061035156</v>
+      </c>
+      <c r="H243" t="n">
+        <v>16.68000030517578</v>
+      </c>
+      <c r="I243" t="n">
+        <v>18.6299991607666</v>
+      </c>
+      <c r="J243" t="n">
+        <v>16.68000030517578</v>
+      </c>
+      <c r="K243" t="n">
+        <v>56343</v>
+      </c>
+      <c r="L243" t="n">
+        <v>-10.47</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>Kamanwala Housing Construction Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>Japanese stocks rebound as bond yields ease - Business Standard</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>Volume Gainers on August 19, 2026 at 3:00 PM IST - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>Horizon Industrial Parks IPO Day 3 Subscription Status: Issue Booked 0.30x So Far - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>Chinese stocks rebound as policy hopes build - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>3</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>BTML.NS</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Bodhi Tree Multimedia Limited</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>8.789999961853027</v>
+      </c>
+      <c r="F244" t="n">
+        <v>8.800000190734863</v>
+      </c>
+      <c r="G244" t="n">
+        <v>7.849999904632568</v>
+      </c>
+      <c r="H244" t="n">
+        <v>7.920000076293945</v>
+      </c>
+      <c r="I244" t="n">
+        <v>8.720000267028809</v>
+      </c>
+      <c r="J244" t="n">
+        <v>7.920000076293945</v>
+      </c>
+      <c r="K244" t="n">
+        <v>1261909</v>
+      </c>
+      <c r="L244" t="n">
+        <v>-9.17</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>Bodhi Tree Multimedia Ltd. Stock News: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>DD Q1 2026 Earnings: EPS Surges Past Estimates by 10.4% as Shares Retreat 1.33% - Earnings Acceleration Picks - Vinanet</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>DD Q1 2026 Earnings: EPS Surges Past Estimates by 10.4% as Shares Retreat 1.33% - Earnings Acceleration Picks - Vinanet</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>4</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>ADDIND.NS</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Addi Industries Limited</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>87.94999694824219</v>
+      </c>
+      <c r="F245" t="n">
+        <v>87.94999694824219</v>
+      </c>
+      <c r="G245" t="n">
+        <v>71.05000305175781</v>
+      </c>
+      <c r="H245" t="n">
+        <v>80</v>
+      </c>
+      <c r="I245" t="n">
+        <v>87</v>
+      </c>
+      <c r="J245" t="n">
+        <v>80</v>
+      </c>
+      <c r="K245" t="n">
+        <v>612</v>
+      </c>
+      <c r="L245" t="n">
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>Addi Industries Limited Statistics – NSE:ADDIND - TradingView</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>Addi Industries Ltd. (ADDIND) Fundamental and Financial Data - Stocktwits</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>Addi Industries Ltd. (ADDIND) Fundamental and Financial Data - Stocktwits</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Addi Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>5</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>NKIND.NS</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NK Industries Limited</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>60.9900016784668</v>
+      </c>
+      <c r="F246" t="n">
+        <v>60.9900016784668</v>
+      </c>
+      <c r="G246" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="H246" t="n">
+        <v>56.59999847412109</v>
+      </c>
+      <c r="I246" t="n">
+        <v>61.54999923706055</v>
+      </c>
+      <c r="J246" t="n">
+        <v>56.59999847412109</v>
+      </c>
+      <c r="K246" t="n">
+        <v>183</v>
+      </c>
+      <c r="L246" t="n">
+        <v>-8.039999999999999</v>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>International (IGIC) Latest Quarter: EPS Misses Its Estimate in Latest Trading; After Earnings: Shares Finish 2.35% Higher - Earnings Call Highlights - Vinanet</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>International (IGIC) Latest Quarter: EPS Misses Its Estimate in Latest Trading; After Earnings: Shares Finish 2.35% Higher - Earnings Call Highlights - Vinanet</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>Record Heat Drives UK Online Retail Sales to Five-Year High in June - Book Value Growth - Vinanet</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Fennec (FENC) Technical Check: Adds 0.51% to Close at $11.89 at the Close; Current Setup: the Supplied Trading Band Runs From $11.30 to $12.48 - Throwback Trade - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>6</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>GCSL.NS</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services Limited</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>526.2999877929688</v>
+      </c>
+      <c r="F247" t="n">
+        <v>540.9500122070312</v>
+      </c>
+      <c r="G247" t="n">
+        <v>470</v>
+      </c>
+      <c r="H247" t="n">
+        <v>482.0499877929688</v>
+      </c>
+      <c r="I247" t="n">
+        <v>521.7000122070312</v>
+      </c>
+      <c r="J247" t="n">
+        <v>482.0499877929688</v>
+      </c>
+      <c r="K247" t="n">
+        <v>615891</v>
+      </c>
+      <c r="L247" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services gets exchange nod for ₹7 crore warrant issue - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services Raises Capital via Preferential Allotment of Warrants to Promoter Group - TipRanks</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services Q1 Results: Revenue at ₹1,785 Mn, Net Profit ₹276 Mn - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services allots 5.55 lakh warrants to promoter group - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services Receives SEBI Show Cause Notice Over Taurian MPS Ltd IPO - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>7</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>MILKYMIST.NS</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Milky Mist Dairy Food Limited</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>207.8000030517578</v>
+      </c>
+      <c r="F248" t="n">
+        <v>211.8000030517578</v>
+      </c>
+      <c r="G248" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="H248" t="n">
+        <v>184.8899993896484</v>
+      </c>
+      <c r="I248" t="n">
+        <v>199.6499938964844</v>
+      </c>
+      <c r="J248" t="n">
+        <v>184.8899993896484</v>
+      </c>
+      <c r="K248" t="n">
+        <v>56530266</v>
+      </c>
+      <c r="L248" t="n">
+        <v>-7.39</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>Average basic shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>Milky Mist Dairy Food Ltd. Financial Statements – NSE:MILKYMIST - TradingView</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>MILKYMIST Share Price Today - Milky Mist Dairy Food Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>MILKYMIST Share Price Today - MILKY MIST DAIRY FOOD L Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>Milky Mist Dairy Food IPO listing date today. Here’s what GMP, experts hint ahead of debut - livemint.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>8</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>WEL.NS</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Wonder Electricals Limited</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>148.3999938964844</v>
+      </c>
+      <c r="F249" t="n">
+        <v>149.7799987792969</v>
+      </c>
+      <c r="G249" t="n">
+        <v>132</v>
+      </c>
+      <c r="H249" t="n">
+        <v>136.0399932861328</v>
+      </c>
+      <c r="I249" t="n">
+        <v>146.2599945068359</v>
+      </c>
+      <c r="J249" t="n">
+        <v>136.0399932861328</v>
+      </c>
+      <c r="K249" t="n">
+        <v>1505497</v>
+      </c>
+      <c r="L249" t="n">
+        <v>-6.99</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Btab uses artificial intelligence to link global manufacturers with U.S. business buyers - Stock Titan</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>Btab uses artificial intelligence to link global manufacturers with U.S. business buyers - Stock Titan</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>Enterprise value to EBIT forward of Wel-Dish. Incorporated – TSE:2901 - TradingView</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr"/>
+      <c r="Q249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>9</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>SINTERCOM.NS</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Sintercom India Limited</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>86.98999786376953</v>
+      </c>
+      <c r="F250" t="n">
+        <v>86.98999786376953</v>
+      </c>
+      <c r="G250" t="n">
+        <v>79.05999755859375</v>
+      </c>
+      <c r="H250" t="n">
+        <v>79.38999938964844</v>
+      </c>
+      <c r="I250" t="n">
+        <v>85</v>
+      </c>
+      <c r="J250" t="n">
+        <v>79.38999938964844</v>
+      </c>
+      <c r="K250" t="n">
+        <v>5959</v>
+      </c>
+      <c r="L250" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>Sintercom India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>Sintercom India standalone net profit rises 88.46% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>Sintercom India standalone net profit rises 88.46% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Copper Hits Record High as "Dr. Copper" Sends Conflicting Economic Signals - Consensus Forecast Report - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>10</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>CENTEXT.NS</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Century Extrusions Limited</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>21.95000076293945</v>
+      </c>
+      <c r="F251" t="n">
+        <v>22.10000038146973</v>
+      </c>
+      <c r="G251" t="n">
+        <v>20.39999961853027</v>
+      </c>
+      <c r="H251" t="n">
+        <v>20.63999938964844</v>
+      </c>
+      <c r="I251" t="n">
+        <v>22.07999992370605</v>
+      </c>
+      <c r="J251" t="n">
+        <v>20.63999938964844</v>
+      </c>
+      <c r="K251" t="n">
+        <v>440018</v>
+      </c>
+      <c r="L251" t="n">
+        <v>-6.52</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>Century Extrusions Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>Vicor Corporation (VICR) Climbs Nearly 8% as Shares Test Key Resistance Zone - WMA Signal - Vinanet</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Century Extrusions Ltd. Share Price Today: 13.47% Increase - Univest</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>Century Extrusions Limited Approves Appointment of Shri Charan Singh as A Non-Executive Independent Director - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>Century Extrusions posts 10.97% sales rise in FY26, sets Aug 14 AGM date - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>11</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>ATAM.NS</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Atam Valves Limited</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>60.95000076293945</v>
+      </c>
+      <c r="F252" t="n">
+        <v>60.95000076293945</v>
+      </c>
+      <c r="G252" t="n">
+        <v>54.59999847412109</v>
+      </c>
+      <c r="H252" t="n">
+        <v>55.52999877929688</v>
+      </c>
+      <c r="I252" t="n">
+        <v>59.36000061035156</v>
+      </c>
+      <c r="J252" t="n">
+        <v>55.52999877929688</v>
+      </c>
+      <c r="K252" t="n">
+        <v>88804</v>
+      </c>
+      <c r="L252" t="n">
+        <v>-6.45</v>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>Atam Valves Q1 Results: Net profit falls 49% YoY to ₹63.5 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>Atam Valves Q1 Results: Net profit falls 49% YoY to ₹63.5 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>VRSN Q2 2026 Earnings: EPS Misses Consensus by 1.45% as Shares Decline 1.95% - ROIC Trend Report - Vinanet</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>Shivansh Finserve: புதிய வளர்ச்சிக்கு முக்கிய முடிவு! பெரும் கையகப்படுத்துதல் திட்டம்? - Whalesbook</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>12</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>BALAXI.NS</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>BALAXI PHARMACEUTICALS LIMITED</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>24.20000076293945</v>
+      </c>
+      <c r="F253" t="n">
+        <v>24.20000076293945</v>
+      </c>
+      <c r="G253" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H253" t="n">
+        <v>22.29999923706055</v>
+      </c>
+      <c r="I253" t="n">
+        <v>23.79000091552734</v>
+      </c>
+      <c r="J253" t="n">
+        <v>22.29999923706055</v>
+      </c>
+      <c r="K253" t="n">
+        <v>139294</v>
+      </c>
+      <c r="L253" t="n">
+        <v>-6.26</v>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>Balaxi Pharma Standalone June 2026 Net Sales at Rs 15.58 crore, down 6.73% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>Balaxi Pharma Standalone June 2026 Net Sales at Rs 15.58 crore, down 6.73% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Balaxi Pharma Q1 results FY27: PAT Rs 1 Cr, Revenue Rs 80 Cr - Univest</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>Balaxi Pharmaceuticals Q1 FY27: Strong Revenue Recovery Masks Deep Structural Concerns - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>13</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>LAXMICOT.NS</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Laxmi Cotspin Limited</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>15.26000022888184</v>
+      </c>
+      <c r="F254" t="n">
+        <v>15.28999996185303</v>
+      </c>
+      <c r="G254" t="n">
+        <v>13.90999984741211</v>
+      </c>
+      <c r="H254" t="n">
+        <v>13.96000003814697</v>
+      </c>
+      <c r="I254" t="n">
+        <v>14.89000034332275</v>
+      </c>
+      <c r="J254" t="n">
+        <v>13.96000003814697</v>
+      </c>
+      <c r="K254" t="n">
+        <v>64470</v>
+      </c>
+      <c r="L254" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>Laxmi Cotspin Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>Laxmi Cotspin Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>GRAIL Inc. Faces Selling Pressure as Shares Dip Below $67 - Gamma Squeeze - Vinanet</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>Coastal Financial (CCB) Advances 2.71% as Shares Approach Key Resistance at $43 - Gap and Reverse - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>14</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>HSCL.NS</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Himadri Speciality Chemical Limited</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>755</v>
+      </c>
+      <c r="F255" t="n">
+        <v>767.5999755859375</v>
+      </c>
+      <c r="G255" t="n">
+        <v>695.5</v>
+      </c>
+      <c r="H255" t="n">
+        <v>704.2000122070312</v>
+      </c>
+      <c r="I255" t="n">
+        <v>750.25</v>
+      </c>
+      <c r="J255" t="n">
+        <v>704.2000122070312</v>
+      </c>
+      <c r="K255" t="n">
+        <v>12470045</v>
+      </c>
+      <c r="L255" t="n">
+        <v>-6.14</v>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>Himadri Speciality Chemical Ltd. (HSCL) Share Price Falls 7.32% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>Himadri Speciality Chemical Ltd. (HSCL) Share Price Falls 7.32% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr"/>
+      <c r="P255" t="inlineStr"/>
+      <c r="Q255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>15</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>DREDGECORP.NS</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Dredging Corporation of India Limited</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>1199</v>
+      </c>
+      <c r="F256" t="n">
+        <v>1204</v>
+      </c>
+      <c r="G256" t="n">
+        <v>1111.5</v>
+      </c>
+      <c r="H256" t="n">
+        <v>1118.300048828125</v>
+      </c>
+      <c r="I256" t="n">
+        <v>1189.199951171875</v>
+      </c>
+      <c r="J256" t="n">
+        <v>1118.300048828125</v>
+      </c>
+      <c r="K256" t="n">
+        <v>253496</v>
+      </c>
+      <c r="L256" t="n">
+        <v>-5.96</v>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr"/>
+      <c r="P256" t="inlineStr"/>
+      <c r="Q256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>16</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>GLOBECIVIL.NS</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Globe Civil Projects Limited</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>45.45999908447266</v>
+      </c>
+      <c r="F257" t="n">
+        <v>45.45999908447266</v>
+      </c>
+      <c r="G257" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="H257" t="n">
+        <v>42.34000015258789</v>
+      </c>
+      <c r="I257" t="n">
+        <v>44.97000122070312</v>
+      </c>
+      <c r="J257" t="n">
+        <v>42.34000015258789</v>
+      </c>
+      <c r="K257" t="n">
+        <v>102543</v>
+      </c>
+      <c r="L257" t="n">
+        <v>-5.85</v>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>Globe Civil Projects Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>Globe Civil Projects Limited Announces Q1 FY27 Results - Business Standard</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>Globe Civil Projects Limited Announces Q1 FY27 Results - Business Standard</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Femasys Inc. (FEMY) Q1 2026 Earnings: EPS Beat on Narrower Loss, Stock Slips - Dividend Earnings Report - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>17</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>SHREEJISPG.NS</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Shreeji Shipping Global Limited</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>657</v>
+      </c>
+      <c r="F258" t="n">
+        <v>661.9500122070312</v>
+      </c>
+      <c r="G258" t="n">
+        <v>609.8499755859375</v>
+      </c>
+      <c r="H258" t="n">
+        <v>613.3499755859375</v>
+      </c>
+      <c r="I258" t="n">
+        <v>649.4500122070312</v>
+      </c>
+      <c r="J258" t="n">
+        <v>613.3499755859375</v>
+      </c>
+      <c r="K258" t="n">
+        <v>1441160</v>
+      </c>
+      <c r="L258" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>Shreeji Shipping Global Ltd. (SHREEJISPG) Share Price Hits 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>Shreeji Shipping Global Q1 FY27: Net Profit Rises 19% YoY to ₹44.29 Cr - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>Shreeji Shipping Global Q1 FY27: Net Profit Rises 19% YoY to ₹44.29 Cr - Trade Brains</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr"/>
+      <c r="Q258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>18</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>AHLADA.NS</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Ahlada Engineers Limited</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>40.81999969482422</v>
+      </c>
+      <c r="F259" t="n">
+        <v>40.81999969482422</v>
+      </c>
+      <c r="G259" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="H259" t="n">
+        <v>38.59000015258789</v>
+      </c>
+      <c r="I259" t="n">
+        <v>40.81999969482422</v>
+      </c>
+      <c r="J259" t="n">
+        <v>38.59000015258789</v>
+      </c>
+      <c r="K259" t="n">
+        <v>42109</v>
+      </c>
+      <c r="L259" t="n">
+        <v>-5.46</v>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>Ahlada Engineers to hold 21st AGM on August 5, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>Ahlada Engineers Ltd is Rated Strong Sell - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>RYN Q1 2026 Earnings: EPS of $0.07 Delivers 112.94% Surprise, Shares Gain 1.82% - Management Tone Analysis - Vinanet</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>15 Best Bank Account Bonuses of August 2026: Earn Up to $3,000 in Cash Rewards - Next Quarter Guidance - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>Ahlada Engineers Ltd is Rated Strong Sell - MarketsMojo</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>19</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>DHABRIYA.NS</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Dhabriya Polywood Limited</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>600</v>
+      </c>
+      <c r="F260" t="n">
+        <v>600</v>
+      </c>
+      <c r="G260" t="n">
+        <v>548</v>
+      </c>
+      <c r="H260" t="n">
+        <v>555.25</v>
+      </c>
+      <c r="I260" t="n">
+        <v>587</v>
+      </c>
+      <c r="J260" t="n">
+        <v>555.25</v>
+      </c>
+      <c r="K260" t="n">
+        <v>59063</v>
+      </c>
+      <c r="L260" t="n">
+        <v>-5.41</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>DHABRIYA Share Price Today - Dhabriya Polywood Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>Dhabriya Polywood Ltd Income Statement – NSE:DHABRIYA - TradingView</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Dhabriya Polywood Ltd. Share Price and 52-Week High View - Univest</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Free float of Dhabriya Polywood Ltd – NSE:DHABRIYA - TradingView</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>Dhabriya Polywood Ltd. Share Price News: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:48 IST</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>20</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>TIJARIA.NS</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes Limited</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>6.119999885559082</v>
+      </c>
+      <c r="F261" t="n">
+        <v>6.289999961853027</v>
+      </c>
+      <c r="G261" t="n">
+        <v>5.619999885559082</v>
+      </c>
+      <c r="H261" t="n">
+        <v>5.789999961853027</v>
+      </c>
+      <c r="I261" t="n">
+        <v>6.119999885559082</v>
+      </c>
+      <c r="J261" t="n">
+        <v>5.789999961853027</v>
+      </c>
+      <c r="K261" t="n">
+        <v>209055</v>
+      </c>
+      <c r="L261" t="n">
+        <v>-5.39</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes Share Price Today, Tijaria Polypipes Stock Price Live NSE/BSE Updates - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes Q1 Results: Net loss widens 36% YoY to ₹36.11 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>Vardhman Jain Tijaria raises stake in Tijaria Polypipes to 4.33% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes board to approve Q2FY27 results, accept director resignation - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes appoints new independent director, renews auditor at 20th AGM - scanx.trade</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q261"/>
+  <dimension ref="A1:Q281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14709,8 +14709,6 @@
           <t>KJMC Financial Services net profit rises to ₹162.85 lakh in Q1FY26 - scanx.trade</t>
         </is>
       </c>
-      <c r="P245" t="inlineStr"/>
-      <c r="Q245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -15115,8 +15113,6 @@
           <t>Somi Conveyor Beltings Ltd. Share Price Near 52-Week Low - Univest</t>
         </is>
       </c>
-      <c r="P251" t="inlineStr"/>
-      <c r="Q251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -15383,8 +15379,6 @@
           <t>Bajaj Hindusthan Sugar Publishes Q1 FY27 Results Extracts and Sets Board Meeting - TipRanks</t>
         </is>
       </c>
-      <c r="P255" t="inlineStr"/>
-      <c r="Q255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -15444,8 +15438,6 @@
           <t>Pacific Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
-      <c r="P256" t="inlineStr"/>
-      <c r="Q256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -15505,8 +15497,6 @@
           <t>CG-VAK Software &amp; Exports Ltd - Equitypandit</t>
         </is>
       </c>
-      <c r="P257" t="inlineStr"/>
-      <c r="Q257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -15635,8 +15625,6 @@
           <t>Uttam Sugar Mills Share Price: Technical, Fundamental View - Univest</t>
         </is>
       </c>
-      <c r="P259" t="inlineStr"/>
-      <c r="Q259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -15701,7 +15689,6 @@
           <t>Swiss Military Consumer Goods equity shares admitted on NSE - scanx.trade</t>
         </is>
       </c>
-      <c r="Q260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -15766,7 +15753,1322 @@
           <t>Kohinoor Foods to Review Quarterly Results and Mull Fundraising at August Board Meeting - TipRanks</t>
         </is>
       </c>
-      <c r="Q261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>1</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>MPDL.NS</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>MPDL Limited</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>34.29999923706055</v>
+      </c>
+      <c r="F262" t="n">
+        <v>34.31999969482422</v>
+      </c>
+      <c r="G262" t="n">
+        <v>23.26000022888184</v>
+      </c>
+      <c r="H262" t="n">
+        <v>34.31999969482422</v>
+      </c>
+      <c r="I262" t="n">
+        <v>28.60000038146973</v>
+      </c>
+      <c r="J262" t="n">
+        <v>34.31999969482422</v>
+      </c>
+      <c r="K262" t="n">
+        <v>8795</v>
+      </c>
+      <c r="L262" t="n">
+        <v>20</v>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>MPDL Share Price Today - MPDL Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>MPDL Share Price Today - MPDL Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of MPDL Ltd – NSE:MPDL - TradingView</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>MPDL Ltd Q1 Results: Board approves financials for quarter ended June 30 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>MPDL reports consolidated net loss of Rs 4.20 crore in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>2</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>KJMCFIN.NS</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>66.34999847412109</v>
+      </c>
+      <c r="F263" t="n">
+        <v>66.41999816894531</v>
+      </c>
+      <c r="G263" t="n">
+        <v>61.90000152587891</v>
+      </c>
+      <c r="H263" t="n">
+        <v>66.41999816894531</v>
+      </c>
+      <c r="I263" t="n">
+        <v>55.34999847412109</v>
+      </c>
+      <c r="J263" t="n">
+        <v>66.41999816894531</v>
+      </c>
+      <c r="K263" t="n">
+        <v>3326</v>
+      </c>
+      <c r="L263" t="n">
+        <v>20</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services net profit rises to ₹162.85 lakh in Q1FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr"/>
+      <c r="Q263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>3</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>KRONOX.NS</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Limited</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>155.0099945068359</v>
+      </c>
+      <c r="F264" t="n">
+        <v>186.1900024414062</v>
+      </c>
+      <c r="G264" t="n">
+        <v>155.0099945068359</v>
+      </c>
+      <c r="H264" t="n">
+        <v>186.1900024414062</v>
+      </c>
+      <c r="I264" t="n">
+        <v>155.1600036621094</v>
+      </c>
+      <c r="J264" t="n">
+        <v>186.1900024414062</v>
+      </c>
+      <c r="K264" t="n">
+        <v>5888825</v>
+      </c>
+      <c r="L264" t="n">
+        <v>20</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>Kronox Lab shares hit 20% upper circuit as Indo Borax and Chemicals to acquire 64.26% stake - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>Indo Borax &amp; Chemicals Limited executed a Share Purchase Agreement to acquire 64.26% stake in Kronox Lab Sciences Limited from Ketan Vinodchandra Ramani, Pritesh Vinodchandra Ramani and Jogindersingh Gianchand Jaswal for INR 2.5 billion. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Share Price Rise With Peer Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>Indo Borax Approves Kronox Lab Stake Purchase; Shares Rise 7.44% - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>Momentum Stocks: Kronox Lab Sciences, Waterways Leisure, Genus Power rise up to % on sheer momentum - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>4</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>BANARISUG.NS</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Limited</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>3635</v>
+      </c>
+      <c r="F265" t="n">
+        <v>4338</v>
+      </c>
+      <c r="G265" t="n">
+        <v>3635</v>
+      </c>
+      <c r="H265" t="n">
+        <v>4240.7001953125</v>
+      </c>
+      <c r="I265" t="n">
+        <v>3617.39990234375</v>
+      </c>
+      <c r="J265" t="n">
+        <v>4240.7001953125</v>
+      </c>
+      <c r="K265" t="n">
+        <v>71288</v>
+      </c>
+      <c r="L265" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars secures Madras HC stay on ₹12.72 crore tax recovery - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>AfCFTA Trade Finance: Small Businesses Gain New Access via ITC-Equity Partnership - Earnings Weakness Phase - Vinanet</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>Stardust Power Inc. (SDST) Drops 5.95% as Stock Tests Key Support at $1.5 - Mutual Fund Flow - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>5</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>SOLARA.NS</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences Limited</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>551.9500122070312</v>
+      </c>
+      <c r="F266" t="n">
+        <v>654.4000244140625</v>
+      </c>
+      <c r="G266" t="n">
+        <v>551.9500122070312</v>
+      </c>
+      <c r="H266" t="n">
+        <v>640</v>
+      </c>
+      <c r="I266" t="n">
+        <v>550.0499877929688</v>
+      </c>
+      <c r="J266" t="n">
+        <v>640</v>
+      </c>
+      <c r="K266" t="n">
+        <v>6915514</v>
+      </c>
+      <c r="L266" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Today Up - Univest</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma shares jump 5% as Q1 profit rises 55%; Ibuprofen business remains a drag - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>SOLARA ACTIVE P Standalone June 2026 Net Sales at Rs 381.60 crore, up 19.57% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>6</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>SOMICONVEY.NS</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Somi Conveyor Beltings Limited</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>96</v>
+      </c>
+      <c r="F267" t="n">
+        <v>103.9300003051758</v>
+      </c>
+      <c r="G267" t="n">
+        <v>95</v>
+      </c>
+      <c r="H267" t="n">
+        <v>100.0699996948242</v>
+      </c>
+      <c r="I267" t="n">
+        <v>86.61000061035156</v>
+      </c>
+      <c r="J267" t="n">
+        <v>100.0699996948242</v>
+      </c>
+      <c r="K267" t="n">
+        <v>687119</v>
+      </c>
+      <c r="L267" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>Somi Conveyor Beltings Ltd. Share Price Today Up 19.97% - Univest</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>Somi Conveyor Beltings Ltd. Share Price Today Up 19.97% - Univest</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>Somi Conveyor Beltings Ltd. Share Price Near 52-Week Low - Univest</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr"/>
+      <c r="Q267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>7</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>KWIL.NS</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Kwality Wall's (India) Limited</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>38</v>
+      </c>
+      <c r="F268" t="n">
+        <v>44.29999923706055</v>
+      </c>
+      <c r="G268" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="H268" t="n">
+        <v>43.47000122070312</v>
+      </c>
+      <c r="I268" t="n">
+        <v>37.70999908447266</v>
+      </c>
+      <c r="J268" t="n">
+        <v>43.47000122070312</v>
+      </c>
+      <c r="K268" t="n">
+        <v>101230788</v>
+      </c>
+      <c r="L268" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>TMICC completes KWIL stake buy in HUL’s ice-cream demerger - Law.asia</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>Kwality Wall's (KWIL.NS) Gains 3.45%: Ice Cream Major Tests ₹34.66 Resistance - Supply Zone - Vinanet</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>HUL Demerger: Ice-Cream Business Spun off Into Kwality Wall’s; Record Date Set for 5 December - Groww</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>HUL completes acquisition of Zywie ventures; KWIL shares to be traded from Feb. 16 - The Hindu</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>Kwality Wall''s Stock Debuts After HUL Demerger - Rediff MoneyWiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>8</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>INDOBORAX.NS</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Indo Borax &amp; Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>439</v>
+      </c>
+      <c r="F269" t="n">
+        <v>509.8999938964844</v>
+      </c>
+      <c r="G269" t="n">
+        <v>431</v>
+      </c>
+      <c r="H269" t="n">
+        <v>498.1499938964844</v>
+      </c>
+      <c r="I269" t="n">
+        <v>433.8500061035156</v>
+      </c>
+      <c r="J269" t="n">
+        <v>498.1499938964844</v>
+      </c>
+      <c r="K269" t="n">
+        <v>6099190</v>
+      </c>
+      <c r="L269" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>Shareholders May Be More Conservative With Indo Borax &amp; Chemicals Limited's (NSE:INDOBORAX) CEO Compensation For Now - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>INDOBORAX Q2 FY2026 Earnings: Robust Revenue Growth of 22.9% Drives Strong EPS of ₹15.67 - EPS Consistency Score - Vinanet</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Indo Borax &amp; Chemicals Limited Receives Open Offer from Zenrock Chemicals for 83.43 Lakh Shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>INDOBORAX Mar 2026 Earnings: Steady Profitability Driven by Stable Input Costs and Consistent Demand - Investor Earnings Call - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>INDOBORAX.NS News: Latest Updates and Market Outlook - Vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>9</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>BAJAJHIND.NS</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>20.73999977111816</v>
+      </c>
+      <c r="F270" t="n">
+        <v>23.97999954223633</v>
+      </c>
+      <c r="G270" t="n">
+        <v>20.59000015258789</v>
+      </c>
+      <c r="H270" t="n">
+        <v>23.32999992370605</v>
+      </c>
+      <c r="I270" t="n">
+        <v>20.3799991607666</v>
+      </c>
+      <c r="J270" t="n">
+        <v>23.32999992370605</v>
+      </c>
+      <c r="K270" t="n">
+        <v>256544491</v>
+      </c>
+      <c r="L270" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Publishes Q1 FY27 Results Extracts and Sets Board Meeting - TipRanks</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr"/>
+      <c r="Q270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>10</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>PACIFICI.NS</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Pacific Industries Limited</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>133.5500030517578</v>
+      </c>
+      <c r="F271" t="n">
+        <v>159</v>
+      </c>
+      <c r="G271" t="n">
+        <v>133.5500030517578</v>
+      </c>
+      <c r="H271" t="n">
+        <v>150.9799957275391</v>
+      </c>
+      <c r="I271" t="n">
+        <v>133.5500030517578</v>
+      </c>
+      <c r="J271" t="n">
+        <v>150.9799957275391</v>
+      </c>
+      <c r="K271" t="n">
+        <v>8374</v>
+      </c>
+      <c r="L271" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>PACIFICI Share Price Today - Pacific Industries Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>PACIFICI Share Price Today - Pacific Industries Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Pacific Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr"/>
+      <c r="Q271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>11</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>CGVAK.NS</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>CG Vak Software &amp; Exports Limited</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>159</v>
+      </c>
+      <c r="F272" t="n">
+        <v>162.5500030517578</v>
+      </c>
+      <c r="G272" t="n">
+        <v>152.0099945068359</v>
+      </c>
+      <c r="H272" t="n">
+        <v>158.5800018310547</v>
+      </c>
+      <c r="I272" t="n">
+        <v>140.7299957275391</v>
+      </c>
+      <c r="J272" t="n">
+        <v>158.5800018310547</v>
+      </c>
+      <c r="K272" t="n">
+        <v>13494</v>
+      </c>
+      <c r="L272" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>CGVAK Share Price Today - CG-VAK Software &amp; Exports Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>CG-VAK Software &amp; Exports Ltd - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>CG-VAK Software &amp; Exports Ltd - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr"/>
+      <c r="Q272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>12</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>KOHINOOR.NS</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Limited</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>32.09999847412109</v>
+      </c>
+      <c r="F273" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G273" t="n">
+        <v>30.95000076293945</v>
+      </c>
+      <c r="H273" t="n">
+        <v>34.81000137329102</v>
+      </c>
+      <c r="I273" t="n">
+        <v>31.27000045776367</v>
+      </c>
+      <c r="J273" t="n">
+        <v>34.81000137329102</v>
+      </c>
+      <c r="K273" t="n">
+        <v>1739882</v>
+      </c>
+      <c r="L273" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd is Rated Strong Sell - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods to Review Quarterly Results and Mull Fundraising at August Board Meeting - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>13</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>UGARSUGAR.NS</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>The Ugar Sugar Works Limited</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>51.40000152587891</v>
+      </c>
+      <c r="F274" t="n">
+        <v>57.63999938964844</v>
+      </c>
+      <c r="G274" t="n">
+        <v>50.7599983215332</v>
+      </c>
+      <c r="H274" t="n">
+        <v>56.06999969482422</v>
+      </c>
+      <c r="I274" t="n">
+        <v>50.40999984741211</v>
+      </c>
+      <c r="J274" t="n">
+        <v>56.06999969482422</v>
+      </c>
+      <c r="K274" t="n">
+        <v>3789357</v>
+      </c>
+      <c r="L274" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>Only Three Days Left To Cash In On Ugar Sugar Works' (NSE:UGARSUGAR) Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>The Ugar Sugar Works Share Price Today: 9.09% Price Rise - Univest</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>The Ugar Sugar Works Ltd. (UGARSUGAR) Share Price Surges 8.63% Today - Univest</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>The Ugar Sugar Works Ltd. Share Price Today: Key Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>The Ugar Sugar Works Share Price Today: 9.09% Price Rise - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>14</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>KOTARISUG.NS</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Kothari Sugars And Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>27.8799991607666</v>
+      </c>
+      <c r="F275" t="n">
+        <v>31.39999961853027</v>
+      </c>
+      <c r="G275" t="n">
+        <v>27.68000030517578</v>
+      </c>
+      <c r="H275" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="I275" t="n">
+        <v>27.21999931335449</v>
+      </c>
+      <c r="J275" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="K275" t="n">
+        <v>1120625</v>
+      </c>
+      <c r="L275" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>Kothari Sugars And Chemicals Ltd. Share Price Up 13.34% - Univest</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>Kothari Sugars And Chemicals Ltd. Share Price Up 13.34% - Univest</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>Turkcell (TKC) Holds Above Support After Modest Gain as Resistance at $5.73 Looms - CTA Positioning - Vinanet</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>Are Wall Street Analysts Predicting PepsiCo Stock Will Climb or Sink? - Earnings Call Q&amp;A - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>15</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>RANASUG.NS</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Rana Sugars Limited</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>13.85999965667725</v>
+      </c>
+      <c r="F276" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G276" t="n">
+        <v>13.85999965667725</v>
+      </c>
+      <c r="H276" t="n">
+        <v>15.21000003814697</v>
+      </c>
+      <c r="I276" t="n">
+        <v>13.76000022888184</v>
+      </c>
+      <c r="J276" t="n">
+        <v>15.21000003814697</v>
+      </c>
+      <c r="K276" t="n">
+        <v>3630422</v>
+      </c>
+      <c r="L276" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>Two Harbors Investment Corp (TWO) Edges Lower to $12.09: Key Support and Resistance in Focus - BPI Bear Correction - Vinanet</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr"/>
+      <c r="Q276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>16</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>SAKHTISUG.NS</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Sakthi Sugars Limited</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>19.76000022888184</v>
+      </c>
+      <c r="F277" t="n">
+        <v>22.05999946594238</v>
+      </c>
+      <c r="G277" t="n">
+        <v>19.76000022888184</v>
+      </c>
+      <c r="H277" t="n">
+        <v>21.77000045776367</v>
+      </c>
+      <c r="I277" t="n">
+        <v>19.70000076293945</v>
+      </c>
+      <c r="J277" t="n">
+        <v>21.77000045776367</v>
+      </c>
+      <c r="K277" t="n">
+        <v>1960983</v>
+      </c>
+      <c r="L277" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>Sakthi Sugars Ltd. Share Price Rises 10.69%: Full Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>Sakthi Sugars Ltd. Share Price Rises 10.69%: Full Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>Sakthi Sugars Limited Appoints R. Jeysree to Head the Internal Audit Department(In-House), Effective August 13, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr"/>
+      <c r="Q277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>17</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>HUBTOWN.NS</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Hubtown Limited</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>180.4499969482422</v>
+      </c>
+      <c r="F278" t="n">
+        <v>205.6999969482422</v>
+      </c>
+      <c r="G278" t="n">
+        <v>180.0099945068359</v>
+      </c>
+      <c r="H278" t="n">
+        <v>198.8099975585938</v>
+      </c>
+      <c r="I278" t="n">
+        <v>180.1199951171875</v>
+      </c>
+      <c r="J278" t="n">
+        <v>198.8099975585938</v>
+      </c>
+      <c r="K278" t="n">
+        <v>4728946</v>
+      </c>
+      <c r="L278" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>Hubtown Q1 PAT slides 69% YoY to Rs 25 crore - Business Standard</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>Hubtown Ltd is Rated Strong Sell - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>Hubtown Consolidated June 2026 Net Sales at Rs 155.62 crore, down 16.96% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>Hubtown Q1 results FY27: PAT Rs 26 Cr, Revenue Rs 155 Cr - Univest</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>Hubtown makes Q1 FY27 earnings call audio available online - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>18</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>PVP.NS</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>PVP Ventures Limited</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>39.97000122070312</v>
+      </c>
+      <c r="F279" t="n">
+        <v>43.70000076293945</v>
+      </c>
+      <c r="G279" t="n">
+        <v>39.45999908447266</v>
+      </c>
+      <c r="H279" t="n">
+        <v>43.15000152587891</v>
+      </c>
+      <c r="I279" t="n">
+        <v>39.13000106811523</v>
+      </c>
+      <c r="J279" t="n">
+        <v>43.15000152587891</v>
+      </c>
+      <c r="K279" t="n">
+        <v>3957967</v>
+      </c>
+      <c r="L279" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>PVP Ventures Share Price Today With Price and Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>PVP Ventures Share Price Today With Price and Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd. Share Price Gain: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - Univest</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>19</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>VERANDA.NS</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Veranda Learning Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>236.8999938964844</v>
+      </c>
+      <c r="F280" t="n">
+        <v>265.8500061035156</v>
+      </c>
+      <c r="G280" t="n">
+        <v>236</v>
+      </c>
+      <c r="H280" t="n">
+        <v>255.8999938964844</v>
+      </c>
+      <c r="I280" t="n">
+        <v>233.6999969482422</v>
+      </c>
+      <c r="J280" t="n">
+        <v>255.8999938964844</v>
+      </c>
+      <c r="K280" t="n">
+        <v>9972204</v>
+      </c>
+      <c r="L280" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>Veranda Learning Solutions Q1 Results: Earnings call audio uploaded - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>Why are Crizac, Jaro, Veranda Learning and other e-learning stocks down today? Explained - Zee Business</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>Veranda Learning Solutions shareholders approve CMD reappointment - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>Veranda Learning Solutions discloses JSCEL scheme compliance updates - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>NCLT approves Veranda Learning Solutions subsidiary amalgamation - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>20</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>RAJSREESUG.NS</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Rajshree Sugars &amp; Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>37.0099983215332</v>
+      </c>
+      <c r="F281" t="n">
+        <v>40.79000091552734</v>
+      </c>
+      <c r="G281" t="n">
+        <v>37</v>
+      </c>
+      <c r="H281" t="n">
+        <v>40.38000106811523</v>
+      </c>
+      <c r="I281" t="n">
+        <v>36.90000152587891</v>
+      </c>
+      <c r="J281" t="n">
+        <v>40.38000106811523</v>
+      </c>
+      <c r="K281" t="n">
+        <v>746681</v>
+      </c>
+      <c r="L281" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>Rajshree Sugars Gains 3%: Sugar Sector Momentum and Key Levels for RAJSREESUG.NS - Stock Analysis - Vinanet</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>Rajshree Sugars &amp; Chemicals: Mild Decline Amid Consolidation near Support - Momentum Surge Alerts - Vinanet</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>RAJSREESUG Share Price Today - Rajshree Sugars &amp; Chemicals Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>Rajshree Sugars &amp; Chemicals Ltd: Stock Climbs 1.67%, Testing Key Resistance at ₹35.72 - Mean Reversion Trade - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>Rajshree Sugars &amp; Chemicals: Mild Decline Amid Consolidation near Support - Momentum Surge Alerts - Vinanet</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15779,7 +17081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q261"/>
+  <dimension ref="A1:Q281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29734,8 +31036,6 @@
           <t>DD Q1 2026 Earnings: EPS Surges Past Estimates by 10.4% as Shares Retreat 1.33% - Earnings Acceleration Picks - Vinanet</t>
         </is>
       </c>
-      <c r="P244" t="inlineStr"/>
-      <c r="Q244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -29800,7 +31100,6 @@
           <t>Addi Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
-      <c r="Q245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -29865,7 +31164,6 @@
           <t>Fennec (FENC) Technical Check: Adds 0.51% to Close at $11.89 at the Close; Current Setup: the Supplied Trading Band Runs From $11.30 to $12.48 - Throwback Trade - Vinanet</t>
         </is>
       </c>
-      <c r="Q246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -30063,8 +31361,6 @@
           <t>Enterprise value to EBIT forward of Wel-Dish. Incorporated – TSE:2901 - TradingView</t>
         </is>
       </c>
-      <c r="P249" t="inlineStr"/>
-      <c r="Q249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -30129,7 +31425,6 @@
           <t>Copper Hits Record High as "Dr. Copper" Sends Conflicting Economic Signals - Consensus Forecast Report - Vinanet</t>
         </is>
       </c>
-      <c r="Q250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -30263,7 +31558,6 @@
           <t>Shivansh Finserve: புதிய வளர்ச்சிக்கு முக்கிய முடிவு! பெரும் கையகப்படுத்துதல் திட்டம்? - Whalesbook</t>
         </is>
       </c>
-      <c r="Q252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -30328,7 +31622,6 @@
           <t>Balaxi Pharmaceuticals Q1 FY27: Strong Revenue Recovery Masks Deep Structural Concerns - MarketsMojo</t>
         </is>
       </c>
-      <c r="Q253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -30393,7 +31686,6 @@
           <t>Coastal Financial (CCB) Advances 2.71% as Shares Approach Key Resistance at $43 - Gap and Reverse - Vinanet</t>
         </is>
       </c>
-      <c r="Q254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -30448,9 +31740,6 @@
           <t>Himadri Speciality Chemical Ltd. (HSCL) Share Price Falls 7.32% Today - Univest</t>
         </is>
       </c>
-      <c r="O255" t="inlineStr"/>
-      <c r="P255" t="inlineStr"/>
-      <c r="Q255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -30505,9 +31794,6 @@
           <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
         </is>
       </c>
-      <c r="O256" t="inlineStr"/>
-      <c r="P256" t="inlineStr"/>
-      <c r="Q256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -30572,7 +31858,6 @@
           <t>Femasys Inc. (FEMY) Q1 2026 Earnings: EPS Beat on Narrower Loss, Stock Slips - Dividend Earnings Report - Vinanet</t>
         </is>
       </c>
-      <c r="Q257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -30632,8 +31917,6 @@
           <t>Shreeji Shipping Global Q1 FY27: Net Profit Rises 19% YoY to ₹44.29 Cr - Trade Brains</t>
         </is>
       </c>
-      <c r="P258" t="inlineStr"/>
-      <c r="Q258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -30839,6 +32122,1330 @@
       <c r="Q261" t="inlineStr">
         <is>
           <t>Tijaria Polypipes appoints new independent director, renews auditor at 20th AGM - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>1</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>TECILCHEM.NS</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>TECIL Chemicals and Hydro Power Limited</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>11.28999996185303</v>
+      </c>
+      <c r="F262" t="n">
+        <v>11.55000019073486</v>
+      </c>
+      <c r="G262" t="n">
+        <v>9</v>
+      </c>
+      <c r="H262" t="n">
+        <v>9.140000343322754</v>
+      </c>
+      <c r="I262" t="n">
+        <v>10.23999977111816</v>
+      </c>
+      <c r="J262" t="n">
+        <v>9.140000343322754</v>
+      </c>
+      <c r="K262" t="n">
+        <v>306021</v>
+      </c>
+      <c r="L262" t="n">
+        <v>-10.74</v>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>TECIL Chemicals (TECILCHEM) Declines to ₹11.6, Approaches Key Support Zone - McClellan Summation - Vinanet</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>Dollar Steadies as US-Iran Tensions Escalate; Yen Weakens on Pension Concerns - Profit Announcement - Vinanet</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>TECILCHEM Holds Support Amid Weakness – Key Levels to Watch - BPI Bear Correction - Vinanet</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>TECIL Chemicals (TECILCHEM.NS) Declines Nearly 3.5%, Approaches Key Support at ₹9.19 - Liquidity Order Flow - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>TECILCHEM.NS Q2 2025 Earnings: No Revenue, Net Loss Amid Minimal Business Activity - EBITDA Margin Trends - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>2</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>KAMANWALA.NS</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Kamanwala Housing Construction Limited</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>18.59000015258789</v>
+      </c>
+      <c r="F263" t="n">
+        <v>18.59000015258789</v>
+      </c>
+      <c r="G263" t="n">
+        <v>16.11000061035156</v>
+      </c>
+      <c r="H263" t="n">
+        <v>16.68000030517578</v>
+      </c>
+      <c r="I263" t="n">
+        <v>18.6299991607666</v>
+      </c>
+      <c r="J263" t="n">
+        <v>16.68000030517578</v>
+      </c>
+      <c r="K263" t="n">
+        <v>56343</v>
+      </c>
+      <c r="L263" t="n">
+        <v>-10.47</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>Kamanwala Housing Construction Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>Japanese stocks rebound as bond yields ease - Business Standard</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>Volume Gainers on August 19, 2026 at 3:00 PM IST - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>Horizon Industrial Parks IPO Day 3 Subscription Status: Issue Booked 0.30x So Far - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>Chinese stocks rebound as policy hopes build - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>3</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>GCSL.NS</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services Limited</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>526.2999877929688</v>
+      </c>
+      <c r="F264" t="n">
+        <v>540.9500122070312</v>
+      </c>
+      <c r="G264" t="n">
+        <v>470</v>
+      </c>
+      <c r="H264" t="n">
+        <v>482.0499877929688</v>
+      </c>
+      <c r="I264" t="n">
+        <v>521.7000122070312</v>
+      </c>
+      <c r="J264" t="n">
+        <v>482.0499877929688</v>
+      </c>
+      <c r="K264" t="n">
+        <v>615891</v>
+      </c>
+      <c r="L264" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services gets exchange nod for ₹7 crore warrant issue - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services Raises Capital via Preferential Allotment of Warrants to Promoter Group - TipRanks</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services Q1 Results: Revenue at ₹1,785 Mn, Net Profit ₹276 Mn - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services allots 5.55 lakh warrants to promoter group - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services Receives SEBI Show Cause Notice Over Taurian MPS Ltd IPO - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>4</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>MILKYMIST.NS</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Milky Mist Dairy Food Limited</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>207.8000030517578</v>
+      </c>
+      <c r="F265" t="n">
+        <v>211.8000030517578</v>
+      </c>
+      <c r="G265" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="H265" t="n">
+        <v>184.8899993896484</v>
+      </c>
+      <c r="I265" t="n">
+        <v>199.6499938964844</v>
+      </c>
+      <c r="J265" t="n">
+        <v>184.8899993896484</v>
+      </c>
+      <c r="K265" t="n">
+        <v>56530266</v>
+      </c>
+      <c r="L265" t="n">
+        <v>-7.39</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>Average basic shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>Milky Mist Dairy Food Ltd. Financial Statements – NSE:MILKYMIST - TradingView</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>MILKYMIST Share Price Today - Milky Mist Dairy Food Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>MILKYMIST Share Price Today - MILKY MIST DAIRY FOOD L Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>Milky Mist Dairy Food IPO listing date today. Here’s what GMP, experts hint ahead of debut - livemint.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>5</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>WEL.NS</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Wonder Electricals Limited</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>148.3999938964844</v>
+      </c>
+      <c r="F266" t="n">
+        <v>149.7799987792969</v>
+      </c>
+      <c r="G266" t="n">
+        <v>132</v>
+      </c>
+      <c r="H266" t="n">
+        <v>136.0399932861328</v>
+      </c>
+      <c r="I266" t="n">
+        <v>146.2599945068359</v>
+      </c>
+      <c r="J266" t="n">
+        <v>136.0399932861328</v>
+      </c>
+      <c r="K266" t="n">
+        <v>1505497</v>
+      </c>
+      <c r="L266" t="n">
+        <v>-6.99</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>Btab uses artificial intelligence to link global manufacturers with U.S. business buyers - Stock Titan</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>Btab uses artificial intelligence to link global manufacturers with U.S. business buyers - Stock Titan</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>Enterprise value to EBIT forward of Wel-Dish. Incorporated – TSE:2901 - TradingView</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr"/>
+      <c r="Q266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>6</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>ATAM.NS</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Atam Valves Limited</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>60.95000076293945</v>
+      </c>
+      <c r="F267" t="n">
+        <v>60.95000076293945</v>
+      </c>
+      <c r="G267" t="n">
+        <v>54.59999847412109</v>
+      </c>
+      <c r="H267" t="n">
+        <v>55.52999877929688</v>
+      </c>
+      <c r="I267" t="n">
+        <v>59.36000061035156</v>
+      </c>
+      <c r="J267" t="n">
+        <v>55.52999877929688</v>
+      </c>
+      <c r="K267" t="n">
+        <v>88804</v>
+      </c>
+      <c r="L267" t="n">
+        <v>-6.45</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>Atam Valves Q1 Results: Net profit falls 49% YoY to ₹63.5 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>Atam Valves Q1 Results: Net profit falls 49% YoY to ₹63.5 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>VRSN Q2 2026 Earnings: EPS Misses Consensus by 1.45% as Shares Decline 1.95% - ROIC Trend Report - Vinanet</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>Shivansh Finserve: புதிய வளர்ச்சிக்கு முக்கிய முடிவு! பெரும் கையகப்படுத்துதல் திட்டம்? - Whalesbook</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>7</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>DREDGECORP.NS</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Dredging Corporation of India Limited</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>1199</v>
+      </c>
+      <c r="F268" t="n">
+        <v>1204</v>
+      </c>
+      <c r="G268" t="n">
+        <v>1111.5</v>
+      </c>
+      <c r="H268" t="n">
+        <v>1118.300048828125</v>
+      </c>
+      <c r="I268" t="n">
+        <v>1189.199951171875</v>
+      </c>
+      <c r="J268" t="n">
+        <v>1118.300048828125</v>
+      </c>
+      <c r="K268" t="n">
+        <v>253496</v>
+      </c>
+      <c r="L268" t="n">
+        <v>-5.96</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr"/>
+      <c r="P268" t="inlineStr"/>
+      <c r="Q268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>8</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>GLOBECIVIL.NS</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Globe Civil Projects Limited</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>45.45999908447266</v>
+      </c>
+      <c r="F269" t="n">
+        <v>45.45999908447266</v>
+      </c>
+      <c r="G269" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="H269" t="n">
+        <v>42.34000015258789</v>
+      </c>
+      <c r="I269" t="n">
+        <v>44.97000122070312</v>
+      </c>
+      <c r="J269" t="n">
+        <v>42.34000015258789</v>
+      </c>
+      <c r="K269" t="n">
+        <v>102543</v>
+      </c>
+      <c r="L269" t="n">
+        <v>-5.85</v>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>Globe Civil Projects Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>Globe Civil Projects Limited Announces Q1 FY27 Results - Business Standard</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Globe Civil Projects Limited Announces Q1 FY27 Results - Business Standard</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>Femasys Inc. (FEMY) Q1 2026 Earnings: EPS Beat on Narrower Loss, Stock Slips - Dividend Earnings Report - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>9</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>DHABRIYA.NS</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Dhabriya Polywood Limited</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>600</v>
+      </c>
+      <c r="F270" t="n">
+        <v>600</v>
+      </c>
+      <c r="G270" t="n">
+        <v>548</v>
+      </c>
+      <c r="H270" t="n">
+        <v>555.25</v>
+      </c>
+      <c r="I270" t="n">
+        <v>587</v>
+      </c>
+      <c r="J270" t="n">
+        <v>555.25</v>
+      </c>
+      <c r="K270" t="n">
+        <v>59063</v>
+      </c>
+      <c r="L270" t="n">
+        <v>-5.41</v>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>DHABRIYA Share Price Today - Dhabriya Polywood Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>Dhabriya Polywood Ltd Income Statement – NSE:DHABRIYA - TradingView</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>Dhabriya Polywood Ltd. Share Price and 52-Week High View - Univest</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>Free float of Dhabriya Polywood Ltd – NSE:DHABRIYA - TradingView</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>Dhabriya Polywood Ltd. Share Price News: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>10</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>TIJARIA.NS</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes Limited</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>6.119999885559082</v>
+      </c>
+      <c r="F271" t="n">
+        <v>6.289999961853027</v>
+      </c>
+      <c r="G271" t="n">
+        <v>5.619999885559082</v>
+      </c>
+      <c r="H271" t="n">
+        <v>5.789999961853027</v>
+      </c>
+      <c r="I271" t="n">
+        <v>6.119999885559082</v>
+      </c>
+      <c r="J271" t="n">
+        <v>5.789999961853027</v>
+      </c>
+      <c r="K271" t="n">
+        <v>209055</v>
+      </c>
+      <c r="L271" t="n">
+        <v>-5.39</v>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes Share Price Today, Tijaria Polypipes Stock Price Live NSE/BSE Updates - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes Q1 Results: Net loss widens 36% YoY to ₹36.11 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Vardhman Jain Tijaria raises stake in Tijaria Polypipes to 4.33% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes board to approve Q2FY27 results, accept director resignation - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes appoints new independent director, renews auditor at 20th AGM - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>11</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>XTRANET.NS</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>161</v>
+      </c>
+      <c r="F272" t="n">
+        <v>166.5399932861328</v>
+      </c>
+      <c r="G272" t="n">
+        <v>155.6100006103516</v>
+      </c>
+      <c r="H272" t="n">
+        <v>160.1799926757812</v>
+      </c>
+      <c r="I272" t="n">
+        <v>169.1100006103516</v>
+      </c>
+      <c r="J272" t="n">
+        <v>160.1799926757812</v>
+      </c>
+      <c r="K272" t="n">
+        <v>961010</v>
+      </c>
+      <c r="L272" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>Aditya Infotech Share Price Up 4.27% Today; XtraNet Falls 4.35% - Univest</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies Ltd (XTRANET) Share Price - Business Today</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies Ltd (XTRANET) Share Price - Business Today</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>Stocks to Watch Today: BSE, United Spirits, Hyundai Motor, XtraNet Tech, Autoline Industries, EMS, Ramco... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies adopts fair disclosure code for UPSI - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>12</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>KEEPLEARN.NS</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>DSJ Keep Learning Limited</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>1.919999957084656</v>
+      </c>
+      <c r="F273" t="n">
+        <v>2</v>
+      </c>
+      <c r="G273" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H273" t="n">
+        <v>1.809999942779541</v>
+      </c>
+      <c r="I273" t="n">
+        <v>1.909999966621399</v>
+      </c>
+      <c r="J273" t="n">
+        <v>1.809999942779541</v>
+      </c>
+      <c r="K273" t="n">
+        <v>65231</v>
+      </c>
+      <c r="L273" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>DSJ Keep Learning Q1 Results: Net profit rises 66% YoY to ₹10 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>DSJ Keep Learning Posts Q1 FY27 Unaudited Results in Line with SEBI Norms - TipRanks</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>DSJ Keep Learning Posts Q1 FY27 Unaudited Results in Line with SEBI Norms - TipRanks</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr"/>
+      <c r="Q273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>13</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>CALSOFT.NS</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>California Software Company Limited</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>29.88999938964844</v>
+      </c>
+      <c r="F274" t="n">
+        <v>29.88999938964844</v>
+      </c>
+      <c r="G274" t="n">
+        <v>27.04999923706055</v>
+      </c>
+      <c r="H274" t="n">
+        <v>27.04999923706055</v>
+      </c>
+      <c r="I274" t="n">
+        <v>28.46999931335449</v>
+      </c>
+      <c r="J274" t="n">
+        <v>27.04999923706055</v>
+      </c>
+      <c r="K274" t="n">
+        <v>1227668</v>
+      </c>
+      <c r="L274" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>CALSOFT Stock Price and Chart — NSE:CALSOFT - TradingView</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>CALSOFT Stock Price and Chart — NSE:CALSOFT - TradingView</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr"/>
+      <c r="P274" t="inlineStr"/>
+      <c r="Q274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>14</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>INDOTHAI.NS</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Limited</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>62.79999923706055</v>
+      </c>
+      <c r="F275" t="n">
+        <v>62.79999923706055</v>
+      </c>
+      <c r="G275" t="n">
+        <v>62.79999923706055</v>
+      </c>
+      <c r="H275" t="n">
+        <v>62.79999923706055</v>
+      </c>
+      <c r="I275" t="n">
+        <v>66.09999847412109</v>
+      </c>
+      <c r="J275" t="n">
+        <v>62.79999923706055</v>
+      </c>
+      <c r="K275" t="n">
+        <v>44689</v>
+      </c>
+      <c r="L275" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>Stock Watch: Shares Of These 10 Companies Slumped And Surged Over 5% Today - Do You Own Any? - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Ltd. (INDOTHAI) Share Price Hits Fresh 52-Week Low - Univest</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Ltd. (INDOTHAI) Share Price Hits Fresh 52-Week Low - Univest</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr"/>
+      <c r="Q275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>15</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>SVGLOBAL.NS</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>S V Global Mill Limited</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="F276" t="n">
+        <v>143.4900054931641</v>
+      </c>
+      <c r="G276" t="n">
+        <v>120.9300003051758</v>
+      </c>
+      <c r="H276" t="n">
+        <v>123.5299987792969</v>
+      </c>
+      <c r="I276" t="n">
+        <v>130</v>
+      </c>
+      <c r="J276" t="n">
+        <v>123.5299987792969</v>
+      </c>
+      <c r="K276" t="n">
+        <v>363</v>
+      </c>
+      <c r="L276" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of S V Global Mill Ltd. – NSE:SVGLOBAL - TradingView</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>SV Global Mill Ltd. Share Price Up 10.44%: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>SVGLOBAL Share Price Today - S V Global Mill Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>SV Global Mill Ltd. Share Price Up 10.44%: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>S V Global Mill Limited Announces Resignation of B. Parameswar as Key Managerial Personnel, Effective August 3, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>16</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>ABANSENT.NS</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Abans Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>28.79000091552734</v>
+      </c>
+      <c r="F277" t="n">
+        <v>29.98999977111816</v>
+      </c>
+      <c r="G277" t="n">
+        <v>27.36000061035156</v>
+      </c>
+      <c r="H277" t="n">
+        <v>27.36000061035156</v>
+      </c>
+      <c r="I277" t="n">
+        <v>28.79000091552734</v>
+      </c>
+      <c r="J277" t="n">
+        <v>27.36000061035156</v>
+      </c>
+      <c r="K277" t="n">
+        <v>22519</v>
+      </c>
+      <c r="L277" t="n">
+        <v>-4.97</v>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>Abans Enterprises (ABANSENT.NS) Gains 1.63%: Support Holds Near ₹26.07 - Channel Breakout - Vinanet</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>ABANSENT.NS Mar 2026 Earnings: Modest EPS of ₹0.15 Despite Revenue Decline - Revenue Surprise History - Vinanet</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>Abans Enterprises Gains 3% as Stock Approaches Key Resistance — ABANSENT.NS - Zero Lag EMA - Vinanet</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>Abans Enterprises (ABANSENT.NS) Surges 3.96% – Support and Resistance Levels in Focus - Zero Gamma Level - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>Abans Enterprises Slips 5% as Stock Tests Crucial Support Levels - Earnings Sentiment - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>17</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>KSR.NS</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>KSR Footwear Limited</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>28.51000022888184</v>
+      </c>
+      <c r="F278" t="n">
+        <v>30</v>
+      </c>
+      <c r="G278" t="n">
+        <v>27</v>
+      </c>
+      <c r="H278" t="n">
+        <v>27.42000007629395</v>
+      </c>
+      <c r="I278" t="n">
+        <v>28.84000015258789</v>
+      </c>
+      <c r="J278" t="n">
+        <v>27.42000007629395</v>
+      </c>
+      <c r="K278" t="n">
+        <v>77833</v>
+      </c>
+      <c r="L278" t="n">
+        <v>-4.92</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>KSR Footwear Standalone June 2026 Net Sales at Rs 52.25 crore, up 0.36% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>Kalen "Big K" Edwards Shares Words of Wisdom from the Changing Kentucky Trenches - On3</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>KSR Footwear Q1 Results: Net profit turns positive at ₹3.17 million - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>KSR Footwear dispatches FY26 annual report, sets August 24 AGM date - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>Kalen "Big K" Edwards Shares Words of Wisdom from the Changing Kentucky Trenches - On3</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>18</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>ALPHAGEO.NS</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Alphageo (India) Limited</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="F279" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="G279" t="n">
+        <v>328.1400146484375</v>
+      </c>
+      <c r="H279" t="n">
+        <v>328.6600036621094</v>
+      </c>
+      <c r="I279" t="n">
+        <v>345.4100036621094</v>
+      </c>
+      <c r="J279" t="n">
+        <v>328.6600036621094</v>
+      </c>
+      <c r="K279" t="n">
+        <v>34455</v>
+      </c>
+      <c r="L279" t="n">
+        <v>-4.85</v>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>Alphageo Standalone June 2026 Net Sales at Rs 54.38 crore, up 33.14% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>Alphageo (India) Ltd Upgraded to Hold on Technical and Financial Improvements - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>Alphageo (India) Ltd. Share Price News and Price Action - Univest</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>Alphageo promoter Anisha Alla sells 2,100 shares on market - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>Alphageo promoter Sashank Alla sells 1,500 equity shares on market - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>19</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>LAOPALA.NS</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>La Opala RG Limited</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>182.0500030517578</v>
+      </c>
+      <c r="F280" t="n">
+        <v>182.0500030517578</v>
+      </c>
+      <c r="G280" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="H280" t="n">
+        <v>178.3500061035156</v>
+      </c>
+      <c r="I280" t="n">
+        <v>187.2400054931641</v>
+      </c>
+      <c r="J280" t="n">
+        <v>178.3500061035156</v>
+      </c>
+      <c r="K280" t="n">
+        <v>395733</v>
+      </c>
+      <c r="L280" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>Interested In La Opala RG's (NSE:LAOPALA) Upcoming ₹5.00 Dividend? You Have Two Days Left - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>Mazagon Dock and 9 Other Stocks in Focus as They Turn Ex-Dividend Tomorrow - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>La Opala RG's (NSE:LAOPALA) Anemic Earnings Might Be Worse Than You Think - webull.com</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>La Opala RG Limited Releases Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>La Opala RG sets Aug 20 record date for ₹5 dividend - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>20</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>TAKE.NS</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>TAKE Limited</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>23.3700008392334</v>
+      </c>
+      <c r="F281" t="n">
+        <v>23.3700008392334</v>
+      </c>
+      <c r="G281" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="H281" t="n">
+        <v>21.84000015258789</v>
+      </c>
+      <c r="I281" t="n">
+        <v>22.88999938964844</v>
+      </c>
+      <c r="J281" t="n">
+        <v>21.84000015258789</v>
+      </c>
+      <c r="K281" t="n">
+        <v>611881</v>
+      </c>
+      <c r="L281" t="n">
+        <v>-4.59</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>GTA 6 leaks cause minor Take-Two stock jump; fo... - Pluang</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive stock steadies as GTA VI launch and fresh guidance shape 2026 outlook - Ad-hoc-news.de</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>Wall Street analysts just called this healthcare stock a buy — here’s our take - CNBC</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>Take-Two director Michael Sheresky sells $31,116 in shares By Investing.com - Investing.com India</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>LLY Stock: Where Compounding Could Take The Price - Trefis</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q281"/>
+  <dimension ref="A1:Q301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15881,8 +15881,6 @@
           <t>KJMC Financial Services net profit rises to ₹162.85 lakh in Q1FY26 - scanx.trade</t>
         </is>
       </c>
-      <c r="P263" t="inlineStr"/>
-      <c r="Q263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -16149,8 +16147,6 @@
           <t>Somi Conveyor Beltings Ltd. Share Price Near 52-Week Low - Univest</t>
         </is>
       </c>
-      <c r="P267" t="inlineStr"/>
-      <c r="Q267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -16348,8 +16344,6 @@
           <t>Bajaj Hindusthan Sugar Publishes Q1 FY27 Results Extracts and Sets Board Meeting - TipRanks</t>
         </is>
       </c>
-      <c r="P270" t="inlineStr"/>
-      <c r="Q270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -16409,8 +16403,6 @@
           <t>Pacific Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
-      <c r="P271" t="inlineStr"/>
-      <c r="Q271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -16470,8 +16462,6 @@
           <t>CG-VAK Software &amp; Exports Ltd - Equitypandit</t>
         </is>
       </c>
-      <c r="P272" t="inlineStr"/>
-      <c r="Q272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -16536,7 +16526,6 @@
           <t>Kohinoor Foods to Review Quarterly Results and Mull Fundraising at August Board Meeting - TipRanks</t>
         </is>
       </c>
-      <c r="Q273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -16670,7 +16659,6 @@
           <t>Are Wall Street Analysts Predicting PepsiCo Stock Will Climb or Sink? - Earnings Call Q&amp;A - Vinanet</t>
         </is>
       </c>
-      <c r="Q275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -16730,8 +16718,6 @@
           <t>Two Harbors Investment Corp (TWO) Edges Lower to $12.09: Key Support and Resistance in Focus - BPI Bear Correction - Vinanet</t>
         </is>
       </c>
-      <c r="P276" t="inlineStr"/>
-      <c r="Q276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -16791,8 +16777,6 @@
           <t>Sakthi Sugars Limited Appoints R. Jeysree to Head the Internal Audit Department(In-House), Effective August 13, 2026 - marketscreener.com</t>
         </is>
       </c>
-      <c r="P277" t="inlineStr"/>
-      <c r="Q277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -17067,6 +17051,1350 @@
       <c r="Q281" t="inlineStr">
         <is>
           <t>Rajshree Sugars &amp; Chemicals: Mild Decline Amid Consolidation near Support - Momentum Surge Alerts - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>1</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>KRONOX.NS</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Limited</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>155.0099945068359</v>
+      </c>
+      <c r="F282" t="n">
+        <v>186.1900024414062</v>
+      </c>
+      <c r="G282" t="n">
+        <v>155.0099945068359</v>
+      </c>
+      <c r="H282" t="n">
+        <v>186.1900024414062</v>
+      </c>
+      <c r="I282" t="n">
+        <v>155.1600036621094</v>
+      </c>
+      <c r="J282" t="n">
+        <v>186.1900024414062</v>
+      </c>
+      <c r="K282" t="n">
+        <v>5889347</v>
+      </c>
+      <c r="L282" t="n">
+        <v>20</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>Indo Borax Approves Kronox Lab Stake Purchase; Shares Rise 7.44% - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>Vadodara-based Kronox Lab Sciences to change hands 2 yrs after listing - BusinessLine</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>Kronox Lab shares hit 20% upper circuit as Indo Borax and Chemicals to acquire 64.26% stake - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Share Price Rise With Peer Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences promoters sell 64.26% stake to Indo Borax - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>2</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>SOLARA.NS</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences Limited</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>551.9500122070312</v>
+      </c>
+      <c r="F283" t="n">
+        <v>654.4000244140625</v>
+      </c>
+      <c r="G283" t="n">
+        <v>551.9500122070312</v>
+      </c>
+      <c r="H283" t="n">
+        <v>640</v>
+      </c>
+      <c r="I283" t="n">
+        <v>550.0499877929688</v>
+      </c>
+      <c r="J283" t="n">
+        <v>640</v>
+      </c>
+      <c r="K283" t="n">
+        <v>6915687</v>
+      </c>
+      <c r="L283" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>SOLARA ACTIVE P Consolidated June 2026 Net Sales at Rs 381.60 crore, up 19.57% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Today Up - Univest</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences revises CIO Ajit Manocha’s joining date - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>3</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>KWIL.NS</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Kwality Wall's (India) Limited</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>38</v>
+      </c>
+      <c r="F284" t="n">
+        <v>44.29999923706055</v>
+      </c>
+      <c r="G284" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="H284" t="n">
+        <v>43.47000122070312</v>
+      </c>
+      <c r="I284" t="n">
+        <v>37.70999908447266</v>
+      </c>
+      <c r="J284" t="n">
+        <v>43.47000122070312</v>
+      </c>
+      <c r="K284" t="n">
+        <v>101299688</v>
+      </c>
+      <c r="L284" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>TMICC completes KWIL stake buy in HUL’s ice-cream demerger - Law.asia</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>Kwality Wall's (KWIL) Consolidates Near Support as Price Action Remains Range-Bound - Technical Analysis Picks - Vinanet</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>HUL Demerger: Ice-Cream Business Spun off Into Kwality Wall’s; Record Date Set for 5 December - Groww</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>HUL completes acquisition of Zywie ventures; KWIL shares to be traded from Feb. 16 - The Hindu</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>Kwality Wall''s Stock Debuts After HUL Demerger - Rediff MoneyWiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>4</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>INDOBORAX.NS</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Indo Borax &amp; Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>439</v>
+      </c>
+      <c r="F285" t="n">
+        <v>509.8999938964844</v>
+      </c>
+      <c r="G285" t="n">
+        <v>431</v>
+      </c>
+      <c r="H285" t="n">
+        <v>498.1499938964844</v>
+      </c>
+      <c r="I285" t="n">
+        <v>433.8500061035156</v>
+      </c>
+      <c r="J285" t="n">
+        <v>498.1499938964844</v>
+      </c>
+      <c r="K285" t="n">
+        <v>6099644</v>
+      </c>
+      <c r="L285" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>Indo Borax &amp; Chemicals Limited Shareholders Approve All Board Appointments Through Postal Ballot - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>INDOBORAX Q2 2026 Earnings: Revenue Surges 22.93% YoY, EPS Stands at ₹15.67 - High Growth Earnings - Vinanet</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>Shareholders May Be More Conservative With Indo Borax &amp; Chemicals Limited's (NSE:INDOBORAX) CEO Compensation For Now - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>INDOBORAX Mar 2026 Earnings: Steady Profitability Driven by Stable Input Costs and Consistent Demand - Investor Earnings Call - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>INDOBORAX.NS News: Latest Updates and Market Outlook - Vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>5</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>BAJAJHIND.NS</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>20.73999977111816</v>
+      </c>
+      <c r="F286" t="n">
+        <v>23.97999954223633</v>
+      </c>
+      <c r="G286" t="n">
+        <v>20.59000015258789</v>
+      </c>
+      <c r="H286" t="n">
+        <v>23.32999992370605</v>
+      </c>
+      <c r="I286" t="n">
+        <v>20.3799991607666</v>
+      </c>
+      <c r="J286" t="n">
+        <v>23.32999992370605</v>
+      </c>
+      <c r="K286" t="n">
+        <v>256556792</v>
+      </c>
+      <c r="L286" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr"/>
+      <c r="P286" t="inlineStr"/>
+      <c r="Q286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>6</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>UTTAMSUGAR.NS</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Limited</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>303.0899963378906</v>
+      </c>
+      <c r="F287" t="n">
+        <v>344</v>
+      </c>
+      <c r="G287" t="n">
+        <v>301.8500061035156</v>
+      </c>
+      <c r="H287" t="n">
+        <v>336.2200012207031</v>
+      </c>
+      <c r="I287" t="n">
+        <v>300.989990234375</v>
+      </c>
+      <c r="J287" t="n">
+        <v>336.2200012207031</v>
+      </c>
+      <c r="K287" t="n">
+        <v>2301215</v>
+      </c>
+      <c r="L287" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Ltd. Stock News: Price Increase Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Share Price Jumps; Technicals in Focus - Univest</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Share Price: Technical, Fundamental View - Univest</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Share Price Jumps; Technicals in Focus - Univest</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>7</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>KOHINOOR.NS</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Limited</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>32.09999847412109</v>
+      </c>
+      <c r="F288" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G288" t="n">
+        <v>30.95000076293945</v>
+      </c>
+      <c r="H288" t="n">
+        <v>34.81000137329102</v>
+      </c>
+      <c r="I288" t="n">
+        <v>31.27000045776367</v>
+      </c>
+      <c r="J288" t="n">
+        <v>34.81000137329102</v>
+      </c>
+      <c r="K288" t="n">
+        <v>1740167</v>
+      </c>
+      <c r="L288" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>Kohinoor Textile to install 48MW battery storage amid 9MW solar expansion - Business Recorder</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd is Rated Strong Sell - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods to Review Quarterly Results and Mull Fundraising at August Board Meeting - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>8</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>RANASUG.NS</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Rana Sugars Limited</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>13.85999965667725</v>
+      </c>
+      <c r="F289" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G289" t="n">
+        <v>13.85999965667725</v>
+      </c>
+      <c r="H289" t="n">
+        <v>15.21000003814697</v>
+      </c>
+      <c r="I289" t="n">
+        <v>13.76000022888184</v>
+      </c>
+      <c r="J289" t="n">
+        <v>15.21000003814697</v>
+      </c>
+      <c r="K289" t="n">
+        <v>3647306</v>
+      </c>
+      <c r="L289" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr"/>
+      <c r="P289" t="inlineStr"/>
+      <c r="Q289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>9</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>KAYA.NS</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Kaya Limited</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>339.9500122070312</v>
+      </c>
+      <c r="F290" t="n">
+        <v>385</v>
+      </c>
+      <c r="G290" t="n">
+        <v>336.5499877929688</v>
+      </c>
+      <c r="H290" t="n">
+        <v>374.1000061035156</v>
+      </c>
+      <c r="I290" t="n">
+        <v>338.4500122070312</v>
+      </c>
+      <c r="J290" t="n">
+        <v>374.1000061035156</v>
+      </c>
+      <c r="K290" t="n">
+        <v>245362</v>
+      </c>
+      <c r="L290" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Scholastic director Kaya Henderson sells $130,812 in stock - Investing.com</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>Wladimir Klitschko vows to protect Hayden Panettiere’s memory for daughter Kaya as WWE star Jacob Fatu sh - The Times of India</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>Wladimir Klitschko vows to protect Hayden Panettiere’s memory for daughter Kaya as WWE star Jacob Fatu sh - The Times of India</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>Kaya To Issue 1.82 Million Equity Shares At 274.10 Rupees Per Share For Aggregate Cash Consideration Of Approx 500 Million Rupees - TradingView</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>Kaya Standalone June 2026 Net Sales at Rs 60.14 crore, up 13.91% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>10</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>HUBTOWN.NS</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Hubtown Limited</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>180.4499969482422</v>
+      </c>
+      <c r="F291" t="n">
+        <v>205.6999969482422</v>
+      </c>
+      <c r="G291" t="n">
+        <v>180.0099945068359</v>
+      </c>
+      <c r="H291" t="n">
+        <v>198.8099975585938</v>
+      </c>
+      <c r="I291" t="n">
+        <v>180.1199951171875</v>
+      </c>
+      <c r="J291" t="n">
+        <v>198.8099975585938</v>
+      </c>
+      <c r="K291" t="n">
+        <v>4731451</v>
+      </c>
+      <c r="L291" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>Hubtown Ltd. Share Price Up 9.01%: Price, Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>Hubtown Ltd. Share Price Up 9.01%: Price, Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>Hubtown Q1 PAT slides 69% YoY to Rs 25 crore - Business Standard</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>Hubtown Consolidated June 2026 Net Sales at Rs 155.62 crore, down 16.96% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>Hubtown makes Q1 FY27 earnings call audio available online - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>11</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>CORDELIA.NS</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Waterways Leisure Tourism Limited</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>820.5499877929688</v>
+      </c>
+      <c r="F292" t="n">
+        <v>907.75</v>
+      </c>
+      <c r="G292" t="n">
+        <v>820.5499877929688</v>
+      </c>
+      <c r="H292" t="n">
+        <v>907.75</v>
+      </c>
+      <c r="I292" t="n">
+        <v>825.25</v>
+      </c>
+      <c r="J292" t="n">
+        <v>907.75</v>
+      </c>
+      <c r="K292" t="n">
+        <v>700284</v>
+      </c>
+      <c r="L292" t="n">
+        <v>10</v>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>Cordelia Cruises Share Price Falls 7.71% to Rs 842.25 After Q1 Results - Univest</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>Josh Da Costa Shares Another Facet of New Wave Graveyard with the Hypnagogic (and Possibly Psychic) “Cordelia” - floodmagazine.com</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>Josh Da Costa Shares Another Facet of New Wave Graveyard with the Hypnagogic (and Possibly Psychic) “Cordelia” - floodmagazine.com</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr"/>
+      <c r="Q292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>12</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>VERANDA.NS</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Veranda Learning Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>236.8999938964844</v>
+      </c>
+      <c r="F293" t="n">
+        <v>265.8500061035156</v>
+      </c>
+      <c r="G293" t="n">
+        <v>236</v>
+      </c>
+      <c r="H293" t="n">
+        <v>255.8999938964844</v>
+      </c>
+      <c r="I293" t="n">
+        <v>233.6999969482422</v>
+      </c>
+      <c r="J293" t="n">
+        <v>255.8999938964844</v>
+      </c>
+      <c r="K293" t="n">
+        <v>9972226</v>
+      </c>
+      <c r="L293" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>Veranda Learning Solutions shareholders approve CMD reappointment - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>Why are Crizac, Jaro, Veranda Learning and other e-learning stocks down today? Explained - Zee Business</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>Veranda Learning Solutions Q1 Results: Earnings call audio uploaded - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>Veranda Learning Solutions discloses JSCEL scheme compliance updates - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>NCLT approves Veranda Learning Solutions subsidiary amalgamation - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>13</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>ORIENTCER.NS</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>ORIENT CERATECH LIMITED</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>43</v>
+      </c>
+      <c r="F294" t="n">
+        <v>47.22999954223633</v>
+      </c>
+      <c r="G294" t="n">
+        <v>42.52000045776367</v>
+      </c>
+      <c r="H294" t="n">
+        <v>46.72999954223633</v>
+      </c>
+      <c r="I294" t="n">
+        <v>43.11999893188477</v>
+      </c>
+      <c r="J294" t="n">
+        <v>46.72999954223633</v>
+      </c>
+      <c r="K294" t="n">
+        <v>353057</v>
+      </c>
+      <c r="L294" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>Do Its Financials Have Any Role To Play In Driving Orient Ceratech Limited's (NSE:ORIENTCER) Stock Up Recently? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>ORIENTCER.NS Mar 2026 Earnings: EPS of ₹0.43 on Revenue of ₹95.24 Crore; Stock Gains 2.37% - Post-Earnings Reaction - Vinanet</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>ORIENTCER.NS Mar 2026 Earnings: EPS of ₹0.43 on Revenue of ₹95.24 Crore; Stock Gains 2.37% - Post-Earnings Reaction - Vinanet</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>Ashapura International Limited Increases Shareholding in Orient Ceratech Limited to 8.35% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>ORIENT CERATECH Limited (ORIENTCER.NS): Modest Uptick Amid Range-Bound Trading - OBV Trend Line - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>14</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>KRYSTAL.NS</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Krystal Integrated Services Limited</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>635</v>
+      </c>
+      <c r="F295" t="n">
+        <v>689</v>
+      </c>
+      <c r="G295" t="n">
+        <v>620.7000122070312</v>
+      </c>
+      <c r="H295" t="n">
+        <v>681.3499755859375</v>
+      </c>
+      <c r="I295" t="n">
+        <v>629.4500122070312</v>
+      </c>
+      <c r="J295" t="n">
+        <v>681.3499755859375</v>
+      </c>
+      <c r="K295" t="n">
+        <v>688365</v>
+      </c>
+      <c r="L295" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>Krystal Integrated Services Shares Gain 4% on Rs 134 Crore Order - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>Krystal Integrated Services Ltd (KRYSTAL) Share Price Rises 8.53% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>Krystal Integrated Services Ltd (KRYSTAL) Share Price Rises 8.53% Today - Univest</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>Small-cap stock jumps after receipt of ₹134 crore order from Maharashtra Road Transport - livemint.com</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>Krystal Integrated Services makes decent debut, lists at 9.7% premium on NSE - Upstox</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>15</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>GENUSPOWER.NS</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Genus Power Infrastructures Limited</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>310.8999938964844</v>
+      </c>
+      <c r="F296" t="n">
+        <v>340.8999938964844</v>
+      </c>
+      <c r="G296" t="n">
+        <v>310.8999938964844</v>
+      </c>
+      <c r="H296" t="n">
+        <v>334.25</v>
+      </c>
+      <c r="I296" t="n">
+        <v>309.2999877929688</v>
+      </c>
+      <c r="J296" t="n">
+        <v>334.25</v>
+      </c>
+      <c r="K296" t="n">
+        <v>16393463</v>
+      </c>
+      <c r="L296" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>GENUSPOWER Forecast — Price Target — Prediction for 2027 - TradingView</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>Genus Power Q2 2026 Earnings: Revenue Surges 94.55% YoY, EPS at ₹21.29 - Revenue Warning Signal - Vinanet</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>Genus Power Infrastructures (NSE:GENUSPOWER) Strong Profits May Be Masking Some Underlying Issues - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>Genus Power Infrastructures Limited (GENUSPOWER.NS) – Moderate Decline on Profit Booking Amid Sector Headwinds - Symmetrical Triangle - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>Genus Power Infrastructures Limited's (NSE:GENUSPOWER) Stock Has Been Sliding But Fundamentals Look Strong: Is The Market Wrong? - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>16</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>JNPR.NS</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Juniper Green Energy Limited</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>252.8099975585938</v>
+      </c>
+      <c r="F297" t="n">
+        <v>275.5199890136719</v>
+      </c>
+      <c r="G297" t="n">
+        <v>251.7299957275391</v>
+      </c>
+      <c r="H297" t="n">
+        <v>273.760009765625</v>
+      </c>
+      <c r="I297" t="n">
+        <v>253.7100067138672</v>
+      </c>
+      <c r="J297" t="n">
+        <v>273.760009765625</v>
+      </c>
+      <c r="K297" t="n">
+        <v>7029425</v>
+      </c>
+      <c r="L297" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>JNPR Share Price Today - Juniper Green Energy Ltd. Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise (HPE Stock) Is Buying Juniper Networks (JNPR Stock) For New AI Technology Solar Flare (dzB5EnUYhH) - Mshale</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>JNPR Share Price Today - Juniper Green Energy Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>Juniper Green Energy Ltd Share Price Today,, JNPR Share Price NSE, BSE - Business Today</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise (HPE Stock) Is Buying Juniper Networks (JNPR Stock) For New AI Technology Solar Flare (dzB5EnUYhH) - Mshale</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>17</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>RENUKA.NS</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Shree Renuka Sugars Limited</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>24.70000076293945</v>
+      </c>
+      <c r="F298" t="n">
+        <v>26.43000030517578</v>
+      </c>
+      <c r="G298" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H298" t="n">
+        <v>26.1299991607666</v>
+      </c>
+      <c r="I298" t="n">
+        <v>24.23999977111816</v>
+      </c>
+      <c r="J298" t="n">
+        <v>26.1299991607666</v>
+      </c>
+      <c r="K298" t="n">
+        <v>95136169</v>
+      </c>
+      <c r="L298" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>Shree Renuka Sugars Ltd. Share Price: 8.7% Gain Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>Shree Renuka Sugars Ltd. Share Price: 8.7% Gain Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>Balrampur Chini, Bajaj Hind, Shree Renuka shares rise up to 13%; here's why - Business Today</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>Bajaj Hind, Dwarikesh, Renuka rally up to 14%; what's driving sugar stocks? - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>Sweet Gains Continue: Shree Renuka, Dalmia Bharat Rally Up To 7% Despite Govt's Inventory Clampdown - NDTV Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>18</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>DHAMPURSUG.NS</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Limited</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>179.6999969482422</v>
+      </c>
+      <c r="F299" t="n">
+        <v>192.8899993896484</v>
+      </c>
+      <c r="G299" t="n">
+        <v>178.9700012207031</v>
+      </c>
+      <c r="H299" t="n">
+        <v>189.7599945068359</v>
+      </c>
+      <c r="I299" t="n">
+        <v>176.1799926757812</v>
+      </c>
+      <c r="J299" t="n">
+        <v>189.7599945068359</v>
+      </c>
+      <c r="K299" t="n">
+        <v>6615935</v>
+      </c>
+      <c r="L299" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Limited Submits Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Ltd. Share Price Gains in Small Cap Move - Univest</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Ltd. Share Price Gains in Small Cap Move - Univest</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills sets book closure dates for 91st AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills settles ₹100 crore commercial paper - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>19</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>EPL.NS</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>EPL Limited</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>252</v>
+      </c>
+      <c r="F300" t="n">
+        <v>273</v>
+      </c>
+      <c r="G300" t="n">
+        <v>251</v>
+      </c>
+      <c r="H300" t="n">
+        <v>270.1000061035156</v>
+      </c>
+      <c r="I300" t="n">
+        <v>250.8000030517578</v>
+      </c>
+      <c r="J300" t="n">
+        <v>270.1000061035156</v>
+      </c>
+      <c r="K300" t="n">
+        <v>6480002</v>
+      </c>
+      <c r="L300" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>EPL Ltd. Share Price Reaches One-Year High: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>EPL Ltd. Share Price Reaches One-Year High: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>EPL Standalone June 2026 Net Sales at Rs 400.30 crore, up 19.85% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>EPL Limited Q1FY27 results: Consolidated revenue up 25% to ₹13,879mn - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>Old Namibia uranium data guides Skeleton Coast's planned fieldwork - Stock Titan</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>20</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>RATNAVEER.NS</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Ratnaveer Precision Engineering Limited</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>253.2299957275391</v>
+      </c>
+      <c r="F301" t="n">
+        <v>270.5</v>
+      </c>
+      <c r="G301" t="n">
+        <v>252</v>
+      </c>
+      <c r="H301" t="n">
+        <v>269.239990234375</v>
+      </c>
+      <c r="I301" t="n">
+        <v>250.3999938964844</v>
+      </c>
+      <c r="J301" t="n">
+        <v>269.239990234375</v>
+      </c>
+      <c r="K301" t="n">
+        <v>11344542</v>
+      </c>
+      <c r="L301" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>Ratnaveer Precision Board Approves 1.25 Crore Shares Rights Issue At ₹264 Totaling ₹330 Crore - Sahi</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>Ratnaveer Precision Engineering appoints Seema Sanghavi as WTD - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>Ratnaveer Precision approves rights issue of 1.25 crore shares at ₹264 each - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>Press Release Distribution India - Business Wire India</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>Ratnaveer Standalone June 2026 Net Sales at Rs 314.64 crore, up 18.9% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>
@@ -17081,7 +18409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q281"/>
+  <dimension ref="A1:Q301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32459,8 +33787,6 @@
           <t>Enterprise value to EBIT forward of Wel-Dish. Incorporated – TSE:2901 - TradingView</t>
         </is>
       </c>
-      <c r="P266" t="inlineStr"/>
-      <c r="Q266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -32525,7 +33851,6 @@
           <t>Shivansh Finserve: புதிய வளர்ச்சிக்கு முக்கிய முடிவு! பெரும் கையகப்படுத்துதல் திட்டம்? - Whalesbook</t>
         </is>
       </c>
-      <c r="Q267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -32580,9 +33905,6 @@
           <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
         </is>
       </c>
-      <c r="O268" t="inlineStr"/>
-      <c r="P268" t="inlineStr"/>
-      <c r="Q268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -32647,7 +33969,6 @@
           <t>Femasys Inc. (FEMY) Q1 2026 Earnings: EPS Beat on Narrower Loss, Stock Slips - Dividend Earnings Report - Vinanet</t>
         </is>
       </c>
-      <c r="Q269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -32914,8 +34235,6 @@
           <t>DSJ Keep Learning Posts Q1 FY27 Unaudited Results in Line with SEBI Norms - TipRanks</t>
         </is>
       </c>
-      <c r="P273" t="inlineStr"/>
-      <c r="Q273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -32970,9 +34289,6 @@
           <t>CALSOFT Stock Price and Chart — NSE:CALSOFT - TradingView</t>
         </is>
       </c>
-      <c r="O274" t="inlineStr"/>
-      <c r="P274" t="inlineStr"/>
-      <c r="Q274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -33032,8 +34348,6 @@
           <t>Indo Thai Securities Ltd. (INDOTHAI) Share Price Hits Fresh 52-Week Low - Univest</t>
         </is>
       </c>
-      <c r="P275" t="inlineStr"/>
-      <c r="Q275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -33446,6 +34760,1294 @@
       <c r="Q281" t="inlineStr">
         <is>
           <t>LLY Stock: Where Compounding Could Take The Price - Trefis</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>1</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>GCSL.NS</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services Limited</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>526.2999877929688</v>
+      </c>
+      <c r="F282" t="n">
+        <v>540.9500122070312</v>
+      </c>
+      <c r="G282" t="n">
+        <v>470</v>
+      </c>
+      <c r="H282" t="n">
+        <v>482.0499877929688</v>
+      </c>
+      <c r="I282" t="n">
+        <v>521.7000122070312</v>
+      </c>
+      <c r="J282" t="n">
+        <v>482.0499877929688</v>
+      </c>
+      <c r="K282" t="n">
+        <v>615899</v>
+      </c>
+      <c r="L282" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services gets exchange nod for ₹7 crore warrant issue - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services Raises Capital via Preferential Allotment of Warrants to Promoter Group - TipRanks</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services Q1 Results: Revenue at ₹1,785 Mn, Net Profit ₹276 Mn - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services allots 5.55 lakh warrants to promoter group - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services Receives SEBI Show Cause Notice Over Taurian MPS Ltd IPO - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>2</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>HSCL.NS</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Himadri Speciality Chemical Limited</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>755</v>
+      </c>
+      <c r="F283" t="n">
+        <v>767.5999755859375</v>
+      </c>
+      <c r="G283" t="n">
+        <v>695.5</v>
+      </c>
+      <c r="H283" t="n">
+        <v>704.2000122070312</v>
+      </c>
+      <c r="I283" t="n">
+        <v>750.25</v>
+      </c>
+      <c r="J283" t="n">
+        <v>704.2000122070312</v>
+      </c>
+      <c r="K283" t="n">
+        <v>12482496</v>
+      </c>
+      <c r="L283" t="n">
+        <v>-6.14</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>Himadri Speciality Chemical Ltd. (HSCL) Share Price Falls 7.32% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>Himadri Speciality Chemicals Share Price - Live NSE: HSCL Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>Himadri Speciality Chemicals Share Price - Live NSE: HSCL Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr"/>
+      <c r="Q283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>3</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>DREDGECORP.NS</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Dredging Corporation of India Limited</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>1199</v>
+      </c>
+      <c r="F284" t="n">
+        <v>1204</v>
+      </c>
+      <c r="G284" t="n">
+        <v>1111.5</v>
+      </c>
+      <c r="H284" t="n">
+        <v>1118.300048828125</v>
+      </c>
+      <c r="I284" t="n">
+        <v>1189.199951171875</v>
+      </c>
+      <c r="J284" t="n">
+        <v>1118.300048828125</v>
+      </c>
+      <c r="K284" t="n">
+        <v>253900</v>
+      </c>
+      <c r="L284" t="n">
+        <v>-5.96</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr"/>
+      <c r="P284" t="inlineStr"/>
+      <c r="Q284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>4</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>SHREEJISPG.NS</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Shreeji Shipping Global Limited</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>657</v>
+      </c>
+      <c r="F285" t="n">
+        <v>661.9500122070312</v>
+      </c>
+      <c r="G285" t="n">
+        <v>609.8499755859375</v>
+      </c>
+      <c r="H285" t="n">
+        <v>613.3499755859375</v>
+      </c>
+      <c r="I285" t="n">
+        <v>649.4500122070312</v>
+      </c>
+      <c r="J285" t="n">
+        <v>613.3499755859375</v>
+      </c>
+      <c r="K285" t="n">
+        <v>1441163</v>
+      </c>
+      <c r="L285" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>Shreeji Shipping Global Ltd. (SHREEJISPG) Share Price Hits 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>Shreeji Shipping Global Q1 FY27: Net Profit Rises 19% YoY to ₹44.29 Cr - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>Shreeji Shipping Global Q1 FY27: Net Profit Rises 19% YoY to ₹44.29 Cr - Trade Brains</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr"/>
+      <c r="Q285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>5</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>UEL.NS</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Ujaas Energy Limited</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>190.7599945068359</v>
+      </c>
+      <c r="F286" t="n">
+        <v>190.7599945068359</v>
+      </c>
+      <c r="G286" t="n">
+        <v>190.7599945068359</v>
+      </c>
+      <c r="H286" t="n">
+        <v>190.7599945068359</v>
+      </c>
+      <c r="I286" t="n">
+        <v>200.8000030517578</v>
+      </c>
+      <c r="J286" t="n">
+        <v>190.7599945068359</v>
+      </c>
+      <c r="K286" t="n">
+        <v>6358</v>
+      </c>
+      <c r="L286" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>Ujaas Energy Ltd. Share Price Shows Strong Price Action - Univest</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>Boehly Holds Talks Over Selling Shares To Majority Owners At Chelsea - Complete Sports</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>Stock Watch: Shares Of These 10 Companies Slumped And Surged Over 5% Today - Do You Own Any? - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>Ujaas Energy Ltd. Share Price Jumps to New 52-Week Peak - Univest</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>Boehly Holds Talks Over Selling Shares To Majority Owners At Chelsea - Complete Sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>6</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>INDOTHAI.NS</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Limited</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>62.79999923706055</v>
+      </c>
+      <c r="F287" t="n">
+        <v>62.79999923706055</v>
+      </c>
+      <c r="G287" t="n">
+        <v>62.79999923706055</v>
+      </c>
+      <c r="H287" t="n">
+        <v>62.79999923706055</v>
+      </c>
+      <c r="I287" t="n">
+        <v>66.09999847412109</v>
+      </c>
+      <c r="J287" t="n">
+        <v>62.79999923706055</v>
+      </c>
+      <c r="K287" t="n">
+        <v>45140</v>
+      </c>
+      <c r="L287" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>Stock Watch: Shares Of These 10 Companies Slumped And Surged Over 5% Today - Do You Own Any? - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Ltd. Share Price Falls 9.97% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Ltd. Share Price Falls 9.97% Today - Univest</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Ltd. (INDOTHAI) Share Price Hits Fresh 52-Week Low - Univest</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities unsecured creditors approve broking demerger - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>7</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>KSR.NS</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>KSR Footwear Limited</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>28.51000022888184</v>
+      </c>
+      <c r="F288" t="n">
+        <v>30</v>
+      </c>
+      <c r="G288" t="n">
+        <v>27</v>
+      </c>
+      <c r="H288" t="n">
+        <v>27.42000007629395</v>
+      </c>
+      <c r="I288" t="n">
+        <v>28.84000015258789</v>
+      </c>
+      <c r="J288" t="n">
+        <v>27.42000007629395</v>
+      </c>
+      <c r="K288" t="n">
+        <v>77843</v>
+      </c>
+      <c r="L288" t="n">
+        <v>-4.92</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>KSR Footwear Standalone June 2026 Net Sales at Rs 52.25 crore, up 0.36% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>Kalen "Big K" Edwards Shares Words of Wisdom from the Changing Kentucky Trenches - On3</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>KSR Footwear Q1 Results: Net profit turns positive at ₹3.17 million - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>KSR Footwear dispatches FY26 annual report, sets August 24 AGM date - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>Kalen "Big K" Edwards Shares Words of Wisdom from the Changing Kentucky Trenches - On3</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>8</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>GANGAFORGE.NS</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Ganga Forging Limited</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>2.150000095367432</v>
+      </c>
+      <c r="F289" t="n">
+        <v>2.150000095367432</v>
+      </c>
+      <c r="G289" t="n">
+        <v>2.150000095367432</v>
+      </c>
+      <c r="H289" t="n">
+        <v>2.150000095367432</v>
+      </c>
+      <c r="I289" t="n">
+        <v>2.259999990463257</v>
+      </c>
+      <c r="J289" t="n">
+        <v>2.150000095367432</v>
+      </c>
+      <c r="K289" t="n">
+        <v>968342</v>
+      </c>
+      <c r="L289" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>Ganga Forging rights issue sees 120% subscription, trading begins - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>Ganga Forging rights issue sees 120% subscription, trading begins - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr"/>
+      <c r="P289" t="inlineStr"/>
+      <c r="Q289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>9</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>ASTERDM.NS</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Aster DM Quality Care Limited</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>798.3499755859375</v>
+      </c>
+      <c r="F290" t="n">
+        <v>798.3499755859375</v>
+      </c>
+      <c r="G290" t="n">
+        <v>756.0499877929688</v>
+      </c>
+      <c r="H290" t="n">
+        <v>765.6500244140625</v>
+      </c>
+      <c r="I290" t="n">
+        <v>800.2000122070312</v>
+      </c>
+      <c r="J290" t="n">
+        <v>765.6500244140625</v>
+      </c>
+      <c r="K290" t="n">
+        <v>9884475</v>
+      </c>
+      <c r="L290" t="n">
+        <v>-4.32</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Aster DM Healthcare to rename as Aster DM Quality Care Limited - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>Aster DM Quality Care Limited (NSE:ASTERDM) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹898 - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>Aster DM Quality Care Limited (NSE:ASTERDM) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹898 - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr"/>
+      <c r="Q290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>10</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>KPEL.NS</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>K.P. Energy Limited</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>268.2000122070312</v>
+      </c>
+      <c r="F291" t="n">
+        <v>271</v>
+      </c>
+      <c r="G291" t="n">
+        <v>255.1499938964844</v>
+      </c>
+      <c r="H291" t="n">
+        <v>256.6499938964844</v>
+      </c>
+      <c r="I291" t="n">
+        <v>268.2000122070312</v>
+      </c>
+      <c r="J291" t="n">
+        <v>256.6499938964844</v>
+      </c>
+      <c r="K291" t="n">
+        <v>442666</v>
+      </c>
+      <c r="L291" t="n">
+        <v>-4.31</v>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>K.P. Energy Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>K.P. Energy Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>K.P. Energy Q1FY27 revenue surges 137% to ₹519.46 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr"/>
+      <c r="Q291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>11</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>YASHO.NS</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Yasho Industries Limited</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F292" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G292" t="n">
+        <v>4230</v>
+      </c>
+      <c r="H292" t="n">
+        <v>4284.2001953125</v>
+      </c>
+      <c r="I292" t="n">
+        <v>4470.7998046875</v>
+      </c>
+      <c r="J292" t="n">
+        <v>4284.2001953125</v>
+      </c>
+      <c r="K292" t="n">
+        <v>123163</v>
+      </c>
+      <c r="L292" t="n">
+        <v>-4.17</v>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>Yasho Industries Share Price Today, Yasho Industries Stock Price Live NSE/BSE Updates - The Economic Times</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>Yasho Ind. Standalone June 2026 Net Sales at Rs 314.09 crore, up 58.73% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>Yasho Industries Q1 FY27 Results: PAT Rs 36 Cr, Revenue Rs 307 Cr - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>12</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>KRISHNADEF.NS</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Krishna Defence And Allied Industries Limited</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>1083.900024414062</v>
+      </c>
+      <c r="F293" t="n">
+        <v>1094.900024414062</v>
+      </c>
+      <c r="G293" t="n">
+        <v>1026</v>
+      </c>
+      <c r="H293" t="n">
+        <v>1037.900024414062</v>
+      </c>
+      <c r="I293" t="n">
+        <v>1077.800048828125</v>
+      </c>
+      <c r="J293" t="n">
+        <v>1037.900024414062</v>
+      </c>
+      <c r="K293" t="n">
+        <v>152475</v>
+      </c>
+      <c r="L293" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>Krishna Defence and Allied Industries Ltd. (KRISHNADEF) Share Price Falls 8.3% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>Krishna Defence and Allied Industries Ltd. (KRISHNADEF) Share Price Falls 8.3% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr"/>
+      <c r="P293" t="inlineStr"/>
+      <c r="Q293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>13</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>CHENNPETRO.NS</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Chennai Petroleum Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>1457</v>
+      </c>
+      <c r="F294" t="n">
+        <v>1466</v>
+      </c>
+      <c r="G294" t="n">
+        <v>1379.599975585938</v>
+      </c>
+      <c r="H294" t="n">
+        <v>1390.5</v>
+      </c>
+      <c r="I294" t="n">
+        <v>1440.300048828125</v>
+      </c>
+      <c r="J294" t="n">
+        <v>1390.5</v>
+      </c>
+      <c r="K294" t="n">
+        <v>2227820</v>
+      </c>
+      <c r="L294" t="n">
+        <v>-3.46</v>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>Chennai Petroleum Corporation Limited (NSE:CHENNPETRO) Looks Interesting, And It's About To Pay A Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>Chennai Petroleum Corporation Ltd. Share Price at 52-Week - Univest</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>Chennai Petroleum Corporation Ltd. (CHENNPETRO) Share Price Rises 5.01% Today - Univest</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>Chennai Petroleum Corporation Ltd. Share Price at 52-Week - Univest</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>Chennai Petroleum Corporation Ltd. Stock News: Price Up 5.8% - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>14</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>SYRMA.NS</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Syrma SGS Technology Limited</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>1504.800048828125</v>
+      </c>
+      <c r="F295" t="n">
+        <v>1525.800048828125</v>
+      </c>
+      <c r="G295" t="n">
+        <v>1415.699951171875</v>
+      </c>
+      <c r="H295" t="n">
+        <v>1443.699951171875</v>
+      </c>
+      <c r="I295" t="n">
+        <v>1494.800048828125</v>
+      </c>
+      <c r="J295" t="n">
+        <v>1443.699951171875</v>
+      </c>
+      <c r="K295" t="n">
+        <v>1342162</v>
+      </c>
+      <c r="L295" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>Syrma SGS Technology Ltd. Share Price Today After 3.43% Fall - Univest</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>Syrma SGS Technology Ltd. Share Price Today After 3.43% Fall - Univest</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>Syrma SGS, Dixon, other EMS companies' shares rise as govt clears 31 electronics component projects worth... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>Syrma SGS Technology Stock Surges Over 3% After ECMS Application Gets Approved By Govt - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>Govt clears ₹7,877 crore ECMS investments; Wipro, PCBL Chemical, Syrma SGS shares in focus - CNBC TV18</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>15</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>AIIL.NS</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Authum Investment &amp; Infrastructure Limited</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>551</v>
+      </c>
+      <c r="F296" t="n">
+        <v>553.75</v>
+      </c>
+      <c r="G296" t="n">
+        <v>527.25</v>
+      </c>
+      <c r="H296" t="n">
+        <v>532.2999877929688</v>
+      </c>
+      <c r="I296" t="n">
+        <v>550.5</v>
+      </c>
+      <c r="J296" t="n">
+        <v>532.2999877929688</v>
+      </c>
+      <c r="K296" t="n">
+        <v>966550</v>
+      </c>
+      <c r="L296" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>AIIL Share Price | Authum Investment &amp; Infrastructure Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>AIIL Share Price | Authum Investment &amp; Infrastructure Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr"/>
+      <c r="P296" t="inlineStr"/>
+      <c r="Q296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>16</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>NOVARTIND.NS</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Novartis India Limited</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>1540</v>
+      </c>
+      <c r="F297" t="n">
+        <v>1574.900024414062</v>
+      </c>
+      <c r="G297" t="n">
+        <v>1476</v>
+      </c>
+      <c r="H297" t="n">
+        <v>1482.199951171875</v>
+      </c>
+      <c r="I297" t="n">
+        <v>1531.699951171875</v>
+      </c>
+      <c r="J297" t="n">
+        <v>1482.199951171875</v>
+      </c>
+      <c r="K297" t="n">
+        <v>16240</v>
+      </c>
+      <c r="L297" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>Novartis India Ltd. Share Price News: New 52-Week Trough - Univest</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>Novartis India Ltd. Share Price News: New 52-Week Trough - Univest</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr"/>
+      <c r="P297" t="inlineStr"/>
+      <c r="Q297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>17</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>NEOGEN.NS</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Neogen Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>2358.89990234375</v>
+      </c>
+      <c r="F298" t="n">
+        <v>2368.699951171875</v>
+      </c>
+      <c r="G298" t="n">
+        <v>2250</v>
+      </c>
+      <c r="H298" t="n">
+        <v>2259.10009765625</v>
+      </c>
+      <c r="I298" t="n">
+        <v>2328.800048828125</v>
+      </c>
+      <c r="J298" t="n">
+        <v>2259.10009765625</v>
+      </c>
+      <c r="K298" t="n">
+        <v>137421</v>
+      </c>
+      <c r="L298" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>SBI Mutual Fund reduces Neogen Chemicals stake to 6.03% under SAST Reg 29 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>Neogen Corp CEO Mikheal Nassif Executes RSU Tax Withholding on August 19, 2026 - Kalkine Media</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>Neogen (NEOG) CEO uses 20K shares to cover RSU taxes - Stock Titan</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>Neogen Chemicals Limited (NEOGEN.BO) stock price, news, quote and history - Yahoo Finance UK</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>Neogen Corporation (NASDAQ:NEOG) Given Average Rating of "Hold" by Brokerages - MarketBeat</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>18</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>MMFL.NS</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>MM Forgings Limited</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>660.0999755859375</v>
+      </c>
+      <c r="F299" t="n">
+        <v>669.4500122070312</v>
+      </c>
+      <c r="G299" t="n">
+        <v>635</v>
+      </c>
+      <c r="H299" t="n">
+        <v>638.9500122070312</v>
+      </c>
+      <c r="I299" t="n">
+        <v>657.7999877929688</v>
+      </c>
+      <c r="J299" t="n">
+        <v>638.9500122070312</v>
+      </c>
+      <c r="K299" t="n">
+        <v>176799</v>
+      </c>
+      <c r="L299" t="n">
+        <v>-2.87</v>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>IOC Share Dividend Stocks Split MMFL KPIT TARIL Afcons Share Midwest Gold FII DII Stock Finshots Atp Rome (HN86imV77B) - Mshale</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>MM Forgings Ltd. Share Price Today Up 8.43%: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>MM Forgings Ltd. Share Price Today Up 8.43%: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>M M Forgings Limited Announces Resignation of Chandrasekar S from Company Secretary and Compliance Officer, Effective August 14, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>M M Forgings postpones Q1FY26 board meeting to Aug 14 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>19</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>PFC.NS</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>374.4500122070312</v>
+      </c>
+      <c r="F300" t="n">
+        <v>375.1000061035156</v>
+      </c>
+      <c r="G300" t="n">
+        <v>363.2000122070312</v>
+      </c>
+      <c r="H300" t="n">
+        <v>363.7999877929688</v>
+      </c>
+      <c r="I300" t="n">
+        <v>374.4500122070312</v>
+      </c>
+      <c r="J300" t="n">
+        <v>363.7999877929688</v>
+      </c>
+      <c r="K300" t="n">
+        <v>13375984</v>
+      </c>
+      <c r="L300" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>PFC, REC shares decline up to 3% after Morgan Stanley cuts growth estimates - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>PFC, REC Shares Fall Up To 3% As Morgan Stanley Cuts Growth Estimates - outlookbusiness.com</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>PFC, REC Shares Fall As Morgan Stanley Downgrades Both Stocks — Check Target Price, Potential Upside - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>'Consensus buy' PFC, 'no sell' REC get downgraded; Check rationale and new targets - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation and REC shares fall up to 3% after Morgan Stanley downgrade - The Economic Times</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:00:58 IST</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>20</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>BAJAJCON.NS</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Bajaj Consumer Care Limited</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>501</v>
+      </c>
+      <c r="F301" t="n">
+        <v>502</v>
+      </c>
+      <c r="G301" t="n">
+        <v>485</v>
+      </c>
+      <c r="H301" t="n">
+        <v>486.9500122070312</v>
+      </c>
+      <c r="I301" t="n">
+        <v>500.7000122070312</v>
+      </c>
+      <c r="J301" t="n">
+        <v>486.9500122070312</v>
+      </c>
+      <c r="K301" t="n">
+        <v>387003</v>
+      </c>
+      <c r="L301" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>Optimistic Investors Push Bajaj Consumer Care Limited (NSE:BAJAJCON) Shares Up 26% But Growth Is Lacking - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>Bajaj Consumer Care Limited (NSE:BAJAJCON) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹696 - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>BAJAJCON Forecast — Price Target — Prediction for 2027 - TradingView</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>Bajaj Consumer Care Limited (NSE:BAJAJCON) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹696 - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>Bajaj Consumer Care (BAJAJCON.NS): Stock Hovers Near Key Levels Amid Thin Trading - BPI Bull Correction - Vinanet</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q301"/>
+  <dimension ref="A1:Q321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17383,9 +17383,6 @@
           <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
-      <c r="O286" t="inlineStr"/>
-      <c r="P286" t="inlineStr"/>
-      <c r="Q286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -17450,7 +17447,6 @@
           <t>Uttam Sugar Mills Share Price Jumps; Technicals in Focus - Univest</t>
         </is>
       </c>
-      <c r="Q287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -17574,9 +17570,6 @@
           <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
         </is>
       </c>
-      <c r="O289" t="inlineStr"/>
-      <c r="P289" t="inlineStr"/>
-      <c r="Q289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -17774,8 +17767,6 @@
           <t>Josh Da Costa Shares Another Facet of New Wave Graveyard with the Hypnagogic (and Possibly Psychic) “Cordelia” - floodmagazine.com</t>
         </is>
       </c>
-      <c r="P292" t="inlineStr"/>
-      <c r="Q292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -18395,6 +18386,1326 @@
       <c r="Q301" t="inlineStr">
         <is>
           <t>Ratnaveer Standalone June 2026 Net Sales at Rs 314.64 crore, up 18.9% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>1</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>VIRAT.NS</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Virat Industries Limited</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>335</v>
+      </c>
+      <c r="F302" t="n">
+        <v>401.7000122070312</v>
+      </c>
+      <c r="G302" t="n">
+        <v>330</v>
+      </c>
+      <c r="H302" t="n">
+        <v>401.7000122070312</v>
+      </c>
+      <c r="I302" t="n">
+        <v>334.75</v>
+      </c>
+      <c r="J302" t="n">
+        <v>401.7000122070312</v>
+      </c>
+      <c r="K302" t="n">
+        <v>51714</v>
+      </c>
+      <c r="L302" t="n">
+        <v>20</v>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>Virat Industries Ltd. Share Price Up 17.36%: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>Virat Industries Ltd. Share Price Up 17.36%: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>Virat Industries seeks 70.28% stake in Brahm Lifestyle for ₹95 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>Gayan Senanayake: Sri Lankan superfan who shares a special bond with Virat and Rohit - Revsportz</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>"He Is Like My Brother": PV Sindhu Shares How Virat Kohli Motivated Her During Tough Phase - Sportscape Magazine</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>2</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>QUADFUTURE.NS</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Quadrant Future Tek Limited</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>340</v>
+      </c>
+      <c r="F303" t="n">
+        <v>405.3500061035156</v>
+      </c>
+      <c r="G303" t="n">
+        <v>339</v>
+      </c>
+      <c r="H303" t="n">
+        <v>405.3500061035156</v>
+      </c>
+      <c r="I303" t="n">
+        <v>337.7999877929688</v>
+      </c>
+      <c r="J303" t="n">
+        <v>405.3500061035156</v>
+      </c>
+      <c r="K303" t="n">
+        <v>7457265</v>
+      </c>
+      <c r="L303" t="n">
+        <v>20</v>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>Quadrant Future Tek Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>Quadrant Future Tek Publishes Q1 FY27 Unaudited Results and Notifies Stock Exchanges - TipRanks</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>Quadrant Future Tek Publishes Q1 FY27 Unaudited Results and Notifies Stock Exchanges - TipRanks</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr"/>
+      <c r="Q303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>3</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>MPDL.NS</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>MPDL Limited</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>39.9900016784668</v>
+      </c>
+      <c r="F304" t="n">
+        <v>41.18000030517578</v>
+      </c>
+      <c r="G304" t="n">
+        <v>39.20000076293945</v>
+      </c>
+      <c r="H304" t="n">
+        <v>41.18000030517578</v>
+      </c>
+      <c r="I304" t="n">
+        <v>34.31999969482422</v>
+      </c>
+      <c r="J304" t="n">
+        <v>41.18000030517578</v>
+      </c>
+      <c r="K304" t="n">
+        <v>14902</v>
+      </c>
+      <c r="L304" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>MPDL Share Price Today - MPDL Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>Oriental Rail Infrastructure Ltd leads gainers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of MPDL Ltd – NSE:MPDL - TradingView</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>Oriental Rail Infrastructure Ltd leads gainers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>MPDL Ltd Q1 Results: Board approves financials for quarter ended June 30 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>4</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>KJMCFIN.NS</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>79.69999694824219</v>
+      </c>
+      <c r="F305" t="n">
+        <v>79.69999694824219</v>
+      </c>
+      <c r="G305" t="n">
+        <v>79.69999694824219</v>
+      </c>
+      <c r="H305" t="n">
+        <v>79.69999694824219</v>
+      </c>
+      <c r="I305" t="n">
+        <v>66.41999816894531</v>
+      </c>
+      <c r="J305" t="n">
+        <v>79.69999694824219</v>
+      </c>
+      <c r="K305" t="n">
+        <v>3747</v>
+      </c>
+      <c r="L305" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services net profit rises to ₹162.85 lakh in Q1FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr"/>
+      <c r="Q305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>5</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>SUPTANERY.NS</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Super Tannery Limited</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>7.730000019073486</v>
+      </c>
+      <c r="F306" t="n">
+        <v>8.770000457763672</v>
+      </c>
+      <c r="G306" t="n">
+        <v>7.309999942779541</v>
+      </c>
+      <c r="H306" t="n">
+        <v>8.770000457763672</v>
+      </c>
+      <c r="I306" t="n">
+        <v>7.309999942779541</v>
+      </c>
+      <c r="J306" t="n">
+        <v>8.770000457763672</v>
+      </c>
+      <c r="K306" t="n">
+        <v>2047504</v>
+      </c>
+      <c r="L306" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>SUPTANERY Share Price Today - Super Tannery Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>SUPTANERY Historical Data - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of Super Tannery Ltd. – NSE:SUPTANERY - TradingView</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>SUPTANERY Historical Data - Equitypandit</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>Super Tannery Ltd. Statistics – NSE:SUPTANERY - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>6</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>NDL.NS</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Nandan Denim Limited</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>2.279999971389771</v>
+      </c>
+      <c r="F307" t="n">
+        <v>2.710000038146973</v>
+      </c>
+      <c r="G307" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H307" t="n">
+        <v>2.710000038146973</v>
+      </c>
+      <c r="I307" t="n">
+        <v>2.259999990463257</v>
+      </c>
+      <c r="J307" t="n">
+        <v>2.710000038146973</v>
+      </c>
+      <c r="K307" t="n">
+        <v>5991494</v>
+      </c>
+      <c r="L307" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>NCLT admits NDL Ventures-Hinduja Leyland merger petition - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>NCLT admits NDL Ventures-Hinduja Leyland merger petition - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>NDL Ventures Shareholders Approve Scheme of Merger by Absorption of Hinduja Leyland Finance Limited - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>Next Digital probe halted - news.gov.hk</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>7</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>NKIND.NS</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>NK Industries Limited</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>60</v>
+      </c>
+      <c r="F308" t="n">
+        <v>67.91999816894531</v>
+      </c>
+      <c r="G308" t="n">
+        <v>58.09999847412109</v>
+      </c>
+      <c r="H308" t="n">
+        <v>67.62000274658203</v>
+      </c>
+      <c r="I308" t="n">
+        <v>56.59999847412109</v>
+      </c>
+      <c r="J308" t="n">
+        <v>67.62000274658203</v>
+      </c>
+      <c r="K308" t="n">
+        <v>327876</v>
+      </c>
+      <c r="L308" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>International (IGIC) Latest Quarter: EPS Misses Its Estimate in Latest Trading; After Earnings: Shares Finish 2.35% Higher - Earnings Call Highlights - Vinanet</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>International (IGIC) Latest Quarter: EPS Misses Its Estimate in Latest Trading; After Earnings: Shares Finish 2.35% Higher - Earnings Call Highlights - Vinanet</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>Record Heat Drives UK Online Retail Sales to Five-Year High in June - Book Value Growth - Vinanet</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr"/>
+      <c r="Q308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>8</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>ALLCARGO.NS</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Allcargo Logistics Limited</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>10.55000019073486</v>
+      </c>
+      <c r="F309" t="n">
+        <v>12.59000015258789</v>
+      </c>
+      <c r="G309" t="n">
+        <v>10.47000026702881</v>
+      </c>
+      <c r="H309" t="n">
+        <v>12.17000007629395</v>
+      </c>
+      <c r="I309" t="n">
+        <v>10.51000022888184</v>
+      </c>
+      <c r="J309" t="n">
+        <v>12.17000007629395</v>
+      </c>
+      <c r="K309" t="n">
+        <v>110039625</v>
+      </c>
+      <c r="L309" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>Allcargo Logistics shares up 20% in three sessions, could well have their best month on record - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>Allcargo Logistics shares up 20% in three sessions, could well have their best month on record - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>Allcargo Logistics Share Price Update With Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>Allcargo Global Ltd Share Price Today,, AGL Share Price NSE, BSE - Business Today</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>Allcargo Logistics shares rally 15% after Q1 profit jumps 258% YoY to Rs 31 crore - The Economic Times</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>9</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>KRONOX.NS</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Limited</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>191</v>
+      </c>
+      <c r="F310" t="n">
+        <v>223.4199981689453</v>
+      </c>
+      <c r="G310" t="n">
+        <v>191</v>
+      </c>
+      <c r="H310" t="n">
+        <v>215.1799926757812</v>
+      </c>
+      <c r="I310" t="n">
+        <v>186.1900024414062</v>
+      </c>
+      <c r="J310" t="n">
+        <v>215.1799926757812</v>
+      </c>
+      <c r="K310" t="n">
+        <v>24328538</v>
+      </c>
+      <c r="L310" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>Indo Borax to acquire 64.26% stake in Kronox Lab Sciences in Rs 246-crore deal - Indian Chemical News</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>Why Did Kronox Lab Sciences Shares Surge by Up to 39% in Two Days? Here’s the Reason - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences shares rally 32% in 2 days as Indo Borax, Zenrock Chemicals eye stake acquisition - The Economic Times</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>Indo Borax Approves Kronox Lab Stake Purchase; Shares Rise 7.44% - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>Kronox Lab shares hit 20% upper circuit as Indo Borax and Chemicals to acquire 64.26% stake - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>10</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>BIRLAPREC.NS</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>39.11999893188477</v>
+      </c>
+      <c r="F311" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="G311" t="n">
+        <v>38.13000106811523</v>
+      </c>
+      <c r="H311" t="n">
+        <v>44.40000152587891</v>
+      </c>
+      <c r="I311" t="n">
+        <v>39.11000061035156</v>
+      </c>
+      <c r="J311" t="n">
+        <v>44.40000152587891</v>
+      </c>
+      <c r="K311" t="n">
+        <v>986260</v>
+      </c>
+      <c r="L311" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies (BIRLAPREC.NS): Stock Eases Marginally, Nears Key Support Level - Symmetrical Triangle - Vinanet</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies (BIRLAPREC.NS) Holds Support Near ₹36.1, Resistance at ₹39.9 in Focus - Gamma Flip Level - Vinanet</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>BIRLAPREC Share Price Today - Birla Precision Technologies Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies (BIRLAPREC.NS) Holds Support Near ₹36.1, Resistance at ₹39.9 in Focus - Gamma Flip Level - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>BIRLAPREC.NS Mar 2026 Earnings: Marginal EPS of ₹0.39 on Modest Revenue of ₹63.91 crore; Stock Slides 0.71% - ROA Comparison - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>11</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>TBZ.NS</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Tribhovandas Bhimji Zaveri Limited</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>252.5</v>
+      </c>
+      <c r="F312" t="n">
+        <v>291</v>
+      </c>
+      <c r="G312" t="n">
+        <v>250.1999969482422</v>
+      </c>
+      <c r="H312" t="n">
+        <v>279.5</v>
+      </c>
+      <c r="I312" t="n">
+        <v>248.8500061035156</v>
+      </c>
+      <c r="J312" t="n">
+        <v>279.5</v>
+      </c>
+      <c r="K312" t="n">
+        <v>7128163</v>
+      </c>
+      <c r="L312" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>TBZ outlines TDS rules for ₹2.50 per share FY26 dividend - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>TBZ outlines TDS rules for ₹2.50 per share FY26 dividend - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>TBZ Reports Strong Unaudited Q1 FY27 Results, Maintains Profit Momentum - TipRanks</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr"/>
+      <c r="Q312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>12</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>MODIRUBBER.NS</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Modi Rubber Limited</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>119</v>
+      </c>
+      <c r="F313" t="n">
+        <v>144</v>
+      </c>
+      <c r="G313" t="n">
+        <v>117.8000030517578</v>
+      </c>
+      <c r="H313" t="n">
+        <v>134.2400054931641</v>
+      </c>
+      <c r="I313" t="n">
+        <v>120.0699996948242</v>
+      </c>
+      <c r="J313" t="n">
+        <v>134.2400054931641</v>
+      </c>
+      <c r="K313" t="n">
+        <v>40792</v>
+      </c>
+      <c r="L313" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>Modi Rubber Ltd. Share Price Today Up 20%: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>SBEV Q2 2025 Earnings: Wider-than-Expected Loss Sends Shares Down 14.63% - High Growth Earnings - Vinanet</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>Modi Rubber seeks shareholder approval to appoint Ajay Kumar Jain as Independent Director - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>Modi Rubber approves comfort letter for Gujarat Guardian expansion project - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>Modi Rubber Ltd. (MODIRUBBER) Share Price Rises 11.8% Today - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>13</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>THOMASCOOK.NS</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Thomas Cook  (India)  Limited</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>101.9899978637695</v>
+      </c>
+      <c r="F314" t="n">
+        <v>115.6999969482422</v>
+      </c>
+      <c r="G314" t="n">
+        <v>101.9899978637695</v>
+      </c>
+      <c r="H314" t="n">
+        <v>113.1699981689453</v>
+      </c>
+      <c r="I314" t="n">
+        <v>101.5800018310547</v>
+      </c>
+      <c r="J314" t="n">
+        <v>113.1699981689453</v>
+      </c>
+      <c r="K314" t="n">
+        <v>25566022</v>
+      </c>
+      <c r="L314" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>Thomas Cook Q1 Results: Earnings call recording now available for investors - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>Thomas Cook India Sets Virtual AGM to Approve Dividend, Financials and Board Changes - TipRanks</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>Thomas Cook India Sets Virtual AGM to Approve Dividend, Financials and Board Changes - TipRanks</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr"/>
+      <c r="Q314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>14</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>ORIRAIL.NS</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Oriental Rail Infrastructure Limited</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>106.8899993896484</v>
+      </c>
+      <c r="F315" t="n">
+        <v>124.3499984741211</v>
+      </c>
+      <c r="G315" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="H315" t="n">
+        <v>114.7799987792969</v>
+      </c>
+      <c r="I315" t="n">
+        <v>103.629997253418</v>
+      </c>
+      <c r="J315" t="n">
+        <v>114.7799987792969</v>
+      </c>
+      <c r="K315" t="n">
+        <v>1142107</v>
+      </c>
+      <c r="L315" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>Oriental Rail uploads Q1FY27 earnings call audio recording - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>Oriental Rail uploads Q1FY27 earnings call audio recording - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>Oriental Rail Infrastructure shares permitted to trade on NSE - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>Free float of Oriental Rail Infrastructure Ltd. – NSE:ORIRAIL - TradingView</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>Oriental Rail Infrastructure seeks ratification for ₹42.04 crore fund variation - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>15</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>QUINT.NS</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Quint Digital Limited</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>38</v>
+      </c>
+      <c r="F316" t="n">
+        <v>41.79999923706055</v>
+      </c>
+      <c r="G316" t="n">
+        <v>36.79999923706055</v>
+      </c>
+      <c r="H316" t="n">
+        <v>40.34000015258789</v>
+      </c>
+      <c r="I316" t="n">
+        <v>36.5099983215332</v>
+      </c>
+      <c r="J316" t="n">
+        <v>40.34000015258789</v>
+      </c>
+      <c r="K316" t="n">
+        <v>65255</v>
+      </c>
+      <c r="L316" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>BJP Shares Misleading Claim About Rahul Gandhi 'Insulting' the National Anthem - The Quint</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>Quint Digital Ltd. Share Price Update With Valuation Check - Univest</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>Quint Digital Ltd. Share Price Update With Valuation Check - Univest</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>Quint Digital Consolidated June 2026 Net Sales at Rs 34.80 crore, up 335.77% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>BJP Shares Video From Bihar as One of Police Action on Jharkhand Protester - The Quint</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>16</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>RHETAN.NS</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Rhetan TMT Limited</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="F317" t="n">
+        <v>24.22999954223633</v>
+      </c>
+      <c r="G317" t="n">
+        <v>20.61000061035156</v>
+      </c>
+      <c r="H317" t="n">
+        <v>24.21999931335449</v>
+      </c>
+      <c r="I317" t="n">
+        <v>22.03000068664551</v>
+      </c>
+      <c r="J317" t="n">
+        <v>24.21999931335449</v>
+      </c>
+      <c r="K317" t="n">
+        <v>38609598</v>
+      </c>
+      <c r="L317" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>Iron, steel stock Rhetan TMT retraces after inching close to 52-week high. Do you own? - livemint.com</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>Rhetan TMT Ltd Surges 9.75% to Day's High of Rs 24.2 — Outperforms Sector by 8.98 Percentage Points - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>Rhetan TMT Ltd. Share Price Jumps to Fresh One-Year High - Univest</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>Rhetan TMT Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>Momentum Stocks: HLE Glascoat, Rhetan TMT, Identical Brain under pressure; stocks trade below key moving... - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>17</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>CRSL.NS</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>3.369999885559082</v>
+      </c>
+      <c r="F318" t="n">
+        <v>3.390000104904175</v>
+      </c>
+      <c r="G318" t="n">
+        <v>3.200000047683716</v>
+      </c>
+      <c r="H318" t="n">
+        <v>3.390000104904175</v>
+      </c>
+      <c r="I318" t="n">
+        <v>3.089999914169312</v>
+      </c>
+      <c r="J318" t="n">
+        <v>3.390000104904175</v>
+      </c>
+      <c r="K318" t="n">
+        <v>4264848</v>
+      </c>
+      <c r="L318" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>CRSL Share Price Today - Cressanda Railway Solutions Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Ltd - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Ltd Statistics – NSE:CRSL - TradingView</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Ltd - Equitypandit</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>18</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>LAMBODHARA.NS</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Lambodhara Textiles Limited</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>107.629997253418</v>
+      </c>
+      <c r="F319" t="n">
+        <v>124</v>
+      </c>
+      <c r="G319" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="H319" t="n">
+        <v>118.0800018310547</v>
+      </c>
+      <c r="I319" t="n">
+        <v>107.629997253418</v>
+      </c>
+      <c r="J319" t="n">
+        <v>118.0800018310547</v>
+      </c>
+      <c r="K319" t="n">
+        <v>83132</v>
+      </c>
+      <c r="L319" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>MDS &amp; Associates LLP resigns as Lambodhara Textiles secretarial auditor - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>Lambodhara Text Standalone June 2026 Net Sales at Rs 53.88 crore, down 8.83% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>Lambodhara Text Standalone June 2026 Net Sales at Rs 53.88 crore, down 8.83% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>Lambodhara Textiles net profit rises 66% in Q1FY26 on lower finance costs - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>19</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>ATLANTAELE.NS</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Atlanta Electricals Limited</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>1712.900024414062</v>
+      </c>
+      <c r="F320" t="n">
+        <v>1857.400024414062</v>
+      </c>
+      <c r="G320" t="n">
+        <v>1700</v>
+      </c>
+      <c r="H320" t="n">
+        <v>1846.900024414062</v>
+      </c>
+      <c r="I320" t="n">
+        <v>1688.599975585938</v>
+      </c>
+      <c r="J320" t="n">
+        <v>1846.900024414062</v>
+      </c>
+      <c r="K320" t="n">
+        <v>402648</v>
+      </c>
+      <c r="L320" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>Atlanta Electricals Schedules Investor and Analyst Meetings in Mumbai - TipRanks</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>Atlanta Electricals Schedules Investor and Analyst Meetings in Mumbai - TipRanks</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr"/>
+      <c r="P320" t="inlineStr"/>
+      <c r="Q320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>20</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>BLUSPRING.NS</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Bluspring Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>118</v>
+      </c>
+      <c r="F321" t="n">
+        <v>129.75</v>
+      </c>
+      <c r="G321" t="n">
+        <v>117.7200012207031</v>
+      </c>
+      <c r="H321" t="n">
+        <v>128.9799957275391</v>
+      </c>
+      <c r="I321" t="n">
+        <v>117.9599990844727</v>
+      </c>
+      <c r="J321" t="n">
+        <v>128.9799957275391</v>
+      </c>
+      <c r="K321" t="n">
+        <v>2549295</v>
+      </c>
+      <c r="L321" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>BLUSPRING Share Price Rise: Price, Valuation, Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>BLUSPRING Share Price Rise: Price, Valuation, Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>BLUSPRING ENTERPRISES LTD Share Price: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>Bluspring revenue rises 20% to ₹930 crore in Q1 FY27 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>Bluspring subsidiary secures ₹125 Cr term loan for LSG acquisition - scanx.trade</t>
         </is>
       </c>
     </row>
@@ -18409,7 +19720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q301"/>
+  <dimension ref="A1:Q321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34890,8 +36201,6 @@
           <t>Himadri Speciality Chemicals Share Price - Live NSE: HSCL Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
-      <c r="P283" t="inlineStr"/>
-      <c r="Q283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -34946,9 +36255,6 @@
           <t>Dredging Corporation Of India Ltd. Share Price Up 9.85% - Univest</t>
         </is>
       </c>
-      <c r="O284" t="inlineStr"/>
-      <c r="P284" t="inlineStr"/>
-      <c r="Q284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -35008,8 +36314,6 @@
           <t>Shreeji Shipping Global Q1 FY27: Net Profit Rises 19% YoY to ₹44.29 Cr - Trade Brains</t>
         </is>
       </c>
-      <c r="P285" t="inlineStr"/>
-      <c r="Q285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -35271,9 +36575,6 @@
           <t>Ganga Forging rights issue sees 120% subscription, trading begins - scanx.trade</t>
         </is>
       </c>
-      <c r="O289" t="inlineStr"/>
-      <c r="P289" t="inlineStr"/>
-      <c r="Q289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -35333,8 +36634,6 @@
           <t>Aster DM Quality Care Limited (NSE:ASTERDM) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹898 - simplywall.st</t>
         </is>
       </c>
-      <c r="P290" t="inlineStr"/>
-      <c r="Q290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -35394,8 +36693,6 @@
           <t>K.P. Energy Q1FY27 revenue surges 137% to ₹519.46 crore - scanx.trade</t>
         </is>
       </c>
-      <c r="P291" t="inlineStr"/>
-      <c r="Q291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -35519,9 +36816,6 @@
           <t>Krishna Defence and Allied Industries Ltd. (KRISHNADEF) Share Price Falls 8.3% Today - Univest</t>
         </is>
       </c>
-      <c r="O293" t="inlineStr"/>
-      <c r="P293" t="inlineStr"/>
-      <c r="Q293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -35714,9 +37008,6 @@
           <t>AIIL Share Price | Authum Investment &amp; Infrastructure Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
         </is>
       </c>
-      <c r="O296" t="inlineStr"/>
-      <c r="P296" t="inlineStr"/>
-      <c r="Q296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -35771,9 +37062,6 @@
           <t>Novartis India Ltd. Share Price News: New 52-Week Trough - Univest</t>
         </is>
       </c>
-      <c r="O297" t="inlineStr"/>
-      <c r="P297" t="inlineStr"/>
-      <c r="Q297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -36048,6 +37336,1342 @@
       <c r="Q301" t="inlineStr">
         <is>
           <t>Bajaj Consumer Care (BAJAJCON.NS): Stock Hovers Near Key Levels Amid Thin Trading - BPI Bull Correction - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>1</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>SHAH.NS</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Shah Metacorp Limited</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>3.980000019073486</v>
+      </c>
+      <c r="F302" t="n">
+        <v>4.050000190734863</v>
+      </c>
+      <c r="G302" t="n">
+        <v>3.160000085830688</v>
+      </c>
+      <c r="H302" t="n">
+        <v>3.329999923706055</v>
+      </c>
+      <c r="I302" t="n">
+        <v>3.950000047683716</v>
+      </c>
+      <c r="J302" t="n">
+        <v>3.329999923706055</v>
+      </c>
+      <c r="K302" t="n">
+        <v>4422848</v>
+      </c>
+      <c r="L302" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>Rocket Pharmaceuticals CEO Gaurav Shah sells $7,752 in shares - Investing.com</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>Rocket Pharmaceuticals CEO Gaurav Shah sells $7,752 in shares - Investing.com</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>New-age stocks, IPOs and valuations: Envision's Nilesh Shah shares his investment playbook - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>'Does True Love Exist?' Kashmera Shah Shares Cryptic Post Amid Govinda-Sunita Ahuja Spat - NDTV</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>Sunshine Pictures IPO day 2 LIVE: GMP, subscription status to review. Should you apply for Vipul Shah's company shares? - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>2</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>AVROIND.NS</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>AVRO INDIA LIMITED</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>9.479999542236328</v>
+      </c>
+      <c r="F303" t="n">
+        <v>9.479999542236328</v>
+      </c>
+      <c r="G303" t="n">
+        <v>8.409999847412109</v>
+      </c>
+      <c r="H303" t="n">
+        <v>8.590000152587891</v>
+      </c>
+      <c r="I303" t="n">
+        <v>9.380000114440918</v>
+      </c>
+      <c r="J303" t="n">
+        <v>8.590000152587891</v>
+      </c>
+      <c r="K303" t="n">
+        <v>1274488</v>
+      </c>
+      <c r="L303" t="n">
+        <v>-8.42</v>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>Avro India Ltd. Share Price Today: Price Rise Breakdown - Univest</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>Avro India Ltd. Share Price Today: Price Rise Breakdown - Univest</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>Avro India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>Protalix BioTherapeutics (PLX) Edges Higher Amid Consolidation Near Support - Retail Driven Moves - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>3</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>UMESLTD.NS</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Usha Martin Education &amp; Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>6.079999923706055</v>
+      </c>
+      <c r="F304" t="n">
+        <v>6.079999923706055</v>
+      </c>
+      <c r="G304" t="n">
+        <v>5.369999885559082</v>
+      </c>
+      <c r="H304" t="n">
+        <v>5.460000038146973</v>
+      </c>
+      <c r="I304" t="n">
+        <v>5.960000038146973</v>
+      </c>
+      <c r="J304" t="n">
+        <v>5.460000038146973</v>
+      </c>
+      <c r="K304" t="n">
+        <v>111981</v>
+      </c>
+      <c r="L304" t="n">
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>Do Usha Martin Education &amp; Solutions' (NSE:UMESLTD) Earnings Warrant Your Attention? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>Usha Martin Education &amp; Solutions Mar 2026 Earnings: Modest profit amid low revenue base - Earnings Per Share - Vinanet</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>Usha Martin Education &amp; Solutions Declines 3.66%: Testing Support at ₹5.24 - Retail Driven Moves - Vinanet</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>Usha Martin Education &amp; Solutions (UMESLTD.NS) Inches Lower Amidst Range-Bound Trading on the NSE - Insider Selling Alerts - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>Usha Martin Education &amp; Solutions (UMESLTD.NS): Stock Slips 1.03% as Support Levels Come Into Focus - Wave Extension - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>4</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>SHERVANI.NS</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate Limited</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>340</v>
+      </c>
+      <c r="F305" t="n">
+        <v>340</v>
+      </c>
+      <c r="G305" t="n">
+        <v>319.5499877929688</v>
+      </c>
+      <c r="H305" t="n">
+        <v>321.1499938964844</v>
+      </c>
+      <c r="I305" t="n">
+        <v>349.9500122070312</v>
+      </c>
+      <c r="J305" t="n">
+        <v>321.1499938964844</v>
+      </c>
+      <c r="K305" t="n">
+        <v>421</v>
+      </c>
+      <c r="L305" t="n">
+        <v>-8.23</v>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>SHERVANI Share Price Today - Shervani Industrial Syndicate Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate Limited: Shareholders Board Members Managers and Company Profile | INE011D01013 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate Limited: Shareholders Board Members Managers and Company Profile | INE011D01013 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>Shervani Indust Standalone June 2026 Net Sales at Rs 4.60 crore, down 40.95% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate consolidated net profit rises 291.18% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>5</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>KPL.NS</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Kwality Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>3604.10009765625</v>
+      </c>
+      <c r="F306" t="n">
+        <v>3634.5</v>
+      </c>
+      <c r="G306" t="n">
+        <v>3327</v>
+      </c>
+      <c r="H306" t="n">
+        <v>3361.10009765625</v>
+      </c>
+      <c r="I306" t="n">
+        <v>3630.300048828125</v>
+      </c>
+      <c r="J306" t="n">
+        <v>3361.10009765625</v>
+      </c>
+      <c r="K306" t="n">
+        <v>113689</v>
+      </c>
+      <c r="L306" t="n">
+        <v>-7.42</v>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>Kino Polska TV Spolka Akcyjna (WSE:KPL) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>KPL Share Price | Kwality Pharmaceuticals Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>Kino Polska TV S.A. Revenue Breakdown – GPW:KPL - TradingView</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>KPL Share Price | Kwality Pharmaceuticals Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>6</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>SIYSIL.NS</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Siyaram Silk Mills Limited</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>635</v>
+      </c>
+      <c r="F307" t="n">
+        <v>645.5</v>
+      </c>
+      <c r="G307" t="n">
+        <v>599.9500122070312</v>
+      </c>
+      <c r="H307" t="n">
+        <v>606.3499755859375</v>
+      </c>
+      <c r="I307" t="n">
+        <v>647.5499877929688</v>
+      </c>
+      <c r="J307" t="n">
+        <v>606.3499755859375</v>
+      </c>
+      <c r="K307" t="n">
+        <v>198647</v>
+      </c>
+      <c r="L307" t="n">
+        <v>-6.36</v>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>Siyaram Silk Mills Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>Siyaram Silk Mills sets Aug 22 record date for bonus preference shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>Siyaram Silk Mills sets Aug 22 record date for bonus preference shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>Siyaram Silk Mills Limited Reports Q1 FY27 Results: Total Income Rises 16.4% YoY to ₹466 Crore; PAT Surges to ₹11 Crore - EquityBulls</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>Siyaram Silk Mills Expands Authorised Share Capital After Scheme Approval - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>7</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>BANARISUG.NS</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Limited</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>4114.89990234375</v>
+      </c>
+      <c r="F308" t="n">
+        <v>4199</v>
+      </c>
+      <c r="G308" t="n">
+        <v>3950</v>
+      </c>
+      <c r="H308" t="n">
+        <v>4019.699951171875</v>
+      </c>
+      <c r="I308" t="n">
+        <v>4240.7001953125</v>
+      </c>
+      <c r="J308" t="n">
+        <v>4019.699951171875</v>
+      </c>
+      <c r="K308" t="n">
+        <v>22810</v>
+      </c>
+      <c r="L308" t="n">
+        <v>-5.21</v>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars secures Madras HC stay on ₹12.72 crore tax recovery - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>AfCFTA Trade Finance: Small Businesses Gain New Access via ITC-Equity Partnership - Earnings Weakness Phase - Vinanet</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>Stardust Power Inc. (SDST) Drops 5.95% as Stock Tests Key Support at $1.5 - Mutual Fund Flow - Vinanet</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>8</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>UEL.NS</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Ujaas Energy Limited</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>181.2299957275391</v>
+      </c>
+      <c r="F309" t="n">
+        <v>181.2299957275391</v>
+      </c>
+      <c r="G309" t="n">
+        <v>181.2299957275391</v>
+      </c>
+      <c r="H309" t="n">
+        <v>181.2299957275391</v>
+      </c>
+      <c r="I309" t="n">
+        <v>190.7599945068359</v>
+      </c>
+      <c r="J309" t="n">
+        <v>181.2299957275391</v>
+      </c>
+      <c r="K309" t="n">
+        <v>8804</v>
+      </c>
+      <c r="L309" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>Stock Watch: Shares Of These 10 Companies Slumped And Surged Over 5% Today - Do You Own Any? - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>Boehly Holds Talks Over Selling Shares To Majority Owners At Chelsea - Complete Sports</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>Ujaas Energy Q1 Standalone Net Profit Rises to 33M Rupees on Revenue of 30M Rupees - Sahi</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>Ujaas Energy Ltd. Share Price Shows Strong Price Action - Univest</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>Ujaas Energy Ltd. Share Price Jumps to New 52-Week Peak - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>9</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>INDOTHAI.NS</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Limited</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>59.65999984741211</v>
+      </c>
+      <c r="F310" t="n">
+        <v>59.65999984741211</v>
+      </c>
+      <c r="G310" t="n">
+        <v>59.65999984741211</v>
+      </c>
+      <c r="H310" t="n">
+        <v>59.65999984741211</v>
+      </c>
+      <c r="I310" t="n">
+        <v>62.79999923706055</v>
+      </c>
+      <c r="J310" t="n">
+        <v>59.65999984741211</v>
+      </c>
+      <c r="K310" t="n">
+        <v>84649</v>
+      </c>
+      <c r="L310" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>Stock Watch: Shares Of These 10 Companies Slumped And Surged Over 5% Today - Do You Own Any? - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>how InvestingPro’s fair value predicted 56% drop in Indo Thai Securities By Investing.com - Investing.com India</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>how InvestingPro’s fair value predicted 56% drop in Indo Thai Securities By Investing.com - Investing.com India</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Ltd. Share Price Falls 9.97% Today - Univest</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Ltd. (INDOTHAI) Share Price Hits Fresh 52-Week Low - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>10</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>NATIONSTD.NS</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>National Standard (India) Limited</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>128</v>
+      </c>
+      <c r="F311" t="n">
+        <v>140.3399963378906</v>
+      </c>
+      <c r="G311" t="n">
+        <v>126.9800033569336</v>
+      </c>
+      <c r="H311" t="n">
+        <v>126.9800033569336</v>
+      </c>
+      <c r="I311" t="n">
+        <v>133.6600036621094</v>
+      </c>
+      <c r="J311" t="n">
+        <v>126.9800033569336</v>
+      </c>
+      <c r="K311" t="n">
+        <v>464929</v>
+      </c>
+      <c r="L311" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>National Standard files FY26 BRSR, reports 100% related-party sales - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>National Standard files FY26 BRSR, reports 100% related-party sales - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr"/>
+      <c r="P311" t="inlineStr"/>
+      <c r="Q311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>11</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>SIEL.NS</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>38.29000091552734</v>
+      </c>
+      <c r="F312" t="n">
+        <v>40.29999923706055</v>
+      </c>
+      <c r="G312" t="n">
+        <v>38.29000091552734</v>
+      </c>
+      <c r="H312" t="n">
+        <v>38.29000091552734</v>
+      </c>
+      <c r="I312" t="n">
+        <v>40.29999923706055</v>
+      </c>
+      <c r="J312" t="n">
+        <v>38.29000091552734</v>
+      </c>
+      <c r="K312" t="n">
+        <v>7981</v>
+      </c>
+      <c r="L312" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises standalone profit rises 21.8% in Q1FY27 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>12</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>STYLEBAAZA.NS</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Baazar Style Retail Limited</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>437.8500061035156</v>
+      </c>
+      <c r="F313" t="n">
+        <v>447.1000061035156</v>
+      </c>
+      <c r="G313" t="n">
+        <v>417.6499938964844</v>
+      </c>
+      <c r="H313" t="n">
+        <v>417.6499938964844</v>
+      </c>
+      <c r="I313" t="n">
+        <v>439.6000061035156</v>
+      </c>
+      <c r="J313" t="n">
+        <v>417.6499938964844</v>
+      </c>
+      <c r="K313" t="n">
+        <v>2692008</v>
+      </c>
+      <c r="L313" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>Aditya Kumar Halwasiya acquires 6 per cent stake in Baazar Style Retail through Block Deal - ET Retail</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>Baazar Style Retail Independent Directors Step Down, Triggering Board Reshuffle - TipRanks</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-17 — cnbctv:75f67e8db094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>Baazar Style Retail Ltd. Share Price: Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>Baazar Style Retail Limited Announces Redesignation of Siddhant Khemani from Chief Marketing Officer to Head E-Commerce, Effective August 13, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>13</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>KMSUGAR.NS</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>K.M.Sugar Mills Limited</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>35.0099983215332</v>
+      </c>
+      <c r="F314" t="n">
+        <v>35.29999923706055</v>
+      </c>
+      <c r="G314" t="n">
+        <v>32.84999847412109</v>
+      </c>
+      <c r="H314" t="n">
+        <v>33.54999923706055</v>
+      </c>
+      <c r="I314" t="n">
+        <v>35.29999923706055</v>
+      </c>
+      <c r="J314" t="n">
+        <v>33.54999923706055</v>
+      </c>
+      <c r="K314" t="n">
+        <v>1436244</v>
+      </c>
+      <c r="L314" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>K.M. Sugar Mills Ltd. Share Price Rise With Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>NCLT Allahabad sanctions KM Sugar Mills distillery demerger scheme - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>K.M. Sugar Mills Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>K.M. Sugar Mills Ltd. Share Price Today With Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>NCLT Allahabad sanctions KM Sugar Mills distillery demerger scheme - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>14</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN.NS</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Limited</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>747.3499755859375</v>
+      </c>
+      <c r="F315" t="n">
+        <v>765</v>
+      </c>
+      <c r="G315" t="n">
+        <v>714</v>
+      </c>
+      <c r="H315" t="n">
+        <v>729.3499755859375</v>
+      </c>
+      <c r="I315" t="n">
+        <v>767.0999755859375</v>
+      </c>
+      <c r="J315" t="n">
+        <v>729.3499755859375</v>
+      </c>
+      <c r="K315" t="n">
+        <v>19992314</v>
+      </c>
+      <c r="L315" t="n">
+        <v>-4.92</v>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd Share Price Target, Forecast for Long Term Equity. - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Stock Update: Shares Slip on Duty-Free Sugar Imports - LatestLY</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price Hits One-Year High - Univest</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>15</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>MODIS.NS</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Modis Navnirman Limited</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>400</v>
+      </c>
+      <c r="F316" t="n">
+        <v>404.4500122070312</v>
+      </c>
+      <c r="G316" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="H316" t="n">
+        <v>383.1499938964844</v>
+      </c>
+      <c r="I316" t="n">
+        <v>402.7000122070312</v>
+      </c>
+      <c r="J316" t="n">
+        <v>383.1499938964844</v>
+      </c>
+      <c r="K316" t="n">
+        <v>142116</v>
+      </c>
+      <c r="L316" t="n">
+        <v>-4.85</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>Modis Navnirman Consolidated June 2026 Net Sales at Rs 58.26 crore, up 27.92% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>Modis Navnirman Consolidated June 2026 Net Sales at Rs 58.26 crore, up 27.92% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>Modis Navnirman reappoints Dinesh Modi at AGM; reports record FY26 growth - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>Modis Navnirman Standalone June 2026 Net Sales at Rs 58.26 crore, up 27.92% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>Modis Navnirman Share Price Target 2027 to 2030: Analyst Outlook - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>16</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>GANGAFORGE.NS</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Ganga Forging Limited</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>2.049999952316284</v>
+      </c>
+      <c r="F317" t="n">
+        <v>2.049999952316284</v>
+      </c>
+      <c r="G317" t="n">
+        <v>2.049999952316284</v>
+      </c>
+      <c r="H317" t="n">
+        <v>2.049999952316284</v>
+      </c>
+      <c r="I317" t="n">
+        <v>2.150000095367432</v>
+      </c>
+      <c r="J317" t="n">
+        <v>2.049999952316284</v>
+      </c>
+      <c r="K317" t="n">
+        <v>846238</v>
+      </c>
+      <c r="L317" t="n">
+        <v>-4.65</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>Ganga Forging rights issue sees 120% subscription, trading begins - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>Ganga Forging rights issue sees 120% subscription, trading begins - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr"/>
+      <c r="P317" t="inlineStr"/>
+      <c r="Q317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>17</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>PRAJIND.NS</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Praj Industries Limited</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>358</v>
+      </c>
+      <c r="F318" t="n">
+        <v>358</v>
+      </c>
+      <c r="G318" t="n">
+        <v>341.1499938964844</v>
+      </c>
+      <c r="H318" t="n">
+        <v>344.3500061035156</v>
+      </c>
+      <c r="I318" t="n">
+        <v>358.4500122070312</v>
+      </c>
+      <c r="J318" t="n">
+        <v>344.3500061035156</v>
+      </c>
+      <c r="K318" t="n">
+        <v>1661248</v>
+      </c>
+      <c r="L318" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>Praj Industries Stock And Two India Energy Names Tied To Higher Oil Prices - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>Praj Industries Ltd. Share Price Up 5.18%: Price Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>Praj Industries Limited Beat Analyst Estimates: See What The Consensus Is Forecasting For This Year - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>Praj Industries Ltd. (PRAJIND) Share Price Rises 6.1% Today - Univest</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>Praj Industries Ltd. Share Price Up 5.18%: Price Analysis - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>18</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>JAIBALAJI.NS</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Jai Balaji Industries Limited</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="F319" t="n">
+        <v>65.95999908447266</v>
+      </c>
+      <c r="G319" t="n">
+        <v>63.11000061035156</v>
+      </c>
+      <c r="H319" t="n">
+        <v>63.56999969482422</v>
+      </c>
+      <c r="I319" t="n">
+        <v>66.08000183105469</v>
+      </c>
+      <c r="J319" t="n">
+        <v>63.56999969482422</v>
+      </c>
+      <c r="K319" t="n">
+        <v>611558</v>
+      </c>
+      <c r="L319" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>Jai Balaji Industries Limited Announces Cessation of Bimal Kumar Choudhary as Whole-Time Director, Effective September 14, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>Jai Balaji Industries Limited Announces Cessation of Bimal Kumar Choudhary as Whole-Time Director, Effective September 14, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>Jai Balaji Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr"/>
+      <c r="Q319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>19</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>MATRIMONY.NS</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Matrimony.Com Limited</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>551.7999877929688</v>
+      </c>
+      <c r="F320" t="n">
+        <v>560.8499755859375</v>
+      </c>
+      <c r="G320" t="n">
+        <v>532</v>
+      </c>
+      <c r="H320" t="n">
+        <v>537.0499877929688</v>
+      </c>
+      <c r="I320" t="n">
+        <v>558.2000122070312</v>
+      </c>
+      <c r="J320" t="n">
+        <v>537.0499877929688</v>
+      </c>
+      <c r="K320" t="n">
+        <v>26974</v>
+      </c>
+      <c r="L320" t="n">
+        <v>-3.79</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>Matrimony.com relieves CFO Harigovind Krishnasamy effective Aug 17 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>Matrimony.com relieves CFO Harigovind Krishnasamy effective Aug 17 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>Income Investors Should Know That Matrimony.com Limited (NSE:MATRIMONY) Goes Ex-Dividend Soon - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>Matrimony.com soars after Q1 PAT spurts 127.5% YoY - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>Matrimony.com Shares Rally 10% After Q1 Net Profit Jumps 127.5% Year-on-Year - Margin Expansion Trends - Vinanet</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:29:09 IST</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>20</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>SALONA.NS</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Salona Cotspin Limited</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>272.989990234375</v>
+      </c>
+      <c r="F321" t="n">
+        <v>273</v>
+      </c>
+      <c r="G321" t="n">
+        <v>260.0499877929688</v>
+      </c>
+      <c r="H321" t="n">
+        <v>263.2999877929688</v>
+      </c>
+      <c r="I321" t="n">
+        <v>273.5299987792969</v>
+      </c>
+      <c r="J321" t="n">
+        <v>263.2999877929688</v>
+      </c>
+      <c r="K321" t="n">
+        <v>331</v>
+      </c>
+      <c r="L321" t="n">
+        <v>-3.74</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>Salona Cotspin Share Price Forecast to 2030 - Univest</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>RRP Semiconductor reports standalone net loss of Rs 0.33 crore in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>Salona Cotspin standalone net profit rises 47.71% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>RRP Semiconductor reports standalone net loss of Rs 0.33 crore in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>STL Global reports standalone net loss of Rs 1.25 crore in the June 2026 quarter - Business Standard</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q321"/>
+  <dimension ref="A1:Q341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18516,8 +18516,6 @@
           <t>Quadrant Future Tek Publishes Q1 FY27 Unaudited Results and Notifies Stock Exchanges - TipRanks</t>
         </is>
       </c>
-      <c r="P303" t="inlineStr"/>
-      <c r="Q303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -18646,8 +18644,6 @@
           <t>KJMC Financial Services net profit rises to ₹162.85 lakh in Q1FY26 - scanx.trade</t>
         </is>
       </c>
-      <c r="P305" t="inlineStr"/>
-      <c r="Q305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -18781,7 +18777,6 @@
           <t>Next Digital probe halted - news.gov.hk</t>
         </is>
       </c>
-      <c r="Q307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -18841,8 +18836,6 @@
           <t>Record Heat Drives UK Online Retail Sales to Five-Year High in June - Book Value Growth - Vinanet</t>
         </is>
       </c>
-      <c r="P308" t="inlineStr"/>
-      <c r="Q308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -19109,8 +19102,6 @@
           <t>TBZ Reports Strong Unaudited Q1 FY27 Results, Maintains Profit Momentum - TipRanks</t>
         </is>
       </c>
-      <c r="P312" t="inlineStr"/>
-      <c r="Q312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -19239,8 +19230,6 @@
           <t>Thomas Cook India Sets Virtual AGM to Approve Dividend, Financials and Board Changes - TipRanks</t>
         </is>
       </c>
-      <c r="P314" t="inlineStr"/>
-      <c r="Q314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -19581,7 +19570,6 @@
           <t>Lambodhara Textiles net profit rises 66% in Q1FY26 on lower finance costs - scanx.trade</t>
         </is>
       </c>
-      <c r="Q319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -19636,9 +19624,6 @@
           <t>Atlanta Electricals Schedules Investor and Analyst Meetings in Mumbai - TipRanks</t>
         </is>
       </c>
-      <c r="O320" t="inlineStr"/>
-      <c r="P320" t="inlineStr"/>
-      <c r="Q320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -19706,6 +19691,1306 @@
       <c r="Q321" t="inlineStr">
         <is>
           <t>Bluspring subsidiary secures ₹125 Cr term loan for LSG acquisition - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>1</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>MINALIND.NS</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Minal Industries Limited</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>3.089999914169312</v>
+      </c>
+      <c r="F322" t="n">
+        <v>3.180000066757202</v>
+      </c>
+      <c r="G322" t="n">
+        <v>3.089999914169312</v>
+      </c>
+      <c r="H322" t="n">
+        <v>3.180000066757202</v>
+      </c>
+      <c r="I322" t="n">
+        <v>2.650000095367432</v>
+      </c>
+      <c r="J322" t="n">
+        <v>3.180000066757202</v>
+      </c>
+      <c r="K322" t="n">
+        <v>148926</v>
+      </c>
+      <c r="L322" t="n">
+        <v>20</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>MINALIND Share Price Today - Minal Industries Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>Minal Industries (NSE:MINALIND) Shiller PE Ratio : (As of Aug. 22, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>Free float of Minal Industries Limited – NSE:MINALIND - TradingView</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>Minal Industries Limited Announces Appointment of Saket Rajendra Sugandh as Company Secretary and Compliance Officer, Effective August 5, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>Minal Industries (NSE:MINALIND) Shiller PE Ratio : (As of Aug. 22, 2026) - GuruFocus</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>2</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>QUADFUTURE.NS</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Quadrant Future Tek Limited</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>340</v>
+      </c>
+      <c r="F323" t="n">
+        <v>405.3500061035156</v>
+      </c>
+      <c r="G323" t="n">
+        <v>339</v>
+      </c>
+      <c r="H323" t="n">
+        <v>405.3500061035156</v>
+      </c>
+      <c r="I323" t="n">
+        <v>337.7999877929688</v>
+      </c>
+      <c r="J323" t="n">
+        <v>405.3500061035156</v>
+      </c>
+      <c r="K323" t="n">
+        <v>7504777</v>
+      </c>
+      <c r="L323" t="n">
+        <v>20</v>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>Quadrant Future Tek Publishes Q1 FY27 Unaudited Results and Notifies Stock Exchanges - TipRanks</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr"/>
+      <c r="Q323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>3</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>SHANTIGEAR.NS</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Shanthi Gears Limited</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>395</v>
+      </c>
+      <c r="F324" t="n">
+        <v>464.25</v>
+      </c>
+      <c r="G324" t="n">
+        <v>395</v>
+      </c>
+      <c r="H324" t="n">
+        <v>464.25</v>
+      </c>
+      <c r="I324" t="n">
+        <v>386.8999938964844</v>
+      </c>
+      <c r="J324" t="n">
+        <v>464.25</v>
+      </c>
+      <c r="K324" t="n">
+        <v>1972065</v>
+      </c>
+      <c r="L324" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>Shanthi Gears Ltd. (SHANTIGEAR) Share Price Hits Fresh 52-Week Low - Univest</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>Shanthi Gears Share: பெற்றோர் கம்பெனி நம்பிக்கை! **18%** குதித்தது ஷேர் விலை! - Whalesbook</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>Shanthi Gears Share Price at Fresh 52-Week Low - Univest</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>Tube Investments of India acquires 2.69% stake in Shanthi Gears - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>Tube Investments of India Increases Stake in Shanthi Gears - InvestyWise</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>4</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>MPDL.NS</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>MPDL Limited</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>39.9900016784668</v>
+      </c>
+      <c r="F325" t="n">
+        <v>41.18000030517578</v>
+      </c>
+      <c r="G325" t="n">
+        <v>39.20000076293945</v>
+      </c>
+      <c r="H325" t="n">
+        <v>41.18000030517578</v>
+      </c>
+      <c r="I325" t="n">
+        <v>34.31999969482422</v>
+      </c>
+      <c r="J325" t="n">
+        <v>41.18000030517578</v>
+      </c>
+      <c r="K325" t="n">
+        <v>14902</v>
+      </c>
+      <c r="L325" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>MPDL Share Price Today - MPDL Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>MPDL (NSE:MPDL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of MPDL Ltd – NSE:MPDL - TradingView</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>MPDL (NSE:MPDL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>MPDL reports consolidated net loss of Rs 4.20 crore in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>5</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>NDL.NS</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Nandan Denim Limited</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>2.279999971389771</v>
+      </c>
+      <c r="F326" t="n">
+        <v>2.710000038146973</v>
+      </c>
+      <c r="G326" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H326" t="n">
+        <v>2.710000038146973</v>
+      </c>
+      <c r="I326" t="n">
+        <v>2.259999990463257</v>
+      </c>
+      <c r="J326" t="n">
+        <v>2.710000038146973</v>
+      </c>
+      <c r="K326" t="n">
+        <v>5991494</v>
+      </c>
+      <c r="L326" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>NCLT admits NDL Ventures-Hinduja Leyland merger petition - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>NCLT admits NDL Ventures-Hinduja Leyland merger petition - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>Next Digital probe halted - news.gov.hk</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>NDL Ventures Shareholders Approve Scheme of Merger by Absorption of Hinduja Leyland Finance Limited - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>NDL Ventures Q1 FY27 Results: Revenue, PAT &amp; Key Highlights - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>6</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>NKIND.NS</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>NK Industries Limited</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>60</v>
+      </c>
+      <c r="F327" t="n">
+        <v>67.91999816894531</v>
+      </c>
+      <c r="G327" t="n">
+        <v>58.09999847412109</v>
+      </c>
+      <c r="H327" t="n">
+        <v>67.62000274658203</v>
+      </c>
+      <c r="I327" t="n">
+        <v>56.59999847412109</v>
+      </c>
+      <c r="J327" t="n">
+        <v>67.62000274658203</v>
+      </c>
+      <c r="K327" t="n">
+        <v>327876</v>
+      </c>
+      <c r="L327" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>NK Industries Limited (NKIND.NS) Holds Near Support as Modest Uptick Stalls at Resistance - High Conviction Picks - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>Record Heat Drives UK Online Retail Sales to Five-Year High in June - Book Value Growth - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>NK Industries (NKIND.NS) Hovers Near ₹59 Amid Narrow Range, Support at ₹56.16 in Focus - Monthly Profile - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>NK Industries Limited Q2 2026 Earnings: Revenue Declines Sharply on Weak Operational Environment; EPS Turns Negative - Performance Review - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>NK Industries Limited (NKIND.NS): Marginal Gain Amid Consolidation Near Key Resistance - Dark Pool Prints - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>7</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>BIRLAPREC.NS</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>39.11999893188477</v>
+      </c>
+      <c r="F328" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="G328" t="n">
+        <v>38.13000106811523</v>
+      </c>
+      <c r="H328" t="n">
+        <v>44.40000152587891</v>
+      </c>
+      <c r="I328" t="n">
+        <v>39.11000061035156</v>
+      </c>
+      <c r="J328" t="n">
+        <v>44.40000152587891</v>
+      </c>
+      <c r="K328" t="n">
+        <v>986460</v>
+      </c>
+      <c r="L328" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies (BIRLAPREC.NS): Stock Eases Marginally, Nears Key Support Level - Symmetrical Triangle - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Mar 2026 Earnings: Steady EPS Delivery Amid Modest Revenue Performance - Tangible Book Value - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>BIRLAPREC Share Price Today - Birla Precision Technologies Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>BIRLAPREC.NS Dec 2025 Earnings: Modest EPS of ₹0.19 on Stable Revenues - Segment Revenue Breakdown - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Mar 2026 Earnings: Steady EPS Delivery Amid Modest Revenue Performance - Tangible Book Value - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>8</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>MODIRUBBER.NS</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Modi Rubber Limited</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>119</v>
+      </c>
+      <c r="F329" t="n">
+        <v>144</v>
+      </c>
+      <c r="G329" t="n">
+        <v>117.8000030517578</v>
+      </c>
+      <c r="H329" t="n">
+        <v>134.2400054931641</v>
+      </c>
+      <c r="I329" t="n">
+        <v>120.0699996948242</v>
+      </c>
+      <c r="J329" t="n">
+        <v>134.2400054931641</v>
+      </c>
+      <c r="K329" t="n">
+        <v>40792</v>
+      </c>
+      <c r="L329" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>Modi Rubber Ltd. Share Price Update: Fundamentals Check - Univest</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>Modi Rubber Ltd. Share Price Update: Fundamentals Check - Univest</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>Modi Rubber seeks shareholder approval to appoint Ajay Kumar Jain as Independent Director - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>Modi Rubber Ltd. Share Price Today Up 20%: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>Modi Rubber approves comfort letter for Gujarat Guardian expansion project - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>9</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>KLBRENG-B.NS</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Kilburn Engineering Limited</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>364</v>
+      </c>
+      <c r="F330" t="n">
+        <v>408.6000061035156</v>
+      </c>
+      <c r="G330" t="n">
+        <v>361.7000122070312</v>
+      </c>
+      <c r="H330" t="n">
+        <v>397.3999938964844</v>
+      </c>
+      <c r="I330" t="n">
+        <v>357.6499938964844</v>
+      </c>
+      <c r="J330" t="n">
+        <v>397.3999938964844</v>
+      </c>
+      <c r="K330" t="n">
+        <v>3833782</v>
+      </c>
+      <c r="L330" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>Kilburn Engineering Ltd. Share Price Rises 9.96% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>Kilburn Engineering (NSE:KLBRENG-B) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>Kilburn Engineering (NSE:KLBRENG-B) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr"/>
+      <c r="Q330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>10</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>ORIRAIL.NS</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Oriental Rail Infrastructure Limited</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>106.8899993896484</v>
+      </c>
+      <c r="F331" t="n">
+        <v>124.3499984741211</v>
+      </c>
+      <c r="G331" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="H331" t="n">
+        <v>114.7799987792969</v>
+      </c>
+      <c r="I331" t="n">
+        <v>103.629997253418</v>
+      </c>
+      <c r="J331" t="n">
+        <v>114.7799987792969</v>
+      </c>
+      <c r="K331" t="n">
+        <v>1142227</v>
+      </c>
+      <c r="L331" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>Average basic shares outstanding of Oriental Rail Infrastructure Ltd. – NSE:ORIRAIL - TradingView</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>Oriental Rail Infrastructure (NSE:ORIRAIL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>Oriental Rail Infrastructure (NSE:ORIRAIL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>Oriental Rail Infrastructure shares permitted to trade on NSE - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>Oriental Rail Infrastructure (NSE:ORIRAIL) Cyclically Adjus - GuruFocus</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>11</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>QUINT.NS</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Quint Digital Limited</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>38</v>
+      </c>
+      <c r="F332" t="n">
+        <v>41.79999923706055</v>
+      </c>
+      <c r="G332" t="n">
+        <v>36.79999923706055</v>
+      </c>
+      <c r="H332" t="n">
+        <v>40.34000015258789</v>
+      </c>
+      <c r="I332" t="n">
+        <v>36.5099983215332</v>
+      </c>
+      <c r="J332" t="n">
+        <v>40.34000015258789</v>
+      </c>
+      <c r="K332" t="n">
+        <v>65255</v>
+      </c>
+      <c r="L332" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>Quint Digital submits Letter of Offer for ₹908.8 lakh rights issue - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>Quint Digital submits Letter of Offer for ₹908.8 lakh rights issue - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>Quint Digital Ltd. Share Price Up 10.53%: Full Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>Quint Digital Ltd. Share Price Update With Valuation Check - Univest</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>BJP Shares Misleading Claim About Rahul Gandhi 'Insulting' the National Anthem - The Quint</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>12</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>S&amp;SPOWER.NS</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Switchgears Limited</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>286</v>
+      </c>
+      <c r="F333" t="n">
+        <v>298.8500061035156</v>
+      </c>
+      <c r="G333" t="n">
+        <v>271.7000122070312</v>
+      </c>
+      <c r="H333" t="n">
+        <v>298.8500061035156</v>
+      </c>
+      <c r="I333" t="n">
+        <v>271.7000122070312</v>
+      </c>
+      <c r="J333" t="n">
+        <v>298.8500061035156</v>
+      </c>
+      <c r="K333" t="n">
+        <v>12178</v>
+      </c>
+      <c r="L333" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Switchgear Ltd. Share Price Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Switchgear Ltd. Share Price Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr"/>
+      <c r="Q333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>13</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>LEENEE.NS</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Lee &amp; Nee Softwares Exports Limited</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>8.439999580383301</v>
+      </c>
+      <c r="F334" t="n">
+        <v>9.510000228881836</v>
+      </c>
+      <c r="G334" t="n">
+        <v>7.559999942779541</v>
+      </c>
+      <c r="H334" t="n">
+        <v>9.189999580383301</v>
+      </c>
+      <c r="I334" t="n">
+        <v>8.359999656677246</v>
+      </c>
+      <c r="J334" t="n">
+        <v>9.189999580383301</v>
+      </c>
+      <c r="K334" t="n">
+        <v>99370</v>
+      </c>
+      <c r="L334" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>Lee &amp; Nee Softwares (Exports) (NSE:LEENEE) Cyclically Adjus - GuruFocus</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>Lee &amp; Nee Softwares (Exports) (NSE:LEENEE) Cyclically Adjus - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr"/>
+      <c r="P334" t="inlineStr"/>
+      <c r="Q334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>14</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>LAMBODHARA.NS</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Lambodhara Textiles Limited</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>107.629997253418</v>
+      </c>
+      <c r="F335" t="n">
+        <v>124</v>
+      </c>
+      <c r="G335" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="H335" t="n">
+        <v>118.0800018310547</v>
+      </c>
+      <c r="I335" t="n">
+        <v>107.629997253418</v>
+      </c>
+      <c r="J335" t="n">
+        <v>118.0800018310547</v>
+      </c>
+      <c r="K335" t="n">
+        <v>83175</v>
+      </c>
+      <c r="L335" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>Lambodhara Textiles Share Price Today: 8.85% Price Rise - Univest</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>Lambodhara Textiles Share Price Today: 8.85% Price Rise - Univest</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>Lambodhara Text Standalone June 2026 Net Sales at Rs 53.88 crore, down 8.83% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>MDS &amp; Associates LLP resigns as Lambodhara Textiles secretarial auditor - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>Lambodhara Textiles Q1 FY27 Results: Revenue, PAT &amp; Key Highlight - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>15</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>CRSL.NS</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>3.369999885559082</v>
+      </c>
+      <c r="F336" t="n">
+        <v>3.390000104904175</v>
+      </c>
+      <c r="G336" t="n">
+        <v>3.200000047683716</v>
+      </c>
+      <c r="H336" t="n">
+        <v>3.390000104904175</v>
+      </c>
+      <c r="I336" t="n">
+        <v>3.089999914169312</v>
+      </c>
+      <c r="J336" t="n">
+        <v>3.390000104904175</v>
+      </c>
+      <c r="K336" t="n">
+        <v>4265503</v>
+      </c>
+      <c r="L336" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>CRSL Share Price Today - Cressanda Railway Solutions Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>CRSL Share Price Today - Cressanda Railway Solutions Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr"/>
+      <c r="P336" t="inlineStr"/>
+      <c r="Q336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>16</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>ATLANTAELE.NS</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Atlanta Electricals Limited</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>1712.900024414062</v>
+      </c>
+      <c r="F337" t="n">
+        <v>1857.400024414062</v>
+      </c>
+      <c r="G337" t="n">
+        <v>1700</v>
+      </c>
+      <c r="H337" t="n">
+        <v>1846.900024414062</v>
+      </c>
+      <c r="I337" t="n">
+        <v>1688.599975585938</v>
+      </c>
+      <c r="J337" t="n">
+        <v>1846.900024414062</v>
+      </c>
+      <c r="K337" t="n">
+        <v>402945</v>
+      </c>
+      <c r="L337" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>ATLANTAELE Forecast — Price Target — Prediction for 2027 - TradingView</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>Atlanta Electricals shares slide 5% despite strong Q1 results; stock hits lower band - BusinessLine</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>Atlanta Electricals Limited (NSE:ATLANTAELE) Stock Has Shown Weakness Lately But Financials Look Strong: Should Prospective Shareholders Make The Leap? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>Atlanta Electricals shares slide 5% despite strong Q1 results; stock hits lower band - BusinessLine</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>Atlanta Electricals Ltd. | Stock Share Price Live - MarketSmith India</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>17</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>SUBEXLTD.NS</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Subex Limited</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>17.23999977111816</v>
+      </c>
+      <c r="F338" t="n">
+        <v>19.38999938964844</v>
+      </c>
+      <c r="G338" t="n">
+        <v>17.14999961853027</v>
+      </c>
+      <c r="H338" t="n">
+        <v>18.65999984741211</v>
+      </c>
+      <c r="I338" t="n">
+        <v>17.07999992370605</v>
+      </c>
+      <c r="J338" t="n">
+        <v>18.65999984741211</v>
+      </c>
+      <c r="K338" t="n">
+        <v>24036145</v>
+      </c>
+      <c r="L338" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>Subex Ltd hosts non-deal analyst roadshow in Mumbai on August 19 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>Subex Ltd hosts non-deal analyst roadshow in Mumbai on August 19 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr"/>
+      <c r="P338" t="inlineStr"/>
+      <c r="Q338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>18</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>SIL.NS</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Standard Industries Limited</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>19.20000076293945</v>
+      </c>
+      <c r="F339" t="n">
+        <v>22.29999923706055</v>
+      </c>
+      <c r="G339" t="n">
+        <v>18.80999946594238</v>
+      </c>
+      <c r="H339" t="n">
+        <v>20.84000015258789</v>
+      </c>
+      <c r="I339" t="n">
+        <v>19.11000061035156</v>
+      </c>
+      <c r="J339" t="n">
+        <v>20.84000015258789</v>
+      </c>
+      <c r="K339" t="n">
+        <v>592621</v>
+      </c>
+      <c r="L339" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>Global X Silver Miners ETF (NYSE: SIL) Share Price, SIL Stock News, SIL Share Price &amp; Updates - kalkine.ca</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>Global X Silver Miners ETF (NYSE: SIL) Share Price, SIL Stock News, SIL Share Price &amp; Updates - kalkine.ca</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>(SIL) Equity Trading Insights (SIL:CA) - Stock Traders Daily</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>SIL News | GLOBAL X SILVER MINERS ETF (NYSEARCA:SIL) - ChartMill</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>Global X Silver Miners ETF (NYSE: SIL) Share Price, SIL Stock News, SIL Share Price &amp; Updates - Kalkine</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>19</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>WHBRADY.NS</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>WH Brady &amp; Company Limited</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>502</v>
+      </c>
+      <c r="F340" t="n">
+        <v>539.8499755859375</v>
+      </c>
+      <c r="G340" t="n">
+        <v>502</v>
+      </c>
+      <c r="H340" t="n">
+        <v>534.5</v>
+      </c>
+      <c r="I340" t="n">
+        <v>490.2000122070312</v>
+      </c>
+      <c r="J340" t="n">
+        <v>534.5</v>
+      </c>
+      <c r="K340" t="n">
+        <v>148</v>
+      </c>
+      <c r="L340" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr"/>
+      <c r="O340" t="inlineStr"/>
+      <c r="P340" t="inlineStr"/>
+      <c r="Q340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>20</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>FCL.NS</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Fineotex Chemical Limited</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>43.68000030517578</v>
+      </c>
+      <c r="F341" t="n">
+        <v>47.90000152587891</v>
+      </c>
+      <c r="G341" t="n">
+        <v>43.43000030517578</v>
+      </c>
+      <c r="H341" t="n">
+        <v>47.43000030517578</v>
+      </c>
+      <c r="I341" t="n">
+        <v>43.54999923706055</v>
+      </c>
+      <c r="J341" t="n">
+        <v>47.43000030517578</v>
+      </c>
+      <c r="K341" t="n">
+        <v>34486545</v>
+      </c>
+      <c r="L341" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>Fineos (ASX:FCL) Shares Edge Lower Amid Weaker Technology Sector Sentiment - Kalkine</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>ETFs Investing in Fineotex Chemical Limited Stocks - TradingView</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>Why Are Investors Watching Fineos (ASX:FCL) After Its Latest Share Price Decline? - Kalkine</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>FINEOS (ASX:FCL) Shares Rebound As Profit Emerges Under Rich P E - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>Fineos (ASX: FCL) Crosses Profitability Inflection Point In H1 FY 2026 - A Rich Life</t>
         </is>
       </c>
     </row>
@@ -19720,7 +21005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q321"/>
+  <dimension ref="A1:Q341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37471,7 +38756,6 @@
           <t>Protalix BioTherapeutics (PLX) Edges Higher Amid Consolidation Near Support - Retail Driven Moves - Vinanet</t>
         </is>
       </c>
-      <c r="Q303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -37674,7 +38958,6 @@
           <t>KPL Share Price | Kwality Pharmaceuticals Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
         </is>
       </c>
-      <c r="Q306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -38005,9 +39288,6 @@
           <t>National Standard files FY26 BRSR, reports 100% related-party sales - scanx.trade</t>
         </is>
       </c>
-      <c r="O311" t="inlineStr"/>
-      <c r="P311" t="inlineStr"/>
-      <c r="Q311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -38072,7 +39352,6 @@
           <t>Superior Industrial Enterprises standalone profit rises 21.8% in Q1FY27 - scanx.trade</t>
         </is>
       </c>
-      <c r="Q312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -38403,9 +39682,6 @@
           <t>Ganga Forging rights issue sees 120% subscription, trading begins - scanx.trade</t>
         </is>
       </c>
-      <c r="O317" t="inlineStr"/>
-      <c r="P317" t="inlineStr"/>
-      <c r="Q317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -38534,8 +39810,6 @@
           <t>Jai Balaji Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
-      <c r="P319" t="inlineStr"/>
-      <c r="Q319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -38672,6 +39946,1310 @@
       <c r="Q321" t="inlineStr">
         <is>
           <t>STL Global reports standalone net loss of Rs 1.25 crore in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>1</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>SHAH.NS</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Shah Metacorp Limited</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>3.980000019073486</v>
+      </c>
+      <c r="F322" t="n">
+        <v>4.050000190734863</v>
+      </c>
+      <c r="G322" t="n">
+        <v>3.160000085830688</v>
+      </c>
+      <c r="H322" t="n">
+        <v>3.329999923706055</v>
+      </c>
+      <c r="I322" t="n">
+        <v>3.950000047683716</v>
+      </c>
+      <c r="J322" t="n">
+        <v>3.329999923706055</v>
+      </c>
+      <c r="K322" t="n">
+        <v>5879851</v>
+      </c>
+      <c r="L322" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>‘Adding a few floors’: Anand Pandit shares renovation details on Shah Rukh Khan’s Mannat - The Indian Express</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>‘Adding a few floors’: Anand Pandit shares renovation details on Shah Rukh Khan’s Mannat - The Indian Express</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>Rocket Pharmaceuticals CEO Gaurav Shah sells $7,752 in shares - Investing.com</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>Yash Chemex promoter Paxal Shah buys 3500 shares on BSE - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>New-age stocks, IPOs and valuations: Envision's Nilesh Shah shares his investment playbook - CNBC TV18</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>2</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>UMESLTD.NS</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Usha Martin Education &amp; Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>6.079999923706055</v>
+      </c>
+      <c r="F323" t="n">
+        <v>6.079999923706055</v>
+      </c>
+      <c r="G323" t="n">
+        <v>5.369999885559082</v>
+      </c>
+      <c r="H323" t="n">
+        <v>5.460000038146973</v>
+      </c>
+      <c r="I323" t="n">
+        <v>5.960000038146973</v>
+      </c>
+      <c r="J323" t="n">
+        <v>5.460000038146973</v>
+      </c>
+      <c r="K323" t="n">
+        <v>111981</v>
+      </c>
+      <c r="L323" t="n">
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>Usha Martin Education &amp; Solutions Declines 3.66%: Testing Support at ₹5.24 - Retail Driven Moves - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>Usha Martin Education &amp; Solutions Mar 2026 Earnings: Modest profit amid low revenue base - Earnings Per Share - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>KASTURI Stock Price and Chart — BSE:KASTURI - TradingView</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>Usha Martin Education &amp; Solutions Mar 2026 Earnings: EPS of ₹0.07 on Revenue of ₹0.32 Cr; Stock Declines Marginally - Strong Earnings Momentum - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>Usha Martin Education &amp; Solutions Share Price - Upstox</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>3</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>SHERVANI.NS</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate Limited</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>340</v>
+      </c>
+      <c r="F324" t="n">
+        <v>340</v>
+      </c>
+      <c r="G324" t="n">
+        <v>319.5499877929688</v>
+      </c>
+      <c r="H324" t="n">
+        <v>321.1499938964844</v>
+      </c>
+      <c r="I324" t="n">
+        <v>349.9500122070312</v>
+      </c>
+      <c r="J324" t="n">
+        <v>321.1499938964844</v>
+      </c>
+      <c r="K324" t="n">
+        <v>421</v>
+      </c>
+      <c r="L324" t="n">
+        <v>-8.23</v>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>SHERVANI Share Price Today - Shervani Industrial Syndicate Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate (NSE:SHERVANI) Cyclically Adj - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate Limited: Shareholders Board Members Managers and Company Profile | INE011D01013 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate (NSE:SHERVANI) Cyclically Adj - GuruFocus</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>Shervani Indust Standalone June 2026 Net Sales at Rs 4.60 crore, down 40.95% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>4</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>KPL.NS</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Kwality Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>3604.10009765625</v>
+      </c>
+      <c r="F325" t="n">
+        <v>3634.5</v>
+      </c>
+      <c r="G325" t="n">
+        <v>3327</v>
+      </c>
+      <c r="H325" t="n">
+        <v>3361.10009765625</v>
+      </c>
+      <c r="I325" t="n">
+        <v>3630.300048828125</v>
+      </c>
+      <c r="J325" t="n">
+        <v>3361.10009765625</v>
+      </c>
+      <c r="K325" t="n">
+        <v>113735</v>
+      </c>
+      <c r="L325" t="n">
+        <v>-7.42</v>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>Kino Polska TV Spolka Akcyjna (WSE:KPL) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>Kino Polska TV Spolka Akcyjna (WSE:KPL) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr"/>
+      <c r="P325" t="inlineStr"/>
+      <c r="Q325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>5</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>HSCL.NS</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Himadri Speciality Chemical Limited</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>705.0999755859375</v>
+      </c>
+      <c r="F326" t="n">
+        <v>711</v>
+      </c>
+      <c r="G326" t="n">
+        <v>650</v>
+      </c>
+      <c r="H326" t="n">
+        <v>654.4000244140625</v>
+      </c>
+      <c r="I326" t="n">
+        <v>704.2000122070312</v>
+      </c>
+      <c r="J326" t="n">
+        <v>654.4000244140625</v>
+      </c>
+      <c r="K326" t="n">
+        <v>17256079</v>
+      </c>
+      <c r="L326" t="n">
+        <v>-7.07</v>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>Himadri Speciality Chemical Ltd. (HSCL) Share Price Falls 3.13% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>HSCL Share Price | Himadri Speciality Chemical Ltd Stock Analysis &amp; Recommendation - marketsmojo.com</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>Himadri Speciality Chemical Ltd. (HSCL) Share Price Falls 7.32% Today - Univest</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>HSCL Share Price | Himadri Speciality Chemical Ltd Stock Analysis &amp; Recommendation - marketsmojo.com</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>6</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>KSE.NS</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>KSE Limited</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>192.0099945068359</v>
+      </c>
+      <c r="F327" t="n">
+        <v>192.8600006103516</v>
+      </c>
+      <c r="G327" t="n">
+        <v>183.3000030517578</v>
+      </c>
+      <c r="H327" t="n">
+        <v>183.8399963378906</v>
+      </c>
+      <c r="I327" t="n">
+        <v>196.8000030517578</v>
+      </c>
+      <c r="J327" t="n">
+        <v>183.8399963378906</v>
+      </c>
+      <c r="K327" t="n">
+        <v>71756</v>
+      </c>
+      <c r="L327" t="n">
+        <v>-6.59</v>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>KSE Q1 FY27 Results: Revenue grew to Rs 454 Cr, PAT -97% - Univest</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>Stock market slips 1.6% on Hormuz uncertainty - The Express Tribune</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>Stock market slips 1.6% on Hormuz uncertainty - The Express Tribune</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>KSE-100 Index gains 575 points as buying returns to PSX - Business Recorder</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>KSE Ltd Q1 Results: Unaudited financials filed for June 2026 quarter - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>7</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>SIYSIL.NS</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Siyaram Silk Mills Limited</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>635</v>
+      </c>
+      <c r="F328" t="n">
+        <v>645.5</v>
+      </c>
+      <c r="G328" t="n">
+        <v>599.9500122070312</v>
+      </c>
+      <c r="H328" t="n">
+        <v>606.3499755859375</v>
+      </c>
+      <c r="I328" t="n">
+        <v>647.5499877929688</v>
+      </c>
+      <c r="J328" t="n">
+        <v>606.3499755859375</v>
+      </c>
+      <c r="K328" t="n">
+        <v>198798</v>
+      </c>
+      <c r="L328" t="n">
+        <v>-6.36</v>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>Siyaram Silk Mills Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>Siyaram Silk Mills Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>Siyaram Silk Mills sets Aug 22 record date for bonus preference shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr"/>
+      <c r="Q328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>8</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>ABINFRA.NS</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>A B Infrabuild Limited</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>13.35000038146973</v>
+      </c>
+      <c r="F329" t="n">
+        <v>13.72999954223633</v>
+      </c>
+      <c r="G329" t="n">
+        <v>12.19999980926514</v>
+      </c>
+      <c r="H329" t="n">
+        <v>12.63000011444092</v>
+      </c>
+      <c r="I329" t="n">
+        <v>13.34000015258789</v>
+      </c>
+      <c r="J329" t="n">
+        <v>12.63000011444092</v>
+      </c>
+      <c r="K329" t="n">
+        <v>14180685</v>
+      </c>
+      <c r="L329" t="n">
+        <v>-5.32</v>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>AB Infrabuild Ltd. Share Price News: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>A B Infrabuild Limited announces Annual dividend, payable on October 28, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>AB Infrabuild Ltd. Share Price News: Price Action Check - Univest</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>A B Infrabuild Limited announces Annual dividend, payable on October 28, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>A B Infrabuild schedules AGM and announces book closure - Business Upturn</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>9</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>RTSPOWR.NS</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>RTS Power Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="F330" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="G330" t="n">
+        <v>92</v>
+      </c>
+      <c r="H330" t="n">
+        <v>93.33000183105469</v>
+      </c>
+      <c r="I330" t="n">
+        <v>98.51999664306641</v>
+      </c>
+      <c r="J330" t="n">
+        <v>93.33000183105469</v>
+      </c>
+      <c r="K330" t="n">
+        <v>10016</v>
+      </c>
+      <c r="L330" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>RTS Power Corporation Ltd Income Statement – NSE:RTSPOWR - TradingView</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>RTS Power (NSE:RTSPOWR) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>RTS Power Corporation Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>RTS Power (NSE:RTSPOWR) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>10</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>BANARISUG.NS</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Limited</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>4114.89990234375</v>
+      </c>
+      <c r="F331" t="n">
+        <v>4199</v>
+      </c>
+      <c r="G331" t="n">
+        <v>3950</v>
+      </c>
+      <c r="H331" t="n">
+        <v>4019.699951171875</v>
+      </c>
+      <c r="I331" t="n">
+        <v>4240.7001953125</v>
+      </c>
+      <c r="J331" t="n">
+        <v>4019.699951171875</v>
+      </c>
+      <c r="K331" t="n">
+        <v>22815</v>
+      </c>
+      <c r="L331" t="n">
+        <v>-5.21</v>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars secures Madras HC stay on ₹12.72 crore tax recovery - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Q1FY26 net loss widens to ₹109 million - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>11</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>HAPPYFORGE.NS</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Happy Forgings Limited</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>2318.10009765625</v>
+      </c>
+      <c r="F332" t="n">
+        <v>2318.10009765625</v>
+      </c>
+      <c r="G332" t="n">
+        <v>2211.800048828125</v>
+      </c>
+      <c r="H332" t="n">
+        <v>2211.800048828125</v>
+      </c>
+      <c r="I332" t="n">
+        <v>2328.199951171875</v>
+      </c>
+      <c r="J332" t="n">
+        <v>2211.800048828125</v>
+      </c>
+      <c r="K332" t="n">
+        <v>91079</v>
+      </c>
+      <c r="L332" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>Happy Forgings Limited Just Beat EPS By 10.0%: Here's What Analysts Think Will Happen Next - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>Happy Forgings Limited Just Beat EPS By 10.0%: Here's What Analysts Think Will Happen Next - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr"/>
+      <c r="P332" t="inlineStr"/>
+      <c r="Q332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>12</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>NATIONSTD.NS</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>National Standard (India) Limited</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>128</v>
+      </c>
+      <c r="F333" t="n">
+        <v>140.3399963378906</v>
+      </c>
+      <c r="G333" t="n">
+        <v>126.9800033569336</v>
+      </c>
+      <c r="H333" t="n">
+        <v>126.9800033569336</v>
+      </c>
+      <c r="I333" t="n">
+        <v>133.6600036621094</v>
+      </c>
+      <c r="J333" t="n">
+        <v>126.9800033569336</v>
+      </c>
+      <c r="K333" t="n">
+        <v>464929</v>
+      </c>
+      <c r="L333" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>National Standard (India) (NSE:NATIONSTD) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>National Standard (India) (NSE:NATIONSTD) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>National Standard files FY26 BRSR, reports 100% related-party sales - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>National Standard (India) sets Aug 28 date for 63rd AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>13</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>STYLEBAAZA.NS</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Baazar Style Retail Limited</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>437.8500061035156</v>
+      </c>
+      <c r="F334" t="n">
+        <v>447.1000061035156</v>
+      </c>
+      <c r="G334" t="n">
+        <v>417.6499938964844</v>
+      </c>
+      <c r="H334" t="n">
+        <v>417.6499938964844</v>
+      </c>
+      <c r="I334" t="n">
+        <v>439.6000061035156</v>
+      </c>
+      <c r="J334" t="n">
+        <v>417.6499938964844</v>
+      </c>
+      <c r="K334" t="n">
+        <v>2692014</v>
+      </c>
+      <c r="L334" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>Aditya Kumar Halwasiya acquires 6 per cent stake in Baazar Style Retail through Block Deal - ET Retail</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>Baazar Style Retail Share Price Today Hits 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-17 — cnbctv:75f67e8db094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>Baazar Style Retail Share Price Today Hits 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>Baazar Style Retail Ltd. Share Price: Near 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>14</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>ONIXSOLAR.NS</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Onix Solar Energy Limited</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>305.8999938964844</v>
+      </c>
+      <c r="F335" t="n">
+        <v>305.8999938964844</v>
+      </c>
+      <c r="G335" t="n">
+        <v>305.8999938964844</v>
+      </c>
+      <c r="H335" t="n">
+        <v>305.8999938964844</v>
+      </c>
+      <c r="I335" t="n">
+        <v>321.9500122070312</v>
+      </c>
+      <c r="J335" t="n">
+        <v>305.8999938964844</v>
+      </c>
+      <c r="K335" t="n">
+        <v>11633</v>
+      </c>
+      <c r="L335" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>Onix Solar Energy Limited: Shareholders Board Members Managers and Company Profile | INE173M01012 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>Onix Solar Energy Limited: Shareholders Board Members Managers and Company Profile | INE173M01012 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr"/>
+      <c r="P335" t="inlineStr"/>
+      <c r="Q335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>15</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>AMBALALSA.NS</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Ambalal Sarabhai Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="F336" t="n">
+        <v>48</v>
+      </c>
+      <c r="G336" t="n">
+        <v>45.36000061035156</v>
+      </c>
+      <c r="H336" t="n">
+        <v>45.36000061035156</v>
+      </c>
+      <c r="I336" t="n">
+        <v>47.7400016784668</v>
+      </c>
+      <c r="J336" t="n">
+        <v>45.36000061035156</v>
+      </c>
+      <c r="K336" t="n">
+        <v>86066</v>
+      </c>
+      <c r="L336" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>Issuance/retirement of stock (net) of Ambalal Sarabhai Enterprises Limited – NSE:AMBALALSA - TradingView</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>Issuance/retirement of stock (net) of Ambalal Sarabhai Enterprises Limited – NSE:AMBALALSA - TradingView</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>Ambalal Sarabhai Share Price Gains 10.31% in Today's Trading - Univest</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>Ambalal Sarabhai Enterprises Ltd. Stock: 11.62% Price Rise - Univest</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>Ambalal Sarabhai Enterprises shareholders approve director reappointments - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>16</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>SIEL.NS</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>38.29000091552734</v>
+      </c>
+      <c r="F337" t="n">
+        <v>40.29999923706055</v>
+      </c>
+      <c r="G337" t="n">
+        <v>38.29000091552734</v>
+      </c>
+      <c r="H337" t="n">
+        <v>38.29000091552734</v>
+      </c>
+      <c r="I337" t="n">
+        <v>40.29999923706055</v>
+      </c>
+      <c r="J337" t="n">
+        <v>38.29000091552734</v>
+      </c>
+      <c r="K337" t="n">
+        <v>7981</v>
+      </c>
+      <c r="L337" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>SIEL Share Price Today - Superior Industrial Enterprises Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises standalone profit rises 21.8% in Q1FY27 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>17</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN.NS</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Limited</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>747.3499755859375</v>
+      </c>
+      <c r="F338" t="n">
+        <v>765</v>
+      </c>
+      <c r="G338" t="n">
+        <v>714</v>
+      </c>
+      <c r="H338" t="n">
+        <v>729.3499755859375</v>
+      </c>
+      <c r="I338" t="n">
+        <v>767.0999755859375</v>
+      </c>
+      <c r="J338" t="n">
+        <v>729.3499755859375</v>
+      </c>
+      <c r="K338" t="n">
+        <v>19995747</v>
+      </c>
+      <c r="L338" t="n">
+        <v>-4.92</v>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>Balrampur Exceeds Analyst Target by 5% After India Reverses Sugar Import Policy - TechStock²</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd Share Price Target, Forecast for Long Term Equity. - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. Share Price Hits One-Year High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>18</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>PAKKA.NS</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>PAKKA LIMITED</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>88.65000152587891</v>
+      </c>
+      <c r="F339" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="G339" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="H339" t="n">
+        <v>84.51999664306641</v>
+      </c>
+      <c r="I339" t="n">
+        <v>88.69000244140625</v>
+      </c>
+      <c r="J339" t="n">
+        <v>84.51999664306641</v>
+      </c>
+      <c r="K339" t="n">
+        <v>190999</v>
+      </c>
+      <c r="L339" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: Pakka posts record Q1 2026 revenue, shares jump 8% - Investing.com India</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>Pakka Limited Confirms No Deviation in Preferential Issue Fund Use - TipRanks</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>Pakka Ltd. Share Price Decline: Technicals, Peers, Sector - Univest</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>SBI Mutual Fund sells 71,698 Pakka Ltd shares, stake falls to 6.45% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>Pakka Ltd. Share Price Rise: Paper Stock Price and Analysis - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>19</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>GANGAFORGE.NS</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Ganga Forging Limited</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>2.049999952316284</v>
+      </c>
+      <c r="F340" t="n">
+        <v>2.049999952316284</v>
+      </c>
+      <c r="G340" t="n">
+        <v>2.049999952316284</v>
+      </c>
+      <c r="H340" t="n">
+        <v>2.049999952316284</v>
+      </c>
+      <c r="I340" t="n">
+        <v>2.150000095367432</v>
+      </c>
+      <c r="J340" t="n">
+        <v>2.049999952316284</v>
+      </c>
+      <c r="K340" t="n">
+        <v>846239</v>
+      </c>
+      <c r="L340" t="n">
+        <v>-4.65</v>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>Ganga Forging submits Letter of Offer for ₹32.96 crore rights issue - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>Ganga Forging submits Letter of Offer for ₹32.96 crore rights issue - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr"/>
+      <c r="P340" t="inlineStr"/>
+      <c r="Q340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:02:59 IST</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>20</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>TAKE.NS</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>TAKE Limited</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>22.14999961853027</v>
+      </c>
+      <c r="F341" t="n">
+        <v>22.18000030517578</v>
+      </c>
+      <c r="G341" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="H341" t="n">
+        <v>20.82999992370605</v>
+      </c>
+      <c r="I341" t="n">
+        <v>21.84000015258789</v>
+      </c>
+      <c r="J341" t="n">
+        <v>20.82999992370605</v>
+      </c>
+      <c r="K341" t="n">
+        <v>515661</v>
+      </c>
+      <c r="L341" t="n">
+        <v>-4.62</v>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>Umpires Adrian Holdstock and Shaun George take stock of the ground at Durban - Cricinfo</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>Take-Two Shares Rebound by 50% From GTA 6 Leak Decline Before Preview Reveal - TechStock²</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>It Won’t Take Much to Burst the Stock Market Bubble - Advisor Perspectives</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>Buy or rent a house? Niranjan Hiranandani shares his take on India's housing market: 'Home will never become obsolete' - livemint.com</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>Govt to take stock of H1N1 as Karnataka cases cross 4,000 - The Times of India</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q341"/>
+  <dimension ref="A1:Q361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19821,8 +19821,6 @@
           <t>Quadrant Future Tek Publishes Q1 FY27 Unaudited Results and Notifies Stock Exchanges - TipRanks</t>
         </is>
       </c>
-      <c r="P323" t="inlineStr"/>
-      <c r="Q323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -20296,8 +20294,6 @@
           <t>Kilburn Engineering (NSE:KLBRENG-B) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
-      <c r="P330" t="inlineStr"/>
-      <c r="Q330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -20495,8 +20491,6 @@
           <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
         </is>
       </c>
-      <c r="P333" t="inlineStr"/>
-      <c r="Q333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -20551,9 +20545,6 @@
           <t>Lee &amp; Nee Softwares (Exports) (NSE:LEENEE) Cyclically Adjus - GuruFocus</t>
         </is>
       </c>
-      <c r="O334" t="inlineStr"/>
-      <c r="P334" t="inlineStr"/>
-      <c r="Q334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -20677,9 +20668,6 @@
           <t>CRSL Share Price Today - Cressanda Railway Solutions Stock Analysis - Equitypandit</t>
         </is>
       </c>
-      <c r="O336" t="inlineStr"/>
-      <c r="P336" t="inlineStr"/>
-      <c r="Q336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -20803,9 +20791,6 @@
           <t>Subex Ltd hosts non-deal analyst roadshow in Mumbai on August 19 - scanx.trade</t>
         </is>
       </c>
-      <c r="O338" t="inlineStr"/>
-      <c r="P338" t="inlineStr"/>
-      <c r="Q338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -20919,11 +20904,6 @@
       <c r="L340" t="n">
         <v>9.039999999999999</v>
       </c>
-      <c r="M340" t="inlineStr"/>
-      <c r="N340" t="inlineStr"/>
-      <c r="O340" t="inlineStr"/>
-      <c r="P340" t="inlineStr"/>
-      <c r="Q340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -20993,6 +20973,1326 @@
           <t>Fineos (ASX: FCL) Crosses Profitability Inflection Point In H1 FY 2026 - A Rich Life</t>
         </is>
       </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>1</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>RAMBHAJO.NS</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Advit Jewels Limited</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>180.8500061035156</v>
+      </c>
+      <c r="F342" t="n">
+        <v>212.8899993896484</v>
+      </c>
+      <c r="G342" t="n">
+        <v>180.8500061035156</v>
+      </c>
+      <c r="H342" t="n">
+        <v>212.8899993896484</v>
+      </c>
+      <c r="I342" t="n">
+        <v>177.4100036621094</v>
+      </c>
+      <c r="J342" t="n">
+        <v>212.8899993896484</v>
+      </c>
+      <c r="K342" t="n">
+        <v>2520932</v>
+      </c>
+      <c r="L342" t="n">
+        <v>20</v>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>Advit Jewels Ltd. Share Price Today - Advit Jewels Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>Advit Jewels Ltd. Share Price Today - Advit Jewels Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr"/>
+      <c r="P342" t="inlineStr"/>
+      <c r="Q342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>2</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>VIRAT.NS</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Virat Industries Limited</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>465</v>
+      </c>
+      <c r="F343" t="n">
+        <v>482</v>
+      </c>
+      <c r="G343" t="n">
+        <v>452.7999877929688</v>
+      </c>
+      <c r="H343" t="n">
+        <v>482</v>
+      </c>
+      <c r="I343" t="n">
+        <v>401.7000122070312</v>
+      </c>
+      <c r="J343" t="n">
+        <v>482</v>
+      </c>
+      <c r="K343" t="n">
+        <v>125540</v>
+      </c>
+      <c r="L343" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>Sanat Sangwan shares a partnership with Virat Kohli in the Ranji Trophy - Cricinfo</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>Sanat Sangwan shares a partnership with Virat Kohli in the Ranji Trophy - Cricinfo</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>Virat Industries Ltd. Share Price Up 17.36%: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>"He Is Like My Brother": PV Sindhu Shares How Virat Kohli Motivated Her During Tough Phase - Sportscape Magazine</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>Virat Industries Approves Acquisition Of 70.28% Shares In Brahm Lifestyle Products - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>3</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>MARATHON.NS</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Marathon Nextgen Realty Limited</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>364</v>
+      </c>
+      <c r="F344" t="n">
+        <v>422.7999877929688</v>
+      </c>
+      <c r="G344" t="n">
+        <v>361.6000061035156</v>
+      </c>
+      <c r="H344" t="n">
+        <v>422.7999877929688</v>
+      </c>
+      <c r="I344" t="n">
+        <v>352.3500061035156</v>
+      </c>
+      <c r="J344" t="n">
+        <v>422.7999877929688</v>
+      </c>
+      <c r="K344" t="n">
+        <v>3183615</v>
+      </c>
+      <c r="L344" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>Why is Marathon Digital stock surging today? By Investing.com - Investing.com India</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>Landscape Capital Management L.L.C. Purchases Shares of 5,091 Marathon Petroleum Corporation $MPC - MarketBeat</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>Marathon Nextgen Realty confirms no new encumbrance by promoters - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>Bank of Nova Scotia Acquires Shares of 113,403 Marathon Petroleum Corporation $MPC - MarketBeat</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>Marathon Petroleum SVP Log &amp; Storage, MPLX GP LLC Sold Shares Worth Over $875K - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>4</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>SUPTANERY.NS</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Super Tannery Limited</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>9.170000076293945</v>
+      </c>
+      <c r="F345" t="n">
+        <v>10.52000045776367</v>
+      </c>
+      <c r="G345" t="n">
+        <v>9.170000076293945</v>
+      </c>
+      <c r="H345" t="n">
+        <v>10.52000045776367</v>
+      </c>
+      <c r="I345" t="n">
+        <v>8.770000457763672</v>
+      </c>
+      <c r="J345" t="n">
+        <v>10.52000045776367</v>
+      </c>
+      <c r="K345" t="n">
+        <v>1630102</v>
+      </c>
+      <c r="L345" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>SUPTANERY Share Price Today - Super Tannery Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>Super Tannery (NSE:SUPTANERY) Cyclically Adjusted PB Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>Super Tannery (NSE:SUPTANERY) Cyclically Adjusted Price-to-FCF : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>SUPTANERY Historical Data - Equitypandit</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>Super Tannery (NSE:SUPTANERY) Cyclically Adjusted PB Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>5</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>SHAH.NS</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Shah Metacorp Limited</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>3.670000076293945</v>
+      </c>
+      <c r="F346" t="n">
+        <v>3.990000009536743</v>
+      </c>
+      <c r="G346" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H346" t="n">
+        <v>3.990000009536743</v>
+      </c>
+      <c r="I346" t="n">
+        <v>3.329999923706055</v>
+      </c>
+      <c r="J346" t="n">
+        <v>3.990000009536743</v>
+      </c>
+      <c r="K346" t="n">
+        <v>7806929</v>
+      </c>
+      <c r="L346" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>What Is Changing At Shah Rukh Khan's Rs 300-Crore Mannat? Anand Pandit Shares Renovation Details - NDTV</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>Hipolin promoter Rajasvee Sagar Shah sells 9.38% stake in open market - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>Hipolin promoter Rajasvee Sagar Shah sells 9.38% stake in open market - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>‘Adding a few floors’: Anand Pandit shares renovation details on Shah Rukh Khan’s Mannat - The Indian Express</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>Rocket Pharmaceuticals CEO Gaurav Shah sells $7,752 in shares - Investing.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>6</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>KOTARISUG.NS</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Kothari Sugars And Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>34.47999954223633</v>
+      </c>
+      <c r="F347" t="n">
+        <v>39.93999862670898</v>
+      </c>
+      <c r="G347" t="n">
+        <v>33.95999908447266</v>
+      </c>
+      <c r="H347" t="n">
+        <v>39.15999984741211</v>
+      </c>
+      <c r="I347" t="n">
+        <v>33.29000091552734</v>
+      </c>
+      <c r="J347" t="n">
+        <v>39.15999984741211</v>
+      </c>
+      <c r="K347" t="n">
+        <v>3630571</v>
+      </c>
+      <c r="L347" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>Kothari Sugars And Chemicals Share Price Today at Rs 36.35 - Univest</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>Sugar stocks extend gains: What’s driving the rally? - Business Today</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>Kothari Sugars and Chemicals gets NSE no objection for merger with Kothari Petrochemicals - ChiniMandi</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>Kothari Sugars And Chemicals Ltd. (KOTARISUG) Share Price Rises 13.52% Today - Univest</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>Kothari Sugars And Chemicals Ltd. Share Price Up 13.34% - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>7</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>NAHARINDUS.NS</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Nahar Industrial Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>127.3499984741211</v>
+      </c>
+      <c r="F348" t="n">
+        <v>150.7299957275391</v>
+      </c>
+      <c r="G348" t="n">
+        <v>125.8000030517578</v>
+      </c>
+      <c r="H348" t="n">
+        <v>147.6000061035156</v>
+      </c>
+      <c r="I348" t="n">
+        <v>125.6100006103516</v>
+      </c>
+      <c r="J348" t="n">
+        <v>147.6000061035156</v>
+      </c>
+      <c r="K348" t="n">
+        <v>570317</v>
+      </c>
+      <c r="L348" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>Nahar Industrial Enterprises Share Price after 10.58% gain - Univest</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>Nahar Industrial Enterprises Share Price after 10.58% gain - Univest</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>Nahar Industrial Enterprises Ltd. (NAHARINDUS) Share Price Rises 8.91% Today - Univest</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>Nahar Industrial Enterprises Limited acquired Emerald Logipark Private Limited for INR 0.10 million. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>Nahar Industrial Enterprises Acquires 100% Stake in Emerald Logipark for ₹1,00,000 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>8</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>RATNAMANI.NS</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Ratnamani Metals &amp; Tubes Limited</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>2354.39990234375</v>
+      </c>
+      <c r="F349" t="n">
+        <v>2777</v>
+      </c>
+      <c r="G349" t="n">
+        <v>2323</v>
+      </c>
+      <c r="H349" t="n">
+        <v>2697</v>
+      </c>
+      <c r="I349" t="n">
+        <v>2354.39990234375</v>
+      </c>
+      <c r="J349" t="n">
+        <v>2697</v>
+      </c>
+      <c r="K349" t="n">
+        <v>903479</v>
+      </c>
+      <c r="L349" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>Ratnamani Metals &amp; Tubes shares jump 18% on securing export orders worth ₹2,700 crore - Upstox</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>This mid-cap metal stock zooms 15% on Rs 2,700 crore order announcement; do you own? - Business Today</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>Ratnamani Subsidiary Wins ₹2,700 Crore Orders - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>Buzzing stocks: Ratnamani, Quadrant, Shanthi Gears zoom up to 42% in 2 days - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>Ratnamani Metals shareholders approve ₹10 dividend, reappoint directors - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>9</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>LEENEE.NS</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Lee &amp; Nee Softwares Exports Limited</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="F350" t="n">
+        <v>11.02000045776367</v>
+      </c>
+      <c r="G350" t="n">
+        <v>9.319999694824219</v>
+      </c>
+      <c r="H350" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I350" t="n">
+        <v>9.189999580383301</v>
+      </c>
+      <c r="J350" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K350" t="n">
+        <v>360638</v>
+      </c>
+      <c r="L350" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>Lee &amp; Nee Softwares (Exports) (NSE:LEENEE) Cyclically Adjus - GuruFocus</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>Lee &amp; Nee Softwares (Exports) (NSE:LEENEE) Cyclically Adjus - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr"/>
+      <c r="P350" t="inlineStr"/>
+      <c r="Q350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>10</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>BALUFORGE.NS</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Balu Forge Industries Limited</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>568</v>
+      </c>
+      <c r="F351" t="n">
+        <v>638</v>
+      </c>
+      <c r="G351" t="n">
+        <v>568</v>
+      </c>
+      <c r="H351" t="n">
+        <v>632.2000122070312</v>
+      </c>
+      <c r="I351" t="n">
+        <v>555.4000244140625</v>
+      </c>
+      <c r="J351" t="n">
+        <v>632.2000122070312</v>
+      </c>
+      <c r="K351" t="n">
+        <v>15539622</v>
+      </c>
+      <c r="L351" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>Solid Earnings May Not Tell The Whole Story For Balu Forge Industries (NSE:BALUFORGE) - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>Balu Forge Industries Declines 3.98%: Stock Approaches Key Support Level - Dark Pool Prints - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>Balu Forge Industries Share Price Rise 8.69% As Company Signs 5-Year MoU For Large Calibre Ammunition Supply - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>Balu Forge Industries Limited (NSE:BALUFORGE) Stock's 29% Dive Might Signal An Opportunity But It Requires Some Scrutiny - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>BALUFORGE Q2 2026 Earnings: Revenue Surges 20% YoY, EPS at ₹23.9 - Energy Earnings Report - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>11</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>NDL.NS</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Nandan Denim Limited</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>2.890000104904175</v>
+      </c>
+      <c r="F352" t="n">
+        <v>3.190000057220459</v>
+      </c>
+      <c r="G352" t="n">
+        <v>2.859999895095825</v>
+      </c>
+      <c r="H352" t="n">
+        <v>3.039999961853027</v>
+      </c>
+      <c r="I352" t="n">
+        <v>2.710000038146973</v>
+      </c>
+      <c r="J352" t="n">
+        <v>3.039999961853027</v>
+      </c>
+      <c r="K352" t="n">
+        <v>15635199</v>
+      </c>
+      <c r="L352" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>NCLT admits NDL Ventures-Hinduja Leyland merger petition - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>NCLT admits NDL Ventures-Hinduja Leyland merger petition - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>Next Digital probe halted - news.gov.hk</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>NDL Ventures Shareholders Approve Scheme of Merger by Absorption of Hinduja Leyland Finance Limited - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>NDL Ventures Q1 FY27 Results: Revenue, PAT &amp; Key Highlights - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>12</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>ATL.NS</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Allcargo Terminals Limited</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>25.3799991607666</v>
+      </c>
+      <c r="F353" t="n">
+        <v>28.18000030517578</v>
+      </c>
+      <c r="G353" t="n">
+        <v>24.55999946594238</v>
+      </c>
+      <c r="H353" t="n">
+        <v>27.59000015258789</v>
+      </c>
+      <c r="I353" t="n">
+        <v>24.86000061035156</v>
+      </c>
+      <c r="J353" t="n">
+        <v>27.59000015258789</v>
+      </c>
+      <c r="K353" t="n">
+        <v>1310266</v>
+      </c>
+      <c r="L353" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>Enterprise value to EBIT forward of Arab Tunisian Lease SA – BVMT:ATL - TradingView</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>Taking Stock - Adam Stewart On Sandals, Jamaica’s Tourism Industry &amp; ATL’s Caribbean Expansion Rocket Launch Today (fXoWngxf0m) - Mshale</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>Reimagining the passenger journey: ATL Airport on AI, human-centred experiences and the airport as a destination - Future Travel Experience</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>Taking Stock - Adam Stewart On Sandals, Jamaica’s Tourism Industry &amp; ATL’s Caribbean Expansion Rocket Launch Today (fXoWngxf0m) - Mshale</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>AtlantaSanad Revenue Breakdown – CSEMA:ATL - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>13</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>MAXESTATES.NS</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Max Estates Limited</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>495.3999938964844</v>
+      </c>
+      <c r="F354" t="n">
+        <v>559.7999877929688</v>
+      </c>
+      <c r="G354" t="n">
+        <v>495.3999938964844</v>
+      </c>
+      <c r="H354" t="n">
+        <v>549.1500244140625</v>
+      </c>
+      <c r="I354" t="n">
+        <v>494.8500061035156</v>
+      </c>
+      <c r="J354" t="n">
+        <v>549.1500244140625</v>
+      </c>
+      <c r="K354" t="n">
+        <v>1963922</v>
+      </c>
+      <c r="L354" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>Max Estates Ltd. (MAXESTATES) Share Price Hits Fresh 52-Week Low - Univest</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>You were invited to TradingView - TradingView</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>WEWORK Stock Price and Chart — NSE:WEWORK - TradingView</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>Max Estates Ltd. Share Price: Fresh 52-Week High Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>You were invited to TradingView - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>14</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>QUADFUTURE.NS</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Quadrant Future Tek Limited</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>410.0499877929688</v>
+      </c>
+      <c r="F355" t="n">
+        <v>464.7999877929688</v>
+      </c>
+      <c r="G355" t="n">
+        <v>395.5</v>
+      </c>
+      <c r="H355" t="n">
+        <v>447.2999877929688</v>
+      </c>
+      <c r="I355" t="n">
+        <v>405.3500061035156</v>
+      </c>
+      <c r="J355" t="n">
+        <v>447.2999877929688</v>
+      </c>
+      <c r="K355" t="n">
+        <v>23856274</v>
+      </c>
+      <c r="L355" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>Quadrant Future Tek Publishes Q1 FY27 Unaudited Results and Notifies Stock Exchanges - TipRanks</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr"/>
+      <c r="Q355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>15</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>S&amp;SPOWER.NS</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Switchgears Limited</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>328.7000122070312</v>
+      </c>
+      <c r="F356" t="n">
+        <v>328.7000122070312</v>
+      </c>
+      <c r="G356" t="n">
+        <v>328.7000122070312</v>
+      </c>
+      <c r="H356" t="n">
+        <v>328.7000122070312</v>
+      </c>
+      <c r="I356" t="n">
+        <v>298.8500061035156</v>
+      </c>
+      <c r="J356" t="n">
+        <v>328.7000122070312</v>
+      </c>
+      <c r="K356" t="n">
+        <v>4808</v>
+      </c>
+      <c r="L356" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Switchgear Ltd. Share Price Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Arm Wins Hitachi Energy Order, Contract Valued At Over ₹8-10 Crore - Free Press Journal</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Switchgear Ltd. Share Price: Price Fall Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Arm Wins Hitachi Energy Order, Contract Valued At Over ₹8-10 Crore - Free Press Journal</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>16</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>MINALIND.NS</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Minal Industries Limited</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>3.400000095367432</v>
+      </c>
+      <c r="F357" t="n">
+        <v>3.490000009536743</v>
+      </c>
+      <c r="G357" t="n">
+        <v>3.400000095367432</v>
+      </c>
+      <c r="H357" t="n">
+        <v>3.490000009536743</v>
+      </c>
+      <c r="I357" t="n">
+        <v>3.180000066757202</v>
+      </c>
+      <c r="J357" t="n">
+        <v>3.490000009536743</v>
+      </c>
+      <c r="K357" t="n">
+        <v>220880</v>
+      </c>
+      <c r="L357" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>MINALIND Share Price Today - Minal Industries Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>Minal Industries (NSE:MINALIND) Shiller PE Ratio : (As of Aug. 22, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>Free float of Minal Industries Limited – NSE:MINALIND - TradingView</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>Minal Industries Limited Announces Appointment of Saket Rajendra Sugandh as Company Secretary and Compliance Officer, Effective August 5, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>Minal Industries (NSE:MINALIND) Shiller PE Ratio : (As of Aug. 22, 2026) - GuruFocus</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>17</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>MOLBIO.NS</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Molbio Diagnostics Limited</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>1125</v>
+      </c>
+      <c r="F358" t="n">
+        <v>1219.949951171875</v>
+      </c>
+      <c r="G358" t="n">
+        <v>1125</v>
+      </c>
+      <c r="H358" t="n">
+        <v>1199.300048828125</v>
+      </c>
+      <c r="I358" t="n">
+        <v>1098.449951171875</v>
+      </c>
+      <c r="J358" t="n">
+        <v>1199.300048828125</v>
+      </c>
+      <c r="K358" t="n">
+        <v>4088665</v>
+      </c>
+      <c r="L358" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>MOLBIO DIAGNOSTICS LTD Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>Molbio Diagnostics Ltd. Share Price Today - Molbio Diagnostics Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>Share Price Today - Molbio Diagnostics Ltd. Stock Price Live NSE/BSE - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>Molbio Diagnostics Ltd. Share Price Today - Molbio Diagnostics Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>Molbio Diagnostics' shares jump over 21 pc in market debut trade - ET HealthWorld</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>18</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>PCJEWELLER.NS</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>PC Jeweller Limited</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>10.27999973297119</v>
+      </c>
+      <c r="F359" t="n">
+        <v>11.35000038146973</v>
+      </c>
+      <c r="G359" t="n">
+        <v>10.1899995803833</v>
+      </c>
+      <c r="H359" t="n">
+        <v>11.11999988555908</v>
+      </c>
+      <c r="I359" t="n">
+        <v>10.22000026702881</v>
+      </c>
+      <c r="J359" t="n">
+        <v>11.11999988555908</v>
+      </c>
+      <c r="K359" t="n">
+        <v>686804747</v>
+      </c>
+      <c r="L359" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>PC Jewellers Share Price - Live NSE: PCJEWELLER Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>PC Jewellers Share Price - Live NSE: PCJEWELLER Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>Penny Stock in Focus: Jewellery Stock Ends Higher After Key Business Update; Should Investors Watch? - Goodreturns</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr"/>
+      <c r="Q359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>19</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>SHIVAAGRO.NS</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Shiva Global Agro Industries Limited</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>41.9900016784668</v>
+      </c>
+      <c r="F360" t="n">
+        <v>44.40000152587891</v>
+      </c>
+      <c r="G360" t="n">
+        <v>38.65000152587891</v>
+      </c>
+      <c r="H360" t="n">
+        <v>42.7599983215332</v>
+      </c>
+      <c r="I360" t="n">
+        <v>39.40000152587891</v>
+      </c>
+      <c r="J360" t="n">
+        <v>42.7599983215332</v>
+      </c>
+      <c r="K360" t="n">
+        <v>18088</v>
+      </c>
+      <c r="L360" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>SHIVAAGRO Share Price Today - Shiva Global Agro Industries Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>Shiva Global Agro Industries Ltd - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>Shiva Global Agro Industries Limited Statistics – NSE:SHIVAAGRO - TradingView</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>Shiva Global Agro Industries Ltd - Equitypandit</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>20</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>CLSEL.NS</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Chaman Lal Setia Exports Limited</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>288.8999938964844</v>
+      </c>
+      <c r="F361" t="n">
+        <v>321</v>
+      </c>
+      <c r="G361" t="n">
+        <v>288.8999938964844</v>
+      </c>
+      <c r="H361" t="n">
+        <v>312.75</v>
+      </c>
+      <c r="I361" t="n">
+        <v>288.3500061035156</v>
+      </c>
+      <c r="J361" t="n">
+        <v>312.75</v>
+      </c>
+      <c r="K361" t="n">
+        <v>2814060</v>
+      </c>
+      <c r="L361" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>CLSEL Share Price Rise: Market Cap, EPS and ROE Snapshot - Univest</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>CLSEL Share Price Rise: Market Cap, EPS and ROE Snapshot - Univest</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr"/>
+      <c r="P361" t="inlineStr"/>
+      <c r="Q361" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21005,7 +22305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q341"/>
+  <dimension ref="A1:Q361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40209,9 +41509,6 @@
           <t>Kino Polska TV Spolka Akcyjna (WSE:KPL) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
         </is>
       </c>
-      <c r="O325" t="inlineStr"/>
-      <c r="P325" t="inlineStr"/>
-      <c r="Q325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -40276,7 +41573,6 @@
           <t>HSCL Share Price | Himadri Speciality Chemical Ltd Stock Analysis &amp; Recommendation - marketsmojo.com</t>
         </is>
       </c>
-      <c r="Q326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -40405,8 +41701,6 @@
           <t>Siyaram Silk Mills sets Aug 22 record date for bonus preference shares - scanx.trade</t>
         </is>
       </c>
-      <c r="P328" t="inlineStr"/>
-      <c r="Q328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -40540,7 +41834,6 @@
           <t>RTS Power (NSE:RTSPOWR) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
-      <c r="Q330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -40605,7 +41898,6 @@
           <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
         </is>
       </c>
-      <c r="Q331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -40660,9 +41952,6 @@
           <t>Happy Forgings Limited Just Beat EPS By 10.0%: Here's What Analysts Think Will Happen Next - simplywall.st</t>
         </is>
       </c>
-      <c r="O332" t="inlineStr"/>
-      <c r="P332" t="inlineStr"/>
-      <c r="Q332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -40727,7 +42016,6 @@
           <t>National Standard (India) sets Aug 28 date for 63rd AGM - scanx.trade</t>
         </is>
       </c>
-      <c r="Q333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -40851,9 +42139,6 @@
           <t>Onix Solar Energy Limited: Shareholders Board Members Managers and Company Profile | INE173M01012 - marketscreener.com</t>
         </is>
       </c>
-      <c r="O335" t="inlineStr"/>
-      <c r="P335" t="inlineStr"/>
-      <c r="Q335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -40987,7 +42272,6 @@
           <t>Superior Industrial Enterprises standalone profit rises 21.8% in Q1FY27 - scanx.trade</t>
         </is>
       </c>
-      <c r="Q337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -41180,9 +42464,6 @@
           <t>Ganga Forging submits Letter of Offer for ₹32.96 crore rights issue - scanx.trade</t>
         </is>
       </c>
-      <c r="O340" t="inlineStr"/>
-      <c r="P340" t="inlineStr"/>
-      <c r="Q340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -41252,6 +42533,1322 @@
           <t>Govt to take stock of H1N1 as Karnataka cases cross 4,000 - The Times of India</t>
         </is>
       </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>1</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>BLS.NS</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>BLS International Services Limited</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>272</v>
+      </c>
+      <c r="F342" t="n">
+        <v>280.1400146484375</v>
+      </c>
+      <c r="G342" t="n">
+        <v>233.4700012207031</v>
+      </c>
+      <c r="H342" t="n">
+        <v>241.5099945068359</v>
+      </c>
+      <c r="I342" t="n">
+        <v>271.2900085449219</v>
+      </c>
+      <c r="J342" t="n">
+        <v>241.5099945068359</v>
+      </c>
+      <c r="K342" t="n">
+        <v>29676902</v>
+      </c>
+      <c r="L342" t="n">
+        <v>-10.98</v>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>BLS International Share Price Slumps 12% Even As Company Rejects Role In Allegations Of Visa Irregularities - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>BLS International shares fall up to 14% after reports of visa fraud; company rejects claims - TradingView</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>BLS International shares slump nearly 13% after reports of visa fraud; company rejects claims - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>Visa fraud case: Why BLS International shares tanked 13% today; clarification issued - Business Today</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>BLS International Shares Plunge 13% On Spanish Visa Probe Report - outlookbusiness.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>2</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>KJMCFIN.NS</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>82</v>
+      </c>
+      <c r="F343" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="G343" t="n">
+        <v>71.73000335693359</v>
+      </c>
+      <c r="H343" t="n">
+        <v>71.73000335693359</v>
+      </c>
+      <c r="I343" t="n">
+        <v>79.69999694824219</v>
+      </c>
+      <c r="J343" t="n">
+        <v>71.73000335693359</v>
+      </c>
+      <c r="K343" t="n">
+        <v>19958</v>
+      </c>
+      <c r="L343" t="n">
+        <v>-10</v>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services (NSE:KJMCFIN) Cyclically Adjusted P - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services (NSE:KJMCFIN) Cyclically Adjusted P - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services net profit rises to ₹162.85 lakh in Q1FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services (NSE:KJMCFIN) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>3</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>CRSL.NS</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>3.509999990463257</v>
+      </c>
+      <c r="F344" t="n">
+        <v>3.559999942779541</v>
+      </c>
+      <c r="G344" t="n">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="H344" t="n">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="I344" t="n">
+        <v>3.390000104904175</v>
+      </c>
+      <c r="J344" t="n">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="K344" t="n">
+        <v>2362969</v>
+      </c>
+      <c r="L344" t="n">
+        <v>-9.73</v>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions (CRSL) Share Price Falls 9.73% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions (CRSL) Share Price Falls 9.73% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Ltd Statistics – NSE:CRSL - TradingView</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>4</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>POLYSPIN.NS</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Polyspin Exports Limited</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>30.96999931335449</v>
+      </c>
+      <c r="F345" t="n">
+        <v>30.96999931335449</v>
+      </c>
+      <c r="G345" t="n">
+        <v>28.11000061035156</v>
+      </c>
+      <c r="H345" t="n">
+        <v>28.29999923706055</v>
+      </c>
+      <c r="I345" t="n">
+        <v>30.96999931335449</v>
+      </c>
+      <c r="J345" t="n">
+        <v>28.29999923706055</v>
+      </c>
+      <c r="K345" t="n">
+        <v>3255</v>
+      </c>
+      <c r="L345" t="n">
+        <v>-8.619999999999999</v>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>Diluted shares outstanding of Polyspin Exports Limited – NSE:POLYSPIN - TradingView</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>Polyspin Exports appoints Durga Ramji as MD at 41st AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>Polyspin Exports appoints Durga Ramji as MD at 41st AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>Polyspin Exports consolidated net profit rises 7.14% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>Shubham Polyspin Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>5</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>ORCHASP.NS</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Orchasp Limited</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>1.440000057220459</v>
+      </c>
+      <c r="F346" t="n">
+        <v>1.440000057220459</v>
+      </c>
+      <c r="G346" t="n">
+        <v>1.259999990463257</v>
+      </c>
+      <c r="H346" t="n">
+        <v>1.289999961853027</v>
+      </c>
+      <c r="I346" t="n">
+        <v>1.409999966621399</v>
+      </c>
+      <c r="J346" t="n">
+        <v>1.289999961853027</v>
+      </c>
+      <c r="K346" t="n">
+        <v>799128</v>
+      </c>
+      <c r="L346" t="n">
+        <v>-8.51</v>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>ORCHASP Consolidated June 2026 Net Sales at Rs 2.08 crore, down 73.12% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>ORCHASP Consolidated June 2026 Net Sales at Rs 2.08 crore, down 73.12% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr"/>
+      <c r="P346" t="inlineStr"/>
+      <c r="Q346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>6</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>NKIND.NS</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>NK Industries Limited</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>67.58999633789062</v>
+      </c>
+      <c r="F347" t="n">
+        <v>67.58999633789062</v>
+      </c>
+      <c r="G347" t="n">
+        <v>62</v>
+      </c>
+      <c r="H347" t="n">
+        <v>62.0099983215332</v>
+      </c>
+      <c r="I347" t="n">
+        <v>67.62000274658203</v>
+      </c>
+      <c r="J347" t="n">
+        <v>62.0099983215332</v>
+      </c>
+      <c r="K347" t="n">
+        <v>33161</v>
+      </c>
+      <c r="L347" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>NK Industries (NKIND.NS) Hovers Near ₹59 Amid Narrow Range, Support at ₹56.16 in Focus - Monthly Profile - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>Record Heat Drives UK Online Retail Sales to Five-Year High in June - Book Value Growth - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>NK Industries Limited Q2 2026 Earnings: Revenue Declines Sharply on Weak Operational Environment; EPS Turns Negative - Performance Review - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>NK Industries Limited (NKIND.NS): Marginal Gain Amid Consolidation Near Key Resistance - Dark Pool Prints - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>NK Industries Limited Slips 2.49% as Stock Tests Key Support at ₹62.89 - BPI Bear Correction - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>7</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>MYSORPETRO.NS</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>165</v>
+      </c>
+      <c r="F348" t="n">
+        <v>165</v>
+      </c>
+      <c r="G348" t="n">
+        <v>150.6000061035156</v>
+      </c>
+      <c r="H348" t="n">
+        <v>153.5299987792969</v>
+      </c>
+      <c r="I348" t="n">
+        <v>166.1100006103516</v>
+      </c>
+      <c r="J348" t="n">
+        <v>153.5299987792969</v>
+      </c>
+      <c r="K348" t="n">
+        <v>49408</v>
+      </c>
+      <c r="L348" t="n">
+        <v>-7.57</v>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals (NSE:MYSORPETRO) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals shareholders approve FY26 financials, dividend, director reappointment - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals (NSE:MYSORPETRO) Cyclically Adjusted PB Ratio : (As of Aug. 20, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals shareholders approve FY26 financials, dividend, director reappointment - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>8</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>RVHL.NS</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Ravinder Heights Limited</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>43.02000045776367</v>
+      </c>
+      <c r="F349" t="n">
+        <v>43.79999923706055</v>
+      </c>
+      <c r="G349" t="n">
+        <v>39</v>
+      </c>
+      <c r="H349" t="n">
+        <v>39.91999816894531</v>
+      </c>
+      <c r="I349" t="n">
+        <v>43.02000045776367</v>
+      </c>
+      <c r="J349" t="n">
+        <v>39.91999816894531</v>
+      </c>
+      <c r="K349" t="n">
+        <v>40751</v>
+      </c>
+      <c r="L349" t="n">
+        <v>-7.21</v>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>Ravinder Heights Q1 Results: Q1FY27 Financials Filed With Exchanges - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>Ravinder Heights Q1 Results: Q1FY27 Financials Filed With Exchanges - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr"/>
+      <c r="P349" t="inlineStr"/>
+      <c r="Q349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>9</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>COMPUSOFT.NS</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Compucom Software Limited</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>13.97999954223633</v>
+      </c>
+      <c r="F350" t="n">
+        <v>14.10000038146973</v>
+      </c>
+      <c r="G350" t="n">
+        <v>12.3100004196167</v>
+      </c>
+      <c r="H350" t="n">
+        <v>13.03999996185303</v>
+      </c>
+      <c r="I350" t="n">
+        <v>13.97999954223633</v>
+      </c>
+      <c r="J350" t="n">
+        <v>13.03999996185303</v>
+      </c>
+      <c r="K350" t="n">
+        <v>101907</v>
+      </c>
+      <c r="L350" t="n">
+        <v>-6.72</v>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>Compucom Software publishes 32nd AGM notice for Sept 9 meeting - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>Compucom Software publishes 32nd AGM notice for Sept 9 meeting - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>ROXHITECH Stock Price and Chart — NSE:ROXHITECH - TradingView</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>Compucom Software Q1 Results: Unaudited financials approved by Board - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>Compucom Software publishes 32nd AGM newspaper notice for September 9 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>10</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>AHLUCONT.NS</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Ahluwalia Contracts (India) Limited</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>688</v>
+      </c>
+      <c r="F351" t="n">
+        <v>690</v>
+      </c>
+      <c r="G351" t="n">
+        <v>645.2999877929688</v>
+      </c>
+      <c r="H351" t="n">
+        <v>649.5999755859375</v>
+      </c>
+      <c r="I351" t="n">
+        <v>696.2000122070312</v>
+      </c>
+      <c r="J351" t="n">
+        <v>649.5999755859375</v>
+      </c>
+      <c r="K351" t="n">
+        <v>316763</v>
+      </c>
+      <c r="L351" t="n">
+        <v>-6.69</v>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>Ahluwalia Contracts trades higher after winning orders worth ₹1,307 crore - Upstox</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>Stocks to Buy: 5 Stocks That Can Deliver Returns of Up to 54%; Do You Own Any? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>Stocks to Buy: 5 Stocks That Can Deliver Returns of Up to 54%; Do You Own Any? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr"/>
+      <c r="Q351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>11</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>CRAVATEX.NS</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Cravatex Limited</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>359</v>
+      </c>
+      <c r="F352" t="n">
+        <v>359</v>
+      </c>
+      <c r="G352" t="n">
+        <v>335</v>
+      </c>
+      <c r="H352" t="n">
+        <v>337.1000061035156</v>
+      </c>
+      <c r="I352" t="n">
+        <v>359</v>
+      </c>
+      <c r="J352" t="n">
+        <v>337.1000061035156</v>
+      </c>
+      <c r="K352" t="n">
+        <v>131</v>
+      </c>
+      <c r="L352" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>CRAVATEX Share Price Today - Cravatex Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>Cravatex (NSE:CRAVATEX) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>Cravatex (NSE:CRAVATEX) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>Cravatex Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>Cravatex Q1FY27 consolidated profit turns positive, revenue up 39% - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>12</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>BRAHMINFRA.NS</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Brahmaputra Infrastructure Limited</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>160</v>
+      </c>
+      <c r="F353" t="n">
+        <v>167.3800048828125</v>
+      </c>
+      <c r="G353" t="n">
+        <v>151.1999969482422</v>
+      </c>
+      <c r="H353" t="n">
+        <v>154.2400054931641</v>
+      </c>
+      <c r="I353" t="n">
+        <v>164.1499938964844</v>
+      </c>
+      <c r="J353" t="n">
+        <v>154.2400054931641</v>
+      </c>
+      <c r="K353" t="n">
+        <v>78920</v>
+      </c>
+      <c r="L353" t="n">
+        <v>-6.04</v>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>Average basic shares outstanding of Brahmaputra Infrastructure Ltd. – NSE:BRAHMINFRA - TradingView</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>Brahmaputra Infrastructure Signs ₹70.18 Cr NH-502A Maintenance Contract in Mizoram - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>Brahmaputra Infrastructure (NSE:BRAHMINFRA) Cyclically Adju - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>Brahmaputra Infrastructure Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>Brahmaputra Infra Secures ₹71 Crore Contract with Market Capitalization at ₹470 Crore - Sahi</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>13</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>SVGLOBAL.NS</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>S V Global Mill Limited</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>125</v>
+      </c>
+      <c r="F354" t="n">
+        <v>125</v>
+      </c>
+      <c r="G354" t="n">
+        <v>115.0100021362305</v>
+      </c>
+      <c r="H354" t="n">
+        <v>118</v>
+      </c>
+      <c r="I354" t="n">
+        <v>125.2600021362305</v>
+      </c>
+      <c r="J354" t="n">
+        <v>118</v>
+      </c>
+      <c r="K354" t="n">
+        <v>345</v>
+      </c>
+      <c r="L354" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>SV Global Mill Ltd. Share Price Up 10.44%: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>SV Global Mill board to consider physical share cancellation scheme - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>S V Global Mill (NSE:SVGLOBAL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>SV Global Mill board to consider physical share cancellation scheme - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>S V Global Mill Limited Announces Resignation of B. Parameswar as Key Managerial Personnel, Effective August 3, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>14</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>MPSLTD.NS</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>MPS Limited</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>2870</v>
+      </c>
+      <c r="F355" t="n">
+        <v>2903.89990234375</v>
+      </c>
+      <c r="G355" t="n">
+        <v>2705.89990234375</v>
+      </c>
+      <c r="H355" t="n">
+        <v>2734.800048828125</v>
+      </c>
+      <c r="I355" t="n">
+        <v>2897.89990234375</v>
+      </c>
+      <c r="J355" t="n">
+        <v>2734.800048828125</v>
+      </c>
+      <c r="K355" t="n">
+        <v>42608</v>
+      </c>
+      <c r="L355" t="n">
+        <v>-5.63</v>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>MPS Limited Amends Share Subscription and Shareholders' Agreement with MPSi and Rodney Charles Beach - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>MPS Ltd shareholders approve ADI BPO amalgamation with 99.99% support - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>Taurian MPS Limited Share Price Rises 8.16% Today - Univest</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>MPS issues addendum on ADI BPO merger, confirms no public dilution - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>MPS Ltd Q1FY27 net profit rises 43% to ₹50.39 cr on margin expansion - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>15</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>DCMFINSERV.NS</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>DCM Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>5.429999828338623</v>
+      </c>
+      <c r="F356" t="n">
+        <v>5.429999828338623</v>
+      </c>
+      <c r="G356" t="n">
+        <v>5.099999904632568</v>
+      </c>
+      <c r="H356" t="n">
+        <v>5.130000114440918</v>
+      </c>
+      <c r="I356" t="n">
+        <v>5.429999828338623</v>
+      </c>
+      <c r="J356" t="n">
+        <v>5.130000114440918</v>
+      </c>
+      <c r="K356" t="n">
+        <v>26143</v>
+      </c>
+      <c r="L356" t="n">
+        <v>-5.52</v>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>DCM Financial Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>Inspire (INSP) Reported Quarter: The Bottom-Line Figure Outpaces Its Comparison at the Close; Post-Earnings Trading: The Stock Ends Up 0.09% for the Current Session - CFO Commentary Report - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>Dcm Financial Services Limited Announces Resignation of Richa Kathuria as Independent Director, Member of the Audit Committee, Nomination and Remuneration Committee and Stakeholders Relationship Committee, Effective August 11, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>Inspire (INSP) Reported Quarter: The Bottom-Line Figure Outpaces Its Comparison at the Close; Post-Earnings Trading: The Stock Ends Up 0.09% for the Current Session - CFO Commentary Report - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>Lagarde Leaves Door Open to Early ECB Exit Amid French Political Speculation - High Estimate Range - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>16</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>REGENCERAM.NS</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Regency Ceramics Limited</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>36</v>
+      </c>
+      <c r="F357" t="n">
+        <v>36.09999847412109</v>
+      </c>
+      <c r="G357" t="n">
+        <v>33.5099983215332</v>
+      </c>
+      <c r="H357" t="n">
+        <v>33.93000030517578</v>
+      </c>
+      <c r="I357" t="n">
+        <v>35.90999984741211</v>
+      </c>
+      <c r="J357" t="n">
+        <v>33.93000030517578</v>
+      </c>
+      <c r="K357" t="n">
+        <v>6418</v>
+      </c>
+      <c r="L357" t="n">
+        <v>-5.51</v>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>Regency Ceramics Ltd. Share Price Fall and Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>Regency Ceramics Ltd. Share Price Fall and Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>Regency Ceramics Q1 Results: Revenue up 173% YoY, net loss narrows - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>Regency Ceramics Publishes June-Quarter Unaudited Results in Leading Dailies - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>17</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>INTENTECH.NS</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Intense Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>83.19999694824219</v>
+      </c>
+      <c r="F358" t="n">
+        <v>87</v>
+      </c>
+      <c r="G358" t="n">
+        <v>79</v>
+      </c>
+      <c r="H358" t="n">
+        <v>80.23999786376953</v>
+      </c>
+      <c r="I358" t="n">
+        <v>84.87999725341797</v>
+      </c>
+      <c r="J358" t="n">
+        <v>80.23999786376953</v>
+      </c>
+      <c r="K358" t="n">
+        <v>63360</v>
+      </c>
+      <c r="L358" t="n">
+        <v>-5.47</v>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>Intense Technologies Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>Intense Technologies Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr"/>
+      <c r="P358" t="inlineStr"/>
+      <c r="Q358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>18</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>AEGISLOG.NS</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Aegis Logistics Limited</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>1424.400024414062</v>
+      </c>
+      <c r="F359" t="n">
+        <v>1438.099975585938</v>
+      </c>
+      <c r="G359" t="n">
+        <v>1337</v>
+      </c>
+      <c r="H359" t="n">
+        <v>1341.5</v>
+      </c>
+      <c r="I359" t="n">
+        <v>1417.900024414062</v>
+      </c>
+      <c r="J359" t="n">
+        <v>1341.5</v>
+      </c>
+      <c r="K359" t="n">
+        <v>928535</v>
+      </c>
+      <c r="L359" t="n">
+        <v>-5.39</v>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>Aegis Logistics Ltd. Share Price Today in Top Decliners - Univest</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>Aegis Logistics Ltd. (AEGISLOG) Share Price Rises 3.1% in Today’s Move - Univest</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>Aegis Logistics Ltd. Share Price Shows Strong Price Action - Univest</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>Aegis Logistics Ltd. (AEGISLOG) Share Price Rises 3.1% in Today’s Move - Univest</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>Aegis Logistics Share Price Update: Market Cap and Fall - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>19</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>STYLEBAAZA.NS</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Baazar Style Retail Limited</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>406.2000122070312</v>
+      </c>
+      <c r="F360" t="n">
+        <v>425.0499877929688</v>
+      </c>
+      <c r="G360" t="n">
+        <v>396.7999877929688</v>
+      </c>
+      <c r="H360" t="n">
+        <v>396.7999877929688</v>
+      </c>
+      <c r="I360" t="n">
+        <v>417.6499938964844</v>
+      </c>
+      <c r="J360" t="n">
+        <v>396.7999877929688</v>
+      </c>
+      <c r="K360" t="n">
+        <v>1673190</v>
+      </c>
+      <c r="L360" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>Aditya Kumar Halwasiya acquires 6 per cent stake in Baazar Style Retail through Block Deal - ET Retail</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>Baazar Style Retail Share Price Today Hits 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>Baazar Style Retail Share Price Today Hits 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-17 — cnbctv:75f67e8db094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>Baazar Style Retail Ltd. Share Price: Near 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:33:12 IST</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>20</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>ONIXSOLAR.NS</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Onix Solar Energy Limited</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>290.6499938964844</v>
+      </c>
+      <c r="F361" t="n">
+        <v>290.6499938964844</v>
+      </c>
+      <c r="G361" t="n">
+        <v>290.6499938964844</v>
+      </c>
+      <c r="H361" t="n">
+        <v>290.6499938964844</v>
+      </c>
+      <c r="I361" t="n">
+        <v>305.8999938964844</v>
+      </c>
+      <c r="J361" t="n">
+        <v>290.6499938964844</v>
+      </c>
+      <c r="K361" t="n">
+        <v>13015</v>
+      </c>
+      <c r="L361" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>Onix Solar Energy Limited: Shareholders Board Members Managers and Company Profile | INE173M01012 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>Onix Solar Energy Limited: Shareholders Board Members Managers and Company Profile | INE173M01012 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr"/>
+      <c r="P361" t="inlineStr"/>
+      <c r="Q361" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q361"/>
+  <dimension ref="A1:Q381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21027,9 +21027,6 @@
           <t>Advit Jewels Ltd. Share Price Today - Advit Jewels Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
         </is>
       </c>
-      <c r="O342" t="inlineStr"/>
-      <c r="P342" t="inlineStr"/>
-      <c r="Q342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -21567,9 +21564,6 @@
           <t>Lee &amp; Nee Softwares (Exports) (NSE:LEENEE) Cyclically Adjus - GuruFocus</t>
         </is>
       </c>
-      <c r="O350" t="inlineStr"/>
-      <c r="P350" t="inlineStr"/>
-      <c r="Q350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -21905,8 +21899,6 @@
           <t>Quadrant Future Tek Publishes Q1 FY27 Unaudited Results and Notifies Stock Exchanges - TipRanks</t>
         </is>
       </c>
-      <c r="P355" t="inlineStr"/>
-      <c r="Q355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -21971,7 +21963,6 @@
           <t>S&amp;S Power Arm Wins Hitachi Energy Order, Contract Valued At Over ₹8-10 Crore - Free Press Journal</t>
         </is>
       </c>
-      <c r="Q356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -22169,8 +22160,6 @@
           <t>Penny Stock in Focus: Jewellery Stock Ends Higher After Key Business Update; Should Investors Watch? - Goodreturns</t>
         </is>
       </c>
-      <c r="P359" t="inlineStr"/>
-      <c r="Q359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -22235,7 +22224,6 @@
           <t>Shiva Global Agro Industries Ltd - Equitypandit</t>
         </is>
       </c>
-      <c r="Q360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -22290,9 +22278,1338 @@
           <t>CLSEL Share Price Rise: Market Cap, EPS and ROE Snapshot - Univest</t>
         </is>
       </c>
-      <c r="O361" t="inlineStr"/>
-      <c r="P361" t="inlineStr"/>
-      <c r="Q361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>1</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>GENESYS.NS</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Genesys International Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>181.3000030517578</v>
+      </c>
+      <c r="F362" t="n">
+        <v>214.25</v>
+      </c>
+      <c r="G362" t="n">
+        <v>181.3000030517578</v>
+      </c>
+      <c r="H362" t="n">
+        <v>214.25</v>
+      </c>
+      <c r="I362" t="n">
+        <v>178.5500030517578</v>
+      </c>
+      <c r="J362" t="n">
+        <v>214.25</v>
+      </c>
+      <c r="K362" t="n">
+        <v>4165927</v>
+      </c>
+      <c r="L362" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>Genesys International Corp fixes rights issue price at ₹50 for 2.5Cr shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>Genesys International shares jump twenty percent | Tap to know more | Inshorts - Inshorts</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>Genesys International shares jump twenty percent | Tap to know more | Inshorts - Inshorts</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>Taxes of Genesys International Corporation Limited Rights 2026-21.08.26 For Shares – BSE:GENESYS_RE - TradingView</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>Genesys International Corporation Ltd. Share Price Live Today - CNBC TV18</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>2</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>DUCON.NS</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Ducon Infratechnologies Limited</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>2.259999990463257</v>
+      </c>
+      <c r="F363" t="n">
+        <v>2.539999961853027</v>
+      </c>
+      <c r="G363" t="n">
+        <v>2.210000038146973</v>
+      </c>
+      <c r="H363" t="n">
+        <v>2.430000066757202</v>
+      </c>
+      <c r="I363" t="n">
+        <v>2.175652027130127</v>
+      </c>
+      <c r="J363" t="n">
+        <v>2.430000066757202</v>
+      </c>
+      <c r="K363" t="n">
+        <v>2870903</v>
+      </c>
+      <c r="L363" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>Ducon Infratechnologies wins contract with India's largest aluminium smelter - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>Ducon Infratechnologies wins contract with India's largest aluminium smelter - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>Ducon Infratechnologies Wins Contract With India's Largest Aluminium Smelter - Sahi</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>Ducon Infratechnologies Share Price and Valuation Check - Univest</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>Ducon Infratechnologies approves rights issue of up to ₹25 Crore - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>3</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>QUINT.NS</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Quint Digital Limited</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>42.79000091552734</v>
+      </c>
+      <c r="F364" t="n">
+        <v>46</v>
+      </c>
+      <c r="G364" t="n">
+        <v>39.97000122070312</v>
+      </c>
+      <c r="H364" t="n">
+        <v>44.97999954223633</v>
+      </c>
+      <c r="I364" t="n">
+        <v>40.5099983215332</v>
+      </c>
+      <c r="J364" t="n">
+        <v>44.97999954223633</v>
+      </c>
+      <c r="K364" t="n">
+        <v>22466</v>
+      </c>
+      <c r="L364" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>Quint Digital Ltd. Share Price Up 10.53%: Full Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>Quint Digital submits Letter of Offer for ₹908.8 lakh rights issue - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>Quint Digital Ltd. Share Price Update With Valuation Check - Univest</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>BJP Shares Misleading Claim About Rahul Gandhi 'Insulting' the National Anthem - The Quint</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>Quint Digital submits Letter of Offer for ₹908.8 lakh rights issue - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>4</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>APOLLOPIPE.NS</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Apollo Pipes Limited</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>609.25</v>
+      </c>
+      <c r="F365" t="n">
+        <v>665</v>
+      </c>
+      <c r="G365" t="n">
+        <v>605.0999755859375</v>
+      </c>
+      <c r="H365" t="n">
+        <v>659.8499755859375</v>
+      </c>
+      <c r="I365" t="n">
+        <v>609.25</v>
+      </c>
+      <c r="J365" t="n">
+        <v>659.8499755859375</v>
+      </c>
+      <c r="K365" t="n">
+        <v>1323174</v>
+      </c>
+      <c r="L365" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>Apollo Pipes appoints Sanjay Gupta as Chairman after AGM approval - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>Apollo Pipes Share Price at fresh 52-week high | APOLLOPIPE - Univest</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>Apollo Pipes Share Price at fresh 52-week high | APOLLOPIPE - Univest</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>Apollo Pipes Ltd. (APOLLOPIPE) Share Price Within 2% of 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>Apollo Pipes Ltd. Share Price Update on Fresh Yearly High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>5</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>IDEA.NS</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Vodafone Idea Limited</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>14.09000015258789</v>
+      </c>
+      <c r="F366" t="n">
+        <v>15.18000030517578</v>
+      </c>
+      <c r="G366" t="n">
+        <v>14.07999992370605</v>
+      </c>
+      <c r="H366" t="n">
+        <v>15.09000015258789</v>
+      </c>
+      <c r="I366" t="n">
+        <v>14.06999969482422</v>
+      </c>
+      <c r="J366" t="n">
+        <v>15.09000015258789</v>
+      </c>
+      <c r="K366" t="n">
+        <v>995891586</v>
+      </c>
+      <c r="L366" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>SBI approves loan share for Vodafone Idea's ₹45,000 crore funding - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>SBI approves loan share for Vodafone Idea's ₹45,000 crore funding - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>Vodafone Idea shares rise 2.04% to Rs 13.99 on Tuesday - TradingView</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>Vodafone Idea shares rise nearly 11% in 3 sessions on buzz of tariff hike; should you buy, sell or hold? - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>Vodafone Idea shares reverse early gains, Q1 loss narrows - BusinessLine</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>6</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>TARMAT.NS</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Tarmat Limited</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>50.02999877929688</v>
+      </c>
+      <c r="F367" t="n">
+        <v>54.93999862670898</v>
+      </c>
+      <c r="G367" t="n">
+        <v>49.59999847412109</v>
+      </c>
+      <c r="H367" t="n">
+        <v>53.65999984741211</v>
+      </c>
+      <c r="I367" t="n">
+        <v>50.13999938964844</v>
+      </c>
+      <c r="J367" t="n">
+        <v>53.65999984741211</v>
+      </c>
+      <c r="K367" t="n">
+        <v>41829</v>
+      </c>
+      <c r="L367" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>Tarmat Limited schedules 41st AGM for September 30, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>Tarmat Limited schedules 41st AGM for September 30, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>Tarmat Ltd. Share Price News: Price Action, Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>Tarmat Ltd. Share Price Drop: Price Action and Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>Tarmat Ltd announces demise of promoter group member holding 4.19% stake - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>7</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>MANAKALUCO.NS</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Manaksia Aluminium Company Limited</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>36.79999923706055</v>
+      </c>
+      <c r="F368" t="n">
+        <v>41.68000030517578</v>
+      </c>
+      <c r="G368" t="n">
+        <v>36.79999923706055</v>
+      </c>
+      <c r="H368" t="n">
+        <v>39.70000076293945</v>
+      </c>
+      <c r="I368" t="n">
+        <v>37.2599983215332</v>
+      </c>
+      <c r="J368" t="n">
+        <v>39.70000076293945</v>
+      </c>
+      <c r="K368" t="n">
+        <v>127456</v>
+      </c>
+      <c r="L368" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>Manaksia Aluminium Company Share Price: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>Manaksia Aluminium Board Clears Q1 Results, Sets AGM and Dividend Record Dates - TipRanks</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>Manaksia Aluminium Q1 Results: Net profit rises 83% YoY to ₹2.85 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>Manaksia Aluminium Board Clears Q1 Results, Sets AGM and Dividend Record Dates - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>8</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>PVP.NS</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>PVP Ventures Limited</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>48</v>
+      </c>
+      <c r="F369" t="n">
+        <v>52</v>
+      </c>
+      <c r="G369" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="H369" t="n">
+        <v>51.68000030517578</v>
+      </c>
+      <c r="I369" t="n">
+        <v>48.59000015258789</v>
+      </c>
+      <c r="J369" t="n">
+        <v>51.68000030517578</v>
+      </c>
+      <c r="K369" t="n">
+        <v>3517997</v>
+      </c>
+      <c r="L369" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>PVP Ventures Share Price Today With Price and Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>PVPFUN Price Today | Live PVP Price, Chart &amp; Market Data - Binance</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd. Share Price Gain: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - Univest</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>9</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>RCF.NS</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Rashtriya Chemicals and Fertilizers Limited</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>121</v>
+      </c>
+      <c r="F370" t="n">
+        <v>128.5500030517578</v>
+      </c>
+      <c r="G370" t="n">
+        <v>120.25</v>
+      </c>
+      <c r="H370" t="n">
+        <v>126.0999984741211</v>
+      </c>
+      <c r="I370" t="n">
+        <v>119.0299987792969</v>
+      </c>
+      <c r="J370" t="n">
+        <v>126.0999984741211</v>
+      </c>
+      <c r="K370" t="n">
+        <v>14586500</v>
+      </c>
+      <c r="L370" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>FACT, Paradeep Phosphates, RCF, other fertiliser stocks rally up to 13%. Here's why - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>FACT, Paradeep Phosphates, RCF, other fertiliser stocks rally up to 13%. Here's why - The Economic Times</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>RCF Q1 PAT jumps 35% YoY to Rs 74 crore - Business Standard</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>Stocks to Watch today: Bajaj Finance, Vedanta, Tata Steel, Dabur, PNB, RCF - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>GAIL and RCF sign MoU for 1.27 MMTPA gas-based fertilizer plant in Maharashtra - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>10</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>GIPCL.NS</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Gujarat Industries Power Company Limited</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>177.3999938964844</v>
+      </c>
+      <c r="F371" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="G371" t="n">
+        <v>177.3999938964844</v>
+      </c>
+      <c r="H371" t="n">
+        <v>188.8999938964844</v>
+      </c>
+      <c r="I371" t="n">
+        <v>178.3899993896484</v>
+      </c>
+      <c r="J371" t="n">
+        <v>188.8999938964844</v>
+      </c>
+      <c r="K371" t="n">
+        <v>2290986</v>
+      </c>
+      <c r="L371" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>Gujarat Industries Power Standalone Q1 Net Profit Rises to ₹160 Crore on ₹500 Crore Revenue - Sahi</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>Gujarat Industries Power Standalone Q1 Net Profit Rises to ₹160 Crore on ₹500 Crore Revenue - Sahi</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr"/>
+      <c r="P371" t="inlineStr"/>
+      <c r="Q371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>11</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>JARO.NS</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Jaro Institute of Technology Management and Research Limited</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>450</v>
+      </c>
+      <c r="F372" t="n">
+        <v>476.3999938964844</v>
+      </c>
+      <c r="G372" t="n">
+        <v>445.8999938964844</v>
+      </c>
+      <c r="H372" t="n">
+        <v>468</v>
+      </c>
+      <c r="I372" t="n">
+        <v>445.2000122070312</v>
+      </c>
+      <c r="J372" t="n">
+        <v>468</v>
+      </c>
+      <c r="K372" t="n">
+        <v>231791</v>
+      </c>
+      <c r="L372" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>Jaro Institute of Technology Management and Research Limited Actuals &amp; Estimates (NSE:JARO) - TradingView</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>Jaro Inst promoter Balkrishna Salunkhe buys 7,390 shares in open market - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>Jaro Inst promoter acquires 300 equity shares in open market - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>Jaro Education shares make muted market debut; later tanks nearly 18 pc - News18</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>Small-cap stock under ₹500 jumps 5% despite muted trend on Dalal Street - Livemint</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>12</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>AWL.NS</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>AWL Agri Business Limited</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>194</v>
+      </c>
+      <c r="F373" t="n">
+        <v>204.8200073242188</v>
+      </c>
+      <c r="G373" t="n">
+        <v>192.9799957275391</v>
+      </c>
+      <c r="H373" t="n">
+        <v>203.3899993896484</v>
+      </c>
+      <c r="I373" t="n">
+        <v>193.8800048828125</v>
+      </c>
+      <c r="J373" t="n">
+        <v>203.3899993896484</v>
+      </c>
+      <c r="K373" t="n">
+        <v>10755878</v>
+      </c>
+      <c r="L373" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>Fortune maker AWL piles up edible oil stocks as Middle East, Ukraine wars rattle supply chains: CEO Shrikant Kanhere - ET Retail</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>Bandhan Small Cap Fund July portfolio: 15 stocks added, 9 exited; HDFC Bank, AWL Agri see higher holdings - TradingView</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>Analyst Estimates: Here's What Brokers Think Of AWL Agri Business Limited (NSE:AWL) After Its First-Quarter Report - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>AWL Agri Business Shares Rise 5.82% to Rs 198.50, Among Nifty Midcap 150 Top Gainers - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>AWL Agri Business Shares Rise 2.23%; Stock Among Top Gainers on Nifty Midcap 150 - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>13</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>DELTACORP.NS</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Delta Corp Limited</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>59.16999816894531</v>
+      </c>
+      <c r="F374" t="n">
+        <v>62.2400016784668</v>
+      </c>
+      <c r="G374" t="n">
+        <v>58.90000152587891</v>
+      </c>
+      <c r="H374" t="n">
+        <v>61.72000122070312</v>
+      </c>
+      <c r="I374" t="n">
+        <v>58.88000106811523</v>
+      </c>
+      <c r="J374" t="n">
+        <v>61.72000122070312</v>
+      </c>
+      <c r="K374" t="n">
+        <v>2541358</v>
+      </c>
+      <c r="L374" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>Why Delta's (NSE:DELTACORP) Earnings Are Weaker Than They Seem - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>DELTACORP Mar 2026 Earnings: Steady Performance Amidst Regulatory Landscape - Performance Review - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>Supreme Court Grants Interim Stay on Rs 1,752.37 crore GST Demand Against Delta Corp - StudyCafe</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>Delta Corp's Marvel Resorts to Acquire 74% Stake in Easymile Parking and Shanta Infratech - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>Delta Corp Shares Edge Higher at ₹67.15, Key Resistance at ₹70.51 in Focus - Leveraged ETF Flow - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>14</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>BVCL.NS</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Barak Valley Cements Limited</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>41.20999908447266</v>
+      </c>
+      <c r="F375" t="n">
+        <v>44.40000152587891</v>
+      </c>
+      <c r="G375" t="n">
+        <v>41.20999908447266</v>
+      </c>
+      <c r="H375" t="n">
+        <v>43.43999862670898</v>
+      </c>
+      <c r="I375" t="n">
+        <v>41.63000106811523</v>
+      </c>
+      <c r="J375" t="n">
+        <v>43.43999862670898</v>
+      </c>
+      <c r="K375" t="n">
+        <v>232091</v>
+      </c>
+      <c r="L375" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>Barak Valley Cements Q1 Results: Net profit rises 19% YoY to ₹3.02 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>Barak Valley Cements Q1 Results: Net profit rises 19% YoY to ₹3.02 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr"/>
+      <c r="P375" t="inlineStr"/>
+      <c r="Q375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>15</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>ABDL.NS</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Allied Blenders and Distillers Limited</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>615</v>
+      </c>
+      <c r="F376" t="n">
+        <v>643.9000244140625</v>
+      </c>
+      <c r="G376" t="n">
+        <v>613.4000244140625</v>
+      </c>
+      <c r="H376" t="n">
+        <v>636.1500244140625</v>
+      </c>
+      <c r="I376" t="n">
+        <v>610.3499755859375</v>
+      </c>
+      <c r="J376" t="n">
+        <v>636.1500244140625</v>
+      </c>
+      <c r="K376" t="n">
+        <v>826406</v>
+      </c>
+      <c r="L376" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>ABDL announces its first overseas local production arrangement - Business Standard</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>ABDL announces its first overseas local production arrangement - Business Standard</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr"/>
+      <c r="P376" t="inlineStr"/>
+      <c r="Q376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>16</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>PARADEEP.NS</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Paradeep Phosphates Limited</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>150.8000030517578</v>
+      </c>
+      <c r="F377" t="n">
+        <v>160.6000061035156</v>
+      </c>
+      <c r="G377" t="n">
+        <v>150.8000030517578</v>
+      </c>
+      <c r="H377" t="n">
+        <v>155.7100067138672</v>
+      </c>
+      <c r="I377" t="n">
+        <v>149.3999938964844</v>
+      </c>
+      <c r="J377" t="n">
+        <v>155.7100067138672</v>
+      </c>
+      <c r="K377" t="n">
+        <v>31196247</v>
+      </c>
+      <c r="L377" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>Fertiliser Stocks Jump Up To 10% — FACT, Paradeep Phosphates, NFL Gain. Here's Why - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>FACT, Rashtriya Chemicals and Fertilisers, Paradeep Phosphates: Fertiliser shares surge up to 15%; here is why - Upstox</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>FACT, Rashtriya Chemicals and Fertilisers, Paradeep Phosphates: Fertiliser shares surge up to 15%; here is why - Upstox</t>
+        </is>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>FACT, Paradeep Phosphates, RCF, other fertiliser stocks rally up to 13%. Here's why - The Economic Times</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-24 — cnbctv:1dafb002e094b:0 - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>17</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>EMPOWER.NS</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Empower India Limited</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>2.380000114440918</v>
+      </c>
+      <c r="F378" t="n">
+        <v>2.470000028610229</v>
+      </c>
+      <c r="G378" t="n">
+        <v>2.369999885559082</v>
+      </c>
+      <c r="H378" t="n">
+        <v>2.470000028610229</v>
+      </c>
+      <c r="I378" t="n">
+        <v>2.369999885559082</v>
+      </c>
+      <c r="J378" t="n">
+        <v>2.470000028610229</v>
+      </c>
+      <c r="K378" t="n">
+        <v>5668630</v>
+      </c>
+      <c r="L378" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>Empower India - 11 penny stocks surged up to 198% in 6 months. Do you own any? - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>More money to help farmer firefighters better protect properties and save time - Stock Journal</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>Empower India shareholders approve Rajesh Chavan as managing director - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>Empower Q2 Results: Base earnings rise 34% to $332 million - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>More money to help farmer firefighters better protect properties and save time - Stock Journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>18</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>PITTIENG.NS</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Pitti Engineering Limited</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F379" t="n">
+        <v>1149.5</v>
+      </c>
+      <c r="G379" t="n">
+        <v>1100.5</v>
+      </c>
+      <c r="H379" t="n">
+        <v>1143.650024414062</v>
+      </c>
+      <c r="I379" t="n">
+        <v>1098.25</v>
+      </c>
+      <c r="J379" t="n">
+        <v>1143.650024414062</v>
+      </c>
+      <c r="K379" t="n">
+        <v>361017</v>
+      </c>
+      <c r="L379" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>Pitti Engineering Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>Pitti Engineering Publishes AGM and E-Voting Details for Shareholders - TipRanks</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>Pitti Engineering Publishes AGM and E-Voting Details for Shareholders - TipRanks</t>
+        </is>
+      </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>Pitti Engineering షేర్: Q1లో అద్భుత వృద్ధి! రెవెన్యూ **16%** పెరిగి **₹529 కోట్లకు**, వాల్యూమ్ **19%** జంప్! - Whalesbook</t>
+        </is>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>Pitti Engineering Share Price: FY27ના પ્રથમ ક્વાર્ટરમાં રેવન્યુમાં **16%** નો વધારો, શેર હોલ્ડર્સની વધી દિશા - Whalesbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>19</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>DHARMAJ.NS</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Dharmaj Crop Guard Limited</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>260.6499938964844</v>
+      </c>
+      <c r="F380" t="n">
+        <v>271.5</v>
+      </c>
+      <c r="G380" t="n">
+        <v>256.8999938964844</v>
+      </c>
+      <c r="H380" t="n">
+        <v>271.2000122070312</v>
+      </c>
+      <c r="I380" t="n">
+        <v>260.6499938964844</v>
+      </c>
+      <c r="J380" t="n">
+        <v>271.2000122070312</v>
+      </c>
+      <c r="K380" t="n">
+        <v>30691</v>
+      </c>
+      <c r="L380" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>Insecticides India vs Dharmaj Crop Guard: Which Agro Stock - Univest</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>Dharmaj Crop Guard publishes notice for 12th AGM to be held via VC - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>Dharmaj Crop Consolidated June 2026 Net Sales at Rs 382.38 crore, up 4.08% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>Dharmaj Crop Standalone June 2026 Net Sales at Rs 384.10 crore, up 4.55% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>Dharmaj Crop Guard publishes notice for 12th AGM to be held via VC - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>20</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>SREEL.NS</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Sreeleathers Limited</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>248.0500030517578</v>
+      </c>
+      <c r="F381" t="n">
+        <v>261.7799987792969</v>
+      </c>
+      <c r="G381" t="n">
+        <v>248.0500030517578</v>
+      </c>
+      <c r="H381" t="n">
+        <v>259.510009765625</v>
+      </c>
+      <c r="I381" t="n">
+        <v>249.7100067138672</v>
+      </c>
+      <c r="J381" t="n">
+        <v>259.510009765625</v>
+      </c>
+      <c r="K381" t="n">
+        <v>28223</v>
+      </c>
+      <c r="L381" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>Sreeleathers Ltd. Share Price Gain: Technicals &amp; Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>Sreeleathers Ltd. Share Price Gain: Technicals &amp; Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>Sreeleathers shareholders approve Bhaskar Chatterjee as independent director - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr"/>
+      <c r="Q381" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22305,7 +23622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q361"/>
+  <dimension ref="A1:Q381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42735,7 +44052,6 @@
           <t>Cressanda Railway Solutions Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com</t>
         </is>
       </c>
-      <c r="Q344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -42859,9 +44175,6 @@
           <t>ORCHASP Consolidated June 2026 Net Sales at Rs 2.08 crore, down 73.12% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
-      <c r="O346" t="inlineStr"/>
-      <c r="P346" t="inlineStr"/>
-      <c r="Q346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -43054,9 +44367,6 @@
           <t>Ravinder Heights Q1 Results: Q1FY27 Financials Filed With Exchanges - scanx.trade</t>
         </is>
       </c>
-      <c r="O349" t="inlineStr"/>
-      <c r="P349" t="inlineStr"/>
-      <c r="Q349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -43185,8 +44495,6 @@
           <t>Stocks to Buy: 5 Stocks That Can Deliver Returns of Up to 54%; Do You Own Any? - Trade Brains</t>
         </is>
       </c>
-      <c r="P351" t="inlineStr"/>
-      <c r="Q351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -43596,7 +44904,6 @@
           <t>Regency Ceramics Publishes June-Quarter Unaudited Results in Leading Dailies - TipRanks</t>
         </is>
       </c>
-      <c r="Q357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -43651,9 +44958,6 @@
           <t>Intense Technologies Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
-      <c r="O358" t="inlineStr"/>
-      <c r="P358" t="inlineStr"/>
-      <c r="Q358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -43846,9 +45150,1358 @@
           <t>Onix Solar Energy Limited: Shareholders Board Members Managers and Company Profile | INE173M01012 - marketscreener.com</t>
         </is>
       </c>
-      <c r="O361" t="inlineStr"/>
-      <c r="P361" t="inlineStr"/>
-      <c r="Q361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>1</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>RPTECH.NS</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Rashi Peripherals Limited</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>868.3499755859375</v>
+      </c>
+      <c r="F362" t="n">
+        <v>878.4500122070312</v>
+      </c>
+      <c r="G362" t="n">
+        <v>703.7000122070312</v>
+      </c>
+      <c r="H362" t="n">
+        <v>743.1500244140625</v>
+      </c>
+      <c r="I362" t="n">
+        <v>867</v>
+      </c>
+      <c r="J362" t="n">
+        <v>743.1500244140625</v>
+      </c>
+      <c r="K362" t="n">
+        <v>1534524</v>
+      </c>
+      <c r="L362" t="n">
+        <v>-14.28</v>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>Rashi Peripherals Limited (NSE:RPTECH) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>Rashi Peripherals Ltd. Share Price Today - Rashi Peripherals Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>Rashi Peripherals Ltd. (RPTECH) Share Price Hits Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>Pros and Cons of Investing in Rashi Peripherals Share: IT Distributor Analysis 2026 - Univest</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>Rashi Peripherals Ltd. (RPTECH) Share Price Hits New 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>2</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>KOTARISUG.NS</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Kothari Sugars And Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>38.59999847412109</v>
+      </c>
+      <c r="F363" t="n">
+        <v>38.59999847412109</v>
+      </c>
+      <c r="G363" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="H363" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="I363" t="n">
+        <v>39.15999984741211</v>
+      </c>
+      <c r="J363" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="K363" t="n">
+        <v>778688</v>
+      </c>
+      <c r="L363" t="n">
+        <v>-9.98</v>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>Kothari Sugars And Chemicals Share Price Today at Rs 36.35 - Univest</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>Sugar stocks extend gains: What’s driving the rally? - Business Today</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>Kothari Sugars And Chemicals Ltd. (KOTARISUG) Share Price Rises 13.52% Today - Univest</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>Kothari Sugars and Chemicals gets NSE no objection for merger with Kothari Petrochemicals - ChiniMandi</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>Sugar stocks extend gains: What’s driving the rally? - Business Today</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>3</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>KRONOX.NS</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Limited</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>205.3600006103516</v>
+      </c>
+      <c r="F364" t="n">
+        <v>205.3600006103516</v>
+      </c>
+      <c r="G364" t="n">
+        <v>185.1000061035156</v>
+      </c>
+      <c r="H364" t="n">
+        <v>188</v>
+      </c>
+      <c r="I364" t="n">
+        <v>205.3600006103516</v>
+      </c>
+      <c r="J364" t="n">
+        <v>188</v>
+      </c>
+      <c r="K364" t="n">
+        <v>791879</v>
+      </c>
+      <c r="L364" t="n">
+        <v>-8.449999999999999</v>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>Indo Borax Approves Kronox Lab Stake Purchase; Shares Rise 7.44% - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences schedules 17th AGM for September 16, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>Kronox Lab shares hit 20% upper circuit as Indo Borax and Chemicals to acquire 64.26% stake - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>Indo Borax to acquire 64.26% stake in Kronox Lab Sciences in Rs 246-crore deal - Indian Chemical News</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>Indo Borax to Acquire Stakes in Kronox Lab Sciences - Entrepreneur India</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>4</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>HINDCOPPER.NS</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Hindustan Copper Limited</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>542</v>
+      </c>
+      <c r="F365" t="n">
+        <v>551.8499755859375</v>
+      </c>
+      <c r="G365" t="n">
+        <v>529.3499755859375</v>
+      </c>
+      <c r="H365" t="n">
+        <v>531.9500122070312</v>
+      </c>
+      <c r="I365" t="n">
+        <v>574.1500244140625</v>
+      </c>
+      <c r="J365" t="n">
+        <v>531.9500122070312</v>
+      </c>
+      <c r="K365" t="n">
+        <v>27269605</v>
+      </c>
+      <c r="L365" t="n">
+        <v>-7.35</v>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>Hindustan Copper: Govt to sell up to 6% stake via OFS; check floor price details - Upstox</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>Govt''s 6% HindCopper Share Sale Begins - Rediff MoneyWiz</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>Top stocks in news: TCS, Suzlon, ICICI Bank, HindCopper, Sunshine, Kotak Bank, Afcons, Shankesh - Business Today</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>Hindustan Copper Share Price Up 3.13% Today - Univest</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>HINDCOPPER Outlook for the Week (August 24, 2026 – August 28, 2026) - Equitypandit</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>5</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>BAJAJHIND.NS</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>24.10000038146973</v>
+      </c>
+      <c r="F366" t="n">
+        <v>24.35000038146973</v>
+      </c>
+      <c r="G366" t="n">
+        <v>22.42000007629395</v>
+      </c>
+      <c r="H366" t="n">
+        <v>22.55999946594238</v>
+      </c>
+      <c r="I366" t="n">
+        <v>24.22999954223633</v>
+      </c>
+      <c r="J366" t="n">
+        <v>22.55999946594238</v>
+      </c>
+      <c r="K366" t="n">
+        <v>72632672</v>
+      </c>
+      <c r="L366" t="n">
+        <v>-6.89</v>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Stock Price Forecast. Should You Buy BAJAJHIND.NS? - StockInvest.us</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>Dwarikesh, Bajaj Hindusthan, other sugar stocks hit 52-week high as govt tightens stockholding limit - TradingView</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>Dwarikesh, Bajaj Hindusthan, other sugar stocks hit 52-week high as govt tightens stockholding limit - TradingView</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>Most Active Equities on August 19, 2026 at 3:00 PM IST - HDFC Sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>6</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>SAKHTISUG.NS</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Sakthi Sugars Limited</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>22</v>
+      </c>
+      <c r="F367" t="n">
+        <v>22.56999969482422</v>
+      </c>
+      <c r="G367" t="n">
+        <v>21</v>
+      </c>
+      <c r="H367" t="n">
+        <v>21.14999961853027</v>
+      </c>
+      <c r="I367" t="n">
+        <v>22.39999961853027</v>
+      </c>
+      <c r="J367" t="n">
+        <v>21.14999961853027</v>
+      </c>
+      <c r="K367" t="n">
+        <v>353444</v>
+      </c>
+      <c r="L367" t="n">
+        <v>-5.58</v>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>Sakthi Sugars Share Price news with sector and peer view - Univest</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>Sakthi Sugars Share Price news with sector and peer view - Univest</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>Sakthi Sugars Limited Appoints R. Jeysree to Head the Internal Audit Department(In-House), Effective August 13, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>Sakthi Sugars Ltd. Share Price Up 10.82%: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>Sakthi Sugars Ltd. Share Price Rises 10.69%: Full Analysis - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>7</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS.NS</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>TD Power Systems Limited</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>780.2000122070312</v>
+      </c>
+      <c r="F368" t="n">
+        <v>782.5</v>
+      </c>
+      <c r="G368" t="n">
+        <v>733.4000244140625</v>
+      </c>
+      <c r="H368" t="n">
+        <v>739</v>
+      </c>
+      <c r="I368" t="n">
+        <v>780.0999755859375</v>
+      </c>
+      <c r="J368" t="n">
+        <v>739</v>
+      </c>
+      <c r="K368" t="n">
+        <v>1130167</v>
+      </c>
+      <c r="L368" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>Up 27x in 5 yrs! Why this multibagger smallcap stock showing 50% fall in some trading apps today? - Business Today</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>Why Did TD Power Systems Shares Crash 50% Today? Check the Reason - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS: Revenue and profit surged year-over-year, with robust EPS and improved margins - TradingView</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>Interested In TD Power Systems' (NSE:TDPOWERSYS) Upcoming ₹1.10 Dividend? You Have One Day Left - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>Brokers Are Upgrading Their Views On TD Power Systems Limited (NSE:TDPOWERSYS) With These New Forecasts - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>8</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>ELITECON.NS</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Elitecon International Limited</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>15.19999980926514</v>
+      </c>
+      <c r="F369" t="n">
+        <v>15.47999954223633</v>
+      </c>
+      <c r="G369" t="n">
+        <v>14.39999961853027</v>
+      </c>
+      <c r="H369" t="n">
+        <v>14.39999961853027</v>
+      </c>
+      <c r="I369" t="n">
+        <v>15.1899995803833</v>
+      </c>
+      <c r="J369" t="n">
+        <v>14.39999961853027</v>
+      </c>
+      <c r="K369" t="n">
+        <v>1197314</v>
+      </c>
+      <c r="L369" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>Elitecon appoints Vipin Sharma and Pradeep Kumar as Executive Directors - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>Elitecon appoints Vipin Sharma and Pradeep Kumar as Executive Directors - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>Small-cap stock under ₹50 Elitecon International hits 10% upper circuit for second day in a row - Livemint</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>Small-cap stock trades green despite tepid stock market trends - Livemint</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>Elitecon International: Kumar Anubhav Upadhyay ceases as Additional Director - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>9</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>TAKE.NS</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>TAKE Limited</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>19.04999923706055</v>
+      </c>
+      <c r="F370" t="n">
+        <v>19.29000091552734</v>
+      </c>
+      <c r="G370" t="n">
+        <v>18.80999946594238</v>
+      </c>
+      <c r="H370" t="n">
+        <v>18.80999946594238</v>
+      </c>
+      <c r="I370" t="n">
+        <v>19.79000091552734</v>
+      </c>
+      <c r="J370" t="n">
+        <v>18.80999946594238</v>
+      </c>
+      <c r="K370" t="n">
+        <v>123313</v>
+      </c>
+      <c r="L370" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>Umpires Adrian Holdstock and Shaun George take stock of the ground at Durban - Cricinfo</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>Take-Two's Twin Headwinds: A Leak Offensive and a Stock That Analysts Refuse to Abandon - Ad-hoc-news.de</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>What Moderna Must Do to Take Its Stock to the Next Level - Barron's</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>Woman shares emotional moment as parents take first-ever flight: ‘Life has come full circle’ | Trending - Hindustan Times</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>Delhi: Swine Flu Cases On The Rise, High-level Meeting To Take Stock - ETV Bharat</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>10</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>ATLANTAELE.NS</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Atlanta Electricals Limited</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>1801</v>
+      </c>
+      <c r="F371" t="n">
+        <v>1812</v>
+      </c>
+      <c r="G371" t="n">
+        <v>1725.099975585938</v>
+      </c>
+      <c r="H371" t="n">
+        <v>1733.699951171875</v>
+      </c>
+      <c r="I371" t="n">
+        <v>1819.5</v>
+      </c>
+      <c r="J371" t="n">
+        <v>1733.699951171875</v>
+      </c>
+      <c r="K371" t="n">
+        <v>68111</v>
+      </c>
+      <c r="L371" t="n">
+        <v>-4.72</v>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>ATLANTAELE Stock Price and Chart — NSE:ATLANTAELE - TradingView</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>ATLANTAELE Stock Price and Chart — NSE:ATLANTAELE - TradingView</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr"/>
+      <c r="P371" t="inlineStr"/>
+      <c r="Q371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>11</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>GRADIENTE.NS</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Gradiente Infotainment Limited</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>3.029999971389771</v>
+      </c>
+      <c r="F372" t="n">
+        <v>3.029999971389771</v>
+      </c>
+      <c r="G372" t="n">
+        <v>2.839999914169312</v>
+      </c>
+      <c r="H372" t="n">
+        <v>2.839999914169312</v>
+      </c>
+      <c r="I372" t="n">
+        <v>2.980000019073486</v>
+      </c>
+      <c r="J372" t="n">
+        <v>2.839999914169312</v>
+      </c>
+      <c r="K372" t="n">
+        <v>1949939</v>
+      </c>
+      <c r="L372" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>Gradiente Infotainment Considers Capital Raising Initiatives in Board Meeting - Sahi</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>Gradiente Asian Fashion Tour India - Mumbai Curtain Raiser Marks the 25th Season with Fashion, Glamour and New Talent - Big News Network.com</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>Gradiente Infotainment approves ₹65 Cr capex for micro dramas and music videos - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>Price Band Hitters, August 11, 2026, 3:30 PM IST - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>Major Push for the Orange Economy: Gradiente Infotainment Unveils ₹5,000 Crore Mega Investment Roadmap - The Tribune</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>12</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>GANGAFORGE.NS</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Ganga Forging Limited</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>1.860000014305115</v>
+      </c>
+      <c r="F373" t="n">
+        <v>2</v>
+      </c>
+      <c r="G373" t="n">
+        <v>1.860000014305115</v>
+      </c>
+      <c r="H373" t="n">
+        <v>1.860000014305115</v>
+      </c>
+      <c r="I373" t="n">
+        <v>1.950000047683716</v>
+      </c>
+      <c r="J373" t="n">
+        <v>1.860000014305115</v>
+      </c>
+      <c r="K373" t="n">
+        <v>18057141</v>
+      </c>
+      <c r="L373" t="n">
+        <v>-4.62</v>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>Ganga Forging submits Letter of Offer for ₹32.96 crore rights issue - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>Adamas (ADAM) Q2 2026 Results: EPS Exceeds Its Estimate on the Day; Trading Response: Shares Finish 0.80% Down at the Close - Product Revenue Analysis - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>Ganga Forging opens Rights Issue at ₹1.63 per share - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>Adamas (ADAM) Q2 2026 Results: EPS Exceeds Its Estimate on the Day; Trading Response: Shares Finish 0.80% Down at the Close - Product Revenue Analysis - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>13</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>DATAPATTNS.NS</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Data Patterns (India) Limited</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>4730</v>
+      </c>
+      <c r="F374" t="n">
+        <v>4768.7001953125</v>
+      </c>
+      <c r="G374" t="n">
+        <v>4500.10009765625</v>
+      </c>
+      <c r="H374" t="n">
+        <v>4522</v>
+      </c>
+      <c r="I374" t="n">
+        <v>4736.2001953125</v>
+      </c>
+      <c r="J374" t="n">
+        <v>4522</v>
+      </c>
+      <c r="K374" t="n">
+        <v>845786</v>
+      </c>
+      <c r="L374" t="n">
+        <v>-4.52</v>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>DATAPATTNS Share Price | Data Patterns (India) Ltd Stock Analysis &amp; Recommendation - marketsmojo.com</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>Defence stock with Rs 2,654-crore order book hits record high; here's why - Business Today</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>Data Patterns shares collapse 7% as Q1FY27 earnings show subdued performance - Upstox</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>Data Patterns Share Price Today: Stock Rises 3.11% - Univest</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>Data Patterns (India) Ltd. Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>14</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>RANASUG.NS</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Rana Sugars Limited</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>15.77999973297119</v>
+      </c>
+      <c r="F375" t="n">
+        <v>16.19000053405762</v>
+      </c>
+      <c r="G375" t="n">
+        <v>15.01000022888184</v>
+      </c>
+      <c r="H375" t="n">
+        <v>15.19999980926514</v>
+      </c>
+      <c r="I375" t="n">
+        <v>15.92000007629395</v>
+      </c>
+      <c r="J375" t="n">
+        <v>15.19999980926514</v>
+      </c>
+      <c r="K375" t="n">
+        <v>670550</v>
+      </c>
+      <c r="L375" t="n">
+        <v>-4.52</v>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>Rana Sugars Share Price rises 8.84%: key stock analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>Rana Sugars Share Price rises 8.84%: key stock analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr"/>
+      <c r="Q375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>15</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>KMSUGAR.NS</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>K.M.Sugar Mills Limited</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>34.04000091552734</v>
+      </c>
+      <c r="F376" t="n">
+        <v>35</v>
+      </c>
+      <c r="G376" t="n">
+        <v>31.1200008392334</v>
+      </c>
+      <c r="H376" t="n">
+        <v>32.54999923706055</v>
+      </c>
+      <c r="I376" t="n">
+        <v>34.04999923706055</v>
+      </c>
+      <c r="J376" t="n">
+        <v>32.54999923706055</v>
+      </c>
+      <c r="K376" t="n">
+        <v>370950</v>
+      </c>
+      <c r="L376" t="n">
+        <v>-4.41</v>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>K.M. Sugar Mills Share Price rises 8.17%: valuation, peers - Univest</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>K.M. Sugar Mills Share Price rises 8.17%: valuation, peers - Univest</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>K.M. Sugar Mills Ltd. Share Price Today With Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>K.M. Sugar Mills Ltd. Share Price Rise With Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>Keysight Technologies (KEYS) Slips 1.5% as Shares Hold Above Key Support - Earnings Breakout Stocks - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>16</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>NETWEB.NS</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Netweb Technologies India Limited</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>5400</v>
+      </c>
+      <c r="F377" t="n">
+        <v>5413.2001953125</v>
+      </c>
+      <c r="G377" t="n">
+        <v>5208</v>
+      </c>
+      <c r="H377" t="n">
+        <v>5220</v>
+      </c>
+      <c r="I377" t="n">
+        <v>5454.5</v>
+      </c>
+      <c r="J377" t="n">
+        <v>5220</v>
+      </c>
+      <c r="K377" t="n">
+        <v>1241468</v>
+      </c>
+      <c r="L377" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>Netweb Technologies shares fall over 3% after Rs 1,200 crore QIP - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>Netweb Technologies shares fall 4% after raising Rs 1,200 crore through QIP - The Economic Times</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>Netweb Technologies shares fall 4% after raising Rs 1,200 crore through QIP - The Economic Times</t>
+        </is>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>Netweb Tech raises Rs 1,200 crore via QIP; stock falls for 2nd day, down 4% - Business Today</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>Netweb Tech Raises ₹1,200 Crore By Issuing 25,05,219 Equity Shares At ₹4,790 Each - Sahi</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>17</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>IIFL.NS</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>IIFL Finance Limited</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>667</v>
+      </c>
+      <c r="F378" t="n">
+        <v>681.0999755859375</v>
+      </c>
+      <c r="G378" t="n">
+        <v>643.5499877929688</v>
+      </c>
+      <c r="H378" t="n">
+        <v>670.2999877929688</v>
+      </c>
+      <c r="I378" t="n">
+        <v>696.4000244140625</v>
+      </c>
+      <c r="J378" t="n">
+        <v>670.2999877929688</v>
+      </c>
+      <c r="K378" t="n">
+        <v>6270881</v>
+      </c>
+      <c r="L378" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>IIFL Finance shares decline over 7% after home finance arm receives ₹963 crore income tax demand notice; here's why - Upstox</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>IFL Finance shares drop 8% as IIFL Home Finance gets Rs 963 crore tax demand - The Economic Times</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>IIFL Finance shares fall 4% after subsidiary faces Rs 963 crore tax demand - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>IIFL Finance shares crack 8% after ₹963-crore tax demand for subsidiary - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>IIFL Finance shares fall nearly 8% after receiving tax demand of ₹963 crore for home finance arm - CNBC TV18</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>18</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>TBZ.NS</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Tribhovandas Bhimji Zaveri Limited</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>285</v>
+      </c>
+      <c r="F379" t="n">
+        <v>285.3999938964844</v>
+      </c>
+      <c r="G379" t="n">
+        <v>274.0499877929688</v>
+      </c>
+      <c r="H379" t="n">
+        <v>275.5</v>
+      </c>
+      <c r="I379" t="n">
+        <v>286.2000122070312</v>
+      </c>
+      <c r="J379" t="n">
+        <v>275.5</v>
+      </c>
+      <c r="K379" t="n">
+        <v>498776</v>
+      </c>
+      <c r="L379" t="n">
+        <v>-3.74</v>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>Tribhovandas Bhimji Zaveri Ltd. (TBZ) Share Price Rises 8.82% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>Tribhovandas Bhimji Zaveri Ltd. (TBZ) Share Price Rises 8.82% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>TBZ outlines TDS rules for ₹2.50 per share FY26 dividend - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>TBZ Reports Strong Unaudited Q1 FY27 Results, Maintains Profit Momentum - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>19</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>VOLTAMP.NS</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Voltamp Transformers Limited</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>11382.5</v>
+      </c>
+      <c r="F380" t="n">
+        <v>11400</v>
+      </c>
+      <c r="G380" t="n">
+        <v>10670</v>
+      </c>
+      <c r="H380" t="n">
+        <v>10875</v>
+      </c>
+      <c r="I380" t="n">
+        <v>11292</v>
+      </c>
+      <c r="J380" t="n">
+        <v>10875</v>
+      </c>
+      <c r="K380" t="n">
+        <v>41420</v>
+      </c>
+      <c r="L380" t="n">
+        <v>-3.69</v>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>Voltamp Transformers Share Price today: price, valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>Voltamp Transformers Share Price today: price, valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>Voltamp Transformers posts ₹912M profit in Q1FY27, updates capex plan - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>Voltamp Trans Standalone June 2026 Net Sales at Rs 543.78 crore, up 28.38% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>Voltamp Transformers declares ₹100 final dividend per share for FY26 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:50:15 IST</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>20</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>RAIN.NS</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Rain Industries Limited</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>213.8899993896484</v>
+      </c>
+      <c r="F381" t="n">
+        <v>213.8899993896484</v>
+      </c>
+      <c r="G381" t="n">
+        <v>204.0099945068359</v>
+      </c>
+      <c r="H381" t="n">
+        <v>205.8999938964844</v>
+      </c>
+      <c r="I381" t="n">
+        <v>213.6900024414062</v>
+      </c>
+      <c r="J381" t="n">
+        <v>205.8999938964844</v>
+      </c>
+      <c r="K381" t="n">
+        <v>2272466</v>
+      </c>
+      <c r="L381" t="n">
+        <v>-3.65</v>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>"2 Hours 15 Minutes In Traffic": Man Shares How Rain Affected His Commute To Bengaluru Airport - NDTV</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>Rain Industries share price: Petrochemical stock jumps 4% amid soaring crude oil prices on US-Iran war - Livemint</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>Rain Industries share price: Petrochemical stock jumps 4% amid soaring crude oil prices on US-Iran war - Livemint</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>RAIN Should I Buy - Intellectia AI</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>Just Three Days Till Rain Industries Limited (NSE:RAIN) Will Be Trading Ex-Dividend - simplywall.st</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q381"/>
+  <dimension ref="A1:Q401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22756,7 +22756,6 @@
           <t>Manaksia Aluminium Board Clears Q1 Results, Sets AGM and Dividend Record Dates - TipRanks</t>
         </is>
       </c>
-      <c r="Q368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -22949,9 +22948,6 @@
           <t>Gujarat Industries Power Standalone Q1 Net Profit Rises to ₹160 Crore on ₹500 Crore Revenue - Sahi</t>
         </is>
       </c>
-      <c r="O371" t="inlineStr"/>
-      <c r="P371" t="inlineStr"/>
-      <c r="Q371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -23213,9 +23209,6 @@
           <t>Barak Valley Cements Q1 Results: Net profit rises 19% YoY to ₹3.02 crore - scanx.trade</t>
         </is>
       </c>
-      <c r="O375" t="inlineStr"/>
-      <c r="P375" t="inlineStr"/>
-      <c r="Q375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -23270,9 +23263,6 @@
           <t>ABDL announces its first overseas local production arrangement - Business Standard</t>
         </is>
       </c>
-      <c r="O376" t="inlineStr"/>
-      <c r="P376" t="inlineStr"/>
-      <c r="Q376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -23608,8 +23598,1346 @@
           <t>Sreeleathers shareholders approve Bhaskar Chatterjee as independent director - scanx.trade</t>
         </is>
       </c>
-      <c r="P381" t="inlineStr"/>
-      <c r="Q381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>1</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>GENESYS.NS</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Genesys International Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>181.3000030517578</v>
+      </c>
+      <c r="F382" t="n">
+        <v>214.25</v>
+      </c>
+      <c r="G382" t="n">
+        <v>181.3000030517578</v>
+      </c>
+      <c r="H382" t="n">
+        <v>214.25</v>
+      </c>
+      <c r="I382" t="n">
+        <v>178.5500030517578</v>
+      </c>
+      <c r="J382" t="n">
+        <v>214.25</v>
+      </c>
+      <c r="K382" t="n">
+        <v>4189199</v>
+      </c>
+      <c r="L382" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>Genesys International shares jump twenty percent | Tap to know more | Inshorts - Inshorts</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>Genesys International Corporation Ltd leads gainers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>Genesys International Corp fixes rights issue price at ₹50 for 2.5Cr shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>Genesys International Corporation Ltd leads gainers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>Taxes of Genesys International Corporation Limited Rights 2026-21.08.26 For Shares – BSE:GENESYS_RE - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>2</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>DUCON.NS</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Ducon Infratechnologies Limited</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>2.259999990463257</v>
+      </c>
+      <c r="F383" t="n">
+        <v>2.539999961853027</v>
+      </c>
+      <c r="G383" t="n">
+        <v>2.210000038146973</v>
+      </c>
+      <c r="H383" t="n">
+        <v>2.400000095367432</v>
+      </c>
+      <c r="I383" t="n">
+        <v>2.175652027130127</v>
+      </c>
+      <c r="J383" t="n">
+        <v>2.400000095367432</v>
+      </c>
+      <c r="K383" t="n">
+        <v>3670210</v>
+      </c>
+      <c r="L383" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>Ducon Infratechnologies Ltd. Share Price Today: 11.98% Gain - Univest</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>Ducon Infratechnologies Ltd. Share Price Today: 11.98% Gain - Univest</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>Ducon Infratechnologies wins contract with India's largest aluminium smelter - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>Ducon Infratechnologies Wins Contract With India's Largest Aluminium Smelter - Sahi</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>Ducon Infratechnologies approves rights issue of up to ₹25 Crore - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>3</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>TARMAT.NS</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Tarmat Limited</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>50.02999877929688</v>
+      </c>
+      <c r="F384" t="n">
+        <v>55.45000076293945</v>
+      </c>
+      <c r="G384" t="n">
+        <v>49.59999847412109</v>
+      </c>
+      <c r="H384" t="n">
+        <v>54.22999954223633</v>
+      </c>
+      <c r="I384" t="n">
+        <v>50.13999938964844</v>
+      </c>
+      <c r="J384" t="n">
+        <v>54.22999954223633</v>
+      </c>
+      <c r="K384" t="n">
+        <v>96996</v>
+      </c>
+      <c r="L384" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>Tarmat Limited schedules 41st AGM for September 30, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>Tarmat Limited schedules 41st AGM for September 30, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>Tarmat Ltd. Share Price News: Price Action, Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>Tarmat Ltd Downgraded to Sell by MarketsMOJO Amid Mixed Financial and Technical Signals - marketsmojo.com</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>Tarmat Ltd. Share Price Drop: Price Action and Sector View - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>4</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>CYIENT.NS</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Cyient Limited</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>909</v>
+      </c>
+      <c r="F385" t="n">
+        <v>989</v>
+      </c>
+      <c r="G385" t="n">
+        <v>898.6500244140625</v>
+      </c>
+      <c r="H385" t="n">
+        <v>979.0499877929688</v>
+      </c>
+      <c r="I385" t="n">
+        <v>909.0499877929688</v>
+      </c>
+      <c r="J385" t="n">
+        <v>979.0499877929688</v>
+      </c>
+      <c r="K385" t="n">
+        <v>4712452</v>
+      </c>
+      <c r="L385" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>Cyient DLM Ltd. (CYIENTDLM) Share Price Hits Fresh 52-Week High at Rs 768.95 - Univest</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>Top Gainers &amp; Losers on 25 Aug: FACT, Vodafone Idea, Cyient, Paytm, Angel One, Pine Labs among top gainers - Livemint</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>Top Gainers &amp; Losers on 25 Aug: FACT, Vodafone Idea, Cyient, Paytm, Angel One, Pine Labs among top gainers - Livemint</t>
+        </is>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>Stocks to Watch Today, August 25, 2026: Cyient, Great Eastern Shipping Company, Tata Consultancy Services, Pace Digitek and Chemplast Sanmar - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>HAL shares gain up to 1% after NCLT dissolves joint venture with Cyient - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>5</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>INVENTURE.NS</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Inventure Growth &amp; Securities Limited</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>0.8500000238418579</v>
+      </c>
+      <c r="F386" t="n">
+        <v>0.9300000071525574</v>
+      </c>
+      <c r="G386" t="n">
+        <v>0.8500000238418579</v>
+      </c>
+      <c r="H386" t="n">
+        <v>0.9100000262260437</v>
+      </c>
+      <c r="I386" t="n">
+        <v>0.8500000238418579</v>
+      </c>
+      <c r="J386" t="n">
+        <v>0.9100000262260437</v>
+      </c>
+      <c r="K386" t="n">
+        <v>2156001</v>
+      </c>
+      <c r="L386" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>Inventure Grow Standalone June 2026 Net Sales at Rs 10.67 crore, down 26.91% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>Inventure Growth &amp; Securities posts ₹4.61 crore profit in Q1FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>Inventure Growth &amp; Securities withdraws scheme after RBI denial - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>Inventure Grow Consolidated June 2026 Net Sales at Rs 13.16 crore, down 23.98% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>Andriy Verevskyi Begins Kernel Share Buyout Ahead of Warsaw Stock Exchange Delisting - Inventure.com.ua.</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>6</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>GIPCL.NS</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Gujarat Industries Power Company Limited</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>177.3999938964844</v>
+      </c>
+      <c r="F387" t="n">
+        <v>191.25</v>
+      </c>
+      <c r="G387" t="n">
+        <v>177.3999938964844</v>
+      </c>
+      <c r="H387" t="n">
+        <v>190.7200012207031</v>
+      </c>
+      <c r="I387" t="n">
+        <v>178.3899993896484</v>
+      </c>
+      <c r="J387" t="n">
+        <v>190.7200012207031</v>
+      </c>
+      <c r="K387" t="n">
+        <v>3502664</v>
+      </c>
+      <c r="L387" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>Gujarat Industries Power Standalone Q1 Net Profit Rises to ₹160 Crore on ₹500 Crore Revenue - Sahi</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>Gujarat Industries Power Standalone Q1 Net Profit Rises to ₹160 Crore on ₹500 Crore Revenue - Sahi</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr"/>
+      <c r="P387" t="inlineStr"/>
+      <c r="Q387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>7</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>PARADEEP.NS</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Paradeep Phosphates Limited</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>150.8000030517578</v>
+      </c>
+      <c r="F388" t="n">
+        <v>160.6000061035156</v>
+      </c>
+      <c r="G388" t="n">
+        <v>150.8000030517578</v>
+      </c>
+      <c r="H388" t="n">
+        <v>159.6300048828125</v>
+      </c>
+      <c r="I388" t="n">
+        <v>149.3999938964844</v>
+      </c>
+      <c r="J388" t="n">
+        <v>159.6300048828125</v>
+      </c>
+      <c r="K388" t="n">
+        <v>51528268</v>
+      </c>
+      <c r="L388" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>Fertiliser Stocks Jump Up To 10% — FACT, Paradeep Phosphates, NFL Gain. Here's Why - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>Vodafone Idea, Paradeep Phosphates, Hindustan Copper shares: What expert says - BusinessToday - India IPO</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>Vodafone Idea, Paradeep Phosphates, Hindustan Copper shares: What expert says - Business Today</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>Vodafone Idea, Paradeep Phosphates, Hindustan Copper shares: What expert says - BusinessToday - India IPO</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>FACT, Paradeep Phosphates, RCF, other fertiliser stocks rally up to 13%. Here's why - The Economic Times</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>8</v>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>SHREEPUSHK.NS</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Shree Pushkar Chemicals &amp; Fertilisers Limited</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>427.5</v>
+      </c>
+      <c r="F389" t="n">
+        <v>459.5</v>
+      </c>
+      <c r="G389" t="n">
+        <v>424.0499877929688</v>
+      </c>
+      <c r="H389" t="n">
+        <v>454.1000061035156</v>
+      </c>
+      <c r="I389" t="n">
+        <v>426.8999938964844</v>
+      </c>
+      <c r="J389" t="n">
+        <v>454.1000061035156</v>
+      </c>
+      <c r="K389" t="n">
+        <v>258193</v>
+      </c>
+      <c r="L389" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>Shree Pushkar Chemicals &amp; Fertilisers Limited Announces Board Changes, Effective August 13, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>Shree Pushkar Chemicals &amp; Fertilisers Adds 10 MW Solar Capacity in Maharashtra - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>Shree Pushkar Chemicals Q1 Results: Earnings call set for Aug 13 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>Shree Pushkar Chemicals &amp; Fertilisers Adds 10 MW Solar Capacity in Maharashtra - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>9</v>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>TFCILTD.NS</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Tourism Finance Corporation of India Limited</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>130</v>
+      </c>
+      <c r="F390" t="n">
+        <v>137.9400024414062</v>
+      </c>
+      <c r="G390" t="n">
+        <v>129.2200012207031</v>
+      </c>
+      <c r="H390" t="n">
+        <v>137.0200042724609</v>
+      </c>
+      <c r="I390" t="n">
+        <v>129.5599975585938</v>
+      </c>
+      <c r="J390" t="n">
+        <v>137.0200042724609</v>
+      </c>
+      <c r="K390" t="n">
+        <v>20325175</v>
+      </c>
+      <c r="L390" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>LIC confirms no fresh encumbrance on TFCI shares in FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>LIC confirms no fresh encumbrance on TFCI shares in FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>Tourism Finance Corporation Of India Ltd. (TFCILTD) Share Price Hits Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>Tourism Finance Corporation Of India Ltd. Share Price Near - Univest</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>10</v>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>NECLIFE.NS</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Nectar Lifesciences Limited</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>10.72000026702881</v>
+      </c>
+      <c r="F391" t="n">
+        <v>11.4399995803833</v>
+      </c>
+      <c r="G391" t="n">
+        <v>10.72000026702881</v>
+      </c>
+      <c r="H391" t="n">
+        <v>11.32999992370605</v>
+      </c>
+      <c r="I391" t="n">
+        <v>10.72000026702881</v>
+      </c>
+      <c r="J391" t="n">
+        <v>11.32999992370605</v>
+      </c>
+      <c r="K391" t="n">
+        <v>317808</v>
+      </c>
+      <c r="L391" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>Nectar Lifesciences Limited Changes Its Corporate Office in Chandigarh - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>Nectar Lifesciences to Relocate Corporate Office Within Chandigarh Industrial Hub - TipRanks</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>Nectar Lifesciences to Relocate Corporate Office Within Chandigarh Industrial Hub - TipRanks</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>Nectar Lifesciences Publishes Q1 FY2026 Results in Press and Online - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>11</v>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>BALAMINES.NS</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Balaji Amines Limited</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>2241.60009765625</v>
+      </c>
+      <c r="F392" t="n">
+        <v>2390</v>
+      </c>
+      <c r="G392" t="n">
+        <v>2205.300048828125</v>
+      </c>
+      <c r="H392" t="n">
+        <v>2343.60009765625</v>
+      </c>
+      <c r="I392" t="n">
+        <v>2224.5</v>
+      </c>
+      <c r="J392" t="n">
+        <v>2343.60009765625</v>
+      </c>
+      <c r="K392" t="n">
+        <v>600301</v>
+      </c>
+      <c r="L392" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>Balaji Amines Share Price news: Rs 2,210.70 and sector view - Univest</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>Balaji Amines Share Price news: Rs 2,210.70 and sector view - Univest</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr"/>
+      <c r="P392" t="inlineStr"/>
+      <c r="Q392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>12</v>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>JARO.NS</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Jaro Institute of Technology Management and Research Limited</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>450</v>
+      </c>
+      <c r="F393" t="n">
+        <v>476.3999938964844</v>
+      </c>
+      <c r="G393" t="n">
+        <v>445.8999938964844</v>
+      </c>
+      <c r="H393" t="n">
+        <v>468.5499877929688</v>
+      </c>
+      <c r="I393" t="n">
+        <v>445.2000122070312</v>
+      </c>
+      <c r="J393" t="n">
+        <v>468.5499877929688</v>
+      </c>
+      <c r="K393" t="n">
+        <v>344015</v>
+      </c>
+      <c r="L393" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>Jaro Institute of Technology Management and Research Limited Actuals &amp; Estimates (NSE:JARO) - TradingView</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>Jaro Inst promoter Balkrishna Salunkhe buys 7,390 shares in open market - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>Jaro Inst promoter acquires 300 equity shares in open market - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>Jaro Education shares make muted market debut; later tanks nearly 18 pc - News18</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>Small-cap stock under ₹500 jumps 5% despite muted trend on Dalal Street - Livemint</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>13</v>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>CEWATER.NS</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Concord Enviro Systems Limited</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="F394" t="n">
+        <v>271.3999938964844</v>
+      </c>
+      <c r="G394" t="n">
+        <v>251.9499969482422</v>
+      </c>
+      <c r="H394" t="n">
+        <v>265.4500122070312</v>
+      </c>
+      <c r="I394" t="n">
+        <v>253.1499938964844</v>
+      </c>
+      <c r="J394" t="n">
+        <v>265.4500122070312</v>
+      </c>
+      <c r="K394" t="n">
+        <v>219118</v>
+      </c>
+      <c r="L394" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>Investors Aren't Entirely Convinced By Concord Enviro Systems Limited's (NSE:CEWATER) Earnings - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>Concord Enviro Systems (CEWATER.NS) Gains 3.43% – Bulls Defend Key Support at ₹366.8 - Double Bottom - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>CONCORD ENVIRO SYSTEMS L Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>Concord Enviro Systems Limited Announces Equity Shareholders Meeting for Scheme of Arrangement Approval - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>CEWATER Mar 2026 Earnings: Strong EPS of ₹2.06 on Revenue of ₹17.64 Crore; Stock Gains 3.35% - Mid-Term Outlook - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>14</v>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>RCF.NS</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Rashtriya Chemicals and Fertilizers Limited</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>121</v>
+      </c>
+      <c r="F395" t="n">
+        <v>128.5500030517578</v>
+      </c>
+      <c r="G395" t="n">
+        <v>120.25</v>
+      </c>
+      <c r="H395" t="n">
+        <v>124.4700012207031</v>
+      </c>
+      <c r="I395" t="n">
+        <v>119.0299987792969</v>
+      </c>
+      <c r="J395" t="n">
+        <v>124.4700012207031</v>
+      </c>
+      <c r="K395" t="n">
+        <v>18084974</v>
+      </c>
+      <c r="L395" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>Why did FACT, RCF, NFL and other fertiliser stocks rally up to 14% today? Explained - Livemint</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>Why did FACT, RCF, NFL and other fertiliser stocks rally up to 14% today? Explained - Livemint</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>FACT, Paradeep Phosphates, RCF, other fertiliser stocks rally up to 13%. Here's why - The Economic Times</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>RCF Q1 PAT jumps 35% YoY to Rs 74 crore - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>Stocks to Watch today: Bajaj Finance, Vedanta, Tata Steel, Dabur, PNB, RCF - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>15</v>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>IREDA.NS</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Indian Renewable Energy Development Agency Limited</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>115</v>
+      </c>
+      <c r="F396" t="n">
+        <v>121.1399993896484</v>
+      </c>
+      <c r="G396" t="n">
+        <v>114.4000015258789</v>
+      </c>
+      <c r="H396" t="n">
+        <v>120.6100006103516</v>
+      </c>
+      <c r="I396" t="n">
+        <v>115.4000015258789</v>
+      </c>
+      <c r="J396" t="n">
+        <v>120.6100006103516</v>
+      </c>
+      <c r="K396" t="n">
+        <v>11092821</v>
+      </c>
+      <c r="L396" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>Stocks to watch: Reliance Industries, Power Grid, IREDA among shares to be in focus today. Details here - Livemint</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>Stocks to watch: Reliance Industries, Power Grid, IREDA among shares to be in focus today. Details here - Livemint</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>IREDA Q1 Results 2027: Revenue Rises 16% YoY to ₹2,249 Cr, PAT Jumps 37% to ₹339 Cr - Sahi</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>Dividend Delight! THIS Navratna PSU To Pay 6% Dividend; Stock Up 4%: How To Get Eligible Before Record Date? - Goodreturns</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>Buy, Sell Or Hold: Suzlon, HDFC Bank, Colgate, Torrent Pharma And IREDA — Ask Profit - NDTV Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>16</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>DELTACORP.NS</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Delta Corp Limited</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>59.16999816894531</v>
+      </c>
+      <c r="F397" t="n">
+        <v>62.2400016784668</v>
+      </c>
+      <c r="G397" t="n">
+        <v>58.90000152587891</v>
+      </c>
+      <c r="H397" t="n">
+        <v>61.52000045776367</v>
+      </c>
+      <c r="I397" t="n">
+        <v>58.88000106811523</v>
+      </c>
+      <c r="J397" t="n">
+        <v>61.52000045776367</v>
+      </c>
+      <c r="K397" t="n">
+        <v>3353931</v>
+      </c>
+      <c r="L397" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>DELTACORP Outlook for the Week (August 24, 2026 – August 28, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>DELTACORP Outlook for the Week (August 24, 2026 – August 28, 2026) - Equitypandit</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>Delta Corp Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>Delta Corp Publishes AGM, Book Closure and E-Voting Notice - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>17</v>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>ACUTAAS.NS</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Acutaas Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>3189.89990234375</v>
+      </c>
+      <c r="F398" t="n">
+        <v>3325</v>
+      </c>
+      <c r="G398" t="n">
+        <v>3138</v>
+      </c>
+      <c r="H398" t="n">
+        <v>3313.39990234375</v>
+      </c>
+      <c r="I398" t="n">
+        <v>3173</v>
+      </c>
+      <c r="J398" t="n">
+        <v>3313.39990234375</v>
+      </c>
+      <c r="K398" t="n">
+        <v>409507</v>
+      </c>
+      <c r="L398" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>We Ran A Stock Scan For Earnings Growth And Acutaas Chemicals (NSE:ACUTAAS) Passed With Ease - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>We Ran A Stock Scan For Earnings Growth And Acutaas Chemicals (NSE:ACUTAAS) Passed With Ease - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>Acutaas Chem Standalone June 2026 Net Sales at Rs 322.41 crore, up 56.53% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>Acutaas Chem Consolidated June 2026 Net Sales at Rs 329.67 crore, up 59.08% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>Acutaas Chemicals - 10 microcap stocks surged up to 170% in 6 months; 5 turned multibaggers - The Economic Times</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>18</v>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>DHARMAJ.NS</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Dharmaj Crop Guard Limited</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>260.6499938964844</v>
+      </c>
+      <c r="F399" t="n">
+        <v>278</v>
+      </c>
+      <c r="G399" t="n">
+        <v>256.8999938964844</v>
+      </c>
+      <c r="H399" t="n">
+        <v>271.25</v>
+      </c>
+      <c r="I399" t="n">
+        <v>260.6499938964844</v>
+      </c>
+      <c r="J399" t="n">
+        <v>271.25</v>
+      </c>
+      <c r="K399" t="n">
+        <v>59403</v>
+      </c>
+      <c r="L399" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>Insecticides India vs Dharmaj Crop Guard: Which Agro Stock - Univest</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>Dharmaj Crop Guard publishes notice for 12th AGM to be held via VC - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>Dharmaj Crop Consolidated June 2026 Net Sales at Rs 382.38 crore, up 4.08% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>Dharmaj Crop Standalone June 2026 Net Sales at Rs 384.10 crore, up 4.55% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>Dharmaj Crop Guard publishes notice for 12th AGM to be held via VC - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>19</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>PINELABS.NS</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Pine Labs Limited</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>157.8500061035156</v>
+      </c>
+      <c r="F400" t="n">
+        <v>165.9499969482422</v>
+      </c>
+      <c r="G400" t="n">
+        <v>156.5099945068359</v>
+      </c>
+      <c r="H400" t="n">
+        <v>163.6900024414062</v>
+      </c>
+      <c r="I400" t="n">
+        <v>157.5399932861328</v>
+      </c>
+      <c r="J400" t="n">
+        <v>163.6900024414062</v>
+      </c>
+      <c r="K400" t="n">
+        <v>32229753</v>
+      </c>
+      <c r="L400" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>Pine Labs Limited: Top Mutual Funds Holders | PINELABS | INE15B701018 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>Pine Labs Limited: Top Mutual Funds Holders | PINELABS | INE15B701018 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>PINELABS Stock Price and Chart — NSE:PINELABS - TradingView</t>
+        </is>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>Pine Labs Q1 profit soars four-fold YoY to ₹20 crore, revenue jumps 20%; shares surge 5% - Upstox</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>Pine Labs reports Rs 737 Cr revenue in Q1 FY27; profit jumps over 4X - Entrackr</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>20</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>DCMFINSERV.NS</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>DCM Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>5.130000114440918</v>
+      </c>
+      <c r="F401" t="n">
+        <v>5.489999771118164</v>
+      </c>
+      <c r="G401" t="n">
+        <v>5.010000228881836</v>
+      </c>
+      <c r="H401" t="n">
+        <v>5.329999923706055</v>
+      </c>
+      <c r="I401" t="n">
+        <v>5.130000114440918</v>
+      </c>
+      <c r="J401" t="n">
+        <v>5.329999923706055</v>
+      </c>
+      <c r="K401" t="n">
+        <v>9336</v>
+      </c>
+      <c r="L401" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>DCM Financial Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>Shinhan (SHG) Latest Quarter: EPS Clears the Reported Estimate in the Latest Reading; Closing Reaction: Shares Move 4.07% Higher for the Current Session - Earnings Decline Risk - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>Shinhan (SHG) Latest Quarter: EPS Clears the Reported Estimate in the Latest Reading; Closing Reaction: Shares Move 4.07% Higher for the Current Session - Earnings Decline Risk - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>Dcm Financial Services Limited Announces Resignation of Richa Kathuria as Independent Director, Member of the Audit Committee, Nomination and Remuneration Committee and Stakeholders Relationship Committee, Effective August 11, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>Inspire (INSP) Reported Quarter: The Bottom-Line Figure Outpaces Its Comparison at the Close; Post-Earnings Trading: The Stock Ends Up 0.09% for the Current Session - CFO Commentary Report - vinanet.vn</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23622,7 +24950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q381"/>
+  <dimension ref="A1:Q401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45825,9 +47153,6 @@
           <t>ATLANTAELE Stock Price and Chart — NSE:ATLANTAELE - TradingView</t>
         </is>
       </c>
-      <c r="O371" t="inlineStr"/>
-      <c r="P371" t="inlineStr"/>
-      <c r="Q371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -45961,7 +47286,6 @@
           <t>Adamas (ADAM) Q2 2026 Results: EPS Exceeds Its Estimate on the Day; Trading Response: Shares Finish 0.80% Down at the Close - Product Revenue Analysis - vinanet.vn</t>
         </is>
       </c>
-      <c r="Q373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -46090,8 +47414,6 @@
           <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
         </is>
       </c>
-      <c r="P375" t="inlineStr"/>
-      <c r="Q375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -46363,7 +47685,6 @@
           <t>TBZ Reports Strong Unaudited Q1 FY27 Results, Maintains Profit Momentum - TipRanks</t>
         </is>
       </c>
-      <c r="Q379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -46502,6 +47823,1334 @@
           <t>Just Three Days Till Rain Industries Limited (NSE:RAIN) Will Be Trading Ex-Dividend - simplywall.st</t>
         </is>
       </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>1</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>RPTECH.NS</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Rashi Peripherals Limited</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>868.3499755859375</v>
+      </c>
+      <c r="F382" t="n">
+        <v>878.4500122070312</v>
+      </c>
+      <c r="G382" t="n">
+        <v>703.7000122070312</v>
+      </c>
+      <c r="H382" t="n">
+        <v>779.4500122070312</v>
+      </c>
+      <c r="I382" t="n">
+        <v>867</v>
+      </c>
+      <c r="J382" t="n">
+        <v>779.4500122070312</v>
+      </c>
+      <c r="K382" t="n">
+        <v>4680449</v>
+      </c>
+      <c r="L382" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>Rashi Peripherals director quits citing governance lapses - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>Rashi Peripherals director quits citing governance lapses - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>Rashi Peripherals Limited (NSE:RPTECH) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>Rashi Peripherals Ltd. (RPTECH) Share Price Hits Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>Rashi Peripherals Ltd. Share Price Today - Rashi Peripherals Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>2</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>KOTARISUG.NS</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Kothari Sugars And Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>38.59999847412109</v>
+      </c>
+      <c r="F383" t="n">
+        <v>38.59999847412109</v>
+      </c>
+      <c r="G383" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="H383" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="I383" t="n">
+        <v>39.15999984741211</v>
+      </c>
+      <c r="J383" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="K383" t="n">
+        <v>805383</v>
+      </c>
+      <c r="L383" t="n">
+        <v>-9.98</v>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>Kothari Sugars And Chemicals Share Price Today at Rs 36.35 - Univest</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>Sugar stocks extend gains: What’s driving the rally? - Business Today</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>Kothari Sugars And Chemicals Ltd. (KOTARISUG) Share Price Rises 13.52% Today - Univest</t>
+        </is>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>Kothari Sugars And Chemicals Ltd. Share Price Up 13.34% - Univest</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>Kothari Sugars and Chemicals gets NSE no objection for merger with Kothari Petrochemicals - ChiniMandi</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>3</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>KRONOX.NS</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Limited</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>205.3600006103516</v>
+      </c>
+      <c r="F384" t="n">
+        <v>205.3600006103516</v>
+      </c>
+      <c r="G384" t="n">
+        <v>184.8300018310547</v>
+      </c>
+      <c r="H384" t="n">
+        <v>186.1399993896484</v>
+      </c>
+      <c r="I384" t="n">
+        <v>205.3600006103516</v>
+      </c>
+      <c r="J384" t="n">
+        <v>186.1399993896484</v>
+      </c>
+      <c r="K384" t="n">
+        <v>1026560</v>
+      </c>
+      <c r="L384" t="n">
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Ltd. Share Price News and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Ltd. Share Price News and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>Indo Borax Approves Kronox Lab Stake Purchase; Shares Rise 7.44% - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>Kronox Lab shares hit 20% upper circuit as Indo Borax and Chemicals to acquire 64.26% stake - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>Indo Borax to acquire 64.26% stake in Kronox Lab Sciences in Rs 246-crore deal - Indian Chemical News</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>4</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>RAJMET.NS</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Rajnandini Metal Limited</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>3.509999990463257</v>
+      </c>
+      <c r="F385" t="n">
+        <v>3.650000095367432</v>
+      </c>
+      <c r="G385" t="n">
+        <v>3.130000114440918</v>
+      </c>
+      <c r="H385" t="n">
+        <v>3.200000047683716</v>
+      </c>
+      <c r="I385" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J385" t="n">
+        <v>3.200000047683716</v>
+      </c>
+      <c r="K385" t="n">
+        <v>2145804</v>
+      </c>
+      <c r="L385" t="n">
+        <v>-8.57</v>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>Rajnandini Metal Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>Rajnandini Metal Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr"/>
+      <c r="P385" t="inlineStr"/>
+      <c r="Q385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>5</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS.NS</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>TD Power Systems Limited</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>780.2000122070312</v>
+      </c>
+      <c r="F386" t="n">
+        <v>782.5</v>
+      </c>
+      <c r="G386" t="n">
+        <v>719</v>
+      </c>
+      <c r="H386" t="n">
+        <v>729.4000244140625</v>
+      </c>
+      <c r="I386" t="n">
+        <v>780.0999755859375</v>
+      </c>
+      <c r="J386" t="n">
+        <v>729.4000244140625</v>
+      </c>
+      <c r="K386" t="n">
+        <v>1924050</v>
+      </c>
+      <c r="L386" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>Up 27x in 5 yrs! Why this multibagger smallcap stock showing 50% fall in some trading apps today? - Business Today</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>TD Power Systems: Promoter Group Adjusts Ownership - InvestyWise</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS: Revenue and profit surged year-over-year, with robust EPS and improved margins - TradingView</t>
+        </is>
+      </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>Interested In TD Power Systems' (NSE:TDPOWERSYS) Upcoming ₹1.10 Dividend? You Have One Day Left - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>Brokers Are Upgrading Their Views On TD Power Systems Limited (NSE:TDPOWERSYS) With These New Forecasts - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>6</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>RAIN.NS</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Rain Industries Limited</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>213.8899993896484</v>
+      </c>
+      <c r="F387" t="n">
+        <v>213.8899993896484</v>
+      </c>
+      <c r="G387" t="n">
+        <v>198.3699951171875</v>
+      </c>
+      <c r="H387" t="n">
+        <v>200.4900054931641</v>
+      </c>
+      <c r="I387" t="n">
+        <v>213.6900024414062</v>
+      </c>
+      <c r="J387" t="n">
+        <v>200.4900054931641</v>
+      </c>
+      <c r="K387" t="n">
+        <v>4541018</v>
+      </c>
+      <c r="L387" t="n">
+        <v>-6.18</v>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>"2 Hours 15 Minutes In Traffic": Man Shares How Rain Affected His Commute To Bengaluru Airport - NDTV</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>Rain Industries share price: Petrochemical stock jumps 4% amid soaring crude oil prices on US-Iran war - Livemint</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>Rain Industries share price: Petrochemical stock jumps 4% amid soaring crude oil prices on US-Iran war - Livemint</t>
+        </is>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>RAIN Should I Buy - Intellectia AI</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>Just Three Days Till Rain Industries Limited (NSE:RAIN) Will Be Trading Ex-Dividend - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>7</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>BAJAJHIND.NS</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>24.10000038146973</v>
+      </c>
+      <c r="F388" t="n">
+        <v>24.35000038146973</v>
+      </c>
+      <c r="G388" t="n">
+        <v>22.20000076293945</v>
+      </c>
+      <c r="H388" t="n">
+        <v>22.80999946594238</v>
+      </c>
+      <c r="I388" t="n">
+        <v>24.22999954223633</v>
+      </c>
+      <c r="J388" t="n">
+        <v>22.80999946594238</v>
+      </c>
+      <c r="K388" t="n">
+        <v>113228799</v>
+      </c>
+      <c r="L388" t="n">
+        <v>-5.86</v>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Stock Price Forecast. Should You Buy BAJAJHIND.NS? - StockInvest.us</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>Dwarikesh, Bajaj Hindusthan, other sugar stocks hit 52-week high as govt tightens stockholding limit - TradingView</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>Dwarikesh, Bajaj Hindusthan, other sugar stocks hit 52-week high as govt tightens stockholding limit - TradingView</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>Most Active Equities on August 19, 2026 at 3:00 PM IST - HDFC Sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>8</v>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>ATLANTAELE.NS</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Atlanta Electricals Limited</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>1801</v>
+      </c>
+      <c r="F389" t="n">
+        <v>1812</v>
+      </c>
+      <c r="G389" t="n">
+        <v>1712.599975585938</v>
+      </c>
+      <c r="H389" t="n">
+        <v>1719.599975585938</v>
+      </c>
+      <c r="I389" t="n">
+        <v>1819.5</v>
+      </c>
+      <c r="J389" t="n">
+        <v>1719.599975585938</v>
+      </c>
+      <c r="K389" t="n">
+        <v>120591</v>
+      </c>
+      <c r="L389" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>ATLANTAELE Stock Price and Chart — NSE:ATLANTAELE - TradingView</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>ATLANTAELE Stock Price and Chart — NSE:ATLANTAELE - TradingView</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr"/>
+      <c r="P389" t="inlineStr"/>
+      <c r="Q389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>9</v>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>GSLSU.NS</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Global Surfaces Limited</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>30</v>
+      </c>
+      <c r="F390" t="n">
+        <v>31.47999954223633</v>
+      </c>
+      <c r="G390" t="n">
+        <v>29.82999992370605</v>
+      </c>
+      <c r="H390" t="n">
+        <v>29.82999992370605</v>
+      </c>
+      <c r="I390" t="n">
+        <v>31.39999961853027</v>
+      </c>
+      <c r="J390" t="n">
+        <v>29.82999992370605</v>
+      </c>
+      <c r="K390" t="n">
+        <v>67344</v>
+      </c>
+      <c r="L390" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>Global Surfaces Limited Announces CFO Changes - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>Global Surfaces posts ₹25.4m standalone PAT in Q1FY27; re-submits results - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>Global Surfaces Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>Global Surfaces posts ₹25.4m standalone PAT in Q1FY27; re-submits results - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>Global Surfaces Ltd to host Q1-FY27 earnings call on Aug 11 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>10</v>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>TAKE.NS</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>TAKE Limited</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>19.04999923706055</v>
+      </c>
+      <c r="F391" t="n">
+        <v>19.29000091552734</v>
+      </c>
+      <c r="G391" t="n">
+        <v>18.80999946594238</v>
+      </c>
+      <c r="H391" t="n">
+        <v>18.80999946594238</v>
+      </c>
+      <c r="I391" t="n">
+        <v>19.79000091552734</v>
+      </c>
+      <c r="J391" t="n">
+        <v>18.80999946594238</v>
+      </c>
+      <c r="K391" t="n">
+        <v>136633</v>
+      </c>
+      <c r="L391" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>What Moderna Must Do to Take Its Stock to the Next Level - Barron's</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>Commerce Bank Buys Shares of 14,555 Take-Two Interactive Software, Inc. $TTWO - MarketBeat</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>Umpires Adrian Holdstock and Shaun George take stock of the ground at Durban - Cricinfo</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>Enter Energy Somalia: Rapid Stock-take Assessment Report, March 2026 - ReliefWeb</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>It Won’t Take Much to Burst the Stock Market Bubble - Advisor Perspectives</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>11</v>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>GRADIENTE.NS</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Gradiente Infotainment Limited</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>3.029999971389771</v>
+      </c>
+      <c r="F392" t="n">
+        <v>3.029999971389771</v>
+      </c>
+      <c r="G392" t="n">
+        <v>2.839999914169312</v>
+      </c>
+      <c r="H392" t="n">
+        <v>2.839999914169312</v>
+      </c>
+      <c r="I392" t="n">
+        <v>2.980000019073486</v>
+      </c>
+      <c r="J392" t="n">
+        <v>2.839999914169312</v>
+      </c>
+      <c r="K392" t="n">
+        <v>1970998</v>
+      </c>
+      <c r="L392" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>Gradiente Infotainment Considers Capital Raising Initiatives in Board Meeting - Sahi</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>Gradiente Asian Fashion Tour India - Mumbai Curtain Raiser Marks the 25th Season with Fashion, Glamour and New Talent - Big News Network.com</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>Gradiente Infotainment approves ₹65 Cr capex for micro dramas and music videos - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>Price Band Hitters, August 11, 2026, 3:30 PM IST - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>Major Push for the Orange Economy: Gradiente Infotainment Unveils ₹5,000 Crore Mega Investment Roadmap - The Tribune</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>12</v>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>IIFL.NS</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>IIFL Finance Limited</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>667</v>
+      </c>
+      <c r="F393" t="n">
+        <v>681.0999755859375</v>
+      </c>
+      <c r="G393" t="n">
+        <v>643.5499877929688</v>
+      </c>
+      <c r="H393" t="n">
+        <v>666.25</v>
+      </c>
+      <c r="I393" t="n">
+        <v>696.4000244140625</v>
+      </c>
+      <c r="J393" t="n">
+        <v>666.25</v>
+      </c>
+      <c r="K393" t="n">
+        <v>8284153</v>
+      </c>
+      <c r="L393" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>IIFL Finance shares decline over 7% after home finance arm receives ₹963 crore income tax demand notice; here's why - Upstox</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>IIFL Finance Shares Plunge Nearly 8% on ₹963 Crore Tax Demand - Business Outreach Magazine</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>IFL Finance shares drop 8% as IIFL Home Finance gets Rs 963 crore tax demand - The Economic Times</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>IIFL Finance shares crack 8% after ₹963-crore tax demand for subsidiary - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>IIFL Finance shares fall 4% after subsidiary faces Rs 963 crore tax demand - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>13</v>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>RANASUG.NS</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Rana Sugars Limited</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>15.77999973297119</v>
+      </c>
+      <c r="F394" t="n">
+        <v>16.19000053405762</v>
+      </c>
+      <c r="G394" t="n">
+        <v>15.01000022888184</v>
+      </c>
+      <c r="H394" t="n">
+        <v>15.26000022888184</v>
+      </c>
+      <c r="I394" t="n">
+        <v>15.92000007629395</v>
+      </c>
+      <c r="J394" t="n">
+        <v>15.26000022888184</v>
+      </c>
+      <c r="K394" t="n">
+        <v>889584</v>
+      </c>
+      <c r="L394" t="n">
+        <v>-4.15</v>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>Rana Sugars Share Price rises 8.84%: key stock analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>Rana Sugars Share Price rises 8.84%: key stock analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr"/>
+      <c r="Q394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>14</v>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>DATAPATTNS.NS</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Data Patterns (India) Limited</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>4730</v>
+      </c>
+      <c r="F395" t="n">
+        <v>4768.7001953125</v>
+      </c>
+      <c r="G395" t="n">
+        <v>4500.10009765625</v>
+      </c>
+      <c r="H395" t="n">
+        <v>4542.2998046875</v>
+      </c>
+      <c r="I395" t="n">
+        <v>4736.2001953125</v>
+      </c>
+      <c r="J395" t="n">
+        <v>4542.2998046875</v>
+      </c>
+      <c r="K395" t="n">
+        <v>1198221</v>
+      </c>
+      <c r="L395" t="n">
+        <v>-4.09</v>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>DATAPATTNS Share Price | Data Patterns (India) Ltd Stock Analysis &amp; Recommendation - marketsmojo.com</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>DATAPATTNS Share Price | Data Patterns (India) Ltd Stock Analysis &amp; Recommendation - marketsmojo.com</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr"/>
+      <c r="P395" t="inlineStr"/>
+      <c r="Q395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>15</v>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>UGARSUGAR.NS</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>The Ugar Sugar Works Limited</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>57.79999923706055</v>
+      </c>
+      <c r="F396" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="G396" t="n">
+        <v>54.13999938964844</v>
+      </c>
+      <c r="H396" t="n">
+        <v>55.65999984741211</v>
+      </c>
+      <c r="I396" t="n">
+        <v>58.0099983215332</v>
+      </c>
+      <c r="J396" t="n">
+        <v>55.65999984741211</v>
+      </c>
+      <c r="K396" t="n">
+        <v>1072021</v>
+      </c>
+      <c r="L396" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>UGARSUGAR Share Price Rise: Fundamentals and Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>UGARSUGAR Share Price Rise: Fundamentals and Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>The Ugar Sugar Works Share Price Today: 9.09% Price Rise - Univest</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>The Ugar Sugar Works Ltd. Share Price Today: Key Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>The Ugar Sugar Works Ltd. Share Price Near 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>16</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>WHEELS.NS</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Wheels India Limited</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>1565</v>
+      </c>
+      <c r="F397" t="n">
+        <v>1579.599975585938</v>
+      </c>
+      <c r="G397" t="n">
+        <v>1489.099975585938</v>
+      </c>
+      <c r="H397" t="n">
+        <v>1499.300048828125</v>
+      </c>
+      <c r="I397" t="n">
+        <v>1561.400024414062</v>
+      </c>
+      <c r="J397" t="n">
+        <v>1499.300048828125</v>
+      </c>
+      <c r="K397" t="n">
+        <v>137084</v>
+      </c>
+      <c r="L397" t="n">
+        <v>-3.98</v>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>Wheels India Approves Issuing 1,269,391 Equity Shares At ₹1,418 To Raise ₹180 Crores - Sahi</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>Wheels Up Experience Stock Price Forecast. Should You Buy UP? - StockInvest.us</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>TSF Investments Approves Subscription To Preferential Issue Of Wheels India Equity Shares - TradingView</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>Wheels India board approves ₹180 crore preferential issue at ₹1,418 per share - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>Stock Alert: Bharat Electronics, Godfrey Phillips India, Wheels India, Tata Chemicals - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>17</v>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>ALICON.NS</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Alicon Castalloy Limited</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>727</v>
+      </c>
+      <c r="F398" t="n">
+        <v>727.25</v>
+      </c>
+      <c r="G398" t="n">
+        <v>690</v>
+      </c>
+      <c r="H398" t="n">
+        <v>697.7999877929688</v>
+      </c>
+      <c r="I398" t="n">
+        <v>726.5</v>
+      </c>
+      <c r="J398" t="n">
+        <v>697.7999877929688</v>
+      </c>
+      <c r="K398" t="n">
+        <v>57256</v>
+      </c>
+      <c r="L398" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>Alicon Castalloy declares ₹3 per share final dividend for FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>₹8,094 Cr Order Book: Smallcap Stock With BMW, Volkswagen and Bosch as Clients to Add to Your Watchlist - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>Alicon Castalloy Ltd. Share Price: Major 8.55% Increase - Univest</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>Alicon Castalloy Q1 Results: Earnings call scheduled for Aug 14 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>Alicon Castalloy approves ₹1,255 mn plant for castings - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>18</v>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>GOCOLORS.NS</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Go Fashion (India) Limited</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>354.7999877929688</v>
+      </c>
+      <c r="F399" t="n">
+        <v>354.7999877929688</v>
+      </c>
+      <c r="G399" t="n">
+        <v>337.1000061035156</v>
+      </c>
+      <c r="H399" t="n">
+        <v>340.25</v>
+      </c>
+      <c r="I399" t="n">
+        <v>353.2999877929688</v>
+      </c>
+      <c r="J399" t="n">
+        <v>340.25</v>
+      </c>
+      <c r="K399" t="n">
+        <v>197680</v>
+      </c>
+      <c r="L399" t="n">
+        <v>-3.69</v>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>GOCOLORS Share Price Today - Go Fashion (India) Ltd. Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>GOCOLORS Share Price Today - Go Fashion (India) Ltd. Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>Go Fashion (India) Limited Just Missed EPS By 18%: Here's What Analysts Think Will Happen Next - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>Go Fashion (India) Ltd sees SSSG turn positive in Q1 FY27 as revenue holds steady - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>19</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>REDINGTON.NS</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Redington Limited</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>365.8999938964844</v>
+      </c>
+      <c r="F400" t="n">
+        <v>366.5</v>
+      </c>
+      <c r="G400" t="n">
+        <v>350.1499938964844</v>
+      </c>
+      <c r="H400" t="n">
+        <v>352.6499938964844</v>
+      </c>
+      <c r="I400" t="n">
+        <v>365.1000061035156</v>
+      </c>
+      <c r="J400" t="n">
+        <v>352.6499938964844</v>
+      </c>
+      <c r="K400" t="n">
+        <v>4485539</v>
+      </c>
+      <c r="L400" t="n">
+        <v>-3.41</v>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>Redington Share Price hits fresh 52-week high at Rs 364 - Univest</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>Redington Share Price hits fresh 52-week high at Rs 364 - Univest</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>Redington shares jump 11% to fresh record high, rally 29% in five sessions; key triggers explained - Upstox</t>
+        </is>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>Redington shares rise up to 15% as Q1 net profit nearly doubles to Rs 453 crore - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>Redington shares rally 15% after Q1 profit surges 77%; revenue rises 35% YoY - The Economic Times</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30:30 IST</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>20</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>SOMICONVEY.NS</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Somi Conveyor Beltings Limited</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>98.62000274658203</v>
+      </c>
+      <c r="F401" t="n">
+        <v>99.19999694824219</v>
+      </c>
+      <c r="G401" t="n">
+        <v>93.19999694824219</v>
+      </c>
+      <c r="H401" t="n">
+        <v>94.05999755859375</v>
+      </c>
+      <c r="I401" t="n">
+        <v>97.36000061035156</v>
+      </c>
+      <c r="J401" t="n">
+        <v>94.05999755859375</v>
+      </c>
+      <c r="K401" t="n">
+        <v>27366</v>
+      </c>
+      <c r="L401" t="n">
+        <v>-3.39</v>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>Somi Conveyor Beltings Ltd. Share Price Up 15.77% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>Somi Conveyor Beltings Ltd. Share Price Up 15.77% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>Somi Conveyor Beltings Ltd. Share Price Today Up 19.97% - Univest</t>
+        </is>
+      </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>Somi Conveyor Beltings Ltd. Share Price Near 52-Week Low - Univest</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q401"/>
+  <dimension ref="A1:Q421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23997,9 +23997,6 @@
           <t>Gujarat Industries Power Standalone Q1 Net Profit Rises to ₹160 Crore on ₹500 Crore Revenue - Sahi</t>
         </is>
       </c>
-      <c r="O387" t="inlineStr"/>
-      <c r="P387" t="inlineStr"/>
-      <c r="Q387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -24133,7 +24130,6 @@
           <t>Shree Pushkar Chemicals &amp; Fertilisers Adds 10 MW Solar Capacity in Maharashtra - marketscreener.com</t>
         </is>
       </c>
-      <c r="Q389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -24198,7 +24194,6 @@
           <t>Tourism Finance Corporation Of India Ltd. Share Price Near - Univest</t>
         </is>
       </c>
-      <c r="Q390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -24263,7 +24258,6 @@
           <t>Nectar Lifesciences Publishes Q1 FY2026 Results in Press and Online - TipRanks</t>
         </is>
       </c>
-      <c r="Q391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -24318,9 +24312,6 @@
           <t>Balaji Amines Share Price news: Rs 2,210.70 and sector view - Univest</t>
         </is>
       </c>
-      <c r="O392" t="inlineStr"/>
-      <c r="P392" t="inlineStr"/>
-      <c r="Q392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -24661,7 +24652,6 @@
           <t>Delta Corp Publishes AGM, Book Closure and E-Voting Notice - TipRanks</t>
         </is>
       </c>
-      <c r="Q397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -24936,6 +24926,1374 @@
       <c r="Q401" t="inlineStr">
         <is>
           <t>Inspire (INSP) Reported Quarter: The Bottom-Line Figure Outpaces Its Comparison at the Close; Post-Earnings Trading: The Stock Ends Up 0.09% for the Current Session - CFO Commentary Report - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>1</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>DTIL.NS</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Dhunseri Tea &amp; Industries Limited</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>172</v>
+      </c>
+      <c r="F402" t="n">
+        <v>183.2200012207031</v>
+      </c>
+      <c r="G402" t="n">
+        <v>165.1199951171875</v>
+      </c>
+      <c r="H402" t="n">
+        <v>183.2200012207031</v>
+      </c>
+      <c r="I402" t="n">
+        <v>152.6900024414062</v>
+      </c>
+      <c r="J402" t="n">
+        <v>183.2200012207031</v>
+      </c>
+      <c r="K402" t="n">
+        <v>437530</v>
+      </c>
+      <c r="L402" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>A gene-editing treatment for Duchenne muscular dystrophy doses its first patient - Stock Titan</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>Precision BioSciences (DTIL) draws 1.1M-share Weinstein stake - Stock Titan</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>Precision (DTIL) Momentum: Rises 1.61% to $8.86 in the Current Update; Chart View: the $8.42 to $9.30 Range Remains in Focus for the Current Session - Retracement Entry - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>Precision BioSciences (DTIL) Stock Faces Dilution Risk As Revenue Fades - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>Precision BioSciences: Promising HBV Editing Evidence (NASDAQ:DTIL) - Seeking Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>2</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>TVSSRICHAK.NS</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>TVS Srichakra Limited</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>4792.89990234375</v>
+      </c>
+      <c r="F403" t="n">
+        <v>5322.60009765625</v>
+      </c>
+      <c r="G403" t="n">
+        <v>4792.89990234375</v>
+      </c>
+      <c r="H403" t="n">
+        <v>5313.2001953125</v>
+      </c>
+      <c r="I403" t="n">
+        <v>4812</v>
+      </c>
+      <c r="J403" t="n">
+        <v>5313.2001953125</v>
+      </c>
+      <c r="K403" t="n">
+        <v>84858</v>
+      </c>
+      <c r="L403" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>TVS Srichakra Ltd. Share Price Today: Market Cap Context - Univest</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>TVS Srichakra Ltd. Share Price Today: Market Cap Context - Univest</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>TVS Srichakra Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>TVS Srichakra share price jumps16% on robust Q1 earnings performance; profit jumps 165% - Upstox</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>3</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>ARIES.NS</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Aries Agro Limited</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>446.6499938964844</v>
+      </c>
+      <c r="F404" t="n">
+        <v>512.5</v>
+      </c>
+      <c r="G404" t="n">
+        <v>445.1000061035156</v>
+      </c>
+      <c r="H404" t="n">
+        <v>491</v>
+      </c>
+      <c r="I404" t="n">
+        <v>446.75</v>
+      </c>
+      <c r="J404" t="n">
+        <v>491</v>
+      </c>
+      <c r="K404" t="n">
+        <v>508690</v>
+      </c>
+      <c r="L404" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>M&amp;S Shares Slip 1.2% as Aries Capsule Tests a 7.7% Fashion Sales Gap - TechStock²</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>M&amp;S Shares Slip 1.2% as Aries Capsule Tests a 7.7% Fashion Sales Gap - TechStock²</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>Aries Agro Ltd. Share Price Gain: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>Salesforce (CRM) Stock Analysis Today - Gotrade</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>Daily Nadi Horoscope for Aries (7th August 2026): Moon–Mars Energy May Bring Profit, but Family Peace Nee - The Times of India</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>4</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>MEIL.NS</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Mangal Electrical Industries Limited</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>280.0499877929688</v>
+      </c>
+      <c r="F405" t="n">
+        <v>304.9500122070312</v>
+      </c>
+      <c r="G405" t="n">
+        <v>280.0499877929688</v>
+      </c>
+      <c r="H405" t="n">
+        <v>298.2999877929688</v>
+      </c>
+      <c r="I405" t="n">
+        <v>276.2000122070312</v>
+      </c>
+      <c r="J405" t="n">
+        <v>298.2999877929688</v>
+      </c>
+      <c r="K405" t="n">
+        <v>538891</v>
+      </c>
+      <c r="L405" t="n">
+        <v>8</v>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>Why Investors Shouldn't Be Surprised By Mangal Electrical Industries Limited's (NSE:MEIL) 30% Share Price Plunge - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>Mangal Electrical Industries Limited (MEIL.NS) Mar 2026 Earnings: Moderate Revenue Growth with Higher EPS - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>MEIL Stock Price and Chart — NSE:MEIL - TradingView</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>MEIL Holdings Limited Releases Share Encumbrance on Olectra Greentech Following Loan Closure - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>Mangal Electrical Industries (MEIL.NS) Holds Near Support After Minor Dip - Price Surge Stocks - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>5</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>WABAG.NS</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>VA Tech Wabag Limited</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>2025.699951171875</v>
+      </c>
+      <c r="F406" t="n">
+        <v>2144</v>
+      </c>
+      <c r="G406" t="n">
+        <v>2016.099975585938</v>
+      </c>
+      <c r="H406" t="n">
+        <v>2142</v>
+      </c>
+      <c r="I406" t="n">
+        <v>2021.5</v>
+      </c>
+      <c r="J406" t="n">
+        <v>2142</v>
+      </c>
+      <c r="K406" t="n">
+        <v>854170</v>
+      </c>
+      <c r="L406" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>Va Tech Wabag Denies Rs 600 Crore Saudi Arabia Contract, Awaits Kuwait Award Letter - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>Va Tech Wabag Denies Rs 600 Crore Saudi Arabia Contract, Awaits Kuwait Award Letter - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>VA Tech Wabag (NSEI:WABAG) Stock Gets Fair Value Boost On Higher P E View - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>Rekha Jhunjhunwala stock: DIIs triple stake in two years; Systematix lists out triggers - Business Today</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>Rekha Jhunjhunwala portfolio stock VA Tech Wabag jumps 5%; Axis Securities raises target price after Q1 results - Livemint</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>6</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>RATNAVEER.NS</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Ratnaveer Precision Engineering Limited</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>265.0299987792969</v>
+      </c>
+      <c r="F407" t="n">
+        <v>279.7999877929688</v>
+      </c>
+      <c r="G407" t="n">
+        <v>264</v>
+      </c>
+      <c r="H407" t="n">
+        <v>278.989990234375</v>
+      </c>
+      <c r="I407" t="n">
+        <v>263.4299926757812</v>
+      </c>
+      <c r="J407" t="n">
+        <v>278.989990234375</v>
+      </c>
+      <c r="K407" t="n">
+        <v>3064038</v>
+      </c>
+      <c r="L407" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>Ratnaveer Precision Board Approves 1.25 Crore Shares Rights Issue At ₹264 Totaling ₹330 Crore - Sahi</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>Ratnaveer Approves ₹330 Crore Rights Issue at ₹264; Shares Touch All-Time High of ₹282.50 - ACCESS Newswire</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>Ratnaveer Approves Rs 330 Crore Rights Issue at Rs 264; Shares Touch All-Time High of Rs 282.50 - Deccan Chronicle</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>80% rally in YTD! Ratnaveer Precision Engineering declares rights issue worth ₹330 crore - Livemint</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>Ratnaveer targets ₹2,500 crore revenue with CCL project - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>7</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>QUESS.NS</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Quess Corp Limited</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>349.5</v>
+      </c>
+      <c r="F408" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="G408" t="n">
+        <v>348</v>
+      </c>
+      <c r="H408" t="n">
+        <v>365.5499877929688</v>
+      </c>
+      <c r="I408" t="n">
+        <v>347</v>
+      </c>
+      <c r="J408" t="n">
+        <v>365.5499877929688</v>
+      </c>
+      <c r="K408" t="n">
+        <v>4331313</v>
+      </c>
+      <c r="L408" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>Only Three Days Left To Cash In On Quess' (NSE:QUESS) Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>Stocks to buy for short term: Grasim, Quess Corp among 6 stocks experts recommend buying today for next 1-2 weeks - Livemint</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>Quess Corp Ltd. Share Price With Price and Market Cap View - Univest</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>Quess Corp Q1 net profit jumps 61% on professional staffing, overseas growth - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>Stocks to buy for short term: Grasim, Quess Corp among 6 stocks experts recommend buying today for next 1-2 weeks - Livemint</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>8</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>ISFT.NS</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Intrasoft Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="F409" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="G409" t="n">
+        <v>91.44000244140625</v>
+      </c>
+      <c r="H409" t="n">
+        <v>96</v>
+      </c>
+      <c r="I409" t="n">
+        <v>91.44000244140625</v>
+      </c>
+      <c r="J409" t="n">
+        <v>96</v>
+      </c>
+      <c r="K409" t="n">
+        <v>82738</v>
+      </c>
+      <c r="L409" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>ICEsoft Technologies Canada Corp (CN: ISFT) Share Price, ISFT Stock News, ISFT Share Price &amp; Updates - Kalkine</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>ICEsoft Releases Q2 2026 Financial Results - TradingView</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>Intrasoft Technologies Ltd. Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>IntraSoft Technologies Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>ICEsoft Releases Q2 2026 Financial Results - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>9</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>HINDZINC.NS</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc Limited</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>605</v>
+      </c>
+      <c r="F410" t="n">
+        <v>623.75</v>
+      </c>
+      <c r="G410" t="n">
+        <v>600.1500244140625</v>
+      </c>
+      <c r="H410" t="n">
+        <v>621.4500122070312</v>
+      </c>
+      <c r="I410" t="n">
+        <v>592.5999755859375</v>
+      </c>
+      <c r="J410" t="n">
+        <v>621.4500122070312</v>
+      </c>
+      <c r="K410" t="n">
+        <v>11140806</v>
+      </c>
+      <c r="L410" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc Share Price - Live NSE: HINDZINC Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc Share Price Today: ₹588, the Market's Biggest Faller - The Eastern Herald</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc Adds Independent Director Appointed by Ministry of Mines - The Globe and Mail</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc Share Price Today, August 24, 2026: Closes at ₹604 - The Eastern Herald</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc Share Price Today: ₹588, the Market's Biggest Faller - The Eastern Herald</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>10</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>OLAELEC.NS</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Ola Electric Mobility Limited</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>36.68999862670898</v>
+      </c>
+      <c r="F411" t="n">
+        <v>38.68000030517578</v>
+      </c>
+      <c r="G411" t="n">
+        <v>36.63000106811523</v>
+      </c>
+      <c r="H411" t="n">
+        <v>37.90000152587891</v>
+      </c>
+      <c r="I411" t="n">
+        <v>36.20000076293945</v>
+      </c>
+      <c r="J411" t="n">
+        <v>37.90000152587891</v>
+      </c>
+      <c r="K411" t="n">
+        <v>65587786</v>
+      </c>
+      <c r="L411" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>Ola Electric Publishes Q1 FY2026 Unaudited Results in Newspapers - The Globe and Mail</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>Ola Electric Mobility Limited (NSE:OLAELEC) Analysts Are Cutting Their Estimates: Here's What You Need To Know - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>Ola Electric Mobility Limited (NSE:OLAELEC) Analysts Are Cutting Their Estimates: Here's What You Need To Know - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr"/>
+      <c r="Q411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>11</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>SURYODAY.NS</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Suryoday Small Finance Bank Limited</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>151.4900054931641</v>
+      </c>
+      <c r="F412" t="n">
+        <v>160.8800048828125</v>
+      </c>
+      <c r="G412" t="n">
+        <v>151.4900054931641</v>
+      </c>
+      <c r="H412" t="n">
+        <v>157.8000030517578</v>
+      </c>
+      <c r="I412" t="n">
+        <v>151.0200042724609</v>
+      </c>
+      <c r="J412" t="n">
+        <v>157.8000030517578</v>
+      </c>
+      <c r="K412" t="n">
+        <v>449439</v>
+      </c>
+      <c r="L412" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>Despite Suryoday Small Finance Bank's Pullback, Insiders Still Gained ₹1.9m - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>Suryoday Small Finance Bank Q4 FY26: Gross Advances At ₹13,201 Crore, Up 29% YoY - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>Suryoday Small Finance Bank Q4 FY26: Gross Advances At ₹13,201 Crore, Up 29% YoY - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>Suryoday Small Finance Bank Share Price Falls 9.5% Today - Univest</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>Suryoday Small Finance Bank vs Utkarsh Small Finance Bank: Which Stock Should You Track - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>12</v>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>PARAS.NS</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Paras Defence and Space Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>1450.099975585938</v>
+      </c>
+      <c r="F413" t="n">
+        <v>1510</v>
+      </c>
+      <c r="G413" t="n">
+        <v>1435</v>
+      </c>
+      <c r="H413" t="n">
+        <v>1508.599975585938</v>
+      </c>
+      <c r="I413" t="n">
+        <v>1445.199951171875</v>
+      </c>
+      <c r="J413" t="n">
+        <v>1508.599975585938</v>
+      </c>
+      <c r="K413" t="n">
+        <v>698453</v>
+      </c>
+      <c r="L413" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>Bonus, dividends &amp; stock splits: Paras Defence, NBCC, MCX among 67 stocks turning ex-record date this week - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>Stock Market Live | Coal India, Tejas Network, Tata Steel, Paras Defence Share में क्या करें? Anas Sarwar (iWHytEj8x1) - Mshale</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>MCX, Honasa Consumer, Paras Defence, other upcoming dividend stocks, bonus issues in focus this week; check list - Upstox</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>Paras Defence, Zen Tech, other defence shares rise up to 8% as MoD notifies sixth Positive Indigenisation... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>Corporate Actions This Week: P&amp;G Health, Gillette India, PFC, TD Power, Senco Gold, Paras Defence &amp; More - NDTV Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>13</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>DCBBANK.NS</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>DCB Bank Limited</t>
+        </is>
+      </c>
+      <c r="E414" t="n">
+        <v>210</v>
+      </c>
+      <c r="F414" t="n">
+        <v>216.6699981689453</v>
+      </c>
+      <c r="G414" t="n">
+        <v>209.2400054931641</v>
+      </c>
+      <c r="H414" t="n">
+        <v>216.3000030517578</v>
+      </c>
+      <c r="I414" t="n">
+        <v>207.3699951171875</v>
+      </c>
+      <c r="J414" t="n">
+        <v>216.3000030517578</v>
+      </c>
+      <c r="K414" t="n">
+        <v>4060703</v>
+      </c>
+      <c r="L414" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>DCB Bank Ltd. Share Price: Price, Valuation, Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>DCB Bank Ltd. Share Price: Price, Valuation, Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>Here's Why We Think DCB Bank (NSE:DCBBANK) Might Deserve Your Attention Today - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>DCB Bank Share Price at 52-week high: price, fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>Bank Stock to Buy Now for an Upside of 54%; Recommended by Anand Rathi - Trade Brains</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>14</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>IDBI.NS</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>IDBI Bank Limited</t>
+        </is>
+      </c>
+      <c r="E415" t="n">
+        <v>87.34999847412109</v>
+      </c>
+      <c r="F415" t="n">
+        <v>92.69999694824219</v>
+      </c>
+      <c r="G415" t="n">
+        <v>87.34999847412109</v>
+      </c>
+      <c r="H415" t="n">
+        <v>92.08999633789062</v>
+      </c>
+      <c r="I415" t="n">
+        <v>88.30999755859375</v>
+      </c>
+      <c r="J415" t="n">
+        <v>92.08999633789062</v>
+      </c>
+      <c r="K415" t="n">
+        <v>20477384</v>
+      </c>
+      <c r="L415" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>IDBI Bank Share Price Jumps 10% In Trade: What's Driving The Rally? - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>IDBI Bank Shares Surge Over 10%! Fairfax Deal May Be Near, Government, LIC Stake Sale &amp; RBI Challenges - Thekanal</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>LIC stake sale in IDBI Bank: Officers’ body seeks IRDAI intervention - BusinessLine</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>Centre may clear Fairfax bid for controlling stake in IDBI Bank within a week: Report - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>IDBI Bank shares rise 2% as lender clarifies on surge in trading volumes; details here - Business Today</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>15</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>OLECTRA.NS</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Olectra Greentech Limited</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>1294.900024414062</v>
+      </c>
+      <c r="F416" t="n">
+        <v>1359.199951171875</v>
+      </c>
+      <c r="G416" t="n">
+        <v>1294.900024414062</v>
+      </c>
+      <c r="H416" t="n">
+        <v>1346.800048828125</v>
+      </c>
+      <c r="I416" t="n">
+        <v>1291.800048828125</v>
+      </c>
+      <c r="J416" t="n">
+        <v>1346.800048828125</v>
+      </c>
+      <c r="K416" t="n">
+        <v>562972</v>
+      </c>
+      <c r="L416" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>Olectra Greentech Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>Olectra Greentech Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>Olectra rally 7% on order win from BEST - Upstox</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>Olectra Greentech Q1FY27 revenue up 66% YoY to ₹575.5 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>Olectra Greentech Shares Decline Nearly 4% After Q1 Results - NDTV Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>16</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>CYIENT.NS</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Cyient Limited</t>
+        </is>
+      </c>
+      <c r="E417" t="n">
+        <v>994</v>
+      </c>
+      <c r="F417" t="n">
+        <v>1054.849975585938</v>
+      </c>
+      <c r="G417" t="n">
+        <v>984.5</v>
+      </c>
+      <c r="H417" t="n">
+        <v>1020.25</v>
+      </c>
+      <c r="I417" t="n">
+        <v>979.0499877929688</v>
+      </c>
+      <c r="J417" t="n">
+        <v>1020.25</v>
+      </c>
+      <c r="K417" t="n">
+        <v>7154604</v>
+      </c>
+      <c r="L417" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>Cyient shares jump 4% after investor day; JPMorgan sees ₹1,050 target on double-digit growth outlook - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>Cyient shares rocket 8% after investor day, but brokerages see up to 24% downside. Here’s why - The Economic Times</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>Cyient shares soar 8% as CCI approves acquisition of California-based Tao Digital Solutions - Upstox</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>Cyient Stock: JPMorgan Sees Transformation, Morgan Stanley Waits for Execution - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>Cyient shares surge 8%: Targets by MOFSL, Antique, Choice, Nuvama post Investor Day - Business Today</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>17</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>AEROFLEX.NS</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Aeroflex Industries Limited</t>
+        </is>
+      </c>
+      <c r="E418" t="n">
+        <v>496</v>
+      </c>
+      <c r="F418" t="n">
+        <v>517.5999755859375</v>
+      </c>
+      <c r="G418" t="n">
+        <v>492</v>
+      </c>
+      <c r="H418" t="n">
+        <v>516.5</v>
+      </c>
+      <c r="I418" t="n">
+        <v>495.75</v>
+      </c>
+      <c r="J418" t="n">
+        <v>516.5</v>
+      </c>
+      <c r="K418" t="n">
+        <v>965740</v>
+      </c>
+      <c r="L418" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>Aeroflex Industries Ltd Dividend History, Yield &amp; Record Date - INDmoney</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>Aeroflex Neu Allots ₹3 Cr Stake in Stilonn Valves - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>Aeroflex Neu Allots ₹3 Cr Stake in Stilonn Valves - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>Market Trading Guide: Aeroflex Industries among 2 stock recommendations for Wednesday - The Economic Times</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>Aeroflex Ind. Consolidated June 2026 Net Sales at Rs 145.38 crore, up 72.38% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>18</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>ALEMBICLTD.NS</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Alembic Limited</t>
+        </is>
+      </c>
+      <c r="E419" t="n">
+        <v>95.86000061035156</v>
+      </c>
+      <c r="F419" t="n">
+        <v>98.62999725341797</v>
+      </c>
+      <c r="G419" t="n">
+        <v>95.02999877929688</v>
+      </c>
+      <c r="H419" t="n">
+        <v>98.62999725341797</v>
+      </c>
+      <c r="I419" t="n">
+        <v>94.66000366210938</v>
+      </c>
+      <c r="J419" t="n">
+        <v>98.62999725341797</v>
+      </c>
+      <c r="K419" t="n">
+        <v>593212</v>
+      </c>
+      <c r="L419" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>Alembic fixes Aug 4 record date for FY26 dividend - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>Beta (BBNX) Earnings Update: EPS Clears the Reported Estimate in Latest Trading; After Earnings: Shares Finish 2.21% Lower on the Day - Profitability Analysis - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>Alembic Limited reports 11.8% net profit decline in Q1FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>Alembic Limited shareholders approve FY26 results, dividend with near-unanimous support - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>Beta (BBNX) Earnings Update: EPS Clears the Reported Estimate in Latest Trading; After Earnings: Shares Finish 2.21% Lower on the Day - Profitability Analysis - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>19</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>TEMBO.NS</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Tembo Global Industries Limited</t>
+        </is>
+      </c>
+      <c r="E420" t="n">
+        <v>56.34999847412109</v>
+      </c>
+      <c r="F420" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="G420" t="n">
+        <v>56</v>
+      </c>
+      <c r="H420" t="n">
+        <v>58.65000152587891</v>
+      </c>
+      <c r="I420" t="n">
+        <v>56.29999923706055</v>
+      </c>
+      <c r="J420" t="n">
+        <v>58.65000152587891</v>
+      </c>
+      <c r="K420" t="n">
+        <v>929246</v>
+      </c>
+      <c r="L420" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>2 Companies Declaring Stock Splits in August 2026 - Equitymaster</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>Tembo Global Industries forms strategic JV for indigenous UAV manufacturing - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>Tembo Global Industries forms strategic JV for indigenous UAV manufacturing - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>Tembo Global Industries Share Price Outlook: Where It Could Be in 3 Years - Univest</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>Lake Victoria’s Tembo holds 600K oz. gold near Barrick - The Northern Miner</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>20</v>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>MAPMYINDIA.NS</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>C.E. Info Systems Limited</t>
+        </is>
+      </c>
+      <c r="E421" t="n">
+        <v>970</v>
+      </c>
+      <c r="F421" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G421" t="n">
+        <v>964.2999877929688</v>
+      </c>
+      <c r="H421" t="n">
+        <v>1004</v>
+      </c>
+      <c r="I421" t="n">
+        <v>964.2999877929688</v>
+      </c>
+      <c r="J421" t="n">
+        <v>1004</v>
+      </c>
+      <c r="K421" t="n">
+        <v>513721</v>
+      </c>
+      <c r="L421" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>MapMyIndia shares drop 8% despite strong Q1 earnings; PAT jumps 8% YoY - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>C.E. Info Systems Ltd (MAPMYINDIA) Share Price - Business Today</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>MapmyIndia Q1 Results 2027: PAT Rises 6%, Shares Open 6% Lower - Sahi</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>C.E. Info Systems Ltd (MAPMYINDIA) Share Price - Business Today</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>Results: C. E. Info Systems Limited Beat Earnings Expectations And Analysts Now Have New Forecasts - simplywall.st</t>
         </is>
       </c>
     </row>
@@ -24950,7 +26308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q401"/>
+  <dimension ref="A1:Q421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48084,9 +49442,6 @@
           <t>Rajnandini Metal Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
-      <c r="O385" t="inlineStr"/>
-      <c r="P385" t="inlineStr"/>
-      <c r="Q385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -48348,9 +49703,6 @@
           <t>ATLANTAELE Stock Price and Chart — NSE:ATLANTAELE - TradingView</t>
         </is>
       </c>
-      <c r="O389" t="inlineStr"/>
-      <c r="P389" t="inlineStr"/>
-      <c r="Q389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -48686,8 +50038,6 @@
           <t>Rana Sugars Ltd. Share Price Up 9.66%: Price, Valuation - Univest</t>
         </is>
       </c>
-      <c r="P394" t="inlineStr"/>
-      <c r="Q394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -48742,9 +50092,6 @@
           <t>DATAPATTNS Share Price | Data Patterns (India) Ltd Stock Analysis &amp; Recommendation - marketsmojo.com</t>
         </is>
       </c>
-      <c r="O395" t="inlineStr"/>
-      <c r="P395" t="inlineStr"/>
-      <c r="Q395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -49016,7 +50363,6 @@
           <t>Go Fashion (India) Ltd sees SSSG turn positive in Q1 FY27 as revenue holds steady - scanx.trade</t>
         </is>
       </c>
-      <c r="Q399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -49150,7 +50496,1374 @@
           <t>Somi Conveyor Beltings Ltd. Share Price Near 52-Week Low - Univest</t>
         </is>
       </c>
-      <c r="Q401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>1</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>SHAH.NS</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Shah Metacorp Limited</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>3.299999952316284</v>
+      </c>
+      <c r="F402" t="n">
+        <v>3.299999952316284</v>
+      </c>
+      <c r="G402" t="n">
+        <v>2.559999942779541</v>
+      </c>
+      <c r="H402" t="n">
+        <v>2.559999942779541</v>
+      </c>
+      <c r="I402" t="n">
+        <v>3.200000047683716</v>
+      </c>
+      <c r="J402" t="n">
+        <v>2.559999942779541</v>
+      </c>
+      <c r="K402" t="n">
+        <v>28315180</v>
+      </c>
+      <c r="L402" t="n">
+        <v>-20</v>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>'Not Too High, Not Too Low': Nilesh Shah's Rule For Stock Picking; Check His Sectoral Picks - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>Welspun Corp shares fall as CEO Vipul Shah among likely sellers in Rs 1,433 cr block deals - Business Today</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>Precigen COO Rutul Shah sells $375,000 in shares - Investing.com India</t>
+        </is>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>Welspun Corp shares fall as CEO Vipul Shah among likely sellers in Rs 1,433 cr block deals - Business Today</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>What Is Changing At Shah Rukh Khan's Rs 300-Crore Mannat? Anand Pandit Shares Renovation Details - NDTV</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>2</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>KOHINOOR.NS</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Limited</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="F403" t="n">
+        <v>36.29999923706055</v>
+      </c>
+      <c r="G403" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="H403" t="n">
+        <v>33.59000015258789</v>
+      </c>
+      <c r="I403" t="n">
+        <v>35.77999877929688</v>
+      </c>
+      <c r="J403" t="n">
+        <v>33.59000015258789</v>
+      </c>
+      <c r="K403" t="n">
+        <v>228119</v>
+      </c>
+      <c r="L403" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>Enterprise value to revenue forward of Kohinoor Chemical Company (Bangladesh) PLC – DSEBD:KOHINOOR - TradingView</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>Enterprise value to revenue forward of Kohinoor Chemical Company (Bangladesh) PLC – DSEBD:KOHINOOR - TradingView</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Ltd. Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>Kohinoor Textile to install 48MW battery storage amid 9MW solar expansion - Business Recorder</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>3</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>TAKE.NS</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>TAKE Limited</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>17.8700008392334</v>
+      </c>
+      <c r="F404" t="n">
+        <v>17.8700008392334</v>
+      </c>
+      <c r="G404" t="n">
+        <v>17.8700008392334</v>
+      </c>
+      <c r="H404" t="n">
+        <v>17.8700008392334</v>
+      </c>
+      <c r="I404" t="n">
+        <v>18.80999946594238</v>
+      </c>
+      <c r="J404" t="n">
+        <v>17.8700008392334</v>
+      </c>
+      <c r="K404" t="n">
+        <v>63703</v>
+      </c>
+      <c r="L404" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>Take-Two Stock Stalled Before GTA VI. The Setup Still Points Up - TIKR.com</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>Take-Two Stock Stalled Before GTA VI. The Setup Still Points Up - TIKR.com</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>Umpires Adrian Holdstock and Shaun George take stock of the ground at Durban - Cricinfo</t>
+        </is>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>What Moderna Must Do to Take Its Stock to the Next Level - Barron's</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>Microsoft Just Ripped 28% in a Month. What Would It Take to Get MSFT Stock Up to $600? - 24/7 Wall St.</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>4</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>KANPRPLA.NS</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Kanpur Plastipack Limited</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>282.9500122070312</v>
+      </c>
+      <c r="F405" t="n">
+        <v>283.010009765625</v>
+      </c>
+      <c r="G405" t="n">
+        <v>264</v>
+      </c>
+      <c r="H405" t="n">
+        <v>264.3599853515625</v>
+      </c>
+      <c r="I405" t="n">
+        <v>277.1900024414062</v>
+      </c>
+      <c r="J405" t="n">
+        <v>264.3599853515625</v>
+      </c>
+      <c r="K405" t="n">
+        <v>26950</v>
+      </c>
+      <c r="L405" t="n">
+        <v>-4.63</v>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>Kanpur Plastipack Share Price Today With Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>Kanpur Plastipack surges 63% after Fair Value identified opportunity - Investing.com India</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>Kanpur Plastipack to allot equity shares on warrant conversion - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>Kanpur Plastipack surges 63% after Fair Value identified opportunity - Investing.com India</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>Kanpur Plastipack shareholders approve all 7 AGM resolutions - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>5</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>GROWW.NS</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Billionbrains Garage Ventures Limited</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>199.9799957275391</v>
+      </c>
+      <c r="F406" t="n">
+        <v>199.9799957275391</v>
+      </c>
+      <c r="G406" t="n">
+        <v>195.1000061035156</v>
+      </c>
+      <c r="H406" t="n">
+        <v>196</v>
+      </c>
+      <c r="I406" t="n">
+        <v>203.0099945068359</v>
+      </c>
+      <c r="J406" t="n">
+        <v>196</v>
+      </c>
+      <c r="K406" t="n">
+        <v>169757187</v>
+      </c>
+      <c r="L406" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>Groww stock falls 3% as 2.1% equity changes hands in Rs 2,500-crore block deal; Ribbit Capital likely... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>Five block deals worth over ₹6,000 crore change hands today — Check details here - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>₹2,500 crore Groww block deal knocks shares down 3% - Dealroom</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>Daily and Weekly Digest - Latest News and Updates on Digest at Groww - Groww</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>Groww Block Deal: Stock down 3% after ₹2,500 crore worth equity changes hands - CNBC TV18</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>6</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>PREMIERENE.NS</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Premier Energies Limited</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>1036.5</v>
+      </c>
+      <c r="F407" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G407" t="n">
+        <v>999.4000244140625</v>
+      </c>
+      <c r="H407" t="n">
+        <v>1005.900024414062</v>
+      </c>
+      <c r="I407" t="n">
+        <v>1036</v>
+      </c>
+      <c r="J407" t="n">
+        <v>1005.900024414062</v>
+      </c>
+      <c r="K407" t="n">
+        <v>1004598</v>
+      </c>
+      <c r="L407" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>Premier Energies Ltd. Share Price Today: Price Action Review - Univest</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>Premier Energies Ltd. Share Price Today: Price Action Review - Univest</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>Premier Energies Limited (NSE:PREMIERENE) Just Released Its First-Quarter Results And Analysts Are Updating Their Estimates - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>Premier Energies’ Long-Term Credit Rating Upgraded to A+/Positive by CRISIL - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>CRISIL Upgrades Premier Energies Group to A+ Positive on Bank Facilities - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>7</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>UTTAMSUGAR.NS</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Limited</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>321</v>
+      </c>
+      <c r="F408" t="n">
+        <v>329.8999938964844</v>
+      </c>
+      <c r="G408" t="n">
+        <v>305.5899963378906</v>
+      </c>
+      <c r="H408" t="n">
+        <v>314.8800048828125</v>
+      </c>
+      <c r="I408" t="n">
+        <v>323.1300048828125</v>
+      </c>
+      <c r="J408" t="n">
+        <v>314.8800048828125</v>
+      </c>
+      <c r="K408" t="n">
+        <v>323738</v>
+      </c>
+      <c r="L408" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Q1 Net Profit Plummets 94.69% YoY to ₹85 lakh - Sahi</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Share Price Today: 8.75% rise - Univest</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Ltd. Stock News: Price Increase Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Share Price Jumps; Technicals in Focus - Univest</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Share Price: Technical, Fundamental View - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>8</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>BI.NS</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Bilcare Limited</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>94</v>
+      </c>
+      <c r="F409" t="n">
+        <v>96</v>
+      </c>
+      <c r="G409" t="n">
+        <v>92</v>
+      </c>
+      <c r="H409" t="n">
+        <v>92</v>
+      </c>
+      <c r="I409" t="n">
+        <v>94.38999938964844</v>
+      </c>
+      <c r="J409" t="n">
+        <v>92</v>
+      </c>
+      <c r="K409" t="n">
+        <v>9407</v>
+      </c>
+      <c r="L409" t="n">
+        <v>-2.53</v>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>'Lee Gyu-hyeok♥' Son Dam-bi shares happy parenting moments with her daughter, who inherited her mother's talent - starnewskorea.com</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>'Lee Gyu-hyeok♥' Son Dam-bi shares happy parenting moments with her daughter, who inherited her mother's talent - starnewskorea.com</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>Fund Update: New $13.2M $SNDK stock position opened by BI Asset Management Fondsmaeglerselskab A|S - Quiver Quantitative</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>Son Dam-bi shares happy home moments with daughter Hae-i - CHOSUNBIZ - Chosunbiz</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>Fund Update: New $8.3M $LYG stock position opened by BI Asset Management Fondsmaeglerselskab A|S - Quiver Quantitative</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>9</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>APOLLOPIPE.NS</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Apollo Pipes Limited</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>658</v>
+      </c>
+      <c r="F410" t="n">
+        <v>664</v>
+      </c>
+      <c r="G410" t="n">
+        <v>646.0499877929688</v>
+      </c>
+      <c r="H410" t="n">
+        <v>647.2000122070312</v>
+      </c>
+      <c r="I410" t="n">
+        <v>663.75</v>
+      </c>
+      <c r="J410" t="n">
+        <v>647.2000122070312</v>
+      </c>
+      <c r="K410" t="n">
+        <v>281130</v>
+      </c>
+      <c r="L410" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>Apollo Pipes board to consider raising funds via equity or convertible securities - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>Apollo Pipes board to consider raising funds via equity or convertible securities - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>Apollo Pipes appoints Sanjay Gupta as Chairman after AGM approval - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>Apollo Pipes Share Price at fresh 52-week high | APOLLOPIPE - Univest</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>Apollo Pipes Ltd. (APOLLOPIPE) Share Price Within 2% of 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>10</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>VBL.NS</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Varun Beverages Limited</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>447.8999938964844</v>
+      </c>
+      <c r="F411" t="n">
+        <v>447.8999938964844</v>
+      </c>
+      <c r="G411" t="n">
+        <v>425.25</v>
+      </c>
+      <c r="H411" t="n">
+        <v>427.3500061035156</v>
+      </c>
+      <c r="I411" t="n">
+        <v>438</v>
+      </c>
+      <c r="J411" t="n">
+        <v>427.3500061035156</v>
+      </c>
+      <c r="K411" t="n">
+        <v>18897319</v>
+      </c>
+      <c r="L411" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>Varun Beverages Begins First Step To Enter Alcoholic Beverages. But Why Is The Stock Falling? - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>Varun Beverages Begins First Step To Enter Alcoholic Beverages. But Why Is The Stock Falling? - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>Varun Beverages shares: VBL stock plunges 8% after Q2 results; here's why - Business Today</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>VBL shares bounce back after mixed earnings, but can India volume growth hold up? - Livemint</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>VBL Q1 Results 2027: PAT Rises 15% YoY; Revenue Grows 21% - Sahi</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>11</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>TIIL.NS</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Technocraft Industries (India) Limited</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>3460</v>
+      </c>
+      <c r="F412" t="n">
+        <v>3485.60009765625</v>
+      </c>
+      <c r="G412" t="n">
+        <v>3355.5</v>
+      </c>
+      <c r="H412" t="n">
+        <v>3371.300048828125</v>
+      </c>
+      <c r="I412" t="n">
+        <v>3454.89990234375</v>
+      </c>
+      <c r="J412" t="n">
+        <v>3371.300048828125</v>
+      </c>
+      <c r="K412" t="n">
+        <v>16621</v>
+      </c>
+      <c r="L412" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>Technocraft Industries (India) Ltd. (TIIL) Share Price Hits Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>Technocraft Industries (India) Ltd. (TIIL) Share Price Hits Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>Technocraft Industries Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>Tube Investments of India acquires Shanthi Gears shares for Rs 77.49 crore - Business Upturn</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>12</v>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>BTML.NS</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Bodhi Tree Multimedia Limited</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>9.090000152587891</v>
+      </c>
+      <c r="F413" t="n">
+        <v>9.090000152587891</v>
+      </c>
+      <c r="G413" t="n">
+        <v>8.649999618530273</v>
+      </c>
+      <c r="H413" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="I413" t="n">
+        <v>8.960000038146973</v>
+      </c>
+      <c r="J413" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="K413" t="n">
+        <v>294142</v>
+      </c>
+      <c r="L413" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>Bodhi Tree Multimedia Share Price Fall and Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>Bodhi Tree Multimedia Share Price Fall and Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>Bodhi Tree Multimedia Ltd. Share Price: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>Bodhi Tree Multimedia Ltd. Share Price Today Gains 10.81% - Univest</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>Bodhi Tree Multimedia Ltd. Stock News: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>13</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>AARNAV.NS</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Limited</t>
+        </is>
+      </c>
+      <c r="E414" t="n">
+        <v>33.2599983215332</v>
+      </c>
+      <c r="F414" t="n">
+        <v>33.2599983215332</v>
+      </c>
+      <c r="G414" t="n">
+        <v>32.02000045776367</v>
+      </c>
+      <c r="H414" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="I414" t="n">
+        <v>33.2599983215332</v>
+      </c>
+      <c r="J414" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="K414" t="n">
+        <v>1705</v>
+      </c>
+      <c r="L414" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Q1 Results: Net profit drops 11% YoY to ₹168 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Ltd. Share Price Declines Significantly - Univest</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>RSD Finance Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>14</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>LEMERITE.NS</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Le Merite Exports Limited</t>
+        </is>
+      </c>
+      <c r="E415" t="n">
+        <v>23</v>
+      </c>
+      <c r="F415" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G415" t="n">
+        <v>22.05999946594238</v>
+      </c>
+      <c r="H415" t="n">
+        <v>22.3799991607666</v>
+      </c>
+      <c r="I415" t="n">
+        <v>22.89999961853027</v>
+      </c>
+      <c r="J415" t="n">
+        <v>22.3799991607666</v>
+      </c>
+      <c r="K415" t="n">
+        <v>146721</v>
+      </c>
+      <c r="L415" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>Do Le Merite Exports' (NSE:LEMERITE) Earnings Warrant Your Attention? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>Le Merite Exports Limited (LEMERITE.NS) Q4 FY26 Earnings: Modest Revenue Amidst Thin Margins - Quarterly Profit Report - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>InvestingPro’s Fair Value spotted 45% decline in Le Merite Exports By Investing.com - Investing.com India</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>Le Merite Exports splits shares 1:5, credits new ISIN - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>Le Merite Exports (LEMERITE) Declines Nearly 5%: Testing Key Support Levels - Trend Following Picks - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>15</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>CLEANMAX.NS</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Clean Max Enviro Energy Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>1237.5</v>
+      </c>
+      <c r="F416" t="n">
+        <v>1243</v>
+      </c>
+      <c r="G416" t="n">
+        <v>1171</v>
+      </c>
+      <c r="H416" t="n">
+        <v>1206</v>
+      </c>
+      <c r="I416" t="n">
+        <v>1233.699951171875</v>
+      </c>
+      <c r="J416" t="n">
+        <v>1206</v>
+      </c>
+      <c r="K416" t="n">
+        <v>237790</v>
+      </c>
+      <c r="L416" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>33,933,666 Equity Shares of Clean Max Enviro Energy Solutions Limited are subject to a Lock-Up Agreement Ending on 26-AUG-2026. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>33,933,666 Equity Shares of Clean Max Enviro Energy Solutions Limited are subject to a Lock-Up Agreement Ending on 26-AUG-2026. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>After muted listing, this stock turns multibagger in just 3 months; should you still buy? - Business Today</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>Clean Max Enviro Energy Solutions Allots 35,800 Equity Shares Under ESOS - SolarQuarter</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>16</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>TRIVENI.NS</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Triveni Engineering &amp; Industries Limited</t>
+        </is>
+      </c>
+      <c r="E417" t="n">
+        <v>290.3500061035156</v>
+      </c>
+      <c r="F417" t="n">
+        <v>294.1199951171875</v>
+      </c>
+      <c r="G417" t="n">
+        <v>282.1000061035156</v>
+      </c>
+      <c r="H417" t="n">
+        <v>286.6099853515625</v>
+      </c>
+      <c r="I417" t="n">
+        <v>292.8800048828125</v>
+      </c>
+      <c r="J417" t="n">
+        <v>286.6099853515625</v>
+      </c>
+      <c r="K417" t="n">
+        <v>470396</v>
+      </c>
+      <c r="L417" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>Triveni Engineering fixes June 3 record date for SSEL merger - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>Triveni Turbines releases Q1 FY27 concall transcript with margin guidance - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>Triveni Turbine Consolidated June 2026 Net Sales at Rs 442.70 crore, up 19.23% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>Triveni Engineering &amp; Industries Share Price Rises 8.27% - Univest</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>Triveni Turbine shares tumble 8% after Q1 profit drops 20%, margins shrink - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>17</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>ACI.NS</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Archean Chemical Industries Limited</t>
+        </is>
+      </c>
+      <c r="E418" t="n">
+        <v>500.75</v>
+      </c>
+      <c r="F418" t="n">
+        <v>500.75</v>
+      </c>
+      <c r="G418" t="n">
+        <v>488.1000061035156</v>
+      </c>
+      <c r="H418" t="n">
+        <v>488.75</v>
+      </c>
+      <c r="I418" t="n">
+        <v>499.25</v>
+      </c>
+      <c r="J418" t="n">
+        <v>488.75</v>
+      </c>
+      <c r="K418" t="n">
+        <v>120558</v>
+      </c>
+      <c r="L418" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>ACI Worldwide (NASDAQ:ACIW) Fits Peter Lynch's Growth-at-a-Reasonable-Price Screen - ChartMill</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>Airport sensing without new cabling: Agereh will discuss its tools in Philadelphia - Stock Titan</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>Airport sensing without new cabling: Agereh will discuss its tools in Philadelphia - Stock Titan</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>ACI Infocom open offer timeline set; Mandavias file draft letter - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>AC Immune shares rise after encouraging early Phase 1 data for ACI-19764 - Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>18</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>ADVENTHTL.NS</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Advent Hotels International Limited</t>
+        </is>
+      </c>
+      <c r="E419" t="n">
+        <v>141.9499969482422</v>
+      </c>
+      <c r="F419" t="n">
+        <v>144.5</v>
+      </c>
+      <c r="G419" t="n">
+        <v>138</v>
+      </c>
+      <c r="H419" t="n">
+        <v>139</v>
+      </c>
+      <c r="I419" t="n">
+        <v>141.8300018310547</v>
+      </c>
+      <c r="J419" t="n">
+        <v>139</v>
+      </c>
+      <c r="K419" t="n">
+        <v>105997</v>
+      </c>
+      <c r="L419" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>ADVENTHTL Stock Price and Chart — NSE:ADVENTHTL - TradingView</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>Advent Hotels International (ADVENTHTL.NS) Faces Pressure Near Resistance; Support at ₹139.29 in Focus - Overnight Profile - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>Advent Hotels Listing Tomorrow After Valor Estate Demerger - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>Advent Hotels International (ADVENTHTL.NS) Faces Pressure Near Resistance; Support at ₹139.29 in Focus - Overnight Profile - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>Advent Hotels International (ADVENTHTL.NS) Gains 1.79%: Nears Key Resistance at ₹136.96 - NAAIM Exposure - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>19</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>WELCORP.NS</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Welspun Corp Limited</t>
+        </is>
+      </c>
+      <c r="E420" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F420" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G420" t="n">
+        <v>2203.699951171875</v>
+      </c>
+      <c r="H420" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I420" t="n">
+        <v>2345.5</v>
+      </c>
+      <c r="J420" t="n">
+        <v>2300</v>
+      </c>
+      <c r="K420" t="n">
+        <v>4217184</v>
+      </c>
+      <c r="L420" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>Welspun Corp shares rise post Q1 results: Target prices by five analysts - Business Today</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>Welspun Investments approves sale of Welspun Corp stake at ₹2,250 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>Welspun Corp publishes Q1 FY27 earnings call transcript online - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>Welspun Corp Ltd. (WELCORP) Share Price Trades Within 2% of 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>Welspun Corp Ltd. (WELCORP) Share Price Hits Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:29:17 IST</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>20</v>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>KUSUMGAR.NS</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Kusumgar Limited</t>
+        </is>
+      </c>
+      <c r="E421" t="n">
+        <v>600</v>
+      </c>
+      <c r="F421" t="n">
+        <v>600.0499877929688</v>
+      </c>
+      <c r="G421" t="n">
+        <v>581.1500244140625</v>
+      </c>
+      <c r="H421" t="n">
+        <v>588.2999877929688</v>
+      </c>
+      <c r="I421" t="n">
+        <v>599.2000122070312</v>
+      </c>
+      <c r="J421" t="n">
+        <v>588.2999877929688</v>
+      </c>
+      <c r="K421" t="n">
+        <v>104765</v>
+      </c>
+      <c r="L421" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>Kusumgar Share Price news: valuation and peers in focus - Univest</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>Kusumgar Share Price news: valuation and peers in focus - Univest</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>Kusumgar Ltd. Share Price and 52-Week High Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>Kusumgar Ltd. Share Price and 52-Week High Price Action - Univest</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>Kusumgar Ltd. Share Price Hits New 52-Week High - Univest</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q421"/>
+  <dimension ref="A1:Q441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25061,7 +25061,6 @@
           <t>TVS Srichakra share price jumps16% on robust Q1 earnings performance; profit jumps 165% - Upstox</t>
         </is>
       </c>
-      <c r="Q403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -25604,8 +25603,6 @@
           <t>Ola Electric Mobility Limited (NSE:OLAELEC) Analysts Are Cutting Their Estimates: Here's What You Need To Know - simplywall.st</t>
         </is>
       </c>
-      <c r="P411" t="inlineStr"/>
-      <c r="Q411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -26294,6 +26291,1334 @@
       <c r="Q421" t="inlineStr">
         <is>
           <t>Results: C. E. Info Systems Limited Beat Earnings Expectations And Analysts Now Have New Forecasts - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>1</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>RAMBHAJO.NS</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Advit Jewels Limited</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>215.0099945068359</v>
+      </c>
+      <c r="F422" t="n">
+        <v>255.8399963378906</v>
+      </c>
+      <c r="G422" t="n">
+        <v>210.6199951171875</v>
+      </c>
+      <c r="H422" t="n">
+        <v>255.6900024414062</v>
+      </c>
+      <c r="I422" t="n">
+        <v>213.1999969482422</v>
+      </c>
+      <c r="J422" t="n">
+        <v>255.6900024414062</v>
+      </c>
+      <c r="K422" t="n">
+        <v>12226520</v>
+      </c>
+      <c r="L422" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>ADVIT JEWELS LIMITED Share Price - Live NSE: RAMBHAJO Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>Advit Jewels Delivers Strong FY26 Growth with 33.68% YoY Rise in Income and 35.56% YoY Increase in Net Profit - indiagazette.com</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>Advit Jewels IPO Listing: Rambhajo Shares Glitter On Debut, List At 37% Premium - Outlook Money</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>Advit Jewels IPO: Check Allotment Status &amp; Listing Date Here - Sahi</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>Jewellery brand Rambhajo parent files RHP, IPO to hit Dalal Street next week - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>2</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>DHUNINV.NS</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Dhunseri Investments Limited</t>
+        </is>
+      </c>
+      <c r="E423" t="n">
+        <v>980</v>
+      </c>
+      <c r="F423" t="n">
+        <v>1151.75</v>
+      </c>
+      <c r="G423" t="n">
+        <v>980</v>
+      </c>
+      <c r="H423" t="n">
+        <v>1115.900024414062</v>
+      </c>
+      <c r="I423" t="n">
+        <v>959.7999877929688</v>
+      </c>
+      <c r="J423" t="n">
+        <v>1115.900024414062</v>
+      </c>
+      <c r="K423" t="n">
+        <v>63610</v>
+      </c>
+      <c r="L423" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>Dhunseri Investments sees Raj Vardhan Kejriwal complete final director term - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>Dhunseri Investments sees Raj Vardhan Kejriwal complete final director term - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr"/>
+      <c r="P423" t="inlineStr"/>
+      <c r="Q423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>3</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>VOEPL.NS</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Virtuoso Optoelectronics Limited</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>508</v>
+      </c>
+      <c r="F424" t="n">
+        <v>593.4500122070312</v>
+      </c>
+      <c r="G424" t="n">
+        <v>497.3999938964844</v>
+      </c>
+      <c r="H424" t="n">
+        <v>579.5499877929688</v>
+      </c>
+      <c r="I424" t="n">
+        <v>498.75</v>
+      </c>
+      <c r="J424" t="n">
+        <v>579.5499877929688</v>
+      </c>
+      <c r="K424" t="n">
+        <v>2738595</v>
+      </c>
+      <c r="L424" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>Virtuoso Optoelectronics Share Price rises 12.29% to Rs 560 - Univest</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>Virtuoso Optoelectronics Share Price rises 12.29% to Rs 560 - Univest</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>Transcript : Virtuoso Optoelectronics Limited, Q1 2027 Earnings Call, Aug 17, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>Virtuoso Optoelectronics Limited announced that it has received INR 662.499446 million in funding from Malabar Investments, Fair Value Capital Management - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>Virtuoso Optoelectronics Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>4</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>RGL.NS</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Renaissance Global Limited</t>
+        </is>
+      </c>
+      <c r="E425" t="n">
+        <v>133.3000030517578</v>
+      </c>
+      <c r="F425" t="n">
+        <v>159</v>
+      </c>
+      <c r="G425" t="n">
+        <v>131.7599945068359</v>
+      </c>
+      <c r="H425" t="n">
+        <v>152.5800018310547</v>
+      </c>
+      <c r="I425" t="n">
+        <v>132.8699951171875</v>
+      </c>
+      <c r="J425" t="n">
+        <v>152.5800018310547</v>
+      </c>
+      <c r="K425" t="n">
+        <v>39921956</v>
+      </c>
+      <c r="L425" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>Riversgold (ASX:RGL) Shares Jump 20% as Kalgoorlie Gold Development Moves Forward - Kalkine</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>Riversgold (ASX:RGL) Shares Jump 20% as Kalgoorlie Gold Development Moves Forward - Kalkine</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>Should You Be Adding Renaissance Global (NSE:RGL) To Your Watchlist Today? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>Renaissance Global Share Price Today: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>Titan Minerals (ASX:TTM) Shares Jump as New Gold Discovery Returns 33.5m at 6.6 g/t - Kalkine</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>5</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>INDSWFTLAB.NS</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Limited</t>
+        </is>
+      </c>
+      <c r="E426" t="n">
+        <v>326</v>
+      </c>
+      <c r="F426" t="n">
+        <v>373.7200012207031</v>
+      </c>
+      <c r="G426" t="n">
+        <v>325.9800109863281</v>
+      </c>
+      <c r="H426" t="n">
+        <v>367.4800109863281</v>
+      </c>
+      <c r="I426" t="n">
+        <v>324.3800048828125</v>
+      </c>
+      <c r="J426" t="n">
+        <v>367.4800109863281</v>
+      </c>
+      <c r="K426" t="n">
+        <v>7364038</v>
+      </c>
+      <c r="L426" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Share Price rises 12.36%: analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Share Price rises 12.36%: analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - Univest</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Limited Is Upgrading the Manufacturing Facility Located At Jammu - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories secures 99.99% shareholder approval for ₹137.20 crore warrant issue - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>6</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>ARIES.NS</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Aries Agro Limited</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>446.6499938964844</v>
+      </c>
+      <c r="F427" t="n">
+        <v>517.9000244140625</v>
+      </c>
+      <c r="G427" t="n">
+        <v>445.1000061035156</v>
+      </c>
+      <c r="H427" t="n">
+        <v>503.7000122070312</v>
+      </c>
+      <c r="I427" t="n">
+        <v>446.75</v>
+      </c>
+      <c r="J427" t="n">
+        <v>503.7000122070312</v>
+      </c>
+      <c r="K427" t="n">
+        <v>1074702</v>
+      </c>
+      <c r="L427" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>M&amp;S Shares Slip 1.2% as Aries Capsule Tests a 7.7% Fashion Sales Gap - TechStock²</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>M&amp;S Shares Slip 1.2% as Aries Capsule Tests a 7.7% Fashion Sales Gap - TechStock²</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>Aries Agro Ltd. Share Price Gain: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>Salesforce (CRM) Stock Analysis Today - Gotrade</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>Daily Nadi Horoscope for Aries (7th August 2026): Moon–Mars Energy May Bring Profit, but Family Peace Nee - The Times of India</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>7</v>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>GENCON.NS</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Generic Engineering Construction and Projects Limited</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>41.40999984741211</v>
+      </c>
+      <c r="F428" t="n">
+        <v>47</v>
+      </c>
+      <c r="G428" t="n">
+        <v>41.40999984741211</v>
+      </c>
+      <c r="H428" t="n">
+        <v>46.77000045776367</v>
+      </c>
+      <c r="I428" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="J428" t="n">
+        <v>46.77000045776367</v>
+      </c>
+      <c r="K428" t="n">
+        <v>1098363</v>
+      </c>
+      <c r="L428" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>Generic Engineering Construction And Projects Ltd. (GENCON) Share Price Rises 8.63% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>Generic Engineering Construction And Projects Ltd. (GENCON) Share Price Rises 8.63% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>Generic Engineering Construction And Projects Ltd. (GENCON) Share Price Rises 12.15% Today - Univest</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>Geeks of Wrath – Gencon 2026 Wrap Up! - Non-Productive.com</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>America’s Biggest Gaming Convention Just Wrapped. These Are the Five Board Games We’re Most Excited to Test. - The New York Times</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>8</v>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>SPLIL.NS</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>SPL Industries Limited</t>
+        </is>
+      </c>
+      <c r="E429" t="n">
+        <v>30.39999961853027</v>
+      </c>
+      <c r="F429" t="n">
+        <v>34.84999847412109</v>
+      </c>
+      <c r="G429" t="n">
+        <v>29.60000038146973</v>
+      </c>
+      <c r="H429" t="n">
+        <v>34.13999938964844</v>
+      </c>
+      <c r="I429" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="J429" t="n">
+        <v>34.13999938964844</v>
+      </c>
+      <c r="K429" t="n">
+        <v>47626</v>
+      </c>
+      <c r="L429" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>SPL Industries Limited's (NSE:SPLIL) Share Price Not Quite Adding Up - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>SPLIL Q2 2026 Earnings: Revenue Plunges 50% YoY, EPS at ₹2.43 - Earnings Season Review - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>SPL Industries Managing Director Mukesh Kumar Aggarwal Completes Term, Continues as Board Director - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>SPL Industries Ltd: Marginal Gains Amid Consolidation – SPLIL.NS Holds Near Key Support - ETF NAV Deviation - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>We Think Shareholders May Want To Consider A Review Of SPL Industries Limited's (NSE:SPLIL) CEO Compensation Package - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>9</v>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>MADHAVIPL.NS</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Madhav Infra Projects Limited</t>
+        </is>
+      </c>
+      <c r="E430" t="n">
+        <v>7.300000190734863</v>
+      </c>
+      <c r="F430" t="n">
+        <v>8.300000190734863</v>
+      </c>
+      <c r="G430" t="n">
+        <v>7.300000190734863</v>
+      </c>
+      <c r="H430" t="n">
+        <v>8.029999732971191</v>
+      </c>
+      <c r="I430" t="n">
+        <v>7.230000019073486</v>
+      </c>
+      <c r="J430" t="n">
+        <v>8.029999732971191</v>
+      </c>
+      <c r="K430" t="n">
+        <v>1016360</v>
+      </c>
+      <c r="L430" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>Madhav Infra Projects (NSE:MADHAVIPL) Cyclically Adjusted P - GuruFocus</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>Madhav Infra Projects (NSE:MADHAVIPL) Shiller PE Ratio : (As of Aug. 25, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>Madhav Infra Projects (NSE:MADHAVIPL) Shiller PE Ratio : (As of Aug. 25, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr"/>
+      <c r="Q430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>10</v>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>ANDREWYU.NS</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Andrew Yule &amp; Company Limited</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>26.98999977111816</v>
+      </c>
+      <c r="F431" t="n">
+        <v>30.48999977111816</v>
+      </c>
+      <c r="G431" t="n">
+        <v>26.54000091552734</v>
+      </c>
+      <c r="H431" t="n">
+        <v>29.44000053405762</v>
+      </c>
+      <c r="I431" t="n">
+        <v>26.76000022888184</v>
+      </c>
+      <c r="J431" t="n">
+        <v>29.44000053405762</v>
+      </c>
+      <c r="K431" t="n">
+        <v>916578</v>
+      </c>
+      <c r="L431" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>Andrew Yule &amp; Company Ltd. Share Price Today: 10.87% gain - Univest</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>Andrew Yule &amp; Company Ltd. Share Price Today: 10.87% gain - Univest</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>Andrew Yule &amp; Company Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>Andrew Yule &amp; Company Receives BSE Fine of Rs.5,42,800 for Board Composition Non-Compliance - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>Andrew Yule &amp; Co. Ltd. Announces Appointment of Singhai Sanjay Jain as Non-official Independent Director, Effective August 17, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>11</v>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>MILKYMIST.NS</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Milky Mist Dairy Food Limited</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>201.8999938964844</v>
+      </c>
+      <c r="F432" t="n">
+        <v>222.1100006103516</v>
+      </c>
+      <c r="G432" t="n">
+        <v>198.0599975585938</v>
+      </c>
+      <c r="H432" t="n">
+        <v>222.1100006103516</v>
+      </c>
+      <c r="I432" t="n">
+        <v>201.9199981689453</v>
+      </c>
+      <c r="J432" t="n">
+        <v>222.1100006103516</v>
+      </c>
+      <c r="K432" t="n">
+        <v>20875349</v>
+      </c>
+      <c r="L432" t="n">
+        <v>10</v>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>Diluted shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>Diluted shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>Milky Mist Dairy Food Limited Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>Milky Mist Dairy Food Limited Stock (MILKYMIST) - Quote NSE India S.E. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>MILKYMIST Share Price Today - MILKY MIST DAIRY FOOD L Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>12</v>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>PVP.NS</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>PVP Ventures Limited</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>54</v>
+      </c>
+      <c r="F433" t="n">
+        <v>56.47999954223633</v>
+      </c>
+      <c r="G433" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="H433" t="n">
+        <v>56.47999954223633</v>
+      </c>
+      <c r="I433" t="n">
+        <v>51.34999847412109</v>
+      </c>
+      <c r="J433" t="n">
+        <v>56.47999954223633</v>
+      </c>
+      <c r="K433" t="n">
+        <v>5796445</v>
+      </c>
+      <c r="L433" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>PVP Ventures Share Price Today With Price and Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd Forms Golden Cross Amid Strong Technical Momentum and Micro-Cap Caveats - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd Locks at Upper Circuit With 3.44% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>PVP Ventures Ltd. Share Price Rise: Fundamental Context - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>13</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>NECLIFE.NS</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Nectar Lifesciences Limited</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>11.39999961853027</v>
+      </c>
+      <c r="F434" t="n">
+        <v>12.46000003814697</v>
+      </c>
+      <c r="G434" t="n">
+        <v>11.32999992370605</v>
+      </c>
+      <c r="H434" t="n">
+        <v>12.46000003814697</v>
+      </c>
+      <c r="I434" t="n">
+        <v>11.32999992370605</v>
+      </c>
+      <c r="J434" t="n">
+        <v>12.46000003814697</v>
+      </c>
+      <c r="K434" t="n">
+        <v>1472512</v>
+      </c>
+      <c r="L434" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>Nectar Lifesciences Limited Changes Its Corporate Office in Chandigarh - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>Nectar Lifesciences Publishes Q1 FY2026 Results in Press and Online - TipRanks</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>Nectar Lifesciences to Relocate Corporate Office Within Chandigarh Industrial Hub - TipRanks</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>Nectar Lifesciences Publishes Q1 FY2026 Results in Press and Online - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>14</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>SAKUMA.NS</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Sakuma Exports Limited</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>1.710000038146973</v>
+      </c>
+      <c r="F435" t="n">
+        <v>1.789999961853027</v>
+      </c>
+      <c r="G435" t="n">
+        <v>1.710000038146973</v>
+      </c>
+      <c r="H435" t="n">
+        <v>1.789999961853027</v>
+      </c>
+      <c r="I435" t="n">
+        <v>1.629999995231628</v>
+      </c>
+      <c r="J435" t="n">
+        <v>1.789999961853027</v>
+      </c>
+      <c r="K435" t="n">
+        <v>2329582</v>
+      </c>
+      <c r="L435" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>Sakuma Exports consolidated net profit rises 70.91% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>Sakuma Exports consolidated net profit rises 70.91% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr"/>
+      <c r="P435" t="inlineStr"/>
+      <c r="Q435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>15</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>LADDERUP.NS</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Ladderup Finance Limited</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>50</v>
+      </c>
+      <c r="F436" t="n">
+        <v>53.95000076293945</v>
+      </c>
+      <c r="G436" t="n">
+        <v>50</v>
+      </c>
+      <c r="H436" t="n">
+        <v>53.47000122070312</v>
+      </c>
+      <c r="I436" t="n">
+        <v>49</v>
+      </c>
+      <c r="J436" t="n">
+        <v>53.47000122070312</v>
+      </c>
+      <c r="K436" t="n">
+        <v>139</v>
+      </c>
+      <c r="L436" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>Blue Cloud Softech Solutions Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>Blue Cloud Softech Solutions Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>Ladderup Finance sets Sep 17 record date for 33rd AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>Ladderup Fin Consolidated June 2026 Net Sales at Rs 9.32 crore, up 61.22% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>Ladderup Finance Q1 FY27 Results: Revenue Rs 9 Cr, PAT Rs 3 Cr and Key Highlights - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>16</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>RRECL.NS</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>RDB Real Estate Constructions Limited</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>151.9900054931641</v>
+      </c>
+      <c r="F437" t="n">
+        <v>151.9900054931641</v>
+      </c>
+      <c r="G437" t="n">
+        <v>151</v>
+      </c>
+      <c r="H437" t="n">
+        <v>151.6600036621094</v>
+      </c>
+      <c r="I437" t="n">
+        <v>139</v>
+      </c>
+      <c r="J437" t="n">
+        <v>151.6600036621094</v>
+      </c>
+      <c r="K437" t="n">
+        <v>3</v>
+      </c>
+      <c r="L437" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>RDB Real Estate Constructions (RRECL) Share Price Falls 9.14% to Rs 126.3, Among Top Losers Today - Univest</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>RDB Real Estate Constructions (NSE:RRECL) Cyclically Adjusted PB Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>RDB Real Estate Constructions (NSE:RRECL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>RDB Real Estate Constructions Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>RDB Real Estate Constructions Share Price Today Up 9.8% - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>17</v>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>PACIFICI.NS</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Pacific Industries Limited</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>133.1000061035156</v>
+      </c>
+      <c r="F438" t="n">
+        <v>152</v>
+      </c>
+      <c r="G438" t="n">
+        <v>133.1000061035156</v>
+      </c>
+      <c r="H438" t="n">
+        <v>146.6699981689453</v>
+      </c>
+      <c r="I438" t="n">
+        <v>134.4499969482422</v>
+      </c>
+      <c r="J438" t="n">
+        <v>146.6699981689453</v>
+      </c>
+      <c r="K438" t="n">
+        <v>1330</v>
+      </c>
+      <c r="L438" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>Pacific Industries (NSE:PACIFICI) Cyclically Adjusted Price-to-FCF : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>Pacific Industries (NSE:PACIFICI) Cyclically Adjusted Price-to-FCF : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>Pacific Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr"/>
+      <c r="Q438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>18</v>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>TECILCHEM.NS</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>TECIL Chemicals and Hydro Power Limited</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>9.289999961853027</v>
+      </c>
+      <c r="F439" t="n">
+        <v>10.18000030517578</v>
+      </c>
+      <c r="G439" t="n">
+        <v>8</v>
+      </c>
+      <c r="H439" t="n">
+        <v>9.489999771118164</v>
+      </c>
+      <c r="I439" t="n">
+        <v>8.699999809265137</v>
+      </c>
+      <c r="J439" t="n">
+        <v>9.489999771118164</v>
+      </c>
+      <c r="K439" t="n">
+        <v>70146</v>
+      </c>
+      <c r="L439" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>TECIL Chemicals (TECILCHEM) Declines to ₹11.6, Approaches Key Support Zone - McClellan Summation - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>TECILCHEM Holds Support Amid Weakness – Key Levels to Watch - BPI Bear Correction - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>TECILCHEM Holds Support Amid Weakness – Key Levels to Watch - BPI Bear Correction - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>Tecil Chemicals board to meet on May 27 for Q4FY26 results - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>19</v>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>TBZ.NS</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Tribhovandas Bhimji Zaveri Limited</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>283</v>
+      </c>
+      <c r="F440" t="n">
+        <v>309.2000122070312</v>
+      </c>
+      <c r="G440" t="n">
+        <v>277.0499877929688</v>
+      </c>
+      <c r="H440" t="n">
+        <v>305.7999877929688</v>
+      </c>
+      <c r="I440" t="n">
+        <v>280.3500061035156</v>
+      </c>
+      <c r="J440" t="n">
+        <v>305.7999877929688</v>
+      </c>
+      <c r="K440" t="n">
+        <v>3966721</v>
+      </c>
+      <c r="L440" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>Tribhovandas Bhimji Zaveri Ltd. (TBZ) Share Price Rises 8.82% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>TBZ outlines TDS rules for ₹2.50 per share FY26 dividend - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>TBZ outlines TDS rules for ₹2.50 per share FY26 dividend - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>TBZ Reports Strong Unaudited Q1 FY27 Results, Maintains Profit Momentum - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>20</v>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>SBFC.NS</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>SBFC Finance Limited</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>92.59999847412109</v>
+      </c>
+      <c r="F441" t="n">
+        <v>102.2099990844727</v>
+      </c>
+      <c r="G441" t="n">
+        <v>92.59999847412109</v>
+      </c>
+      <c r="H441" t="n">
+        <v>101.1399993896484</v>
+      </c>
+      <c r="I441" t="n">
+        <v>92.76999664306641</v>
+      </c>
+      <c r="J441" t="n">
+        <v>101.1399993896484</v>
+      </c>
+      <c r="K441" t="n">
+        <v>17100733</v>
+      </c>
+      <c r="L441" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>Volumes jump at SBFC Finance Ltd counter - Business Standard</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>Volumes jump at SBFC Finance Ltd counter - Business Standard</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>Top Gainers &amp; Losers on 26 Aug: SBFC Finance, Capri Global, Hindustan Copper, SAIL, OLA, Vedanta among top gainers - Livemint</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>SBFC Finance Ltd is Rated Sell - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>SBFC Finance vs MAS Financial Services: Which MSME NBFC Stock - Univest</t>
         </is>
       </c>
     </row>
@@ -26308,7 +27633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q421"/>
+  <dimension ref="A1:Q441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50629,7 +51954,6 @@
           <t>Kohinoor Textile to install 48MW battery storage amid 9MW solar expansion - Business Recorder</t>
         </is>
       </c>
-      <c r="Q403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -51246,7 +52570,6 @@
           <t>Tube Investments of India acquires Shanthi Gears shares for Rs 77.49 crore - Business Upturn</t>
         </is>
       </c>
-      <c r="Q412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -51518,7 +52841,6 @@
           <t>Clean Max Enviro Energy Solutions Allots 35,800 Equity Shares Under ESOS - SolarQuarter</t>
         </is>
       </c>
-      <c r="Q416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -51862,6 +53184,1346 @@
       <c r="Q421" t="inlineStr">
         <is>
           <t>Kusumgar Ltd. Share Price Hits New 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>1</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>ELITECON.NS</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Elitecon International Limited</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>13.88000011444092</v>
+      </c>
+      <c r="F422" t="n">
+        <v>14.27000045776367</v>
+      </c>
+      <c r="G422" t="n">
+        <v>12.39000034332275</v>
+      </c>
+      <c r="H422" t="n">
+        <v>12.39000034332275</v>
+      </c>
+      <c r="I422" t="n">
+        <v>13.76000022888184</v>
+      </c>
+      <c r="J422" t="n">
+        <v>12.39000034332275</v>
+      </c>
+      <c r="K422" t="n">
+        <v>8072629</v>
+      </c>
+      <c r="L422" t="n">
+        <v>-9.960000000000001</v>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>Elitecon International Ltd Hits Intraday Low Amid Price Pressure - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>Elitecon International Ltd Hits Intraday Low Amid Price Pressure - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>Elitecon International: Kumar Anubhav Upadhyay ceases as Additional Director - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>Small-cap stock under ₹50 Elitecon International hits 10% upper circuit for second day in a row - Livemint</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>Small-cap stock trades green despite tepid stock market trends - Livemint</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>2</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>NEXTMEDIA.NS</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Next Mediaworks Limited</t>
+        </is>
+      </c>
+      <c r="E423" t="n">
+        <v>3.910000085830688</v>
+      </c>
+      <c r="F423" t="n">
+        <v>3.950000047683716</v>
+      </c>
+      <c r="G423" t="n">
+        <v>3.160000085830688</v>
+      </c>
+      <c r="H423" t="n">
+        <v>3.579999923706055</v>
+      </c>
+      <c r="I423" t="n">
+        <v>3.910000085830688</v>
+      </c>
+      <c r="J423" t="n">
+        <v>3.579999923706055</v>
+      </c>
+      <c r="K423" t="n">
+        <v>80986</v>
+      </c>
+      <c r="L423" t="n">
+        <v>-8.44</v>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>Next Mediaworks schedules 45th AGM for Sep 22 via video conference - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>Next Mediaworks schedules 45th AGM for Sep 22 via video conference - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>Next Mediaworks Q1FY26 loss narrows to ₹88 lakh as going concern risk persists - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>MannKind Corporation (MNKD) Declines 4.38% to $3.93 as Shares Approach Key Support - Put Spread Alert - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>3</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>FILATEX.NS</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Filatex India Limited</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>82.11000061035156</v>
+      </c>
+      <c r="F424" t="n">
+        <v>83.27999877929688</v>
+      </c>
+      <c r="G424" t="n">
+        <v>70.73999786376953</v>
+      </c>
+      <c r="H424" t="n">
+        <v>75.19000244140625</v>
+      </c>
+      <c r="I424" t="n">
+        <v>82.11000061035156</v>
+      </c>
+      <c r="J424" t="n">
+        <v>75.19000244140625</v>
+      </c>
+      <c r="K424" t="n">
+        <v>10801532</v>
+      </c>
+      <c r="L424" t="n">
+        <v>-8.43</v>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>Filatex India shares can rally to Rs 118? Why Equirus Prive initiated coverage on the stock - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>Filatex Fashions Ltd Locks at Upper Circuit With 5.56% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>Filatex Fashions fined ₹24,780 each by NSE, BSE for non-compliance - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>Filatex Fashions Ltd Locks at Upper Circuit With 5.56% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>Filatex India vs Indo Rama Synthetics India: Which Fibre Stock to Track - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>4</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>SAMBANDAM.NS</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Sambandam Spinning Mills Limited</t>
+        </is>
+      </c>
+      <c r="E425" t="n">
+        <v>135.1999969482422</v>
+      </c>
+      <c r="F425" t="n">
+        <v>135.1999969482422</v>
+      </c>
+      <c r="G425" t="n">
+        <v>124</v>
+      </c>
+      <c r="H425" t="n">
+        <v>125.4700012207031</v>
+      </c>
+      <c r="I425" t="n">
+        <v>134.1399993896484</v>
+      </c>
+      <c r="J425" t="n">
+        <v>125.4700012207031</v>
+      </c>
+      <c r="K425" t="n">
+        <v>6243</v>
+      </c>
+      <c r="L425" t="n">
+        <v>-6.46</v>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>Sambandam Spinning Mills FY26 Results: Net loss narrows to ₹5.74 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>Sambandam Spinning Mills FY26 Results: Net loss narrows to ₹5.74 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>SAMBANDAM Stock Price and Chart — NSE:SAMBANDAM - TradingView</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>Sambandam Spinning Mills Ltd leads gainers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>dj mediaprint and logistics ltd leads losers in b group - Capital Market</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>5</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>WHBRADY.NS</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>WH Brady &amp; Company Limited</t>
+        </is>
+      </c>
+      <c r="E426" t="n">
+        <v>500</v>
+      </c>
+      <c r="F426" t="n">
+        <v>500.0499877929688</v>
+      </c>
+      <c r="G426" t="n">
+        <v>497.5499877929688</v>
+      </c>
+      <c r="H426" t="n">
+        <v>497.7999877929688</v>
+      </c>
+      <c r="I426" t="n">
+        <v>529.9500122070312</v>
+      </c>
+      <c r="J426" t="n">
+        <v>497.7999877929688</v>
+      </c>
+      <c r="K426" t="n">
+        <v>176</v>
+      </c>
+      <c r="L426" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="M426" t="inlineStr"/>
+      <c r="N426" t="inlineStr"/>
+      <c r="O426" t="inlineStr"/>
+      <c r="P426" t="inlineStr"/>
+      <c r="Q426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>6</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>TANLA.NS</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Tanla Platforms Limited</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>558</v>
+      </c>
+      <c r="F427" t="n">
+        <v>563.9000244140625</v>
+      </c>
+      <c r="G427" t="n">
+        <v>522.0999755859375</v>
+      </c>
+      <c r="H427" t="n">
+        <v>526.0499877929688</v>
+      </c>
+      <c r="I427" t="n">
+        <v>556.0499877929688</v>
+      </c>
+      <c r="J427" t="n">
+        <v>526.0499877929688</v>
+      </c>
+      <c r="K427" t="n">
+        <v>1298318</v>
+      </c>
+      <c r="L427" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>Route Mobile vs Tanla Platforms: Which CPaaS Stock to Track - Univest</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>Tanla Platforms Share Pros and Cons 2026 | TANLA CPaaS Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>Tanla Platforms Share Pros and Cons 2026 | TANLA CPaaS Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>Tanla Platforms Consolidated June 2026 Net Sales at Rs 1,226.39 crore, up 17.85% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>Tanla Platforms Standalone June 2026 Net Sales at Rs 214.34 crore, up 28.41% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>7</v>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>VIYASH.NS</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Viyash Scientific Limited</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>268.8500061035156</v>
+      </c>
+      <c r="F428" t="n">
+        <v>271.1499938964844</v>
+      </c>
+      <c r="G428" t="n">
+        <v>259.1000061035156</v>
+      </c>
+      <c r="H428" t="n">
+        <v>263.3999938964844</v>
+      </c>
+      <c r="I428" t="n">
+        <v>278.3500061035156</v>
+      </c>
+      <c r="J428" t="n">
+        <v>263.3999938964844</v>
+      </c>
+      <c r="K428" t="n">
+        <v>115373365</v>
+      </c>
+      <c r="L428" t="n">
+        <v>-5.37</v>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>Six block deals worth over ₹6,000 crore change hands today — Check details here - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>Viyash Scientific Ltd leads losers in 'A' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>Viyash Scientific Share Price Gains 7.19%, Most in Three Months - Univest</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>Viyash Scientif Consolidated June 2026 Net Sales at Rs 946.36 crore, up 114.39% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>Viyash Scientif Standalone June 2026 Net Sales at Rs 353.69 crore, up 761.19% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>8</v>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>DCMSRIND.NS</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>DCM Shriram Industries Limited</t>
+        </is>
+      </c>
+      <c r="E429" t="n">
+        <v>50.29999923706055</v>
+      </c>
+      <c r="F429" t="n">
+        <v>51.38000106811523</v>
+      </c>
+      <c r="G429" t="n">
+        <v>47.27999877929688</v>
+      </c>
+      <c r="H429" t="n">
+        <v>47.84000015258789</v>
+      </c>
+      <c r="I429" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="J429" t="n">
+        <v>47.84000015258789</v>
+      </c>
+      <c r="K429" t="n">
+        <v>268616</v>
+      </c>
+      <c r="L429" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>DCM Shriram Industries Limited (NSE:DCMSRIND) Stock Goes Ex-Dividend In Just Three Days - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>DCM Shriram Industries (DCMSRIND.NS) Slips 2.89% to ₹40.0: Support at ₹38.0 Under Focus - Wave Truncation - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>DCM Shriram Industries (DCMSRIND.NS) Slips 2.89% to ₹40.0: Support at ₹38.0 Under Focus - Wave Truncation - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>DCM Shriram Industries Limited's (NSE:DCMSRIND) 68% Dip In Price Shows Sentiment Is Matching Earnings - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>DCM Shriram Industries (DCMSRIND.NS) Mild Decline in Range-Bound Trading – Key Levels in Focus - Option Breadth - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>9</v>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>SHYAMTEL.NS</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Shyam Telecom Limited</t>
+        </is>
+      </c>
+      <c r="E430" t="n">
+        <v>13.82999992370605</v>
+      </c>
+      <c r="F430" t="n">
+        <v>13.85999965667725</v>
+      </c>
+      <c r="G430" t="n">
+        <v>13.02000045776367</v>
+      </c>
+      <c r="H430" t="n">
+        <v>13.14999961853027</v>
+      </c>
+      <c r="I430" t="n">
+        <v>13.85999965667725</v>
+      </c>
+      <c r="J430" t="n">
+        <v>13.14999961853027</v>
+      </c>
+      <c r="K430" t="n">
+        <v>7708</v>
+      </c>
+      <c r="L430" t="n">
+        <v>-5.12</v>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>Shyam Telecom (SHYAMTEL.NS) Slides 2% Amid Weak Volume – Key Support at ₹19.16 in Focus - Dynamic Hedging - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>SHYAMTEL Q4 FY26 Earnings: Net Loss Persists as Business Activities Remain Minimal - Margin Compression Risk - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>SHYAMTEL Mar 2026 Earnings: Continued Revenue Absence and Nominal Loss - Dividend Increase Stocks - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>SHYAMTEL Mar 2026 Earnings: Revenue Stays at Zero, EPS Remains Negative Amidst Operational Lull - Debt Analysis Report - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>Shyam Telecom Limited Q4 FY26 Earnings: Zero Revenue and Negative EPS Highlight Persistent Operational Challenges - Financial Summary - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>10</v>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>KANPRPLA.NS</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Kanpur Plastipack Limited</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>282.9500122070312</v>
+      </c>
+      <c r="F431" t="n">
+        <v>283.010009765625</v>
+      </c>
+      <c r="G431" t="n">
+        <v>260.3200073242188</v>
+      </c>
+      <c r="H431" t="n">
+        <v>263.2699890136719</v>
+      </c>
+      <c r="I431" t="n">
+        <v>277.1900024414062</v>
+      </c>
+      <c r="J431" t="n">
+        <v>263.2699890136719</v>
+      </c>
+      <c r="K431" t="n">
+        <v>47054</v>
+      </c>
+      <c r="L431" t="n">
+        <v>-5.02</v>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>Kanpur Plastipack Share Price Today With Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>Kanpur Plastipack surges 63% after Fair Value identified opportunity - Investing.com India</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>Kanpur Plastipack to allot equity shares on warrant conversion - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>Kanpur Plastipack surges 63% after Fair Value identified opportunity - Investing.com India</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>Kanpur Plastipack shareholders approve all 7 AGM resolutions - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>11</v>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>SIMPLXREA.NS</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Simplex Realty Limited</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>132</v>
+      </c>
+      <c r="F432" t="n">
+        <v>132</v>
+      </c>
+      <c r="G432" t="n">
+        <v>125.4000015258789</v>
+      </c>
+      <c r="H432" t="n">
+        <v>125.4000015258789</v>
+      </c>
+      <c r="I432" t="n">
+        <v>132</v>
+      </c>
+      <c r="J432" t="n">
+        <v>125.4000015258789</v>
+      </c>
+      <c r="K432" t="n">
+        <v>3</v>
+      </c>
+      <c r="L432" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of Simplex Realty Limited – NSE:SIMPLXREA - TradingView</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>Simplex Realty (NSE:SIMPLXREA) Shiller PE Ratio : (As of Aug. 25, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>Simplex Realty Limited Announces Board and Committee Changes, Effective August 5, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>Simplex Realty (NSE:SIMPLXREA) Shiller PE Ratio : (As of Aug. 25, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>12</v>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>NATIONSTD.NS</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>National Standard (India) Limited</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>110.0199966430664</v>
+      </c>
+      <c r="F433" t="n">
+        <v>114.9000015258789</v>
+      </c>
+      <c r="G433" t="n">
+        <v>108.879997253418</v>
+      </c>
+      <c r="H433" t="n">
+        <v>108.879997253418</v>
+      </c>
+      <c r="I433" t="n">
+        <v>114.6100006103516</v>
+      </c>
+      <c r="J433" t="n">
+        <v>108.879997253418</v>
+      </c>
+      <c r="K433" t="n">
+        <v>171484</v>
+      </c>
+      <c r="L433" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>National Standard (India) (NSE:NATIONSTD) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>National Standard (India) (NSE:NATIONSTD) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>National Standard files FY26 BRSR, reports 100% related-party sales - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>National Standard (India) sets Aug 28 date for 63rd AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>13</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>TAKE.NS</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>TAKE Limited</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>17.8700008392334</v>
+      </c>
+      <c r="F434" t="n">
+        <v>17.8700008392334</v>
+      </c>
+      <c r="G434" t="n">
+        <v>17.8700008392334</v>
+      </c>
+      <c r="H434" t="n">
+        <v>17.8700008392334</v>
+      </c>
+      <c r="I434" t="n">
+        <v>18.80999946594238</v>
+      </c>
+      <c r="J434" t="n">
+        <v>17.8700008392334</v>
+      </c>
+      <c r="K434" t="n">
+        <v>82918</v>
+      </c>
+      <c r="L434" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>Umpires Adrian Holdstock and Shaun George take stock of the ground at Durban - Cricinfo</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>Silver Mines Shares Retreat as Precious-Metal Traders Take Profits - Kalkine</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>Take-Two Stock Stalled Before GTA VI. The Setup Still Points Up - TIKR.com</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>What Moderna Must Do to Take Its Stock to the Next Level - Barron's</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>Silver Mines Shares Retreat as Precious-Metal Traders Take Profits - Kalkine</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>14</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>SIEL.NS</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>34.45000076293945</v>
+      </c>
+      <c r="F435" t="n">
+        <v>34.45000076293945</v>
+      </c>
+      <c r="G435" t="n">
+        <v>32.84999847412109</v>
+      </c>
+      <c r="H435" t="n">
+        <v>32.84999847412109</v>
+      </c>
+      <c r="I435" t="n">
+        <v>34.56999969482422</v>
+      </c>
+      <c r="J435" t="n">
+        <v>32.84999847412109</v>
+      </c>
+      <c r="K435" t="n">
+        <v>3833</v>
+      </c>
+      <c r="L435" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>SIEL Stock Price and Chart — NSE:SIEL - TradingView</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>5 Under the Radar Trading Stocks in India - Univest</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>5 Under the Radar Trading Stocks in India - Univest</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises standalone profit rises 21.8% in Q1FY27 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>15</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>AQYLON.NS</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Aqylon Nexus Limited</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>24.34000015258789</v>
+      </c>
+      <c r="F436" t="n">
+        <v>24.79000091552734</v>
+      </c>
+      <c r="G436" t="n">
+        <v>23.94000053405762</v>
+      </c>
+      <c r="H436" t="n">
+        <v>23.95000076293945</v>
+      </c>
+      <c r="I436" t="n">
+        <v>25.20000076293945</v>
+      </c>
+      <c r="J436" t="n">
+        <v>23.95000076293945</v>
+      </c>
+      <c r="K436" t="n">
+        <v>1652410</v>
+      </c>
+      <c r="L436" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>Leading Leasing Finance Increases Stake in Aqylon Nexus to 14.17% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>Leading Leasing Finance Increases Stake in Aqylon Nexus to 14.17% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>Leading Leasing sells 1.47 cr Aqylon Nexus shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>Leading Leasing raises Aqylon Nexus stake to 10.30% via open market buy - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>Aqylon Nexus appoints Rupareliya as director, Sanghani as CFO - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>16</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>ABINFRA.NS</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>A B Infrabuild Limited</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>12.01000022888184</v>
+      </c>
+      <c r="F437" t="n">
+        <v>12.77000045776367</v>
+      </c>
+      <c r="G437" t="n">
+        <v>11.94999980926514</v>
+      </c>
+      <c r="H437" t="n">
+        <v>11.94999980926514</v>
+      </c>
+      <c r="I437" t="n">
+        <v>12.56999969482422</v>
+      </c>
+      <c r="J437" t="n">
+        <v>11.94999980926514</v>
+      </c>
+      <c r="K437" t="n">
+        <v>451661</v>
+      </c>
+      <c r="L437" t="n">
+        <v>-4.93</v>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>A B Infrabuild Limited announces Annual dividend, payable on October 28, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>A B Infrabuild Limited announces Annual dividend, payable on October 28, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>A B Infrabuild schedules AGM and announces book closure - Business Upturn</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>A B Infrabuild reports Q1 FY27 revenue of ₹7,625.1 lakh, a 25.9% increase YoY - Business Upturn</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>17</v>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>GRADIENTE.NS</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Gradiente Infotainment Limited</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>2.849999904632568</v>
+      </c>
+      <c r="F438" t="n">
+        <v>2.849999904632568</v>
+      </c>
+      <c r="G438" t="n">
+        <v>2.700000047683716</v>
+      </c>
+      <c r="H438" t="n">
+        <v>2.700000047683716</v>
+      </c>
+      <c r="I438" t="n">
+        <v>2.839999914169312</v>
+      </c>
+      <c r="J438" t="n">
+        <v>2.700000047683716</v>
+      </c>
+      <c r="K438" t="n">
+        <v>480408</v>
+      </c>
+      <c r="L438" t="n">
+        <v>-4.93</v>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>Gradiente Infotainment Considers Capital Raising Initiatives in Board Meeting - Sahi</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>Momentum Stocks: PNB Housing Finance, Divis Labs, Ipca Labs, Paytm hit 52-week high - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>Momentum Stocks: PNB Housing Finance, Divis Labs, Ipca Labs, Paytm hit 52-week high - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>Price Band Hitters, August 11, 2026, 3:30 PM IST - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>Major Push for the Orange Economy: Gradiente Infotainment Unveils ₹5,000 Crore Mega Investment Roadmap - The Tribune</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>18</v>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>PNC.NS</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Pritish Nandy Communications Limited</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>18.14999961853027</v>
+      </c>
+      <c r="F439" t="n">
+        <v>18.14999961853027</v>
+      </c>
+      <c r="G439" t="n">
+        <v>16.70999908447266</v>
+      </c>
+      <c r="H439" t="n">
+        <v>16.98999977111816</v>
+      </c>
+      <c r="I439" t="n">
+        <v>17.8700008392334</v>
+      </c>
+      <c r="J439" t="n">
+        <v>16.98999977111816</v>
+      </c>
+      <c r="K439" t="n">
+        <v>39491</v>
+      </c>
+      <c r="L439" t="n">
+        <v>-4.92</v>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>280,552 Shares in The PNC Financial Services Group, Inc $PNC Acquired by The Manufacturers Life Insurance Company - MarketBeat</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>PDT Partners LLC Makes New $3.96 Million Investment in The PNC Financial Services Group, Inc $PNC - MarketBeat</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>AXIA Energia (OTC: AXIAY) exec in 485-share mandatory redemption - Stock Titan</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>PNC Financial Services Group (PNC) Stock Stays Reasonable After A 129% Run - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>Are Wall Street Analysts Predicting PNC Financial Services Stock Will Climb or Sink? - Barchart.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>19</v>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>EMPOWER.NS</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Empower India Limited</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>2.339999914169312</v>
+      </c>
+      <c r="F440" t="n">
+        <v>2.339999914169312</v>
+      </c>
+      <c r="G440" t="n">
+        <v>2.339999914169312</v>
+      </c>
+      <c r="H440" t="n">
+        <v>2.339999914169312</v>
+      </c>
+      <c r="I440" t="n">
+        <v>2.460000038146973</v>
+      </c>
+      <c r="J440" t="n">
+        <v>2.339999914169312</v>
+      </c>
+      <c r="K440" t="n">
+        <v>2078514</v>
+      </c>
+      <c r="L440" t="n">
+        <v>-4.88</v>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>Empower India - 11 penny stocks surged up to 198% in 6 months. Do you own any? - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>More money to help farmer firefighters better protect properties and save time - Stock Journal</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>Empower Q2 Results: Base earnings rise 34% to $332 million - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>More money to help farmer firefighters better protect properties and save time - Stock Journal</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>Domestic Abuse Survivor Shares Story to Empower Others - People Newspapers</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:32:49 IST</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>20</v>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>MPDL.NS</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>MPDL Limited</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>34.90000152587891</v>
+      </c>
+      <c r="F441" t="n">
+        <v>41.18000030517578</v>
+      </c>
+      <c r="G441" t="n">
+        <v>34.90000152587891</v>
+      </c>
+      <c r="H441" t="n">
+        <v>35.61999893188477</v>
+      </c>
+      <c r="I441" t="n">
+        <v>37.43999862670898</v>
+      </c>
+      <c r="J441" t="n">
+        <v>35.61999893188477</v>
+      </c>
+      <c r="K441" t="n">
+        <v>4590</v>
+      </c>
+      <c r="L441" t="n">
+        <v>-4.86</v>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>MPDL Stock Price and Chart — NSE:MPDL - TradingView</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>Shah Metacorp Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>MPDL shareholders approve Santosh Kumar Jha's remuneration - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>Shah Metacorp Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>MPDL (NSE:MPDL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q441"/>
+  <dimension ref="A1:Q461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26416,9 +26416,6 @@
           <t>Dhunseri Investments sees Raj Vardhan Kejriwal complete final director term - scanx.trade</t>
         </is>
       </c>
-      <c r="O423" t="inlineStr"/>
-      <c r="P423" t="inlineStr"/>
-      <c r="Q423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -26892,8 +26889,6 @@
           <t>Madhav Infra Projects (NSE:MADHAVIPL) Shiller PE Ratio : (As of Aug. 25, 2026) - GuruFocus</t>
         </is>
       </c>
-      <c r="P430" t="inlineStr"/>
-      <c r="Q430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -27165,7 +27160,6 @@
           <t>Nectar Lifesciences Publishes Q1 FY2026 Results in Press and Online - TipRanks</t>
         </is>
       </c>
-      <c r="Q434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -27220,9 +27214,6 @@
           <t>Sakuma Exports consolidated net profit rises 70.91% in the June 2026 quarter - Business Standard</t>
         </is>
       </c>
-      <c r="O435" t="inlineStr"/>
-      <c r="P435" t="inlineStr"/>
-      <c r="Q435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -27420,8 +27411,6 @@
           <t>Pacific Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
-      <c r="P438" t="inlineStr"/>
-      <c r="Q438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -27486,7 +27475,6 @@
           <t>Tecil Chemicals board to meet on May 27 for Q4FY26 results - scanx.trade</t>
         </is>
       </c>
-      <c r="Q439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -27551,7 +27539,6 @@
           <t>TBZ Reports Strong Unaudited Q1 FY27 Results, Maintains Profit Momentum - TipRanks</t>
         </is>
       </c>
-      <c r="Q440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -27621,6 +27608,1322 @@
           <t>SBFC Finance vs MAS Financial Services: Which MSME NBFC Stock - Univest</t>
         </is>
       </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>1</v>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>IMAGICAA.NS</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Imagicaaworld Entertainment Limited</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>50.09999847412109</v>
+      </c>
+      <c r="F442" t="n">
+        <v>60.20999908447266</v>
+      </c>
+      <c r="G442" t="n">
+        <v>50.04999923706055</v>
+      </c>
+      <c r="H442" t="n">
+        <v>60.20999908447266</v>
+      </c>
+      <c r="I442" t="n">
+        <v>50.18000030517578</v>
+      </c>
+      <c r="J442" t="n">
+        <v>60.20999908447266</v>
+      </c>
+      <c r="K442" t="n">
+        <v>34242785</v>
+      </c>
+      <c r="L442" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>Imagicaaworld completes ₹50 crore MNPPL stake buyout - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>Imagicaaworld shares hit 20% upper circuit as PL Capital gives 'buy' rating -- check target price - TradingView</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>Imagicaaworld shares hit 20% upper circuit as PL Capital gives 'buy' rating -- check target price - TradingView</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>Imagicaaworld Entertainment Share Price: 15.96% rise - Univest</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>Imagicaaworld Entertainment hosts Q1FY27 earnings call on Aug 10 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>2</v>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>SHAH.NS</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Shah Metacorp Limited</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>3.200000047683716</v>
+      </c>
+      <c r="F443" t="n">
+        <v>3.789999961853027</v>
+      </c>
+      <c r="G443" t="n">
+        <v>3.140000104904175</v>
+      </c>
+      <c r="H443" t="n">
+        <v>3.779999971389771</v>
+      </c>
+      <c r="I443" t="n">
+        <v>3.160000085830688</v>
+      </c>
+      <c r="J443" t="n">
+        <v>3.779999971389771</v>
+      </c>
+      <c r="K443" t="n">
+        <v>43874206</v>
+      </c>
+      <c r="L443" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>Shah Metacorp Share Price Rise: Price Action and Metrics - Univest</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>Fine Organic Industries promoter Jayen Shah transfers 1% stake via HUF partition - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>Yash Chemex promoter Paxal Shah buys 1600 shares on BSE - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>Precigen COO Rutul Shah sells $375,000 in shares - Investing.com India</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>'Not Too High, Not Too Low': Nilesh Shah's Rule For Stock Picking - NDTV Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>3</v>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>ANSALBU.NS</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Ansal Buildwell Limited</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="F444" t="n">
+        <v>85.69000244140625</v>
+      </c>
+      <c r="G444" t="n">
+        <v>72.01000213623047</v>
+      </c>
+      <c r="H444" t="n">
+        <v>85.69000244140625</v>
+      </c>
+      <c r="I444" t="n">
+        <v>72.01000213623047</v>
+      </c>
+      <c r="J444" t="n">
+        <v>85.69000244140625</v>
+      </c>
+      <c r="K444" t="n">
+        <v>263</v>
+      </c>
+      <c r="L444" t="n">
+        <v>19</v>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>Ansal Buildwell (NSE:ANSALBU) Cyclically Adjusted PS Ratio : (As of Aug. 22, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>Ansal Buildwell (NSE:ANSALBU) Cyclically Adjusted PS Ratio : (As of Aug. 22, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>Ansal Buildwell Ltd - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr"/>
+      <c r="Q444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>4</v>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>NATCAPSUQ.NS</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Natural Capsules Limited</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>181</v>
+      </c>
+      <c r="F445" t="n">
+        <v>216.3300018310547</v>
+      </c>
+      <c r="G445" t="n">
+        <v>179.1699981689453</v>
+      </c>
+      <c r="H445" t="n">
+        <v>214.1600036621094</v>
+      </c>
+      <c r="I445" t="n">
+        <v>180.2799987792969</v>
+      </c>
+      <c r="J445" t="n">
+        <v>214.1600036621094</v>
+      </c>
+      <c r="K445" t="n">
+        <v>268433</v>
+      </c>
+      <c r="L445" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>Natural Capsules Ltd. (NATCAPSUQ) Share Price rises 9.11% as stock gains today - Univest</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>Natural Capsules Ltd. (NATCAPSUQ) Share Price rises 9.11% as stock gains today - Univest</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>Natural Capsules Ltd. Share Price Today: 11.68% Price Rise - Univest</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>Natural Capsules adds preferential equity raise to Aug 12 board agenda - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>Natural Capsules Ltd. Share Price: Today's Rally Explained - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>5</v>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>MVELECTRO.NS</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>MV Electrosystems Limited</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>565.5</v>
+      </c>
+      <c r="F446" t="n">
+        <v>672.1500244140625</v>
+      </c>
+      <c r="G446" t="n">
+        <v>559.9500122070312</v>
+      </c>
+      <c r="H446" t="n">
+        <v>646.7999877929688</v>
+      </c>
+      <c r="I446" t="n">
+        <v>560.1500244140625</v>
+      </c>
+      <c r="J446" t="n">
+        <v>646.7999877929688</v>
+      </c>
+      <c r="K446" t="n">
+        <v>14676894</v>
+      </c>
+      <c r="L446" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>MV Electrosystems Share Price: price rise and valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>MV Electrosystems Share Price: price rise and valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>MV ELECTROSYSTEMS LIMITED Share Price - Live NSE: MVELECTRO Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>Mv Electrosystems Limited Financial Statements – NSE:MVELECTRO - TradingView</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>MV Electrosystems IPO Review: India's Railway Propulsion Bet With ₹990 Crore Order Book and Execution Challenges - India Infoline</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>6</v>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>BBTC.NS</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>The Bombay Burmah Trading Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>1450</v>
+      </c>
+      <c r="F447" t="n">
+        <v>1639</v>
+      </c>
+      <c r="G447" t="n">
+        <v>1449</v>
+      </c>
+      <c r="H447" t="n">
+        <v>1613.599975585938</v>
+      </c>
+      <c r="I447" t="n">
+        <v>1426.199951171875</v>
+      </c>
+      <c r="J447" t="n">
+        <v>1613.599975585938</v>
+      </c>
+      <c r="K447" t="n">
+        <v>14319799</v>
+      </c>
+      <c r="L447" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>Why did BBTC shares jump nearly 15% in early trade? - Business Today</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>HDFC Bank shares hit 52-week low, down 28% YTD; experts see further downside - Business Today</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>Bombay Burmah Trading Corporation Share Price rises 12.13% - Univest</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>Bombay Burmah Trading Corporation shares post best day in over a year; here is why - Upstox</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>BSE shares down 6% in a month but up 26% YTD; NSE IPO, CAS weigh on stock? - Business Today</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>7</v>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>INOXINDIA.NS</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>INOX India Limited</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>1935.900024414062</v>
+      </c>
+      <c r="F448" t="n">
+        <v>2224</v>
+      </c>
+      <c r="G448" t="n">
+        <v>1916.900024414062</v>
+      </c>
+      <c r="H448" t="n">
+        <v>2177.89990234375</v>
+      </c>
+      <c r="I448" t="n">
+        <v>1926.699951171875</v>
+      </c>
+      <c r="J448" t="n">
+        <v>2177.89990234375</v>
+      </c>
+      <c r="K448" t="n">
+        <v>4484155</v>
+      </c>
+      <c r="L448" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>Inox India Ltd Dividend History, Yield &amp; Record Date - INDmoney</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>Inox India Ltd Dividend History, Yield &amp; Record Date - INDmoney</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>INOX India Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr"/>
+      <c r="Q448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>8</v>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>SHAHALLOYS.NS</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Shah Alloys Limited</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>78.91999816894531</v>
+      </c>
+      <c r="F449" t="n">
+        <v>86.75</v>
+      </c>
+      <c r="G449" t="n">
+        <v>78</v>
+      </c>
+      <c r="H449" t="n">
+        <v>85.95999908447266</v>
+      </c>
+      <c r="I449" t="n">
+        <v>76.05999755859375</v>
+      </c>
+      <c r="J449" t="n">
+        <v>85.95999908447266</v>
+      </c>
+      <c r="K449" t="n">
+        <v>213084</v>
+      </c>
+      <c r="L449" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>Shah Alloys Ltd. Share Price Up 8.77%: Price, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>Shah Alloys Ltd. Share Price Up 8.77%: Price, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>Shah Alloys Q1 Results: Net loss narrows to ₹2.07 crore as revenue falls 99% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr"/>
+      <c r="Q449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>9</v>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>AASTHA.NS</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Aastha Spintex Limited</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>88.37000274658203</v>
+      </c>
+      <c r="F450" t="n">
+        <v>88.37000274658203</v>
+      </c>
+      <c r="G450" t="n">
+        <v>88.36000061035156</v>
+      </c>
+      <c r="H450" t="n">
+        <v>88.36000061035156</v>
+      </c>
+      <c r="I450" t="n">
+        <v>80.33999633789062</v>
+      </c>
+      <c r="J450" t="n">
+        <v>88.36000061035156</v>
+      </c>
+      <c r="K450" t="n">
+        <v>2787073</v>
+      </c>
+      <c r="L450" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>Aastha Spintex shares extend rise to 3rd day, hit upper circuit; check details - TradingView</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>Aastha Spintex shares extend rise to 3rd day, hit upper circuit; check details - TradingView</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>Aastha Spintex: Announced 1:1 Bonus Shares; What’s Next? - Investing.com India</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>Aastha Spintex Share Price News: Rs 88.42 and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>Textile stock under ₹100 hits 10% upper circuit after declaration of final dividend move | Details here - Livemint</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>10</v>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>WHIRLPOOL.NS</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Whirlpool of India Limited</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>777.8499755859375</v>
+      </c>
+      <c r="F451" t="n">
+        <v>858.7000122070312</v>
+      </c>
+      <c r="G451" t="n">
+        <v>772</v>
+      </c>
+      <c r="H451" t="n">
+        <v>841.1500244140625</v>
+      </c>
+      <c r="I451" t="n">
+        <v>771.7000122070312</v>
+      </c>
+      <c r="J451" t="n">
+        <v>841.1500244140625</v>
+      </c>
+      <c r="K451" t="n">
+        <v>5451720</v>
+      </c>
+      <c r="L451" t="n">
+        <v>9</v>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>Whirlpool stock trades close to 12-month low as guidance stays cautious - Ad-hoc-news.de</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>Whirlpool stock trades close to 12-month low as guidance stays cautious - Ad-hoc-news.de</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>Don't Race Out To Buy Whirlpool of India Limited (NSE:WHIRLPOOL) Just Because It's Going Ex-Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>Whirlpool Abandoned Its Global Ambitions. Now It’s in a World of Hurt. - WSJ</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>Wells Fargo initiates Whirlpool stock coverage at Equal Weight - Investing.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>11</v>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>POLYSPIN.NS</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Polyspin Exports Limited</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>29</v>
+      </c>
+      <c r="F452" t="n">
+        <v>31.93000030517578</v>
+      </c>
+      <c r="G452" t="n">
+        <v>28</v>
+      </c>
+      <c r="H452" t="n">
+        <v>31.93000030517578</v>
+      </c>
+      <c r="I452" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="J452" t="n">
+        <v>31.93000030517578</v>
+      </c>
+      <c r="K452" t="n">
+        <v>114</v>
+      </c>
+      <c r="L452" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>Polyspin Exports appoints Durga Ramji as MD at 41st AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>Polyspin Exports appoints Durga Ramji as MD at 41st AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>Polyspin Exports reports ₹390.04 Lakhs net profit in FY26, sets Aug 21 AGM date - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>Polyspin Exports consolidated net profit rises 7.14% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>Shubham Polyspin Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>12</v>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>CLEANMAX.NS</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Clean Max Enviro Energy Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>1182.300048828125</v>
+      </c>
+      <c r="F453" t="n">
+        <v>1283.5</v>
+      </c>
+      <c r="G453" t="n">
+        <v>1182.300048828125</v>
+      </c>
+      <c r="H453" t="n">
+        <v>1274.599975585938</v>
+      </c>
+      <c r="I453" t="n">
+        <v>1182.300048828125</v>
+      </c>
+      <c r="J453" t="n">
+        <v>1274.599975585938</v>
+      </c>
+      <c r="K453" t="n">
+        <v>285446</v>
+      </c>
+      <c r="L453" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>33,933,666 Equity Shares of Clean Max Enviro Energy Solutions Limited are subject to a Lock-Up Agreement Ending on 26-AUG-2026. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>33,933,666 Equity Shares of Clean Max Enviro Energy Solutions Limited are subject to a Lock-Up Agreement Ending on 26-AUG-2026. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>Renewable stock to buy: Recent debutant in bear grip after multibagger rise; Ventura sees 55% rally - Business Today</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>After muted listing, this stock turns multibagger in just 3 months; should you still buy? - Business Today</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>Clean Max Enviro Energy Solutions Allots 35,800 Equity Shares Under ESOS - SolarQuarter</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>13</v>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>NEXTMEDIA.NS</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Next Mediaworks Limited</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F454" t="n">
+        <v>3.940000057220459</v>
+      </c>
+      <c r="G454" t="n">
+        <v>3.609999895095825</v>
+      </c>
+      <c r="H454" t="n">
+        <v>3.849999904632568</v>
+      </c>
+      <c r="I454" t="n">
+        <v>3.579999923706055</v>
+      </c>
+      <c r="J454" t="n">
+        <v>3.849999904632568</v>
+      </c>
+      <c r="K454" t="n">
+        <v>21424</v>
+      </c>
+      <c r="L454" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>Next Mediaworks schedules 45th AGM for Sep 22 via video conference - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>Next Mediaworks Schedules Virtual AGM to Approve FY26 Results and Director Reappointment - TipRanks</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>Next Mediaworks Schedules Virtual AGM to Approve FY26 Results and Director Reappointment - TipRanks</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr"/>
+      <c r="Q454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>14</v>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>AZADIND.NS</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Azad India Mobility Limited</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>92</v>
+      </c>
+      <c r="F455" t="n">
+        <v>98.90000152587891</v>
+      </c>
+      <c r="G455" t="n">
+        <v>89.94999694824219</v>
+      </c>
+      <c r="H455" t="n">
+        <v>96.80000305175781</v>
+      </c>
+      <c r="I455" t="n">
+        <v>90.02999877929688</v>
+      </c>
+      <c r="J455" t="n">
+        <v>96.80000305175781</v>
+      </c>
+      <c r="K455" t="n">
+        <v>11894</v>
+      </c>
+      <c r="L455" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>Azad India Mobility Limited Provides Earnings Guidance for the Year 2027 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>Azad India Mobility (NSE:AZADIND) Cyclically Adjusted PS Ra - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>Azad India Mobility (NSE:AZADIND) Cyclically Adjusted PS Ra - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>Azad India Mobility (NSE:AZADIND) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>Azad India Mobility (NSE:AZADIND) Cyclically Adjusted Price-to-FCF : (As of Aug. 25, 2026) - GuruFocus</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>15</v>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>BIRLAPREC.NS</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>43.5099983215332</v>
+      </c>
+      <c r="F456" t="n">
+        <v>47.79999923706055</v>
+      </c>
+      <c r="G456" t="n">
+        <v>43.5099983215332</v>
+      </c>
+      <c r="H456" t="n">
+        <v>47.36999893188477</v>
+      </c>
+      <c r="I456" t="n">
+        <v>44.11999893188477</v>
+      </c>
+      <c r="J456" t="n">
+        <v>47.36999893188477</v>
+      </c>
+      <c r="K456" t="n">
+        <v>436976</v>
+      </c>
+      <c r="L456" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies (BIRLAPREC.NS): Stock Eases Marginally, Nears Key Support Level - Symmetrical Triangle - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Mar 2026 Earnings: Steady EPS Delivery Amid Modest Revenue Performance - Tangible Book Value - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Gains 2.37%: Testing Key Resistance Levels (BIRLAPREC.NS) - Double Top - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>BIRLAPREC.NS Mar 2026 Earnings: Marginal EPS of ₹0.39 on Modest Revenue of ₹63.91 crore; Stock Slides 0.71% - ROA Comparison - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Trades Flat with Marginal Decline; Support at ₹35.62 Holds Key - Risk Reversal - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>16</v>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>MOHITIND.NS</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Mohit Industries Limited</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>23.05999946594238</v>
+      </c>
+      <c r="F457" t="n">
+        <v>25.85000038146973</v>
+      </c>
+      <c r="G457" t="n">
+        <v>23.05999946594238</v>
+      </c>
+      <c r="H457" t="n">
+        <v>25.06999969482422</v>
+      </c>
+      <c r="I457" t="n">
+        <v>23.47999954223633</v>
+      </c>
+      <c r="J457" t="n">
+        <v>25.06999969482422</v>
+      </c>
+      <c r="K457" t="n">
+        <v>36059</v>
+      </c>
+      <c r="L457" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>Mohit Industries updates contact details of key managerial personnel - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>Mohit Industries updates contact details of key managerial personnel - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr"/>
+      <c r="P457" t="inlineStr"/>
+      <c r="Q457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>17</v>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>MENNPIS.NS</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Menon Pistons Limited</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>69.91000366210938</v>
+      </c>
+      <c r="F458" t="n">
+        <v>75.59999847412109</v>
+      </c>
+      <c r="G458" t="n">
+        <v>69.91000366210938</v>
+      </c>
+      <c r="H458" t="n">
+        <v>74.58999633789062</v>
+      </c>
+      <c r="I458" t="n">
+        <v>69.88999938964844</v>
+      </c>
+      <c r="J458" t="n">
+        <v>74.58999633789062</v>
+      </c>
+      <c r="K458" t="n">
+        <v>125327</v>
+      </c>
+      <c r="L458" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>MENNPIS Stock Price and Chart — NSE:MENNPIS - TradingView</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>MENNPIS Mar 2026 Earnings: Revenue at ₹60.2 Crore, EPS of ₹0.77; Stock Declines 2.1% - Revenue Surprise History - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>Menon Pistons (MENNPIS.NS) Gains 3% as Price Approaches Key Resistance - Sector Leader Stocks - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>Menon Pistons Limited (MENNPIS.NS): Navigating a Mild Pullback Near Support - Iceberg Order - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>MENNPIS Mar 2026 Earnings: Revenue at ₹60.2 Crore, EPS of ₹0.77; Stock Declines 2.1% - Revenue Surprise History - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>18</v>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>MOSCHIP.NS</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Moschip Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>206</v>
+      </c>
+      <c r="F459" t="n">
+        <v>224</v>
+      </c>
+      <c r="G459" t="n">
+        <v>206</v>
+      </c>
+      <c r="H459" t="n">
+        <v>219.3600006103516</v>
+      </c>
+      <c r="I459" t="n">
+        <v>205.5399932861328</v>
+      </c>
+      <c r="J459" t="n">
+        <v>219.3600006103516</v>
+      </c>
+      <c r="K459" t="n">
+        <v>17472466</v>
+      </c>
+      <c r="L459" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>Moschip Tech Consolidated June 2026 Net Sales at Rs 116.21 crore, down 14.29% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>Moschip Tech Consolidated June 2026 Net Sales at Rs 116.21 crore, down 14.29% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>Moschip Tech Standalone June 2026 Net Sales at Rs 101.15 crore, down 14.13% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr"/>
+      <c r="Q459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>19</v>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>VINCOFE.NS</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Vintage Coffee And Beverages Limited</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>164.1100006103516</v>
+      </c>
+      <c r="F460" t="n">
+        <v>179</v>
+      </c>
+      <c r="G460" t="n">
+        <v>164.1100006103516</v>
+      </c>
+      <c r="H460" t="n">
+        <v>174.6499938964844</v>
+      </c>
+      <c r="I460" t="n">
+        <v>164.0899963378906</v>
+      </c>
+      <c r="J460" t="n">
+        <v>174.6499938964844</v>
+      </c>
+      <c r="K460" t="n">
+        <v>9709137</v>
+      </c>
+      <c r="L460" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>VINCOFE Forecast — Price Target — Prediction for 2027 - TradingView</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>NCLT sanctions Vintage Coffee merger with subsidiaries - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>Vintage Coffee and Beverages' (NSE:VINCOFE) Earnings Might Be Weaker Than You Think - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>With EPS Growth And More, Vintage Coffee and Beverages (NSE:VINCOFE) Makes An Interesting Case - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>Vintage Coffee FY26 PAT Rises 80% to ₹72.19 Cr - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>20</v>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>HEADSUP.NS</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Heads UP Ventures Limited</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F461" t="n">
+        <v>6.980000019073486</v>
+      </c>
+      <c r="G461" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H461" t="n">
+        <v>6.869999885559082</v>
+      </c>
+      <c r="I461" t="n">
+        <v>6.460000038146973</v>
+      </c>
+      <c r="J461" t="n">
+        <v>6.869999885559082</v>
+      </c>
+      <c r="K461" t="n">
+        <v>8022</v>
+      </c>
+      <c r="L461" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>#HeadsUp: Water service shut off scheduled for Aug. 8 in Ethete for repairs - County 10</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>#HeadsUp: Water service shut off scheduled for Aug. 8 in Ethete for repairs - County 10</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr"/>
+      <c r="P461" t="inlineStr"/>
+      <c r="Q461" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27633,7 +28936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q441"/>
+  <dimension ref="A1:Q461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53319,7 +54622,6 @@
           <t>MannKind Corporation (MNKD) Declines 4.38% to $3.93 as Shares Approach Key Support - Put Spread Alert - vinanet.vn</t>
         </is>
       </c>
-      <c r="Q423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -53502,11 +54804,6 @@
       <c r="L426" t="n">
         <v>-6.07</v>
       </c>
-      <c r="M426" t="inlineStr"/>
-      <c r="N426" t="inlineStr"/>
-      <c r="O426" t="inlineStr"/>
-      <c r="P426" t="inlineStr"/>
-      <c r="Q426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -53916,7 +55213,6 @@
           <t>Simplex Realty (NSE:SIMPLXREA) Shiller PE Ratio : (As of Aug. 25, 2026) - GuruFocus</t>
         </is>
       </c>
-      <c r="Q432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -53981,7 +55277,6 @@
           <t>National Standard (India) sets Aug 28 date for 63rd AGM - scanx.trade</t>
         </is>
       </c>
-      <c r="Q433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -54115,7 +55410,6 @@
           <t>Superior Industrial Enterprises standalone profit rises 21.8% in Q1FY27 - scanx.trade</t>
         </is>
       </c>
-      <c r="Q435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -54249,7 +55543,6 @@
           <t>A B Infrabuild reports Q1 FY27 revenue of ₹7,625.1 lakh, a 25.9% increase YoY - Business Upturn</t>
         </is>
       </c>
-      <c r="Q437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -54524,6 +55817,1334 @@
       <c r="Q441" t="inlineStr">
         <is>
           <t>MPDL (NSE:MPDL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>1</v>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>WEL.NS</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Wonder Electricals Limited</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="F442" t="n">
+        <v>179.1999969482422</v>
+      </c>
+      <c r="G442" t="n">
+        <v>124.7399978637695</v>
+      </c>
+      <c r="H442" t="n">
+        <v>124.7399978637695</v>
+      </c>
+      <c r="I442" t="n">
+        <v>155.9199981689453</v>
+      </c>
+      <c r="J442" t="n">
+        <v>124.7399978637695</v>
+      </c>
+      <c r="K442" t="n">
+        <v>129564647</v>
+      </c>
+      <c r="L442" t="n">
+        <v>-20</v>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>Wonder Electricals Share Price: stock news and analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>Wonder Electricals Share Price: stock news and analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>Wonder Electricals Share Price Today: Market Cap and P/E - Univest</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>Btab uses artificial intelligence to link global manufacturers with U.S. business buyers - Stock Titan</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>Wonder Electricals Share Price Today With Valuation View - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>2</v>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>DAVANGERE.NS</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Davangere Sugar Company Limited</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>2.630000114440918</v>
+      </c>
+      <c r="F443" t="n">
+        <v>2.650000095367432</v>
+      </c>
+      <c r="G443" t="n">
+        <v>2.119999885559082</v>
+      </c>
+      <c r="H443" t="n">
+        <v>2.119999885559082</v>
+      </c>
+      <c r="I443" t="n">
+        <v>2.650000095367432</v>
+      </c>
+      <c r="J443" t="n">
+        <v>2.119999885559082</v>
+      </c>
+      <c r="K443" t="n">
+        <v>39331776</v>
+      </c>
+      <c r="L443" t="n">
+        <v>-20</v>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>Davangere Sugar Company Share Price Update and Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>Davangere Sugar Company Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>Davangere Sugar Company Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>Davangere Sugar to convert Rs 40.12 crore promoter loan into equity warrants, doubles authorised capital - ChiniMandi</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>Davangere Sugar Company allots 26.59 cr equity shares on conversion of FCCBs - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>3</v>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>ARCHIDPLY.NS</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Archidply Industries Limited</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>114.9499969482422</v>
+      </c>
+      <c r="F444" t="n">
+        <v>114.9899978637695</v>
+      </c>
+      <c r="G444" t="n">
+        <v>102.2600021362305</v>
+      </c>
+      <c r="H444" t="n">
+        <v>103.0400009155273</v>
+      </c>
+      <c r="I444" t="n">
+        <v>112.9400024414062</v>
+      </c>
+      <c r="J444" t="n">
+        <v>103.0400009155273</v>
+      </c>
+      <c r="K444" t="n">
+        <v>113516</v>
+      </c>
+      <c r="L444" t="n">
+        <v>-8.77</v>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>Archidply Ind Consolidated June 2026 Net Sales at Rs 189.01 crore, up 27.83% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>5 Plywood Stocks India 2026: Strong Future Roadmaps - Univest</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>Archidply Industries Ltd. Share Price Today: 10.14% Gain - Univest</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>Archidply Decor Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>Archidply Ind Standalone June 2026 Net Sales at Rs 140.12 crore, up 17.42% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>4</v>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>UGARSUGAR.NS</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>The Ugar Sugar Works Limited</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>54.7599983215332</v>
+      </c>
+      <c r="F445" t="n">
+        <v>55.90000152587891</v>
+      </c>
+      <c r="G445" t="n">
+        <v>50.15000152587891</v>
+      </c>
+      <c r="H445" t="n">
+        <v>50.70000076293945</v>
+      </c>
+      <c r="I445" t="n">
+        <v>54.97000122070312</v>
+      </c>
+      <c r="J445" t="n">
+        <v>50.70000076293945</v>
+      </c>
+      <c r="K445" t="n">
+        <v>757395</v>
+      </c>
+      <c r="L445" t="n">
+        <v>-7.77</v>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>UGARSUGAR Share Price Rise: Fundamentals and Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>UGARSUGAR Share Price Rise: Fundamentals and Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>UGARSUGAR Share Price Today - The Ugar Sugar Works Ltd. Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>The Ugar Sugar Works Ltd. Share Price Today: Key Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>The Ugar Sugar Works Share Price Today: 9.09% Price Rise - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>5</v>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>MOLBIO.NS</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Molbio Diagnostics Limited</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>1234</v>
+      </c>
+      <c r="F446" t="n">
+        <v>1243.699951171875</v>
+      </c>
+      <c r="G446" t="n">
+        <v>1130.099975585938</v>
+      </c>
+      <c r="H446" t="n">
+        <v>1144.150024414062</v>
+      </c>
+      <c r="I446" t="n">
+        <v>1238.849975585938</v>
+      </c>
+      <c r="J446" t="n">
+        <v>1144.150024414062</v>
+      </c>
+      <c r="K446" t="n">
+        <v>1151150</v>
+      </c>
+      <c r="L446" t="n">
+        <v>-7.64</v>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>Solid debut! Molbio Diagnostics shares list at 21% premium over IPO price - Business Standard</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>MOLBIO Share Price Today - MOLBIO DIAGNOSTICS LTD Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>Molbio Diagnostics' shares jump over 21 pc in market debut trade - ET HealthWorld</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>Molbio Diagnostics IPO listing: Shares debut at 21% premium at ₹980 - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>Molbio Diagnostics IPO: Price, Dates, P/E Ratio &amp; How to Apply - INDmoney</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>6</v>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>ALOKINDS.NS</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Alok Industries Limited</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>11.35000038146973</v>
+      </c>
+      <c r="F447" t="n">
+        <v>11.35000038146973</v>
+      </c>
+      <c r="G447" t="n">
+        <v>9.550000190734863</v>
+      </c>
+      <c r="H447" t="n">
+        <v>10.43000030517578</v>
+      </c>
+      <c r="I447" t="n">
+        <v>11.27999973297119</v>
+      </c>
+      <c r="J447" t="n">
+        <v>10.43000030517578</v>
+      </c>
+      <c r="K447" t="n">
+        <v>59972039</v>
+      </c>
+      <c r="L447" t="n">
+        <v>-7.54</v>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>Alok Industries (NSE:ALOKINDS) shareholder returns have been , earning 28% in 3 years - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>Alok Industries Stock In Focus After Reporting 6% YoY Revenue Growth In Q1 - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>Alok Industries (ALOKINDS.NS) Maintains Upward Bias as Price Holds Above Key Support - Fibonacci Extension - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>Alok Industries Limited Schedules Board Meeting for April 16, 2026 to Review Q4FY26 and FY26 Audited Financial Results - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>Alok Industries Limited: Price Gains Momentum Toward Resistance at ₹13.26 - Monthly Profile - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>7</v>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>SHANTIGOLD.NS</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Shanti Gold International Limited</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>258.8999938964844</v>
+      </c>
+      <c r="F448" t="n">
+        <v>259.989990234375</v>
+      </c>
+      <c r="G448" t="n">
+        <v>242.5</v>
+      </c>
+      <c r="H448" t="n">
+        <v>246.0500030517578</v>
+      </c>
+      <c r="I448" t="n">
+        <v>266.0700073242188</v>
+      </c>
+      <c r="J448" t="n">
+        <v>246.0500030517578</v>
+      </c>
+      <c r="K448" t="n">
+        <v>8498549</v>
+      </c>
+      <c r="L448" t="n">
+        <v>-7.52</v>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>Shanti Gold International Limited Right 2026-21.08.26 For Shares - TradingView</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>Shanti Gold International Limited Right 2026-21.08.26 For Shares - TradingView</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>Shanti Gold International Limited Right 2026-21.08.26 For Shares Revenue Breakdown – NSE:SHANTI_RE - TradingView</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>Shanti Gold International Limited Right 2026-21.08.26 For Shares Earnings and Revenue – NSE:SHANTI_RE - TradingView</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>8</v>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>BOHRAIND.NS</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Bohra Industries Limited</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>13.98999977111816</v>
+      </c>
+      <c r="F449" t="n">
+        <v>14.73999977111816</v>
+      </c>
+      <c r="G449" t="n">
+        <v>12.72999954223633</v>
+      </c>
+      <c r="H449" t="n">
+        <v>12.85000038146973</v>
+      </c>
+      <c r="I449" t="n">
+        <v>13.85999965667725</v>
+      </c>
+      <c r="J449" t="n">
+        <v>12.85000038146973</v>
+      </c>
+      <c r="K449" t="n">
+        <v>90454</v>
+      </c>
+      <c r="L449" t="n">
+        <v>-7.29</v>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>Bohra Industries (BOHRAIND.NS) Edges Higher, Holds Near Key Support Level - Buyback Factor - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>Bohra Industries accepts resignation of director effective July 11 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>Bohra Industries accepts resignation of director effective July 11 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>BOHRA INDUSTRIES LIMITED Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>Bohra Industries (BOHRAIND.NS) Slides 1.82% as Price Approaches Key Support at ₹15.39 - Upthrust Pattern - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>9</v>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>DHAMPURSUG.NS</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Limited</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>186</v>
+      </c>
+      <c r="F450" t="n">
+        <v>186.1999969482422</v>
+      </c>
+      <c r="G450" t="n">
+        <v>170.1000061035156</v>
+      </c>
+      <c r="H450" t="n">
+        <v>170.9199981689453</v>
+      </c>
+      <c r="I450" t="n">
+        <v>183.6699981689453</v>
+      </c>
+      <c r="J450" t="n">
+        <v>170.9199981689453</v>
+      </c>
+      <c r="K450" t="n">
+        <v>1242517</v>
+      </c>
+      <c r="L450" t="n">
+        <v>-6.94</v>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Ltd. Share Price Gains in Small Cap Move - Univest</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Ltd. Share Price Gains in Small Cap Move - Univest</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Limited Submits Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills sets book closure dates for 91st AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Ltd. Share Price: 52-Week High Focus - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>10</v>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>KIRIINDUS.NS</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Kiri Industries Limited</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>514</v>
+      </c>
+      <c r="F451" t="n">
+        <v>518.8499755859375</v>
+      </c>
+      <c r="G451" t="n">
+        <v>473.1499938964844</v>
+      </c>
+      <c r="H451" t="n">
+        <v>481.1000061035156</v>
+      </c>
+      <c r="I451" t="n">
+        <v>516.2000122070312</v>
+      </c>
+      <c r="J451" t="n">
+        <v>481.1000061035156</v>
+      </c>
+      <c r="K451" t="n">
+        <v>1021899</v>
+      </c>
+      <c r="L451" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>Kiri Industries Ltd. Share Price Today Up 8.18%: Stock News - Univest</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>Kiri Industries Share Price rises 9.56%: valuation view - Univest</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>Kiri Industries Share Price rises 9.56%: valuation view - Univest</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr"/>
+      <c r="Q451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>11</v>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>SILLYMONKS.NS</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Silly Monks Entertainment Limited</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>16.63999938964844</v>
+      </c>
+      <c r="F452" t="n">
+        <v>16.63999938964844</v>
+      </c>
+      <c r="G452" t="n">
+        <v>15.35000038146973</v>
+      </c>
+      <c r="H452" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="I452" t="n">
+        <v>16.57999992370605</v>
+      </c>
+      <c r="J452" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="K452" t="n">
+        <v>45633</v>
+      </c>
+      <c r="L452" t="n">
+        <v>-6.51</v>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>Synthetic (GJH): Settles Near the Prior Close at $9.45 on the Day; Levels: the Price Remains Bounded by the Supplied Support and Resistance in Latest Trading - RVOL Spike - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>Synthetic (GJH): Settles Near the Prior Close at $9.45 on the Day; Levels: the Price Remains Bounded by the Supplied Support and Resistance in Latest Trading - RVOL Spike - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr"/>
+      <c r="P452" t="inlineStr"/>
+      <c r="Q452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>12</v>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>KJMCFIN.NS</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>72.94999694824219</v>
+      </c>
+      <c r="F453" t="n">
+        <v>72.94999694824219</v>
+      </c>
+      <c r="G453" t="n">
+        <v>66.41000366210938</v>
+      </c>
+      <c r="H453" t="n">
+        <v>69.11000061035156</v>
+      </c>
+      <c r="I453" t="n">
+        <v>73.77999877929688</v>
+      </c>
+      <c r="J453" t="n">
+        <v>69.11000061035156</v>
+      </c>
+      <c r="K453" t="n">
+        <v>7457</v>
+      </c>
+      <c r="L453" t="n">
+        <v>-6.33</v>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services (NSE:KJMCFIN) Cyclically Adjusted P - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services (NSE:KJMCFIN) Cyclically Adjusted P - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services net profit rises to ₹162.85 lakh in Q1FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services (NSE:KJMCFIN) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>13</v>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>CLSEL.NS</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Chaman Lal Setia Exports Limited</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>313.2000122070312</v>
+      </c>
+      <c r="F454" t="n">
+        <v>313.3500061035156</v>
+      </c>
+      <c r="G454" t="n">
+        <v>294.0499877929688</v>
+      </c>
+      <c r="H454" t="n">
+        <v>295.2000122070312</v>
+      </c>
+      <c r="I454" t="n">
+        <v>313.2000122070312</v>
+      </c>
+      <c r="J454" t="n">
+        <v>295.2000122070312</v>
+      </c>
+      <c r="K454" t="n">
+        <v>258000</v>
+      </c>
+      <c r="L454" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>CLSEL Share Price Rise: Market Cap, EPS and ROE Snapshot - Univest</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>CLSEL Share Price Rise: Market Cap, EPS and ROE Snapshot - Univest</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr"/>
+      <c r="P454" t="inlineStr"/>
+      <c r="Q454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>14</v>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>LCL.NS</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Lohia Corp Limited</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>594.9000244140625</v>
+      </c>
+      <c r="F455" t="n">
+        <v>594.9000244140625</v>
+      </c>
+      <c r="G455" t="n">
+        <v>562.3499755859375</v>
+      </c>
+      <c r="H455" t="n">
+        <v>566</v>
+      </c>
+      <c r="I455" t="n">
+        <v>598.2000122070312</v>
+      </c>
+      <c r="J455" t="n">
+        <v>566</v>
+      </c>
+      <c r="K455" t="n">
+        <v>377423</v>
+      </c>
+      <c r="L455" t="n">
+        <v>-5.38</v>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>LOHIA CORP LIMITED Share Price Hits One-Year High Today - Univest</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>Lohia Corp Files Q1 FY27 Earnings Call Transcript With Exchanges - TipRanks</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>Lohia Corp Ltd Share Price Today,, LCL Share Price NSE, BSE - Business Today</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>Lohia Corp IPO - Check Allotment Status, Listing Date, Listing Price - Groww</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>Lohia Corp Shares List At Over 8% Premium On NSE - fintechbiznews.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>15</v>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>OPTIFIN.NS</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Optimus Finance Limited</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>13.9399995803833</v>
+      </c>
+      <c r="F456" t="n">
+        <v>13.9399995803833</v>
+      </c>
+      <c r="G456" t="n">
+        <v>12.89999961853027</v>
+      </c>
+      <c r="H456" t="n">
+        <v>13.09000015258789</v>
+      </c>
+      <c r="I456" t="n">
+        <v>13.81999969482422</v>
+      </c>
+      <c r="J456" t="n">
+        <v>13.09000015258789</v>
+      </c>
+      <c r="K456" t="n">
+        <v>50770</v>
+      </c>
+      <c r="L456" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>OPTIFIN Stock Price and Chart — NSE:OPTIFIN - TradingView</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>Optimus Finance appoints Kheradia as director, new auditor - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>Optimus Finance Limited: Shareholders Board Members Managers and Company Profile | INE031G01022 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>Optimus Finance shares permitted to trade on NSE from August 17 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>Optimus Finance (NSE:OPTIFIN) Cyclically Adjusted PB Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>16</v>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>RAMCOCEM.NS</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>The Ramco Cements Limited</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>943</v>
+      </c>
+      <c r="F457" t="n">
+        <v>943</v>
+      </c>
+      <c r="G457" t="n">
+        <v>890.3499755859375</v>
+      </c>
+      <c r="H457" t="n">
+        <v>892.5499877929688</v>
+      </c>
+      <c r="I457" t="n">
+        <v>940.6500244140625</v>
+      </c>
+      <c r="J457" t="n">
+        <v>892.5499877929688</v>
+      </c>
+      <c r="K457" t="n">
+        <v>706080</v>
+      </c>
+      <c r="L457" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>The Ramco Cements Limited (NSE:RAMCOCEM) Pays A ₹2.50 Dividend In Just Three Days - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>The Ramco Cements Share Price rise: valuation and peers - Univest</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>The Ramco Cements Ltd. Share Price Declines: August 5, 2026 - Univest</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>The Ramco Cements Share Price rise: valuation and peers - Univest</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>Ramco Cements Details Virtual 68th Annual General Meeting Proceedings - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>17</v>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>MODIS.NS</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Modis Navnirman Limited</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>402.1000061035156</v>
+      </c>
+      <c r="F458" t="n">
+        <v>404</v>
+      </c>
+      <c r="G458" t="n">
+        <v>377.3999938964844</v>
+      </c>
+      <c r="H458" t="n">
+        <v>379.7000122070312</v>
+      </c>
+      <c r="I458" t="n">
+        <v>399.8999938964844</v>
+      </c>
+      <c r="J458" t="n">
+        <v>379.7000122070312</v>
+      </c>
+      <c r="K458" t="n">
+        <v>216453</v>
+      </c>
+      <c r="L458" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>Modis Navnirman Consolidated June 2026 Net Sales at Rs 58.26 crore, up 27.92% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>Modis Navnirman Consolidated June 2026 Net Sales at Rs 58.26 crore, up 27.92% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>Modis Navnirman Standalone June 2026 Net Sales at Rs 58.26 crore, up 27.92% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>Modis Navnirman Share Price Target 2027 to 2030: Analyst Outlook - Univest</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>Modis Navnirman hosts Q1 FY27 earnings call on Aug 10 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>18</v>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>NATIONSTD.NS</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>National Standard (India) Limited</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>103.4400024414062</v>
+      </c>
+      <c r="F459" t="n">
+        <v>107.4499969482422</v>
+      </c>
+      <c r="G459" t="n">
+        <v>103.4400024414062</v>
+      </c>
+      <c r="H459" t="n">
+        <v>103.4400024414062</v>
+      </c>
+      <c r="I459" t="n">
+        <v>108.879997253418</v>
+      </c>
+      <c r="J459" t="n">
+        <v>103.4400024414062</v>
+      </c>
+      <c r="K459" t="n">
+        <v>39226</v>
+      </c>
+      <c r="L459" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>National Standard (India) (NSE:NATIONSTD) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>National Standard (India) (NSE:NATIONSTD) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>National Standard files FY26 BRSR, reports 100% related-party sales - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr"/>
+      <c r="Q459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>19</v>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>NEAGI.NS</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Neelamalai Agro Industries Limited</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>3400</v>
+      </c>
+      <c r="F460" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G460" t="n">
+        <v>3306</v>
+      </c>
+      <c r="H460" t="n">
+        <v>3306</v>
+      </c>
+      <c r="I460" t="n">
+        <v>3480</v>
+      </c>
+      <c r="J460" t="n">
+        <v>3306</v>
+      </c>
+      <c r="K460" t="n">
+        <v>99</v>
+      </c>
+      <c r="L460" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>Neelamalai Agro Industries (NSE:NEAGI) Cyclically Adjusted PB Ratio : (As of Aug. 26, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>Neelamalai Agro Industries (NSE:NEAGI) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>Neelamalai Agro Industries (NSE:NEAGI) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr"/>
+      <c r="Q460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:30:33 IST</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>20</v>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>MYSORPETRO.NS</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>131.6499938964844</v>
+      </c>
+      <c r="F461" t="n">
+        <v>131.6499938964844</v>
+      </c>
+      <c r="G461" t="n">
+        <v>131.6499938964844</v>
+      </c>
+      <c r="H461" t="n">
+        <v>131.6499938964844</v>
+      </c>
+      <c r="I461" t="n">
+        <v>138.5700073242188</v>
+      </c>
+      <c r="J461" t="n">
+        <v>131.6499938964844</v>
+      </c>
+      <c r="K461" t="n">
+        <v>2605</v>
+      </c>
+      <c r="L461" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>MYSORPETRO Stock Price and Chart — NSE:MYSORPETRO - TradingView</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals: Denies Undisclosed Material Events Amidst Share Price Movement - InvestyWise</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals (NSE:MYSORPETRO) Cyclically Adjusted PB Ratio : (As of Aug. 20, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals (NSE:MYSORPETRO) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q461"/>
+  <dimension ref="A1:Q481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27805,8 +27805,6 @@
           <t>Ansal Buildwell Ltd - Equitypandit</t>
         </is>
       </c>
-      <c r="P444" t="inlineStr"/>
-      <c r="Q444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -28073,8 +28071,6 @@
           <t>INOX India Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
         </is>
       </c>
-      <c r="P448" t="inlineStr"/>
-      <c r="Q448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -28134,8 +28130,6 @@
           <t>Shah Alloys Q1 Results: Net loss narrows to ₹2.07 crore as revenue falls 99% - scanx.trade</t>
         </is>
       </c>
-      <c r="P449" t="inlineStr"/>
-      <c r="Q449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -28471,8 +28465,6 @@
           <t>Next Mediaworks Schedules Virtual AGM to Approve FY26 Results and Director Reappointment - TipRanks</t>
         </is>
       </c>
-      <c r="P454" t="inlineStr"/>
-      <c r="Q454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -28665,9 +28657,6 @@
           <t>Mohit Industries updates contact details of key managerial personnel - scanx.trade</t>
         </is>
       </c>
-      <c r="O457" t="inlineStr"/>
-      <c r="P457" t="inlineStr"/>
-      <c r="Q457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -28796,8 +28785,6 @@
           <t>Moschip Tech Standalone June 2026 Net Sales at Rs 101.15 crore, down 14.13% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
-      <c r="P459" t="inlineStr"/>
-      <c r="Q459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -28921,9 +28908,1346 @@
           <t>#HeadsUp: Water service shut off scheduled for Aug. 8 in Ethete for repairs - County 10</t>
         </is>
       </c>
-      <c r="O461" t="inlineStr"/>
-      <c r="P461" t="inlineStr"/>
-      <c r="Q461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>1</v>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>NIRAJISPAT.NS</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Niraj Ispat Industries Limited</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>286</v>
+      </c>
+      <c r="F462" t="n">
+        <v>295.8999938964844</v>
+      </c>
+      <c r="G462" t="n">
+        <v>278.989990234375</v>
+      </c>
+      <c r="H462" t="n">
+        <v>295.8999938964844</v>
+      </c>
+      <c r="I462" t="n">
+        <v>246.5899963378906</v>
+      </c>
+      <c r="J462" t="n">
+        <v>295.8999938964844</v>
+      </c>
+      <c r="K462" t="n">
+        <v>3053</v>
+      </c>
+      <c r="L462" t="n">
+        <v>20</v>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr"/>
+      <c r="P462" t="inlineStr"/>
+      <c r="Q462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>2</v>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>XTRANET.NS</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>165</v>
+      </c>
+      <c r="F463" t="n">
+        <v>197.1100006103516</v>
+      </c>
+      <c r="G463" t="n">
+        <v>163</v>
+      </c>
+      <c r="H463" t="n">
+        <v>197.1100006103516</v>
+      </c>
+      <c r="I463" t="n">
+        <v>164.2599945068359</v>
+      </c>
+      <c r="J463" t="n">
+        <v>197.1100006103516</v>
+      </c>
+      <c r="K463" t="n">
+        <v>5428284</v>
+      </c>
+      <c r="L463" t="n">
+        <v>20</v>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>1,970,100 Equity Shares of Xtranet Technologies Limited are subject to a Lock-Up Agreement Ending on 26-AUG-2026. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>1,970,100 Equity Shares of Xtranet Technologies Limited are subject to a Lock-Up Agreement Ending on 26-AUG-2026. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies Ltd (XTRANET) Share Price - Business Today</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies releases Q1FY27 earnings call audio recording - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies Shares List at 7% Premium on NSE, Trim Early Gains Amid Profit Booking - India Infoline</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>3</v>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>PRECWIRE.NS</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Precision Wires India Limited</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>422.7999877929688</v>
+      </c>
+      <c r="F464" t="n">
+        <v>507.3500061035156</v>
+      </c>
+      <c r="G464" t="n">
+        <v>421.7000122070312</v>
+      </c>
+      <c r="H464" t="n">
+        <v>507.3500061035156</v>
+      </c>
+      <c r="I464" t="n">
+        <v>422.7999877929688</v>
+      </c>
+      <c r="J464" t="n">
+        <v>507.3500061035156</v>
+      </c>
+      <c r="K464" t="n">
+        <v>8561372</v>
+      </c>
+      <c r="L464" t="n">
+        <v>20</v>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>Should You Be Adding Precision Wires India (NSE:PRECWIRE) To Your Watchlist Today? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>Precision Wires India Ltd. (PRECWIRE) Share Price Hits Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>Precision Wires India Ltd. Share Price Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>Precision Wires India Limited Announces Chief Financial Officer Changes, Effective August 10, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>4</v>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>SHAHALLOYS.NS</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Shah Alloys Limited</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>89.01000213623047</v>
+      </c>
+      <c r="F465" t="n">
+        <v>103.1500015258789</v>
+      </c>
+      <c r="G465" t="n">
+        <v>87</v>
+      </c>
+      <c r="H465" t="n">
+        <v>103.1500015258789</v>
+      </c>
+      <c r="I465" t="n">
+        <v>85.95999908447266</v>
+      </c>
+      <c r="J465" t="n">
+        <v>103.1500015258789</v>
+      </c>
+      <c r="K465" t="n">
+        <v>1390956</v>
+      </c>
+      <c r="L465" t="n">
+        <v>20</v>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>Shah Alloys Share Price Today: Valuation and Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>Shah Alloys Q1 Results: Net loss narrows to ₹2.07 crore as revenue falls 99% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>Shah Alloys Ltd. Share Price Up 8.77%: Price, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>5</v>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>GVPTECH.NS</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>GVP Infotech Limited</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>7.880000114440918</v>
+      </c>
+      <c r="F466" t="n">
+        <v>9.029999732971191</v>
+      </c>
+      <c r="G466" t="n">
+        <v>7.869999885559082</v>
+      </c>
+      <c r="H466" t="n">
+        <v>9.029999732971191</v>
+      </c>
+      <c r="I466" t="n">
+        <v>7.53000020980835</v>
+      </c>
+      <c r="J466" t="n">
+        <v>9.029999732971191</v>
+      </c>
+      <c r="K466" t="n">
+        <v>1285327</v>
+      </c>
+      <c r="L466" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>GVP Infotech Limited (GVPTECH.NS) Mar 2026 Earnings: Negative EPS Amid Modest Revenue - EPS Surprise History - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>GVP Infotech Limited (GVPTECH) Gains 1.47%; Near Key Resistance at ₹7.23 - IPO Entry Watch - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>GVP Infotech Ltd (GVPTECH.NS) Modestly Declines as Stock Tests Support Near ₹7.0 Zone - Channel Breakout - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>GVP INFOTECH LIMITED Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>GVP Infotech Limited (GVPTECH) Gains 1.47%; Near Key Resistance at ₹7.23 - IPO Entry Watch - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>6</v>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>EXXARO.NS</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Exxaro Tiles Limited</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>6.199999809265137</v>
+      </c>
+      <c r="F467" t="n">
+        <v>7.420000076293945</v>
+      </c>
+      <c r="G467" t="n">
+        <v>6.199999809265137</v>
+      </c>
+      <c r="H467" t="n">
+        <v>7.409999847412109</v>
+      </c>
+      <c r="I467" t="n">
+        <v>6.190000057220459</v>
+      </c>
+      <c r="J467" t="n">
+        <v>7.409999847412109</v>
+      </c>
+      <c r="K467" t="n">
+        <v>12070592</v>
+      </c>
+      <c r="L467" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>Momentum Stocks: Next Mediaworks, Exxaro, Tejas Networks gains up to 19% on sheer momentum - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>Next Mediaworks, Exxaro Shares See Sharp Price Swings - Whalesbook</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>Exxaro Tiles Standalone June 2026 Net Sales at Rs 73.79 crore, up 16.85% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>Eskom supplier Exxaro crashes as robust rand and rising costs tear into profits - news24.com</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>Exxaro Tiles Consolidated June 2026 Net Sales at Rs 85.22 crore, up 31.26% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>7</v>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>MASTEK.NS</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Mastek Limited</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>1615</v>
+      </c>
+      <c r="F468" t="n">
+        <v>1933.900024414062</v>
+      </c>
+      <c r="G468" t="n">
+        <v>1615</v>
+      </c>
+      <c r="H468" t="n">
+        <v>1901.400024414062</v>
+      </c>
+      <c r="I468" t="n">
+        <v>1611.599975585938</v>
+      </c>
+      <c r="J468" t="n">
+        <v>1901.400024414062</v>
+      </c>
+      <c r="K468" t="n">
+        <v>5448423</v>
+      </c>
+      <c r="L468" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>Volume Gainers Today; SecMark, Exxaro Tiles And Mastek Lead Trading Surge asof 4:00 PM IST - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>Volume Gainers Today; SecMark, Exxaro Tiles And Mastek Lead Trading Surge asof 4:00 PM IST - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>Mid-cap IT stock jumps 19%; brokerage sees turnaround potential, here's what it said - Business Today</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>Glenmark Pharma, Mastek, Triveni Engineering Dividends: Last Day To Buy Shares To Qualify - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>Should You Buy Mastek Limited (NSE:MASTEK) For Its Upcoming Dividend? - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>8</v>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>IKIO.NS</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>IKIO Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>186.1399993896484</v>
+      </c>
+      <c r="F469" t="n">
+        <v>217.6999969482422</v>
+      </c>
+      <c r="G469" t="n">
+        <v>186.1399993896484</v>
+      </c>
+      <c r="H469" t="n">
+        <v>213.7200012207031</v>
+      </c>
+      <c r="I469" t="n">
+        <v>186.1399993896484</v>
+      </c>
+      <c r="J469" t="n">
+        <v>213.7200012207031</v>
+      </c>
+      <c r="K469" t="n">
+        <v>6393269</v>
+      </c>
+      <c r="L469" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-28 — cnbctv:5fd8494be094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-28 — cnbctv:5fd8494be094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>IKIO Share Price rise highlights valuation versus peers - Univest</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>IKIO Technologies holds investor meet on Aug 27, no UPSI shared - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>IKIO Tech Standalone June 2026 Net Sales at Rs 44.84 crore, up 15.9% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>9</v>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>OAL.NS</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Oriental Aromatics Limited</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>425</v>
+      </c>
+      <c r="F470" t="n">
+        <v>492.7000122070312</v>
+      </c>
+      <c r="G470" t="n">
+        <v>424</v>
+      </c>
+      <c r="H470" t="n">
+        <v>487.7999877929688</v>
+      </c>
+      <c r="I470" t="n">
+        <v>428.9500122070312</v>
+      </c>
+      <c r="J470" t="n">
+        <v>487.7999877929688</v>
+      </c>
+      <c r="K470" t="n">
+        <v>765462</v>
+      </c>
+      <c r="L470" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>Oriental Aromatics Q1 Results: Earnings Call Recording Available Online - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>Coal India incorporates Singapore-based wholly owned subsidiary; shares fall - Dailyhunt</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>Oriental Aromatics appoints Nitin Budhavalekar as VP Sales Fragrance - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>Oriental Aromatics crosses ₹1,000 crore revenue in FY26; declares ₹0.50 dividend - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>Oriental Aromatics profit surges 42% as margins recover sequentially - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>10</v>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>ASIANTNE.NS</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Asian Tea &amp; Exports Limited</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>9.899999618530273</v>
+      </c>
+      <c r="F471" t="n">
+        <v>10.98999977111816</v>
+      </c>
+      <c r="G471" t="n">
+        <v>9.720000267028809</v>
+      </c>
+      <c r="H471" t="n">
+        <v>10.89000034332275</v>
+      </c>
+      <c r="I471" t="n">
+        <v>9.649999618530273</v>
+      </c>
+      <c r="J471" t="n">
+        <v>10.89000034332275</v>
+      </c>
+      <c r="K471" t="n">
+        <v>58850</v>
+      </c>
+      <c r="L471" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>Asian Tea &amp; Exports Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>Asian Tea &amp; Exports Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr"/>
+      <c r="P471" t="inlineStr"/>
+      <c r="Q471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>11</v>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>ODYCORP.NS</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Odyssey Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>7.590000152587891</v>
+      </c>
+      <c r="F472" t="n">
+        <v>8.479999542236328</v>
+      </c>
+      <c r="G472" t="n">
+        <v>6.980000019073486</v>
+      </c>
+      <c r="H472" t="n">
+        <v>7.980000019073486</v>
+      </c>
+      <c r="I472" t="n">
+        <v>7.099999904632568</v>
+      </c>
+      <c r="J472" t="n">
+        <v>7.980000019073486</v>
+      </c>
+      <c r="K472" t="n">
+        <v>105386</v>
+      </c>
+      <c r="L472" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>Odyssey Corporation Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>Odyssey (NSE:ODYCORP) Cyclically Adjusted PB Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>Odyssey (NSE:ODYCORP) Cyclically Adjusted PB Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>Odyssey Corp. Ltd. (ODYCORP) Fundamental and Financial Data - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>You were invited to TradingView - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>12</v>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>MOHITE.NS</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Mohite Industries Limited</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>2.640000104904175</v>
+      </c>
+      <c r="F473" t="n">
+        <v>3.160000085830688</v>
+      </c>
+      <c r="G473" t="n">
+        <v>2.599999904632568</v>
+      </c>
+      <c r="H473" t="n">
+        <v>2.950000047683716</v>
+      </c>
+      <c r="I473" t="n">
+        <v>2.640000104904175</v>
+      </c>
+      <c r="J473" t="n">
+        <v>2.950000047683716</v>
+      </c>
+      <c r="K473" t="n">
+        <v>838557</v>
+      </c>
+      <c r="L473" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>Mohite Industries Ltd. Financials – Balance Sheet, Profit &amp; Loss, Cash Flow - Value Research</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>Mohite Industries Q1 Results: Net loss widens 142% YoY to ₹245.62 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>13</v>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>KALYANIFRG.NS</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Kalyani Forge Limited</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>679.2999877929688</v>
+      </c>
+      <c r="F474" t="n">
+        <v>784.5</v>
+      </c>
+      <c r="G474" t="n">
+        <v>672.0499877929688</v>
+      </c>
+      <c r="H474" t="n">
+        <v>761.9500122070312</v>
+      </c>
+      <c r="I474" t="n">
+        <v>682.4500122070312</v>
+      </c>
+      <c r="J474" t="n">
+        <v>761.9500122070312</v>
+      </c>
+      <c r="K474" t="n">
+        <v>14669</v>
+      </c>
+      <c r="L474" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>Kalyani Forge makes Q1 FY27 investor meet recordings available online - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>Kalyani Forge Q1FY27 Results: Net profit up 218% YoY to ₹4.48 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>Kalyani Forge Q1FY27 Results: Net profit up 218% YoY to ₹4.48 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr"/>
+      <c r="Q474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>14</v>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>KAPSTON.NS</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Kapston Services Limited</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>504.7000122070312</v>
+      </c>
+      <c r="F475" t="n">
+        <v>566.4000244140625</v>
+      </c>
+      <c r="G475" t="n">
+        <v>504.7000122070312</v>
+      </c>
+      <c r="H475" t="n">
+        <v>559.2000122070312</v>
+      </c>
+      <c r="I475" t="n">
+        <v>501</v>
+      </c>
+      <c r="J475" t="n">
+        <v>559.2000122070312</v>
+      </c>
+      <c r="K475" t="n">
+        <v>242587</v>
+      </c>
+      <c r="L475" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>Kapston Services Share Price Today: Price Fall Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>Kapston Service Consolidated June 2026 Net Sales at Rs 221.66 crore, up 16.23% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>Kapston Services Ltd. Stock News: Share Price Jumps 8.87% - Univest</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>Kapston Services Ltd. Share Price Today Near Yearly High - Univest</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>Kapston Service Consolidated June 2026 Net Sales at Rs 221.66 crore, up 16.23% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>15</v>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>VADILENT.NS</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Vadilal Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>9700</v>
+      </c>
+      <c r="F476" t="n">
+        <v>11754</v>
+      </c>
+      <c r="G476" t="n">
+        <v>9700</v>
+      </c>
+      <c r="H476" t="n">
+        <v>10833</v>
+      </c>
+      <c r="I476" t="n">
+        <v>9795</v>
+      </c>
+      <c r="J476" t="n">
+        <v>10833</v>
+      </c>
+      <c r="K476" t="n">
+        <v>298</v>
+      </c>
+      <c r="L476" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>VADILENT Stock Price and Chart — NSE:VADILENT - TradingView</t>
+        </is>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>IVG Trust acquired 10.64% stake in Vadilal Enterprises Limited from Virendra Ramchandra Gandhi. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>IVG Trust acquired 10.64% stake in Vadilal Enterprises Limited from Virendra Ramchandra Gandhi. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>Vadilal Enterprises (NSE:VADILENT) Cyclically Adjusted Pric - GuruFocus</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>Vadilal Enterprises (NSE:VADILENT) Cyclically Adjusted PB R - GuruFocus</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B477" t="n">
+        <v>16</v>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>FMGOETZE.NS</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Federal-Mogul Goetze (India) Limited.</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>576.1500244140625</v>
+      </c>
+      <c r="F477" t="n">
+        <v>614.7999877929688</v>
+      </c>
+      <c r="G477" t="n">
+        <v>561.9500122070312</v>
+      </c>
+      <c r="H477" t="n">
+        <v>602.0499877929688</v>
+      </c>
+      <c r="I477" t="n">
+        <v>545.5499877929688</v>
+      </c>
+      <c r="J477" t="n">
+        <v>602.0499877929688</v>
+      </c>
+      <c r="K477" t="n">
+        <v>18184889</v>
+      </c>
+      <c r="L477" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>FMGOETZE Share Price Today: Stock News and Peer Context - Univest</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>Rs.94 dividend declared after 25 years; share price jumps nearly 10% - Record date fixed | Do you own? - TradingView</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-28 — cnbctv:a82234c70094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>Federal-Mogul Goetze (India) Share Price at 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>Rs.94 dividend declared after 25 years; share price jumps nearly 10% - Record date fixed | Do you own? - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>17</v>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>KSR.NS</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>KSR Footwear Limited</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F478" t="n">
+        <v>31.43000030517578</v>
+      </c>
+      <c r="G478" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="H478" t="n">
+        <v>31.42000007629395</v>
+      </c>
+      <c r="I478" t="n">
+        <v>28.57999992370605</v>
+      </c>
+      <c r="J478" t="n">
+        <v>31.42000007629395</v>
+      </c>
+      <c r="K478" t="n">
+        <v>329368</v>
+      </c>
+      <c r="L478" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>KSR Footwear Ltd Locks at Upper Circuit With 9.97% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>KSR Footwear Ltd Locks at Upper Circuit With 9.97% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>KSR Footwear AGM passes FY26 results; promoters vote 100% in favour - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>KSR Footwear Standalone June 2026 Net Sales at Rs 52.25 crore, up 0.36% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>KSR Footwear authorizes KMPs to decide disclosure materiality - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>18</v>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>SHRIKRISH.NS</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Shri Krishna Devcon Limited</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="F479" t="n">
+        <v>42.86999893188477</v>
+      </c>
+      <c r="G479" t="n">
+        <v>35.59999847412109</v>
+      </c>
+      <c r="H479" t="n">
+        <v>39.90000152587891</v>
+      </c>
+      <c r="I479" t="n">
+        <v>36.54999923706055</v>
+      </c>
+      <c r="J479" t="n">
+        <v>39.90000152587891</v>
+      </c>
+      <c r="K479" t="n">
+        <v>3128</v>
+      </c>
+      <c r="L479" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>Shri Krishna Devcon Limited (SHRIKRISH.NS) Rises Modestly, Resistance in Sight - IV Spike - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>SHRIKRISH.NS Mar 2026 Earnings: Modest Profitability Amidst Stable Operations - Profitability Analysis - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>Shri Krishna Devcon Limited Gains 3.44%: Approaching Key Resistance at ₹42.58 - Motive Wave - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>SHRIKRISH.NS Mar 2026 Earnings: Stable Bottom-Line Performance Amidst Limited Revenue Visibility - Earnings Forecast Report - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>Shri Krishna Devcon Limited (SHRIKRISH.NS) Mar 2026 Earnings: Modest Profitability Amid Low Revenue Base - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>19</v>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>NSLNISP.NS</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>NMDC Steel Limited</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>44.9900016784668</v>
+      </c>
+      <c r="F480" t="n">
+        <v>49.40000152587891</v>
+      </c>
+      <c r="G480" t="n">
+        <v>44.77999877929688</v>
+      </c>
+      <c r="H480" t="n">
+        <v>49.02000045776367</v>
+      </c>
+      <c r="I480" t="n">
+        <v>44.9900016784668</v>
+      </c>
+      <c r="J480" t="n">
+        <v>49.02000045776367</v>
+      </c>
+      <c r="K480" t="n">
+        <v>57433613</v>
+      </c>
+      <c r="L480" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-17 — cnbctv:597c6efef094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>NMDC Steel Share Price Today: Market Cap, P/E, Peer View - Univest</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>NMDC Steel Share Price Today: Market Cap, P/E, Peer View - Univest</t>
+        </is>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>NMDC Steel reports ₹50.51 crore profit in Q1 2026 - Business Upturn</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>NMDC Steel: Clarifies Stock Price Spurt Amidst Financial Results &amp; Rating Upgrade - InvestyWise</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>20</v>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>JTLIND.NS</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>JTL INDUSTRIES LIMITED</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>83.37000274658203</v>
+      </c>
+      <c r="F481" t="n">
+        <v>91.01000213623047</v>
+      </c>
+      <c r="G481" t="n">
+        <v>82.83000183105469</v>
+      </c>
+      <c r="H481" t="n">
+        <v>89.87000274658203</v>
+      </c>
+      <c r="I481" t="n">
+        <v>82.56999969482422</v>
+      </c>
+      <c r="J481" t="n">
+        <v>89.87000274658203</v>
+      </c>
+      <c r="K481" t="n">
+        <v>18581536</v>
+      </c>
+      <c r="L481" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>JTL Industries Limited Just Beat Revenue Estimates By 7.9% - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>JTL Industries Subsidiary to Double Narrow-Width HR Coil Capacity with Rs. 15 Crore Capex - TipRanks</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>JTL Industries Schedules Mumbai One-on-One Investor Meetings - TipRanks</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>JTL Industries Subsidiary to Double Narrow-Width HR Coil Capacity with Rs. 15 Crore Capex - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28936,7 +30260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q461"/>
+  <dimension ref="A1:Q481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56297,7 +57621,6 @@
           <t>Shanti Gold International Limited Right 2026-21.08.26 For Shares Earnings and Revenue – NSE:SHANTI_RE - TradingView</t>
         </is>
       </c>
-      <c r="Q448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -56495,8 +57818,6 @@
           <t>Kiri Industries Share Price rises 9.56%: valuation view - Univest</t>
         </is>
       </c>
-      <c r="P451" t="inlineStr"/>
-      <c r="Q451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -56551,9 +57872,6 @@
           <t>Synthetic (GJH): Settles Near the Prior Close at $9.45 on the Day; Levels: the Price Remains Bounded by the Supplied Support and Resistance in Latest Trading - RVOL Spike - vinanet.vn</t>
         </is>
       </c>
-      <c r="O452" t="inlineStr"/>
-      <c r="P452" t="inlineStr"/>
-      <c r="Q452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -56677,9 +57995,6 @@
           <t>CLSEL Share Price Rise: Market Cap, EPS and ROE Snapshot - Univest</t>
         </is>
       </c>
-      <c r="O454" t="inlineStr"/>
-      <c r="P454" t="inlineStr"/>
-      <c r="Q454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -57015,8 +58330,6 @@
           <t>National Standard files FY26 BRSR, reports 100% related-party sales - scanx.trade</t>
         </is>
       </c>
-      <c r="P459" t="inlineStr"/>
-      <c r="Q459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -57076,8 +58389,6 @@
           <t>Neelamalai Agro Industries (NSE:NEAGI) Cyclically Adjusted PS Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
         </is>
       </c>
-      <c r="P460" t="inlineStr"/>
-      <c r="Q460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -57145,6 +58456,1330 @@
       <c r="Q461" t="inlineStr">
         <is>
           <t>Mysore Petro Chemicals (NSE:MYSORPETRO) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>1</v>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>ALOKINDS.NS</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Alok Industries Limited</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>10.48999977111816</v>
+      </c>
+      <c r="F462" t="n">
+        <v>10.48999977111816</v>
+      </c>
+      <c r="G462" t="n">
+        <v>9.159999847412109</v>
+      </c>
+      <c r="H462" t="n">
+        <v>9.239999771118164</v>
+      </c>
+      <c r="I462" t="n">
+        <v>10.43000030517578</v>
+      </c>
+      <c r="J462" t="n">
+        <v>9.239999771118164</v>
+      </c>
+      <c r="K462" t="n">
+        <v>85081353</v>
+      </c>
+      <c r="L462" t="n">
+        <v>-11.41</v>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>Alok Industries Share Price: fresh 52-week low, analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>Alok Industries Share Price: fresh 52-week low, analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr"/>
+      <c r="P462" t="inlineStr"/>
+      <c r="Q462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>2</v>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>AASTHA.NS</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Aastha Spintex Limited</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>85</v>
+      </c>
+      <c r="F463" t="n">
+        <v>85</v>
+      </c>
+      <c r="G463" t="n">
+        <v>79.52999877929688</v>
+      </c>
+      <c r="H463" t="n">
+        <v>79.61000061035156</v>
+      </c>
+      <c r="I463" t="n">
+        <v>88.36000061035156</v>
+      </c>
+      <c r="J463" t="n">
+        <v>79.61000061035156</v>
+      </c>
+      <c r="K463" t="n">
+        <v>2378542</v>
+      </c>
+      <c r="L463" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>Aastha Spintex Share Price News and Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>Aastha Spintex Share Price News and Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>Aastha Spintex: Announced 1:1 Bonus Shares; What’s Next? - Investing.com India</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>Aastha Spintex shares extend rise to 3rd day, hit upper circuit; check details - TradingView</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>Aastha Spintex sets September 16 AGM for bonus shares and capital hike - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>3</v>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>TERAI.NS</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Terai Tea Company Limited</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>113.9499969482422</v>
+      </c>
+      <c r="F464" t="n">
+        <v>124.8000030517578</v>
+      </c>
+      <c r="G464" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="H464" t="n">
+        <v>115</v>
+      </c>
+      <c r="I464" t="n">
+        <v>125.9000015258789</v>
+      </c>
+      <c r="J464" t="n">
+        <v>115</v>
+      </c>
+      <c r="K464" t="n">
+        <v>77</v>
+      </c>
+      <c r="L464" t="n">
+        <v>-8.66</v>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>Terai Tea promotes Rajendra Kanodia to executive director for five years - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>ITA seeks West Bengal tea policy push for Darjeeling, Dooars-Terai - Business Standard</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>ITA seeks West Bengal tea policy push for Darjeeling, Dooars-Terai - Business Standard</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>Terai Tea Q1 FY27 Results: Revenue Rs 6 Cr, PAT Rs 6 Cr - Univest</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>Volume Gainers, August 21, 2026 at 3:00 PM IST - HDFC Sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>4</v>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>POLYSPIN.NS</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Polyspin Exports Limited</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>31.93000030517578</v>
+      </c>
+      <c r="F465" t="n">
+        <v>31.93000030517578</v>
+      </c>
+      <c r="G465" t="n">
+        <v>28.05999946594238</v>
+      </c>
+      <c r="H465" t="n">
+        <v>29.52000045776367</v>
+      </c>
+      <c r="I465" t="n">
+        <v>31.93000030517578</v>
+      </c>
+      <c r="J465" t="n">
+        <v>29.52000045776367</v>
+      </c>
+      <c r="K465" t="n">
+        <v>742</v>
+      </c>
+      <c r="L465" t="n">
+        <v>-7.55</v>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>Polyspin Exports appoints Durga Ramji as MD at 41st AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>Polyspin Exports appoints Durga Ramji as MD at 41st AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>Polyspin Exports reports ₹390.04 Lakhs net profit in FY26, sets Aug 21 AGM date - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>Polyspin Exports Q1FY27 standalone net profit falls 24% to ₹87 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>Polyspin Exports consolidated net profit rises 7.14% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>5</v>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>RPPINFRA.NS</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>R.P.P. Infra Projects Limited</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="F466" t="n">
+        <v>57.90000152587891</v>
+      </c>
+      <c r="G466" t="n">
+        <v>53.59999847412109</v>
+      </c>
+      <c r="H466" t="n">
+        <v>53.83000183105469</v>
+      </c>
+      <c r="I466" t="n">
+        <v>57.52999877929688</v>
+      </c>
+      <c r="J466" t="n">
+        <v>53.83000183105469</v>
+      </c>
+      <c r="K466" t="n">
+        <v>228233</v>
+      </c>
+      <c r="L466" t="n">
+        <v>-6.43</v>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>R.P.P. Infra Projects Receives Termination of ₹205.89 Crore Tamil Nadu Sports City Order - Sahi</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>Tamil Nadu terminates Rs 205.89-crore work order for Global Sports City - The New Indian Express</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-27 — cnbctv:d6dc0c5bd094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>Tamil Nadu terminates Rs 205.89-crore work order for Global Sports City - The New Indian Express</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>RPP Infra Projects: Promoter Group Member Sells 3.50% Stake - Whalesbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>6</v>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>SREEL.NS</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Sreeleathers Limited</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>269.3900146484375</v>
+      </c>
+      <c r="F467" t="n">
+        <v>269.3900146484375</v>
+      </c>
+      <c r="G467" t="n">
+        <v>242.9499969482422</v>
+      </c>
+      <c r="H467" t="n">
+        <v>249.4799957275391</v>
+      </c>
+      <c r="I467" t="n">
+        <v>263.239990234375</v>
+      </c>
+      <c r="J467" t="n">
+        <v>249.4799957275391</v>
+      </c>
+      <c r="K467" t="n">
+        <v>35472</v>
+      </c>
+      <c r="L467" t="n">
+        <v>-5.23</v>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>Sreeleathers Ltd. Share Price Gain: Technicals &amp; Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>Sreeleathers Publishes AGM Notice, Sets September 28 Virtual Meeting - TipRanks</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>Sreeleathers schedules 35th AGM for September 28 via video conferencing - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>Sreeleathers shareholders approve Bhaskar Chatterjee as independent director - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>Sreeleathers Publishes AGM Notice, Sets September 28 Virtual Meeting - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>7</v>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>TPLPLASTEH.NS</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>TPL Plastech Limited</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>78.01999664306641</v>
+      </c>
+      <c r="F468" t="n">
+        <v>78.38999938964844</v>
+      </c>
+      <c r="G468" t="n">
+        <v>72.90000152587891</v>
+      </c>
+      <c r="H468" t="n">
+        <v>73.40000152587891</v>
+      </c>
+      <c r="I468" t="n">
+        <v>77.44000244140625</v>
+      </c>
+      <c r="J468" t="n">
+        <v>73.40000152587891</v>
+      </c>
+      <c r="K468" t="n">
+        <v>258728</v>
+      </c>
+      <c r="L468" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>Time Technoplast Limited proposed to acquire remaining 25.14% stake in TPL Plastech Limited. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>Time Technoplast: Approves Merger, Invests ₹50 Crore in New Subsidiary - InvestyWise</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>Time Technoplast: Approves Merger, Invests ₹50 Crore in New Subsidiary - InvestyWise</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr"/>
+      <c r="Q468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>8</v>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>VALIANTLAB.NS</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Valiant Laboratories Limited</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="F469" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="G469" t="n">
+        <v>99.65000152587891</v>
+      </c>
+      <c r="H469" t="n">
+        <v>99.65000152587891</v>
+      </c>
+      <c r="I469" t="n">
+        <v>104.8899993896484</v>
+      </c>
+      <c r="J469" t="n">
+        <v>99.65000152587891</v>
+      </c>
+      <c r="K469" t="n">
+        <v>94454</v>
+      </c>
+      <c r="L469" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>Valiant Laboratories Limited Approves the Opening of New Corporate Office - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>Valiant Laboratories Limited Approves the Opening of New Corporate Office - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr"/>
+      <c r="P469" t="inlineStr"/>
+      <c r="Q469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>9</v>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>MYSORPETRO.NS</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>125.0699996948242</v>
+      </c>
+      <c r="F470" t="n">
+        <v>125.0699996948242</v>
+      </c>
+      <c r="G470" t="n">
+        <v>125.0699996948242</v>
+      </c>
+      <c r="H470" t="n">
+        <v>125.0699996948242</v>
+      </c>
+      <c r="I470" t="n">
+        <v>131.6499938964844</v>
+      </c>
+      <c r="J470" t="n">
+        <v>125.0699996948242</v>
+      </c>
+      <c r="K470" t="n">
+        <v>4981</v>
+      </c>
+      <c r="L470" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>MYSORPETRO Stock Price and Chart — NSE:MYSORPETRO - TradingView</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals: Denies Undisclosed Material Events Amidst Share Price Movement - InvestyWise</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals (NSE:MYSORPETRO) Cyclically Adjusted PB Ratio : (As of Aug. 20, 2026) - GuruFocus</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals shareholders approve FY26 financials, dividend, director reappointment - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>10</v>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>INDOTHAI.NS</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Limited</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>46.18000030517578</v>
+      </c>
+      <c r="F471" t="n">
+        <v>46.18000030517578</v>
+      </c>
+      <c r="G471" t="n">
+        <v>46.18000030517578</v>
+      </c>
+      <c r="H471" t="n">
+        <v>46.18000030517578</v>
+      </c>
+      <c r="I471" t="n">
+        <v>48.61000061035156</v>
+      </c>
+      <c r="J471" t="n">
+        <v>46.18000030517578</v>
+      </c>
+      <c r="K471" t="n">
+        <v>276690</v>
+      </c>
+      <c r="L471" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>Here's Why We Think Indo Thai Securities (NSE:INDOTHAI) Might Deserve Your Attention Today - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>Here's Why We Think Indo Thai Securities (NSE:INDOTHAI) Might Deserve Your Attention Today - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>Stock Watch: Shares Of These 10 Companies Slumped And Surged Over 5% Today - Do You Own Any? - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Ltd. Share Price Falls 9.97% Today - Univest</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Ltd. (INDOTHAI) Share Price Hits Fresh 52-Week Low - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>11</v>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>MPDL.NS</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>MPDL Limited</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>34.97999954223633</v>
+      </c>
+      <c r="F472" t="n">
+        <v>34.9900016784668</v>
+      </c>
+      <c r="G472" t="n">
+        <v>32.45000076293945</v>
+      </c>
+      <c r="H472" t="n">
+        <v>32.45000076293945</v>
+      </c>
+      <c r="I472" t="n">
+        <v>34.15000152587891</v>
+      </c>
+      <c r="J472" t="n">
+        <v>32.45000076293945</v>
+      </c>
+      <c r="K472" t="n">
+        <v>2655</v>
+      </c>
+      <c r="L472" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>MPDL Stock Price and Chart — NSE:MPDL - TradingView</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>Shah Metacorp Ltd leads losers in 'B' group - Capital Market</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>Shah Metacorp Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>MPDL Ltd Q1 Results: Board approves financials for quarter ended June 30 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>MPDL (NSE:MPDL) Shiller PE Ratio : (As of Aug. 21, 2026) - GuruFocus</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>12</v>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>RSSOFTWARE.NS</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>R. S. Software (India) Limited</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>33.93999862670898</v>
+      </c>
+      <c r="F473" t="n">
+        <v>33.93999862670898</v>
+      </c>
+      <c r="G473" t="n">
+        <v>31.29000091552734</v>
+      </c>
+      <c r="H473" t="n">
+        <v>31.29000091552734</v>
+      </c>
+      <c r="I473" t="n">
+        <v>32.93000030517578</v>
+      </c>
+      <c r="J473" t="n">
+        <v>31.29000091552734</v>
+      </c>
+      <c r="K473" t="n">
+        <v>69139</v>
+      </c>
+      <c r="L473" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>AVANCE Stock Price and Chart — NSE:AVANCE - TradingView</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>NMR Q2 2026 Earnings: EPS of 34.04 Misses Estimates by 12.5% as ADR Edges Higher - Earnings Decline Risk - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>NMR Q2 2026 Earnings: EPS of 34.04 Misses Estimates by 12.5% as ADR Edges Higher - Earnings Decline Risk - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr"/>
+      <c r="Q473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>13</v>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>AQYLON.NS</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Aqylon Nexus Limited</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>23.20000076293945</v>
+      </c>
+      <c r="F474" t="n">
+        <v>23.34000015258789</v>
+      </c>
+      <c r="G474" t="n">
+        <v>22.11000061035156</v>
+      </c>
+      <c r="H474" t="n">
+        <v>22.11000061035156</v>
+      </c>
+      <c r="I474" t="n">
+        <v>23.27000045776367</v>
+      </c>
+      <c r="J474" t="n">
+        <v>22.11000061035156</v>
+      </c>
+      <c r="K474" t="n">
+        <v>1071799</v>
+      </c>
+      <c r="L474" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>Leading Leasing sells 1.47 cr Aqylon Nexus shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>InvestingPro Fair Value flagged Aqylon Nexus 54% decline in advance By Investing.com - Investing.com India</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>Aqylon Nexus Standalone June 2026 Net Sales at Rs 8.47 crore, up 24294.81% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>Leading Leasing raises Aqylon Nexus stake to 10.30% via open market buy - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>Aqylon Nexus appoints Rupareliya as director, Sanghani as CFO - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>14</v>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>SHANTIGEAR.NS</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Shanthi Gears Limited</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>542.0499877929688</v>
+      </c>
+      <c r="F475" t="n">
+        <v>542.0999755859375</v>
+      </c>
+      <c r="G475" t="n">
+        <v>510.2000122070312</v>
+      </c>
+      <c r="H475" t="n">
+        <v>517.75</v>
+      </c>
+      <c r="I475" t="n">
+        <v>544.7999877929688</v>
+      </c>
+      <c r="J475" t="n">
+        <v>517.75</v>
+      </c>
+      <c r="K475" t="n">
+        <v>183473</v>
+      </c>
+      <c r="L475" t="n">
+        <v>-4.97</v>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-24 — cnbctv:cc141adf4094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>Shanthi Gears Denies Undisclosed Factors Behind Surge in Trading Volume - TipRanks</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>Tube Investments of India acquires 2.69% stake in Shanthi Gears - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-21 — cnbctv:102eb5c57094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>Why Did Shanthi Gears Shares Skyrocket 19% in Today’s Trading Session? - Trade Brains</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>15</v>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>DVL.NS</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Dhunseri Ventures Limited</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>291.5499877929688</v>
+      </c>
+      <c r="F476" t="n">
+        <v>293.1400146484375</v>
+      </c>
+      <c r="G476" t="n">
+        <v>278</v>
+      </c>
+      <c r="H476" t="n">
+        <v>279.3699951171875</v>
+      </c>
+      <c r="I476" t="n">
+        <v>293.9700012207031</v>
+      </c>
+      <c r="J476" t="n">
+        <v>279.3699951171875</v>
+      </c>
+      <c r="K476" t="n">
+        <v>18238</v>
+      </c>
+      <c r="L476" t="n">
+        <v>-4.97</v>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>dorsaVi (ASX:DVL) Reaches New Chip Development Milestone Ahead of Electrical Testing - Kalkine</t>
+        </is>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>Dhunseri Ventures AGM voting results: Aruna Dhanuka reappointed as MD - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>Could dorsaVi (ASX:DVL) Be a Penny Stock to Watch? - Kalkine Media</t>
+        </is>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>dorsaVi (ASX:DVL) Gains 8.7% as v6.5 Sensor Pushes Its Physical AI Strategy Forward - Kalkine</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>Dhunseri Ventures AGM voting results: Aruna Dhanuka reappointed as MD - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B477" t="n">
+        <v>16</v>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>SIEL.NS</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>36.20999908447266</v>
+      </c>
+      <c r="F477" t="n">
+        <v>36.20999908447266</v>
+      </c>
+      <c r="G477" t="n">
+        <v>32.77000045776367</v>
+      </c>
+      <c r="H477" t="n">
+        <v>32.77999877929688</v>
+      </c>
+      <c r="I477" t="n">
+        <v>34.4900016784668</v>
+      </c>
+      <c r="J477" t="n">
+        <v>32.77999877929688</v>
+      </c>
+      <c r="K477" t="n">
+        <v>5545</v>
+      </c>
+      <c r="L477" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>SIEL Stock Price and Chart — NSE:SIEL - TradingView</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>5 Under the Radar Trading Stocks in India - Univest</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>5 Under the Radar Trading Stocks in India - Univest</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises standalone profit rises 21.8% in Q1FY27 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>17</v>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>TAKE.NS</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>TAKE Limited</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>16.13999938964844</v>
+      </c>
+      <c r="F478" t="n">
+        <v>16.13999938964844</v>
+      </c>
+      <c r="G478" t="n">
+        <v>16.13999938964844</v>
+      </c>
+      <c r="H478" t="n">
+        <v>16.13999938964844</v>
+      </c>
+      <c r="I478" t="n">
+        <v>16.97999954223633</v>
+      </c>
+      <c r="J478" t="n">
+        <v>16.13999938964844</v>
+      </c>
+      <c r="K478" t="n">
+        <v>60287</v>
+      </c>
+      <c r="L478" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>Take-Two shares move higher pre-market as gamers get first look at GTA 6 - CNBC</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>Take-Two stock rebounds after GTA6 reveal, but risks remain ahead of November release - Pluang</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>Take-Two shares rise after GTA 6 trailer sparks huge viewer interest and strong sales forecasts. - Pluang</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>‘Prove Sabareesan link, take 50 per cent of G Square shares’ - The New Indian Express</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>Take-Two shares rise after Rockstar Games releases extended GTA VI preview - Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>18</v>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>EMPOWER.NS</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Empower India Limited</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>2.119999885559082</v>
+      </c>
+      <c r="F479" t="n">
+        <v>2.119999885559082</v>
+      </c>
+      <c r="G479" t="n">
+        <v>2.119999885559082</v>
+      </c>
+      <c r="H479" t="n">
+        <v>2.119999885559082</v>
+      </c>
+      <c r="I479" t="n">
+        <v>2.230000019073486</v>
+      </c>
+      <c r="J479" t="n">
+        <v>2.119999885559082</v>
+      </c>
+      <c r="K479" t="n">
+        <v>1655956</v>
+      </c>
+      <c r="L479" t="n">
+        <v>-4.93</v>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>Empower India - 11 penny stocks surged up to 198% in 6 months. Do you own any? - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>More money to help farmer firefighters better protect properties and save time - Stock Journal</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>More money to help farmer firefighters better protect properties and save time - Stock Journal</t>
+        </is>
+      </c>
+      <c r="P479" t="inlineStr"/>
+      <c r="Q479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>19</v>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>ELITECON.NS</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Elitecon International Limited</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>11.19999980926514</v>
+      </c>
+      <c r="F480" t="n">
+        <v>11.19999980926514</v>
+      </c>
+      <c r="G480" t="n">
+        <v>11.19999980926514</v>
+      </c>
+      <c r="H480" t="n">
+        <v>11.19999980926514</v>
+      </c>
+      <c r="I480" t="n">
+        <v>11.77999973297119</v>
+      </c>
+      <c r="J480" t="n">
+        <v>11.19999980926514</v>
+      </c>
+      <c r="K480" t="n">
+        <v>1116061</v>
+      </c>
+      <c r="L480" t="n">
+        <v>-4.92</v>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>Small-cap stock under ₹50 Elitecon International hits 10% upper circuit for second day in a row - Livemint</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>Small-cap stock trades green despite tepid stock market trends - Livemint</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>Small-cap stock trades green despite tepid stock market trends - Livemint</t>
+        </is>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>Elitecon International discontinues G Aakash &amp; Associates as secretarial auditor - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:01:22 IST</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>20</v>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>SAYAJIHOTL.NS</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Sayaji Hotels Limited</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>365.2000122070312</v>
+      </c>
+      <c r="F481" t="n">
+        <v>365.2000122070312</v>
+      </c>
+      <c r="G481" t="n">
+        <v>310</v>
+      </c>
+      <c r="H481" t="n">
+        <v>315.7000122070312</v>
+      </c>
+      <c r="I481" t="n">
+        <v>332</v>
+      </c>
+      <c r="J481" t="n">
+        <v>315.7000122070312</v>
+      </c>
+      <c r="K481" t="n">
+        <v>956</v>
+      </c>
+      <c r="L481" t="n">
+        <v>-4.91</v>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>Sayaji Hotels Limited (SAYAJIHOTL.NS): Consolidating Near Mid‑Cap Support Levels - Call Flow Alert - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>SAYAJIHOTL Mar 2026 Earnings: Steady Performance with EPS of ₹5.7 on Revenue of ₹37.65 Crore - Earnings Power Value - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>Sayaji Hotels (SAYAJIHOTL.NS) Gains 3.16% — Trading Above Key Support, Eyes Resistance - Factor Valuation - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>Sayaji Hotels Limited Issues Postal Ballot Notice for Director Appointment with E-Voting Period from March 7 to April 6, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>Sayaji Hotels Limited (SAYAJIHOTL.NS) Mar 2026 Earnings: Strong Quarter Driven by Higher Occupancy and Revenue Growth - Revenue Growth Report - vinanet.vn</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q481"/>
+  <dimension ref="A1:Q501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28962,9 +28962,6 @@
           <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
         </is>
       </c>
-      <c r="O462" t="inlineStr"/>
-      <c r="P462" t="inlineStr"/>
-      <c r="Q462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -29571,9 +29568,6 @@
           <t>Asian Tea &amp; Exports Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
         </is>
       </c>
-      <c r="O471" t="inlineStr"/>
-      <c r="P471" t="inlineStr"/>
-      <c r="Q471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -29707,7 +29701,6 @@
           <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
         </is>
       </c>
-      <c r="Q473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -29767,8 +29760,6 @@
           <t>Kalyani Forge Q1FY27 Results: Net profit up 218% YoY to ₹4.48 crore - scanx.trade</t>
         </is>
       </c>
-      <c r="P474" t="inlineStr"/>
-      <c r="Q474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -30247,7 +30238,1374 @@
           <t>JTL Industries Subsidiary to Double Narrow-Width HR Coil Capacity with Rs. 15 Crore Capex - TipRanks</t>
         </is>
       </c>
-      <c r="Q481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>1</v>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>DISAQ.NS</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Disa India Limited</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>11754</v>
+      </c>
+      <c r="F482" t="n">
+        <v>12400</v>
+      </c>
+      <c r="G482" t="n">
+        <v>11734</v>
+      </c>
+      <c r="H482" t="n">
+        <v>12208</v>
+      </c>
+      <c r="I482" t="n">
+        <v>11590</v>
+      </c>
+      <c r="J482" t="n">
+        <v>12208</v>
+      </c>
+      <c r="K482" t="n">
+        <v>819</v>
+      </c>
+      <c r="L482" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>DISAQ Stock Price and Chart — NSE:DISAQ - TradingView</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>Disa India (DISAQ) Slips 1.83% – Testing Key Support Levels Near ₹11,244 - BPI Bull Correction - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>Disa India Limited (DISAQ.NS) – Modest Decline Near Mid-Range Levels - OBV Divergence - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>Disa India (DISAQ) Slips 1.83% – Testing Key Support Levels Near ₹11,244 - BPI Bull Correction - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>Disa India Ltd (DISAQ) Up 2.6%, Approaching Crucial Resistance at ₹12,345.9 - Entry Point Alerts - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>2</v>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>AARNAV.NS</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Limited</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>33.36000061035156</v>
+      </c>
+      <c r="F483" t="n">
+        <v>33.66999816894531</v>
+      </c>
+      <c r="G483" t="n">
+        <v>31.86000061035156</v>
+      </c>
+      <c r="H483" t="n">
+        <v>33.65999984741211</v>
+      </c>
+      <c r="I483" t="n">
+        <v>33.36000061035156</v>
+      </c>
+      <c r="J483" t="n">
+        <v>33.65999984741211</v>
+      </c>
+      <c r="K483" t="n">
+        <v>4573</v>
+      </c>
+      <c r="L483" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>HAMPTON Stock Price and Chart — NSE:HAMPTON - TradingView</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr"/>
+      <c r="Q483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>3</v>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>ZODIAC.NS</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Zodiac Energy Limited</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>245</v>
+      </c>
+      <c r="F484" t="n">
+        <v>251.8999938964844</v>
+      </c>
+      <c r="G484" t="n">
+        <v>243.3500061035156</v>
+      </c>
+      <c r="H484" t="n">
+        <v>247.25</v>
+      </c>
+      <c r="I484" t="n">
+        <v>245.8000030517578</v>
+      </c>
+      <c r="J484" t="n">
+        <v>247.25</v>
+      </c>
+      <c r="K484" t="n">
+        <v>11449</v>
+      </c>
+      <c r="L484" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>Zodiac Energy incorporates wholly-owned subsidiary for solar projects - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>Zodiac Energy incorporates wholly-owned subsidiary for solar projects - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>Zodiac Energy Ltd. Share Price Gains 9.91%; Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>Zodiac Energy shares gain after securing order for 2,500 Kwp solar plant - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>Zodiac Partners II, LLC Announces Final Results of its Tender Offer - The Manila Times</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>4</v>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>AXITA.NS</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Axita Cotton Limited</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>8.050000190734863</v>
+      </c>
+      <c r="F485" t="n">
+        <v>8.229999542236328</v>
+      </c>
+      <c r="G485" t="n">
+        <v>8.050000190734863</v>
+      </c>
+      <c r="H485" t="n">
+        <v/>
+      </c>
+      <c r="I485" t="n">
+        <v>7.980000019073486</v>
+      </c>
+      <c r="J485" t="n">
+        <v/>
+      </c>
+      <c r="K485" t="n">
+        <v>1263568</v>
+      </c>
+      <c r="L485" t="n">
+        <v>0</v>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>Penny stock under ₹10 to be in focus on Monday | Here's why - Livemint</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>Textile Stock Jumps 5% After Plans to Expand Into Yarn Manufacturing Business - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>Axita Cotton files interest to acquire Varidhi Cotspin via CIRP - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>Axita Cotton standalone net profit rises 122.98% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>Penny Stock Under Rs 10: THIS Textile Stock In Focus Due to Business Update - Goodreturns</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>5</v>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>CHEVIOT.NS</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Cheviot Company Limited</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>1142.5</v>
+      </c>
+      <c r="F486" t="n">
+        <v>1146</v>
+      </c>
+      <c r="G486" t="n">
+        <v>1135</v>
+      </c>
+      <c r="H486" t="n">
+        <v/>
+      </c>
+      <c r="I486" t="n">
+        <v>1135.800048828125</v>
+      </c>
+      <c r="J486" t="n">
+        <v/>
+      </c>
+      <c r="K486" t="n">
+        <v>725</v>
+      </c>
+      <c r="L486" t="n">
+        <v>0</v>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>Cheviot Company Standalone June 2026 Net Sales at Rs 170.55 crore, up 42.46% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>Cheviot Company Share Price Target 2027 to 2030: Analyst Outlook - Univest</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>Marico, JK Tyre, IG Petrochemicals, Kokuyo Camlin, Cheviot Dividend Record Date: Last Day To Buy Shares To Qualify - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>Cheviot Company approves ₹25 dividend, reappoints Utkarsh Kanoria at AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>Cheviot Company Share Price Target 2027 to 2030: Analyst Outlook - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>6</v>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>WEWIN.NS</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>WE WIN LIMITED</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>46</v>
+      </c>
+      <c r="F487" t="n">
+        <v>47.47999954223633</v>
+      </c>
+      <c r="G487" t="n">
+        <v>45.70000076293945</v>
+      </c>
+      <c r="H487" t="n">
+        <v/>
+      </c>
+      <c r="I487" t="n">
+        <v>46.20999908447266</v>
+      </c>
+      <c r="J487" t="n">
+        <v/>
+      </c>
+      <c r="K487" t="n">
+        <v>2307</v>
+      </c>
+      <c r="L487" t="n">
+        <v>0</v>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>We Win Limited schedules board meeting on Aug 29 for auditor appointment - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>Treasury Boosts Long-Dated Bond Buybacks, Sparking Sharpest 30-Year Yield Drop in 10 Months - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>We Win Q1 Results: Net Profit Falls 22% YoY to ₹46.22 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>Treasury Boosts Long-Dated Bond Buybacks, Sparking Sharpest 30-Year Yield Drop in 10 Months - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>We Win Limited (NSE: WEWIN) Reports Fifth Consecutive Quarter of Revenue Growth; AI Solutions Segment Crosses Rs. 9.47 Crore in First Year of Operations - Big News Network.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>7</v>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>EMUDHRA.NS</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>eMudhra Limited</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>559.25</v>
+      </c>
+      <c r="F488" t="n">
+        <v>564</v>
+      </c>
+      <c r="G488" t="n">
+        <v>550.4000244140625</v>
+      </c>
+      <c r="H488" t="n">
+        <v/>
+      </c>
+      <c r="I488" t="n">
+        <v>559.25</v>
+      </c>
+      <c r="J488" t="n">
+        <v/>
+      </c>
+      <c r="K488" t="n">
+        <v>121639</v>
+      </c>
+      <c r="L488" t="n">
+        <v>0</v>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>eMudhra to host virtual analyst meet with Karma Capital on Sep 3 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>eMudhra to host virtual analyst meet with Karma Capital on Sep 3 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>eMudhra Limited (NSE:EMUDHRA) Analysts Are Cutting Their Estimates: Here's What You Need To Know - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>eMudhra Consolidated June 2026 Net Sales at Rs 190.72 crore, up 29.47% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>eMudhra Q1 Results FY27: PAT Rs 32 Cr, Revenue Rs 190 Cr - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>8</v>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>MEDICO.NS</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Medico Remedies Limited</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>43.61999893188477</v>
+      </c>
+      <c r="F489" t="n">
+        <v>43.61999893188477</v>
+      </c>
+      <c r="G489" t="n">
+        <v>42</v>
+      </c>
+      <c r="H489" t="n">
+        <v/>
+      </c>
+      <c r="I489" t="n">
+        <v>43.31000137329102</v>
+      </c>
+      <c r="J489" t="n">
+        <v/>
+      </c>
+      <c r="K489" t="n">
+        <v>166991</v>
+      </c>
+      <c r="L489" t="n">
+        <v>0</v>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>Medico Intercontinental Q1 Results: Standalone profit rises 9% YoY to ₹60.8 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>Medico Remedies Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>Medico Remedies Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>Naidu orders stringent action over medico Priyanka’s death - The New Indian Express</t>
+        </is>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>Medico Remedies standalone net profit rises 38.46% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>9</v>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>SPLPETRO.NS</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Supreme Petrochem Limited</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>692.8499755859375</v>
+      </c>
+      <c r="F490" t="n">
+        <v>717</v>
+      </c>
+      <c r="G490" t="n">
+        <v>691.9500122070312</v>
+      </c>
+      <c r="H490" t="n">
+        <v/>
+      </c>
+      <c r="I490" t="n">
+        <v>692</v>
+      </c>
+      <c r="J490" t="n">
+        <v/>
+      </c>
+      <c r="K490" t="n">
+        <v>199388</v>
+      </c>
+      <c r="L490" t="n">
+        <v>0</v>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>SPLPETRO Forecast — Price Target — Prediction for 2027 - TradingView</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>Debt-Free Chemical Stock: Q1 Profit Surges 192% With ₹874 Cr Cash Surplus; Worth Watching? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>Shareholders Should Be Pleased With Supreme Petrochem Limited's (NSE:SPLPETRO) Price - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>Supreme Petrochem Promoters Declare No Share Encumbrance as of March 31, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>Supreme Petrochem Limited (SPLPETRO.NS) Mar 2026 Earnings: Steady Performance Amidst Volatile Input Costs - Revenue Miss Report - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>10</v>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>DELHIVERY.NS</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Delhivery Limited</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>466.7000122070312</v>
+      </c>
+      <c r="F491" t="n">
+        <v>471.0499877929688</v>
+      </c>
+      <c r="G491" t="n">
+        <v>460</v>
+      </c>
+      <c r="H491" t="n">
+        <v/>
+      </c>
+      <c r="I491" t="n">
+        <v>466</v>
+      </c>
+      <c r="J491" t="n">
+        <v/>
+      </c>
+      <c r="K491" t="n">
+        <v>1424904</v>
+      </c>
+      <c r="L491" t="n">
+        <v>0</v>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>Delhivery FY26: Rs.10,508 Cr Revenue, Turns FCF Positive; Macquarie Adds Outperform - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>Delhivery FY26: Rs.10,508 Cr Revenue, Turns FCF Positive; Macquarie Adds Outperform - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>Five Stocks To Buy Today: Piramal Pharma, Wockhardt, CG Power, And More | August 28 - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>Why Delhivery shares are under pressure after Q1 results? - BusinessLine</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>Delhivery shares decline over 4% as freight costs weigh down Q1 FY27 earnings; what investors should know - Upstox</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>11</v>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>PRUDENT.NS</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Prudent Corporate Advisory Services Limited</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>3485</v>
+      </c>
+      <c r="F492" t="n">
+        <v>3485</v>
+      </c>
+      <c r="G492" t="n">
+        <v>3361.60009765625</v>
+      </c>
+      <c r="H492" t="n">
+        <v/>
+      </c>
+      <c r="I492" t="n">
+        <v>3473.5</v>
+      </c>
+      <c r="J492" t="n">
+        <v/>
+      </c>
+      <c r="K492" t="n">
+        <v>26505</v>
+      </c>
+      <c r="L492" t="n">
+        <v>0</v>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>Prudent Corporate PAT surges 44% to ₹74.8 cr in Q1FY27 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>Prudent Corporate PAT surges 44% to ₹74.8 cr in Q1FY27 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>PRUDENT Share Price news after 3.56% rise to Rs 3,467.30 - Univest</t>
+        </is>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>Here's Why CNO Financial Shares Are Attracting Prudent Investors Now - TradingView</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>Prudent Advisor Standalone June 2026 Net Sales at Rs 339.87 crore, up 23.44% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>12</v>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>SHAILY.NS</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Shaily Engineering Plastics Limited</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>3302.300048828125</v>
+      </c>
+      <c r="F493" t="n">
+        <v>3310</v>
+      </c>
+      <c r="G493" t="n">
+        <v>3244</v>
+      </c>
+      <c r="H493" t="n">
+        <v/>
+      </c>
+      <c r="I493" t="n">
+        <v>3289</v>
+      </c>
+      <c r="J493" t="n">
+        <v/>
+      </c>
+      <c r="K493" t="n">
+        <v>88702</v>
+      </c>
+      <c r="L493" t="n">
+        <v>0</v>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>Shaily Engineering Plastics Limited investor meet scheduled on 30 May 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>Shaily Engineering Plastics Limited investor meet scheduled on 30 May 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>Shaily Engineering Plastics Stock Leads 3 Healthy High Growth Picks - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>Shaily Engg Consolidated June 2026 Net Sales at Rs 280.67 crore, up 13.77% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>Shaily Engineering Plastics Ltd. Share Price Near 52W High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>13</v>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>RAINBOW.NS</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Rainbow Childrens Medicare Limited</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>1441</v>
+      </c>
+      <c r="F494" t="n">
+        <v>1457.800048828125</v>
+      </c>
+      <c r="G494" t="n">
+        <v>1430.599975585938</v>
+      </c>
+      <c r="H494" t="n">
+        <v/>
+      </c>
+      <c r="I494" t="n">
+        <v>1441</v>
+      </c>
+      <c r="J494" t="n">
+        <v/>
+      </c>
+      <c r="K494" t="n">
+        <v>68321</v>
+      </c>
+      <c r="L494" t="n">
+        <v>0</v>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>Price Action | Advait Energy up 4% on Rs 134cr contract win; Rainbow Children shares fall on CFO... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>Price Action | Advait Energy up 4% on Rs 134cr contract win; Rainbow Children shares fall on CFO... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>Rainbow Children's Medicare accepts CFO resignation effective August 31 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>'Reading Rainbow' Mychal Threets reassures fans he is fine after a 5-day psychiatric hold: ‘I am not okay - The Times of India</t>
+        </is>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>Rainbow Children's Medicare Limited Just Recorded A 8.0% Revenue Beat: Here's What Analysts Think - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>14</v>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>CAMPUS.NS</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Campus Activewear Limited</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>225</v>
+      </c>
+      <c r="F495" t="n">
+        <v>227.8000030517578</v>
+      </c>
+      <c r="G495" t="n">
+        <v>223.1000061035156</v>
+      </c>
+      <c r="H495" t="n">
+        <v/>
+      </c>
+      <c r="I495" t="n">
+        <v>224.9900054931641</v>
+      </c>
+      <c r="J495" t="n">
+        <v/>
+      </c>
+      <c r="K495" t="n">
+        <v>428511</v>
+      </c>
+      <c r="L495" t="n">
+        <v>0</v>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>Oklo stock rises on HALEU supply deal for Ohio campus - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>What Underwear Should You Buy for Fall? Duluth Trading Shares First-Layer Essentials for Back to Campus and Back to Work - The Manila Times</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>PayPal stock holds firm after campus payments expand - Ad-hoc-news.de</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>Artist behind CSUF new Titan statue shares the sculpture's journey to campus - Daily Titan</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>What Underwear Should You Buy for Fall? Duluth Trading Shares First-Layer Essentials for Back to Campus and Back to Work - The Manila Times</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>15</v>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>KRITIKA.NS</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Kritika Wires Limited</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>5.550000190734863</v>
+      </c>
+      <c r="F496" t="n">
+        <v>5.550000190734863</v>
+      </c>
+      <c r="G496" t="n">
+        <v>5.360000133514404</v>
+      </c>
+      <c r="H496" t="n">
+        <v/>
+      </c>
+      <c r="I496" t="n">
+        <v>5.440000057220459</v>
+      </c>
+      <c r="J496" t="n">
+        <v/>
+      </c>
+      <c r="K496" t="n">
+        <v>103920</v>
+      </c>
+      <c r="L496" t="n">
+        <v>0</v>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>Kritika Wires Standalone June 2026 Net Sales at Rs 161.86 crore, down 21.75% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>Kritika Wires Standalone June 2026 Net Sales at Rs 161.86 crore, down 21.75% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>Kritika Wires confirms no fund raising activity in Q1FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>Kritika Kamra on National Handloom Day: We need to make handloom feel fun again - The Times of India</t>
+        </is>
+      </c>
+      <c r="Q496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>16</v>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>ROTO.NS</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Roto Pumps Limited</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>65.37999725341797</v>
+      </c>
+      <c r="F497" t="n">
+        <v>65.37999725341797</v>
+      </c>
+      <c r="G497" t="n">
+        <v>64.30000305175781</v>
+      </c>
+      <c r="H497" t="n">
+        <v/>
+      </c>
+      <c r="I497" t="n">
+        <v>65.01999664306641</v>
+      </c>
+      <c r="J497" t="n">
+        <v/>
+      </c>
+      <c r="K497" t="n">
+        <v>136747</v>
+      </c>
+      <c r="L497" t="n">
+        <v>0</v>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>Roto Pumps promoter Shalini Gupta sells 4,900 shares in open market - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>Roto Pumps promoter Shalini Gupta sells 4,900 shares in open market - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>Roto Pumps Consolidated June 2026 Net Sales at Rs 75.60 crore, up 14.74% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>Dhanalaxmi Roto Spinners fixes Sep 14 record date for dividend - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>Roto Pumps Standalone June 2026 Net Sales at Rs 57.45 crore, up 11.28% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>17</v>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>RITCO.NS</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Ritco Logistics Limited</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>312.3500061035156</v>
+      </c>
+      <c r="F498" t="n">
+        <v>314</v>
+      </c>
+      <c r="G498" t="n">
+        <v>307.7000122070312</v>
+      </c>
+      <c r="H498" t="n">
+        <v/>
+      </c>
+      <c r="I498" t="n">
+        <v>310.1000061035156</v>
+      </c>
+      <c r="J498" t="n">
+        <v/>
+      </c>
+      <c r="K498" t="n">
+        <v>29324</v>
+      </c>
+      <c r="L498" t="n">
+        <v>0</v>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>Ritco Logistics to approve FY26 results at Aug 31 board meeting - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>TrucksUp Funding: लॉजिस्टिक क्षेत्रातील मोठी डील! TrucksUp ने उभारले **$8.2 दशलक्ष**, व्हॅल्युएशन पोहोचले **$42 दशलक्षवर - Whalesbook</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>Ritco Logistics Ltd. (RITCO) Share Price Today: Price Action Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>Ritco Logistics Secures Contracts Worth ₹342 Crore; Shares Fall 1.27% - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>Ritco Logistics Publishes Q1 FY 2026-27 Unaudited Results in Newspapers - The Globe and Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>18</v>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>HARDWYN.NS</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Hardwyn India Limited</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>9.069999694824219</v>
+      </c>
+      <c r="F499" t="n">
+        <v>9.239999771118164</v>
+      </c>
+      <c r="G499" t="n">
+        <v>9</v>
+      </c>
+      <c r="H499" t="n">
+        <v/>
+      </c>
+      <c r="I499" t="n">
+        <v>9.050000190734863</v>
+      </c>
+      <c r="J499" t="n">
+        <v/>
+      </c>
+      <c r="K499" t="n">
+        <v>1619287</v>
+      </c>
+      <c r="L499" t="n">
+        <v>0</v>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>Hardwyn India Reports Q1 Net Profit of ₹2.8 Crore on ₹34.6 Crore Revenue - Sahi</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>Hardwyn India Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>Hardwyn Q1 FY27 Results: Revenue Rs 35 Cr, PAT Rs 3 Cr - Univest</t>
+        </is>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>Hardwyn India net profit falls 22% to ₹28 million in Q1FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>Hardwyn India Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>19</v>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>VERANDA.NS</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Veranda Learning Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>242.5</v>
+      </c>
+      <c r="F500" t="n">
+        <v>244</v>
+      </c>
+      <c r="G500" t="n">
+        <v>238.6000061035156</v>
+      </c>
+      <c r="H500" t="n">
+        <v/>
+      </c>
+      <c r="I500" t="n">
+        <v>243.5500030517578</v>
+      </c>
+      <c r="J500" t="n">
+        <v/>
+      </c>
+      <c r="K500" t="n">
+        <v>182954</v>
+      </c>
+      <c r="L500" t="n">
+        <v>0</v>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>Veranda Learning Announces Lapse of 6,23,054 Warrants and Forfeiture of ₹5 Crore - Sahi</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>Veranda Learning Announces Lapse of 6,23,054 Warrants and Forfeiture of ₹5 Crore - Sahi</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>Veranda Learning Solutions Ltd. Share Price Rises 8.03% - Univest</t>
+        </is>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>Veranda Learning Solutions Q1 Results: Earnings call audio uploaded - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>NCLT approves Veranda Learning Solutions subsidiary amalgamation - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>20</v>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>SONAMLTD.NS</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>SONAM LIMITED</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>64.80000305175781</v>
+      </c>
+      <c r="F501" t="n">
+        <v>74.59999847412109</v>
+      </c>
+      <c r="G501" t="n">
+        <v>63.59999847412109</v>
+      </c>
+      <c r="H501" t="n">
+        <v/>
+      </c>
+      <c r="I501" t="n">
+        <v>63.2400016784668</v>
+      </c>
+      <c r="J501" t="n">
+        <v/>
+      </c>
+      <c r="K501" t="n">
+        <v>1074943</v>
+      </c>
+      <c r="L501" t="n">
+        <v>0</v>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>Sonam Limited promoters declare no share encumbrance in FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>SONAM LIMITED Inches Lower at ₹54 as Key Support Holds Steady - MFI Oversold - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>SONAM LIMITED (SONAMLTD.NS) Faces Selling Pressure, Down 1.85% Amid Weakness - Volume Breadth - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>Sonam Limited (SONAMLTD.NS): Minor Uptick Amid Narrow Range – Resistance in Focus - Combination Correction - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>SONAM Limited (SONAMLTD.NS) Edges Higher: Support and Resistance Levels in Focus - High Volume Node - vinanet.vn</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -30260,7 +31618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q481"/>
+  <dimension ref="A1:Q501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58512,9 +59870,6 @@
           <t>Alok Industries Share Price: fresh 52-week low, analysis - Univest</t>
         </is>
       </c>
-      <c r="O462" t="inlineStr"/>
-      <c r="P462" t="inlineStr"/>
-      <c r="Q462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -58919,8 +60274,6 @@
           <t>Time Technoplast: Approves Merger, Invests ₹50 Crore in New Subsidiary - InvestyWise</t>
         </is>
       </c>
-      <c r="P468" t="inlineStr"/>
-      <c r="Q468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -58975,9 +60328,6 @@
           <t>Valiant Laboratories Limited Approves the Opening of New Corporate Office - marketscreener.com</t>
         </is>
       </c>
-      <c r="O469" t="inlineStr"/>
-      <c r="P469" t="inlineStr"/>
-      <c r="Q469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -59244,8 +60594,6 @@
           <t>NMR Q2 2026 Earnings: EPS of 34.04 Misses Estimates by 12.5% as ADR Edges Higher - Earnings Decline Risk - vinanet.vn</t>
         </is>
       </c>
-      <c r="P473" t="inlineStr"/>
-      <c r="Q473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -59517,7 +60865,6 @@
           <t>Superior Industrial Enterprises standalone profit rises 21.8% in Q1FY27 - scanx.trade</t>
         </is>
       </c>
-      <c r="Q477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -59646,8 +60993,6 @@
           <t>More money to help farmer firefighters better protect properties and save time - Stock Journal</t>
         </is>
       </c>
-      <c r="P479" t="inlineStr"/>
-      <c r="Q479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -59712,7 +61057,6 @@
           <t>Elitecon International discontinues G Aakash &amp; Associates as secretarial auditor - scanx.trade</t>
         </is>
       </c>
-      <c r="Q480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -59780,6 +61124,1374 @@
       <c r="Q481" t="inlineStr">
         <is>
           <t>Sayaji Hotels Limited (SAYAJIHOTL.NS) Mar 2026 Earnings: Strong Quarter Driven by Higher Occupancy and Revenue Growth - Revenue Growth Report - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>1</v>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>TCC.NS</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>TCC Concept Limited</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>232.9499969482422</v>
+      </c>
+      <c r="F482" t="n">
+        <v>233.25</v>
+      </c>
+      <c r="G482" t="n">
+        <v>218.0500030517578</v>
+      </c>
+      <c r="H482" t="n">
+        <v>223.25</v>
+      </c>
+      <c r="I482" t="n">
+        <v>231.75</v>
+      </c>
+      <c r="J482" t="n">
+        <v>223.25</v>
+      </c>
+      <c r="K482" t="n">
+        <v>362460</v>
+      </c>
+      <c r="L482" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>Volume Gainers as of 12:25 PM IST, Mumbai, August 26: Indo Thai Securities, TCC Concept Lead Trading Surge - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>Volume Gainers as of 12:25 PM IST, Mumbai, August 26: Indo Thai Securities, TCC Concept Lead Trading Surge - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>TCC Concept fixes September 4 record date for 1:5 share split - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>TCC Concept Ltd. Share Price: 52-Week Low, Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>TCC CONCEPT Standalone June 2026 Net Sales at Rs 17.12 crore, up 58.91% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>2</v>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>CAMPUS.NS</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Campus Activewear Limited</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>225</v>
+      </c>
+      <c r="F483" t="n">
+        <v>227.8000030517578</v>
+      </c>
+      <c r="G483" t="n">
+        <v>223.1000061035156</v>
+      </c>
+      <c r="H483" t="n">
+        <v/>
+      </c>
+      <c r="I483" t="n">
+        <v>224.9900054931641</v>
+      </c>
+      <c r="J483" t="n">
+        <v/>
+      </c>
+      <c r="K483" t="n">
+        <v>428511</v>
+      </c>
+      <c r="L483" t="n">
+        <v>0</v>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>Oklo stock rises on HALEU supply deal for Ohio campus - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>What Underwear Should You Buy for Fall? Duluth Trading Shares First-Layer Essentials for Back to Campus and Back to Work - The Manila Times</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>PayPal stock holds firm after campus payments expand - Ad-hoc-news.de</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>Artist behind CSUF new Titan statue shares the sculpture's journey to campus - Daily Titan</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>What Underwear Should You Buy for Fall? Duluth Trading Shares First-Layer Essentials for Back to Campus and Back to Work - The Manila Times</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>3</v>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>AXITA.NS</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Axita Cotton Limited</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>8.050000190734863</v>
+      </c>
+      <c r="F484" t="n">
+        <v>8.229999542236328</v>
+      </c>
+      <c r="G484" t="n">
+        <v>8.050000190734863</v>
+      </c>
+      <c r="H484" t="n">
+        <v/>
+      </c>
+      <c r="I484" t="n">
+        <v>7.980000019073486</v>
+      </c>
+      <c r="J484" t="n">
+        <v/>
+      </c>
+      <c r="K484" t="n">
+        <v>1263568</v>
+      </c>
+      <c r="L484" t="n">
+        <v>0</v>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>Penny stock under ₹10 to be in focus on Monday | Here's why - Livemint</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>Textile Stock Jumps 5% After Plans to Expand Into Yarn Manufacturing Business - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>Axita Cotton files interest to acquire Varidhi Cotspin via CIRP - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>Axita Cotton standalone net profit rises 122.98% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>Penny Stock Under Rs 10: THIS Textile Stock In Focus Due to Business Update - Goodreturns</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>4</v>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>CHEVIOT.NS</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Cheviot Company Limited</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>1142.5</v>
+      </c>
+      <c r="F485" t="n">
+        <v>1146</v>
+      </c>
+      <c r="G485" t="n">
+        <v>1135</v>
+      </c>
+      <c r="H485" t="n">
+        <v/>
+      </c>
+      <c r="I485" t="n">
+        <v>1135.800048828125</v>
+      </c>
+      <c r="J485" t="n">
+        <v/>
+      </c>
+      <c r="K485" t="n">
+        <v>725</v>
+      </c>
+      <c r="L485" t="n">
+        <v>0</v>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>Cheviot Company Standalone June 2026 Net Sales at Rs 170.55 crore, up 42.46% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>Cheviot Company Share Price Target 2027 to 2030: Analyst Outlook - Univest</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>Marico, JK Tyre, IG Petrochemicals, Kokuyo Camlin, Cheviot Dividend Record Date: Last Day To Buy Shares To Qualify - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>Cheviot Company approves ₹25 dividend, reappoints Utkarsh Kanoria at AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>Cheviot Company Share Price Target 2027 to 2030: Analyst Outlook - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>5</v>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>WEWIN.NS</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>WE WIN LIMITED</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>46</v>
+      </c>
+      <c r="F486" t="n">
+        <v>47.47999954223633</v>
+      </c>
+      <c r="G486" t="n">
+        <v>45.70000076293945</v>
+      </c>
+      <c r="H486" t="n">
+        <v/>
+      </c>
+      <c r="I486" t="n">
+        <v>46.20999908447266</v>
+      </c>
+      <c r="J486" t="n">
+        <v/>
+      </c>
+      <c r="K486" t="n">
+        <v>2307</v>
+      </c>
+      <c r="L486" t="n">
+        <v>0</v>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>We Win Limited schedules board meeting on Aug 29 for auditor appointment - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>Treasury Boosts Long-Dated Bond Buybacks, Sparking Sharpest 30-Year Yield Drop in 10 Months - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>We Win Q1 Results: Net Profit Falls 22% YoY to ₹46.22 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>Treasury Boosts Long-Dated Bond Buybacks, Sparking Sharpest 30-Year Yield Drop in 10 Months - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>We Win Limited (NSE: WEWIN) Reports Fifth Consecutive Quarter of Revenue Growth; AI Solutions Segment Crosses Rs. 9.47 Crore in First Year of Operations - Big News Network.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>6</v>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>EMUDHRA.NS</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>eMudhra Limited</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>559.25</v>
+      </c>
+      <c r="F487" t="n">
+        <v>564</v>
+      </c>
+      <c r="G487" t="n">
+        <v>550.4000244140625</v>
+      </c>
+      <c r="H487" t="n">
+        <v/>
+      </c>
+      <c r="I487" t="n">
+        <v>559.25</v>
+      </c>
+      <c r="J487" t="n">
+        <v/>
+      </c>
+      <c r="K487" t="n">
+        <v>121639</v>
+      </c>
+      <c r="L487" t="n">
+        <v>0</v>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>eMudhra to host virtual analyst meet with Karma Capital on Sep 3 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>eMudhra to host virtual analyst meet with Karma Capital on Sep 3 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>eMudhra Limited (NSE:EMUDHRA) Analysts Are Cutting Their Estimates: Here's What You Need To Know - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>eMudhra Consolidated June 2026 Net Sales at Rs 190.72 crore, up 29.47% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>eMudhra Q1 Results FY27: PAT Rs 32 Cr, Revenue Rs 190 Cr - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>7</v>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>MEDICO.NS</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Medico Remedies Limited</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>43.61999893188477</v>
+      </c>
+      <c r="F488" t="n">
+        <v>43.61999893188477</v>
+      </c>
+      <c r="G488" t="n">
+        <v>42</v>
+      </c>
+      <c r="H488" t="n">
+        <v/>
+      </c>
+      <c r="I488" t="n">
+        <v>43.31000137329102</v>
+      </c>
+      <c r="J488" t="n">
+        <v/>
+      </c>
+      <c r="K488" t="n">
+        <v>166991</v>
+      </c>
+      <c r="L488" t="n">
+        <v>0</v>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>Medico Intercontinental Q1 Results: Standalone profit rises 9% YoY to ₹60.8 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>Medico Remedies Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>Medico Remedies Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>Naidu orders stringent action over medico Priyanka’s death - The New Indian Express</t>
+        </is>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>Medico Remedies standalone net profit rises 38.46% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>8</v>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>SPLPETRO.NS</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Supreme Petrochem Limited</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>692.8499755859375</v>
+      </c>
+      <c r="F489" t="n">
+        <v>717</v>
+      </c>
+      <c r="G489" t="n">
+        <v>691.9500122070312</v>
+      </c>
+      <c r="H489" t="n">
+        <v/>
+      </c>
+      <c r="I489" t="n">
+        <v>692</v>
+      </c>
+      <c r="J489" t="n">
+        <v/>
+      </c>
+      <c r="K489" t="n">
+        <v>199388</v>
+      </c>
+      <c r="L489" t="n">
+        <v>0</v>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>SPLPETRO Forecast — Price Target — Prediction for 2027 - TradingView</t>
+        </is>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>Debt-Free Chemical Stock: Q1 Profit Surges 192% With ₹874 Cr Cash Surplus; Worth Watching? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>Shareholders Should Be Pleased With Supreme Petrochem Limited's (NSE:SPLPETRO) Price - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>Supreme Petrochem Promoters Declare No Share Encumbrance as of March 31, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>Supreme Petrochem Limited (SPLPETRO.NS) Mar 2026 Earnings: Steady Performance Amidst Volatile Input Costs - Revenue Miss Report - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>9</v>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>DELHIVERY.NS</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Delhivery Limited</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>466.7000122070312</v>
+      </c>
+      <c r="F490" t="n">
+        <v>471.0499877929688</v>
+      </c>
+      <c r="G490" t="n">
+        <v>460</v>
+      </c>
+      <c r="H490" t="n">
+        <v/>
+      </c>
+      <c r="I490" t="n">
+        <v>466</v>
+      </c>
+      <c r="J490" t="n">
+        <v/>
+      </c>
+      <c r="K490" t="n">
+        <v>1424904</v>
+      </c>
+      <c r="L490" t="n">
+        <v>0</v>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>Delhivery FY26: Rs.10,508 Cr Revenue, Turns FCF Positive; Macquarie Adds Outperform - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>Delhivery FY26: Rs.10,508 Cr Revenue, Turns FCF Positive; Macquarie Adds Outperform - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>Five Stocks To Buy Today: Piramal Pharma, Wockhardt, CG Power, And More | August 28 - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>Why Delhivery shares are under pressure after Q1 results? - BusinessLine</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>Delhivery shares decline over 4% as freight costs weigh down Q1 FY27 earnings; what investors should know - Upstox</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>10</v>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>PRUDENT.NS</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Prudent Corporate Advisory Services Limited</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>3485</v>
+      </c>
+      <c r="F491" t="n">
+        <v>3485</v>
+      </c>
+      <c r="G491" t="n">
+        <v>3361.60009765625</v>
+      </c>
+      <c r="H491" t="n">
+        <v/>
+      </c>
+      <c r="I491" t="n">
+        <v>3473.5</v>
+      </c>
+      <c r="J491" t="n">
+        <v/>
+      </c>
+      <c r="K491" t="n">
+        <v>26505</v>
+      </c>
+      <c r="L491" t="n">
+        <v>0</v>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>Prudent Corporate PAT surges 44% to ₹74.8 cr in Q1FY27 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>Prudent Corporate PAT surges 44% to ₹74.8 cr in Q1FY27 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>PRUDENT Share Price news after 3.56% rise to Rs 3,467.30 - Univest</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>Here's Why CNO Financial Shares Are Attracting Prudent Investors Now - TradingView</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>Prudent Advisor Standalone June 2026 Net Sales at Rs 339.87 crore, up 23.44% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>11</v>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>SILVERTUC.NS</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Silver Touch Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>177.5200042724609</v>
+      </c>
+      <c r="F492" t="n">
+        <v>184</v>
+      </c>
+      <c r="G492" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="H492" t="n">
+        <v/>
+      </c>
+      <c r="I492" t="n">
+        <v>178.5800018310547</v>
+      </c>
+      <c r="J492" t="n">
+        <v/>
+      </c>
+      <c r="K492" t="n">
+        <v>402068</v>
+      </c>
+      <c r="L492" t="n">
+        <v>0</v>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>Here's Why We Think Silver Touch Technologies (NSE:SILVERTUC) Is Well Worth Watching - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>Here's Why We Think Silver Touch Technologies (NSE:SILVERTUC) Is Well Worth Watching - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>Stocks To Buy or Sell Today, August 12, 2026: Cochin Shipyard and Poonawalla Fincorp Among Shares That May - LatestLY</t>
+        </is>
+      </c>
+      <c r="P492" t="inlineStr"/>
+      <c r="Q492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>12</v>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>RAINBOW.NS</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Rainbow Childrens Medicare Limited</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>1441</v>
+      </c>
+      <c r="F493" t="n">
+        <v>1457.800048828125</v>
+      </c>
+      <c r="G493" t="n">
+        <v>1430.599975585938</v>
+      </c>
+      <c r="H493" t="n">
+        <v/>
+      </c>
+      <c r="I493" t="n">
+        <v>1441</v>
+      </c>
+      <c r="J493" t="n">
+        <v/>
+      </c>
+      <c r="K493" t="n">
+        <v>68321</v>
+      </c>
+      <c r="L493" t="n">
+        <v>0</v>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>Price Action | Advait Energy up 4% on Rs 134cr contract win; Rainbow Children shares fall on CFO... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>Price Action | Advait Energy up 4% on Rs 134cr contract win; Rainbow Children shares fall on CFO... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>Rainbow Children's Medicare accepts CFO resignation effective August 31 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>'Reading Rainbow' Mychal Threets reassures fans he is fine after a 5-day psychiatric hold: ‘I am not okay - The Times of India</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>Rainbow Children's Medicare Limited Just Recorded A 8.0% Revenue Beat: Here's What Analysts Think - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>13</v>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>MANORAMA.NS</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Manorama Industries Limited</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>1898.5</v>
+      </c>
+      <c r="F494" t="n">
+        <v>1907.5</v>
+      </c>
+      <c r="G494" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H494" t="n">
+        <v/>
+      </c>
+      <c r="I494" t="n">
+        <v>1887.199951171875</v>
+      </c>
+      <c r="J494" t="n">
+        <v/>
+      </c>
+      <c r="K494" t="n">
+        <v>115933</v>
+      </c>
+      <c r="L494" t="n">
+        <v>0</v>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>Manorama Industries shares surge over 8% after strong Q1 results - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>How Is This Market Leader's Stock Building a Moat With Clients Like Nestlé, Ferrero and L’Oréal? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>Manorama Industries Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>Manorama Industries Ltd leads gainers in 'A' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>Manorama Industries paid ₹20.64 Cr to settle customs inquiry - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>14</v>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>KRITIKA.NS</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Kritika Wires Limited</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>5.550000190734863</v>
+      </c>
+      <c r="F495" t="n">
+        <v>5.550000190734863</v>
+      </c>
+      <c r="G495" t="n">
+        <v>5.360000133514404</v>
+      </c>
+      <c r="H495" t="n">
+        <v/>
+      </c>
+      <c r="I495" t="n">
+        <v>5.440000057220459</v>
+      </c>
+      <c r="J495" t="n">
+        <v/>
+      </c>
+      <c r="K495" t="n">
+        <v>103920</v>
+      </c>
+      <c r="L495" t="n">
+        <v>0</v>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>Kritika Wires Standalone June 2026 Net Sales at Rs 161.86 crore, down 21.75% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>Kritika Wires Standalone June 2026 Net Sales at Rs 161.86 crore, down 21.75% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>Kritika Wires confirms no fund raising activity in Q1FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>Kritika Kamra on National Handloom Day: We need to make handloom feel fun again - The Times of India</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>15</v>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>ROTO.NS</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Roto Pumps Limited</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>65.37999725341797</v>
+      </c>
+      <c r="F496" t="n">
+        <v>65.37999725341797</v>
+      </c>
+      <c r="G496" t="n">
+        <v>64.30000305175781</v>
+      </c>
+      <c r="H496" t="n">
+        <v/>
+      </c>
+      <c r="I496" t="n">
+        <v>65.01999664306641</v>
+      </c>
+      <c r="J496" t="n">
+        <v/>
+      </c>
+      <c r="K496" t="n">
+        <v>136747</v>
+      </c>
+      <c r="L496" t="n">
+        <v>0</v>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>Roto Pumps promoter Shalini Gupta sells 4,900 shares in open market - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>Roto Pumps promoter Shalini Gupta sells 4,900 shares in open market - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>Roto Pumps Consolidated June 2026 Net Sales at Rs 75.60 crore, up 14.74% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>Dhanalaxmi Roto Spinners fixes Sep 14 record date for dividend - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>Roto Pumps Standalone June 2026 Net Sales at Rs 57.45 crore, up 11.28% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>16</v>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>RITCO.NS</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Ritco Logistics Limited</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>312.3500061035156</v>
+      </c>
+      <c r="F497" t="n">
+        <v>314</v>
+      </c>
+      <c r="G497" t="n">
+        <v>307.7000122070312</v>
+      </c>
+      <c r="H497" t="n">
+        <v/>
+      </c>
+      <c r="I497" t="n">
+        <v>310.1000061035156</v>
+      </c>
+      <c r="J497" t="n">
+        <v/>
+      </c>
+      <c r="K497" t="n">
+        <v>29324</v>
+      </c>
+      <c r="L497" t="n">
+        <v>0</v>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>Ritco Logistics to approve FY26 results at Aug 31 board meeting - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>TrucksUp Funding: लॉजिस्टिक क्षेत्रातील मोठी डील! TrucksUp ने उभारले **$8.2 दशलक्ष**, व्हॅल्युएशन पोहोचले **$42 दशलक्षवर - Whalesbook</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>Ritco Logistics Ltd. (RITCO) Share Price Today: Price Action Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>Ritco Logistics Secures Contracts Worth ₹342 Crore; Shares Fall 1.27% - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>Ritco Logistics Publishes Q1 FY 2026-27 Unaudited Results in Newspapers - The Globe and Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>17</v>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>HARDWYN.NS</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Hardwyn India Limited</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>9.069999694824219</v>
+      </c>
+      <c r="F498" t="n">
+        <v>9.239999771118164</v>
+      </c>
+      <c r="G498" t="n">
+        <v>9</v>
+      </c>
+      <c r="H498" t="n">
+        <v/>
+      </c>
+      <c r="I498" t="n">
+        <v>9.050000190734863</v>
+      </c>
+      <c r="J498" t="n">
+        <v/>
+      </c>
+      <c r="K498" t="n">
+        <v>1619287</v>
+      </c>
+      <c r="L498" t="n">
+        <v>0</v>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>Hardwyn India Reports Q1 Net Profit of ₹2.8 Crore on ₹34.6 Crore Revenue - Sahi</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>Hardwyn India Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>Hardwyn Q1 FY27 Results: Revenue Rs 35 Cr, PAT Rs 3 Cr - Univest</t>
+        </is>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>Hardwyn India net profit falls 22% to ₹28 million in Q1FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>Hardwyn India Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>18</v>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>VERANDA.NS</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Veranda Learning Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>242.5</v>
+      </c>
+      <c r="F499" t="n">
+        <v>244</v>
+      </c>
+      <c r="G499" t="n">
+        <v>238.6000061035156</v>
+      </c>
+      <c r="H499" t="n">
+        <v/>
+      </c>
+      <c r="I499" t="n">
+        <v>243.5500030517578</v>
+      </c>
+      <c r="J499" t="n">
+        <v/>
+      </c>
+      <c r="K499" t="n">
+        <v>182954</v>
+      </c>
+      <c r="L499" t="n">
+        <v>0</v>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>Veranda Learning Announces Lapse of 6,23,054 Warrants and Forfeiture of ₹5 Crore - Sahi</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>Veranda Learning Announces Lapse of 6,23,054 Warrants and Forfeiture of ₹5 Crore - Sahi</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>Veranda Learning Solutions Ltd. Share Price Rises 8.03% - Univest</t>
+        </is>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>Veranda Learning Solutions Q1 Results: Earnings call audio uploaded - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>NCLT approves Veranda Learning Solutions subsidiary amalgamation - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>19</v>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>SONAMLTD.NS</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>SONAM LIMITED</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>64.80000305175781</v>
+      </c>
+      <c r="F500" t="n">
+        <v>74.59999847412109</v>
+      </c>
+      <c r="G500" t="n">
+        <v>63.59999847412109</v>
+      </c>
+      <c r="H500" t="n">
+        <v/>
+      </c>
+      <c r="I500" t="n">
+        <v>63.2400016784668</v>
+      </c>
+      <c r="J500" t="n">
+        <v/>
+      </c>
+      <c r="K500" t="n">
+        <v>1074943</v>
+      </c>
+      <c r="L500" t="n">
+        <v>0</v>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>Sonam Limited promoters declare no share encumbrance in FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>SONAM LIMITED Inches Lower at ₹54 as Key Support Holds Steady - MFI Oversold - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>SONAM LIMITED (SONAMLTD.NS) Faces Selling Pressure, Down 1.85% Amid Weakness - Volume Breadth - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>Sonam Limited (SONAMLTD.NS): Minor Uptick Amid Narrow Range – Resistance in Focus - Combination Correction - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>SONAM Limited (SONAMLTD.NS) Edges Higher: Support and Resistance Levels in Focus - High Volume Node - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-08-29 02:44:54 IST</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>20</v>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>OBCL.NS</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>OBCL Limited</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>56.09999847412109</v>
+      </c>
+      <c r="F501" t="n">
+        <v>56.09999847412109</v>
+      </c>
+      <c r="G501" t="n">
+        <v>55.20999908447266</v>
+      </c>
+      <c r="H501" t="n">
+        <v/>
+      </c>
+      <c r="I501" t="n">
+        <v>56.15999984741211</v>
+      </c>
+      <c r="J501" t="n">
+        <v/>
+      </c>
+      <c r="K501" t="n">
+        <v>774</v>
+      </c>
+      <c r="L501" t="n">
+        <v>0</v>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>OBCL promoter group raises stake to 11.05% after buying 20,629 shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>OBCL schedules AGM for September 16; seeks ₹250 crore borrowing limit - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>OBCL schedules AGM for September 16; seeks ₹250 crore borrowing limit - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>OBCL Consolidated June 2026 Net Sales at Rs 82.37 crore, down 3.35% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>OBCL promoter group boosts stake to 9.80% with 67,081 share buy - scanx.trade</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q501"/>
+  <dimension ref="A1:Q521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30366,8 +30366,6 @@
           <t>HAMPTON Stock Price and Chart — NSE:HAMPTON - TradingView</t>
         </is>
       </c>
-      <c r="P483" t="inlineStr"/>
-      <c r="Q483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -30466,15 +30464,9 @@
       <c r="G485" t="n">
         <v>8.050000190734863</v>
       </c>
-      <c r="H485" t="n">
-        <v/>
-      </c>
       <c r="I485" t="n">
         <v>7.980000019073486</v>
       </c>
-      <c r="J485" t="n">
-        <v/>
-      </c>
       <c r="K485" t="n">
         <v>1263568</v>
       </c>
@@ -30535,15 +30527,9 @@
       <c r="G486" t="n">
         <v>1135</v>
       </c>
-      <c r="H486" t="n">
-        <v/>
-      </c>
       <c r="I486" t="n">
         <v>1135.800048828125</v>
       </c>
-      <c r="J486" t="n">
-        <v/>
-      </c>
       <c r="K486" t="n">
         <v>725</v>
       </c>
@@ -30604,15 +30590,9 @@
       <c r="G487" t="n">
         <v>45.70000076293945</v>
       </c>
-      <c r="H487" t="n">
-        <v/>
-      </c>
       <c r="I487" t="n">
         <v>46.20999908447266</v>
       </c>
-      <c r="J487" t="n">
-        <v/>
-      </c>
       <c r="K487" t="n">
         <v>2307</v>
       </c>
@@ -30673,15 +30653,9 @@
       <c r="G488" t="n">
         <v>550.4000244140625</v>
       </c>
-      <c r="H488" t="n">
-        <v/>
-      </c>
       <c r="I488" t="n">
         <v>559.25</v>
       </c>
-      <c r="J488" t="n">
-        <v/>
-      </c>
       <c r="K488" t="n">
         <v>121639</v>
       </c>
@@ -30742,15 +30716,9 @@
       <c r="G489" t="n">
         <v>42</v>
       </c>
-      <c r="H489" t="n">
-        <v/>
-      </c>
       <c r="I489" t="n">
         <v>43.31000137329102</v>
       </c>
-      <c r="J489" t="n">
-        <v/>
-      </c>
       <c r="K489" t="n">
         <v>166991</v>
       </c>
@@ -30811,15 +30779,9 @@
       <c r="G490" t="n">
         <v>691.9500122070312</v>
       </c>
-      <c r="H490" t="n">
-        <v/>
-      </c>
       <c r="I490" t="n">
         <v>692</v>
       </c>
-      <c r="J490" t="n">
-        <v/>
-      </c>
       <c r="K490" t="n">
         <v>199388</v>
       </c>
@@ -30880,15 +30842,9 @@
       <c r="G491" t="n">
         <v>460</v>
       </c>
-      <c r="H491" t="n">
-        <v/>
-      </c>
       <c r="I491" t="n">
         <v>466</v>
       </c>
-      <c r="J491" t="n">
-        <v/>
-      </c>
       <c r="K491" t="n">
         <v>1424904</v>
       </c>
@@ -30949,15 +30905,9 @@
       <c r="G492" t="n">
         <v>3361.60009765625</v>
       </c>
-      <c r="H492" t="n">
-        <v/>
-      </c>
       <c r="I492" t="n">
         <v>3473.5</v>
       </c>
-      <c r="J492" t="n">
-        <v/>
-      </c>
       <c r="K492" t="n">
         <v>26505</v>
       </c>
@@ -31018,15 +30968,9 @@
       <c r="G493" t="n">
         <v>3244</v>
       </c>
-      <c r="H493" t="n">
-        <v/>
-      </c>
       <c r="I493" t="n">
         <v>3289</v>
       </c>
-      <c r="J493" t="n">
-        <v/>
-      </c>
       <c r="K493" t="n">
         <v>88702</v>
       </c>
@@ -31087,15 +31031,9 @@
       <c r="G494" t="n">
         <v>1430.599975585938</v>
       </c>
-      <c r="H494" t="n">
-        <v/>
-      </c>
       <c r="I494" t="n">
         <v>1441</v>
       </c>
-      <c r="J494" t="n">
-        <v/>
-      </c>
       <c r="K494" t="n">
         <v>68321</v>
       </c>
@@ -31156,15 +31094,9 @@
       <c r="G495" t="n">
         <v>223.1000061035156</v>
       </c>
-      <c r="H495" t="n">
-        <v/>
-      </c>
       <c r="I495" t="n">
         <v>224.9900054931641</v>
       </c>
-      <c r="J495" t="n">
-        <v/>
-      </c>
       <c r="K495" t="n">
         <v>428511</v>
       </c>
@@ -31225,15 +31157,9 @@
       <c r="G496" t="n">
         <v>5.360000133514404</v>
       </c>
-      <c r="H496" t="n">
-        <v/>
-      </c>
       <c r="I496" t="n">
         <v>5.440000057220459</v>
       </c>
-      <c r="J496" t="n">
-        <v/>
-      </c>
       <c r="K496" t="n">
         <v>103920</v>
       </c>
@@ -31260,7 +31186,6 @@
           <t>Kritika Kamra on National Handloom Day: We need to make handloom feel fun again - The Times of India</t>
         </is>
       </c>
-      <c r="Q496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -31290,15 +31215,9 @@
       <c r="G497" t="n">
         <v>64.30000305175781</v>
       </c>
-      <c r="H497" t="n">
-        <v/>
-      </c>
       <c r="I497" t="n">
         <v>65.01999664306641</v>
       </c>
-      <c r="J497" t="n">
-        <v/>
-      </c>
       <c r="K497" t="n">
         <v>136747</v>
       </c>
@@ -31359,15 +31278,9 @@
       <c r="G498" t="n">
         <v>307.7000122070312</v>
       </c>
-      <c r="H498" t="n">
-        <v/>
-      </c>
       <c r="I498" t="n">
         <v>310.1000061035156</v>
       </c>
-      <c r="J498" t="n">
-        <v/>
-      </c>
       <c r="K498" t="n">
         <v>29324</v>
       </c>
@@ -31428,15 +31341,9 @@
       <c r="G499" t="n">
         <v>9</v>
       </c>
-      <c r="H499" t="n">
-        <v/>
-      </c>
       <c r="I499" t="n">
         <v>9.050000190734863</v>
       </c>
-      <c r="J499" t="n">
-        <v/>
-      </c>
       <c r="K499" t="n">
         <v>1619287</v>
       </c>
@@ -31497,15 +31404,9 @@
       <c r="G500" t="n">
         <v>238.6000061035156</v>
       </c>
-      <c r="H500" t="n">
-        <v/>
-      </c>
       <c r="I500" t="n">
         <v>243.5500030517578</v>
       </c>
-      <c r="J500" t="n">
-        <v/>
-      </c>
       <c r="K500" t="n">
         <v>182954</v>
       </c>
@@ -31566,15 +31467,9 @@
       <c r="G501" t="n">
         <v>63.59999847412109</v>
       </c>
-      <c r="H501" t="n">
-        <v/>
-      </c>
       <c r="I501" t="n">
         <v>63.2400016784668</v>
       </c>
-      <c r="J501" t="n">
-        <v/>
-      </c>
       <c r="K501" t="n">
         <v>1074943</v>
       </c>
@@ -31604,6 +31499,1346 @@
       <c r="Q501" t="inlineStr">
         <is>
           <t>SONAM Limited (SONAMLTD.NS) Edges Higher: Support and Resistance Levels in Focus - High Volume Node - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>1</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>MANALIPETC.NS</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Manali Petrochemicals Limited</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>75</v>
+      </c>
+      <c r="F502" t="n">
+        <v>84.80000305175781</v>
+      </c>
+      <c r="G502" t="n">
+        <v>73.62000274658203</v>
+      </c>
+      <c r="H502" t="n">
+        <v>83.37999725341797</v>
+      </c>
+      <c r="I502" t="n">
+        <v>73.36000061035156</v>
+      </c>
+      <c r="J502" t="n">
+        <v>83.37999725341797</v>
+      </c>
+      <c r="K502" t="n">
+        <v>52795527</v>
+      </c>
+      <c r="L502" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>Manali Petrochemicals Share Price - Live NSE: MANALIPETC Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>Manali Petrochemicals Share Price - Live NSE: MANALIPETC Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr"/>
+      <c r="P502" t="inlineStr"/>
+      <c r="Q502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>2</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>INNOVISION.NS</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Innovision Limited</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>296.7000122070312</v>
+      </c>
+      <c r="F503" t="n">
+        <v>296.7000122070312</v>
+      </c>
+      <c r="G503" t="n">
+        <v>257</v>
+      </c>
+      <c r="H503" t="n">
+        <v>274.6499938964844</v>
+      </c>
+      <c r="I503" t="n">
+        <v>247.25</v>
+      </c>
+      <c r="J503" t="n">
+        <v>274.6499938964844</v>
+      </c>
+      <c r="K503" t="n">
+        <v>313940</v>
+      </c>
+      <c r="L503" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>INNOVISION LIMITED Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>Innovision Ltd wins ₹205.20 Cr NHAI order for Kishangarh plaza - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>Innovision Ltd wins ₹205.20 Cr NHAI order for Kishangarh plaza - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>Innovision Ltd Falls to 52-Week Low of Rs 265.2 as Sell-Off Deepens - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>Innovision wins order worth ₹9.23 Cr from NHAI for toll collection - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>3</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>ASHOKA.NS</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Ashoka Buildcon Limited</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>117.6999969482422</v>
+      </c>
+      <c r="F504" t="n">
+        <v>129</v>
+      </c>
+      <c r="G504" t="n">
+        <v>116.9100036621094</v>
+      </c>
+      <c r="H504" t="n">
+        <v>122.2300033569336</v>
+      </c>
+      <c r="I504" t="n">
+        <v>112.6500015258789</v>
+      </c>
+      <c r="J504" t="n">
+        <v>122.2300033569336</v>
+      </c>
+      <c r="K504" t="n">
+        <v>88783641</v>
+      </c>
+      <c r="L504" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>Ashoka Buildcon shares rally 13% on bagging ₹602-crore order from RVNL - Business Standard</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>Ashoka Buildcon shares rally 15% on bagging order from RVNL; check details - Upstox</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>Ashoka Buildcon shares rally 15% on bagging order from RVNL; check details - Upstox</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>Ashoka Buildcon shares rally 10% after securing Rs 602 crore order from RVNL - The Economic Times</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>Buzzing Stocks: Ultramarine and Pigments, Northern Arc Capital gain on block deals; Ashoka Buildcon jumps... - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>4</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>ULTRAMAR.NS</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Ultramarine &amp; Pigments Limited</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>416.2000122070312</v>
+      </c>
+      <c r="F505" t="n">
+        <v>448.6499938964844</v>
+      </c>
+      <c r="G505" t="n">
+        <v>416.2000122070312</v>
+      </c>
+      <c r="H505" t="n">
+        <v>442.25</v>
+      </c>
+      <c r="I505" t="n">
+        <v>411.2999877929688</v>
+      </c>
+      <c r="J505" t="n">
+        <v>442.25</v>
+      </c>
+      <c r="K505" t="n">
+        <v>404133</v>
+      </c>
+      <c r="L505" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>Thirumalai Chemicals approves sale of 5% stake in Ultramarine - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>Ultramarine &amp; Pigments block deal today: 14.60 lakh shares trade after Thirumalai Chemicals proposed 5% stake sale - Business Upturn</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>Thirumalai Chemicals to Divest 5% Stake in Ultramarine &amp; Pigments Limited - Whalesbook</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>Ultramarine &amp; Pigments block deal today: 14.60 lakh shares trade after Thirumalai Chemicals proposed 5% stake sale - Business Upturn</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>Thirumalai Chemicals to Sell Part of Promoter Stake in Ultramarine &amp; Pigments - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>5</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>OLAELEC.NS</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Ola Electric Mobility Limited</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>39</v>
+      </c>
+      <c r="F506" t="n">
+        <v>41.9900016784668</v>
+      </c>
+      <c r="G506" t="n">
+        <v>38.31000137329102</v>
+      </c>
+      <c r="H506" t="n">
+        <v>41.84000015258789</v>
+      </c>
+      <c r="I506" t="n">
+        <v>38.97999954223633</v>
+      </c>
+      <c r="J506" t="n">
+        <v>41.84000015258789</v>
+      </c>
+      <c r="K506" t="n">
+        <v>109553489</v>
+      </c>
+      <c r="L506" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>Ola Electric Share Price - Live NSE: OLAELEC Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>Stocks To Buy or Sell Today, August 31, 2026: Ola Electric and HDFC Bank Among Shares That May Remain in - LatestLY</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>OLA Electric Mobility Share Price rises 5.82%: analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>Ola Electric Heralds New ‘LFP Era’ as Gigafactory Ramp-Up Powers Thousands of EVs - The Globe and Mail</t>
+        </is>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>Stocks To Buy or Sell Today, August 31, 2026: Ola Electric and HDFC Bank Among Shares That May Remain in - LatestLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>6</v>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>GAEL.NS</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Gujarat Ambuja Exports Limited</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>167.9900054931641</v>
+      </c>
+      <c r="F507" t="n">
+        <v>177.9900054931641</v>
+      </c>
+      <c r="G507" t="n">
+        <v>167.3699951171875</v>
+      </c>
+      <c r="H507" t="n">
+        <v>176.9700012207031</v>
+      </c>
+      <c r="I507" t="n">
+        <v>166.9799957275391</v>
+      </c>
+      <c r="J507" t="n">
+        <v>176.9700012207031</v>
+      </c>
+      <c r="K507" t="n">
+        <v>1785601</v>
+      </c>
+      <c r="L507" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>Aptargroup segment pres., CEO designate Gael Touya sells $500k in shares - Investing.com</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>Aptargroup segment pres., CEO designate Gael Touya sells $500k in shares - Investing.com</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr"/>
+      <c r="P507" t="inlineStr"/>
+      <c r="Q507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>7</v>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>BAJAJHIND.NS</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="F508" t="n">
+        <v>23.10000038146973</v>
+      </c>
+      <c r="G508" t="n">
+        <v>21.04000091552734</v>
+      </c>
+      <c r="H508" t="n">
+        <v>22.80999946594238</v>
+      </c>
+      <c r="I508" t="n">
+        <v>21.67000007629395</v>
+      </c>
+      <c r="J508" t="n">
+        <v>22.80999946594238</v>
+      </c>
+      <c r="K508" t="n">
+        <v>90942610</v>
+      </c>
+      <c r="L508" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>Dwarikesh, Bajaj Hindusthan, other sugar stocks hit 52-week high as govt tightens stockholding limit - TradingView</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>Dwarikesh, Bajaj Hindusthan, other sugar stocks hit 52-week high as govt tightens stockholding limit - TradingView</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>Most Active Equities on August 19, 2026 at 3:00 PM IST - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar turns profitable in FY26, sets Aug 27 AGM - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>8</v>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>PARACABLES.NS</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Paramount Communications Limited</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>62</v>
+      </c>
+      <c r="F509" t="n">
+        <v>67.63999938964844</v>
+      </c>
+      <c r="G509" t="n">
+        <v>61.31000137329102</v>
+      </c>
+      <c r="H509" t="n">
+        <v>65.59999847412109</v>
+      </c>
+      <c r="I509" t="n">
+        <v>62.36999893188477</v>
+      </c>
+      <c r="J509" t="n">
+        <v>65.59999847412109</v>
+      </c>
+      <c r="K509" t="n">
+        <v>5150083</v>
+      </c>
+      <c r="L509" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>Paramount Communications approves preferential issue at EGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>Paramount Communications approves preferential issue at EGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>Paramount Opens One-Year SEBI-Mandated Window to Dematerialise Legacy Physical Shares - TipRanks</t>
+        </is>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>Paramount Communications Publishes Q1 FY27 Investor Call Recording - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>9</v>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM.NS</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Sudeep Pharma Limited</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>1179</v>
+      </c>
+      <c r="F510" t="n">
+        <v>1209.699951171875</v>
+      </c>
+      <c r="G510" t="n">
+        <v>1143.650024414062</v>
+      </c>
+      <c r="H510" t="n">
+        <v>1209.699951171875</v>
+      </c>
+      <c r="I510" t="n">
+        <v>1152.099975585938</v>
+      </c>
+      <c r="J510" t="n">
+        <v>1209.699951171875</v>
+      </c>
+      <c r="K510" t="n">
+        <v>327903</v>
+      </c>
+      <c r="L510" t="n">
+        <v>5</v>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM Stock Price and Chart — NSE:SUDEEPPHRM - TradingView</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM Stock Price and Chart — NSE:SUDEEPPHRM - TradingView</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>SUDEEP PHARMA LIMITED Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM Forecast — Price Target — Prediction for 2027 - TradingView</t>
+        </is>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>Sudeep Pharma (SUDEEPPHRM) Edges Higher: Stock Holds Above Key Support Zone - Covered Call Trade - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>10</v>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>SHADOWFAX.NS</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Shadowfax Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>246.6999969482422</v>
+      </c>
+      <c r="F511" t="n">
+        <v>259.8900146484375</v>
+      </c>
+      <c r="G511" t="n">
+        <v>244.6600036621094</v>
+      </c>
+      <c r="H511" t="n">
+        <v>257.5799865722656</v>
+      </c>
+      <c r="I511" t="n">
+        <v>245.3600006103516</v>
+      </c>
+      <c r="J511" t="n">
+        <v>257.5799865722656</v>
+      </c>
+      <c r="K511" t="n">
+        <v>3142149</v>
+      </c>
+      <c r="L511" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>Shadowfax Technologies Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>Shadowfax publishes 11th AGM notice in Financial Express, Hosadigantha - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>Qualcomm Ventures affiliate sells 75 lakh Shadowfax shares for Rs 184 crore - Indian Startup News</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>Qualcomm Offloads Shadowfax Shares Worth ₹184 Cr In Bulk Deal - Inc42</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>Qualcomm Ventures Sells 75 Lakh Shadowfax Shares For Rs 183.85 Cr In Block Deal - BW Disrupt</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>11</v>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>GANGAFORGE.NS</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Ganga Forging Limited</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>1.529999971389771</v>
+      </c>
+      <c r="F512" t="n">
+        <v>1.690000057220459</v>
+      </c>
+      <c r="G512" t="n">
+        <v>1.529999971389771</v>
+      </c>
+      <c r="H512" t="n">
+        <v>1.690000057220459</v>
+      </c>
+      <c r="I512" t="n">
+        <v>1.610000014305115</v>
+      </c>
+      <c r="J512" t="n">
+        <v>1.690000057220459</v>
+      </c>
+      <c r="K512" t="n">
+        <v>13516262</v>
+      </c>
+      <c r="L512" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>Ganga Forging submits Letter of Offer for ₹32.96 crore rights issue - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>Ganga Forging rights issue sees 120% subscription, trading begins - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>Ganga Forging Limited (GANGAFORGE.NS) Q4 FY2026 Earnings: Marginal Loss Amid Modest Revenue - EPS Consistency Score - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>NARMADESH Stock Price and Chart — BSE:NARMADESH - TradingView</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>Ganga Forging: Will Railway Diversification Boost the Stock Further? - Investing.com India</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>12</v>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>AASTHA.NS</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Aastha Spintex Limited</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>81.05000305175781</v>
+      </c>
+      <c r="F513" t="n">
+        <v>85.26000213623047</v>
+      </c>
+      <c r="G513" t="n">
+        <v>81.05000305175781</v>
+      </c>
+      <c r="H513" t="n">
+        <v>83.51999664306641</v>
+      </c>
+      <c r="I513" t="n">
+        <v>79.61000061035156</v>
+      </c>
+      <c r="J513" t="n">
+        <v>83.51999664306641</v>
+      </c>
+      <c r="K513" t="n">
+        <v>894675</v>
+      </c>
+      <c r="L513" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>AASTHA SPINTEX LIMITED Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>Aastha Spintex Ltd is Rated Sell - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>Aastha Spintex shares extend rise to 3rd day, hit upper circuit; check details - TradingView</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>Aastha Spintex Share Price News and Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>Aastha Spintex sets Sept 16 AGM for bonus shares, capital hike - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>13</v>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>AVALON.NS</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Avalon Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>2244</v>
+      </c>
+      <c r="F514" t="n">
+        <v>2342</v>
+      </c>
+      <c r="G514" t="n">
+        <v>2193</v>
+      </c>
+      <c r="H514" t="n">
+        <v>2337.89990234375</v>
+      </c>
+      <c r="I514" t="n">
+        <v>2231.699951171875</v>
+      </c>
+      <c r="J514" t="n">
+        <v>2337.89990234375</v>
+      </c>
+      <c r="K514" t="n">
+        <v>280082</v>
+      </c>
+      <c r="L514" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>Avalon Technologies Has Returned 158% in One Year. The Business Behind That Move Is More Interesting Than the Stock Price - Dalal Street Investment Journal</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>Avalon Technologies Has Returned 158% in One Year. The Business Behind That Move Is More Interesting Than the Stock Price - Dalal Street Investment Journal</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>Why is Avalon Advanced Materials stock surging today? - Investing.com</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>Avalon Technologies Share Price Today Near One-Year High - Univest</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>Tech view: Avalon Technologies, Healthcare Global on analyst radar - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>14</v>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>RATNAVEER.NS</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Ratnaveer Precision Engineering Limited</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>297</v>
+      </c>
+      <c r="F515" t="n">
+        <v>314.8999938964844</v>
+      </c>
+      <c r="G515" t="n">
+        <v>296</v>
+      </c>
+      <c r="H515" t="n">
+        <v>308.8900146484375</v>
+      </c>
+      <c r="I515" t="n">
+        <v>294.9500122070312</v>
+      </c>
+      <c r="J515" t="n">
+        <v>308.8900146484375</v>
+      </c>
+      <c r="K515" t="n">
+        <v>8120919</v>
+      </c>
+      <c r="L515" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>Ratnaveer Precision completes dispatch of ₹330 crore rights issue offer - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>Ratnaveer Precision Engineering Appoints Kashyap Shah as Independent Director for 5-Year Term - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>Ratnaveer Precision Board Approves 1.25 Crore Shares Rights Issue At ₹264 Totaling ₹330 Crore - Sahi</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>Ratnaveer Approves ₹330 Crore Rights Issue at ₹264; Shares Touch All-Time High of ₹282.50 - ACCESS Newswire</t>
+        </is>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>Ratnaveer Approves Rs 330 Crore Rights Issue at Rs 264; Shares Touch All-Time High of Rs 282.50 - Deccan Chronicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>15</v>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>SKMEGGPROD.NS</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>SKM Egg Products Export (India) Limited</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>257.1000061035156</v>
+      </c>
+      <c r="F516" t="n">
+        <v>274.2999877929688</v>
+      </c>
+      <c r="G516" t="n">
+        <v>255.1000061035156</v>
+      </c>
+      <c r="H516" t="n">
+        <v>269.5299987792969</v>
+      </c>
+      <c r="I516" t="n">
+        <v>257.5499877929688</v>
+      </c>
+      <c r="J516" t="n">
+        <v>269.5299987792969</v>
+      </c>
+      <c r="K516" t="n">
+        <v>638899</v>
+      </c>
+      <c r="L516" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>Impressive Earnings May Not Tell The Whole Story For SKM Egg Products Export (India) (NSE:SKMEGGPROD) - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>SKM Egg Products Export (SKMEGGPROD.NS) Rises 1.53%; Support and Resistance Levels in Focus - Trend Reversal Picks - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>SKM Egg Products Export (India) Limited Schedules Board Meeting on 22 May 2026 to Approve Audited Financial Results - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>SKM Egg Products Export (India) Limited (NSE:SKMEGGPROD) Stock's 27% Dive Might Signal An Opportunity But It Requires Some Scrutiny - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q516" t="inlineStr">
+        <is>
+          <t>SKMEGGPROD Q2 2026 Earnings: Revenue Surges 54% YoY to ₹768 Crore, EPS at ₹19.7 Amid Stock Decline - Analyst Coverage Count - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>16</v>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>ATLANTAELE.NS</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Atlanta Electricals Limited</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>1755</v>
+      </c>
+      <c r="F517" t="n">
+        <v>1845</v>
+      </c>
+      <c r="G517" t="n">
+        <v>1745</v>
+      </c>
+      <c r="H517" t="n">
+        <v>1825.199951171875</v>
+      </c>
+      <c r="I517" t="n">
+        <v>1745.099975585938</v>
+      </c>
+      <c r="J517" t="n">
+        <v>1825.199951171875</v>
+      </c>
+      <c r="K517" t="n">
+        <v>260579</v>
+      </c>
+      <c r="L517" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>ATLANTA ELECTRICALS LTD Share Price - Live NSE: ATLANTAELE Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>ATLANTA ELECTRICALS LTD Share Price - Live NSE: ATLANTAELE Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr"/>
+      <c r="P517" t="inlineStr"/>
+      <c r="Q517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>17</v>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>UTTAMSUGAR.NS</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Limited</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="F518" t="n">
+        <v>318.7000122070312</v>
+      </c>
+      <c r="G518" t="n">
+        <v>296.5</v>
+      </c>
+      <c r="H518" t="n">
+        <v>312.1799926757812</v>
+      </c>
+      <c r="I518" t="n">
+        <v>299.5499877929688</v>
+      </c>
+      <c r="J518" t="n">
+        <v>312.1799926757812</v>
+      </c>
+      <c r="K518" t="n">
+        <v>462306</v>
+      </c>
+      <c r="L518" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Q1 Net Profit Plummets 94.69% YoY to ₹85 lakh - Sahi</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Share Price Today: 8.75% rise - Univest</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Ltd. Stock News: Price Increase Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Share Price Jumps; Technicals in Focus - Univest</t>
+        </is>
+      </c>
+      <c r="Q518" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Share Price Today: 8.75% rise - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>18</v>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>APCOTEXIND.NS</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Apcotex Industries Limited</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>628.8499755859375</v>
+      </c>
+      <c r="F519" t="n">
+        <v>656</v>
+      </c>
+      <c r="G519" t="n">
+        <v>622.0499877929688</v>
+      </c>
+      <c r="H519" t="n">
+        <v>649.9000244140625</v>
+      </c>
+      <c r="I519" t="n">
+        <v>625.25</v>
+      </c>
+      <c r="J519" t="n">
+        <v>649.9000244140625</v>
+      </c>
+      <c r="K519" t="n">
+        <v>388060</v>
+      </c>
+      <c r="L519" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>APCOTEXIND Forecast — Price Target — Prediction for 2027 - TradingView</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>Apcotex Industries Ltd. Share Price Today: 52-Week Peak - Univest</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>Apcotex Industries Limited (NSE:APCOTEXIND) Analysts Are Pretty Bullish On The Stock After Recent Results - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>Apcotex Industries Limited Issues Public Notice for Transfer of Equity Shares and Dividend to IEPF Authority - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q519" t="inlineStr">
+        <is>
+          <t>Apcotex Industries Ltd. (APCOTEXIND) Share Price Hits New 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>19</v>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS.NS</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>TD Power Systems Limited</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>760</v>
+      </c>
+      <c r="F520" t="n">
+        <v>784.9000244140625</v>
+      </c>
+      <c r="G520" t="n">
+        <v>751.4000244140625</v>
+      </c>
+      <c r="H520" t="n">
+        <v>782.2999877929688</v>
+      </c>
+      <c r="I520" t="n">
+        <v>752.7000122070312</v>
+      </c>
+      <c r="J520" t="n">
+        <v>782.2999877929688</v>
+      </c>
+      <c r="K520" t="n">
+        <v>2149783</v>
+      </c>
+      <c r="L520" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>TD Power Systems Limited: Shareholders Board Members Managers and Company Profile | INE419M01035 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>TD Power Systems: Promoter Group Adjusts Ownership - InvestyWise</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>Up 27x in 5 yrs! Why this multibagger smallcap stock showing 50% fall in some trading apps today? - Business Today</t>
+        </is>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>TD Power Systems Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q520" t="inlineStr">
+        <is>
+          <t>Brokers Are Upgrading Their Views On TD Power Systems Limited (NSE:TDPOWERSYS) With These New Forecasts - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>20</v>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>CYIENT.NS</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Cyient Limited</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>1111.349975585938</v>
+      </c>
+      <c r="F521" t="n">
+        <v>1155</v>
+      </c>
+      <c r="G521" t="n">
+        <v>1081.349975585938</v>
+      </c>
+      <c r="H521" t="n">
+        <v>1150.650024414062</v>
+      </c>
+      <c r="I521" t="n">
+        <v>1107.449951171875</v>
+      </c>
+      <c r="J521" t="n">
+        <v>1150.650024414062</v>
+      </c>
+      <c r="K521" t="n">
+        <v>1389799</v>
+      </c>
+      <c r="L521" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>Cyient shares rocket 8% after investor day, but brokerages see up to 24% downside. Here’s why - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>Cyient Confirms Postal Ballot Notice Dispatch and Newspaper Ads for ₹720 Cr Buyback - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>Cyient shares jump 4% after investor day; JPMorgan sees ₹1,050 target on double-digit growth outlook - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>Cyient acquires Tao Digital for US$218m to boost AI capabilities - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q521" t="inlineStr">
+        <is>
+          <t>Cyient Stock: JPMorgan Sees Transformation, Morgan Stanley Waits for Execution - NDTV Profit</t>
         </is>
       </c>
     </row>
@@ -31618,7 +32853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q501"/>
+  <dimension ref="A1:Q521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61224,15 +62459,9 @@
       <c r="G483" t="n">
         <v>223.1000061035156</v>
       </c>
-      <c r="H483" t="n">
-        <v/>
-      </c>
       <c r="I483" t="n">
         <v>224.9900054931641</v>
       </c>
-      <c r="J483" t="n">
-        <v/>
-      </c>
       <c r="K483" t="n">
         <v>428511</v>
       </c>
@@ -61293,15 +62522,9 @@
       <c r="G484" t="n">
         <v>8.050000190734863</v>
       </c>
-      <c r="H484" t="n">
-        <v/>
-      </c>
       <c r="I484" t="n">
         <v>7.980000019073486</v>
       </c>
-      <c r="J484" t="n">
-        <v/>
-      </c>
       <c r="K484" t="n">
         <v>1263568</v>
       </c>
@@ -61362,15 +62585,9 @@
       <c r="G485" t="n">
         <v>1135</v>
       </c>
-      <c r="H485" t="n">
-        <v/>
-      </c>
       <c r="I485" t="n">
         <v>1135.800048828125</v>
       </c>
-      <c r="J485" t="n">
-        <v/>
-      </c>
       <c r="K485" t="n">
         <v>725</v>
       </c>
@@ -61431,15 +62648,9 @@
       <c r="G486" t="n">
         <v>45.70000076293945</v>
       </c>
-      <c r="H486" t="n">
-        <v/>
-      </c>
       <c r="I486" t="n">
         <v>46.20999908447266</v>
       </c>
-      <c r="J486" t="n">
-        <v/>
-      </c>
       <c r="K486" t="n">
         <v>2307</v>
       </c>
@@ -61500,15 +62711,9 @@
       <c r="G487" t="n">
         <v>550.4000244140625</v>
       </c>
-      <c r="H487" t="n">
-        <v/>
-      </c>
       <c r="I487" t="n">
         <v>559.25</v>
       </c>
-      <c r="J487" t="n">
-        <v/>
-      </c>
       <c r="K487" t="n">
         <v>121639</v>
       </c>
@@ -61569,15 +62774,9 @@
       <c r="G488" t="n">
         <v>42</v>
       </c>
-      <c r="H488" t="n">
-        <v/>
-      </c>
       <c r="I488" t="n">
         <v>43.31000137329102</v>
       </c>
-      <c r="J488" t="n">
-        <v/>
-      </c>
       <c r="K488" t="n">
         <v>166991</v>
       </c>
@@ -61638,15 +62837,9 @@
       <c r="G489" t="n">
         <v>691.9500122070312</v>
       </c>
-      <c r="H489" t="n">
-        <v/>
-      </c>
       <c r="I489" t="n">
         <v>692</v>
       </c>
-      <c r="J489" t="n">
-        <v/>
-      </c>
       <c r="K489" t="n">
         <v>199388</v>
       </c>
@@ -61707,15 +62900,9 @@
       <c r="G490" t="n">
         <v>460</v>
       </c>
-      <c r="H490" t="n">
-        <v/>
-      </c>
       <c r="I490" t="n">
         <v>466</v>
       </c>
-      <c r="J490" t="n">
-        <v/>
-      </c>
       <c r="K490" t="n">
         <v>1424904</v>
       </c>
@@ -61776,15 +62963,9 @@
       <c r="G491" t="n">
         <v>3361.60009765625</v>
       </c>
-      <c r="H491" t="n">
-        <v/>
-      </c>
       <c r="I491" t="n">
         <v>3473.5</v>
       </c>
-      <c r="J491" t="n">
-        <v/>
-      </c>
       <c r="K491" t="n">
         <v>26505</v>
       </c>
@@ -61845,15 +63026,9 @@
       <c r="G492" t="n">
         <v>176.5</v>
       </c>
-      <c r="H492" t="n">
-        <v/>
-      </c>
       <c r="I492" t="n">
         <v>178.5800018310547</v>
       </c>
-      <c r="J492" t="n">
-        <v/>
-      </c>
       <c r="K492" t="n">
         <v>402068</v>
       </c>
@@ -61875,8 +63050,6 @@
           <t>Stocks To Buy or Sell Today, August 12, 2026: Cochin Shipyard and Poonawalla Fincorp Among Shares That May - LatestLY</t>
         </is>
       </c>
-      <c r="P492" t="inlineStr"/>
-      <c r="Q492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -61906,15 +63079,9 @@
       <c r="G493" t="n">
         <v>1430.599975585938</v>
       </c>
-      <c r="H493" t="n">
-        <v/>
-      </c>
       <c r="I493" t="n">
         <v>1441</v>
       </c>
-      <c r="J493" t="n">
-        <v/>
-      </c>
       <c r="K493" t="n">
         <v>68321</v>
       </c>
@@ -61975,15 +63142,9 @@
       <c r="G494" t="n">
         <v>1872</v>
       </c>
-      <c r="H494" t="n">
-        <v/>
-      </c>
       <c r="I494" t="n">
         <v>1887.199951171875</v>
       </c>
-      <c r="J494" t="n">
-        <v/>
-      </c>
       <c r="K494" t="n">
         <v>115933</v>
       </c>
@@ -62044,15 +63205,9 @@
       <c r="G495" t="n">
         <v>5.360000133514404</v>
       </c>
-      <c r="H495" t="n">
-        <v/>
-      </c>
       <c r="I495" t="n">
         <v>5.440000057220459</v>
       </c>
-      <c r="J495" t="n">
-        <v/>
-      </c>
       <c r="K495" t="n">
         <v>103920</v>
       </c>
@@ -62079,7 +63234,6 @@
           <t>Kritika Kamra on National Handloom Day: We need to make handloom feel fun again - The Times of India</t>
         </is>
       </c>
-      <c r="Q495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -62109,15 +63263,9 @@
       <c r="G496" t="n">
         <v>64.30000305175781</v>
       </c>
-      <c r="H496" t="n">
-        <v/>
-      </c>
       <c r="I496" t="n">
         <v>65.01999664306641</v>
       </c>
-      <c r="J496" t="n">
-        <v/>
-      </c>
       <c r="K496" t="n">
         <v>136747</v>
       </c>
@@ -62178,15 +63326,9 @@
       <c r="G497" t="n">
         <v>307.7000122070312</v>
       </c>
-      <c r="H497" t="n">
-        <v/>
-      </c>
       <c r="I497" t="n">
         <v>310.1000061035156</v>
       </c>
-      <c r="J497" t="n">
-        <v/>
-      </c>
       <c r="K497" t="n">
         <v>29324</v>
       </c>
@@ -62247,15 +63389,9 @@
       <c r="G498" t="n">
         <v>9</v>
       </c>
-      <c r="H498" t="n">
-        <v/>
-      </c>
       <c r="I498" t="n">
         <v>9.050000190734863</v>
       </c>
-      <c r="J498" t="n">
-        <v/>
-      </c>
       <c r="K498" t="n">
         <v>1619287</v>
       </c>
@@ -62316,15 +63452,9 @@
       <c r="G499" t="n">
         <v>238.6000061035156</v>
       </c>
-      <c r="H499" t="n">
-        <v/>
-      </c>
       <c r="I499" t="n">
         <v>243.5500030517578</v>
       </c>
-      <c r="J499" t="n">
-        <v/>
-      </c>
       <c r="K499" t="n">
         <v>182954</v>
       </c>
@@ -62385,15 +63515,9 @@
       <c r="G500" t="n">
         <v>63.59999847412109</v>
       </c>
-      <c r="H500" t="n">
-        <v/>
-      </c>
       <c r="I500" t="n">
         <v>63.2400016784668</v>
       </c>
-      <c r="J500" t="n">
-        <v/>
-      </c>
       <c r="K500" t="n">
         <v>1074943</v>
       </c>
@@ -62454,15 +63578,9 @@
       <c r="G501" t="n">
         <v>55.20999908447266</v>
       </c>
-      <c r="H501" t="n">
-        <v/>
-      </c>
       <c r="I501" t="n">
         <v>56.15999984741211</v>
       </c>
-      <c r="J501" t="n">
-        <v/>
-      </c>
       <c r="K501" t="n">
         <v>774</v>
       </c>
@@ -62494,6 +63612,1370 @@
           <t>OBCL promoter group boosts stake to 9.80% with 67,081 share buy - scanx.trade</t>
         </is>
       </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>1</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>WEL.NS</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Wonder Electricals Limited</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>89.81999969482422</v>
+      </c>
+      <c r="F502" t="n">
+        <v>89.81999969482422</v>
+      </c>
+      <c r="G502" t="n">
+        <v>89.81999969482422</v>
+      </c>
+      <c r="H502" t="n">
+        <v>89.81999969482422</v>
+      </c>
+      <c r="I502" t="n">
+        <v>99.80000305175781</v>
+      </c>
+      <c r="J502" t="n">
+        <v>89.81999969482422</v>
+      </c>
+      <c r="K502" t="n">
+        <v>386517</v>
+      </c>
+      <c r="L502" t="n">
+        <v>-10</v>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>Integrated Wellness Acquisition Corp (WEL-UN) Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>Integrated Wellness Acquisition Corp (WEL-UN) Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>Wonder Electricals Share Price Today After Sharp Fall - Univest</t>
+        </is>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>Integrated Wellness Acquisition Corp (WEL-UN) Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+        </is>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>Wonder Electricals Share Price: stock news and analysis - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>2</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>DCI.NS</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Dc Infotech And Communication Limited</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>416</v>
+      </c>
+      <c r="F503" t="n">
+        <v>424.3999938964844</v>
+      </c>
+      <c r="G503" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="H503" t="n">
+        <v>375.7999877929688</v>
+      </c>
+      <c r="I503" t="n">
+        <v>410.0499877929688</v>
+      </c>
+      <c r="J503" t="n">
+        <v>375.7999877929688</v>
+      </c>
+      <c r="K503" t="n">
+        <v>1013714</v>
+      </c>
+      <c r="L503" t="n">
+        <v>-8.35</v>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>DCI Share Price Rise: Fundamentals, Peers and Market Cap - Univest</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>104,544 Shares in Donaldson Company, Inc. $DCI Purchased by Caisse de depot et placement du Quebec - MarketBeat</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>Donaldson (DCI) Stock Slips After Record Margins Set A Higher Bar - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>Donaldson (DCI) Stock Looks Reasonable On Earnings But Rich On Cash Flow - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>Donaldson (DCI) Stock Slips After Record Margins Set A Higher Bar - Sahm</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>3</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>ZEEL.NS</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Zee Entertainment Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>101</v>
+      </c>
+      <c r="F504" t="n">
+        <v>101.1800003051758</v>
+      </c>
+      <c r="G504" t="n">
+        <v>86.90000152587891</v>
+      </c>
+      <c r="H504" t="n">
+        <v>94.62000274658203</v>
+      </c>
+      <c r="I504" t="n">
+        <v>101.5100021362305</v>
+      </c>
+      <c r="J504" t="n">
+        <v>94.62000274658203</v>
+      </c>
+      <c r="K504" t="n">
+        <v>94643991</v>
+      </c>
+      <c r="L504" t="n">
+        <v>-6.79</v>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>ZEEL tanks 15% as Chandra's insolvency resolution plan faces fresh hurdle - Business Standard</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>Zee Entertainment shares extends losing streak as Subhash Chandra insolvency appeal rattles investors - Storyboard18</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>Zee Entertainment shares extends losing streak as Subhash Chandra insolvency appeal rattles investors - Storyboard18</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>ZEE Entertainment shares tumble 14%, take losing to 4th session; key details - Business Today</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>Zee Share Price Crash 11% After SEBI Action; Company Says Fundraising Plan Remains Unaffected - India Infoline</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>4</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>NEWGEN.NS</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Newgen Software Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>562</v>
+      </c>
+      <c r="F505" t="n">
+        <v>562.0499877929688</v>
+      </c>
+      <c r="G505" t="n">
+        <v>529.25</v>
+      </c>
+      <c r="H505" t="n">
+        <v>531.5499877929688</v>
+      </c>
+      <c r="I505" t="n">
+        <v>567.0999755859375</v>
+      </c>
+      <c r="J505" t="n">
+        <v>531.5499877929688</v>
+      </c>
+      <c r="K505" t="n">
+        <v>1809763</v>
+      </c>
+      <c r="L505" t="n">
+        <v>-6.27</v>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>Mid-Cap IT Stock Newgen Software Surges 18%, Extends 3-Day Rally to 35%; Analysts See More Upside Ahead - Goodreturns</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>Newgen Software Technologies Downgraded to Sell Amidst Mixed Financial and Technical Signals - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>Newgen Software Technologies Share Price today: key move - Univest</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>Newgen Software Technologies Downgraded to Sell Amidst Mixed Financial and Technical Signals - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>Newgen Software to host investor meet at Elara India Dialogue 2026 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>5</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>KELLTONTEC.NS</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Kellton Tech Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>15</v>
+      </c>
+      <c r="F506" t="n">
+        <v>15.05000019073486</v>
+      </c>
+      <c r="G506" t="n">
+        <v>14.10000038146973</v>
+      </c>
+      <c r="H506" t="n">
+        <v>14.21000003814697</v>
+      </c>
+      <c r="I506" t="n">
+        <v>15.06999969482422</v>
+      </c>
+      <c r="J506" t="n">
+        <v>14.21000003814697</v>
+      </c>
+      <c r="K506" t="n">
+        <v>3295887</v>
+      </c>
+      <c r="L506" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>IT Stock Announces Q3 Results, Revenue Crosses Rs 300 Cr; Watch The Stock Now? - Goodreturns</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>Kellton Tech Solutions Share Price: price rise and valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>Kellton Tech Solutions Share Price: price rise and valuation - Univest</t>
+        </is>
+      </c>
+      <c r="P506" t="inlineStr"/>
+      <c r="Q506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>6</v>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>KAYNES.NS</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Kaynes Technology India Limited</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>3943</v>
+      </c>
+      <c r="F507" t="n">
+        <v>3943</v>
+      </c>
+      <c r="G507" t="n">
+        <v>3717</v>
+      </c>
+      <c r="H507" t="n">
+        <v>3718.300048828125</v>
+      </c>
+      <c r="I507" t="n">
+        <v>3943.10009765625</v>
+      </c>
+      <c r="J507" t="n">
+        <v>3718.300048828125</v>
+      </c>
+      <c r="K507" t="n">
+        <v>1487843</v>
+      </c>
+      <c r="L507" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>Kaynes Tech shares fall up to 5% as Investec raises balance sheet concerns - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>Kaynes Tech shares fall up to 5% as Investec raises balance sheet concerns - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>Prime Minister Modi Inaugurates Kaynes Semicon Manufacturing Plant in Ahmedabad - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>Kaynes Technology India Limited Just Missed EPS By 17%: Here's What Analysts Think Will Happen Next - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>Kaynes Technology Share Price rises 3.29% on market move - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>7</v>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>EXXARO.NS</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Exxaro Tiles Limited</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>7.409999847412109</v>
+      </c>
+      <c r="F508" t="n">
+        <v>7.409999847412109</v>
+      </c>
+      <c r="G508" t="n">
+        <v>6.670000076293945</v>
+      </c>
+      <c r="H508" t="n">
+        <v>7</v>
+      </c>
+      <c r="I508" t="n">
+        <v>7.409999847412109</v>
+      </c>
+      <c r="J508" t="n">
+        <v>7</v>
+      </c>
+      <c r="K508" t="n">
+        <v>1968875</v>
+      </c>
+      <c r="L508" t="n">
+        <v>-5.53</v>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>Momentum Stocks: Next Mediaworks, Exxaro, Tejas Networks gains up to 19% on sheer momentum - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>Next Mediaworks, Exxaro Shares See Sharp Price Swings - Whalesbook</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>Exxaro Tiles Standalone June 2026 Net Sales at Rs 73.79 crore, up 16.85% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>Eskom supplier Exxaro crashes as robust rand and rising costs tear into profits - news24.com</t>
+        </is>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>Exxaro Tiles Consolidated June 2026 Net Sales at Rs 85.22 crore, up 31.26% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>8</v>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>GVPTECH.NS</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>GVP Infotech Limited</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>9.369999885559082</v>
+      </c>
+      <c r="F509" t="n">
+        <v>9.390000343322754</v>
+      </c>
+      <c r="G509" t="n">
+        <v>8.319999694824219</v>
+      </c>
+      <c r="H509" t="n">
+        <v>8.569999694824219</v>
+      </c>
+      <c r="I509" t="n">
+        <v>9.029999732971191</v>
+      </c>
+      <c r="J509" t="n">
+        <v>8.569999694824219</v>
+      </c>
+      <c r="K509" t="n">
+        <v>570291</v>
+      </c>
+      <c r="L509" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>GVP Infotech Limited (GVPTECH.NS) Mar 2026 Earnings: Negative EPS Amid Modest Revenue - EPS Surprise History - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>GVP Infotech Limited (GVPTECH) Gains 1.47%; Near Key Resistance at ₹7.23 - IPO Entry Watch - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>GVP Infotech Limited (GVPTECH) Gains 1.47%; Near Key Resistance at ₹7.23 - IPO Entry Watch - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>GVP INFOTECH LIMITED Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>GVP Infotech Share Price Today - GVP Infotech Ltd. Stock Price Live NSE/BSE - HDFC Sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>9</v>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>RCF.NS</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Rashtriya Chemicals and Fertilizers Limited</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="F510" t="n">
+        <v>119.6999969482422</v>
+      </c>
+      <c r="G510" t="n">
+        <v>113.5999984741211</v>
+      </c>
+      <c r="H510" t="n">
+        <v>113.7699966430664</v>
+      </c>
+      <c r="I510" t="n">
+        <v>119.8099975585938</v>
+      </c>
+      <c r="J510" t="n">
+        <v>113.7699966430664</v>
+      </c>
+      <c r="K510" t="n">
+        <v>2868923</v>
+      </c>
+      <c r="L510" t="n">
+        <v>-5.04</v>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>Why did FACT, RCF, NFL and other fertiliser stocks rally up to 14% today? Explained - Livemint</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>RCF Share Price | Rashtriya Chemicals &amp; Fertilizers Ltd. Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>Rashtriya Chemicals Share Price News and Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>FACT, Paradeep Phosphates, RCF, other fertiliser stocks rally up to 13%. Here's why - The Economic Times</t>
+        </is>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>RCF Share Price | Rashtriya Chemicals &amp; Fertilizers Ltd. Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>10</v>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>VAML.NS</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Vedanta Aluminium Metal Limited</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>451</v>
+      </c>
+      <c r="F511" t="n">
+        <v>452.3999938964844</v>
+      </c>
+      <c r="G511" t="n">
+        <v>432.1000061035156</v>
+      </c>
+      <c r="H511" t="n">
+        <v>433.25</v>
+      </c>
+      <c r="I511" t="n">
+        <v>456.1499938964844</v>
+      </c>
+      <c r="J511" t="n">
+        <v>433.25</v>
+      </c>
+      <c r="K511" t="n">
+        <v>9180950</v>
+      </c>
+      <c r="L511" t="n">
+        <v>-5.02</v>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>Vedanta Aluminium share price target: Buy VAML stock for 21% upside, says MOFSL - Business Today</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>Vedanta Aluminium Metal Ltd. Share Price Today - Vedanta Aluminium Metal Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>Vedanta Aluminium shares slip 2% in weak market; India Ratings upgrades NCDs to IND AA+ - Upstox</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>Vedanta Aluminium shares may remain in focus after latest clarification; key details here - Upstox</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>Vedanta Aluminium Metal Ltd. Share Price Today - Vedanta Aluminium Metal Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>11</v>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>AQYLON.NS</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Aqylon Nexus Limited</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>21.31999969482422</v>
+      </c>
+      <c r="F512" t="n">
+        <v>21.93000030517578</v>
+      </c>
+      <c r="G512" t="n">
+        <v>21.01000022888184</v>
+      </c>
+      <c r="H512" t="n">
+        <v>21.01000022888184</v>
+      </c>
+      <c r="I512" t="n">
+        <v>22.11000061035156</v>
+      </c>
+      <c r="J512" t="n">
+        <v>21.01000022888184</v>
+      </c>
+      <c r="K512" t="n">
+        <v>691059</v>
+      </c>
+      <c r="L512" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>Leading Leasing Finance Discloses Share Acquisition in Aqylon Nexus Under SEBI Regulation 29 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>Leading Leasing Finance Discloses Share Acquisition in Aqylon Nexus Under SEBI Regulation 29 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>InvestingPro Fair Value flagged Aqylon Nexus 54% decline in advance By Investing.com - Investing.com India</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>Aqylon Nexus Standalone June 2026 Net Sales at Rs 8.47 crore, up 24294.81% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>Leading Leasing sells 1.47 cr Aqylon Nexus shares - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>12</v>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>VCL.NS</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Vaxtex Cotfab Limited</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>1.919999957084656</v>
+      </c>
+      <c r="F513" t="n">
+        <v>1.919999957084656</v>
+      </c>
+      <c r="G513" t="n">
+        <v>1.919999957084656</v>
+      </c>
+      <c r="H513" t="n">
+        <v>1.919999957084656</v>
+      </c>
+      <c r="I513" t="n">
+        <v>2.019999980926514</v>
+      </c>
+      <c r="J513" t="n">
+        <v>1.919999957084656</v>
+      </c>
+      <c r="K513" t="n">
+        <v>96773</v>
+      </c>
+      <c r="L513" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>SEBI slaps ₹33 crore fine on Varanium Cloud, eight others for diversion of IPO proceeds - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>SEBI slaps ₹33 crore fine on Varanium Cloud, eight others for diversion of IPO proceeds - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>Sebi bars Varanium Cloud, promoter for 7 years, orders ₹128.8 crore disgorgement - Livemint</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>Sebi fines Varanium Cloud, promoter Sabale and 7 others Rs 33.08 crore over fund diversion - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>Sebi Fines Varanium Cloud ₹33.08 Crore, Bars Promoter Harshawardhan Sabale From Markets For 7 Years - Free Press Journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>13</v>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>WABAG.NS</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>VA Tech Wabag Limited</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>2085</v>
+      </c>
+      <c r="F514" t="n">
+        <v>2085</v>
+      </c>
+      <c r="G514" t="n">
+        <v>1975.599975585938</v>
+      </c>
+      <c r="H514" t="n">
+        <v>1984.300048828125</v>
+      </c>
+      <c r="I514" t="n">
+        <v>2086.10009765625</v>
+      </c>
+      <c r="J514" t="n">
+        <v>1984.300048828125</v>
+      </c>
+      <c r="K514" t="n">
+        <v>568512</v>
+      </c>
+      <c r="L514" t="n">
+        <v>-4.88</v>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>WABAG Secures Delhi Wastewater Treatment Plant Order - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>WABAG Secures Delhi Wastewater Treatment Plant Order - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>VA Tech Wabag Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>VA Tech Wabag (NSEI:WABAG) Stock Gets Fair Value Boost On Higher P E View - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>Rekha Jhunjhunwala portfolio stock VA Tech Wabag jumps 5%; Axis Securities raises target price after Q1 results - Livemint</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>14</v>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>ADANIENT.NS</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Adani Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>3165</v>
+      </c>
+      <c r="F515" t="n">
+        <v>3165</v>
+      </c>
+      <c r="G515" t="n">
+        <v>2960</v>
+      </c>
+      <c r="H515" t="n">
+        <v>3014.39990234375</v>
+      </c>
+      <c r="I515" t="n">
+        <v>3168.5</v>
+      </c>
+      <c r="J515" t="n">
+        <v>3014.39990234375</v>
+      </c>
+      <c r="K515" t="n">
+        <v>2599230</v>
+      </c>
+      <c r="L515" t="n">
+        <v>-4.86</v>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>Adani Enterprises Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>Adani Enterprises Opening Bell Updates: Geopolitical Jitters Dampen Early Trade - LatestLY</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>Should You Think About Buying Adani Enterprises Limited (NSE:ADANIENT) Now? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>Weekly Recap: Charges dismissed and Promoter buys via loan repayments - TradingView</t>
+        </is>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>Adani Enterprises Opening Bell Updates: Geopolitical Jitters Dampen Early Trade - LatestLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>15</v>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>RAYMONDREL.NS</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Raymond Realty Limited</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>556</v>
+      </c>
+      <c r="F516" t="n">
+        <v>559</v>
+      </c>
+      <c r="G516" t="n">
+        <v>528.0499877929688</v>
+      </c>
+      <c r="H516" t="n">
+        <v>531.7999877929688</v>
+      </c>
+      <c r="I516" t="n">
+        <v>557.0499877929688</v>
+      </c>
+      <c r="J516" t="n">
+        <v>531.7999877929688</v>
+      </c>
+      <c r="K516" t="n">
+        <v>334187</v>
+      </c>
+      <c r="L516" t="n">
+        <v>-4.53</v>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>Impressive Earnings May Not Tell The Whole Story For Raymond Realty (NSE:RAYMONDREL) - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>Raymond Realty Limited Faces Mild Correction: Support Levels in Focus - Long Term Entry Picks - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>RAYMONDREL Stock Price and Chart — NSE:RAYMONDREL - TradingView</t>
+        </is>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>How Did Raymond Realty Limited's (NSE:RAYMONDREL) 6.1% ROE Fare Against The Industry? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q516" t="inlineStr">
+        <is>
+          <t>Raymond Realty (RAYMONDREL.NS) Faces Resistance: Price Drops Over 2% Amid Sector Headwinds - TRIN Signal - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>16</v>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>ARIS.NS</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Arisinfra Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>152.4499969482422</v>
+      </c>
+      <c r="F517" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="G517" t="n">
+        <v>144.1000061035156</v>
+      </c>
+      <c r="H517" t="n">
+        <v>144.4900054931641</v>
+      </c>
+      <c r="I517" t="n">
+        <v>151.3099975585938</v>
+      </c>
+      <c r="J517" t="n">
+        <v>144.4900054931641</v>
+      </c>
+      <c r="K517" t="n">
+        <v>718274</v>
+      </c>
+      <c r="L517" t="n">
+        <v>-4.51</v>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>ARISINFRA SOLUTIONS LTD Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>Responsive Playbooks and the ARIS Inflection - Stock Traders Daily</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>Aris Water Solutions Inc (ARIS) Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>Aris Mining (TSX:ARIS) Stock Looks Fairly Valued After A Very Large Run - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="Q517" t="inlineStr">
+        <is>
+          <t>Aris stock trades higher in 2026 as mining earnings and water solutions remain in view - AD HOC NEWS</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>17</v>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>EIHOTEL.NS</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>EIH Limited</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>297.7999877929688</v>
+      </c>
+      <c r="F518" t="n">
+        <v>297.7999877929688</v>
+      </c>
+      <c r="G518" t="n">
+        <v>284.1000061035156</v>
+      </c>
+      <c r="H518" t="n">
+        <v>284.7999877929688</v>
+      </c>
+      <c r="I518" t="n">
+        <v>297.7999877929688</v>
+      </c>
+      <c r="J518" t="n">
+        <v>284.7999877929688</v>
+      </c>
+      <c r="K518" t="n">
+        <v>335855</v>
+      </c>
+      <c r="L518" t="n">
+        <v>-4.37</v>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: EIH Limited Q1 2027 revenue rises, stock falls - Investing.com</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>EIH Hotels schedules institutional meet with Ashika Equities on Sep 1 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>EIH Limited Q1FY27 profit surges 248%, RevPAR leads industry - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>EIH Limited schedules 76th AGM on August 7, 2026 via VC - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q518" t="inlineStr">
+        <is>
+          <t>EIH Hotels schedules institutional meet with Ashika Equities on Sep 1 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>18</v>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>FINKURVE.NS</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Finkurve Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>75.94999694824219</v>
+      </c>
+      <c r="F519" t="n">
+        <v>76.08000183105469</v>
+      </c>
+      <c r="G519" t="n">
+        <v>69.26999664306641</v>
+      </c>
+      <c r="H519" t="n">
+        <v>72.27999877929688</v>
+      </c>
+      <c r="I519" t="n">
+        <v>75.55999755859375</v>
+      </c>
+      <c r="J519" t="n">
+        <v>72.27999877929688</v>
+      </c>
+      <c r="K519" t="n">
+        <v>173682</v>
+      </c>
+      <c r="L519" t="n">
+        <v>-4.34</v>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>Finkurve Financial Services Ltd. Share Price Rises 8.83% - Univest</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>Finkurve Financial Services Ltd. Peer Comparison – Compare with Others - Value Research</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>Finkurve Financial Services Share: Small NBFC Worth Buying? - Univest</t>
+        </is>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>Finkurve Financial Services Ltd. Share Price Falls 8.81% - Univest</t>
+        </is>
+      </c>
+      <c r="Q519" t="inlineStr">
+        <is>
+          <t>Finkurve Financial Services Share Price Today Gains 8.27% - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>19</v>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>WOCKPHARMA.NS</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Wockhardt Limited</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>1974.900024414062</v>
+      </c>
+      <c r="F520" t="n">
+        <v>1977.099975585938</v>
+      </c>
+      <c r="G520" t="n">
+        <v>1887.699951171875</v>
+      </c>
+      <c r="H520" t="n">
+        <v>1891.300048828125</v>
+      </c>
+      <c r="I520" t="n">
+        <v>1977.099975585938</v>
+      </c>
+      <c r="J520" t="n">
+        <v>1891.300048828125</v>
+      </c>
+      <c r="K520" t="n">
+        <v>621224</v>
+      </c>
+      <c r="L520" t="n">
+        <v>-4.34</v>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>Wockhardt Share Price - Live NSE: WOCKPHARMA Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>Wockhardt Share Price - Live NSE: WOCKPHARMA Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>Wockhardt Share Price Today: 3.57% Rise, Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>Wockhardt Ltd. Share Price Today: Volume and Price Move - Univest</t>
+        </is>
+      </c>
+      <c r="Q520" t="inlineStr">
+        <is>
+          <t>Wockhardt Share Price Falls 4.84%: Price Action Analysis - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:19:51 IST</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>20</v>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>GENUSPOWER.NS</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Genus Power Infrastructures Limited</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>352.0499877929688</v>
+      </c>
+      <c r="F521" t="n">
+        <v>352.1000061035156</v>
+      </c>
+      <c r="G521" t="n">
+        <v>332.0499877929688</v>
+      </c>
+      <c r="H521" t="n">
+        <v>334.7999877929688</v>
+      </c>
+      <c r="I521" t="n">
+        <v>349.7000122070312</v>
+      </c>
+      <c r="J521" t="n">
+        <v>334.7999877929688</v>
+      </c>
+      <c r="K521" t="n">
+        <v>3344585</v>
+      </c>
+      <c r="L521" t="n">
+        <v>-4.26</v>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>Chiswick Investment cuts stake in Genus Power Infrastructures to 4.08% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>Chiswick Investment cuts stake in Genus Power Infrastructures to 4.08% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>Smart Meter Stock to Buy Now for an Upside of 32%; Do You Own It? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="P521" t="inlineStr"/>
+      <c r="Q521" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q521"/>
+  <dimension ref="A1:Q541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31555,9 +31555,6 @@
           <t>Manali Petrochemicals Share Price - Live NSE: MANALIPETC Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
-      <c r="O502" t="inlineStr"/>
-      <c r="P502" t="inlineStr"/>
-      <c r="Q502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -31888,9 +31885,6 @@
           <t>Aptargroup segment pres., CEO designate Gael Touya sells $500k in shares - Investing.com</t>
         </is>
       </c>
-      <c r="O507" t="inlineStr"/>
-      <c r="P507" t="inlineStr"/>
-      <c r="Q507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -32024,7 +32018,6 @@
           <t>Paramount Communications Publishes Q1 FY27 Investor Call Recording - TipRanks</t>
         </is>
       </c>
-      <c r="Q509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -32562,9 +32555,6 @@
           <t>ATLANTA ELECTRICALS LTD Share Price - Live NSE: ATLANTAELE Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
-      <c r="O517" t="inlineStr"/>
-      <c r="P517" t="inlineStr"/>
-      <c r="Q517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -32839,6 +32829,1358 @@
       <c r="Q521" t="inlineStr">
         <is>
           <t>Cyient Stock: JPMorgan Sees Transformation, Morgan Stanley Waits for Execution - NDTV Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>1</v>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>MANALIPETC.NS</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Manali Petrochemicals Limited</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>75</v>
+      </c>
+      <c r="F522" t="n">
+        <v>84.80000305175781</v>
+      </c>
+      <c r="G522" t="n">
+        <v>73.62000274658203</v>
+      </c>
+      <c r="H522" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="I522" t="n">
+        <v>73.36000061035156</v>
+      </c>
+      <c r="J522" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="K522" t="n">
+        <v>73396983</v>
+      </c>
+      <c r="L522" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>Manali Petrochemicals Share Price - Live NSE: MANALIPETC Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>Manali Petrochemicals Share Price - Live NSE: MANALIPETC Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr"/>
+      <c r="P522" t="inlineStr"/>
+      <c r="Q522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>2</v>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>INNOVISION.NS</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Innovision Limited</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>296.7000122070312</v>
+      </c>
+      <c r="F523" t="n">
+        <v>296.7000122070312</v>
+      </c>
+      <c r="G523" t="n">
+        <v>257</v>
+      </c>
+      <c r="H523" t="n">
+        <v>274.25</v>
+      </c>
+      <c r="I523" t="n">
+        <v>247.25</v>
+      </c>
+      <c r="J523" t="n">
+        <v>274.25</v>
+      </c>
+      <c r="K523" t="n">
+        <v>344082</v>
+      </c>
+      <c r="L523" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>Innovision Ltd wins ₹205.20 Cr NHAI order for Kishangarh plaza - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>Innovision Ltd wins ₹205.20 Cr NHAI order for Kishangarh plaza - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>Innovision Ltd Falls to 52-Week Low of Rs 265.2 as Sell-Off Deepens - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>Innovision Q1 Results FY27: Revenue Rs 263 crore, Net Loss Rs 7 Crore on Consolidated Basis - Univest</t>
+        </is>
+      </c>
+      <c r="Q523" t="inlineStr">
+        <is>
+          <t>Innovision wins order worth ₹9.23 Cr from NHAI for toll collection - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>3</v>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>MOHITE.NS</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Mohite Industries Limited</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>3.009999990463257</v>
+      </c>
+      <c r="F524" t="n">
+        <v>3.299999952316284</v>
+      </c>
+      <c r="G524" t="n">
+        <v>2.950000047683716</v>
+      </c>
+      <c r="H524" t="n">
+        <v>3.240000009536743</v>
+      </c>
+      <c r="I524" t="n">
+        <v>2.950000047683716</v>
+      </c>
+      <c r="J524" t="n">
+        <v>3.240000009536743</v>
+      </c>
+      <c r="K524" t="n">
+        <v>202176</v>
+      </c>
+      <c r="L524" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>Mohite Industries Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>Abhishek Corporation Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>Mohite Industries Ltd. Financials – Balance Sheet, Profit &amp; Loss, Cash Flow - Value Research</t>
+        </is>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>Mohite Industries Ltd Upgraded to Sell on Technical Improvements Despite Weak Fundamentals - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q524" t="inlineStr">
+        <is>
+          <t>Mohite Industries Q1 Results: Net loss widens 142% YoY to ₹245.62 lakh - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>4</v>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>GEEKAYWIRE.NS</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Geekay Wires Limited</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>24.69000053405762</v>
+      </c>
+      <c r="F525" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="G525" t="n">
+        <v>24.20999908447266</v>
+      </c>
+      <c r="H525" t="n">
+        <v>26.70000076293945</v>
+      </c>
+      <c r="I525" t="n">
+        <v>24.69000053405762</v>
+      </c>
+      <c r="J525" t="n">
+        <v>26.70000076293945</v>
+      </c>
+      <c r="K525" t="n">
+        <v>1392182</v>
+      </c>
+      <c r="L525" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>Geekay Wires sets e-voting dates for auditor appointment - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>Geekay Wires Discloses Promoter Group Share Acquisition - TipRanks</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>Geekay Wires Q1 Results: Net profit falls 20% YoY to ₹5.77 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>Weis (WMK) Chart: Stays Close to Unchanged at $70.29 in the Current Update - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q525" t="inlineStr">
+        <is>
+          <t>Geekay Wires Discloses Promoter Group Share Acquisition - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>5</v>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>ULTRAMAR.NS</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Ultramarine &amp; Pigments Limited</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>416.2000122070312</v>
+      </c>
+      <c r="F526" t="n">
+        <v>448.6499938964844</v>
+      </c>
+      <c r="G526" t="n">
+        <v>416.2000122070312</v>
+      </c>
+      <c r="H526" t="n">
+        <v>442.8500061035156</v>
+      </c>
+      <c r="I526" t="n">
+        <v>411.2999877929688</v>
+      </c>
+      <c r="J526" t="n">
+        <v>442.8500061035156</v>
+      </c>
+      <c r="K526" t="n">
+        <v>464925</v>
+      </c>
+      <c r="L526" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>Thirumalai Chemicals approves sale of 5% stake in Ultramarine - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>Ultramarine &amp; Pigments block deal today: 14.60 lakh shares trade after Thirumalai Chemicals proposed 5% stake sale - Business Upturn</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>Thirumalai Chemicals to Divest 5% Stake in Ultramarine &amp; Pigments Limited - Whalesbook</t>
+        </is>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>Ultramarine &amp; Pigments block deal today: 14.60 lakh shares trade after Thirumalai Chemicals proposed 5% stake sale - Business Upturn</t>
+        </is>
+      </c>
+      <c r="Q526" t="inlineStr">
+        <is>
+          <t>Thirumalai Chemicals to Sell Part of Promoter Stake in Ultramarine &amp; Pigments - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>6</v>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>AVALON.NS</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Avalon Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>2244</v>
+      </c>
+      <c r="F527" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G527" t="n">
+        <v>2193</v>
+      </c>
+      <c r="H527" t="n">
+        <v>2373.300048828125</v>
+      </c>
+      <c r="I527" t="n">
+        <v>2231.699951171875</v>
+      </c>
+      <c r="J527" t="n">
+        <v>2373.300048828125</v>
+      </c>
+      <c r="K527" t="n">
+        <v>519151</v>
+      </c>
+      <c r="L527" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>Avalon Technologies Share Price today: valuation and peers - Univest</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>Avalon Technologies Share Price today: valuation and peers - Univest</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>Avalon Technologies Has Returned 158% in One Year. The Business Behind That Move Is More Interesting Than the Stock Price - Dalal Street Investment Journal</t>
+        </is>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>Why is Avalon Advanced Materials stock surging today? - Investing.com</t>
+        </is>
+      </c>
+      <c r="Q527" t="inlineStr">
+        <is>
+          <t>Tech view: Avalon Technologies, Healthcare Global on analyst radar - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>7</v>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN.NS</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Limited</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>650.2000122070312</v>
+      </c>
+      <c r="F528" t="n">
+        <v>738.9500122070312</v>
+      </c>
+      <c r="G528" t="n">
+        <v>647.5499877929688</v>
+      </c>
+      <c r="H528" t="n">
+        <v>693.5</v>
+      </c>
+      <c r="I528" t="n">
+        <v>654.8499755859375</v>
+      </c>
+      <c r="J528" t="n">
+        <v>693.5</v>
+      </c>
+      <c r="K528" t="n">
+        <v>39555091</v>
+      </c>
+      <c r="L528" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN Share Price today: financial context and news - Univest</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN Share Price today: financial context and news - Univest</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Drops 4.6% From Session High as India’s Sugar Trade Divides Markets - TechStock²</t>
+        </is>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd Share Price Target, Forecast for Long Term Equity. - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="Q528" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Clears Q1 FY27 Results and Appoints New Independent Director - The Globe and Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>8</v>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>OLAELEC.NS</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Ola Electric Mobility Limited</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>39</v>
+      </c>
+      <c r="F529" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="G529" t="n">
+        <v>38.31000137329102</v>
+      </c>
+      <c r="H529" t="n">
+        <v>41.11999893188477</v>
+      </c>
+      <c r="I529" t="n">
+        <v>38.97999954223633</v>
+      </c>
+      <c r="J529" t="n">
+        <v>41.11999893188477</v>
+      </c>
+      <c r="K529" t="n">
+        <v>178343484</v>
+      </c>
+      <c r="L529" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>Ola Electric Share Price - Live NSE: OLAELEC Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>Stocks To Buy or Sell Today, August 31, 2026: Ola Electric and HDFC Bank Among Shares That May Remain in - LatestLY</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>OLA Electric Mobility Share Price rises 5.82%: analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>Ola Electric Heralds New ‘LFP Era’ as Gigafactory Ramp-Up Powers Thousands of EVs - The Globe and Mail</t>
+        </is>
+      </c>
+      <c r="Q529" t="inlineStr">
+        <is>
+          <t>Ola Electric Launches New Battery Energy Storage Portfolio in India - The Globe and Mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>9</v>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>SHADOWFAX.NS</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Shadowfax Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>246.6999969482422</v>
+      </c>
+      <c r="F530" t="n">
+        <v>260</v>
+      </c>
+      <c r="G530" t="n">
+        <v>244.6600036621094</v>
+      </c>
+      <c r="H530" t="n">
+        <v>258.4800109863281</v>
+      </c>
+      <c r="I530" t="n">
+        <v>245.3600006103516</v>
+      </c>
+      <c r="J530" t="n">
+        <v>258.4800109863281</v>
+      </c>
+      <c r="K530" t="n">
+        <v>4362971</v>
+      </c>
+      <c r="L530" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>Shadowfax Technologies Share Price rise and valuation view - Univest</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>Shadowfax publishes 11th AGM notice in Financial Express, Hosadigantha - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>Shadowfax publishes 11th AGM notice in Financial Express, Hosadigantha - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>Qualcomm Ventures affiliate sells 75 lakh Shadowfax shares for Rs 184 crore - Indian Startup News</t>
+        </is>
+      </c>
+      <c r="Q530" t="inlineStr">
+        <is>
+          <t>Qualcomm Offloads Shadowfax Shares Worth ₹184 Cr In Bulk Deal - Inc42</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>10</v>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM.NS</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Sudeep Pharma Limited</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>1179</v>
+      </c>
+      <c r="F531" t="n">
+        <v>1209.699951171875</v>
+      </c>
+      <c r="G531" t="n">
+        <v>1143.650024414062</v>
+      </c>
+      <c r="H531" t="n">
+        <v>1209.699951171875</v>
+      </c>
+      <c r="I531" t="n">
+        <v>1152.099975585938</v>
+      </c>
+      <c r="J531" t="n">
+        <v>1209.699951171875</v>
+      </c>
+      <c r="K531" t="n">
+        <v>329218</v>
+      </c>
+      <c r="L531" t="n">
+        <v>5</v>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM Stock Price and Chart — NSE:SUDEEPPHRM - TradingView</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM Stock Price and Chart — NSE:SUDEEPPHRM - TradingView</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>SUDEEP PHARMA LIMITED Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM Forecast — Price Target — Prediction for 2027 - TradingView</t>
+        </is>
+      </c>
+      <c r="Q531" t="inlineStr">
+        <is>
+          <t>Sudeep Pharma (SUDEEPPHRM) Edges Higher: Stock Holds Above Key Support Zone - Covered Call Trade - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>11</v>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>TGBHOTELS.NS</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>TGB Banquets And Hotels Limited</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>9.689999580383301</v>
+      </c>
+      <c r="F532" t="n">
+        <v>10.23999977111816</v>
+      </c>
+      <c r="G532" t="n">
+        <v>9.449999809265137</v>
+      </c>
+      <c r="H532" t="n">
+        <v>9.840000152587891</v>
+      </c>
+      <c r="I532" t="n">
+        <v>9.399999618530273</v>
+      </c>
+      <c r="J532" t="n">
+        <v>9.840000152587891</v>
+      </c>
+      <c r="K532" t="n">
+        <v>54811</v>
+      </c>
+      <c r="L532" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>Brandywine (BDN) Chart: Closes 0.33% Lower at $3.02 for the Current Session; Price Setup - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>Brandywine (BDN) Chart: Closes 0.33% Lower at $3.02 for the Current Session; Price Setup - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>TGB Banquets &amp; Hotels Sets AGM, Moves to Fully Digital Shareholder Communication - TipRanks</t>
+        </is>
+      </c>
+      <c r="P532" t="inlineStr"/>
+      <c r="Q532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>12</v>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>INDHOTEL.NS</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>The Indian Hotels Company Limited</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>702</v>
+      </c>
+      <c r="F533" t="n">
+        <v>737.9000244140625</v>
+      </c>
+      <c r="G533" t="n">
+        <v>701.5499877929688</v>
+      </c>
+      <c r="H533" t="n">
+        <v>737.9000244140625</v>
+      </c>
+      <c r="I533" t="n">
+        <v>706.4000244140625</v>
+      </c>
+      <c r="J533" t="n">
+        <v>737.9000244140625</v>
+      </c>
+      <c r="K533" t="n">
+        <v>5170401</v>
+      </c>
+      <c r="L533" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>Indian Hotels Co Ltd (INDHOTEL) Share Price - Business Today</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>The Indian Hotels Company Ltd. Share Price Update Today - Univest</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>INDHOTEL Share Price Today - The Indian Hotels Company Ltd. Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>IHCL AND ORIENTAL HOTELS LIMITED ANNOUNCE MERGER - The Indian Hotels Company Limited (IHCL)</t>
+        </is>
+      </c>
+      <c r="Q533" t="inlineStr">
+        <is>
+          <t>INDHOTEL Outlook for the Week (August 31, 2026 – September 04, 2026) - equitypandit.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>13</v>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>TRIVENI.NS</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Triveni Engineering &amp; Industries Limited</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>282.4500122070312</v>
+      </c>
+      <c r="F534" t="n">
+        <v>297.989990234375</v>
+      </c>
+      <c r="G534" t="n">
+        <v>282</v>
+      </c>
+      <c r="H534" t="n">
+        <v>295.6400146484375</v>
+      </c>
+      <c r="I534" t="n">
+        <v>283.8200073242188</v>
+      </c>
+      <c r="J534" t="n">
+        <v>295.6400146484375</v>
+      </c>
+      <c r="K534" t="n">
+        <v>1894993</v>
+      </c>
+      <c r="L534" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>Sugar stocks rebound; Balrampur, Shree Renuka, Triveni rally up to 13% - Business Standard</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>Sugar stocks rebound; Balrampur, Shree Renuka, Triveni rally up to 13% - Business Standard</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>Triveni Turbine Limited (NSE:TRITURBINE) Stock Goes Ex-Dividend In Just Three Days - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>Triveni Engineering &amp; Industries Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="Q534" t="inlineStr">
+        <is>
+          <t>Triveni Engineering &amp; Industries Ltd. Stock News - Value Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>14</v>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>SANSERA.NS</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Sansera Engineering Limited</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>3858.89990234375</v>
+      </c>
+      <c r="F535" t="n">
+        <v>4051</v>
+      </c>
+      <c r="G535" t="n">
+        <v>3820.60009765625</v>
+      </c>
+      <c r="H535" t="n">
+        <v>4018</v>
+      </c>
+      <c r="I535" t="n">
+        <v>3859</v>
+      </c>
+      <c r="J535" t="n">
+        <v>4018</v>
+      </c>
+      <c r="K535" t="n">
+        <v>292150</v>
+      </c>
+      <c r="L535" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>Sansera Engineering Share Price Rises 2.51%; Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>Sansera Engineering schedules 44th AGM for September 24, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>Sansera Engineering schedules 44th AGM for September 24, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>Auto ancillary stocks in focus: Gabriel, Sansera, Uniparts hit record highs - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q535" t="inlineStr">
+        <is>
+          <t>Sansera Engineering Delivers Record Q3FY26 Results with Revenue of ₹9,077 Million - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>15</v>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>EPL.NS</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>EPL Limited</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>253.7200012207031</v>
+      </c>
+      <c r="F536" t="n">
+        <v>265.7000122070312</v>
+      </c>
+      <c r="G536" t="n">
+        <v>248.3800048828125</v>
+      </c>
+      <c r="H536" t="n">
+        <v>262.0599975585938</v>
+      </c>
+      <c r="I536" t="n">
+        <v>251.9400024414062</v>
+      </c>
+      <c r="J536" t="n">
+        <v>262.0599975585938</v>
+      </c>
+      <c r="K536" t="n">
+        <v>6317710</v>
+      </c>
+      <c r="L536" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>EPL Block Deal: Blackstone-owned Epsilon Bidco likely to sell 26% stake for ₹235/share - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>EPL Block Deal: Blackstone-owned Epsilon Bidco likely to sell 26% stake for ₹235/share - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>Blackstone-backed Epsilon Bidco may sell 26% stake in EPL in Rs 1,985-crore block deal - The Economic Times</t>
+        </is>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>Epsilon Bidco confirms no additional encumbrance on EPL shares in FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q536" t="inlineStr">
+        <is>
+          <t>EPL Standalone June 2026 Net Sales at Rs 400.30 crore, up 19.85% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>16</v>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>SKMEGGPROD.NS</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>SKM Egg Products Export (India) Limited</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>257.1000061035156</v>
+      </c>
+      <c r="F537" t="n">
+        <v>274.2999877929688</v>
+      </c>
+      <c r="G537" t="n">
+        <v>255.1000061035156</v>
+      </c>
+      <c r="H537" t="n">
+        <v>267.8999938964844</v>
+      </c>
+      <c r="I537" t="n">
+        <v>257.5499877929688</v>
+      </c>
+      <c r="J537" t="n">
+        <v>267.8999938964844</v>
+      </c>
+      <c r="K537" t="n">
+        <v>761571</v>
+      </c>
+      <c r="L537" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>Impressive Earnings May Not Tell The Whole Story For SKM Egg Products Export (India) (NSE:SKMEGGPROD) - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>SKM Egg Products Export (SKMEGGPROD.NS) Rises 1.53%; Support and Resistance Levels in Focus - Trend Reversal Picks - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>SKM Egg Products Export (India) Limited Schedules Board Meeting on 22 May 2026 to Approve Audited Financial Results - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>SKM Egg Products Export (India) Limited (NSE:SKMEGGPROD) Stock's 27% Dive Might Signal An Opportunity But It Requires Some Scrutiny - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q537" t="inlineStr">
+        <is>
+          <t>SKMEGGPROD Q2 2026 Earnings: Revenue Surges 54% YoY to ₹768 Crore, EPS at ₹19.7 Amid Stock Decline - Analyst Coverage Count - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>17</v>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>PAYTM.NS</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>One 97 Communications Limited</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>1622.5</v>
+      </c>
+      <c r="F538" t="n">
+        <v>1717.099975585938</v>
+      </c>
+      <c r="G538" t="n">
+        <v>1622.5</v>
+      </c>
+      <c r="H538" t="n">
+        <v>1717.099975585938</v>
+      </c>
+      <c r="I538" t="n">
+        <v>1650.900024414062</v>
+      </c>
+      <c r="J538" t="n">
+        <v>1717.099975585938</v>
+      </c>
+      <c r="K538" t="n">
+        <v>2673159</v>
+      </c>
+      <c r="L538" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>Paytm Stock Leads 3 Founder Led Indian Companies Investors May Want To Watch - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>Bernstein reshuffles India model portfolio: Adani Ports, Eternal, Paytm in, DMart out; sets Nifty 50 target at 26,000 - Livemint</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>Bernstein reshuffles India model portfolio: Adani Ports, Eternal, Paytm in, DMart out; sets Nifty 50 target at 26,000 - Livemint</t>
+        </is>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>Paytm shares jump 5.6%, hit 52-week high; check what the firm said on Vijay Shekhar Sharma's pay - Upstox</t>
+        </is>
+      </c>
+      <c r="Q538" t="inlineStr">
+        <is>
+          <t>Trilegal Advises Goldman Sachs On USD 309 Million Block Sale Of Paytm Shares - LawBeat</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>18</v>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>FOODSIN.NS</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Foods &amp; Inns Limited</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>53</v>
+      </c>
+      <c r="F539" t="n">
+        <v>55.2400016784668</v>
+      </c>
+      <c r="G539" t="n">
+        <v>52.72000122070312</v>
+      </c>
+      <c r="H539" t="n">
+        <v>54.97000122070312</v>
+      </c>
+      <c r="I539" t="n">
+        <v>52.86999893188477</v>
+      </c>
+      <c r="J539" t="n">
+        <v>54.97000122070312</v>
+      </c>
+      <c r="K539" t="n">
+        <v>154105</v>
+      </c>
+      <c r="L539" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>MPIL Corporation Limited Increases Shareholding in Foods &amp; Inns Limited to 4.08% Through Strategic Acquisitions - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>Foods &amp; Inns (FOODSIN.NS) Surges Over 6.7% – Breaking Above Key Support Zone - Liquidity Order Flow - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>Foods &amp; Inns Limited (FOODSIN.NS) Gains 1.97%: Price Action and Key Levels - McClellan Summation - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>Is Foods and Inns (NSE:FOODSIN) A Risky Investment? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q539" t="inlineStr">
+        <is>
+          <t>Foods &amp; Inns Limited (FOODSIN.NS) Inching Higher: Test of Resistance at ₹59.1 - Hull Moving Average - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>19</v>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>JSWHL.NS</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>JSW Holdings Limited</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>11601</v>
+      </c>
+      <c r="F540" t="n">
+        <v>12210</v>
+      </c>
+      <c r="G540" t="n">
+        <v>11253</v>
+      </c>
+      <c r="H540" t="n">
+        <v>12027</v>
+      </c>
+      <c r="I540" t="n">
+        <v>11578</v>
+      </c>
+      <c r="J540" t="n">
+        <v>12027</v>
+      </c>
+      <c r="K540" t="n">
+        <v>10502</v>
+      </c>
+      <c r="L540" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>JSW Holdings schedules 25th AGM for August 6 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>JSW Holdings schedules 25th AGM for August 6 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>JSW Holdings Ltd. (JSWHL) Share Price Rises 5.14% Amid Mid Cap Rally - Univest</t>
+        </is>
+      </c>
+      <c r="P540" t="inlineStr"/>
+      <c r="Q540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>20</v>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>FMGOETZE.NS</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Federal-Mogul Goetze (India) Limited.</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>616</v>
+      </c>
+      <c r="F541" t="n">
+        <v>641.0999755859375</v>
+      </c>
+      <c r="G541" t="n">
+        <v>608.0499877929688</v>
+      </c>
+      <c r="H541" t="n">
+        <v>624.8499755859375</v>
+      </c>
+      <c r="I541" t="n">
+        <v>602.0499877929688</v>
+      </c>
+      <c r="J541" t="n">
+        <v>624.8499755859375</v>
+      </c>
+      <c r="K541" t="n">
+        <v>8524758</v>
+      </c>
+      <c r="L541" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>FMGOETZE Share Price Today: Stock News and Peer Context - Univest</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>Rs.94 dividend declared after 25 years; share price jumps nearly 10% - Record date fixed | Do you own? - TradingView</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-28 — cnbctv:a82234c70094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>Federal-Mogul Goetze (India) Share Price at 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q541" t="inlineStr">
+        <is>
+          <t>Rs.94 dividend declared after 25 years; share price jumps nearly 10% - Record date fixed | Do you own? - TradingView</t>
         </is>
       </c>
     </row>
@@ -32853,7 +34195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q521"/>
+  <dimension ref="A1:Q541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63947,8 +65289,6 @@
           <t>Kellton Tech Solutions Share Price: price rise and valuation - Univest</t>
         </is>
       </c>
-      <c r="P506" t="inlineStr"/>
-      <c r="Q506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -64974,8 +66314,1346 @@
           <t>Smart Meter Stock to Buy Now for an Upside of 32%; Do You Own It? - Trade Brains</t>
         </is>
       </c>
-      <c r="P521" t="inlineStr"/>
-      <c r="Q521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>1</v>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>WEL.NS</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Wonder Electricals Limited</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>89.81999969482422</v>
+      </c>
+      <c r="F522" t="n">
+        <v>89.81999969482422</v>
+      </c>
+      <c r="G522" t="n">
+        <v>89.81999969482422</v>
+      </c>
+      <c r="H522" t="n">
+        <v>89.81999969482422</v>
+      </c>
+      <c r="I522" t="n">
+        <v>99.80000305175781</v>
+      </c>
+      <c r="J522" t="n">
+        <v>89.81999969482422</v>
+      </c>
+      <c r="K522" t="n">
+        <v>519670</v>
+      </c>
+      <c r="L522" t="n">
+        <v>-10</v>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>Wonder Electricals Share Price - Live NSE: WEL Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>Integrated Wellness Acquisition Corp (WEL-UN) Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>Integrated Wellness Acquisition Corp (WEL-UN) Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>Wonder Electricals Share Price Today After Sharp Fall - Univest</t>
+        </is>
+      </c>
+      <c r="Q522" t="inlineStr">
+        <is>
+          <t>Integrated Wellness Acquisition Corp (WEL-UN) Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>2</v>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>ADANIENT.NS</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Adani Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>3165</v>
+      </c>
+      <c r="F523" t="n">
+        <v>3165</v>
+      </c>
+      <c r="G523" t="n">
+        <v>2859.10009765625</v>
+      </c>
+      <c r="H523" t="n">
+        <v>2859.10009765625</v>
+      </c>
+      <c r="I523" t="n">
+        <v>3168.5</v>
+      </c>
+      <c r="J523" t="n">
+        <v>2859.10009765625</v>
+      </c>
+      <c r="K523" t="n">
+        <v>12690120</v>
+      </c>
+      <c r="L523" t="n">
+        <v>-9.76</v>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>Adani Enterprises Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>Adani Enterprises Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>Should You Think About Buying Adani Enterprises Limited (NSE:ADANIENT) Now? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>Weekly Recap: Charges dismissed and Promoter buys via loan repayments - TradingView</t>
+        </is>
+      </c>
+      <c r="Q523" t="inlineStr">
+        <is>
+          <t>Adani Enterprises Opening Bell Updates: Geopolitical Jitters Dampen Early Trade - LatestLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>3</v>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>DCI.NS</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Dc Infotech And Communication Limited</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>416</v>
+      </c>
+      <c r="F524" t="n">
+        <v>424.3999938964844</v>
+      </c>
+      <c r="G524" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="H524" t="n">
+        <v>372.6000061035156</v>
+      </c>
+      <c r="I524" t="n">
+        <v>410.0499877929688</v>
+      </c>
+      <c r="J524" t="n">
+        <v>372.6000061035156</v>
+      </c>
+      <c r="K524" t="n">
+        <v>1111548</v>
+      </c>
+      <c r="L524" t="n">
+        <v>-9.130000000000001</v>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>DCI Share Price Rise: Fundamentals, Peers and Market Cap - Univest</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>80,002 Shares in Donaldson Company, Inc. $DCI Bought by The Manufacturers Life Insurance Company - MarketBeat</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>Donaldson (DCI) Stock Slips After Record Margins Set A Higher Bar - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>Donaldson (DCI) Stock Looks Reasonable On Earnings But Rich On Cash Flow - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="Q524" t="inlineStr">
+        <is>
+          <t>Donaldson (DCI) Stock Slips After Record Margins Set A Higher Bar - Sahm</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>4</v>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>ADANIPOWER.NS</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Adani Power Limited</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>212.3699951171875</v>
+      </c>
+      <c r="F525" t="n">
+        <v>213.1300048828125</v>
+      </c>
+      <c r="G525" t="n">
+        <v>198</v>
+      </c>
+      <c r="H525" t="n">
+        <v>198</v>
+      </c>
+      <c r="I525" t="n">
+        <v>212.6300048828125</v>
+      </c>
+      <c r="J525" t="n">
+        <v>198</v>
+      </c>
+      <c r="K525" t="n">
+        <v>53722599</v>
+      </c>
+      <c r="L525" t="n">
+        <v>-6.88</v>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>Adani Power Share Price Falls 2.07% Today: Key Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>Adani Power Share Price Falls 2.07% Today: Key Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>Adani Power Opening Bell Updates: Stock Slips 1.43% Amid Mixed Cues - LatestLY</t>
+        </is>
+      </c>
+      <c r="P525" t="inlineStr"/>
+      <c r="Q525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>5</v>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>ADANIPORTS.NS</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Adani Ports and Special Economic Zone Limited</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>1710</v>
+      </c>
+      <c r="F526" t="n">
+        <v>1711.400024414062</v>
+      </c>
+      <c r="G526" t="n">
+        <v>1593.099975585938</v>
+      </c>
+      <c r="H526" t="n">
+        <v>1593.099975585938</v>
+      </c>
+      <c r="I526" t="n">
+        <v>1707.5</v>
+      </c>
+      <c r="J526" t="n">
+        <v>1593.099975585938</v>
+      </c>
+      <c r="K526" t="n">
+        <v>9166870</v>
+      </c>
+      <c r="L526" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>Adani Ports Share Price Today: Market Cap and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>Adani Ports Share Price Today: Market Cap and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>Adani Ports Reports 46.3 MMT Cargo Volume in July'26, Up 15% Year-on-Year - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P526" t="inlineStr"/>
+      <c r="Q526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>6</v>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>KAYNES.NS</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Kaynes Technology India Limited</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>3943</v>
+      </c>
+      <c r="F527" t="n">
+        <v>3943</v>
+      </c>
+      <c r="G527" t="n">
+        <v>3645</v>
+      </c>
+      <c r="H527" t="n">
+        <v>3685</v>
+      </c>
+      <c r="I527" t="n">
+        <v>3943.10009765625</v>
+      </c>
+      <c r="J527" t="n">
+        <v>3685</v>
+      </c>
+      <c r="K527" t="n">
+        <v>2143332</v>
+      </c>
+      <c r="L527" t="n">
+        <v>-6.55</v>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>Explained - Here's why Kaynes Technology shares are down 5% on Monday - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>Explained: Why Jefferies prefers Kaynes Tech shares over Dixon Tech; urges caution on Syrma SGS - The Economic Times</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>Kaynes Tech shares fall up to 5% as Investec raises balance sheet concerns - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>Kaynes Tech, Wockhardt, Persistent Systems shares fall up to 5% as broader markets tumble. What lies ahead? - economictimes.indiatimes.com</t>
+        </is>
+      </c>
+      <c r="Q527" t="inlineStr">
+        <is>
+          <t>Prime Minister Modi Inaugurates Kaynes Semicon Manufacturing Plant in Ahmedabad - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>7</v>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>LODHA.NS</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Lodha Developers Limited</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F528" t="n">
+        <v>1260</v>
+      </c>
+      <c r="G528" t="n">
+        <v>1198.599975585938</v>
+      </c>
+      <c r="H528" t="n">
+        <v>1198.599975585938</v>
+      </c>
+      <c r="I528" t="n">
+        <v>1274</v>
+      </c>
+      <c r="J528" t="n">
+        <v>1198.599975585938</v>
+      </c>
+      <c r="K528" t="n">
+        <v>2178510</v>
+      </c>
+      <c r="L528" t="n">
+        <v>-5.92</v>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>Lodha Developers FY26 Results: ₹34,307 Cr Profit, ₹4.25 Dividend - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>Lodha Developers FY26 Results: ₹34,307 Cr Profit, ₹4.25 Dividend - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>Lodha Developers shares decline 2.05% in early trade - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>Lodha Developers Limited (NSE:LODHA) Passed Our Checks, And It's About To Pay A ₹4.25 Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q528" t="inlineStr">
+        <is>
+          <t>Lodha Developers shares gain 2.20% - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>8</v>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>NSLNISP.NS</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>NMDC Steel Limited</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>48.34999847412109</v>
+      </c>
+      <c r="F529" t="n">
+        <v>48.47999954223633</v>
+      </c>
+      <c r="G529" t="n">
+        <v>45.79999923706055</v>
+      </c>
+      <c r="H529" t="n">
+        <v>46.18999862670898</v>
+      </c>
+      <c r="I529" t="n">
+        <v>49.02000045776367</v>
+      </c>
+      <c r="J529" t="n">
+        <v>46.18999862670898</v>
+      </c>
+      <c r="K529" t="n">
+        <v>16315812</v>
+      </c>
+      <c r="L529" t="n">
+        <v>-5.77</v>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>NMDC Steel reports ₹50.51 crore profit in Q1 2026 - Business Upturn</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>NMDC Steel reports ₹50.51 crore profit in Q1 2026 - Business Upturn</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>NMDC Steel: Clarifies Stock Price Spurt Amidst Financial Results &amp; Rating Upgrade - investywise.com</t>
+        </is>
+      </c>
+      <c r="P529" t="inlineStr"/>
+      <c r="Q529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>9</v>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>AEROENTER.NS</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Aeroflex Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>147.4600067138672</v>
+      </c>
+      <c r="F530" t="n">
+        <v>149</v>
+      </c>
+      <c r="G530" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="H530" t="n">
+        <v>138.4499969482422</v>
+      </c>
+      <c r="I530" t="n">
+        <v>146.2899932861328</v>
+      </c>
+      <c r="J530" t="n">
+        <v>138.4499969482422</v>
+      </c>
+      <c r="K530" t="n">
+        <v>652969</v>
+      </c>
+      <c r="L530" t="n">
+        <v>-5.36</v>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>A Flex Invest raises Aeroflex Enterprises stake to 7.38% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>A Flex Invest raises Aeroflex Enterprises stake to 7.38% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr"/>
+      <c r="P530" t="inlineStr"/>
+      <c r="Q530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>10</v>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>ELITECON.NS</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Elitecon International Limited</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>10.64000034332275</v>
+      </c>
+      <c r="F531" t="n">
+        <v>10.64000034332275</v>
+      </c>
+      <c r="G531" t="n">
+        <v>10.64000034332275</v>
+      </c>
+      <c r="H531" t="n">
+        <v>10.64000034332275</v>
+      </c>
+      <c r="I531" t="n">
+        <v>11.19999980926514</v>
+      </c>
+      <c r="J531" t="n">
+        <v>10.64000034332275</v>
+      </c>
+      <c r="K531" t="n">
+        <v>689842</v>
+      </c>
+      <c r="L531" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>Elitecon appoints Vipin Sharma and Pradeep Kumar as Executive Directors - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>Elitecon appoints Vipin Sharma and Pradeep Kumar as Executive Directors - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>Elitecon International Ltd. Share Price Today - Elitecon International Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>Small-cap stock trades green despite tepid stock market trends - Livemint</t>
+        </is>
+      </c>
+      <c r="Q531" t="inlineStr">
+        <is>
+          <t>Elitecon International discontinues G Aakash &amp; Associates as secretarial auditor - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>11</v>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>VCL.NS</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Vaxtex Cotfab Limited</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>1.919999957084656</v>
+      </c>
+      <c r="F532" t="n">
+        <v>1.919999957084656</v>
+      </c>
+      <c r="G532" t="n">
+        <v>1.919999957084656</v>
+      </c>
+      <c r="H532" t="n">
+        <v>1.919999957084656</v>
+      </c>
+      <c r="I532" t="n">
+        <v>2.019999980926514</v>
+      </c>
+      <c r="J532" t="n">
+        <v>1.919999957084656</v>
+      </c>
+      <c r="K532" t="n">
+        <v>113928</v>
+      </c>
+      <c r="L532" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>SEBI slaps ₹33 crore fine on Varanium Cloud, eight others for diversion of IPO proceeds - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>SEBI slaps ₹33 crore fine on Varanium Cloud, eight others for diversion of IPO proceeds - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>Sebi bars Varanium Cloud, promoter for 7 years, orders ₹128.8 crore disgorgement - Livemint</t>
+        </is>
+      </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>Sebi fines Varanium Cloud, promoter Sabale and 7 others Rs 33.08 crore over fund diversion - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q532" t="inlineStr">
+        <is>
+          <t>Sebi Fines Varanium Cloud ₹33.08 Crore, Bars Promoter Harshawardhan Sabale From Markets For 7 Years - Free Press Journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>12</v>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>GVPTECH.NS</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>GVP Infotech Limited</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>9.369999885559082</v>
+      </c>
+      <c r="F533" t="n">
+        <v>9.390000343322754</v>
+      </c>
+      <c r="G533" t="n">
+        <v>8.319999694824219</v>
+      </c>
+      <c r="H533" t="n">
+        <v>8.590000152587891</v>
+      </c>
+      <c r="I533" t="n">
+        <v>9.029999732971191</v>
+      </c>
+      <c r="J533" t="n">
+        <v>8.590000152587891</v>
+      </c>
+      <c r="K533" t="n">
+        <v>623315</v>
+      </c>
+      <c r="L533" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>GVP Infotech Limited (GVPTECH.NS) Mar 2026 Earnings: Negative EPS Amid Modest Revenue - EPS Surprise History - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>GVP Infotech Limited (GVPTECH) Gains 1.47%; Near Key Resistance at ₹7.23 - IPO Entry Watch - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>GVP Infotech Limited (GVPTECH) Gains 1.47%; Near Key Resistance at ₹7.23 - IPO Entry Watch - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>GVP INFOTECH LIMITED Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="Q533" t="inlineStr">
+        <is>
+          <t>GVPTECH Stock Price and Chart — NSE:GVPTECH - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>13</v>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>PERSISTENT.NS</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Persistent Systems Limited</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>5855.5</v>
+      </c>
+      <c r="F534" t="n">
+        <v>5855.5</v>
+      </c>
+      <c r="G534" t="n">
+        <v>5593</v>
+      </c>
+      <c r="H534" t="n">
+        <v>5594.5</v>
+      </c>
+      <c r="I534" t="n">
+        <v>5875</v>
+      </c>
+      <c r="J534" t="n">
+        <v>5594.5</v>
+      </c>
+      <c r="K534" t="n">
+        <v>1111436</v>
+      </c>
+      <c r="L534" t="n">
+        <v>-4.77</v>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>Kaynes Tech, Wockhardt, Persistent Systems shares fall up to 5% as broader markets tumble. What lies ahead? - economictimes.indiatimes.com</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-31 — cnbctv:60b0ba8ff094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-31 — cnbctv:60b0ba8ff094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>Persistent Systems shares update on fundraising, stock slips 4% - Business Today</t>
+        </is>
+      </c>
+      <c r="Q534" t="inlineStr">
+        <is>
+          <t>Persistent Systems publishes 36th AGM notice in newspapers - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>14</v>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT.NS</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>GMR AIRPORTS LIMITED</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>97.84999847412109</v>
+      </c>
+      <c r="F535" t="n">
+        <v>98</v>
+      </c>
+      <c r="G535" t="n">
+        <v>93.62999725341797</v>
+      </c>
+      <c r="H535" t="n">
+        <v>93.62999725341797</v>
+      </c>
+      <c r="I535" t="n">
+        <v>98.30999755859375</v>
+      </c>
+      <c r="J535" t="n">
+        <v>93.62999725341797</v>
+      </c>
+      <c r="K535" t="n">
+        <v>59706242</v>
+      </c>
+      <c r="L535" t="n">
+        <v>-4.76</v>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>GMR Airports Releases Q3FY26 Conference Call Transcript Following Results - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>Will GMR Airports Share Benefit From Hyderabad Airport’s New Tariff Framework? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>Will GMR Airports Share Benefit From Hyderabad Airport’s New Tariff Framework? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>GMR Airports Urges Investors to Use SEBI Window to Demat Old Physical Shares - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>15</v>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>VAML.NS</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Vedanta Aluminium Metal Limited</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>451</v>
+      </c>
+      <c r="F536" t="n">
+        <v>452.3999938964844</v>
+      </c>
+      <c r="G536" t="n">
+        <v>432.1000061035156</v>
+      </c>
+      <c r="H536" t="n">
+        <v>435.1499938964844</v>
+      </c>
+      <c r="I536" t="n">
+        <v>456.1499938964844</v>
+      </c>
+      <c r="J536" t="n">
+        <v>435.1499938964844</v>
+      </c>
+      <c r="K536" t="n">
+        <v>18470616</v>
+      </c>
+      <c r="L536" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>Vedanta Aluminium share price target: Buy VAML stock for 21% upside, says MOFSL - Business Today</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>Vedanta Aluminium Metal Ltd. Share Price Today - Vedanta Aluminium Metal Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>Vedanta Aluminium shares slip 2% in weak market; India Ratings upgrades NCDs to IND AA+ - Upstox</t>
+        </is>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>Vedanta Aluminium shares may remain in focus after latest clarification; key details here - Upstox</t>
+        </is>
+      </c>
+      <c r="Q536" t="inlineStr">
+        <is>
+          <t>Vedanta Aluminium dividend: Did you check bank account? Anil Agarwal's company starts crediting stock rewards - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>16</v>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>VISL.NS</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Vedanta Iron and Steel Limited</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>38.68000030517578</v>
+      </c>
+      <c r="F537" t="n">
+        <v>39.09000015258789</v>
+      </c>
+      <c r="G537" t="n">
+        <v>36.66999816894531</v>
+      </c>
+      <c r="H537" t="n">
+        <v>36.83000183105469</v>
+      </c>
+      <c r="I537" t="n">
+        <v>38.59000015258789</v>
+      </c>
+      <c r="J537" t="n">
+        <v>36.83000183105469</v>
+      </c>
+      <c r="K537" t="n">
+        <v>30899916</v>
+      </c>
+      <c r="L537" t="n">
+        <v>-4.56</v>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>Vedanta Iron and Steel shares hit upper circuit for 3rd straight session post-Q1 results - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>Vedanta Iron And Steel,VEDL,visl Share Analysis,Vedanta Power,Buy ? Vedanta Iron &amp; Steel Target 2030 Fa Cup Final (Z7HpU44d6K) - Mshale</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>Vislink Posts Positive EBITDA for Second Straight Quarter - Stock Titan</t>
+        </is>
+      </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>Vislink CEO Mickey Miller Takes Investor Questions Aug. 19 - Stock Titan</t>
+        </is>
+      </c>
+      <c r="Q537" t="inlineStr">
+        <is>
+          <t>Vedanta Iron And Steel,VEDL,visl Share Analysis,Vedanta Power,Buy ? Vedanta Iron &amp; Steel Target 2030 Fa Cup Final (Z7HpU44d6K) - Mshale</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>17</v>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>ELIN.NS</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Elin Electronics Limited</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>103.8000030517578</v>
+      </c>
+      <c r="F538" t="n">
+        <v>104.379997253418</v>
+      </c>
+      <c r="G538" t="n">
+        <v>99.69999694824219</v>
+      </c>
+      <c r="H538" t="n">
+        <v>100.129997253418</v>
+      </c>
+      <c r="I538" t="n">
+        <v>104.879997253418</v>
+      </c>
+      <c r="J538" t="n">
+        <v>100.129997253418</v>
+      </c>
+      <c r="K538" t="n">
+        <v>148734</v>
+      </c>
+      <c r="L538" t="n">
+        <v>-4.53</v>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>Elin Electronics Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>Elin Electronics Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>Elin Electronics vs PG Electroplast: Which EMS Stock to Know - Univest</t>
+        </is>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>Elin Electronics Q1 Results: Net loss widens 128% YoY to ₹214 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q538" t="inlineStr">
+        <is>
+          <t>Elin Electronics Q1 Results: Earnings Call Recording Now Available - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>18</v>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>RAYMONDREL.NS</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Raymond Realty Limited</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>556</v>
+      </c>
+      <c r="F539" t="n">
+        <v>559</v>
+      </c>
+      <c r="G539" t="n">
+        <v>528.0499877929688</v>
+      </c>
+      <c r="H539" t="n">
+        <v>532.2000122070312</v>
+      </c>
+      <c r="I539" t="n">
+        <v>557.0499877929688</v>
+      </c>
+      <c r="J539" t="n">
+        <v>532.2000122070312</v>
+      </c>
+      <c r="K539" t="n">
+        <v>440418</v>
+      </c>
+      <c r="L539" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>Impressive Earnings May Not Tell The Whole Story For Raymond Realty (NSE:RAYMONDREL) - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>Stocks To Buy or Sell Today, July 16, 2026: Larsen &amp; Toubro, UCO Bank, and United Breweries Among Shares - LatestLY</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>RAYMONDREL Stock Price and Chart — NSE:RAYMONDREL - TradingView</t>
+        </is>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>Raymond Realty Limited Schedules Conference Call for Q4FY26 Results Discussion on May 6, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q539" t="inlineStr">
+        <is>
+          <t>How Did Raymond Realty Limited's (NSE:RAYMONDREL) 6.1% ROE Fare Against The Industry? - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>19</v>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>OMNI.NS</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Omnitech Engineering Limited</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>568.25</v>
+      </c>
+      <c r="F540" t="n">
+        <v>568.2999877929688</v>
+      </c>
+      <c r="G540" t="n">
+        <v>536.5499877929688</v>
+      </c>
+      <c r="H540" t="n">
+        <v>540.5</v>
+      </c>
+      <c r="I540" t="n">
+        <v>565.5499877929688</v>
+      </c>
+      <c r="J540" t="n">
+        <v>540.5</v>
+      </c>
+      <c r="K540" t="n">
+        <v>515003</v>
+      </c>
+      <c r="L540" t="n">
+        <v>-4.43</v>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>Omni-Lite Industries Stock Falls 2.18%: Aerospace Demand Risks and Growth Uncertainty Pressure TSXV:OML Sentiment - kalkine.ca</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>Omni Bridgeway (ASX:OBL) Shares Reflect Valuation Strain Despite Profitable FY 2026 - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>Omni Bridgeway raises US$1B; record cash proceeds reach A$350.5M - Stock Titan</t>
+        </is>
+      </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>Axis Income Plus Arbitrage Omni FoF Regular-IDCW (₹ 15.36) - NAV, Reviews &amp; asset allocation - The Economic Times</t>
+        </is>
+      </c>
+      <c r="Q540" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: Omni-Lite posts record Q2 2026 revenue as stock jumps 21% - Investing.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-08-31 23:12:02 IST</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>20</v>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>UCAL.NS</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>UCAL LIMITED</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>158.3000030517578</v>
+      </c>
+      <c r="F541" t="n">
+        <v>158.3000030517578</v>
+      </c>
+      <c r="G541" t="n">
+        <v>148.8999938964844</v>
+      </c>
+      <c r="H541" t="n">
+        <v>149.8899993896484</v>
+      </c>
+      <c r="I541" t="n">
+        <v>156.7299957275391</v>
+      </c>
+      <c r="J541" t="n">
+        <v>149.8899993896484</v>
+      </c>
+      <c r="K541" t="n">
+        <v>19165</v>
+      </c>
+      <c r="L541" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>Ucal holds 40th AGM on Sep 29; urges KYC updates for shareholders - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>Ucal holds 40th AGM on Sep 29; urges KYC updates for shareholders - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>UCAL Share Price Rises 10.34%: Technicals, Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>UCAL Ltd. Share Price Today: 9.08% Rise, Valuation Check - Univest</t>
+        </is>
+      </c>
+      <c r="Q541" t="inlineStr">
+        <is>
+          <t>Ucal Q1 net profit up 1,702% to ₹5.87 crore; appoints new CEO - scanx.trade</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q541"/>
+  <dimension ref="A1:Q561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32885,9 +32885,6 @@
           <t>Manali Petrochemicals Share Price - Live NSE: MANALIPETC Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
-      <c r="O522" t="inlineStr"/>
-      <c r="P522" t="inlineStr"/>
-      <c r="Q522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -33568,8 +33565,6 @@
           <t>TGB Banquets &amp; Hotels Sets AGM, Moves to Fully Digital Shareholder Communication - TipRanks</t>
         </is>
       </c>
-      <c r="P532" t="inlineStr"/>
-      <c r="Q532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -34112,8 +34107,6 @@
           <t>JSW Holdings Ltd. (JSWHL) Share Price Rises 5.14% Amid Mid Cap Rally - Univest</t>
         </is>
       </c>
-      <c r="P540" t="inlineStr"/>
-      <c r="Q540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -34181,6 +34174,1342 @@
       <c r="Q541" t="inlineStr">
         <is>
           <t>Rs.94 dividend declared after 25 years; share price jumps nearly 10% - Record date fixed | Do you own? - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:26:54 IST</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>1</v>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>SSWL.NS</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Steel Strips Wheels Limited</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>310</v>
+      </c>
+      <c r="F542" t="n">
+        <v>349.2999877929688</v>
+      </c>
+      <c r="G542" t="n">
+        <v>303.6000061035156</v>
+      </c>
+      <c r="H542" t="n">
+        <v>345.5499877929688</v>
+      </c>
+      <c r="I542" t="n">
+        <v>305.6499938964844</v>
+      </c>
+      <c r="J542" t="n">
+        <v>345.5499877929688</v>
+      </c>
+      <c r="K542" t="n">
+        <v>14730915</v>
+      </c>
+      <c r="L542" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>Steel Strips Wheels Ltd. Share Price Today Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>Steel Strips Wheels Ltd. Share Price Today Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr"/>
+      <c r="P542" t="inlineStr"/>
+      <c r="Q542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:26:54 IST</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>2</v>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>SGRL.NS</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Shree Ganesh Remedies Limited</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>610.4500122070312</v>
+      </c>
+      <c r="F543" t="n">
+        <v>700.0499877929688</v>
+      </c>
+      <c r="G543" t="n">
+        <v>610.4500122070312</v>
+      </c>
+      <c r="H543" t="n">
+        <v>685.0999755859375</v>
+      </c>
+      <c r="I543" t="n">
+        <v>606.7000122070312</v>
+      </c>
+      <c r="J543" t="n">
+        <v>685.0999755859375</v>
+      </c>
+      <c r="K543" t="n">
+        <v>116905</v>
+      </c>
+      <c r="L543" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>SGRL Stock Price and Chart — NSE:SGRL - TradingView</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>Shree Ganesh Remedies Share Price rises 17.45%: analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>Shree Ganesh Remedies Share Price rises 17.45%: analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P543" t="inlineStr"/>
+      <c r="Q543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:26:54 IST</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>3</v>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>AYMSYNTEX.NS</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>AYM Syntex Limited</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>275.8500061035156</v>
+      </c>
+      <c r="F544" t="n">
+        <v>306.8999938964844</v>
+      </c>
+      <c r="G544" t="n">
+        <v>271.25</v>
+      </c>
+      <c r="H544" t="n">
+        <v>300.8999938964844</v>
+      </c>
+      <c r="I544" t="n">
+        <v>280.4500122070312</v>
+      </c>
+      <c r="J544" t="n">
+        <v>300.8999938964844</v>
+      </c>
+      <c r="K544" t="n">
+        <v>376518</v>
+      </c>
+      <c r="L544" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>AYM Syntex Share Price Today: Textile Sector Comparison - Univest</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>AYM Syntex Says Surge in Share Volume Is Market Driven, Affirms SEBI Compliance - TipRanks</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>AYM Syntex appoints Vireshwar Joshi as President and Unit Head - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>AYM Syntex accepts Rasik Chauhan's resignation as President - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q544" t="inlineStr">
+        <is>
+          <t>MAPS Q2 2026 Earnings: EPS Misses Estimates But Shares Rise 2.03% - Earnings Stability Report - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:26:54 IST</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>4</v>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>YATRA.NS</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Yatra Online Limited</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="F545" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="G545" t="n">
+        <v>106.7099990844727</v>
+      </c>
+      <c r="H545" t="n">
+        <v>114.1600036621094</v>
+      </c>
+      <c r="I545" t="n">
+        <v>106.4199981689453</v>
+      </c>
+      <c r="J545" t="n">
+        <v>114.1600036621094</v>
+      </c>
+      <c r="K545" t="n">
+        <v>4596221</v>
+      </c>
+      <c r="L545" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>Yatra FY26 net profit rises 28.1% to INR 468.10 million - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>Yatra FY26 net profit rises 28.1% to INR 468.10 million - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>National Award-winning actress Manasi Parekh shares safety update from China amid Tibet flash floods as s - The Times of India</t>
+        </is>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>Yatra Online Share Price Rises 9%: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="Q545" t="inlineStr">
+        <is>
+          <t>Yatra Online (NASDAQ: YTRA) director granted 18,737 shares at $0 - Stock Titan</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:26:54 IST</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>5</v>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>ENGINERSIN.NS</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Engineers India Limited</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>263</v>
+      </c>
+      <c r="F546" t="n">
+        <v>289.6499938964844</v>
+      </c>
+      <c r="G546" t="n">
+        <v>260.4500122070312</v>
+      </c>
+      <c r="H546" t="n">
+        <v>280.6000061035156</v>
+      </c>
+      <c r="I546" t="n">
+        <v>261.8699951171875</v>
+      </c>
+      <c r="J546" t="n">
+        <v>280.6000061035156</v>
+      </c>
+      <c r="K546" t="n">
+        <v>46801017</v>
+      </c>
+      <c r="L546" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>Revenue Miss: Engineers India Limited Fell 15% Short Of Analyst Revenue Estimates And Analysts Have Been Revising Their Models - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>Engineers India 61st AGM on 18 Sept 2026; Record Date for Final Dividend Fixed as 24 Sept - PSU Connect</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>Engineers India Shares Detailed Profile of Interim CMD Praveen M. Khanooja - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>Does Engineers India (NSE:ENGINERSIN) Deserve A Spot On Your Watchlist? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q546" t="inlineStr">
+        <is>
+          <t>Engineers India 61st AGM on 18 Sept 2026; Record Date for Final Dividend Fixed as 24 Sept - PSU Connect</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:26:54 IST</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>6</v>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>TNPETRO.NS</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Tamilnadu PetroProducts Limited</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>121</v>
+      </c>
+      <c r="F547" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="G547" t="n">
+        <v>120.6100006103516</v>
+      </c>
+      <c r="H547" t="n">
+        <v>129.3999938964844</v>
+      </c>
+      <c r="I547" t="n">
+        <v>120.7699966430664</v>
+      </c>
+      <c r="J547" t="n">
+        <v>129.3999938964844</v>
+      </c>
+      <c r="K547" t="n">
+        <v>11370945</v>
+      </c>
+      <c r="L547" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>Tamilnadu Petroproducts Ltd. (TNPETRO) Share Price Rises 14.15% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>TGVSL Stock Price and Chart — NSE:TGVSL - TradingView</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>Tamilnadu Petroproducts Limited Approves Appointment of Mr. Sanket Balvantrao Waghe, as an Additional Director, Effective August 11, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>TGVSL Stock Price and Chart — NSE:TGVSL - TradingView</t>
+        </is>
+      </c>
+      <c r="Q547" t="inlineStr">
+        <is>
+          <t>Tamil Nadu Petro Products wins partial GST appeal, demand cut to ₹4.05 lakh - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:26:54 IST</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>7</v>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>EBGNG.NS</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>GNG Electronics Limited</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>621.4000244140625</v>
+      </c>
+      <c r="F548" t="n">
+        <v>669.0999755859375</v>
+      </c>
+      <c r="G548" t="n">
+        <v>606.2999877929688</v>
+      </c>
+      <c r="H548" t="n">
+        <v>653.0999755859375</v>
+      </c>
+      <c r="I548" t="n">
+        <v>612.5</v>
+      </c>
+      <c r="J548" t="n">
+        <v>653.0999755859375</v>
+      </c>
+      <c r="K548" t="n">
+        <v>1586361</v>
+      </c>
+      <c r="L548" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>GNG Electronics Limited (NSE: EBGNG) Stock Price, News &amp; Analysis - Kalkine</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>Should You Be Adding GNG Electronics (NSE:EBGNG) To Your Watchlist Today? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>Should You Be Adding GNG Electronics (NSE:EBGNG) To Your Watchlist Today? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P548" t="inlineStr"/>
+      <c r="Q548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:26:54 IST</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>8</v>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>SMLMAH.NS</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>SML Mahindra Limited</t>
+        </is>
+      </c>
+      <c r="E549" t="n">
+        <v>5268</v>
+      </c>
+      <c r="F549" t="n">
+        <v>5499</v>
+      </c>
+      <c r="G549" t="n">
+        <v>5169</v>
+      </c>
+      <c r="H549" t="n">
+        <v>5444.5</v>
+      </c>
+      <c r="I549" t="n">
+        <v>5108</v>
+      </c>
+      <c r="J549" t="n">
+        <v>5444.5</v>
+      </c>
+      <c r="K549" t="n">
+        <v>180842</v>
+      </c>
+      <c r="L549" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>Here's Why SML Mahindra (NSE:SMLMAH) Has Caught The Eye Of Investors - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>SML Isuzu Ltd. (SMLMAH) Share Price Hits 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>SMLMAH Stock Price and Chart — NSE:SMLMAH - TradingView</t>
+        </is>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>SML Isuzu Share Price - Live NSE: SMLMAH Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="Q549" t="inlineStr">
+        <is>
+          <t>Be Sure To Check Out SML Mahindra Limited (NSE:SMLMAH) Before It Goes Ex-Dividend - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:26:54 IST</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>9</v>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>RADHIKAJWE.NS</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Radhika Jeweltech Limited</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>67.15000152587891</v>
+      </c>
+      <c r="F550" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="G550" t="n">
+        <v>67.15000152587891</v>
+      </c>
+      <c r="H550" t="n">
+        <v>71.69999694824219</v>
+      </c>
+      <c r="I550" t="n">
+        <v>67.44999694824219</v>
+      </c>
+      <c r="J550" t="n">
+        <v>71.69999694824219</v>
+      </c>
+      <c r="K550" t="n">
+        <v>3589996</v>
+      </c>
+      <c r="L550" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>Here's Why Radhika Jeweltech (NSE:RADHIKAJWE) Has Caught The Eye Of Investors - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>Radhika Jeweltech Surges 13% as Strong Demand Lifts Shares Past Key Levels - Social Sentiment - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>Radhika Jeweltech Limited (RADHIKAJWE.NS) – Marginal Decline Amid Consolidation Near Key Support - Bullish Sentiment - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>Radhika Jeweltech (RADHIKAJWE.NS) Eases Marginally: Key Support and Resistance Levels in Focus - Factor Timing - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q550" t="inlineStr">
+        <is>
+          <t>RADHIKAJWE Stock Price and Chart — NSE:RADHIKAJWE - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:26:54 IST</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>10</v>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>BEPL.NS</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Bhansali Engineering Polymers Limited</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>122.3000030517578</v>
+      </c>
+      <c r="F551" t="n">
+        <v>128.8000030517578</v>
+      </c>
+      <c r="G551" t="n">
+        <v>122.0999984741211</v>
+      </c>
+      <c r="H551" t="n">
+        <v>128.0800018310547</v>
+      </c>
+      <c r="I551" t="n">
+        <v>121.0899963378906</v>
+      </c>
+      <c r="J551" t="n">
+        <v>128.0800018310547</v>
+      </c>
+      <c r="K551" t="n">
+        <v>2316057</v>
+      </c>
+      <c r="L551" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>Dividend Investors: Don't Be Too Quick To Buy Bhansali Engineering Polymers Limited (NSE:BEPL) For Its Upcoming Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>Hidden Gem Stock with a Debt-Free Balance Sheet, ₹200 Cr Capex and Specialty Polymer Push - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>BEPL confirms no encumbrance on promoter shares in FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>Bhansali Engineering Polymers (BEPL) Edges Higher Amid Consolidation: ₹99.42 Holds Above Key Support - Trend Following Picks - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q551" t="inlineStr">
+        <is>
+          <t>Bhansali Engineering Polymers Schedules Board Meeting for Q4FY26 Results on April 24, 2026 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:26:54 IST</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>11</v>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>AARNAV.NS</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Limited</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>32.38999938964844</v>
+      </c>
+      <c r="F552" t="n">
+        <v>33.63000106811523</v>
+      </c>
+      <c r="G552" t="n">
+        <v>31.22999954223633</v>
+      </c>
+      <c r="H552" t="n">
+        <v>33.63000106811523</v>
+      </c>
+      <c r="I552" t="n">
+        <v>32.02999877929688</v>
+      </c>
+      <c r="J552" t="n">
+        <v>33.63000106811523</v>
+      </c>
+      <c r="K552" t="n">
+        <v>37710</v>
+      </c>
+      <c r="L552" t="n">
+        <v>5</v>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+        </is>
+      </c>
+      <c r="P552" t="inlineStr"/>
+      <c r="Q552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:26:54 IST</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>12</v>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>KENNAMET.NS</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Kennametal India Limited</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>4415</v>
+      </c>
+      <c r="F553" t="n">
+        <v>4630</v>
+      </c>
+      <c r="G553" t="n">
+        <v>4364.10009765625</v>
+      </c>
+      <c r="H553" t="n">
+        <v>4614.39990234375</v>
+      </c>
+      <c r="I553" t="n">
+        <v>4396.10009765625</v>
+      </c>
+      <c r="J553" t="n">
+        <v>4614.39990234375</v>
+      </c>
+      <c r="K553" t="n">
+        <v>34422</v>
+      </c>
+      <c r="L553" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>Kennametal India Share Price: 52-week high and valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>Kennametal India Share Price: 52-week high and valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>Kennametal India Share Price at 52-week high, Rs 4,325.55 - Univest</t>
+        </is>
+      </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>Kennametal India Share Price Near 52-Week High Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q553" t="inlineStr">
+        <is>
+          <t>Kennametal India Share Price Today After Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:26:54 IST</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>13</v>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>SAILIFE.NS</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Sai Life Sciences Limited</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>1460.099975585938</v>
+      </c>
+      <c r="F554" t="n">
+        <v>1560</v>
+      </c>
+      <c r="G554" t="n">
+        <v>1460.099975585938</v>
+      </c>
+      <c r="H554" t="n">
+        <v>1532.099975585938</v>
+      </c>
+      <c r="I554" t="n">
+        <v>1459.699951171875</v>
+      </c>
+      <c r="J554" t="n">
+        <v>1532.099975585938</v>
+      </c>
+      <c r="K554" t="n">
+        <v>1980745</v>
+      </c>
+      <c r="L554" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>SAI LIFE SCIENCES LIMITED Share Price Hits One-Year High - Univest</t>
+        </is>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>Sai Life Sciences Publishes AGM Notice and E‑Voting Details - TipRanks</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>SAI LIFE SCIENCES LIMITED Share Price: New 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>SAI LIFE SCIENCES LIMITED Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q554" t="inlineStr">
+        <is>
+          <t>SAI LIFE SCIENCES LIMITED Stock Reaches New 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:26:54 IST</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>14</v>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>DEEDEV.NS</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>DEE Development Engineers Limited</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>580.2999877929688</v>
+      </c>
+      <c r="F555" t="n">
+        <v>619.25</v>
+      </c>
+      <c r="G555" t="n">
+        <v>580.2999877929688</v>
+      </c>
+      <c r="H555" t="n">
+        <v>618</v>
+      </c>
+      <c r="I555" t="n">
+        <v>590.2999877929688</v>
+      </c>
+      <c r="J555" t="n">
+        <v>618</v>
+      </c>
+      <c r="K555" t="n">
+        <v>257781</v>
+      </c>
+      <c r="L555" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>We Ran A Stock Scan For Earnings Growth And DEE Development Engineers (NSE:DEEDEV) Passed With Ease - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>DEE Development Order Book Hits ₹2,428 Crore in June Boosting Revenue Visibility - Sahi</t>
+        </is>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>DEE Development Order Book Hits ₹2,428 Crore in June Boosting Revenue Visibility - Sahi</t>
+        </is>
+      </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>Why DEE Development Engineers' shares skyrocketed over 11% on Monday, February 23 - Upstox</t>
+        </is>
+      </c>
+      <c r="Q555" t="inlineStr">
+        <is>
+          <t>DEE Development Engineers Limited Files SEBI Compliance Certificate for Q4 FY26 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:26:54 IST</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>15</v>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>JSL.NS</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Jindal Stainless Limited</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>700.5</v>
+      </c>
+      <c r="F556" t="n">
+        <v>738.6500244140625</v>
+      </c>
+      <c r="G556" t="n">
+        <v>700.5</v>
+      </c>
+      <c r="H556" t="n">
+        <v>733.75</v>
+      </c>
+      <c r="I556" t="n">
+        <v>702.1500244140625</v>
+      </c>
+      <c r="J556" t="n">
+        <v>733.75</v>
+      </c>
+      <c r="K556" t="n">
+        <v>715187</v>
+      </c>
+      <c r="L556" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>JSL Industries Ltd. Share Price Up 9.95%: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>JSL Industries Ltd. Share Price Up 9.95%: Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: JSL beats Q2 2026 estimates but shares fall - Investing.com</t>
+        </is>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>JSL Industries Share Price Today, JSL Industries Stock Price Live NSE/BSE Updates - The Economic Times</t>
+        </is>
+      </c>
+      <c r="Q556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:26:54 IST</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>16</v>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>WAKEFIT.NS</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Wakefit Innovations Limited</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>148.8300018310547</v>
+      </c>
+      <c r="F557" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="G557" t="n">
+        <v>146.1999969482422</v>
+      </c>
+      <c r="H557" t="n">
+        <v>153.1399993896484</v>
+      </c>
+      <c r="I557" t="n">
+        <v>146.7799987792969</v>
+      </c>
+      <c r="J557" t="n">
+        <v>153.1399993896484</v>
+      </c>
+      <c r="K557" t="n">
+        <v>1092706</v>
+      </c>
+      <c r="L557" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>Wakefit Innovations Share Price Today, Wakefit Innovations Stock Price Live NSE/BSE Updates - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>Wakefit Innovations alters MOA after shareholder approval - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>Wakefit Innovations uploads Q1 FY27 earnings call audio recording - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P557" t="inlineStr">
+        <is>
+          <t>Wakefit Innovations alters MOA after shareholder approval - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q557" t="inlineStr">
+        <is>
+          <t>Wakefit Inno Standalone June 2026 Net Sales at Rs 404.91 crore, up 16.65% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:26:54 IST</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>17</v>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>DHATRE.NS</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Dhatre Udyog Limited</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>4.260000228881836</v>
+      </c>
+      <c r="F558" t="n">
+        <v>4.519999980926514</v>
+      </c>
+      <c r="G558" t="n">
+        <v>4.170000076293945</v>
+      </c>
+      <c r="H558" t="n">
+        <v>4.440000057220459</v>
+      </c>
+      <c r="I558" t="n">
+        <v>4.260000228881836</v>
+      </c>
+      <c r="J558" t="n">
+        <v>4.440000057220459</v>
+      </c>
+      <c r="K558" t="n">
+        <v>16837</v>
+      </c>
+      <c r="L558" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>Dhatre Udyog Q1FY26 net profit hits ₹573 lakh on OCI surge - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>Dhatre Udyog Ltd. (DHATRE) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>Dhatre Udyog Q1 FY27 Results: Revenue and PAT Highlights - Univest</t>
+        </is>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>Dhatre Udyog reports standalone net loss of Rs 0.29 crore in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q558" t="inlineStr">
+        <is>
+          <t>Dhatre Udyog Ltd. (DHATRE) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:26:54 IST</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>18</v>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>BALAMINES.NS</t>
+        </is>
+      </c>
+  